--- a/engine/swdy_study/SWDY_Valuation_Model_05082026_public.xlsx
+++ b/engine/swdy_study/SWDY_Valuation_Model_05082026_public.xlsx
@@ -36,8 +36,8 @@
     <numFmt numFmtId="165" formatCode="0.0%;(0.0%);&quot;-&quot;"/>
     <numFmt numFmtId="166" formatCode="#,##0;(#,##0);&quot;-&quot;"/>
     <numFmt numFmtId="167" formatCode="#,##0.0;(#,##0.0);&quot;-&quot;"/>
-    <numFmt numFmtId="168" formatCode="0.000"/>
-    <numFmt numFmtId="169" formatCode="0.00x"/>
+    <numFmt numFmtId="168" formatCode="0.00x"/>
+    <numFmt numFmtId="169" formatCode="0.000"/>
     <numFmt numFmtId="170" formatCode="0.0000"/>
   </numFmts>
   <fonts count="11">
@@ -153,7 +153,7 @@
     <xf numFmtId="166" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="8" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -887,19 +887,19 @@
         <v>33024.2555</v>
       </c>
       <c r="E5" s="28" t="n">
-        <v>39246.399311</v>
+        <v>40132.12386118259</v>
       </c>
       <c r="F5" s="28" t="n">
-        <v>45954.88155356</v>
+        <v>47668.20777099267</v>
       </c>
       <c r="G5" s="28" t="n">
-        <v>53110.91465519</v>
+        <v>55385.17707040044</v>
       </c>
       <c r="H5" s="28" t="n">
-        <v>60174.99508932464</v>
+        <v>62760.37931810715</v>
       </c>
       <c r="I5" s="28" t="n">
-        <v>66999.80540275812</v>
+        <v>69681.59948157847</v>
       </c>
     </row>
     <row r="6">
@@ -1061,19 +1061,19 @@
         <v>70464.12212399999</v>
       </c>
       <c r="E14" s="29" t="n">
-        <v>85583.90990632106</v>
+        <v>87961.92034341724</v>
       </c>
       <c r="F14" s="29" t="n">
-        <v>103752.8664413939</v>
+        <v>107470.9017036169</v>
       </c>
       <c r="G14" s="29" t="n">
-        <v>125359.4887684642</v>
+        <v>129065.4508130986</v>
       </c>
       <c r="H14" s="29" t="n">
-        <v>150508.5713249746</v>
+        <v>152846.5474155039</v>
       </c>
       <c r="I14" s="29" t="n">
-        <v>179342.3587509482</v>
+        <v>178921.6539620425</v>
       </c>
     </row>
     <row r="15">
@@ -1108,19 +1108,19 @@
         <v>64641.27</v>
       </c>
       <c r="E16" s="28" t="n">
-        <v>73389.38854</v>
+        <v>83836.39605497415</v>
       </c>
       <c r="F16" s="28" t="n">
-        <v>83402.75220480001</v>
+        <v>93691.85401385502</v>
       </c>
       <c r="G16" s="28" t="n">
-        <v>94050.72076428002</v>
+        <v>101423.0250779308</v>
       </c>
       <c r="H16" s="28" t="n">
-        <v>104821.8387000624</v>
+        <v>109438.4849659704</v>
       </c>
       <c r="I16" s="28" t="n">
-        <v>116274.5460807185</v>
+        <v>117917.0842665484</v>
       </c>
     </row>
     <row r="17">
@@ -1139,19 +1139,19 @@
         <v>19789</v>
       </c>
       <c r="E17" s="29" t="n">
-        <v>18542.22920043165</v>
+        <v>27158.4765596999</v>
       </c>
       <c r="F17" s="29" t="n">
-        <v>15648.25602157406</v>
+        <v>23403.44199721687</v>
       </c>
       <c r="G17" s="29" t="n">
-        <v>10000.60978629734</v>
+        <v>15413.72612410572</v>
       </c>
       <c r="H17" s="29" t="n">
-        <v>435.9120783173039</v>
+        <v>4967.190504984501</v>
       </c>
       <c r="I17" s="29" t="n">
-        <v>-12789.33125879109</v>
+        <v>-7984.413161997869</v>
       </c>
     </row>
     <row r="18">
@@ -1318,19 +1318,19 @@
         <v>31601.6</v>
       </c>
       <c r="D5" s="28" t="n">
-        <v>35820.40329348</v>
+        <v>40976.20503287411</v>
       </c>
       <c r="E5" s="28" t="n">
-        <v>41591.50204188672</v>
+        <v>44697.79828930313</v>
       </c>
       <c r="F5" s="28" t="n">
-        <v>48218.57778731467</v>
+        <v>48531.38475177478</v>
       </c>
       <c r="G5" s="28" t="n">
-        <v>55190.97681120677</v>
+        <v>52710.1452280135</v>
       </c>
       <c r="H5" s="28" t="n">
-        <v>62535.48413123862</v>
+        <v>57182.60531240865</v>
       </c>
     </row>
     <row r="6">
@@ -1391,19 +1391,19 @@
         <v>-8765.700000000001</v>
       </c>
       <c r="D9" s="28" t="n">
-        <v>-9572.52894</v>
+        <v>-10935.18209412706</v>
       </c>
       <c r="E9" s="28" t="n">
-        <v>-10515.99919104</v>
+        <v>-11813.32072348607</v>
       </c>
       <c r="F9" s="28" t="n">
-        <v>-11449.652962608</v>
+        <v>-12347.15087905244</v>
       </c>
       <c r="G9" s="28" t="n">
-        <v>-11849.42524435488</v>
+        <v>-12371.30699615317</v>
       </c>
       <c r="H9" s="28" t="n">
-        <v>-12132.99611277063</v>
+        <v>-12304.39140172679</v>
       </c>
     </row>
     <row r="10">
@@ -1421,19 +1421,19 @@
         <v>-16840.00000000001</v>
       </c>
       <c r="D10" s="28" t="n">
-        <v>-8748.118539999996</v>
+        <v>-19195.12605497414</v>
       </c>
       <c r="E10" s="28" t="n">
-        <v>-10013.36366480001</v>
+        <v>-9855.45795888087</v>
       </c>
       <c r="F10" s="28" t="n">
-        <v>-10647.96855948001</v>
+        <v>-7731.171064075766</v>
       </c>
       <c r="G10" s="28" t="n">
-        <v>-10771.1179357824</v>
+        <v>-8015.459888039608</v>
       </c>
       <c r="H10" s="28" t="n">
-        <v>-11452.70738065611</v>
+        <v>-8478.599300578047</v>
       </c>
     </row>
     <row r="11">
@@ -1453,19 +1453,19 @@
         </is>
       </c>
       <c r="D11" s="28" t="n">
-        <v>24352.51362336</v>
+        <v>27861.66847494723</v>
       </c>
       <c r="E11" s="28" t="n">
-        <v>28337.98882005504</v>
+        <v>30315.42110672035</v>
       </c>
       <c r="F11" s="28" t="n">
-        <v>32943.71844475249</v>
+        <v>32925.90237909758</v>
       </c>
       <c r="G11" s="28" t="n">
-        <v>37804.22400073989</v>
+        <v>35785.53035967527</v>
       </c>
       <c r="H11" s="28" t="n">
-        <v>42920.4737489261</v>
+        <v>38849.57555561488</v>
       </c>
     </row>
     <row r="12">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D12" s="29" t="n">
-        <v>9382.251272360005</v>
+        <v>1558.674058790493</v>
       </c>
       <c r="E12" s="29" t="n">
-        <v>11616.14291269503</v>
+        <v>12923.87923802941</v>
       </c>
       <c r="F12" s="29" t="n">
-        <v>15139.71678364249</v>
+        <v>17477.76201561404</v>
       </c>
       <c r="G12" s="29" t="n">
-        <v>19969.02563082285</v>
+        <v>20394.86822392896</v>
       </c>
       <c r="H12" s="29" t="n">
-        <v>24642.95605483652</v>
+        <v>23449.75609156551</v>
       </c>
       <c r="I12" s="14" t="n"/>
     </row>
@@ -1628,19 +1628,19 @@
         <v>281049</v>
       </c>
       <c r="E5" s="28" t="n">
-        <v>319084.298</v>
+        <v>364506.0698042354</v>
       </c>
       <c r="F5" s="28" t="n">
-        <v>362620.66176</v>
+        <v>407355.8870167609</v>
       </c>
       <c r="G5" s="28" t="n">
-        <v>408916.1772360001</v>
+        <v>440969.6742518729</v>
       </c>
       <c r="H5" s="28" t="n">
-        <v>455747.1247828801</v>
+        <v>475819.4998520451</v>
       </c>
       <c r="I5" s="28" t="n">
-        <v>505541.5046987762</v>
+        <v>512682.9750719497</v>
       </c>
     </row>
     <row r="6">
@@ -1661,19 +1661,19 @@
         <v>0.2115131445656513</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>0.1353333333333333</v>
+        <v>0.29694846736418</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>0.1364415736934823</v>
+        <v>0.1175558399769276</v>
       </c>
       <c r="G6" s="10" t="n">
-        <v>0.1276692708333333</v>
+        <v>0.08251700369738102</v>
       </c>
       <c r="H6" s="10" t="n">
-        <v>0.1145245655562612</v>
+        <v>0.07902998241159476</v>
       </c>
       <c r="I6" s="10" t="n">
-        <v>0.1092587911325131</v>
+        <v>0.077473653835892</v>
       </c>
     </row>
     <row r="7">
@@ -1689,22 +1689,22 @@
         <v>31601.6</v>
       </c>
       <c r="D7" s="28" t="n">
-        <v>30915.39</v>
+        <v>30622.08783333333</v>
       </c>
       <c r="E7" s="28" t="n">
-        <v>35820.40329348</v>
+        <v>40976.20503287411</v>
       </c>
       <c r="F7" s="28" t="n">
-        <v>41591.50204188672</v>
+        <v>44697.79828930313</v>
       </c>
       <c r="G7" s="28" t="n">
-        <v>48218.57778731467</v>
+        <v>48531.38475177478</v>
       </c>
       <c r="H7" s="28" t="n">
-        <v>55190.97681120677</v>
+        <v>52710.1452280135</v>
       </c>
       <c r="I7" s="28" t="n">
-        <v>62535.48413123862</v>
+        <v>57182.60531240865</v>
       </c>
     </row>
     <row r="8">
@@ -1720,22 +1720,22 @@
         <v>0.1362244796790093</v>
       </c>
       <c r="D8" s="10" t="n">
-        <v>0.11</v>
+        <v>0.1089564020271673</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>0.11226</v>
+        <v>0.112415700114078</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>0.114697</v>
+        <v>0.1097266535575169</v>
       </c>
       <c r="G8" s="10" t="n">
-        <v>0.117918</v>
+        <v>0.1100560596011748</v>
       </c>
       <c r="H8" s="10" t="n">
-        <v>0.1211</v>
+        <v>0.1107776063074413</v>
       </c>
       <c r="I8" s="10" t="n">
-        <v>0.1237</v>
+        <v>0.1115359941577613</v>
       </c>
     </row>
     <row r="9">
@@ -1751,22 +1751,22 @@
         <v>29341.7</v>
       </c>
       <c r="D9" s="28" t="n">
-        <v>27964.3755</v>
+        <v>27671.07333333333</v>
       </c>
       <c r="E9" s="28" t="n">
-        <v>32470.01816448</v>
+        <v>37148.89129992964</v>
       </c>
       <c r="F9" s="28" t="n">
-        <v>37783.98509340672</v>
+        <v>40420.56147562714</v>
       </c>
       <c r="G9" s="28" t="n">
-        <v>43924.95792633666</v>
+        <v>43901.20317213011</v>
       </c>
       <c r="H9" s="28" t="n">
-        <v>50405.63200098653</v>
+        <v>47714.04047956703</v>
       </c>
       <c r="I9" s="28" t="n">
-        <v>57227.29833190147</v>
+        <v>51799.43407415318</v>
       </c>
     </row>
     <row r="10">
@@ -1785,19 +1785,19 @@
         <v>17330</v>
       </c>
       <c r="E10" s="28" t="n">
-        <v>20159.71704309476</v>
+        <v>23330.39762588968</v>
       </c>
       <c r="F10" s="28" t="n">
-        <v>24225.27538009706</v>
+        <v>26011.97514693281</v>
       </c>
       <c r="G10" s="28" t="n">
-        <v>28808.82976942713</v>
+        <v>28792.73214597563</v>
       </c>
       <c r="H10" s="28" t="n">
-        <v>33532.11007534728</v>
+        <v>31708.12880320703</v>
       </c>
       <c r="I10" s="28" t="n">
-        <v>38445.04990129814</v>
+        <v>34766.80872871818</v>
       </c>
     </row>
     <row r="11">
@@ -1822,19 +1822,19 @@
         </is>
       </c>
       <c r="E11" s="28" t="n">
-        <v>9382.251272360005</v>
+        <v>1558.674058790493</v>
       </c>
       <c r="F11" s="28" t="n">
-        <v>11616.14291269503</v>
+        <v>12923.87923802941</v>
       </c>
       <c r="G11" s="28" t="n">
-        <v>15139.71678364249</v>
+        <v>17477.76201561404</v>
       </c>
       <c r="H11" s="28" t="n">
-        <v>19969.02563082285</v>
+        <v>20394.86822392896</v>
       </c>
       <c r="I11" s="28" t="n">
-        <v>24642.95605483652</v>
+        <v>23449.75609156551</v>
       </c>
     </row>
     <row r="12">
@@ -1853,19 +1853,19 @@
         <v>19789</v>
       </c>
       <c r="E12" s="28" t="n">
-        <v>18542.22920043165</v>
+        <v>27158.4765596999</v>
       </c>
       <c r="F12" s="28" t="n">
-        <v>15648.25602157406</v>
+        <v>23403.44199721687</v>
       </c>
       <c r="G12" s="28" t="n">
-        <v>10000.60978629734</v>
+        <v>15413.72612410572</v>
       </c>
       <c r="H12" s="28" t="n">
-        <v>435.9120783173039</v>
+        <v>4967.190504984501</v>
       </c>
       <c r="I12" s="28" t="n">
-        <v>-12789.33125879109</v>
+        <v>-7984.413161997869</v>
       </c>
     </row>
     <row r="13">
@@ -1890,19 +1890,19 @@
         </is>
       </c>
       <c r="E13" s="28" t="n">
-        <v>114094.987851</v>
+        <v>125427.7199161567</v>
       </c>
       <c r="F13" s="28" t="n">
-        <v>130816.83375836</v>
+        <v>142819.2617848477</v>
       </c>
       <c r="G13" s="28" t="n">
-        <v>148620.83541947</v>
+        <v>158267.4021483312</v>
       </c>
       <c r="H13" s="28" t="n">
-        <v>166456.0337893871</v>
+        <v>173658.0642840776</v>
       </c>
       <c r="I13" s="28" t="n">
-        <v>184733.5514834767</v>
+        <v>189057.8837481269</v>
       </c>
     </row>
     <row r="14">
@@ -1927,19 +1927,19 @@
         </is>
       </c>
       <c r="E14" s="10" t="n">
-        <v>0.213440696055489</v>
+        <v>0.2221332612405902</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>0.2166234115740786</v>
+        <v>0.2122642333244201</v>
       </c>
       <c r="G14" s="10" t="n">
-        <v>0.2216628533393152</v>
+        <v>0.2080396969442817</v>
       </c>
       <c r="H14" s="10" t="n">
-        <v>0.2271123679936571</v>
+        <v>0.2060689234744418</v>
       </c>
       <c r="I14" s="10" t="n">
-        <v>0.2323371872854677</v>
+        <v>0.2054903756744277</v>
       </c>
     </row>
   </sheetData>
@@ -2284,19 +2284,19 @@
         </is>
       </c>
       <c r="B6" s="9" t="n">
-        <v>79.68123670415163</v>
+        <v>70.33785026611987</v>
       </c>
       <c r="C6" s="9" t="n">
-        <v>84.01149521077141</v>
+        <v>73.67916459076592</v>
       </c>
       <c r="D6" s="9" t="n">
-        <v>89.32569292537724</v>
+        <v>77.75959437327495</v>
       </c>
       <c r="E6" s="9" t="n">
-        <v>96.03719178942801</v>
+        <v>82.88964883834787</v>
       </c>
       <c r="F6" s="9" t="n">
-        <v>104.8286010601025</v>
+        <v>89.58209041029527</v>
       </c>
     </row>
     <row r="7">
@@ -2306,19 +2306,19 @@
         </is>
       </c>
       <c r="B7" s="9" t="n">
-        <v>72.04339267486468</v>
+        <v>63.5344468678846</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>75.27674949702067</v>
+        <v>65.96239254313653</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>79.14809516564586</v>
+        <v>68.85048182392777</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>83.8925318229104</v>
+        <v>72.36827997455242</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>89.87685305037411</v>
+        <v>76.78033350243246</v>
       </c>
     </row>
     <row r="8">
@@ -2328,19 +2328,19 @@
         </is>
       </c>
       <c r="B8" s="9" t="n">
-        <v>65.67571614885223</v>
+        <v>57.85893383172429</v>
       </c>
       <c r="C8" s="9" t="n">
-        <v>68.12091433767503</v>
+        <v>59.63644342622118</v>
       </c>
       <c r="D8" s="9" t="n">
-        <v>70.9872231444748</v>
+        <v>61.70195167480045</v>
       </c>
       <c r="E8" s="9" t="n">
-        <v>74.41284756366471</v>
+        <v>64.14997733495557</v>
       </c>
       <c r="F8" s="9" t="n">
-        <v>78.60389824960801</v>
+        <v>67.12148002279349</v>
       </c>
     </row>
     <row r="9">
@@ -2350,19 +2350,19 @@
         </is>
       </c>
       <c r="B9" s="9" t="n">
-        <v>60.2877965249138</v>
+        <v>53.05352385509302</v>
       </c>
       <c r="C9" s="9" t="n">
-        <v>62.15344207203882</v>
+        <v>54.35740254637418</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>64.2996613922935</v>
+        <v>55.83973620233307</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>66.80945629214551</v>
+        <v>57.55331694347389</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>69.80214924602792</v>
+        <v>59.57403813546187</v>
       </c>
     </row>
     <row r="10">
@@ -2372,19 +2372,19 @@
         </is>
       </c>
       <c r="B10" s="9" t="n">
-        <v>55.67138867590096</v>
+        <v>48.93336177056653</v>
       </c>
       <c r="C10" s="9" t="n">
-        <v>57.10268104309385</v>
+        <v>49.88605070421014</v>
       </c>
       <c r="D10" s="9" t="n">
-        <v>58.72104435657906</v>
+        <v>50.94582955927424</v>
       </c>
       <c r="E10" s="9" t="n">
-        <v>60.57685226673597</v>
+        <v>52.14153504379775</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>62.74034772692379</v>
+        <v>53.51337817132742</v>
       </c>
     </row>
     <row r="12">
@@ -2429,19 +2429,19 @@
         </is>
       </c>
       <c r="B14" s="9" t="n">
-        <v>94.4411516960047</v>
+        <v>82.30413193593803</v>
       </c>
       <c r="C14" s="9" t="n">
-        <v>91.83793386263895</v>
+        <v>79.99134516193502</v>
       </c>
       <c r="D14" s="9" t="n">
-        <v>89.32569292537724</v>
+        <v>77.75959437327495</v>
       </c>
       <c r="E14" s="9" t="n">
-        <v>86.90043531192872</v>
+        <v>75.60531904976452</v>
       </c>
       <c r="F14" s="9" t="n">
-        <v>84.55837936054179</v>
+        <v>73.52514768373331</v>
       </c>
     </row>
     <row r="15">
@@ -2451,19 +2451,19 @@
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>83.6853102993899</v>
+        <v>72.8886819346058</v>
       </c>
       <c r="C15" s="9" t="n">
-        <v>81.3764819233737</v>
+        <v>70.83367768088289</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>79.14809516564586</v>
+        <v>68.85048182392777</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>76.99662618872641</v>
+        <v>66.9359453582495</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>74.91873786045032</v>
+        <v>65.08708620594727</v>
       </c>
     </row>
     <row r="16">
@@ -2473,19 +2473,19 @@
         </is>
       </c>
       <c r="B16" s="9" t="n">
-        <v>75.06101753174484</v>
+        <v>65.33406077050365</v>
       </c>
       <c r="C16" s="9" t="n">
-        <v>72.98811919556634</v>
+        <v>63.48580082611725</v>
       </c>
       <c r="D16" s="9" t="n">
-        <v>70.9872231444748</v>
+        <v>61.70195167480045</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>69.05518167214285</v>
+        <v>59.97969409530537</v>
       </c>
       <c r="F16" s="9" t="n">
-        <v>67.18901360200252</v>
+        <v>58.31635810092311</v>
       </c>
     </row>
     <row r="17">
@@ -2495,19 +2495,19 @@
         </is>
       </c>
       <c r="B17" s="9" t="n">
-        <v>67.99391096892251</v>
+        <v>59.13899137370171</v>
       </c>
       <c r="C17" s="9" t="n">
-        <v>66.11423924782518</v>
+        <v>57.46018877233019</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>64.2996613922935</v>
+        <v>55.83973620233307</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>62.54733746305856</v>
+        <v>54.27508452482181</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>60.85457754823204</v>
+        <v>52.76381935034907</v>
       </c>
     </row>
     <row r="18">
@@ -2517,19 +2517,19 @@
         </is>
       </c>
       <c r="B18" s="9" t="n">
-        <v>62.09887513361004</v>
+        <v>53.96735779694362</v>
       </c>
       <c r="C18" s="9" t="n">
-        <v>60.38029098876037</v>
+        <v>52.42994594952477</v>
       </c>
       <c r="D18" s="9" t="n">
-        <v>58.72104435657906</v>
+        <v>50.94582955927424</v>
       </c>
       <c r="E18" s="9" t="n">
-        <v>57.1185516233497</v>
+        <v>49.51268463786545</v>
       </c>
       <c r="F18" s="9" t="n">
-        <v>55.57036546404807</v>
+        <v>48.12830987545653</v>
       </c>
     </row>
     <row r="20">
@@ -2575,25 +2575,25 @@
         </is>
       </c>
       <c r="B22" s="9" t="n">
-        <v>97.22796869406002</v>
+        <v>84.75563520629989</v>
       </c>
       <c r="C22" s="9" t="n">
-        <v>82.76416632907222</v>
+        <v>72.055512422107</v>
       </c>
       <c r="D22" s="9" t="n">
-        <v>71.43883974103514</v>
+        <v>62.0992379086121</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>70.9872231444748</v>
+        <v>61.70195167480045</v>
       </c>
       <c r="F22" s="9" t="n">
-        <v>64.45290812234732</v>
+        <v>55.95111872909561</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>58.46543295327148</v>
+        <v>50.67676982890725</v>
       </c>
       <c r="H22" s="9" t="n">
-        <v>38.76253574078854</v>
+        <v>34.07886537739263</v>
       </c>
     </row>
     <row r="23">
@@ -2603,22 +2603,22 @@
         </is>
       </c>
       <c r="B23" s="9" t="n">
-        <v>65.21795282222483</v>
+        <v>56.86120849951797</v>
       </c>
       <c r="C23" s="9" t="n">
-        <v>68.10258798334984</v>
+        <v>59.28158008715921</v>
       </c>
       <c r="D23" s="9" t="n">
-        <v>70.9872231444748</v>
+        <v>61.70195167480045</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>75.60263940227475</v>
+        <v>65.57454621502646</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>82.52576378897464</v>
+        <v>71.38343802536546</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>17.30781096674981</v>
+        <v>14.52222952584749</v>
       </c>
     </row>
     <row r="24">
@@ -2628,22 +2628,22 @@
         </is>
       </c>
       <c r="B24" s="9" t="n">
-        <v>50.76974883395968</v>
+        <v>40.70537584468816</v>
       </c>
       <c r="C24" s="9" t="n">
-        <v>60.87848598921724</v>
+        <v>51.20366375974433</v>
       </c>
       <c r="D24" s="9" t="n">
-        <v>70.9872231444748</v>
+        <v>61.70195167480045</v>
       </c>
       <c r="E24" s="9" t="n">
-        <v>81.09596029973233</v>
+        <v>72.20023958985661</v>
       </c>
       <c r="F24" s="9" t="n">
-        <v>91.20469745498988</v>
+        <v>82.69852750491278</v>
       </c>
       <c r="H24" s="9" t="n">
-        <v>40.4349486210302</v>
+        <v>41.99315166022461</v>
       </c>
     </row>
     <row r="25">
@@ -2653,22 +2653,22 @@
         </is>
       </c>
       <c r="B25" s="9" t="n">
-        <v>72.55623902138905</v>
+        <v>63.49802109023506</v>
       </c>
       <c r="C25" s="9" t="n">
-        <v>71.77173108293192</v>
+        <v>62.59998638251776</v>
       </c>
       <c r="D25" s="9" t="n">
-        <v>70.9872231444748</v>
+        <v>61.70195167480045</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>70.20271520601769</v>
+        <v>60.80391696708316</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>69.41820726756056</v>
+        <v>59.90588225936586</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>3.138031753828486</v>
+        <v>3.592138830869196</v>
       </c>
     </row>
     <row r="26">
@@ -2678,22 +2678,22 @@
         </is>
       </c>
       <c r="B26" s="9" t="n">
-        <v>62.17907809677004</v>
+        <v>55.62682821155775</v>
       </c>
       <c r="C26" s="9" t="n">
-        <v>66.32151505438871</v>
+        <v>59.37636551887614</v>
       </c>
       <c r="D26" s="9" t="n">
-        <v>70.9872231444748</v>
+        <v>61.70195167480045</v>
       </c>
       <c r="E26" s="9" t="n">
-        <v>72.69449498918665</v>
+        <v>65.14488445321211</v>
       </c>
       <c r="F26" s="9" t="n">
-        <v>74.60638896962602</v>
+        <v>66.87544013351288</v>
       </c>
       <c r="H26" s="9" t="n">
-        <v>12.42731087285598</v>
+        <v>11.24861192195513</v>
       </c>
     </row>
   </sheetData>
@@ -2806,19 +2806,19 @@
         <v>8.095188293136117</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>9.417005504916174</v>
+        <v>10.89809357964875</v>
       </c>
       <c r="F5" s="9" t="n">
-        <v>11.31610880871092</v>
+        <v>12.15071186905933</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v>13.45717838940668</v>
+        <v>13.44965886875394</v>
       </c>
       <c r="H5" s="9" t="n">
-        <v>15.66351672972319</v>
+        <v>14.81149873542837</v>
       </c>
       <c r="I5" s="9" t="n">
-        <v>17.95844881073413</v>
+        <v>16.24026907157657</v>
       </c>
     </row>
     <row r="6">
@@ -2837,19 +2837,19 @@
         <v>32.91519541282852</v>
       </c>
       <c r="E6" s="9" t="n">
-        <v>39.97794954151566</v>
+        <v>41.08876559756508</v>
       </c>
       <c r="F6" s="9" t="n">
-        <v>48.46503114804884</v>
+        <v>50.20179949935957</v>
       </c>
       <c r="G6" s="9" t="n">
-        <v>58.55791494010386</v>
+        <v>60.28904365092503</v>
       </c>
       <c r="H6" s="9" t="n">
-        <v>70.30555248739624</v>
+        <v>71.39766770249631</v>
       </c>
       <c r="I6" s="9" t="n">
-        <v>83.77438909544684</v>
+        <v>83.57786950617874</v>
       </c>
     </row>
     <row r="7">
@@ -2874,19 +2874,19 @@
         </is>
       </c>
       <c r="E7" s="9" t="n">
-        <v>4.382636506824589</v>
+        <v>0.7280877088018324</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>5.42613180139901</v>
+        <v>6.037001495072163</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>7.072063362281535</v>
+        <v>8.16421087472694</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>9.327929746795855</v>
+        <v>9.526849306774581</v>
       </c>
       <c r="I7" s="9" t="n">
-        <v>11.51121577399771</v>
+        <v>10.95384829713436</v>
       </c>
     </row>
     <row r="8">
@@ -2943,22 +2943,22 @@
         <v>0.1362244796790093</v>
       </c>
       <c r="D9" s="10" t="n">
-        <v>0.11</v>
+        <v>0.1089564020271673</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>0.11226</v>
+        <v>0.112415700114078</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>0.114697</v>
+        <v>0.1097266535575169</v>
       </c>
       <c r="G9" s="10" t="n">
-        <v>0.117918</v>
+        <v>0.1100560596011748</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>0.1211</v>
+        <v>0.1107776063074413</v>
       </c>
       <c r="I9" s="10" t="n">
-        <v>0.1237</v>
+        <v>0.1115359941577613</v>
       </c>
     </row>
     <row r="10">
@@ -2974,22 +2974,22 @@
         <v>0.126482767182598</v>
       </c>
       <c r="D10" s="10" t="n">
-        <v>0.09949999999999999</v>
+        <v>0.09845640202716727</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>0.10176</v>
+        <v>0.101915700114078</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>0.104197</v>
+        <v>0.09922665355751691</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>0.107418</v>
+        <v>0.09955605960117482</v>
       </c>
       <c r="H10" s="10" t="n">
-        <v>0.1106</v>
+        <v>0.1002776063074413</v>
       </c>
       <c r="I10" s="10" t="n">
-        <v>0.1132</v>
+        <v>0.1010359941577613</v>
       </c>
     </row>
     <row r="11">
@@ -3008,19 +3008,19 @@
         <v>0.06166184544332127</v>
       </c>
       <c r="E11" s="10" t="n">
-        <v>0.06317990941407826</v>
+        <v>0.06400551200263878</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>0.06680610879291407</v>
+        <v>0.06385565049134183</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>0.07045167536328729</v>
+        <v>0.06529413206208327</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>0.0735761308232545</v>
+        <v>0.06663898560917868</v>
       </c>
       <c r="I11" s="10" t="n">
-        <v>0.07604726722528032</v>
+        <v>0.0678134644978976</v>
       </c>
     </row>
     <row r="12">
@@ -3041,19 +3041,19 @@
         <v>0.2756503065994848</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>0.2355549900111049</v>
+        <v>0.2652329273258715</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>0.233490179221034</v>
+        <v>0.242037376951285</v>
       </c>
       <c r="G12" s="10" t="n">
-        <v>0.2298097260322775</v>
+        <v>0.223086286566889</v>
       </c>
       <c r="H12" s="10" t="n">
-        <v>0.2227920295844515</v>
+        <v>0.2074507363062016</v>
       </c>
       <c r="I12" s="10" t="n">
-        <v>0.214366813111266</v>
+        <v>0.1943130300823947</v>
       </c>
     </row>
     <row r="13">
@@ -3069,22 +3069,22 @@
         <v>0.2486105500867294</v>
       </c>
       <c r="D13" s="10" t="n">
-        <v>0.2091856009334676</v>
+        <v>0.2093655734764178</v>
       </c>
       <c r="E13" s="10" t="n">
-        <v>0.213440696055489</v>
+        <v>0.2221332612405902</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>0.2166234115740786</v>
+        <v>0.2122642333244201</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>0.2216628533393152</v>
+        <v>0.2080396969442817</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>0.2271123679936571</v>
+        <v>0.2060689234744418</v>
       </c>
       <c r="I13" s="10" t="n">
-        <v>0.2323371872854677</v>
+        <v>0.2054903756744277</v>
       </c>
     </row>
     <row r="14">
@@ -3100,22 +3100,22 @@
         <v>0.6337653789681534</v>
       </c>
       <c r="D14" s="32" t="n">
-        <v>0.6401019039384591</v>
+        <v>0.6462328796032941</v>
       </c>
       <c r="E14" s="32" t="n">
-        <v>0.5176443449983907</v>
+        <v>0.6627865254459602</v>
       </c>
       <c r="F14" s="32" t="n">
-        <v>0.3762368573708816</v>
+        <v>0.5235927247633061</v>
       </c>
       <c r="G14" s="32" t="n">
-        <v>0.2074015917766928</v>
+        <v>0.3176032623619305</v>
       </c>
       <c r="H14" s="32" t="n">
-        <v>0.007898249016473107</v>
+        <v>0.09423594800388868</v>
       </c>
       <c r="I14" s="32" t="n">
-        <v>-0.2045131885754824</v>
+        <v>-0.1396301046161891</v>
       </c>
     </row>
     <row r="15">
@@ -3133,7 +3133,7 @@
         <v>8.346617739090858</v>
       </c>
       <c r="D15" s="32" t="n">
-        <v>8.224816323529412</v>
+        <v>8.138550980392157</v>
       </c>
       <c r="E15" s="32" t="inlineStr">
         <is>
@@ -3238,7 +3238,7 @@
         <v>0.3172037113507076</v>
       </c>
       <c r="D18" s="10" t="n">
-        <v>0.2643034737032398</v>
+        <v>0.2640762760437433</v>
       </c>
       <c r="E18" s="10" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
         <v>0.07886018916845154</v>
       </c>
       <c r="D19" s="10" t="n">
-        <v>0.05528848097541516</v>
+        <v>0.05528848097541515</v>
       </c>
       <c r="E19" s="10" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Terminal growth reconciliation: actual NOPAT compound growth FY2023–FY2025 was 30.4%; the implied growth from stable years only (FY2024 excluded as a debt-funded capacity burst) is 5.1%; the adopted terminal growth is 5.0%, below the blended nominal ceiling of 9.6%.</t>
+          <t>Terminal growth reconciliation: actual NOPAT compound growth FY2023–FY2025 was 30.5%; the implied growth from stable years only (FY2024 excluded as a debt-funded capacity burst) is 5.1%; the adopted terminal growth is 5.0%, below the blended nominal ceiling of 10.5%.</t>
         </is>
       </c>
     </row>
@@ -3484,7 +3484,7 @@
         </is>
       </c>
       <c r="B11" s="32" t="n">
-        <v>7.924817786713997</v>
+        <v>8.000722677325394</v>
       </c>
     </row>
     <row r="12">
@@ -3614,13 +3614,13 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>40.56529733053896</v>
+        <v>33.91940897889238</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>70.98722314447478</v>
+        <v>61.70195167480045</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>129.3657551944428</v>
+        <v>115.429420600699</v>
       </c>
       <c r="E5" s="8" t="n">
         <v>0.45</v>
@@ -3641,13 +3641,13 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>91.33860936168992</v>
+        <v>98.54941705689527</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>108.8928867560292</v>
+        <v>117.4147503958174</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>135.2243028475382</v>
+        <v>145.7127504042006</v>
       </c>
       <c r="E6" s="8" t="n">
         <v>0.2</v>
@@ -3668,13 +3668,13 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>82.45205242479992</v>
+        <v>84.26500301112208</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>106.0097816890285</v>
+        <v>108.340718157157</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>135.4569432693142</v>
+        <v>138.4353620897006</v>
       </c>
       <c r="E7" s="8" t="n">
         <v>0.2</v>
@@ -3859,7 +3859,7 @@
         </is>
       </c>
       <c r="C21" s="17" t="n">
-        <v>30915.39</v>
+        <v>30622.08783333333</v>
       </c>
     </row>
     <row r="22">
@@ -3981,7 +3981,7 @@
         </is>
       </c>
       <c r="C6" s="9" t="n">
-        <v>40.56529733053896</v>
+        <v>33.91940897889238</v>
       </c>
     </row>
     <row r="7">
@@ -3996,7 +3996,7 @@
         </is>
       </c>
       <c r="C7" s="9" t="n">
-        <v>129.3657551944428</v>
+        <v>115.429420600699</v>
       </c>
     </row>
     <row r="8">
@@ -4073,7 +4073,7 @@
         </is>
       </c>
       <c r="C15" s="8" t="n">
-        <v>0.7242520484138188</v>
+        <v>0.6026295957756825</v>
       </c>
     </row>
     <row r="16">
@@ -4105,7 +4105,7 @@
         </is>
       </c>
       <c r="C18" s="22" t="n">
-        <v>134.4043758858767</v>
+        <v>108.2656760498812</v>
       </c>
     </row>
     <row r="19">
@@ -4164,13 +4164,13 @@
         </is>
       </c>
       <c r="C23" s="9" t="n">
-        <v>126.9269548097662</v>
+        <v>137.2890386682185</v>
       </c>
       <c r="D23" s="9" t="n">
-        <v>93.52512459666983</v>
+        <v>101.1603442818452</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>160.3287850228626</v>
+        <v>173.4177330545918</v>
       </c>
     </row>
     <row r="24">
@@ -4185,13 +4185,13 @@
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>44.10008548785977</v>
+        <v>45.39027567108655</v>
       </c>
       <c r="D24" s="9" t="n">
-        <v>30.62358339411352</v>
+        <v>31.51950561814614</v>
       </c>
       <c r="E24" s="9" t="n">
-        <v>63.12895820269197</v>
+        <v>64.97585625854424</v>
       </c>
     </row>
     <row r="25">
@@ -4206,13 +4206,13 @@
         </is>
       </c>
       <c r="C25" s="9" t="n">
-        <v>65.21797762845104</v>
+        <v>55.09900810054334</v>
       </c>
       <c r="D25" s="9" t="n">
-        <v>52.48301668482841</v>
+        <v>46.82211783514564</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>134.4043758858767</v>
+        <v>108.2656760498812</v>
       </c>
     </row>
     <row r="26">
@@ -4240,7 +4240,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H49"/>
+  <dimension ref="A1:H56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -4373,7 +4373,7 @@
     <row r="11">
       <c r="A11" s="11" t="inlineStr">
         <is>
-          <t>Revenue drivers</t>
+          <t>Revenue drivers — the unit build</t>
         </is>
       </c>
       <c r="B11" s="14" t="n"/>
@@ -4387,207 +4387,249 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Domestic revenue growth</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="C12" s="8" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="D12" s="8" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="E12" s="8" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="F12" s="8" t="n">
-        <v>0.08</v>
+          <t>Copper (USD/tonne)</t>
+        </is>
+      </c>
+      <c r="B12" s="17" t="n">
+        <v>13400</v>
+      </c>
+      <c r="C12" s="17" t="n">
+        <v>14000</v>
+      </c>
+      <c r="D12" s="17" t="n">
+        <v>14000</v>
+      </c>
+      <c r="E12" s="17" t="n">
+        <v>14000</v>
+      </c>
+      <c r="F12" s="17" t="n">
+        <v>14000</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>Foreign revenue growth (USD)</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="C13" s="8" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="D13" s="8" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="E13" s="8" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="F13" s="8" t="n">
-        <v>0.06</v>
+          <t>USD/EGP path</t>
+        </is>
+      </c>
+      <c r="B13" s="23" t="n">
+        <v>51</v>
+      </c>
+      <c r="C13" s="23" t="n">
+        <v>54</v>
+      </c>
+      <c r="D13" s="23" t="n">
+        <v>57.5</v>
+      </c>
+      <c r="E13" s="23" t="n">
+        <v>61</v>
+      </c>
+      <c r="F13" s="23" t="n">
+        <v>64.5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>USD/EGP path</t>
-        </is>
-      </c>
-      <c r="B14" s="23" t="n">
-        <v>51</v>
-      </c>
-      <c r="C14" s="23" t="n">
-        <v>54</v>
-      </c>
-      <c r="D14" s="23" t="n">
-        <v>57.5</v>
-      </c>
-      <c r="E14" s="23" t="n">
-        <v>61</v>
-      </c>
-      <c r="F14" s="23" t="n">
-        <v>64.5</v>
+          <t>Cable volume growth</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="C14" s="8" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D14" s="8" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="E14" s="8" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="F14" s="8" t="n">
+        <v>0.04</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>Foreign share of FY2025 revenue</t>
-        </is>
-      </c>
-      <c r="C15" s="8" t="n">
-        <v>0.7</v>
+          <t>Cable fabrication uplift over copper</t>
+        </is>
+      </c>
+      <c r="B15" s="24" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="C15" s="24" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="D15" s="24" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E15" s="24" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F15" s="24" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Raw-material volume growth</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="C16" s="8" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="D16" s="8" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="E16" s="8" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F16" s="8" t="n">
+        <v>0.03</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="11" t="inlineStr">
-        <is>
-          <t>Segment EBITDA margins</t>
-        </is>
-      </c>
-      <c r="B17" s="14" t="n"/>
-      <c r="C17" s="14" t="n"/>
-      <c r="D17" s="14" t="n"/>
-      <c r="E17" s="14" t="n"/>
-      <c r="F17" s="14" t="n"/>
-      <c r="G17" s="14" t="n"/>
-      <c r="H17" s="14" t="n"/>
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>Transformer MVA growth</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="C17" s="8" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="D17" s="8" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="E17" s="8" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F17" s="8" t="n">
+        <v>0.05</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Wires, Cables &amp; Accessories</t>
+          <t>Meter unit growth</t>
         </is>
       </c>
       <c r="B18" s="8" t="n">
-        <v>0.091</v>
+        <v>0.06</v>
       </c>
       <c r="C18" s="8" t="n">
-        <v>0.0925</v>
+        <v>0.05</v>
       </c>
       <c r="D18" s="8" t="n">
-        <v>0.095</v>
+        <v>0.05</v>
       </c>
       <c r="E18" s="8" t="n">
-        <v>0.098</v>
+        <v>0.04</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>0.1</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>Engineering &amp; Construction</t>
+          <t>Order-book conversion rate</t>
         </is>
       </c>
       <c r="B19" s="8" t="n">
-        <v>0.056</v>
+        <v>0.27</v>
       </c>
       <c r="C19" s="8" t="n">
-        <v>0.058</v>
+        <v>0.265</v>
       </c>
       <c r="D19" s="8" t="n">
-        <v>0.061</v>
+        <v>0.26</v>
       </c>
       <c r="E19" s="8" t="n">
-        <v>0.063</v>
+        <v>0.255</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>0.065</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Electrical Products</t>
-        </is>
-      </c>
-      <c r="B20" s="8" t="n">
-        <v>0.345</v>
-      </c>
-      <c r="C20" s="8" t="n">
-        <v>0.345</v>
-      </c>
-      <c r="D20" s="8" t="n">
-        <v>0.345</v>
-      </c>
-      <c r="E20" s="8" t="n">
-        <v>0.345</v>
-      </c>
-      <c r="F20" s="8" t="n">
-        <v>0.345</v>
+          <t>Order-book book-to-bill</t>
+        </is>
+      </c>
+      <c r="B20" s="24" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="C20" s="24" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="D20" s="24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="E20" s="24" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="F20" s="24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>Digital Solutions</t>
+          <t>Other-lines revenue growth</t>
         </is>
       </c>
       <c r="B21" s="8" t="n">
-        <v>0.177</v>
+        <v>0.12</v>
       </c>
       <c r="C21" s="8" t="n">
-        <v>0.18</v>
+        <v>0.11</v>
       </c>
       <c r="D21" s="8" t="n">
-        <v>0.182</v>
+        <v>0.1</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>0.1835</v>
+        <v>0.09</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>0.185</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Infrastructure Investment</t>
+          <t>Meter price inflation</t>
         </is>
       </c>
       <c r="B22" s="8" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.08</v>
       </c>
       <c r="C22" s="8" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.075</v>
       </c>
       <c r="D22" s="8" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t>Capital intensity</t>
+          <t>Unit gross profit and cost load</t>
         </is>
       </c>
       <c r="B24" s="14" t="n"/>
@@ -4601,262 +4643,362 @@
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>Working capital / revenue</t>
-        </is>
+          <t>Gross profit per unit — growth</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="n">
+        <v>0.08500000000000001</v>
       </c>
       <c r="C25" s="8" t="n">
-        <v>0.23</v>
+        <v>0.08</v>
+      </c>
+      <c r="D25" s="8" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="E25" s="8" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="F25" s="8" t="n">
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>Capital expenditure / revenue</t>
-        </is>
-      </c>
-      <c r="B26" s="8" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="C26" s="8" t="n">
-        <v>0.029</v>
-      </c>
-      <c r="D26" s="8" t="n">
-        <v>0.028</v>
-      </c>
-      <c r="E26" s="8" t="n">
-        <v>0.026</v>
-      </c>
-      <c r="F26" s="8" t="n">
-        <v>0.024</v>
+          <t>Non-cable margin recovery factor</t>
+        </is>
+      </c>
+      <c r="B26" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" s="24" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="D26" s="24" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="E26" s="24" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="F26" s="24" t="n">
+        <v>1.1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>Depreciation and amortisation / revenue</t>
-        </is>
+          <t>Operating load (% of revenue)</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="n">
+        <v>0.04</v>
       </c>
       <c r="C27" s="8" t="n">
-        <v>0.0105</v>
+        <v>0.043</v>
+      </c>
+      <c r="D27" s="8" t="n">
+        <v>0.046</v>
+      </c>
+      <c r="E27" s="8" t="n">
+        <v>0.048</v>
+      </c>
+      <c r="F27" s="8" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>Cable gross profit per tonne, FY2025 (EGP)</t>
+        </is>
+      </c>
+      <c r="C28" s="17" t="n">
+        <v>88173</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="11" t="inlineStr">
-        <is>
-          <t>Cost of capital</t>
-        </is>
-      </c>
-      <c r="B29" s="14" t="n"/>
-      <c r="C29" s="14" t="n"/>
-      <c r="D29" s="14" t="n"/>
-      <c r="E29" s="14" t="n"/>
-      <c r="F29" s="14" t="n"/>
-      <c r="G29" s="14" t="n"/>
-      <c r="H29" s="14" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="6" t="inlineStr">
-        <is>
-          <t>Risk-free rate (10-year local currency)</t>
-        </is>
-      </c>
-      <c r="C30" s="8" t="n">
-        <v>0.2231</v>
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>Order book at FY2025 (EGP mn)</t>
+        </is>
+      </c>
+      <c r="C29" s="17" t="n">
+        <v>323700</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="6" t="inlineStr">
-        <is>
-          <t>Sovereign default spread (netted out)</t>
-        </is>
-      </c>
-      <c r="C31" s="8" t="n">
-        <v>0.034</v>
-      </c>
+      <c r="A31" s="11" t="inlineStr">
+        <is>
+          <t>Capital intensity</t>
+        </is>
+      </c>
+      <c r="B31" s="14" t="n"/>
+      <c r="C31" s="14" t="n"/>
+      <c r="D31" s="14" t="n"/>
+      <c r="E31" s="14" t="n"/>
+      <c r="F31" s="14" t="n"/>
+      <c r="G31" s="14" t="n"/>
+      <c r="H31" s="14" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>Equity risk premium</t>
+          <t>Working capital / revenue</t>
         </is>
       </c>
       <c r="C32" s="8" t="n">
-        <v>0.0941</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>Beta</t>
-        </is>
-      </c>
-      <c r="C33" s="24" t="n">
-        <v>1.009</v>
+          <t>Capital expenditure / revenue</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="C33" s="8" t="n">
+        <v>0.029</v>
+      </c>
+      <c r="D33" s="8" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="E33" s="8" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="F33" s="8" t="n">
+        <v>0.024</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>Cost of debt, blended</t>
+          <t>Depreciation and amortisation / revenue</t>
         </is>
       </c>
       <c r="C34" s="8" t="n">
-        <v>0.13</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="6" t="inlineStr">
-        <is>
-          <t>Cost of debt path</t>
-        </is>
-      </c>
-      <c r="B35" s="8" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="C35" s="8" t="n">
-        <v>0.122</v>
-      </c>
-      <c r="D35" s="8" t="n">
-        <v>0.115</v>
-      </c>
-      <c r="E35" s="8" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="F35" s="8" t="n">
-        <v>0.106</v>
+        <v>0.0105</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="6" t="inlineStr">
-        <is>
-          <t>Terminal risk-free rate</t>
-        </is>
-      </c>
-      <c r="C36" s="8" t="n">
-        <v>0.105</v>
-      </c>
+      <c r="A36" s="11" t="inlineStr">
+        <is>
+          <t>Cost of capital</t>
+        </is>
+      </c>
+      <c r="B36" s="14" t="n"/>
+      <c r="C36" s="14" t="n"/>
+      <c r="D36" s="14" t="n"/>
+      <c r="E36" s="14" t="n"/>
+      <c r="F36" s="14" t="n"/>
+      <c r="G36" s="14" t="n"/>
+      <c r="H36" s="14" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>Terminal equity risk premium</t>
+          <t>Risk-free rate (10-year local currency)</t>
         </is>
       </c>
       <c r="C37" s="8" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.2231</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>Terminal cost of debt</t>
+          <t>Sovereign default spread (netted out)</t>
         </is>
       </c>
       <c r="C38" s="8" t="n">
-        <v>0.105</v>
+        <v>0.034</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>Terminal debt weight</t>
+          <t>Equity risk premium</t>
         </is>
       </c>
       <c r="C39" s="8" t="n">
-        <v>0.25</v>
+        <v>0.0941</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>Terminal growth</t>
-        </is>
-      </c>
-      <c r="C40" s="8" t="n">
-        <v>0.05</v>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="C40" s="25" t="n">
+        <v>1.009</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>Cost of debt, blended</t>
+        </is>
+      </c>
+      <c r="C41" s="8" t="n">
+        <v>0.13</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="11" t="inlineStr">
-        <is>
-          <t>Lens inputs</t>
-        </is>
-      </c>
-      <c r="B42" s="14" t="n"/>
-      <c r="C42" s="14" t="n"/>
-      <c r="D42" s="14" t="n"/>
-      <c r="E42" s="14" t="n"/>
-      <c r="F42" s="14" t="n"/>
-      <c r="G42" s="14" t="n"/>
-      <c r="H42" s="14" t="n"/>
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>Cost of debt path</t>
+        </is>
+      </c>
+      <c r="B42" s="8" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="C42" s="8" t="n">
+        <v>0.122</v>
+      </c>
+      <c r="D42" s="8" t="n">
+        <v>0.115</v>
+      </c>
+      <c r="E42" s="8" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="F42" s="8" t="n">
+        <v>0.106</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>Justified EV/EBITDA</t>
-        </is>
-      </c>
-      <c r="C43" s="25" t="n">
-        <v>6.5</v>
+          <t>Terminal risk-free rate</t>
+        </is>
+      </c>
+      <c r="C43" s="8" t="n">
+        <v>0.105</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>Justified price/earnings</t>
-        </is>
-      </c>
-      <c r="C44" s="25" t="n">
-        <v>9</v>
+          <t>Terminal equity risk premium</t>
+        </is>
+      </c>
+      <c r="C44" s="8" t="n">
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>Sustainable return on equity</t>
+          <t>Terminal cost of debt</t>
         </is>
       </c>
       <c r="C45" s="8" t="n">
-        <v>0.235</v>
+        <v>0.105</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>Weight — discounted cash flow</t>
+          <t>Terminal debt weight</t>
         </is>
       </c>
       <c r="C46" s="8" t="n">
-        <v>0.45</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
+          <t>Terminal growth</t>
+        </is>
+      </c>
+      <c r="C47" s="8" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="11" t="inlineStr">
+        <is>
+          <t>Lens inputs</t>
+        </is>
+      </c>
+      <c r="B49" s="14" t="n"/>
+      <c r="C49" s="14" t="n"/>
+      <c r="D49" s="14" t="n"/>
+      <c r="E49" s="14" t="n"/>
+      <c r="F49" s="14" t="n"/>
+      <c r="G49" s="14" t="n"/>
+      <c r="H49" s="14" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>Justified EV/EBITDA</t>
+        </is>
+      </c>
+      <c r="C50" s="24" t="n">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>Justified price/earnings</t>
+        </is>
+      </c>
+      <c r="C51" s="24" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>Sustainable return on equity</t>
+        </is>
+      </c>
+      <c r="C52" s="8" t="n">
+        <v>0.235</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>Weight — discounted cash flow</t>
+        </is>
+      </c>
+      <c r="C53" s="8" t="n">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
           <t>Weight — relative</t>
         </is>
       </c>
-      <c r="C47" s="8" t="n">
+      <c r="C54" s="8" t="n">
         <v>0.2</v>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="6" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="6" t="inlineStr">
         <is>
           <t>Weight — normalised</t>
         </is>
       </c>
-      <c r="C48" s="8" t="n">
+      <c r="C55" s="8" t="n">
         <v>0.2</v>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="6" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="6" t="inlineStr">
         <is>
           <t>Weight — book</t>
         </is>
       </c>
-      <c r="C49" s="8" t="n">
+      <c r="C56" s="8" t="n">
         <v>0.15</v>
       </c>
     </row>
@@ -5061,7 +5203,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5145,383 +5287,489 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Wires, Cables &amp; Accessories</t>
+          <t>Cables</t>
         </is>
       </c>
       <c r="B5" s="28" t="n">
-        <v>165818.91</v>
-      </c>
-      <c r="C5" s="8" t="n">
-        <v>0.59</v>
+        <v>99104.38752626561</v>
+      </c>
+      <c r="C5" s="10" t="n">
+        <v>0.3526231636699138</v>
       </c>
       <c r="D5" s="8" t="n">
-        <v>0.1245</v>
+        <v>0.1375659154735564</v>
       </c>
       <c r="E5" s="28" t="n">
-        <v>186345.230032</v>
+        <v>145610.3678770696</v>
       </c>
       <c r="F5" s="28" t="n">
-        <v>209594.74249728</v>
+        <v>169133.0260767016</v>
       </c>
       <c r="G5" s="28" t="n">
-        <v>233900.0533789921</v>
+        <v>187299.1659145696</v>
       </c>
       <c r="H5" s="28" t="n">
-        <v>257952.8726271101</v>
+        <v>206647.9840977443</v>
       </c>
       <c r="I5" s="28" t="n">
-        <v>283103.2426313147</v>
+        <v>227245.0290701096</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Engineering &amp; Construction</t>
+          <t>Raw material (copper rod)</t>
         </is>
       </c>
       <c r="B6" s="28" t="n">
-        <v>75883.23000000001</v>
-      </c>
-      <c r="C6" s="8" t="n">
-        <v>0.27</v>
+        <v>60448.00314509805</v>
+      </c>
+      <c r="C6" s="10" t="n">
+        <v>0.2150799438713465</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>0.09</v>
+        <v>0.1347135486293534</v>
       </c>
       <c r="E6" s="28" t="n">
-        <v>86790.92905600001</v>
+        <v>86793.07467340285</v>
       </c>
       <c r="F6" s="28" t="n">
-        <v>99358.06132224001</v>
+        <v>99853.94648992721</v>
       </c>
       <c r="G6" s="28" t="n">
-        <v>112860.864917136</v>
+        <v>109515.7403864063</v>
       </c>
       <c r="H6" s="28" t="n">
-        <v>126697.7006896406</v>
+        <v>119667.3733648332</v>
       </c>
       <c r="I6" s="28" t="n">
-        <v>141551.6213156573</v>
+        <v>130329.5401556179</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>Electrical Products</t>
+          <t>Engineering &amp; construction</t>
         </is>
       </c>
       <c r="B7" s="28" t="n">
-        <v>16862.94</v>
-      </c>
-      <c r="C7" s="8" t="n">
-        <v>0.06</v>
+        <v>87553</v>
+      </c>
+      <c r="C7" s="10" t="n">
+        <v>0.3115221900807332</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>0.38</v>
+        <v>0.09770663311824808</v>
       </c>
       <c r="E7" s="28" t="n">
-        <v>19464.142178</v>
+        <v>87399</v>
       </c>
       <c r="F7" s="28" t="n">
-        <v>22482.48102912</v>
+        <v>86938.53675000001</v>
       </c>
       <c r="G7" s="28" t="n">
-        <v>25761.71916586801</v>
+        <v>86428.38797775001</v>
       </c>
       <c r="H7" s="28" t="n">
-        <v>29167.81598610432</v>
+        <v>85427.48076159229</v>
       </c>
       <c r="I7" s="28" t="n">
-        <v>32860.19780542045</v>
+        <v>84179.56952301609</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Digital Solutions</t>
+          <t>Transformers</t>
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>16862.94</v>
-      </c>
-      <c r="C8" s="8" t="n">
-        <v>0.06</v>
+        <v>12254.56652975496</v>
+      </c>
+      <c r="C8" s="10" t="n">
+        <v>0.04360295368336113</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>0.21</v>
+        <v>0.3009934715480775</v>
       </c>
       <c r="E8" s="28" t="n">
-        <v>19783.226476</v>
+        <v>20025.95817760357</v>
       </c>
       <c r="F8" s="28" t="n">
-        <v>23207.72235264</v>
+        <v>23704.12363041715</v>
       </c>
       <c r="G8" s="28" t="n">
-        <v>26988.467697576</v>
+        <v>26754.93213470232</v>
       </c>
       <c r="H8" s="28" t="n">
-        <v>30990.80448523584</v>
+        <v>29802.66788222058</v>
       </c>
       <c r="I8" s="28" t="n">
-        <v>35387.90532891433</v>
+        <v>33088.28987415392</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>Infrastructure Investment</t>
+          <t>Meters &amp; digital</t>
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>5620.98</v>
-      </c>
-      <c r="C9" s="8" t="n">
-        <v>0.02</v>
+        <v>15562.14279888138</v>
+      </c>
+      <c r="C9" s="10" t="n">
+        <v>0.05537163554711592</v>
       </c>
       <c r="D9" s="8" t="n">
-        <v>0.6</v>
+        <v>0.2379981199493308</v>
       </c>
       <c r="E9" s="28" t="n">
-        <v>6700.770258</v>
+        <v>17815.54107615941</v>
       </c>
       <c r="F9" s="28" t="n">
-        <v>7977.654558720002</v>
+        <v>20109.29198971493</v>
       </c>
       <c r="G9" s="28" t="n">
-        <v>9405.072076428001</v>
+        <v>22592.78955044473</v>
       </c>
       <c r="H9" s="28" t="n">
-        <v>10937.93099478912</v>
+        <v>25141.25621173489</v>
       </c>
       <c r="I9" s="28" t="n">
-        <v>12638.5376174694</v>
+        <v>27977.18991241859</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Other electrical products</t>
+        </is>
+      </c>
+      <c r="B10" s="28" t="n">
+        <v>3206.5</v>
+      </c>
+      <c r="C10" s="10" t="n">
+        <v>0.01140904255129888</v>
+      </c>
+      <c r="D10" s="8" t="n">
+        <v>0.4430145873816911</v>
+      </c>
+      <c r="E10" s="28" t="n">
+        <v>3591.28</v>
+      </c>
+      <c r="F10" s="28" t="n">
+        <v>3986.3208</v>
+      </c>
+      <c r="G10" s="28" t="n">
+        <v>4384.952880000001</v>
+      </c>
+      <c r="H10" s="28" t="n">
+        <v>4779.598639200001</v>
+      </c>
+      <c r="I10" s="28" t="n">
+        <v>5161.966530336002</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Infrastructure investment</t>
+        </is>
+      </c>
+      <c r="B11" s="28" t="n">
+        <v>2920.4</v>
+      </c>
+      <c r="C11" s="10" t="n">
+        <v>0.01039107059623055</v>
+      </c>
+      <c r="D11" s="8" t="n">
+        <v>0.5396893633758121</v>
+      </c>
+      <c r="E11" s="28" t="n">
+        <v>3270.848</v>
+      </c>
+      <c r="F11" s="28" t="n">
+        <v>3630.641280000001</v>
+      </c>
+      <c r="G11" s="28" t="n">
+        <v>3993.705408000001</v>
+      </c>
+      <c r="H11" s="28" t="n">
+        <v>4353.138894720001</v>
+      </c>
+      <c r="I11" s="28" t="n">
+        <v>4701.390006297602</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>Total revenue</t>
         </is>
       </c>
-      <c r="B10" s="31">
-        <f>SUM(B5:B9)</f>
-        <v/>
-      </c>
-      <c r="C10" s="13">
-        <f>SUM(C5:C9)</f>
-        <v/>
-      </c>
-      <c r="D10" s="14" t="n"/>
-      <c r="E10" s="31">
-        <f>SUM(E5:E9)</f>
-        <v/>
-      </c>
-      <c r="F10" s="31">
-        <f>SUM(F5:F9)</f>
-        <v/>
-      </c>
-      <c r="G10" s="31">
-        <f>SUM(G5:G9)</f>
-        <v/>
-      </c>
-      <c r="H10" s="31">
-        <f>SUM(H5:H9)</f>
-        <v/>
-      </c>
-      <c r="I10" s="31">
-        <f>SUM(I5:I9)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="B12" s="31">
+        <f>SUM(B5:B11)</f>
+        <v/>
+      </c>
+      <c r="C12" s="13">
+        <f>SUM(C5:C11)</f>
+        <v/>
+      </c>
+      <c r="D12" s="14" t="n"/>
+      <c r="E12" s="31">
+        <f>SUM(E5:E11)</f>
+        <v/>
+      </c>
+      <c r="F12" s="31">
+        <f>SUM(F5:F11)</f>
+        <v/>
+      </c>
+      <c r="G12" s="31">
+        <f>SUM(G5:G11)</f>
+        <v/>
+      </c>
+      <c r="H12" s="31">
+        <f>SUM(H5:H11)</f>
+        <v/>
+      </c>
+      <c r="I12" s="31">
+        <f>SUM(I5:I11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>Segment EBITDA</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>FY26E</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>FY27E</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>FY28E</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>FY29E</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="F14" s="5" t="inlineStr">
         <is>
           <t>FY30E</t>
         </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>Wires, Cables &amp; Accessories</t>
-        </is>
-      </c>
-      <c r="B13" s="28" t="n">
-        <v>16957.415932912</v>
-      </c>
-      <c r="C13" s="28" t="n">
-        <v>19387.5136809984</v>
-      </c>
-      <c r="D13" s="28" t="n">
-        <v>22220.50507100425</v>
-      </c>
-      <c r="E13" s="28" t="n">
-        <v>25279.38151745679</v>
-      </c>
-      <c r="F13" s="28" t="n">
-        <v>28310.32426313147</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>Engineering &amp; Construction</t>
-        </is>
-      </c>
-      <c r="B14" s="28" t="n">
-        <v>4860.292027136001</v>
-      </c>
-      <c r="C14" s="28" t="n">
-        <v>5762.767556689921</v>
-      </c>
-      <c r="D14" s="28" t="n">
-        <v>6884.512759945298</v>
-      </c>
-      <c r="E14" s="28" t="n">
-        <v>7981.955143447361</v>
-      </c>
-      <c r="F14" s="28" t="n">
-        <v>9200.855385517727</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>Electrical Products</t>
+          <t>Cables</t>
         </is>
       </c>
       <c r="B15" s="28" t="n">
-        <v>6715.12905141</v>
+        <v>20065.66069631773</v>
       </c>
       <c r="C15" s="28" t="n">
-        <v>7756.4559550464</v>
+        <v>22086.62539523002</v>
       </c>
       <c r="D15" s="28" t="n">
-        <v>8887.793112224461</v>
+        <v>24207.98665540832</v>
       </c>
       <c r="E15" s="28" t="n">
-        <v>10062.89651520599</v>
+        <v>26607.16385761438</v>
       </c>
       <c r="F15" s="28" t="n">
-        <v>11336.76824287006</v>
+        <v>29284.17856903834</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Digital Solutions</t>
+          <t>Raw material (copper rod)</t>
         </is>
       </c>
       <c r="B16" s="28" t="n">
-        <v>3501.631086252</v>
+        <v>5717.024411740862</v>
       </c>
       <c r="C16" s="28" t="n">
-        <v>4177.390023475201</v>
+        <v>6027.081379127109</v>
       </c>
       <c r="D16" s="28" t="n">
-        <v>4911.901120958833</v>
+        <v>6389.982936055597</v>
       </c>
       <c r="E16" s="28" t="n">
-        <v>5686.812623040776</v>
+        <v>6850.441956388367</v>
       </c>
       <c r="F16" s="28" t="n">
-        <v>6546.762485849152</v>
+        <v>7363.89485725309</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>Infrastructure Investment</t>
+          <t>Engineering &amp; construction</t>
         </is>
       </c>
       <c r="B17" s="28" t="n">
-        <v>3785.93519577</v>
+        <v>5043.502027901764</v>
       </c>
       <c r="C17" s="28" t="n">
-        <v>4507.3748256768</v>
+        <v>5095.893502382363</v>
       </c>
       <c r="D17" s="28" t="n">
-        <v>5313.865723181821</v>
+        <v>5060.044823827177</v>
       </c>
       <c r="E17" s="28" t="n">
-        <v>6179.931012055851</v>
+        <v>4997.527281321682</v>
       </c>
       <c r="F17" s="28" t="n">
-        <v>7140.773753870213</v>
+        <v>4838.414070830325</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="11" t="inlineStr">
-        <is>
-          <t>Group EBITDA</t>
-        </is>
-      </c>
-      <c r="B18" s="31">
-        <f>SUM(B13:B17)</f>
-        <v/>
-      </c>
-      <c r="C18" s="31">
-        <f>SUM(C13:C17)</f>
-        <v/>
-      </c>
-      <c r="D18" s="31">
-        <f>SUM(D13:D17)</f>
-        <v/>
-      </c>
-      <c r="E18" s="31">
-        <f>SUM(E13:E17)</f>
-        <v/>
-      </c>
-      <c r="F18" s="31">
-        <f>SUM(F13:F17)</f>
-        <v/>
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Transformers</t>
+        </is>
+      </c>
+      <c r="B18" s="28" t="n">
+        <v>3521.198143901805</v>
+      </c>
+      <c r="C18" s="28" t="n">
+        <v>3975.499149786538</v>
+      </c>
+      <c r="D18" s="28" t="n">
+        <v>4460.820904690448</v>
+      </c>
+      <c r="E18" s="28" t="n">
+        <v>4963.925875726681</v>
+      </c>
+      <c r="F18" s="28" t="n">
+        <v>5529.754501223622</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
+          <t>Meters &amp; digital</t>
+        </is>
+      </c>
+      <c r="B19" s="28" t="n">
+        <v>3547.073570820779</v>
+      </c>
+      <c r="C19" s="28" t="n">
+        <v>3965.794816967612</v>
+      </c>
+      <c r="D19" s="28" t="n">
+        <v>4413.152203667537</v>
+      </c>
+      <c r="E19" s="28" t="n">
+        <v>4860.673259817765</v>
+      </c>
+      <c r="F19" s="28" t="n">
+        <v>5353.002823700373</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Other electrical products</t>
+        </is>
+      </c>
+      <c r="B20" s="28" t="n">
+        <v>1447.33822737212</v>
+      </c>
+      <c r="C20" s="28" t="n">
+        <v>1665.226400558375</v>
+      </c>
+      <c r="D20" s="28" t="n">
+        <v>1876.872124698853</v>
+      </c>
+      <c r="E20" s="28" t="n">
+        <v>2078.580057023256</v>
+      </c>
+      <c r="F20" s="28" t="n">
+        <v>2257.410793249594</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>Infrastructure investment</t>
+        </is>
+      </c>
+      <c r="B21" s="28" t="n">
+        <v>1634.407954819048</v>
+      </c>
+      <c r="C21" s="28" t="n">
+        <v>1881.67764525111</v>
+      </c>
+      <c r="D21" s="28" t="n">
+        <v>2122.525103426843</v>
+      </c>
+      <c r="E21" s="28" t="n">
+        <v>2351.832940121377</v>
+      </c>
+      <c r="F21" s="28" t="n">
+        <v>2555.949697113294</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="11" t="inlineStr">
+        <is>
+          <t>Group EBITDA</t>
+        </is>
+      </c>
+      <c r="B22" s="31">
+        <f>SUM(B15:B21)</f>
+        <v/>
+      </c>
+      <c r="C22" s="31">
+        <f>SUM(C15:C21)</f>
+        <v/>
+      </c>
+      <c r="D22" s="31">
+        <f>SUM(D15:D21)</f>
+        <v/>
+      </c>
+      <c r="E22" s="31">
+        <f>SUM(E15:E21)</f>
+        <v/>
+      </c>
+      <c r="F22" s="31">
+        <f>SUM(F15:F21)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
           <t>Group EBITDA margin</t>
         </is>
       </c>
-      <c r="B19" s="10" t="n">
-        <v>0.11226</v>
-      </c>
-      <c r="C19" s="10" t="n">
-        <v>0.114697</v>
-      </c>
-      <c r="D19" s="10" t="n">
-        <v>0.117918</v>
-      </c>
-      <c r="E19" s="10" t="n">
-        <v>0.1211</v>
-      </c>
-      <c r="F19" s="10" t="n">
-        <v>0.1237</v>
+      <c r="B23" s="10" t="n">
+        <v>0.112415700114078</v>
+      </c>
+      <c r="C23" s="10" t="n">
+        <v>0.1097266535575169</v>
+      </c>
+      <c r="D23" s="10" t="n">
+        <v>0.1100560596011748</v>
+      </c>
+      <c r="E23" s="10" t="n">
+        <v>0.1107776063074413</v>
+      </c>
+      <c r="F23" s="10" t="n">
+        <v>0.1115359941577613</v>
       </c>
     </row>
   </sheetData>
@@ -5585,7 +5833,7 @@
           <t>Justified enterprise value / EBITDA</t>
         </is>
       </c>
-      <c r="C6" s="25" t="n">
+      <c r="C6" s="24" t="n">
         <v>6.5</v>
       </c>
     </row>
@@ -5630,7 +5878,7 @@
         </is>
       </c>
       <c r="C11" s="32" t="n">
-        <v>7.924817786713997</v>
+        <v>8.000722677325394</v>
       </c>
     </row>
     <row r="12">
@@ -5660,7 +5908,7 @@
         </is>
       </c>
       <c r="C14" s="32" t="n">
-        <v>0.6401019039384591</v>
+        <v>0.6462328796032941</v>
       </c>
     </row>
     <row r="16">
@@ -5682,7 +5930,7 @@
         </is>
       </c>
       <c r="C17" s="17" t="n">
-        <v>362620.66176</v>
+        <v>407355.8870167609</v>
       </c>
     </row>
     <row r="18">
@@ -5692,7 +5940,7 @@
         </is>
       </c>
       <c r="C18" s="8" t="n">
-        <v>0.120906</v>
+        <v>0.1107898866887925</v>
       </c>
     </row>
     <row r="19">
@@ -5702,7 +5950,7 @@
         </is>
       </c>
       <c r="C19" s="17" t="n">
-        <v>40035.49678227457</v>
+        <v>40853.6757509235</v>
       </c>
     </row>
     <row r="20">
@@ -5722,7 +5970,7 @@
         </is>
       </c>
       <c r="C21" s="17" t="n">
-        <v>25215.93280882912</v>
+        <v>25770.37916675479</v>
       </c>
     </row>
     <row r="22">
@@ -5732,7 +5980,7 @@
         </is>
       </c>
       <c r="C22" s="22" t="n">
-        <v>11.77886463211427</v>
+        <v>12.03785757301744</v>
       </c>
     </row>
     <row r="23">
@@ -5741,7 +5989,7 @@
           <t>Justified price / earnings</t>
         </is>
       </c>
-      <c r="C23" s="25" t="n">
+      <c r="C23" s="24" t="n">
         <v>9</v>
       </c>
     </row>
@@ -5815,7 +6063,7 @@
           <t>Justified price / book</t>
         </is>
       </c>
-      <c r="C31" s="25" t="n">
+      <c r="C31" s="24" t="n">
         <v>1.028701036958448</v>
       </c>
     </row>
@@ -5911,19 +6159,19 @@
         </is>
       </c>
       <c r="B5" s="28" t="n">
-        <v>319084.298</v>
+        <v>364506.0698042354</v>
       </c>
       <c r="C5" s="28" t="n">
-        <v>362620.66176</v>
+        <v>407355.8870167609</v>
       </c>
       <c r="D5" s="28" t="n">
-        <v>408916.1772360001</v>
+        <v>440969.6742518729</v>
       </c>
       <c r="E5" s="28" t="n">
-        <v>455747.1247828801</v>
+        <v>475819.4998520451</v>
       </c>
       <c r="F5" s="28" t="n">
-        <v>505541.5046987762</v>
+        <v>512682.9750719497</v>
       </c>
     </row>
     <row r="6">
@@ -5933,19 +6181,19 @@
         </is>
       </c>
       <c r="B6" s="28" t="n">
-        <v>35820.40329348</v>
+        <v>40976.20503287411</v>
       </c>
       <c r="C6" s="28" t="n">
-        <v>41591.50204188672</v>
+        <v>44697.79828930313</v>
       </c>
       <c r="D6" s="28" t="n">
-        <v>48218.57778731467</v>
+        <v>48531.38475177478</v>
       </c>
       <c r="E6" s="28" t="n">
-        <v>55190.97681120677</v>
+        <v>52710.1452280135</v>
       </c>
       <c r="F6" s="28" t="n">
-        <v>62535.48413123862</v>
+        <v>57182.60531240865</v>
       </c>
     </row>
     <row r="7">
@@ -5955,19 +6203,19 @@
         </is>
       </c>
       <c r="B7" s="10" t="n">
-        <v>0.11226</v>
+        <v>0.112415700114078</v>
       </c>
       <c r="C7" s="10" t="n">
-        <v>0.114697</v>
+        <v>0.1097266535575169</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>0.117918</v>
+        <v>0.1100560596011748</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.1211</v>
+        <v>0.1107776063074413</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>0.1237</v>
+        <v>0.1115359941577613</v>
       </c>
     </row>
     <row r="8">
@@ -5977,19 +6225,19 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>-3350.385129</v>
+        <v>-3827.313732944472</v>
       </c>
       <c r="C8" s="28" t="n">
-        <v>-3807.516948480001</v>
+        <v>-4277.236813675991</v>
       </c>
       <c r="D8" s="28" t="n">
-        <v>-4293.619860978001</v>
+        <v>-4630.181579644666</v>
       </c>
       <c r="E8" s="28" t="n">
-        <v>-4785.344810220241</v>
+        <v>-4996.104748446474</v>
       </c>
       <c r="F8" s="28" t="n">
-        <v>-5308.18579933715</v>
+        <v>-5383.171238255472</v>
       </c>
     </row>
     <row r="9">
@@ -5999,19 +6247,19 @@
         </is>
       </c>
       <c r="B9" s="29" t="n">
-        <v>32470.01816448</v>
+        <v>37148.89129992964</v>
       </c>
       <c r="C9" s="29" t="n">
-        <v>37783.98509340672</v>
+        <v>40420.56147562714</v>
       </c>
       <c r="D9" s="29" t="n">
-        <v>43924.95792633666</v>
+        <v>43901.20317213011</v>
       </c>
       <c r="E9" s="29" t="n">
-        <v>50405.63200098653</v>
+        <v>47714.04047956703</v>
       </c>
       <c r="F9" s="29" t="n">
-        <v>57227.29833190147</v>
+        <v>51799.43407415318</v>
       </c>
     </row>
     <row r="10">
@@ -6021,19 +6269,19 @@
         </is>
       </c>
       <c r="B10" s="28" t="n">
-        <v>24352.51362336</v>
+        <v>27861.66847494723</v>
       </c>
       <c r="C10" s="28" t="n">
-        <v>28337.98882005504</v>
+        <v>30315.42110672035</v>
       </c>
       <c r="D10" s="28" t="n">
-        <v>32943.71844475249</v>
+        <v>32925.90237909758</v>
       </c>
       <c r="E10" s="28" t="n">
-        <v>37804.22400073989</v>
+        <v>35785.53035967527</v>
       </c>
       <c r="F10" s="28" t="n">
-        <v>42920.4737489261</v>
+        <v>38849.57555561488</v>
       </c>
     </row>
     <row r="11">
@@ -6043,19 +6291,19 @@
         </is>
       </c>
       <c r="B11" s="28" t="n">
-        <v>3350.385129</v>
+        <v>3827.313732944472</v>
       </c>
       <c r="C11" s="28" t="n">
-        <v>3807.516948480001</v>
+        <v>4277.236813675991</v>
       </c>
       <c r="D11" s="28" t="n">
-        <v>4293.619860978001</v>
+        <v>4630.181579644666</v>
       </c>
       <c r="E11" s="28" t="n">
-        <v>4785.344810220241</v>
+        <v>4996.104748446474</v>
       </c>
       <c r="F11" s="28" t="n">
-        <v>5308.18579933715</v>
+        <v>5383.171238255472</v>
       </c>
     </row>
     <row r="12">
@@ -6065,19 +6313,19 @@
         </is>
       </c>
       <c r="B12" s="28" t="n">
-        <v>-9572.52894</v>
+        <v>-10935.18209412706</v>
       </c>
       <c r="C12" s="28" t="n">
-        <v>-10515.99919104</v>
+        <v>-11813.32072348607</v>
       </c>
       <c r="D12" s="28" t="n">
-        <v>-11449.652962608</v>
+        <v>-12347.15087905244</v>
       </c>
       <c r="E12" s="28" t="n">
-        <v>-11849.42524435488</v>
+        <v>-12371.30699615317</v>
       </c>
       <c r="F12" s="28" t="n">
-        <v>-12132.99611277063</v>
+        <v>-12304.39140172679</v>
       </c>
     </row>
     <row r="13">
@@ -6087,19 +6335,19 @@
         </is>
       </c>
       <c r="B13" s="28" t="n">
-        <v>-8748.118539999996</v>
+        <v>-19195.12605497414</v>
       </c>
       <c r="C13" s="28" t="n">
-        <v>-10013.36366480001</v>
+        <v>-9855.45795888087</v>
       </c>
       <c r="D13" s="28" t="n">
-        <v>-10647.96855948001</v>
+        <v>-7731.171064075766</v>
       </c>
       <c r="E13" s="28" t="n">
-        <v>-10771.1179357824</v>
+        <v>-8015.459888039608</v>
       </c>
       <c r="F13" s="28" t="n">
-        <v>-11452.70738065611</v>
+        <v>-8478.599300578047</v>
       </c>
     </row>
     <row r="14">
@@ -6109,19 +6357,19 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>9382.251272360005</v>
+        <v>1558.674058790493</v>
       </c>
       <c r="C14" s="29" t="n">
-        <v>11616.14291269503</v>
+        <v>12923.87923802941</v>
       </c>
       <c r="D14" s="29" t="n">
-        <v>15139.71678364249</v>
+        <v>17477.76201561404</v>
       </c>
       <c r="E14" s="29" t="n">
-        <v>19969.02563082285</v>
+        <v>20394.86822392896</v>
       </c>
       <c r="F14" s="29" t="n">
-        <v>24642.95605483652</v>
+        <v>23449.75609156551</v>
       </c>
     </row>
     <row r="15">
@@ -6175,19 +6423,19 @@
         </is>
       </c>
       <c r="B17" s="29" t="n">
-        <v>7393.542387907464</v>
+        <v>1228.28971299769</v>
       </c>
       <c r="C17" s="29" t="n">
-        <v>7443.49142045507</v>
+        <v>8281.473889421228</v>
       </c>
       <c r="D17" s="29" t="n">
-        <v>8114.905813403943</v>
+        <v>9368.100778413231</v>
       </c>
       <c r="E17" s="29" t="n">
-        <v>9140.372792339163</v>
+        <v>9335.292670945473</v>
       </c>
       <c r="F17" s="29" t="n">
-        <v>9796.475125240544</v>
+        <v>9322.134557752976</v>
       </c>
     </row>
     <row r="19">
@@ -6204,7 +6452,7 @@
         </is>
       </c>
       <c r="C20" s="17" t="n">
-        <v>45066.49743637241</v>
+        <v>40792.05433339562</v>
       </c>
     </row>
     <row r="21">
@@ -6214,7 +6462,7 @@
         </is>
       </c>
       <c r="C21" s="8" t="n">
-        <v>0.2323371872854677</v>
+        <v>0.2054903756744277</v>
       </c>
     </row>
     <row r="22">
@@ -6224,7 +6472,7 @@
         </is>
       </c>
       <c r="C22" s="8" t="n">
-        <v>0.2152044646153269</v>
+        <v>0.2433203980278784</v>
       </c>
     </row>
     <row r="23">
@@ -6254,7 +6502,7 @@
         </is>
       </c>
       <c r="C25" s="17" t="n">
-        <v>348762.3112463257</v>
+        <v>304373.4881828119</v>
       </c>
     </row>
     <row r="26">
@@ -6435,19 +6683,19 @@
         <v>281049</v>
       </c>
       <c r="E5" s="29" t="n">
-        <v>319084.298</v>
+        <v>364506.0698042354</v>
       </c>
       <c r="F5" s="29" t="n">
-        <v>362620.66176</v>
+        <v>407355.8870167609</v>
       </c>
       <c r="G5" s="29" t="n">
-        <v>408916.1772360001</v>
+        <v>440969.6742518729</v>
       </c>
       <c r="H5" s="29" t="n">
-        <v>455747.1247828801</v>
+        <v>475819.4998520451</v>
       </c>
       <c r="I5" s="29" t="n">
-        <v>505541.5046987762</v>
+        <v>512682.9750719497</v>
       </c>
     </row>
     <row r="6">
@@ -6479,22 +6727,22 @@
         <v>31601.6</v>
       </c>
       <c r="D7" s="29" t="n">
-        <v>30915.39</v>
+        <v>30622.08783333333</v>
       </c>
       <c r="E7" s="29" t="n">
-        <v>35820.40329348</v>
+        <v>40976.20503287411</v>
       </c>
       <c r="F7" s="29" t="n">
-        <v>41591.50204188672</v>
+        <v>44697.79828930313</v>
       </c>
       <c r="G7" s="29" t="n">
-        <v>48218.57778731467</v>
+        <v>48531.38475177478</v>
       </c>
       <c r="H7" s="29" t="n">
-        <v>55190.97681120677</v>
+        <v>52710.1452280135</v>
       </c>
       <c r="I7" s="29" t="n">
-        <v>62535.48413123862</v>
+        <v>57182.60531240865</v>
       </c>
     </row>
     <row r="8">
@@ -6552,19 +6800,19 @@
         <v>-2951.0145</v>
       </c>
       <c r="E9" s="28" t="n">
-        <v>-3350.385129</v>
+        <v>-3827.313732944472</v>
       </c>
       <c r="F9" s="28" t="n">
-        <v>-3807.516948480001</v>
+        <v>-4277.236813675991</v>
       </c>
       <c r="G9" s="28" t="n">
-        <v>-4293.619860978001</v>
+        <v>-4630.181579644666</v>
       </c>
       <c r="H9" s="28" t="n">
-        <v>-4785.344810220241</v>
+        <v>-4996.104748446474</v>
       </c>
       <c r="I9" s="28" t="n">
-        <v>-5308.18579933715</v>
+        <v>-5383.171238255472</v>
       </c>
     </row>
     <row r="10">
@@ -6580,22 +6828,22 @@
         <v>29341.7</v>
       </c>
       <c r="D10" s="29" t="n">
-        <v>27964.3755</v>
+        <v>27671.07333333333</v>
       </c>
       <c r="E10" s="29" t="n">
-        <v>32470.01816448</v>
+        <v>37148.89129992964</v>
       </c>
       <c r="F10" s="29" t="n">
-        <v>37783.98509340672</v>
+        <v>40420.56147562714</v>
       </c>
       <c r="G10" s="29" t="n">
-        <v>43924.95792633666</v>
+        <v>43901.20317213011</v>
       </c>
       <c r="H10" s="29" t="n">
-        <v>50405.63200098653</v>
+        <v>47714.04047956703</v>
       </c>
       <c r="I10" s="29" t="n">
-        <v>57227.29833190147</v>
+        <v>51799.43407415318</v>
       </c>
     </row>
     <row r="11">
@@ -6673,7 +6921,7 @@
         <v>26958.7</v>
       </c>
       <c r="D13" s="28" t="n">
-        <v>25866.6355</v>
+        <v>25573.33333333333</v>
       </c>
     </row>
     <row r="14">
@@ -6689,7 +6937,7 @@
         <v>-8121.5</v>
       </c>
       <c r="D14" s="28" t="n">
-        <v>-6686.635499999997</v>
+        <v>-6393.333333333332</v>
       </c>
     </row>
     <row r="15">
@@ -6740,19 +6988,19 @@
         <v>17330</v>
       </c>
       <c r="E17" s="29" t="n">
-        <v>20159.71704309476</v>
+        <v>23330.39762588968</v>
       </c>
       <c r="F17" s="29" t="n">
-        <v>24225.27538009706</v>
+        <v>26011.97514693281</v>
       </c>
       <c r="G17" s="29" t="n">
-        <v>28808.82976942713</v>
+        <v>28792.73214597563</v>
       </c>
       <c r="H17" s="29" t="n">
-        <v>33532.11007534728</v>
+        <v>31708.12880320703</v>
       </c>
       <c r="I17" s="29" t="n">
-        <v>38445.04990129814</v>
+        <v>34766.80872871818</v>
       </c>
     </row>
     <row r="18">

--- a/engine/swdy_study/SWDY_Valuation_Model_05082026_public.xlsx
+++ b/engine/swdy_study/SWDY_Valuation_Model_05082026_public.xlsx
@@ -1064,16 +1064,16 @@
         <v>87961.92034341724</v>
       </c>
       <c r="F14" s="29" t="n">
-        <v>107470.9017036169</v>
+        <v>107096.3522839686</v>
       </c>
       <c r="G14" s="29" t="n">
-        <v>129065.4508130986</v>
+        <v>128485.4536652163</v>
       </c>
       <c r="H14" s="29" t="n">
-        <v>152846.5474155039</v>
+        <v>152455.2472744598</v>
       </c>
       <c r="I14" s="29" t="n">
-        <v>178921.6539620425</v>
+        <v>179260.9454792387</v>
       </c>
     </row>
     <row r="15">
@@ -1142,16 +1142,16 @@
         <v>27158.4765596999</v>
       </c>
       <c r="F17" s="29" t="n">
-        <v>23403.44199721687</v>
+        <v>23831.30293264496</v>
       </c>
       <c r="G17" s="29" t="n">
-        <v>15413.72612410572</v>
+        <v>16076.27720340416</v>
       </c>
       <c r="H17" s="29" t="n">
-        <v>4967.190504984501</v>
+        <v>5414.186376817659</v>
       </c>
       <c r="I17" s="29" t="n">
-        <v>-7984.413161997869</v>
+        <v>-8371.997759156626</v>
       </c>
     </row>
     <row r="18">
@@ -1788,16 +1788,16 @@
         <v>23330.39762588968</v>
       </c>
       <c r="F10" s="28" t="n">
-        <v>26011.97514693281</v>
+        <v>25512.57592073521</v>
       </c>
       <c r="G10" s="28" t="n">
-        <v>28792.73214597563</v>
+        <v>28518.80184166357</v>
       </c>
       <c r="H10" s="28" t="n">
-        <v>31708.12880320703</v>
+        <v>31959.72481232462</v>
       </c>
       <c r="I10" s="28" t="n">
-        <v>34766.80872871818</v>
+        <v>35740.93093970522</v>
       </c>
     </row>
     <row r="11">
@@ -1856,16 +1856,16 @@
         <v>27158.4765596999</v>
       </c>
       <c r="F12" s="28" t="n">
-        <v>23403.44199721687</v>
+        <v>23831.30293264496</v>
       </c>
       <c r="G12" s="28" t="n">
-        <v>15413.72612410572</v>
+        <v>16076.27720340416</v>
       </c>
       <c r="H12" s="28" t="n">
-        <v>4967.190504984501</v>
+        <v>5414.186376817659</v>
       </c>
       <c r="I12" s="28" t="n">
-        <v>-7984.413161997869</v>
+        <v>-8371.997759156626</v>
       </c>
     </row>
     <row r="13">
@@ -2603,22 +2603,22 @@
         </is>
       </c>
       <c r="B23" s="9" t="n">
-        <v>56.86120849951797</v>
+        <v>70.59325137430652</v>
       </c>
       <c r="C23" s="9" t="n">
-        <v>59.28158008715921</v>
+        <v>66.14760152455349</v>
       </c>
       <c r="D23" s="9" t="n">
         <v>61.70195167480045</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>65.57454621502646</v>
+        <v>54.58891191519561</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>71.38343802536546</v>
+        <v>43.91935227578834</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>14.52222952584749</v>
+        <v>26.67389909851818</v>
       </c>
     </row>
     <row r="24">
@@ -2628,22 +2628,22 @@
         </is>
       </c>
       <c r="B24" s="9" t="n">
-        <v>40.70537584468816</v>
+        <v>41.14097469461054</v>
       </c>
       <c r="C24" s="9" t="n">
-        <v>51.20366375974433</v>
+        <v>51.42146318470549</v>
       </c>
       <c r="D24" s="9" t="n">
         <v>61.70195167480045</v>
       </c>
       <c r="E24" s="9" t="n">
-        <v>72.20023958985661</v>
+        <v>71.98244016489542</v>
       </c>
       <c r="F24" s="9" t="n">
-        <v>82.69852750491278</v>
+        <v>82.26292865499039</v>
       </c>
       <c r="H24" s="9" t="n">
-        <v>41.99315166022461</v>
+        <v>41.12195396037985</v>
       </c>
     </row>
     <row r="25">
@@ -2653,22 +2653,22 @@
         </is>
       </c>
       <c r="B25" s="9" t="n">
-        <v>63.49802109023506</v>
+        <v>64.83401371532563</v>
       </c>
       <c r="C25" s="9" t="n">
-        <v>62.59998638251776</v>
+        <v>63.26798269506304</v>
       </c>
       <c r="D25" s="9" t="n">
         <v>61.70195167480045</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>60.80391696708316</v>
+        <v>60.13592065453789</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>59.90588225936586</v>
+        <v>58.56988963427531</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>3.592138830869196</v>
+        <v>6.264124081050312</v>
       </c>
     </row>
     <row r="26">
@@ -2809,16 +2809,16 @@
         <v>10.89809357964875</v>
       </c>
       <c r="F5" s="9" t="n">
-        <v>12.15071186905933</v>
+        <v>11.91743254017785</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v>13.44965886875394</v>
+        <v>13.32170056566091</v>
       </c>
       <c r="H5" s="9" t="n">
-        <v>14.81149873542837</v>
+        <v>14.9290242442344</v>
       </c>
       <c r="I5" s="9" t="n">
-        <v>16.24026907157657</v>
+        <v>16.69530096531379</v>
       </c>
     </row>
     <row r="6">
@@ -2840,16 +2840,16 @@
         <v>41.08876559756508</v>
       </c>
       <c r="F6" s="9" t="n">
-        <v>50.20179949935957</v>
+        <v>50.02684000269846</v>
       </c>
       <c r="G6" s="9" t="n">
-        <v>60.28904365092503</v>
+        <v>60.01811542694414</v>
       </c>
       <c r="H6" s="9" t="n">
-        <v>71.39766770249631</v>
+        <v>71.21488361011995</v>
       </c>
       <c r="I6" s="9" t="n">
-        <v>83.57786950617874</v>
+        <v>83.7363593341053</v>
       </c>
     </row>
     <row r="7">
@@ -3011,16 +3011,16 @@
         <v>0.06400551200263878</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>0.06385565049134183</v>
+        <v>0.06262969735769519</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>0.06529413206208327</v>
+        <v>0.06467293219209948</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>0.06663898560917868</v>
+        <v>0.06716774916173553</v>
       </c>
       <c r="I11" s="10" t="n">
-        <v>0.0678134644978976</v>
+        <v>0.0697135123995279</v>
       </c>
     </row>
     <row r="12">
@@ -3044,16 +3044,16 @@
         <v>0.2652329273258715</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>0.242037376951285</v>
+        <v>0.2382207738792819</v>
       </c>
       <c r="G12" s="10" t="n">
-        <v>0.223086286566889</v>
+        <v>0.2219613273575124</v>
       </c>
       <c r="H12" s="10" t="n">
-        <v>0.2074507363062016</v>
+        <v>0.2096334851288435</v>
       </c>
       <c r="I12" s="10" t="n">
-        <v>0.1943130300823947</v>
+        <v>0.1993793508349234</v>
       </c>
     </row>
     <row r="13">
@@ -3106,16 +3106,16 @@
         <v>0.6627865254459602</v>
       </c>
       <c r="F14" s="32" t="n">
-        <v>0.5235927247633061</v>
+        <v>0.5331650292571156</v>
       </c>
       <c r="G14" s="32" t="n">
-        <v>0.3176032623619305</v>
+        <v>0.3312552750272855</v>
       </c>
       <c r="H14" s="32" t="n">
-        <v>0.09423594800388868</v>
+        <v>0.1027162105776218</v>
       </c>
       <c r="I14" s="32" t="n">
-        <v>-0.1396301046161891</v>
+        <v>-0.1464081203264081</v>
       </c>
     </row>
     <row r="15">
@@ -3614,13 +3614,13 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>33.91940897889238</v>
+        <v>35.09053831893958</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>61.70195167480045</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>115.429420600699</v>
+        <v>107.0919422587579</v>
       </c>
       <c r="E5" s="8" t="n">
         <v>0.45</v>
@@ -3981,7 +3981,7 @@
         </is>
       </c>
       <c r="C6" s="9" t="n">
-        <v>33.91940897889238</v>
+        <v>35.09053831893958</v>
       </c>
     </row>
     <row r="7">
@@ -3996,7 +3996,7 @@
         </is>
       </c>
       <c r="C7" s="9" t="n">
-        <v>115.429420600699</v>
+        <v>107.0919422587579</v>
       </c>
     </row>
     <row r="8">
@@ -6991,16 +6991,16 @@
         <v>23330.39762588968</v>
       </c>
       <c r="F17" s="29" t="n">
-        <v>26011.97514693281</v>
+        <v>25512.57592073521</v>
       </c>
       <c r="G17" s="29" t="n">
-        <v>28792.73214597563</v>
+        <v>28518.80184166357</v>
       </c>
       <c r="H17" s="29" t="n">
-        <v>31708.12880320703</v>
+        <v>31959.72481232462</v>
       </c>
       <c r="I17" s="29" t="n">
-        <v>34766.80872871818</v>
+        <v>35740.93093970522</v>
       </c>
     </row>
     <row r="18">

--- a/engine/swdy_study/SWDY_Valuation_Model_05082026_public.xlsx
+++ b/engine/swdy_study/SWDY_Valuation_Model_05082026_public.xlsx
@@ -524,7 +524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I38"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="112" customWidth="1" min="1" max="1"/>
@@ -573,76 +573,76 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>every black cell is a formula; green cells link across sheets. All inputs live on the Assumptions sheet —</t>
+          <t>every black cell is a formula; green cells link across sheets.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>change one (the domestic growth path, the foreign growth path in US dollars, the exchange-rate path, the</t>
-        </is>
-      </c>
+      <c r="A7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>segment EBITDA margins, the working-capital intensity, the cost-of-capital anchors) and the whole model</t>
+          <t>IMPORTANT, so the workbook is not over-read. The Assumptions sheet is a complete REGISTER of every input</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>reprices.</t>
+          <t>and its value, not a live driver: the forecast is computed in the accompanying model and the results are</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr"/>
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>written here, so editing an Assumptions cell will NOT reprice the workbook. Formulas here aggregate,</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>How revenue is built. Not as one growth rate. Revenue splits into a domestic Egyptian-pound leg and a</t>
+          <t>cross-link and derive ratios. Every input is listed so the build can be reproduced independently, and the</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>foreign leg forecast in US dollars and translated at an explicit exchange-rate path, because more than 70%</t>
+          <t>sensitivity tables show what happens when each driver moves.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>of this company's revenue is earned outside Egypt. Margins come from a segment build; group EBITDA margin</t>
-        </is>
-      </c>
+      <c r="A13" s="3" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>is an output of that build, not an input.</t>
+          <t>How revenue is built. Not as one growth rate. Revenue splits into a domestic Egyptian-pound leg and a</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr"/>
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>foreign leg forecast in US dollars and translated at an explicit exchange-rate path, because more than 70%</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>What it is not. It is not investment advice, a recommendation, or a price target. Values are model outputs</t>
+          <t>of this company's revenue is earned outside Egypt. Margins come from a segment build; group EBITDA margin</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>shown as ranges.</t>
+          <t>is an output of that build, not an input.</t>
         </is>
       </c>
     </row>
@@ -652,126 +652,143 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Sourcing note, up front. FY2023 and FY2024 come from the company's audited consolidated statements and</t>
+          <t>What it is not. It is not investment advice, a recommendation, or a price target. Values are model outputs</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>earnings releases and are not estimated. For FY2025, revenue, profit after tax, profit after minority</t>
+          <t>shown as ranges.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>interests, total assets and net bank debt are disclosed; the intermediate income-statement lines are</t>
-        </is>
-      </c>
+      <c r="A21" s="3" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>derived by closing the profit-and-loss account to the reported profit, and the balance sheet beyond total</t>
+          <t>Sourcing note, up front. FY2023 and FY2024 come from the company's audited consolidated statements and</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>assets and net debt is triangulated by three methods. Every derived line is annotated where it appears and</t>
+          <t>earnings releases and are not estimated. For FY2025, revenue, profit after tax, profit after minority</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>listed with source and date in the companion bibliography document.</t>
+          <t>interests, total assets and net bank debt are disclosed; the intermediate income-statement lines are</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="inlineStr"/>
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>derived by closing the profit-and-loss account to the reported profit, and the balance sheet beyond total</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>Discount convention. Each explicit year is discounted at its own forward cost of capital, gliding</t>
+          <t>assets and net debt is triangulated by three methods. Every derived line is annotated where it appears and</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>26.9% -&gt; 15.1% on the same easing calendar as the interest forecast; the terminal value is</t>
+          <t>listed with source and date in the companion bibliography document.</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>capitalised at the terminal rate and discounted at the year-5 cumulative factor. One date, one price of time.</t>
-        </is>
-      </c>
+      <c r="A28" s="3" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="inlineStr"/>
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Discount convention. Each explicit year is discounted at its own forward cost of capital, gliding</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>The open question. This company earns most of its revenue in hard currency but reports, lists and borrows</t>
+          <t>26.9% -&gt; 15.1% on the same easing calendar as the interest forecast; the terminal value is</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>in Egyptian pounds. The primary model charges the full Egyptian cost of capital. The Fundamental Valuation</t>
+          <t>capitalised at the terminal rate and discounted at the year-5 cumulative factor. One date, one price of time.</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>sheet also shows what the same cash flows are worth if the hard-currency leg is discounted at a</t>
-        </is>
-      </c>
+      <c r="A32" s="3" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>hard-currency rate. Both are shown; they are not averaged.</t>
+          <t>The open question. This company earns most of its revenue in hard currency but reports, lists and borrows</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="inlineStr"/>
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>in Egyptian pounds. The primary model charges the full Egyptian cost of capital. The Fundamental Valuation</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>Currency. EGP million unless stated. Spot EGP 105.20 (2026-08-05 close). Sheets: READ FIRST · Summary ·</t>
+          <t>sheet also shows what the same cash flows are worth if the hard-currency leg is discounted at a</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>Fundamental Valuation · Assumptions · SOTP Bridge · Segments · Relative &amp; Normalized · DCF · Income</t>
+          <t>hard-currency rate. Both are shown; they are not averaged.</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>Statement · Balance Sheet · Cash Flow · Summary Financials · Monte Carlo · Sensitivity · Per-Share &amp;</t>
-        </is>
-      </c>
+      <c r="A37" s="3" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>Currency. EGP million unless stated. Spot EGP 105.20 (2026-08-05 close). Sheets: READ FIRST · Summary ·</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>Fundamental Valuation · Assumptions · SOTP Bridge · Segments · Relative &amp; Normalized · DCF · Income</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>Statement · Balance Sheet · Cash Flow · Summary Financials · Monte Carlo · Sensitivity · Per-Share &amp;</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
         <is>
           <t>Ratios · Peer &amp; Sector.</t>
         </is>
@@ -887,19 +904,19 @@
         <v>33024.2555</v>
       </c>
       <c r="E5" s="28" t="n">
-        <v>40132.12386118259</v>
+        <v>40152.59886118259</v>
       </c>
       <c r="F5" s="28" t="n">
-        <v>47668.20777099267</v>
+        <v>47710.24452099267</v>
       </c>
       <c r="G5" s="28" t="n">
-        <v>55385.17707040044</v>
+        <v>55449.64969540044</v>
       </c>
       <c r="H5" s="28" t="n">
-        <v>62760.37931810715</v>
+        <v>62846.51217785713</v>
       </c>
       <c r="I5" s="28" t="n">
-        <v>69681.59948157847</v>
+        <v>69788.10693633846</v>
       </c>
     </row>
     <row r="6">
@@ -1061,19 +1078,19 @@
         <v>70464.12212399999</v>
       </c>
       <c r="E14" s="29" t="n">
-        <v>87961.92034341724</v>
+        <v>88016.30831700345</v>
       </c>
       <c r="F14" s="29" t="n">
-        <v>107096.3522839686</v>
+        <v>107257.8480990719</v>
       </c>
       <c r="G14" s="29" t="n">
-        <v>128485.4536652163</v>
+        <v>128828.3971928497</v>
       </c>
       <c r="H14" s="29" t="n">
-        <v>152455.2472744598</v>
+        <v>153061.8093358987</v>
       </c>
       <c r="I14" s="29" t="n">
-        <v>179260.9454792387</v>
+        <v>180229.6468638956</v>
       </c>
     </row>
     <row r="15">
@@ -1108,19 +1125,19 @@
         <v>64641.27</v>
       </c>
       <c r="E16" s="28" t="n">
-        <v>83836.39605497415</v>
+        <v>84077.89605497415</v>
       </c>
       <c r="F16" s="28" t="n">
-        <v>93691.85401385502</v>
+        <v>93959.91901385502</v>
       </c>
       <c r="G16" s="28" t="n">
-        <v>101423.0250779308</v>
+        <v>101717.8965779308</v>
       </c>
       <c r="H16" s="28" t="n">
-        <v>109438.4849659704</v>
+        <v>109759.8949009704</v>
       </c>
       <c r="I16" s="28" t="n">
-        <v>117917.0842665484</v>
+        <v>118264.2069963484</v>
       </c>
     </row>
     <row r="17">
@@ -1139,19 +1156,19 @@
         <v>19789</v>
       </c>
       <c r="E17" s="29" t="n">
-        <v>27158.4765596999</v>
+        <v>27358.32227038879</v>
       </c>
       <c r="F17" s="29" t="n">
-        <v>23831.30293264496</v>
+        <v>23956.92235029294</v>
       </c>
       <c r="G17" s="29" t="n">
-        <v>16076.27720340416</v>
+        <v>16043.86491166744</v>
       </c>
       <c r="H17" s="29" t="n">
-        <v>5414.186376817659</v>
+        <v>5128.832060029791</v>
       </c>
       <c r="I17" s="29" t="n">
-        <v>-8371.997759156626</v>
+        <v>-9024.949133257413</v>
       </c>
     </row>
     <row r="18">
@@ -1196,23 +1213,27 @@
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>Balance check — assets less liabilities less equity</t>
-        </is>
-      </c>
-      <c r="B19" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" s="28" t="n">
-        <v>0</v>
+          <t>Residual: other liabilities, provisions and deferred tax not shown separately (total assets less the lines above)</t>
+        </is>
+      </c>
+      <c r="B19" s="28">
+        <f>B10-(B11+B12+B13+B14+B15)</f>
+        <v/>
+      </c>
+      <c r="C19" s="28">
+        <f>C10-(C11+C12+C13+C14+C15)</f>
+        <v/>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Note: FY2025 shows only the disclosed lines (total assets, net bank debt) plus the rolled-forward equity and the triangulated debt and cash. The valuation bridge uses only the disclosed net bank debt.</t>
+          <t>Note: this is a CONDENSED layout, so it does not foot to zero — the residual row above is the block of other liabilities, provisions, deferred tax and related-party balances that is not shown separately. For FY2024 that residual is 22,828, which reconciles to the audited statements (provisions 13,440 + 943, deferred tax 3,670, related parties 2,050 + 95, other liabilities 2,631 = 22,829). FY2025 shows only the disclosed lines (total assets, net bank debt) plus rolled-forward equity and triangulated debt and cash; the valuation bridge uses only the disclosed net bank debt.</t>
         </is>
       </c>
     </row>
@@ -1318,19 +1339,19 @@
         <v>31601.6</v>
       </c>
       <c r="D5" s="28" t="n">
-        <v>40976.20503287411</v>
+        <v>41094.2415179939</v>
       </c>
       <c r="E5" s="28" t="n">
-        <v>44697.79828930313</v>
+        <v>44940.76148621193</v>
       </c>
       <c r="F5" s="28" t="n">
-        <v>48531.38475177478</v>
+        <v>48914.41709217701</v>
       </c>
       <c r="G5" s="28" t="n">
-        <v>52710.1452280135</v>
+        <v>53240.26178029377</v>
       </c>
       <c r="H5" s="28" t="n">
-        <v>57182.60531240865</v>
+        <v>57882.44686110957</v>
       </c>
     </row>
     <row r="6">
@@ -1391,19 +1412,19 @@
         <v>-8765.700000000001</v>
       </c>
       <c r="D9" s="28" t="n">
-        <v>-10935.18209412706</v>
+        <v>-10966.68209412706</v>
       </c>
       <c r="E9" s="28" t="n">
-        <v>-11813.32072348607</v>
+        <v>-11847.12022348607</v>
       </c>
       <c r="F9" s="28" t="n">
-        <v>-12347.15087905244</v>
+        <v>-12383.04827905244</v>
       </c>
       <c r="G9" s="28" t="n">
-        <v>-12371.30699615317</v>
+        <v>-12407.64029315317</v>
       </c>
       <c r="H9" s="28" t="n">
-        <v>-12304.39140172679</v>
+        <v>-12340.61290396679</v>
       </c>
     </row>
     <row r="10">
@@ -1421,19 +1442,19 @@
         <v>-16840.00000000001</v>
       </c>
       <c r="D10" s="28" t="n">
-        <v>-19195.12605497414</v>
+        <v>-19436.62605497414</v>
       </c>
       <c r="E10" s="28" t="n">
-        <v>-9855.45795888087</v>
+        <v>-9882.022958880872</v>
       </c>
       <c r="F10" s="28" t="n">
-        <v>-7731.171064075766</v>
+        <v>-7757.977564075773</v>
       </c>
       <c r="G10" s="28" t="n">
-        <v>-8015.459888039608</v>
+        <v>-8041.998323039588</v>
       </c>
       <c r="H10" s="28" t="n">
-        <v>-8478.599300578047</v>
+        <v>-8504.31209537806</v>
       </c>
     </row>
     <row r="11">
@@ -1453,19 +1474,19 @@
         </is>
       </c>
       <c r="D11" s="28" t="n">
-        <v>27861.66847494723</v>
+        <v>27941.92708878707</v>
       </c>
       <c r="E11" s="28" t="n">
-        <v>30315.42110672035</v>
+        <v>30488.46519190195</v>
       </c>
       <c r="F11" s="28" t="n">
-        <v>32925.90237909758</v>
+        <v>33203.08049064926</v>
       </c>
       <c r="G11" s="28" t="n">
-        <v>35785.53035967527</v>
+        <v>36172.11297719798</v>
       </c>
       <c r="H11" s="28" t="n">
-        <v>38849.57555561488</v>
+        <v>39362.57153671807</v>
       </c>
     </row>
     <row r="12">
@@ -1485,19 +1506,19 @@
         </is>
       </c>
       <c r="D12" s="29" t="n">
-        <v>1558.674058790493</v>
+        <v>1376.957672630335</v>
       </c>
       <c r="E12" s="29" t="n">
-        <v>12923.87923802941</v>
+        <v>13048.796573211</v>
       </c>
       <c r="F12" s="29" t="n">
-        <v>17477.76201561404</v>
+        <v>17705.69775216571</v>
       </c>
       <c r="G12" s="29" t="n">
-        <v>20394.86822392896</v>
+        <v>20733.25217170169</v>
       </c>
       <c r="H12" s="29" t="n">
-        <v>23449.75609156551</v>
+        <v>23916.66468285869</v>
       </c>
       <c r="I12" s="14" t="n"/>
     </row>
@@ -1628,19 +1649,19 @@
         <v>281049</v>
       </c>
       <c r="E5" s="28" t="n">
-        <v>364506.0698042354</v>
+        <v>365556.0698042354</v>
       </c>
       <c r="F5" s="28" t="n">
-        <v>407355.8870167609</v>
+        <v>408521.3870167609</v>
       </c>
       <c r="G5" s="28" t="n">
-        <v>440969.6742518729</v>
+        <v>442251.724251873</v>
       </c>
       <c r="H5" s="28" t="n">
-        <v>475819.4998520451</v>
+        <v>477216.9343520451</v>
       </c>
       <c r="I5" s="28" t="n">
-        <v>512682.9750719497</v>
+        <v>514192.2043319497</v>
       </c>
     </row>
     <row r="6">
@@ -1661,19 +1682,19 @@
         <v>0.2115131445656513</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>0.29694846736418</v>
+        <v>0.3006844706945602</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>0.1175558399769276</v>
+        <v>0.1175341370628438</v>
       </c>
       <c r="G6" s="10" t="n">
-        <v>0.08251700369738102</v>
+        <v>0.08256688219294661</v>
       </c>
       <c r="H6" s="10" t="n">
-        <v>0.07902998241159476</v>
+        <v>0.07906178355623239</v>
       </c>
       <c r="I6" s="10" t="n">
-        <v>0.077473653835892</v>
+        <v>0.07748105173616437</v>
       </c>
     </row>
     <row r="7">
@@ -1692,19 +1713,19 @@
         <v>30622.08783333333</v>
       </c>
       <c r="E7" s="28" t="n">
-        <v>40976.20503287411</v>
+        <v>41094.2415179939</v>
       </c>
       <c r="F7" s="28" t="n">
-        <v>44697.79828930313</v>
+        <v>44940.76148621193</v>
       </c>
       <c r="G7" s="28" t="n">
-        <v>48531.38475177478</v>
+        <v>48914.41709217701</v>
       </c>
       <c r="H7" s="28" t="n">
-        <v>52710.1452280135</v>
+        <v>53240.26178029377</v>
       </c>
       <c r="I7" s="28" t="n">
-        <v>57182.60531240865</v>
+        <v>57882.44686110957</v>
       </c>
     </row>
     <row r="8">
@@ -1726,16 +1747,16 @@
         <v>0.112415700114078</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>0.1097266535575169</v>
+        <v>0.1100083445187365</v>
       </c>
       <c r="G8" s="10" t="n">
-        <v>0.1100560596011748</v>
+        <v>0.1106031122318905</v>
       </c>
       <c r="H8" s="10" t="n">
-        <v>0.1107776063074413</v>
+        <v>0.1115640664608482</v>
       </c>
       <c r="I8" s="10" t="n">
-        <v>0.1115359941577613</v>
+        <v>0.1125696702000991</v>
       </c>
     </row>
     <row r="9">
@@ -1754,19 +1775,19 @@
         <v>27671.07333333333</v>
       </c>
       <c r="E9" s="28" t="n">
-        <v>37148.89129992964</v>
+        <v>37255.90278504942</v>
       </c>
       <c r="F9" s="28" t="n">
-        <v>40420.56147562714</v>
+        <v>40651.28692253594</v>
       </c>
       <c r="G9" s="28" t="n">
-        <v>43901.20317213011</v>
+        <v>44270.77398753235</v>
       </c>
       <c r="H9" s="28" t="n">
-        <v>47714.04047956703</v>
+        <v>48229.4839695973</v>
       </c>
       <c r="I9" s="28" t="n">
-        <v>51799.43407415318</v>
+        <v>52483.42871562409</v>
       </c>
     </row>
     <row r="10">
@@ -1785,19 +1806,19 @@
         <v>17330</v>
       </c>
       <c r="E10" s="28" t="n">
-        <v>23330.39762588968</v>
+        <v>23402.91492400461</v>
       </c>
       <c r="F10" s="28" t="n">
-        <v>25512.57592073521</v>
+        <v>25655.38637609128</v>
       </c>
       <c r="G10" s="28" t="n">
-        <v>28518.80184166357</v>
+        <v>28760.73212503701</v>
       </c>
       <c r="H10" s="28" t="n">
-        <v>31959.72481232462</v>
+        <v>32311.21619073199</v>
       </c>
       <c r="I10" s="28" t="n">
-        <v>35740.93093970522</v>
+        <v>36223.78337066263</v>
       </c>
     </row>
     <row r="11">
@@ -1822,19 +1843,19 @@
         </is>
       </c>
       <c r="E11" s="28" t="n">
-        <v>1558.674058790493</v>
+        <v>1376.957672630335</v>
       </c>
       <c r="F11" s="28" t="n">
-        <v>12923.87923802941</v>
+        <v>13048.796573211</v>
       </c>
       <c r="G11" s="28" t="n">
-        <v>17477.76201561404</v>
+        <v>17705.69775216571</v>
       </c>
       <c r="H11" s="28" t="n">
-        <v>20394.86822392896</v>
+        <v>20733.25217170169</v>
       </c>
       <c r="I11" s="28" t="n">
-        <v>23449.75609156551</v>
+        <v>23916.66468285869</v>
       </c>
     </row>
     <row r="12">
@@ -1853,19 +1874,19 @@
         <v>19789</v>
       </c>
       <c r="E12" s="28" t="n">
-        <v>27158.4765596999</v>
+        <v>27358.32227038879</v>
       </c>
       <c r="F12" s="28" t="n">
-        <v>23831.30293264496</v>
+        <v>23956.92235029294</v>
       </c>
       <c r="G12" s="28" t="n">
-        <v>16076.27720340416</v>
+        <v>16043.86491166744</v>
       </c>
       <c r="H12" s="28" t="n">
-        <v>5414.186376817659</v>
+        <v>5128.832060029791</v>
       </c>
       <c r="I12" s="28" t="n">
-        <v>-8371.997759156626</v>
+        <v>-9024.949133257413</v>
       </c>
     </row>
     <row r="13">
@@ -1890,19 +1911,19 @@
         </is>
       </c>
       <c r="E13" s="28" t="n">
-        <v>125427.7199161567</v>
+        <v>125689.6949161567</v>
       </c>
       <c r="F13" s="28" t="n">
-        <v>142819.2617848477</v>
+        <v>143129.3635348477</v>
       </c>
       <c r="G13" s="28" t="n">
-        <v>158267.4021483312</v>
+        <v>158626.7462733312</v>
       </c>
       <c r="H13" s="28" t="n">
-        <v>173658.0642840776</v>
+        <v>174065.6070788275</v>
       </c>
       <c r="I13" s="28" t="n">
-        <v>189057.8837481269</v>
+        <v>189511.5139326869</v>
       </c>
     </row>
     <row r="14">
@@ -1927,19 +1948,19 @@
         </is>
       </c>
       <c r="E14" s="10" t="n">
-        <v>0.2221332612405902</v>
+        <v>0.2223088146361256</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>0.2122642333244201</v>
+        <v>0.2130133498740734</v>
       </c>
       <c r="G14" s="10" t="n">
-        <v>0.2080396969442817</v>
+        <v>0.2093157760005789</v>
       </c>
       <c r="H14" s="10" t="n">
-        <v>0.2060689234744418</v>
+        <v>0.2078073525507945</v>
       </c>
       <c r="I14" s="10" t="n">
-        <v>0.2054903756744277</v>
+        <v>0.2077054355161732</v>
       </c>
     </row>
   </sheetData>
@@ -2284,19 +2305,19 @@
         </is>
       </c>
       <c r="B6" s="9" t="n">
-        <v>70.33785026611987</v>
+        <v>71.40604255139132</v>
       </c>
       <c r="C6" s="9" t="n">
-        <v>73.67916459076592</v>
+        <v>74.8455484835976</v>
       </c>
       <c r="D6" s="9" t="n">
-        <v>77.75959437327495</v>
+        <v>79.04809647022493</v>
       </c>
       <c r="E6" s="9" t="n">
-        <v>82.88964883834787</v>
+        <v>84.3342475199925</v>
       </c>
       <c r="F6" s="9" t="n">
-        <v>89.58209041029527</v>
+        <v>91.23336316838652</v>
       </c>
     </row>
     <row r="7">
@@ -2306,19 +2327,19 @@
         </is>
       </c>
       <c r="B7" s="9" t="n">
-        <v>63.5344468678846</v>
+        <v>64.49978173034609</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>65.96239254313653</v>
+        <v>67.00642468255586</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>68.85048182392777</v>
+        <v>69.99025922223638</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>72.36827997455242</v>
+        <v>73.62713288192815</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>76.78033350243246</v>
+        <v>78.19139342245379</v>
       </c>
     </row>
     <row r="8">
@@ -2328,19 +2349,19 @@
         </is>
       </c>
       <c r="B8" s="9" t="n">
-        <v>57.85893383172429</v>
+        <v>58.73840333856804</v>
       </c>
       <c r="C8" s="9" t="n">
-        <v>59.63644342622118</v>
+        <v>60.5801332665243</v>
       </c>
       <c r="D8" s="9" t="n">
-        <v>61.70195167480045</v>
+        <v>62.72237722300294</v>
       </c>
       <c r="E8" s="9" t="n">
-        <v>64.14997733495557</v>
+        <v>65.26376140705965</v>
       </c>
       <c r="F8" s="9" t="n">
-        <v>67.12148002279349</v>
+        <v>68.35137102723559</v>
       </c>
     </row>
     <row r="9">
@@ -2350,19 +2371,19 @@
         </is>
       </c>
       <c r="B9" s="9" t="n">
-        <v>53.05352385509302</v>
+        <v>53.86023933636113</v>
       </c>
       <c r="C9" s="9" t="n">
-        <v>54.35740254637418</v>
+        <v>55.21731960809319</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>55.83973620233307</v>
+        <v>56.76227199734095</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>57.55331694347389</v>
+        <v>58.55067448976136</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>59.57403813546187</v>
+        <v>60.66242537979906</v>
       </c>
     </row>
     <row r="10">
@@ -2372,19 +2393,19 @@
         </is>
       </c>
       <c r="B10" s="9" t="n">
-        <v>48.93336177056653</v>
+        <v>49.67765160561232</v>
       </c>
       <c r="C10" s="9" t="n">
-        <v>49.88605070421014</v>
+        <v>50.67498049644503</v>
       </c>
       <c r="D10" s="9" t="n">
-        <v>50.94582955927424</v>
+        <v>51.78663329144614</v>
       </c>
       <c r="E10" s="9" t="n">
-        <v>52.14153504379775</v>
+        <v>53.04339463405028</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>53.51337817132742</v>
+        <v>54.48819181375644</v>
       </c>
     </row>
     <row r="12">
@@ -2429,19 +2450,19 @@
         </is>
       </c>
       <c r="B14" s="9" t="n">
-        <v>82.30413193593803</v>
+        <v>83.66571992603276</v>
       </c>
       <c r="C14" s="9" t="n">
-        <v>79.99134516193502</v>
+        <v>81.31573210887528</v>
       </c>
       <c r="D14" s="9" t="n">
-        <v>77.75959437327495</v>
+        <v>79.04809647022493</v>
       </c>
       <c r="E14" s="9" t="n">
-        <v>75.60531904976452</v>
+        <v>76.8591944099261</v>
       </c>
       <c r="F14" s="9" t="n">
-        <v>73.52514768373331</v>
+        <v>74.74559943059796</v>
       </c>
     </row>
     <row r="15">
@@ -2451,19 +2472,19 @@
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>72.8886819346058</v>
+        <v>74.09309219727253</v>
       </c>
       <c r="C15" s="9" t="n">
-        <v>70.83367768088289</v>
+        <v>72.00519044120513</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>68.85048182392777</v>
+        <v>69.99025922223638</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>66.9359453582495</v>
+        <v>68.04509832510135</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>65.08708620594727</v>
+        <v>66.16667718367351</v>
       </c>
     </row>
     <row r="16">
@@ -2473,19 +2494,19 @@
         </is>
       </c>
       <c r="B16" s="9" t="n">
-        <v>65.33406077050365</v>
+        <v>66.41233867790525</v>
       </c>
       <c r="C16" s="9" t="n">
-        <v>63.48580082611725</v>
+        <v>64.53463324396715</v>
       </c>
       <c r="D16" s="9" t="n">
-        <v>61.70195167480045</v>
+        <v>62.72237722300294</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>59.97969409530537</v>
+        <v>60.97270569052243</v>
       </c>
       <c r="F16" s="9" t="n">
-        <v>58.31635810092311</v>
+        <v>59.28290538269756</v>
       </c>
     </row>
     <row r="17">
@@ -2495,19 +2516,19 @@
         </is>
       </c>
       <c r="B17" s="9" t="n">
-        <v>59.13899137370171</v>
+        <v>60.11382102859078</v>
       </c>
       <c r="C17" s="9" t="n">
-        <v>57.46018877233019</v>
+        <v>58.40840279419519</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>55.83973620233307</v>
+        <v>56.76227199734095</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>54.27508452482181</v>
+        <v>55.17283830621533</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>52.76381935034907</v>
+        <v>53.63764832267511</v>
       </c>
     </row>
     <row r="18">
@@ -2517,19 +2538,19 @@
         </is>
       </c>
       <c r="B18" s="9" t="n">
-        <v>53.96735779694362</v>
+        <v>54.85581681153326</v>
       </c>
       <c r="C18" s="9" t="n">
-        <v>52.42994594952477</v>
+        <v>53.29415083110127</v>
       </c>
       <c r="D18" s="9" t="n">
-        <v>50.94582955927424</v>
+        <v>51.78663329144614</v>
       </c>
       <c r="E18" s="9" t="n">
-        <v>49.51268463786545</v>
+        <v>50.33090277179734</v>
       </c>
       <c r="F18" s="9" t="n">
-        <v>48.12830987545653</v>
+        <v>48.92472251249137</v>
       </c>
     </row>
     <row r="20">
@@ -2575,25 +2596,25 @@
         </is>
       </c>
       <c r="B22" s="9" t="n">
-        <v>84.75563520629989</v>
+        <v>86.15763153561919</v>
       </c>
       <c r="C22" s="9" t="n">
-        <v>72.055512422107</v>
+        <v>73.24713700573579</v>
       </c>
       <c r="D22" s="9" t="n">
-        <v>62.0992379086121</v>
+        <v>63.12622637075465</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>61.70195167480045</v>
+        <v>62.72237722300294</v>
       </c>
       <c r="F22" s="9" t="n">
-        <v>55.95111872909561</v>
+        <v>56.87661209559251</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>50.67676982890725</v>
+        <v>51.51532544021109</v>
       </c>
       <c r="H22" s="9" t="n">
-        <v>34.07886537739263</v>
+        <v>34.6423060954081</v>
       </c>
     </row>
     <row r="23">
@@ -2603,19 +2624,19 @@
         </is>
       </c>
       <c r="B23" s="9" t="n">
-        <v>70.59325137430652</v>
+        <v>71.61367692250901</v>
       </c>
       <c r="C23" s="9" t="n">
-        <v>66.14760152455349</v>
+        <v>67.16802707275598</v>
       </c>
       <c r="D23" s="9" t="n">
-        <v>61.70195167480045</v>
+        <v>62.72237722300294</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>54.58891191519561</v>
+        <v>55.60933746339811</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>43.91935227578834</v>
+        <v>44.93977782399083</v>
       </c>
       <c r="H23" s="9" t="n">
         <v>26.67389909851818</v>
@@ -2628,22 +2649,22 @@
         </is>
       </c>
       <c r="B24" s="9" t="n">
-        <v>41.14097469461054</v>
+        <v>41.84129022062721</v>
       </c>
       <c r="C24" s="9" t="n">
-        <v>51.42146318470549</v>
+        <v>52.28183372181507</v>
       </c>
       <c r="D24" s="9" t="n">
-        <v>61.70195167480045</v>
+        <v>62.72237722300294</v>
       </c>
       <c r="E24" s="9" t="n">
-        <v>71.98244016489542</v>
+        <v>73.16292072419081</v>
       </c>
       <c r="F24" s="9" t="n">
-        <v>82.26292865499039</v>
+        <v>83.60346422537874</v>
       </c>
       <c r="H24" s="9" t="n">
-        <v>41.12195396037985</v>
+        <v>41.76217400475154</v>
       </c>
     </row>
     <row r="25">
@@ -2653,22 +2674,22 @@
         </is>
       </c>
       <c r="B25" s="9" t="n">
-        <v>64.83401371532563</v>
+        <v>65.87180866666164</v>
       </c>
       <c r="C25" s="9" t="n">
-        <v>63.26798269506304</v>
+        <v>64.2970929448323</v>
       </c>
       <c r="D25" s="9" t="n">
-        <v>61.70195167480045</v>
+        <v>62.72237722300294</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>60.13592065453789</v>
+        <v>61.1476615011736</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>58.56988963427531</v>
+        <v>59.57294577934427</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>6.264124081050312</v>
+        <v>6.298862887317362</v>
       </c>
     </row>
     <row r="26">
@@ -2678,22 +2699,22 @@
         </is>
       </c>
       <c r="B26" s="9" t="n">
-        <v>55.62682821155775</v>
+        <v>56.38958884826296</v>
       </c>
       <c r="C26" s="9" t="n">
-        <v>59.37636551887614</v>
+        <v>60.18863757345764</v>
       </c>
       <c r="D26" s="9" t="n">
-        <v>61.70195167480045</v>
+        <v>62.72237722300294</v>
       </c>
       <c r="E26" s="9" t="n">
-        <v>65.14488445321211</v>
+        <v>66.03332791991097</v>
       </c>
       <c r="F26" s="9" t="n">
-        <v>66.87544013351288</v>
+        <v>67.78673502384697</v>
       </c>
       <c r="H26" s="9" t="n">
-        <v>11.24861192195513</v>
+        <v>11.39714617558401</v>
       </c>
     </row>
   </sheetData>
@@ -2806,19 +2827,19 @@
         <v>8.095188293136117</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>10.89809357964875</v>
+        <v>10.93196785447563</v>
       </c>
       <c r="F5" s="9" t="n">
-        <v>11.91743254017785</v>
+        <v>11.98414214931436</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v>13.32170056566091</v>
+        <v>13.43471102138623</v>
       </c>
       <c r="H5" s="9" t="n">
-        <v>14.9290242442344</v>
+        <v>15.09321287040991</v>
       </c>
       <c r="I5" s="9" t="n">
-        <v>16.69530096531379</v>
+        <v>16.92085095645048</v>
       </c>
     </row>
     <row r="6">
@@ -2837,19 +2858,19 @@
         <v>32.91519541282852</v>
       </c>
       <c r="E6" s="9" t="n">
-        <v>41.08876559756508</v>
+        <v>41.11417130368525</v>
       </c>
       <c r="F6" s="9" t="n">
-        <v>50.02684000269846</v>
+        <v>50.10227791567102</v>
       </c>
       <c r="G6" s="9" t="n">
-        <v>60.01811542694414</v>
+        <v>60.17831118171069</v>
       </c>
       <c r="H6" s="9" t="n">
-        <v>71.21488361011995</v>
+        <v>71.49822083451812</v>
       </c>
       <c r="I6" s="9" t="n">
-        <v>83.7363593341053</v>
+        <v>84.18885905185599</v>
       </c>
     </row>
     <row r="7">
@@ -2874,19 +2895,19 @@
         </is>
       </c>
       <c r="E7" s="9" t="n">
-        <v>0.7280877088018324</v>
+        <v>0.6432043642020219</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>6.037001495072163</v>
+        <v>6.095352871262111</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>8.16421087472694</v>
+        <v>8.270684198796207</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>9.526849306774581</v>
+        <v>9.684915190940478</v>
       </c>
       <c r="I7" s="9" t="n">
-        <v>10.95384829713436</v>
+        <v>11.17195060308942</v>
       </c>
     </row>
     <row r="8">
@@ -2949,16 +2970,16 @@
         <v>0.112415700114078</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>0.1097266535575169</v>
+        <v>0.1100083445187365</v>
       </c>
       <c r="G9" s="10" t="n">
-        <v>0.1100560596011748</v>
+        <v>0.1106031122318905</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>0.1107776063074413</v>
+        <v>0.1115640664608482</v>
       </c>
       <c r="I9" s="10" t="n">
-        <v>0.1115359941577613</v>
+        <v>0.1125696702000991</v>
       </c>
     </row>
     <row r="10">
@@ -2980,16 +3001,16 @@
         <v>0.101915700114078</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>0.09922665355751691</v>
+        <v>0.09950834451873651</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>0.09955605960117482</v>
+        <v>0.1001031122318905</v>
       </c>
       <c r="H10" s="10" t="n">
-        <v>0.1002776063074413</v>
+        <v>0.1010640664608482</v>
       </c>
       <c r="I10" s="10" t="n">
-        <v>0.1010359941577613</v>
+        <v>0.1020696702000991</v>
       </c>
     </row>
     <row r="11">
@@ -3008,19 +3029,19 @@
         <v>0.06166184544332127</v>
       </c>
       <c r="E11" s="10" t="n">
-        <v>0.06400551200263878</v>
+        <v>0.06402004195016504</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>0.06262969735769519</v>
+        <v>0.06280059549254072</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>0.06467293219209948</v>
+        <v>0.06503249291721717</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>0.06716774916173553</v>
+        <v>0.06770760604839697</v>
       </c>
       <c r="I11" s="10" t="n">
-        <v>0.0697135123995279</v>
+        <v>0.07044794352284163</v>
       </c>
     </row>
     <row r="12">
@@ -3041,19 +3062,19 @@
         <v>0.2756503065994848</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>0.2652329273258715</v>
+        <v>0.2658929392916098</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>0.2382207738792819</v>
+        <v>0.2391935586139479</v>
       </c>
       <c r="G12" s="10" t="n">
-        <v>0.2219613273575124</v>
+        <v>0.2232483889556092</v>
       </c>
       <c r="H12" s="10" t="n">
-        <v>0.2096334851288435</v>
+        <v>0.2110991391707913</v>
       </c>
       <c r="I12" s="10" t="n">
-        <v>0.1993793508349234</v>
+        <v>0.2009868187669358</v>
       </c>
     </row>
     <row r="13">
@@ -3072,19 +3093,19 @@
         <v>0.2093655734764178</v>
       </c>
       <c r="E13" s="10" t="n">
-        <v>0.2221332612405902</v>
+        <v>0.2223088146361256</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>0.2122642333244201</v>
+        <v>0.2130133498740734</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>0.2080396969442817</v>
+        <v>0.2093157760005789</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>0.2060689234744418</v>
+        <v>0.2078073525507945</v>
       </c>
       <c r="I13" s="10" t="n">
-        <v>0.2054903756744277</v>
+        <v>0.2077054355161732</v>
       </c>
     </row>
     <row r="14">
@@ -3103,19 +3124,19 @@
         <v>0.6462328796032941</v>
       </c>
       <c r="E14" s="32" t="n">
-        <v>0.6627865254459602</v>
+        <v>0.6657458870097267</v>
       </c>
       <c r="F14" s="32" t="n">
-        <v>0.5331650292571156</v>
+        <v>0.53307780193362</v>
       </c>
       <c r="G14" s="32" t="n">
-        <v>0.3312552750272855</v>
+        <v>0.3279986937477656</v>
       </c>
       <c r="H14" s="32" t="n">
-        <v>0.1027162105776218</v>
+        <v>0.09633371227953212</v>
       </c>
       <c r="I14" s="32" t="n">
-        <v>-0.1464081203264081</v>
+        <v>-0.1559185836582377</v>
       </c>
     </row>
     <row r="15">
@@ -3614,13 +3635,13 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>35.09053831893958</v>
+        <v>35.60479630603451</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>61.70195167480045</v>
+        <v>62.72237722300294</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>107.0919422587579</v>
+        <v>108.9676974718246</v>
       </c>
       <c r="E5" s="8" t="n">
         <v>0.45</v>
@@ -3641,13 +3662,13 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>98.54941705689527</v>
+        <v>99.11342021383139</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>117.4147503958174</v>
+        <v>118.0812995812873</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>145.7127504042006</v>
+        <v>146.5331186324713</v>
       </c>
       <c r="E6" s="8" t="n">
         <v>0.2</v>
@@ -3668,13 +3689,13 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>84.26500301112208</v>
+        <v>94.15599509791565</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>108.340718157157</v>
+        <v>121.0577079830344</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>138.4353620897006</v>
+        <v>154.6848490894329</v>
       </c>
       <c r="E7" s="8" t="n">
         <v>0.2</v>
@@ -3981,7 +4002,7 @@
         </is>
       </c>
       <c r="C6" s="9" t="n">
-        <v>35.09053831893958</v>
+        <v>35.60479630603451</v>
       </c>
     </row>
     <row r="7">
@@ -3996,7 +4017,7 @@
         </is>
       </c>
       <c r="C7" s="9" t="n">
-        <v>107.0919422587579</v>
+        <v>108.9676974718246</v>
       </c>
     </row>
     <row r="8">
@@ -4073,7 +4094,7 @@
         </is>
       </c>
       <c r="C15" s="8" t="n">
-        <v>0.6026295957756825</v>
+        <v>0.600860789848202</v>
       </c>
     </row>
     <row r="16">
@@ -4105,7 +4126,7 @@
         </is>
       </c>
       <c r="C18" s="22" t="n">
-        <v>108.2656760498812</v>
+        <v>90.38294164821865</v>
       </c>
     </row>
     <row r="19">
@@ -4164,13 +4185,13 @@
         </is>
       </c>
       <c r="C23" s="9" t="n">
-        <v>137.2890386682185</v>
+        <v>137.7034929664235</v>
       </c>
       <c r="D23" s="9" t="n">
-        <v>101.1603442818452</v>
+        <v>101.4657316594699</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>173.4177330545918</v>
+        <v>173.941254273377</v>
       </c>
     </row>
     <row r="24">
@@ -4185,13 +4206,13 @@
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>45.39027567108655</v>
+        <v>46.2389872519482</v>
       </c>
       <c r="D24" s="9" t="n">
-        <v>31.51950561814614</v>
+        <v>32.10886025513935</v>
       </c>
       <c r="E24" s="9" t="n">
-        <v>64.97585625854424</v>
+        <v>66.19078084024615</v>
       </c>
     </row>
     <row r="25">
@@ -4206,13 +4227,13 @@
         </is>
       </c>
       <c r="C25" s="9" t="n">
-        <v>55.09900810054334</v>
+        <v>56.08425905816016</v>
       </c>
       <c r="D25" s="9" t="n">
-        <v>46.82211783514564</v>
+        <v>47.37467423206117</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>108.2656760498812</v>
+        <v>90.38294164821865</v>
       </c>
     </row>
     <row r="26">
@@ -5291,13 +5312,13 @@
         </is>
       </c>
       <c r="B5" s="28" t="n">
-        <v>99104.38752626561</v>
+        <v>92138.29685490194</v>
       </c>
       <c r="C5" s="10" t="n">
-        <v>0.3526231636699138</v>
+        <v>0.3278371275290143</v>
       </c>
       <c r="D5" s="8" t="n">
-        <v>0.1375659154735564</v>
+        <v>0.1479665487953016</v>
       </c>
       <c r="E5" s="28" t="n">
         <v>145610.3678770696</v>
@@ -5328,7 +5349,7 @@
         <v>0.2150799438713465</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>0.1347135486293534</v>
+        <v>0.1239697053155375</v>
       </c>
       <c r="E6" s="28" t="n">
         <v>86793.07467340285</v>
@@ -5353,13 +5374,13 @@
         </is>
       </c>
       <c r="B7" s="28" t="n">
-        <v>87553</v>
+        <v>87100.7</v>
       </c>
       <c r="C7" s="10" t="n">
-        <v>0.3115221900807332</v>
+        <v>0.3099128621699419</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>0.09770663311824808</v>
+        <v>0.08991421158660849</v>
       </c>
       <c r="E7" s="28" t="n">
         <v>87399</v>
@@ -5384,13 +5405,13 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>12254.56652975496</v>
+        <v>17703.5</v>
       </c>
       <c r="C8" s="10" t="n">
-        <v>0.04360295368336113</v>
+        <v>0.06299079519941363</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>0.3009934715480775</v>
+        <v>0.2769882639821222</v>
       </c>
       <c r="E8" s="28" t="n">
         <v>20025.95817760357</v>
@@ -5415,13 +5436,13 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>15562.14279888138</v>
+        <v>16594.1</v>
       </c>
       <c r="C9" s="10" t="n">
-        <v>0.05537163554711592</v>
+        <v>0.05904344082348629</v>
       </c>
       <c r="D9" s="8" t="n">
-        <v>0.2379981199493308</v>
+        <v>0.2190169964043364</v>
       </c>
       <c r="E9" s="28" t="n">
         <v>17815.54107615941</v>
@@ -5452,7 +5473,7 @@
         <v>0.01140904255129888</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>0.4430145873816911</v>
+        <v>0.4076827342682428</v>
       </c>
       <c r="E10" s="28" t="n">
         <v>3591.28</v>
@@ -5477,28 +5498,28 @@
         </is>
       </c>
       <c r="B11" s="28" t="n">
-        <v>2920.4</v>
+        <v>3857.9</v>
       </c>
       <c r="C11" s="10" t="n">
-        <v>0.01039107059623055</v>
+        <v>0.01372678785549851</v>
       </c>
       <c r="D11" s="8" t="n">
-        <v>0.5396893633758121</v>
+        <v>0.4966473826898447</v>
       </c>
       <c r="E11" s="28" t="n">
-        <v>3270.848</v>
+        <v>4320.848000000001</v>
       </c>
       <c r="F11" s="28" t="n">
-        <v>3630.641280000001</v>
+        <v>4796.141280000002</v>
       </c>
       <c r="G11" s="28" t="n">
-        <v>3993.705408000001</v>
+        <v>5275.755408000002</v>
       </c>
       <c r="H11" s="28" t="n">
-        <v>4353.138894720001</v>
+        <v>5750.573394720002</v>
       </c>
       <c r="I11" s="28" t="n">
-        <v>4701.390006297602</v>
+        <v>6210.619266297603</v>
       </c>
     </row>
     <row r="12">
@@ -5576,19 +5597,19 @@
         </is>
       </c>
       <c r="B15" s="28" t="n">
-        <v>20065.66069631773</v>
+        <v>20041.67909882659</v>
       </c>
       <c r="C15" s="28" t="n">
-        <v>22086.62539523002</v>
+        <v>22059.43026367506</v>
       </c>
       <c r="D15" s="28" t="n">
-        <v>24207.98665540832</v>
+        <v>24177.58249832987</v>
       </c>
       <c r="E15" s="28" t="n">
-        <v>26607.16385761438</v>
+        <v>26573.33011161748</v>
       </c>
       <c r="F15" s="28" t="n">
-        <v>29284.17856903834</v>
+        <v>29246.528376493</v>
       </c>
     </row>
     <row r="16">
@@ -5598,19 +5619,19 @@
         </is>
       </c>
       <c r="B16" s="28" t="n">
-        <v>5717.024411740862</v>
+        <v>4984.191943840839</v>
       </c>
       <c r="C16" s="28" t="n">
-        <v>6027.081379127109</v>
+        <v>5203.963951181807</v>
       </c>
       <c r="D16" s="28" t="n">
-        <v>6389.982936055597</v>
+        <v>5478.586163963156</v>
       </c>
       <c r="E16" s="28" t="n">
-        <v>6850.441956388367</v>
+        <v>5845.99157386529</v>
       </c>
       <c r="F16" s="28" t="n">
-        <v>7363.89485725309</v>
+        <v>6256.890090674406</v>
       </c>
     </row>
     <row r="17">
@@ -5620,19 +5641,19 @@
         </is>
       </c>
       <c r="B17" s="28" t="n">
-        <v>5043.502027901764</v>
+        <v>4362.452178457996</v>
       </c>
       <c r="C17" s="28" t="n">
-        <v>5095.893502382363</v>
+        <v>4391.333307654424</v>
       </c>
       <c r="D17" s="28" t="n">
-        <v>5060.044823827177</v>
+        <v>4339.414342204866</v>
       </c>
       <c r="E17" s="28" t="n">
-        <v>4997.527281321682</v>
+        <v>4271.928516198092</v>
       </c>
       <c r="F17" s="28" t="n">
-        <v>4838.414070830325</v>
+        <v>4116.855111747494</v>
       </c>
     </row>
     <row r="18">
@@ -5642,19 +5663,19 @@
         </is>
       </c>
       <c r="B18" s="28" t="n">
-        <v>3521.198143901805</v>
+        <v>4945.072489759165</v>
       </c>
       <c r="C18" s="28" t="n">
-        <v>3975.499149786538</v>
+        <v>5620.928343859304</v>
       </c>
       <c r="D18" s="28" t="n">
-        <v>4460.820904690448</v>
+        <v>6335.787471336365</v>
       </c>
       <c r="E18" s="28" t="n">
-        <v>4963.925875726681</v>
+        <v>7070.450813353369</v>
       </c>
       <c r="F18" s="28" t="n">
-        <v>5529.754501223622</v>
+        <v>7896.435268647207</v>
       </c>
     </row>
     <row r="19">
@@ -5664,19 +5685,19 @@
         </is>
       </c>
       <c r="B19" s="28" t="n">
-        <v>3547.073570820779</v>
+        <v>3467.290226985804</v>
       </c>
       <c r="C19" s="28" t="n">
-        <v>3965.794816967612</v>
+        <v>3875.320505058752</v>
       </c>
       <c r="D19" s="28" t="n">
-        <v>4413.152203667537</v>
+        <v>4311.02932410041</v>
       </c>
       <c r="E19" s="28" t="n">
-        <v>4860.673259817765</v>
+        <v>4747.030919435468</v>
       </c>
       <c r="F19" s="28" t="n">
-        <v>5353.002823700373</v>
+        <v>5226.541627322952</v>
       </c>
     </row>
     <row r="20">
@@ -5686,19 +5707,19 @@
         </is>
       </c>
       <c r="B20" s="28" t="n">
-        <v>1447.33822737212</v>
+        <v>1320.451649922855</v>
       </c>
       <c r="C20" s="28" t="n">
-        <v>1665.226400558375</v>
+        <v>1518.748535550944</v>
       </c>
       <c r="D20" s="28" t="n">
-        <v>1876.872124698853</v>
+        <v>1711.098617858713</v>
       </c>
       <c r="E20" s="28" t="n">
-        <v>2078.580057023256</v>
+        <v>1894.509493026274</v>
       </c>
       <c r="F20" s="28" t="n">
-        <v>2257.410793249594</v>
+        <v>2056.790765700589</v>
       </c>
     </row>
     <row r="21">
@@ -5708,19 +5729,19 @@
         </is>
       </c>
       <c r="B21" s="28" t="n">
-        <v>1634.407954819048</v>
+        <v>1973.103930200651</v>
       </c>
       <c r="C21" s="28" t="n">
-        <v>1881.67764525111</v>
+        <v>2271.036579231632</v>
       </c>
       <c r="D21" s="28" t="n">
-        <v>2122.525103426843</v>
+        <v>2560.918674383644</v>
       </c>
       <c r="E21" s="28" t="n">
-        <v>2351.832940121377</v>
+        <v>2837.020352797803</v>
       </c>
       <c r="F21" s="28" t="n">
-        <v>2555.949697113294</v>
+        <v>3082.405620523931</v>
       </c>
     </row>
     <row r="22">
@@ -5760,16 +5781,16 @@
         <v>0.112415700114078</v>
       </c>
       <c r="C23" s="10" t="n">
-        <v>0.1097266535575169</v>
+        <v>0.1100083445187365</v>
       </c>
       <c r="D23" s="10" t="n">
-        <v>0.1100560596011748</v>
+        <v>0.1106031122318905</v>
       </c>
       <c r="E23" s="10" t="n">
-        <v>0.1107776063074413</v>
+        <v>0.1115640664608482</v>
       </c>
       <c r="F23" s="10" t="n">
-        <v>0.1115359941577613</v>
+        <v>0.1125696702000991</v>
       </c>
     </row>
   </sheetData>
@@ -5930,7 +5951,7 @@
         </is>
       </c>
       <c r="C17" s="17" t="n">
-        <v>407355.8870167609</v>
+        <v>442251.724251873</v>
       </c>
     </row>
     <row r="18">
@@ -5940,7 +5961,7 @@
         </is>
       </c>
       <c r="C18" s="8" t="n">
-        <v>0.1107898866887925</v>
+        <v>0.1106031122318905</v>
       </c>
     </row>
     <row r="19">
@@ -5950,7 +5971,7 @@
         </is>
       </c>
       <c r="C19" s="17" t="n">
-        <v>40853.6757509235</v>
+        <v>44270.77398753235</v>
       </c>
     </row>
     <row r="20">
@@ -5960,7 +5981,7 @@
         </is>
       </c>
       <c r="C20" s="17" t="n">
-        <v>-4127.401616023958</v>
+        <v>-3418.938394042807</v>
       </c>
     </row>
     <row r="21">
@@ -5970,7 +5991,7 @@
         </is>
       </c>
       <c r="C21" s="17" t="n">
-        <v>25770.37916675479</v>
+        <v>28795.29588548318</v>
       </c>
     </row>
     <row r="22">
@@ -5980,7 +6001,7 @@
         </is>
       </c>
       <c r="C22" s="22" t="n">
-        <v>12.03785757301744</v>
+        <v>13.45085644255938</v>
       </c>
     </row>
     <row r="23">
@@ -6159,19 +6180,19 @@
         </is>
       </c>
       <c r="B5" s="28" t="n">
-        <v>364506.0698042354</v>
+        <v>365556.0698042354</v>
       </c>
       <c r="C5" s="28" t="n">
-        <v>407355.8870167609</v>
+        <v>408521.3870167609</v>
       </c>
       <c r="D5" s="28" t="n">
-        <v>440969.6742518729</v>
+        <v>442251.724251873</v>
       </c>
       <c r="E5" s="28" t="n">
-        <v>475819.4998520451</v>
+        <v>477216.9343520451</v>
       </c>
       <c r="F5" s="28" t="n">
-        <v>512682.9750719497</v>
+        <v>514192.2043319497</v>
       </c>
     </row>
     <row r="6">
@@ -6181,19 +6202,19 @@
         </is>
       </c>
       <c r="B6" s="28" t="n">
-        <v>40976.20503287411</v>
+        <v>41094.2415179939</v>
       </c>
       <c r="C6" s="28" t="n">
-        <v>44697.79828930313</v>
+        <v>44940.76148621193</v>
       </c>
       <c r="D6" s="28" t="n">
-        <v>48531.38475177478</v>
+        <v>48914.41709217701</v>
       </c>
       <c r="E6" s="28" t="n">
-        <v>52710.1452280135</v>
+        <v>53240.26178029377</v>
       </c>
       <c r="F6" s="28" t="n">
-        <v>57182.60531240865</v>
+        <v>57882.44686110957</v>
       </c>
     </row>
     <row r="7">
@@ -6206,16 +6227,16 @@
         <v>0.112415700114078</v>
       </c>
       <c r="C7" s="10" t="n">
-        <v>0.1097266535575169</v>
+        <v>0.1100083445187365</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>0.1100560596011748</v>
+        <v>0.1106031122318905</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.1107776063074413</v>
+        <v>0.1115640664608482</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>0.1115359941577613</v>
+        <v>0.1125696702000991</v>
       </c>
     </row>
     <row r="8">
@@ -6225,19 +6246,19 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>-3827.313732944472</v>
+        <v>-3838.338732944472</v>
       </c>
       <c r="C8" s="28" t="n">
-        <v>-4277.236813675991</v>
+        <v>-4289.47456367599</v>
       </c>
       <c r="D8" s="28" t="n">
-        <v>-4630.181579644666</v>
+        <v>-4643.643104644667</v>
       </c>
       <c r="E8" s="28" t="n">
-        <v>-4996.104748446474</v>
+        <v>-5010.777810696474</v>
       </c>
       <c r="F8" s="28" t="n">
-        <v>-5383.171238255472</v>
+        <v>-5399.018145485472</v>
       </c>
     </row>
     <row r="9">
@@ -6247,19 +6268,19 @@
         </is>
       </c>
       <c r="B9" s="29" t="n">
-        <v>37148.89129992964</v>
+        <v>37255.90278504942</v>
       </c>
       <c r="C9" s="29" t="n">
-        <v>40420.56147562714</v>
+        <v>40651.28692253594</v>
       </c>
       <c r="D9" s="29" t="n">
-        <v>43901.20317213011</v>
+        <v>44270.77398753235</v>
       </c>
       <c r="E9" s="29" t="n">
-        <v>47714.04047956703</v>
+        <v>48229.4839695973</v>
       </c>
       <c r="F9" s="29" t="n">
-        <v>51799.43407415318</v>
+        <v>52483.42871562409</v>
       </c>
     </row>
     <row r="10">
@@ -6269,19 +6290,19 @@
         </is>
       </c>
       <c r="B10" s="28" t="n">
-        <v>27861.66847494723</v>
+        <v>27941.92708878707</v>
       </c>
       <c r="C10" s="28" t="n">
-        <v>30315.42110672035</v>
+        <v>30488.46519190195</v>
       </c>
       <c r="D10" s="28" t="n">
-        <v>32925.90237909758</v>
+        <v>33203.08049064926</v>
       </c>
       <c r="E10" s="28" t="n">
-        <v>35785.53035967527</v>
+        <v>36172.11297719798</v>
       </c>
       <c r="F10" s="28" t="n">
-        <v>38849.57555561488</v>
+        <v>39362.57153671807</v>
       </c>
     </row>
     <row r="11">
@@ -6291,19 +6312,19 @@
         </is>
       </c>
       <c r="B11" s="28" t="n">
-        <v>3827.313732944472</v>
+        <v>3838.338732944472</v>
       </c>
       <c r="C11" s="28" t="n">
-        <v>4277.236813675991</v>
+        <v>4289.47456367599</v>
       </c>
       <c r="D11" s="28" t="n">
-        <v>4630.181579644666</v>
+        <v>4643.643104644667</v>
       </c>
       <c r="E11" s="28" t="n">
-        <v>4996.104748446474</v>
+        <v>5010.777810696474</v>
       </c>
       <c r="F11" s="28" t="n">
-        <v>5383.171238255472</v>
+        <v>5399.018145485472</v>
       </c>
     </row>
     <row r="12">
@@ -6313,19 +6334,19 @@
         </is>
       </c>
       <c r="B12" s="28" t="n">
-        <v>-10935.18209412706</v>
+        <v>-10966.68209412706</v>
       </c>
       <c r="C12" s="28" t="n">
-        <v>-11813.32072348607</v>
+        <v>-11847.12022348607</v>
       </c>
       <c r="D12" s="28" t="n">
-        <v>-12347.15087905244</v>
+        <v>-12383.04827905244</v>
       </c>
       <c r="E12" s="28" t="n">
-        <v>-12371.30699615317</v>
+        <v>-12407.64029315317</v>
       </c>
       <c r="F12" s="28" t="n">
-        <v>-12304.39140172679</v>
+        <v>-12340.61290396679</v>
       </c>
     </row>
     <row r="13">
@@ -6335,19 +6356,19 @@
         </is>
       </c>
       <c r="B13" s="28" t="n">
-        <v>-19195.12605497414</v>
+        <v>-19436.62605497414</v>
       </c>
       <c r="C13" s="28" t="n">
-        <v>-9855.45795888087</v>
+        <v>-9882.022958880872</v>
       </c>
       <c r="D13" s="28" t="n">
-        <v>-7731.171064075766</v>
+        <v>-7757.977564075773</v>
       </c>
       <c r="E13" s="28" t="n">
-        <v>-8015.459888039608</v>
+        <v>-8041.998323039588</v>
       </c>
       <c r="F13" s="28" t="n">
-        <v>-8478.599300578047</v>
+        <v>-8504.31209537806</v>
       </c>
     </row>
     <row r="14">
@@ -6357,19 +6378,19 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>1558.674058790493</v>
+        <v>1376.957672630335</v>
       </c>
       <c r="C14" s="29" t="n">
-        <v>12923.87923802941</v>
+        <v>13048.796573211</v>
       </c>
       <c r="D14" s="29" t="n">
-        <v>17477.76201561404</v>
+        <v>17705.69775216571</v>
       </c>
       <c r="E14" s="29" t="n">
-        <v>20394.86822392896</v>
+        <v>20733.25217170169</v>
       </c>
       <c r="F14" s="29" t="n">
-        <v>23449.75609156551</v>
+        <v>23916.66468285869</v>
       </c>
     </row>
     <row r="15">
@@ -6423,19 +6444,19 @@
         </is>
       </c>
       <c r="B17" s="29" t="n">
-        <v>1228.28971299769</v>
+        <v>1085.090840504208</v>
       </c>
       <c r="C17" s="29" t="n">
-        <v>8281.473889421228</v>
+        <v>8361.519488005773</v>
       </c>
       <c r="D17" s="29" t="n">
-        <v>9368.100778413231</v>
+        <v>9490.274598442946</v>
       </c>
       <c r="E17" s="29" t="n">
-        <v>9335.292670945473</v>
+        <v>9490.18031978559</v>
       </c>
       <c r="F17" s="29" t="n">
-        <v>9322.134557752976</v>
+        <v>9507.747776807799</v>
       </c>
     </row>
     <row r="19">
@@ -6452,7 +6473,7 @@
         </is>
       </c>
       <c r="C20" s="17" t="n">
-        <v>40792.05433339562</v>
+        <v>41330.70011355398</v>
       </c>
     </row>
     <row r="21">
@@ -6462,7 +6483,7 @@
         </is>
       </c>
       <c r="C21" s="8" t="n">
-        <v>0.2054903756744277</v>
+        <v>0.2077054355161732</v>
       </c>
     </row>
     <row r="22">
@@ -6472,7 +6493,7 @@
         </is>
       </c>
       <c r="C22" s="8" t="n">
-        <v>0.2433203980278784</v>
+        <v>0.2407255249519298</v>
       </c>
     </row>
     <row r="23">
@@ -6502,7 +6523,7 @@
         </is>
       </c>
       <c r="C25" s="17" t="n">
-        <v>304373.4881828119</v>
+        <v>309450.2083826832</v>
       </c>
     </row>
     <row r="26">
@@ -6683,19 +6704,19 @@
         <v>281049</v>
       </c>
       <c r="E5" s="29" t="n">
-        <v>364506.0698042354</v>
+        <v>365556.0698042354</v>
       </c>
       <c r="F5" s="29" t="n">
-        <v>407355.8870167609</v>
+        <v>408521.3870167609</v>
       </c>
       <c r="G5" s="29" t="n">
-        <v>440969.6742518729</v>
+        <v>442251.724251873</v>
       </c>
       <c r="H5" s="29" t="n">
-        <v>475819.4998520451</v>
+        <v>477216.9343520451</v>
       </c>
       <c r="I5" s="29" t="n">
-        <v>512682.9750719497</v>
+        <v>514192.2043319497</v>
       </c>
     </row>
     <row r="6">
@@ -6730,19 +6751,19 @@
         <v>30622.08783333333</v>
       </c>
       <c r="E7" s="29" t="n">
-        <v>40976.20503287411</v>
+        <v>41094.2415179939</v>
       </c>
       <c r="F7" s="29" t="n">
-        <v>44697.79828930313</v>
+        <v>44940.76148621193</v>
       </c>
       <c r="G7" s="29" t="n">
-        <v>48531.38475177478</v>
+        <v>48914.41709217701</v>
       </c>
       <c r="H7" s="29" t="n">
-        <v>52710.1452280135</v>
+        <v>53240.26178029377</v>
       </c>
       <c r="I7" s="29" t="n">
-        <v>57182.60531240865</v>
+        <v>57882.44686110957</v>
       </c>
     </row>
     <row r="8">
@@ -6800,19 +6821,19 @@
         <v>-2951.0145</v>
       </c>
       <c r="E9" s="28" t="n">
-        <v>-3827.313732944472</v>
+        <v>-3838.338732944472</v>
       </c>
       <c r="F9" s="28" t="n">
-        <v>-4277.236813675991</v>
+        <v>-4289.47456367599</v>
       </c>
       <c r="G9" s="28" t="n">
-        <v>-4630.181579644666</v>
+        <v>-4643.643104644667</v>
       </c>
       <c r="H9" s="28" t="n">
-        <v>-4996.104748446474</v>
+        <v>-5010.777810696474</v>
       </c>
       <c r="I9" s="28" t="n">
-        <v>-5383.171238255472</v>
+        <v>-5399.018145485472</v>
       </c>
     </row>
     <row r="10">
@@ -6831,19 +6852,19 @@
         <v>27671.07333333333</v>
       </c>
       <c r="E10" s="29" t="n">
-        <v>37148.89129992964</v>
+        <v>37255.90278504942</v>
       </c>
       <c r="F10" s="29" t="n">
-        <v>40420.56147562714</v>
+        <v>40651.28692253594</v>
       </c>
       <c r="G10" s="29" t="n">
-        <v>43901.20317213011</v>
+        <v>44270.77398753235</v>
       </c>
       <c r="H10" s="29" t="n">
-        <v>47714.04047956703</v>
+        <v>48229.4839695973</v>
       </c>
       <c r="I10" s="29" t="n">
-        <v>51799.43407415318</v>
+        <v>52483.42871562409</v>
       </c>
     </row>
     <row r="11">
@@ -6988,19 +7009,19 @@
         <v>17330</v>
       </c>
       <c r="E17" s="29" t="n">
-        <v>23330.39762588968</v>
+        <v>23402.91492400461</v>
       </c>
       <c r="F17" s="29" t="n">
-        <v>25512.57592073521</v>
+        <v>25655.38637609128</v>
       </c>
       <c r="G17" s="29" t="n">
-        <v>28518.80184166357</v>
+        <v>28760.73212503701</v>
       </c>
       <c r="H17" s="29" t="n">
-        <v>31959.72481232462</v>
+        <v>32311.21619073199</v>
       </c>
       <c r="I17" s="29" t="n">
-        <v>35740.93093970522</v>
+        <v>36223.78337066263</v>
       </c>
     </row>
     <row r="18">

--- a/engine/swdy_study/SWDY_Valuation_Model_05082026_public.xlsx
+++ b/engine/swdy_study/SWDY_Valuation_Model_05082026_public.xlsx
@@ -120,7 +120,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -153,6 +153,7 @@
     <xf numFmtId="166" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="8" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1177,35 +1178,35 @@
           <t>Net debt / EBITDA</t>
         </is>
       </c>
-      <c r="B18" s="32">
+      <c r="B18" s="33">
         <f>B17/'Income Statement'!B7</f>
         <v/>
       </c>
-      <c r="C18" s="32">
+      <c r="C18" s="33">
         <f>C17/'Income Statement'!C7</f>
         <v/>
       </c>
-      <c r="D18" s="32">
+      <c r="D18" s="33">
         <f>D17/'Income Statement'!D7</f>
         <v/>
       </c>
-      <c r="E18" s="32">
+      <c r="E18" s="33">
         <f>E17/'Income Statement'!E7</f>
         <v/>
       </c>
-      <c r="F18" s="32">
+      <c r="F18" s="33">
         <f>F17/'Income Statement'!F7</f>
         <v/>
       </c>
-      <c r="G18" s="32">
+      <c r="G18" s="33">
         <f>G17/'Income Statement'!G7</f>
         <v/>
       </c>
-      <c r="H18" s="32">
+      <c r="H18" s="33">
         <f>H17/'Income Statement'!H7</f>
         <v/>
       </c>
-      <c r="I18" s="32">
+      <c r="I18" s="33">
         <f>I17/'Income Statement'!I7</f>
         <v/>
       </c>
@@ -2305,19 +2306,19 @@
         </is>
       </c>
       <c r="B6" s="9" t="n">
-        <v>71.40604255139132</v>
+        <v>71.48013737611937</v>
       </c>
       <c r="C6" s="9" t="n">
-        <v>74.8455484835976</v>
+        <v>75.158505958635</v>
       </c>
       <c r="D6" s="9" t="n">
-        <v>79.04809647022493</v>
+        <v>79.66249997898875</v>
       </c>
       <c r="E6" s="9" t="n">
-        <v>84.3342475199925</v>
+        <v>85.33897230281774</v>
       </c>
       <c r="F6" s="9" t="n">
-        <v>91.23336316838652</v>
+        <v>92.76070177891306</v>
       </c>
     </row>
     <row r="7">
@@ -2327,19 +2328,19 @@
         </is>
       </c>
       <c r="B7" s="9" t="n">
-        <v>64.49978173034609</v>
+        <v>64.51999723358476</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>67.00642468255586</v>
+        <v>67.23266415979741</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>69.99025922223638</v>
+        <v>70.47099233404454</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>73.62713288192815</v>
+        <v>74.42869060586594</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>78.19139342245379</v>
+        <v>79.40797299188714</v>
       </c>
     </row>
     <row r="8">
@@ -2349,19 +2350,19 @@
         </is>
       </c>
       <c r="B8" s="9" t="n">
-        <v>58.73840333856804</v>
+        <v>58.71390500851878</v>
       </c>
       <c r="C8" s="9" t="n">
-        <v>60.5801332665243</v>
+        <v>60.7356474116613</v>
       </c>
       <c r="D8" s="9" t="n">
-        <v>62.72237722300294</v>
+        <v>63.09639197519306</v>
       </c>
       <c r="E8" s="9" t="n">
-        <v>65.26376140705965</v>
+        <v>65.90739638220869</v>
       </c>
       <c r="F8" s="9" t="n">
-        <v>68.35137102723559</v>
+        <v>69.3345836803008</v>
       </c>
     </row>
     <row r="9">
@@ -2371,19 +2372,19 @@
         </is>
       </c>
       <c r="B9" s="9" t="n">
-        <v>53.86023933636113</v>
+        <v>53.79809034203993</v>
       </c>
       <c r="C9" s="9" t="n">
-        <v>55.21731960809319</v>
+        <v>55.314134925563</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>56.76227199734095</v>
+        <v>57.04924305755583</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>58.55067448976136</v>
+        <v>59.06822004769293</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>60.66242537979906</v>
+        <v>61.46422928886715</v>
       </c>
     </row>
     <row r="10">
@@ -2393,19 +2394,19 @@
         </is>
       </c>
       <c r="B10" s="9" t="n">
-        <v>49.67765160561232</v>
+        <v>49.58340787307901</v>
       </c>
       <c r="C10" s="9" t="n">
-        <v>50.67498049644503</v>
+        <v>50.72236517614795</v>
       </c>
       <c r="D10" s="9" t="n">
-        <v>51.78663329144614</v>
+        <v>52.00135637265844</v>
       </c>
       <c r="E10" s="9" t="n">
-        <v>53.04339463405028</v>
+        <v>53.45808918007977</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>54.48819181375644</v>
+        <v>55.14514468831749</v>
       </c>
     </row>
     <row r="12">
@@ -2450,19 +2451,19 @@
         </is>
       </c>
       <c r="B14" s="9" t="n">
-        <v>83.66571992603276</v>
+        <v>84.33728753089692</v>
       </c>
       <c r="C14" s="9" t="n">
-        <v>81.31573210887528</v>
+        <v>81.95820408756369</v>
       </c>
       <c r="D14" s="9" t="n">
-        <v>79.04809647022493</v>
+        <v>79.66249997898875</v>
       </c>
       <c r="E14" s="9" t="n">
-        <v>76.8591944099261</v>
+        <v>77.44651129819714</v>
       </c>
       <c r="F14" s="9" t="n">
-        <v>74.74559943059796</v>
+        <v>75.30676865150218</v>
       </c>
     </row>
     <row r="15">
@@ -2472,19 +2473,19 @@
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>74.09309219727253</v>
+        <v>74.62341007610547</v>
       </c>
       <c r="C15" s="9" t="n">
-        <v>72.00519044120513</v>
+        <v>72.51027129509237</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>69.99025922223638</v>
+        <v>70.47099233404454</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>68.04509832510135</v>
+        <v>68.50233381059978</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>66.16667718367351</v>
+        <v>66.60122807292484</v>
       </c>
     </row>
     <row r="16">
@@ -2494,19 +2495,19 @@
         </is>
       </c>
       <c r="B16" s="9" t="n">
-        <v>66.41233867790525</v>
+        <v>66.82989265057586</v>
       </c>
       <c r="C16" s="9" t="n">
-        <v>64.53463324396715</v>
+        <v>64.9300279088521</v>
       </c>
       <c r="D16" s="9" t="n">
-        <v>62.72237722300294</v>
+        <v>63.09639197519306</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>60.97270569052243</v>
+        <v>61.32608564835102</v>
       </c>
       <c r="F16" s="9" t="n">
-        <v>59.28290538269756</v>
+        <v>59.61636320712214</v>
       </c>
     </row>
     <row r="17">
@@ -2516,19 +2517,19 @@
         </is>
       </c>
       <c r="B17" s="9" t="n">
-        <v>60.11382102859078</v>
+        <v>60.43940513969982</v>
       </c>
       <c r="C17" s="9" t="n">
-        <v>58.40840279419519</v>
+        <v>58.71433541623137</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>56.76227199734095</v>
+        <v>57.04924305755583</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>55.17283830621533</v>
+        <v>55.44150743399135</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>53.63764832267511</v>
+        <v>53.88864645585161</v>
       </c>
     </row>
     <row r="18">
@@ -2538,19 +2539,19 @@
         </is>
       </c>
       <c r="B18" s="9" t="n">
-        <v>54.85581681153326</v>
+        <v>55.10506833536628</v>
       </c>
       <c r="C18" s="9" t="n">
-        <v>53.29415083110127</v>
+        <v>53.52583022982751</v>
       </c>
       <c r="D18" s="9" t="n">
-        <v>51.78663329144614</v>
+        <v>52.00135637265844</v>
       </c>
       <c r="E18" s="9" t="n">
-        <v>50.33090277179734</v>
+        <v>50.52925833918371</v>
       </c>
       <c r="F18" s="9" t="n">
-        <v>48.92472251249137</v>
+        <v>49.1072737958847</v>
       </c>
     </row>
     <row r="20">
@@ -2596,25 +2597,22 @@
         </is>
       </c>
       <c r="B22" s="9" t="n">
-        <v>86.15763153561919</v>
+        <v>86.86398352810841</v>
       </c>
       <c r="C22" s="9" t="n">
-        <v>73.24713700573579</v>
+        <v>73.76938856958702</v>
       </c>
       <c r="D22" s="9" t="n">
-        <v>63.12622637075465</v>
+        <v>63.09639197519306</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>62.72237722300294</v>
+        <v>57.1692154119707</v>
       </c>
       <c r="F22" s="9" t="n">
-        <v>56.87661209559251</v>
-      </c>
-      <c r="G22" s="9" t="n">
-        <v>51.51532544021109</v>
+        <v>51.73397898456535</v>
       </c>
       <c r="H22" s="9" t="n">
-        <v>34.6423060954081</v>
+        <v>35.13000454354306</v>
       </c>
     </row>
     <row r="23">
@@ -2624,22 +2622,22 @@
         </is>
       </c>
       <c r="B23" s="9" t="n">
-        <v>71.61367692250901</v>
+        <v>71.93944315776433</v>
       </c>
       <c r="C23" s="9" t="n">
-        <v>67.16802707275598</v>
+        <v>63.09639197519306</v>
       </c>
       <c r="D23" s="9" t="n">
-        <v>62.72237722300294</v>
+        <v>45.41028961005051</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>55.60933746339811</v>
+        <v>23.30266165362228</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>44.93977782399083</v>
+        <v>1.195033697194072</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>26.67389909851818</v>
+        <v>70.74440946057025</v>
       </c>
     </row>
     <row r="24">
@@ -2649,19 +2647,19 @@
         </is>
       </c>
       <c r="B24" s="9" t="n">
-        <v>41.84129022062721</v>
+        <v>42.21530497281732</v>
       </c>
       <c r="C24" s="9" t="n">
-        <v>52.28183372181507</v>
+        <v>52.6558484740052</v>
       </c>
       <c r="D24" s="9" t="n">
-        <v>62.72237722300294</v>
+        <v>63.09639197519306</v>
       </c>
       <c r="E24" s="9" t="n">
-        <v>73.16292072419081</v>
+        <v>73.53693547638095</v>
       </c>
       <c r="F24" s="9" t="n">
-        <v>83.60346422537874</v>
+        <v>83.97747897756886</v>
       </c>
       <c r="H24" s="9" t="n">
         <v>41.76217400475154</v>
@@ -2674,22 +2672,22 @@
         </is>
       </c>
       <c r="B25" s="9" t="n">
-        <v>65.87180866666164</v>
+        <v>66.1820174425543</v>
       </c>
       <c r="C25" s="9" t="n">
-        <v>64.2970929448323</v>
+        <v>64.63920470887369</v>
       </c>
       <c r="D25" s="9" t="n">
-        <v>62.72237722300294</v>
+        <v>63.09639197519306</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>61.1476615011736</v>
+        <v>61.55357924151245</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>59.57294577934427</v>
+        <v>60.01076650783185</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>6.298862887317362</v>
+        <v>6.171250934722451</v>
       </c>
     </row>
     <row r="26">
@@ -2699,19 +2697,19 @@
         </is>
       </c>
       <c r="B26" s="9" t="n">
-        <v>56.38958884826296</v>
+        <v>55.97972245871841</v>
       </c>
       <c r="C26" s="9" t="n">
-        <v>60.18863757345764</v>
+        <v>59.77877118391308</v>
       </c>
       <c r="D26" s="9" t="n">
-        <v>62.72237722300294</v>
+        <v>63.09639197519306</v>
       </c>
       <c r="E26" s="9" t="n">
-        <v>66.03332791991097</v>
+        <v>65.62346153036643</v>
       </c>
       <c r="F26" s="9" t="n">
-        <v>67.78673502384697</v>
+        <v>67.37686863430243</v>
       </c>
       <c r="H26" s="9" t="n">
         <v>11.39714617558401</v>
@@ -3114,28 +3112,28 @@
           <t>Net debt / EBITDA</t>
         </is>
       </c>
-      <c r="B14" s="32" t="n">
+      <c r="B14" s="33" t="n">
         <v>0.7371063783060728</v>
       </c>
-      <c r="C14" s="32" t="n">
+      <c r="C14" s="33" t="n">
         <v>0.6337653789681534</v>
       </c>
-      <c r="D14" s="32" t="n">
+      <c r="D14" s="33" t="n">
         <v>0.6462328796032941</v>
       </c>
-      <c r="E14" s="32" t="n">
+      <c r="E14" s="33" t="n">
         <v>0.6657458870097267</v>
       </c>
-      <c r="F14" s="32" t="n">
+      <c r="F14" s="33" t="n">
         <v>0.53307780193362</v>
       </c>
-      <c r="G14" s="32" t="n">
+      <c r="G14" s="33" t="n">
         <v>0.3279986937477656</v>
       </c>
-      <c r="H14" s="32" t="n">
+      <c r="H14" s="33" t="n">
         <v>0.09633371227953212</v>
       </c>
-      <c r="I14" s="32" t="n">
+      <c r="I14" s="33" t="n">
         <v>-0.1559185836582377</v>
       </c>
     </row>
@@ -3145,38 +3143,38 @@
           <t>Interest cover (EBIT / net interest)</t>
         </is>
       </c>
-      <c r="B15" s="32" t="inlineStr">
+      <c r="B15" s="33" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C15" s="32" t="n">
+      <c r="C15" s="33" t="n">
         <v>8.346617739090858</v>
       </c>
-      <c r="D15" s="32" t="n">
+      <c r="D15" s="33" t="n">
         <v>8.138550980392157</v>
       </c>
-      <c r="E15" s="32" t="inlineStr">
+      <c r="E15" s="33" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F15" s="32" t="inlineStr">
+      <c r="F15" s="33" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G15" s="32" t="inlineStr">
+      <c r="G15" s="33" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H15" s="32" t="inlineStr">
+      <c r="H15" s="33" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I15" s="32" t="inlineStr">
+      <c r="I15" s="33" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3409,12 +3407,12 @@
           <t>Saudi Arabia</t>
         </is>
       </c>
-      <c r="C5" s="35" t="inlineStr">
+      <c r="C5" s="36" t="inlineStr">
         <is>
           <t>nearest listed regional cable manufacturer</t>
         </is>
       </c>
-      <c r="D5" s="35" t="inlineStr">
+      <c r="D5" s="36" t="inlineStr">
         <is>
           <t>far smaller, no contracting arm, lighter balance sheet, pegged currency</t>
         </is>
@@ -3431,12 +3429,12 @@
           <t>Egypt</t>
         </is>
       </c>
-      <c r="C6" s="35" t="inlineStr">
+      <c r="C6" s="36" t="inlineStr">
         <is>
           <t>the only other listed Egyptian cable manufacturer</t>
         </is>
       </c>
-      <c r="D6" s="35" t="inlineStr">
+      <c r="D6" s="36" t="inlineStr">
         <is>
           <t>much smaller, domestic, heavily levered, currently loss-making</t>
         </is>
@@ -3453,12 +3451,12 @@
           <t>Europe</t>
         </is>
       </c>
-      <c r="C7" s="35" t="inlineStr">
+      <c r="C7" s="36" t="inlineStr">
         <is>
           <t>closest match on business model — cables plus projects</t>
         </is>
       </c>
-      <c r="D7" s="35" t="inlineStr">
+      <c r="D7" s="36" t="inlineStr">
         <is>
           <t>developed-market cost of capital; no convertibility risk</t>
         </is>
@@ -3475,12 +3473,12 @@
           <t>Gulf and North Africa</t>
         </is>
       </c>
-      <c r="C8" s="35" t="inlineStr">
+      <c r="C8" s="36" t="inlineStr">
         <is>
           <t>the right frame for the roughly 27% that is turnkey project work</t>
         </is>
       </c>
-      <c r="D8" s="35" t="inlineStr">
+      <c r="D8" s="36" t="inlineStr">
         <is>
           <t>project accounting and backlog quality are not comparable</t>
         </is>
@@ -3504,7 +3502,7 @@
           <t>Trailing enterprise value / EBITDA</t>
         </is>
       </c>
-      <c r="B11" s="32" t="n">
+      <c r="B11" s="33" t="n">
         <v>8.000722677325394</v>
       </c>
     </row>
@@ -3514,7 +3512,7 @@
           <t>Trailing price / earnings</t>
         </is>
       </c>
-      <c r="B12" s="32" t="n">
+      <c r="B12" s="33" t="n">
         <v>12.9953740655049</v>
       </c>
     </row>
@@ -3524,7 +3522,7 @@
           <t>Trailing price / book</t>
         </is>
       </c>
-      <c r="B13" s="32" t="n">
+      <c r="B13" s="33" t="n">
         <v>3.196092220646482</v>
       </c>
     </row>
@@ -3534,7 +3532,7 @@
           <t>Justified enterprise value / EBITDA applied</t>
         </is>
       </c>
-      <c r="B14" s="32" t="n">
+      <c r="B14" s="33" t="n">
         <v>6.5</v>
       </c>
     </row>
@@ -3544,7 +3542,7 @@
           <t>Justified price / earnings applied</t>
         </is>
       </c>
-      <c r="B15" s="32" t="n">
+      <c r="B15" s="33" t="n">
         <v>9</v>
       </c>
     </row>
@@ -3635,13 +3633,13 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>35.60479630603451</v>
+        <v>35.37439268305282</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>62.72237722300294</v>
+        <v>63.09639197519306</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>108.9676974718246</v>
+        <v>110.3869768355961</v>
       </c>
       <c r="E5" s="8" t="n">
         <v>0.45</v>
@@ -3662,13 +3660,13 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>99.11342021383139</v>
+        <v>61.2294172643708</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>118.0812995812873</v>
+        <v>73.38381725729656</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>146.5331186324713</v>
+        <v>91.61541724668523</v>
       </c>
       <c r="E6" s="8" t="n">
         <v>0.2</v>
@@ -3716,13 +3714,13 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>26.5605093375666</v>
+        <v>33.76534925901321</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>33.85989565286666</v>
+        <v>48.47019940598007</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>48.47019940598007</v>
+        <v>53.71022096338332</v>
       </c>
       <c r="E8" s="8" t="n">
         <v>0.15</v>
@@ -4002,7 +4000,7 @@
         </is>
       </c>
       <c r="C6" s="9" t="n">
-        <v>35.60479630603451</v>
+        <v>35.37439268305282</v>
       </c>
     </row>
     <row r="7">
@@ -4017,7 +4015,7 @@
         </is>
       </c>
       <c r="C7" s="9" t="n">
-        <v>108.9676974718246</v>
+        <v>110.3869768355961</v>
       </c>
     </row>
     <row r="8">
@@ -4032,7 +4030,7 @@
         </is>
       </c>
       <c r="C8" s="7">
-        <f>'Relative &amp; Normalized'!C9</f>
+        <f>'Relative &amp; Normalized'!C11</f>
         <v/>
       </c>
     </row>
@@ -4048,7 +4046,7 @@
         </is>
       </c>
       <c r="C9" s="7">
-        <f>'Relative &amp; Normalized'!C24</f>
+        <f>'Relative &amp; Normalized'!C26</f>
         <v/>
       </c>
     </row>
@@ -4064,7 +4062,7 @@
         </is>
       </c>
       <c r="C10" s="7">
-        <f>'Relative &amp; Normalized'!C32</f>
+        <f>'Relative &amp; Normalized'!C34</f>
         <v/>
       </c>
     </row>
@@ -4126,7 +4124,7 @@
         </is>
       </c>
       <c r="C18" s="22" t="n">
-        <v>90.38294164821865</v>
+        <v>91.14622861923802</v>
       </c>
     </row>
     <row r="19">
@@ -4206,13 +4204,13 @@
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>46.2389872519482</v>
+        <v>66.19078084024615</v>
       </c>
       <c r="D24" s="9" t="n">
-        <v>32.10886025513935</v>
+        <v>40.8187533998155</v>
       </c>
       <c r="E24" s="9" t="n">
-        <v>66.19078084024615</v>
+        <v>72.60004748131544</v>
       </c>
     </row>
     <row r="25">
@@ -4227,13 +4225,13 @@
         </is>
       </c>
       <c r="C25" s="9" t="n">
-        <v>56.08425905816016</v>
+        <v>60.72264310179215</v>
       </c>
       <c r="D25" s="9" t="n">
-        <v>47.37467423206117</v>
+        <v>49.99375810242254</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>90.38294164821865</v>
+        <v>91.14622861923802</v>
       </c>
     </row>
     <row r="26">
@@ -5139,7 +5137,7 @@
         </is>
       </c>
       <c r="C9" s="28" t="n">
-        <v>7445.099999999999</v>
+        <v>6474</v>
       </c>
       <c r="D9" s="9">
         <f>C9/2140.777876</f>
@@ -5804,7 +5802,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -5840,7 +5838,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Mid-cycle EBITDA (FY2027E, EGP mn)</t>
+          <t>FY2027E EBITDA (EGP mn)</t>
         </is>
       </c>
       <c r="C5" s="18">
@@ -5861,7 +5859,7 @@
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>Implied enterprise value (EGP mn)</t>
+          <t>Implied enterprise value AS AT end-FY2027 (EGP mn)</t>
         </is>
       </c>
       <c r="C7" s="28">
@@ -5872,231 +5870,252 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Less net bank debt, plus associates, less minority share (EGP mn)</t>
-        </is>
-      </c>
-      <c r="C8" s="28">
-        <f>(-19789.0+7445.099999999999)*1</f>
-        <v/>
+          <t>Discount factor back to today (year-2)</t>
+        </is>
+      </c>
+      <c r="C8" s="32" t="n">
+        <v>0.6407885540320136</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="14" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Implied enterprise value TODAY (EGP mn)</t>
+        </is>
+      </c>
+      <c r="C9" s="28">
+        <f>C7*C8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Less net bank debt, plus associates (EGP mn)</t>
+        </is>
+      </c>
+      <c r="C10" s="28">
+        <f>-19789.0+6474.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>Implied value per share (EGP)</t>
         </is>
       </c>
-      <c r="B9" s="14" t="n"/>
-      <c r="C9" s="30">
-        <f>(C7+C8)*(1-0.09645464025026068)/2140.777876</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>Trailing enterprise value / EBITDA</t>
-        </is>
-      </c>
-      <c r="C11" s="32" t="n">
-        <v>8.000722677325394</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>Trailing price / earnings</t>
-        </is>
-      </c>
-      <c r="C12" s="32" t="n">
-        <v>12.9953740655049</v>
+      <c r="B11" s="14" t="n"/>
+      <c r="C11" s="30">
+        <f>(C9+C10)*(1-0.09645464025026068)/2140.777876</f>
+        <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>Trailing price / book</t>
-        </is>
-      </c>
-      <c r="C13" s="32" t="n">
-        <v>3.196092220646482</v>
+          <t>Trailing enterprise value / EBITDA</t>
+        </is>
+      </c>
+      <c r="C13" s="33" t="n">
+        <v>8.000722677325394</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
+          <t>Trailing price / earnings</t>
+        </is>
+      </c>
+      <c r="C14" s="33" t="n">
+        <v>12.9953740655049</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>Trailing price / book</t>
+        </is>
+      </c>
+      <c r="C15" s="33" t="n">
+        <v>3.196092220646482</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
           <t>Net bank debt / EBITDA</t>
         </is>
       </c>
-      <c r="C14" s="32" t="n">
+      <c r="C16" s="33" t="n">
         <v>0.6462328796032941</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>Normalised earnings lens</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>Mid-cycle revenue (EGP mn)</t>
-        </is>
-      </c>
-      <c r="C17" s="17" t="n">
-        <v>442251.724251873</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>Mid-cycle EBITDA margin</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="n">
-        <v>0.1106031122318905</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>Mid-cycle EBIT (EGP mn)</t>
+          <t>Mid-cycle revenue (EGP mn)</t>
         </is>
       </c>
       <c r="C19" s="17" t="n">
-        <v>44270.77398753235</v>
+        <v>442251.724251873</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Less net interest (EGP mn)</t>
-        </is>
-      </c>
-      <c r="C20" s="17" t="n">
-        <v>-3418.938394042807</v>
+          <t>Mid-cycle EBITDA margin</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="n">
+        <v>0.1106031122318905</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>Normalised attributable earnings (EGP mn)</t>
+          <t>Mid-cycle EBIT (EGP mn)</t>
         </is>
       </c>
       <c r="C21" s="17" t="n">
-        <v>28795.29588548318</v>
+        <v>44270.77398753235</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Normalised earnings per share (EGP)</t>
-        </is>
-      </c>
-      <c r="C22" s="22" t="n">
-        <v>13.45085644255938</v>
+          <t>Less net interest (EGP mn)</t>
+        </is>
+      </c>
+      <c r="C22" s="17" t="n">
+        <v>-3418.938394042807</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
+          <t>Normalised attributable earnings (EGP mn)</t>
+        </is>
+      </c>
+      <c r="C23" s="17" t="n">
+        <v>28795.29588548318</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>Normalised earnings per share (EGP)</t>
+        </is>
+      </c>
+      <c r="C24" s="22" t="n">
+        <v>13.45085644255938</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
           <t>Justified price / earnings</t>
         </is>
       </c>
-      <c r="C23" s="24" t="n">
+      <c r="C25" s="24" t="n">
         <v>9</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="14" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="14" t="inlineStr">
         <is>
           <t>Implied value per share (EGP)</t>
         </is>
       </c>
-      <c r="B24" s="14" t="n"/>
-      <c r="C24" s="30">
-        <f>C22*C23</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+      <c r="B26" s="14" t="n"/>
+      <c r="C26" s="30">
+        <f>C24*C25</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>Book lens</t>
         </is>
       </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="B28" s="5" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>Book value per share (EGP)</t>
-        </is>
-      </c>
-      <c r="C27" s="22" t="n">
-        <v>32.91519541282852</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t>Sustainable return on equity</t>
-        </is>
-      </c>
-      <c r="C28" s="8" t="n">
-        <v>0.235</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>Trailing return on equity</t>
-        </is>
-      </c>
-      <c r="C29" s="8" t="n">
-        <v>0.2756503065994848</v>
+          <t>Book value per share (EGP)</t>
+        </is>
+      </c>
+      <c r="C29" s="22" t="n">
+        <v>32.91519541282852</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>Blended cost of equity</t>
+          <t>Sustainable return on equity</t>
         </is>
       </c>
       <c r="C30" s="8" t="n">
-        <v>0.22983845</v>
+        <v>0.235</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
+          <t>Trailing return on equity</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="n">
+        <v>0.2756503065994848</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>Perpetual cost of equity</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="n">
+        <v>0.17563</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
           <t>Justified price / book</t>
         </is>
       </c>
-      <c r="C31" s="24" t="n">
-        <v>1.028701036958448</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="14" t="inlineStr">
+      <c r="C33" s="24" t="n">
+        <v>1.472578205842553</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="14" t="inlineStr">
         <is>
           <t>Implied value per share (EGP)</t>
         </is>
       </c>
-      <c r="B32" s="14" t="n"/>
-      <c r="C32" s="30">
-        <f>C27*C31</f>
+      <c r="B34" s="14" t="n"/>
+      <c r="C34" s="30">
+        <f>C29*C33</f>
         <v/>
       </c>
     </row>
@@ -6399,19 +6418,19 @@
           <t>Forward cost of capital</t>
         </is>
       </c>
-      <c r="B15" s="33" t="n">
+      <c r="B15" s="34" t="n">
         <v>0.2689791685924707</v>
       </c>
-      <c r="C15" s="33" t="n">
+      <c r="C15" s="34" t="n">
         <v>0.2297894457283138</v>
       </c>
-      <c r="D15" s="33" t="n">
+      <c r="D15" s="34" t="n">
         <v>0.1954984382221766</v>
       </c>
-      <c r="E15" s="33" t="n">
+      <c r="E15" s="34" t="n">
         <v>0.1710048614320785</v>
       </c>
-      <c r="F15" s="33" t="n">
+      <c r="F15" s="34" t="n">
         <v>0.15141</v>
       </c>
     </row>
@@ -6421,19 +6440,19 @@
           <t>Discount factor</t>
         </is>
       </c>
-      <c r="B16" s="34" t="n">
+      <c r="B16" s="35" t="n">
         <v>0.7880350006920778</v>
       </c>
-      <c r="C16" s="34" t="n">
+      <c r="C16" s="35" t="n">
         <v>0.6407885540320136</v>
       </c>
-      <c r="D16" s="34" t="n">
+      <c r="D16" s="35" t="n">
         <v>0.536001163652651</v>
       </c>
-      <c r="E16" s="34" t="n">
+      <c r="E16" s="35" t="n">
         <v>0.4577275306928695</v>
       </c>
-      <c r="F16" s="34" t="n">
+      <c r="F16" s="35" t="n">
         <v>0.3975365253844151</v>
       </c>
     </row>
@@ -6483,7 +6502,7 @@
         </is>
       </c>
       <c r="C21" s="8" t="n">
-        <v>0.2077054355161732</v>
+        <v>0.2180907072919819</v>
       </c>
     </row>
     <row r="22">
@@ -6493,7 +6512,7 @@
         </is>
       </c>
       <c r="C22" s="8" t="n">
-        <v>0.2407255249519298</v>
+        <v>0.2292624047161236</v>
       </c>
     </row>
     <row r="23">
@@ -6523,7 +6542,7 @@
         </is>
       </c>
       <c r="C25" s="17" t="n">
-        <v>309450.2083826832</v>
+        <v>314122.1222455342</v>
       </c>
     </row>
     <row r="26">

--- a/engine/swdy_study/SWDY_Valuation_Model_05082026_public.xlsx
+++ b/engine/swdy_study/SWDY_Valuation_Model_05082026_public.xlsx
@@ -67,10 +67,10 @@
       <color rgb="00000000"/>
     </font>
     <font>
-      <color rgb="00008000"/>
+      <color rgb="000000FF"/>
     </font>
     <font>
-      <color rgb="000000FF"/>
+      <color rgb="00008000"/>
     </font>
     <font>
       <b val="1"/>
@@ -120,7 +120,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -129,34 +129,38 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="8" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="8" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="9" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="10" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="8" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -525,7 +529,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I41"/>
+  <dimension ref="A1:I50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="112" customWidth="1" min="1" max="1"/>
@@ -584,212 +588,271 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>IMPORTANT, so the workbook is not over-read. The Assumptions sheet is a complete REGISTER of every input</t>
+          <t>IT IS FORMULA-DRIVEN. Every figure that can be derived arithmetically from a driver is a live formula, so</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>and its value, not a live driver: the forecast is computed in the accompanying model and the results are</t>
+          <t>you can change a blue cell on Assumptions and watch the model reprice: the cost of capital is built from</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>written here, so editing an Assumptions cell will NOT reprice the workbook. Formulas here aggregate,</t>
+          <t>the risk-free rate, beta and the premium rather than pasted; the discount factors compound from the glide;</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>cross-link and derive ratios. Every input is listed so the build can be reproduced independently, and the</t>
+          <t>and the income statement, balance sheet, cash flow, ratios and all four lenses chain off the same cells.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>sensitivity tables show what happens when each driver moves.</t>
-        </is>
-      </c>
+      <c r="A12" s="3" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr"/>
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>THREE THINGS ARE PASTED VALUES, and it is worth knowing which. First, audited and disclosed history — the</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>How revenue is built. Not as one growth rate. Revenue splits into a domestic Egyptian-pound leg and a</t>
+          <t>primary record, not a calculation. Second, the sub-segment unit build: revenue and gross profit per segment</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>foreign leg forecast in US dollars and translated at an explicit exchange-rate path, because more than 70%</t>
+          <t>come from a seven-line tonnage, megavolt-ampere, meter-unit and order-book model, and only its OUTPUT is</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>of this company's revenue is earned outside Egypt. Margins come from a segment build; group EBITDA margin</t>
+          <t>carried here; everything downstream of it is formula. Third, the Monte Carlo price map and the sensitivity</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>is an output of that build, not an input.</t>
+          <t>grids, where each individual cell is a complete re-run of the whole valuation and so cannot be a formula in</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr"/>
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>a grid. Changing a driver reprices the model but does NOT redraw those two grids.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>What it is not. It is not investment advice, a recommendation, or a price target. Values are model outputs</t>
-        </is>
-      </c>
+      <c r="A19" s="3" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>shown as ranges.</t>
+          <t>How revenue is built. Not as one growth rate. Revenue splits into a domestic Egyptian-pound leg and a</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr"/>
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>foreign leg forecast in US dollars and translated at an explicit exchange-rate path, because more than 70%</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>Sourcing note, up front. FY2023 and FY2024 come from the company's audited consolidated statements and</t>
+          <t>of this company's revenue is earned outside Egypt. Margins come from a segment build; group EBITDA margin</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>earnings releases and are not estimated. For FY2025, revenue, profit after tax, profit after minority</t>
+          <t>is an output of that build, not an input.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>interests, total assets and net bank debt are disclosed; the intermediate income-statement lines are</t>
-        </is>
-      </c>
+      <c r="A24" s="3" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>derived by closing the profit-and-loss account to the reported profit, and the balance sheet beyond total</t>
+          <t>What it is not. It is not investment advice, a recommendation, or a price target. Values are model outputs</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>assets and net debt is triangulated by three methods. Every derived line is annotated where it appears and</t>
+          <t>shown as ranges.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>listed with source and date in the companion bibliography document.</t>
-        </is>
-      </c>
+      <c r="A27" s="3" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="inlineStr"/>
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Sourcing note, up front. FY2023 and FY2024 come from the company's audited consolidated statements and</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>Discount convention. Each explicit year is discounted at its own forward cost of capital, gliding</t>
+          <t>earnings releases and are not estimated. For FY2025, revenue, profit after tax, profit after minority</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>26.9% -&gt; 15.1% on the same easing calendar as the interest forecast; the terminal value is</t>
+          <t>interests, total assets and net bank debt are disclosed; the intermediate income-statement lines are</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>capitalised at the terminal rate and discounted at the year-5 cumulative factor. One date, one price of time.</t>
+          <t>derived by closing the profit-and-loss account to the reported profit, and the balance sheet beyond total</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="inlineStr"/>
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>assets and net debt is triangulated by three methods, which are shown and averaged on the Balance Sheet</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>The open question. This company earns most of its revenue in hard currency but reports, lists and borrows</t>
+          <t>sheet rather than asserted. Every derived line is annotated where it appears and listed with source and</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>in Egyptian pounds. The primary model charges the full Egyptian cost of capital. The Fundamental Valuation</t>
+          <t>date in the companion bibliography document.</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>sheet also shows what the same cash flows are worth if the hard-currency leg is discounted at a</t>
-        </is>
-      </c>
+      <c r="A35" s="3" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>hard-currency rate. Both are shown; they are not averaged.</t>
+          <t>Discount convention. Each explicit year is discounted at its own forward cost of capital, gliding</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="inlineStr"/>
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>26.9% -&gt; 15.1% on the same easing calendar as the interest forecast; the terminal value is</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>Currency. EGP million unless stated. Spot EGP 105.20 (2026-08-05 close). Sheets: READ FIRST · Summary ·</t>
+          <t>capitalised at the terminal rate and discounted at the year-5 cumulative factor. One date, one price of time.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>Fundamental Valuation · Assumptions · SOTP Bridge · Segments · Relative &amp; Normalized · DCF · Income</t>
+          <t>The glide fractions are not a free parameter: they are the cost-of-debt path's own cumulative progress, and</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
+          <t>the DCF sheet computes them in front of you.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>The open question. This company earns most of its revenue in hard currency but reports, lists and borrows</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>in Egyptian pounds. The primary model charges the full Egyptian cost of capital. The Fundamental Valuation</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>sheet also shows what the same cash flows are worth if the hard-currency leg is discounted at a</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>hard-currency rate. Both are shown; they are not averaged.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>Currency. EGP million unless stated. Spot EGP 105.20 (2026-08-05 close). Sheets: READ FIRST · Summary ·</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>Fundamental Valuation · Assumptions · SOTP Bridge · Segments · Relative &amp; Normalized · DCF · Income</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
           <t>Statement · Balance Sheet · Cash Flow · Summary Financials · Monte Carlo · Sensitivity · Per-Share &amp;</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="3" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
         <is>
           <t>Ratios · Peer &amp; Sector.</t>
         </is>
@@ -806,7 +869,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -838,7 +901,7 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>EGP mn, consolidated</t>
+          <t>EGP mn, consolidated. The FY2025 debt and cash lines are triangulated by three methods, shown and averaged below rather than asserted</t>
         </is>
       </c>
     </row>
@@ -895,29 +958,35 @@
           <t>Property, plant and equipment</t>
         </is>
       </c>
-      <c r="B5" s="28" t="n">
+      <c r="B5" s="22" t="n">
         <v>18009.2</v>
       </c>
-      <c r="C5" s="28" t="n">
+      <c r="C5" s="22" t="n">
         <v>27543.8</v>
       </c>
-      <c r="D5" s="28" t="n">
-        <v>33024.2555</v>
-      </c>
-      <c r="E5" s="28" t="n">
-        <v>40152.59886118259</v>
-      </c>
-      <c r="F5" s="28" t="n">
-        <v>47710.24452099267</v>
-      </c>
-      <c r="G5" s="28" t="n">
-        <v>55449.64969540044</v>
-      </c>
-      <c r="H5" s="28" t="n">
-        <v>62846.51217785713</v>
-      </c>
-      <c r="I5" s="28" t="n">
-        <v>69788.10693633846</v>
+      <c r="D5" s="28">
+        <f>C5+'Income Statement'!D5*(Assumptions!$B$33-Assumptions!$C$34)</f>
+        <v/>
+      </c>
+      <c r="E5" s="28">
+        <f>D5-DCF!B12+DCF!B8</f>
+        <v/>
+      </c>
+      <c r="F5" s="28">
+        <f>E5-DCF!C12+DCF!C8</f>
+        <v/>
+      </c>
+      <c r="G5" s="28">
+        <f>F5-DCF!D12+DCF!D8</f>
+        <v/>
+      </c>
+      <c r="H5" s="28">
+        <f>G5-DCF!E12+DCF!E8</f>
+        <v/>
+      </c>
+      <c r="I5" s="28">
+        <f>H5-DCF!F12+DCF!F8</f>
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -926,13 +995,13 @@
           <t>Inventories</t>
         </is>
       </c>
-      <c r="B6" s="28" t="n">
+      <c r="B6" s="22" t="n">
         <v>30881.8</v>
       </c>
-      <c r="C6" s="28" t="n">
+      <c r="C6" s="22" t="n">
         <v>56795.9</v>
       </c>
-      <c r="D6" s="28" t="inlineStr">
+      <c r="D6" s="22" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -944,13 +1013,13 @@
           <t>Contract assets</t>
         </is>
       </c>
-      <c r="B7" s="28" t="n">
+      <c r="B7" s="22" t="n">
         <v>16179.6</v>
       </c>
-      <c r="C7" s="28" t="n">
+      <c r="C7" s="22" t="n">
         <v>18052</v>
       </c>
-      <c r="D7" s="28" t="inlineStr">
+      <c r="D7" s="22" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -962,13 +1031,13 @@
           <t>Trade and other receivables</t>
         </is>
       </c>
-      <c r="B8" s="28" t="n">
+      <c r="B8" s="22" t="n">
         <v>46591.9</v>
       </c>
-      <c r="C8" s="28" t="n">
+      <c r="C8" s="22" t="n">
         <v>86736.3</v>
       </c>
-      <c r="D8" s="28" t="inlineStr">
+      <c r="D8" s="22" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -980,18 +1049,19 @@
           <t>Cash and cash equivalents</t>
         </is>
       </c>
-      <c r="B9" s="28" t="n">
+      <c r="B9" s="22" t="n">
         <v>25552</v>
       </c>
-      <c r="C9" s="28" t="n">
+      <c r="C9" s="22" t="n">
         <v>38180</v>
       </c>
-      <c r="D9" s="28" t="n">
-        <v>51827.72053413192</v>
+      <c r="D9" s="28">
+        <f>D11-D17</f>
+        <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="14" t="inlineStr">
+      <c r="A10" s="15" t="inlineStr">
         <is>
           <t>Total assets</t>
         </is>
@@ -1005,11 +1075,11 @@
       <c r="D10" s="29" t="n">
         <v>311090</v>
       </c>
-      <c r="E10" s="14" t="n"/>
-      <c r="F10" s="14" t="n"/>
-      <c r="G10" s="14" t="n"/>
-      <c r="H10" s="14" t="n"/>
-      <c r="I10" s="14" t="n"/>
+      <c r="E10" s="15" t="n"/>
+      <c r="F10" s="15" t="n"/>
+      <c r="G10" s="15" t="n"/>
+      <c r="H10" s="15" t="n"/>
+      <c r="I10" s="15" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -1017,14 +1087,15 @@
           <t>Loans and borrowings</t>
         </is>
       </c>
-      <c r="B11" s="28" t="n">
+      <c r="B11" s="22" t="n">
         <v>41766.5</v>
       </c>
-      <c r="C11" s="28" t="n">
+      <c r="C11" s="22" t="n">
         <v>59082.9</v>
       </c>
-      <c r="D11" s="28" t="n">
-        <v>71616.72053413192</v>
+      <c r="D11" s="28">
+        <f>AVERAGE(B23:B25)</f>
+        <v/>
       </c>
     </row>
     <row r="12">
@@ -1033,13 +1104,13 @@
           <t>Trade and other payables</t>
         </is>
       </c>
-      <c r="B12" s="28" t="n">
+      <c r="B12" s="22" t="n">
         <v>31938.1</v>
       </c>
-      <c r="C12" s="28" t="n">
+      <c r="C12" s="22" t="n">
         <v>54808.2</v>
       </c>
-      <c r="D12" s="28" t="inlineStr">
+      <c r="D12" s="22" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1051,20 +1122,20 @@
           <t>Contract liabilities</t>
         </is>
       </c>
-      <c r="B13" s="28" t="n">
+      <c r="B13" s="22" t="n">
         <v>25060.3</v>
       </c>
-      <c r="C13" s="28" t="n">
+      <c r="C13" s="22" t="n">
         <v>53281.1</v>
       </c>
-      <c r="D13" s="28" t="inlineStr">
+      <c r="D13" s="22" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="14" t="inlineStr">
+      <c r="A14" s="15" t="inlineStr">
         <is>
           <t>Equity attributable to shareholders</t>
         </is>
@@ -1075,23 +1146,29 @@
       <c r="C14" s="29" t="n">
         <v>55274.9</v>
       </c>
-      <c r="D14" s="29" t="n">
-        <v>70464.12212399999</v>
-      </c>
-      <c r="E14" s="29" t="n">
-        <v>88016.30831700345</v>
-      </c>
-      <c r="F14" s="29" t="n">
-        <v>107257.8480990719</v>
-      </c>
-      <c r="G14" s="29" t="n">
-        <v>128828.3971928497</v>
-      </c>
-      <c r="H14" s="29" t="n">
-        <v>153061.8093358987</v>
-      </c>
-      <c r="I14" s="29" t="n">
-        <v>180229.6468638956</v>
+      <c r="D14" s="29">
+        <f>C14+'Income Statement'!D17-Assumptions!$C$55*Assumptions!$C$6</f>
+        <v/>
+      </c>
+      <c r="E14" s="29">
+        <f>D14+'Income Statement'!E17*(1-Assumptions!$C$56)</f>
+        <v/>
+      </c>
+      <c r="F14" s="29">
+        <f>E14+'Income Statement'!F17*(1-Assumptions!$C$56)</f>
+        <v/>
+      </c>
+      <c r="G14" s="29">
+        <f>F14+'Income Statement'!G17*(1-Assumptions!$C$56)</f>
+        <v/>
+      </c>
+      <c r="H14" s="29">
+        <f>G14+'Income Statement'!H17*(1-Assumptions!$C$56)</f>
+        <v/>
+      </c>
+      <c r="I14" s="29">
+        <f>H14+'Income Statement'!I17*(1-Assumptions!$C$56)</f>
+        <v/>
       </c>
     </row>
     <row r="15">
@@ -1100,13 +1177,13 @@
           <t>Non-controlling interests</t>
         </is>
       </c>
-      <c r="B15" s="28" t="n">
+      <c r="B15" s="22" t="n">
         <v>2384</v>
       </c>
-      <c r="C15" s="28" t="n">
+      <c r="C15" s="22" t="n">
         <v>4251.8</v>
       </c>
-      <c r="D15" s="28" t="n">
+      <c r="D15" s="22" t="n">
         <v>5851.8</v>
       </c>
     </row>
@@ -1116,33 +1193,39 @@
           <t>Net working capital</t>
         </is>
       </c>
-      <c r="B16" s="28" t="n">
+      <c r="B16" s="22" t="n">
         <v>36654.90000000001</v>
       </c>
-      <c r="C16" s="28" t="n">
+      <c r="C16" s="22" t="n">
         <v>53494.90000000002</v>
       </c>
-      <c r="D16" s="28" t="n">
-        <v>64641.27</v>
-      </c>
-      <c r="E16" s="28" t="n">
-        <v>84077.89605497415</v>
-      </c>
-      <c r="F16" s="28" t="n">
-        <v>93959.91901385502</v>
-      </c>
-      <c r="G16" s="28" t="n">
-        <v>101717.8965779308</v>
-      </c>
-      <c r="H16" s="28" t="n">
-        <v>109759.8949009704</v>
-      </c>
-      <c r="I16" s="28" t="n">
-        <v>118264.2069963484</v>
+      <c r="D16" s="28">
+        <f>'Income Statement'!D5*Assumptions!$C$32</f>
+        <v/>
+      </c>
+      <c r="E16" s="28">
+        <f>'Income Statement'!E5*Assumptions!$C$32</f>
+        <v/>
+      </c>
+      <c r="F16" s="28">
+        <f>'Income Statement'!F5*Assumptions!$C$32</f>
+        <v/>
+      </c>
+      <c r="G16" s="28">
+        <f>'Income Statement'!G5*Assumptions!$C$32</f>
+        <v/>
+      </c>
+      <c r="H16" s="28">
+        <f>'Income Statement'!H5*Assumptions!$C$32</f>
+        <v/>
+      </c>
+      <c r="I16" s="28">
+        <f>'Income Statement'!I5*Assumptions!$C$32</f>
+        <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="14" t="inlineStr">
+      <c r="A17" s="15" t="inlineStr">
         <is>
           <t>Net bank debt</t>
         </is>
@@ -1153,23 +1236,29 @@
       <c r="C17" s="29" t="n">
         <v>20028</v>
       </c>
-      <c r="D17" s="29" t="n">
-        <v>19789</v>
-      </c>
-      <c r="E17" s="29" t="n">
-        <v>27358.32227038879</v>
-      </c>
-      <c r="F17" s="29" t="n">
-        <v>23956.92235029294</v>
-      </c>
-      <c r="G17" s="29" t="n">
-        <v>16043.86491166744</v>
-      </c>
-      <c r="H17" s="29" t="n">
-        <v>5128.832060029791</v>
-      </c>
-      <c r="I17" s="29" t="n">
-        <v>-9024.949133257413</v>
+      <c r="D17" s="29">
+        <f>Assumptions!$C$50</f>
+        <v/>
+      </c>
+      <c r="E17" s="29">
+        <f>D17-DCF!B14-'Income Statement'!E11*(1-Assumptions!$C$7)+Assumptions!$C$56*'Income Statement'!E17</f>
+        <v/>
+      </c>
+      <c r="F17" s="29">
+        <f>E17-DCF!C14-'Income Statement'!F11*(1-Assumptions!$C$7)+Assumptions!$C$56*'Income Statement'!F17</f>
+        <v/>
+      </c>
+      <c r="G17" s="29">
+        <f>F17-DCF!D14-'Income Statement'!G11*(1-Assumptions!$C$7)+Assumptions!$C$56*'Income Statement'!G17</f>
+        <v/>
+      </c>
+      <c r="H17" s="29">
+        <f>G17-DCF!E14-'Income Statement'!H11*(1-Assumptions!$C$7)+Assumptions!$C$56*'Income Statement'!H17</f>
+        <v/>
+      </c>
+      <c r="I17" s="29">
+        <f>H17-DCF!F14-'Income Statement'!I11*(1-Assumptions!$C$7)+Assumptions!$C$56*'Income Statement'!I17</f>
+        <v/>
       </c>
     </row>
     <row r="18">
@@ -1178,35 +1267,35 @@
           <t>Net debt / EBITDA</t>
         </is>
       </c>
-      <c r="B18" s="33">
+      <c r="B18" s="34">
         <f>B17/'Income Statement'!B7</f>
         <v/>
       </c>
-      <c r="C18" s="33">
+      <c r="C18" s="34">
         <f>C17/'Income Statement'!C7</f>
         <v/>
       </c>
-      <c r="D18" s="33">
+      <c r="D18" s="34">
         <f>D17/'Income Statement'!D7</f>
         <v/>
       </c>
-      <c r="E18" s="33">
+      <c r="E18" s="34">
         <f>E17/'Income Statement'!E7</f>
         <v/>
       </c>
-      <c r="F18" s="33">
+      <c r="F18" s="34">
         <f>F17/'Income Statement'!F7</f>
         <v/>
       </c>
-      <c r="G18" s="33">
+      <c r="G18" s="34">
         <f>G17/'Income Statement'!G7</f>
         <v/>
       </c>
-      <c r="H18" s="33">
+      <c r="H18" s="34">
         <f>H17/'Income Statement'!H7</f>
         <v/>
       </c>
-      <c r="I18" s="33">
+      <c r="I18" s="34">
         <f>I17/'Income Statement'!I7</f>
         <v/>
       </c>
@@ -1236,6 +1325,59 @@
         <is>
           <t>Note: this is a CONDENSED layout, so it does not foot to zero — the residual row above is the block of other liabilities, provisions, deferred tax and related-party balances that is not shown separately. For FY2024 that residual is 22,828, which reconciles to the audited statements (provisions 13,440 + 943, deferred tax 3,670, related parties 2,050 + 95, other liabilities 2,631 = 22,829). FY2025 shows only the disclosed lines (total assets, net bank debt) plus rolled-forward equity and triangulated debt and cash; the valuation bridge uses only the disclosed net bank debt.</t>
         </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>FY2025 gross debt — three independent triangulations</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>EGP mn</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>Balance-sheet residual (assets less equity and non-debt liabilities)</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="n">
+        <v>76165.80577232633</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>FY2024 debt scaled with revenue growth</t>
+        </is>
+      </c>
+      <c r="B24" s="22" t="n">
+        <v>71579.70996905792</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>Implied from the cash balance and the disclosed net debt</t>
+        </is>
+      </c>
+      <c r="B25" s="22" t="n">
+        <v>67104.64586101151</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="15" t="inlineStr">
+        <is>
+          <t>Average — the figure carried on row 11</t>
+        </is>
+      </c>
+      <c r="B26" s="29">
+        <f>AVERAGE(B23:B25)</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -1249,7 +1391,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -1333,26 +1475,33 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B5" s="28" t="n">
-        <v>20035.1</v>
-      </c>
-      <c r="C5" s="28" t="n">
-        <v>31601.6</v>
-      </c>
-      <c r="D5" s="28" t="n">
-        <v>41094.2415179939</v>
-      </c>
-      <c r="E5" s="28" t="n">
-        <v>44940.76148621193</v>
-      </c>
-      <c r="F5" s="28" t="n">
-        <v>48914.41709217701</v>
-      </c>
-      <c r="G5" s="28" t="n">
-        <v>53240.26178029377</v>
-      </c>
-      <c r="H5" s="28" t="n">
-        <v>57882.44686110957</v>
+      <c r="B5" s="18">
+        <f>'Income Statement'!B7</f>
+        <v/>
+      </c>
+      <c r="C5" s="18">
+        <f>'Income Statement'!C7</f>
+        <v/>
+      </c>
+      <c r="D5" s="18">
+        <f>'Income Statement'!E7</f>
+        <v/>
+      </c>
+      <c r="E5" s="18">
+        <f>'Income Statement'!F7</f>
+        <v/>
+      </c>
+      <c r="F5" s="18">
+        <f>'Income Statement'!G7</f>
+        <v/>
+      </c>
+      <c r="G5" s="18">
+        <f>'Income Statement'!H7</f>
+        <v/>
+      </c>
+      <c r="H5" s="18">
+        <f>'Income Statement'!I7</f>
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -1366,7 +1515,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C6" s="28" t="n">
+      <c r="C6" s="22" t="n">
         <v>-7706.9</v>
       </c>
     </row>
@@ -1381,7 +1530,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C7" s="28" t="n">
+      <c r="C7" s="22" t="n">
         <v>-4891</v>
       </c>
     </row>
@@ -1396,42 +1545,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C8" s="28" t="n">
+      <c r="C8" s="22" t="n">
         <v>3979.4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>Capital expenditure</t>
-        </is>
-      </c>
-      <c r="B9" s="28" t="n">
-        <v>-4830</v>
-      </c>
-      <c r="C9" s="28" t="n">
-        <v>-8765.700000000001</v>
-      </c>
-      <c r="D9" s="28" t="n">
-        <v>-10966.68209412706</v>
-      </c>
-      <c r="E9" s="28" t="n">
-        <v>-11847.12022348607</v>
-      </c>
-      <c r="F9" s="28" t="n">
-        <v>-12383.04827905244</v>
-      </c>
-      <c r="G9" s="28" t="n">
-        <v>-12407.64029315317</v>
-      </c>
-      <c r="H9" s="28" t="n">
-        <v>-12340.61290396679</v>
+          <t>NOPAT</t>
+        </is>
+      </c>
+      <c r="B9" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C9" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D9" s="18">
+        <f>DCF!B10</f>
+        <v/>
+      </c>
+      <c r="E9" s="18">
+        <f>DCF!C10</f>
+        <v/>
+      </c>
+      <c r="F9" s="18">
+        <f>DCF!D10</f>
+        <v/>
+      </c>
+      <c r="G9" s="18">
+        <f>DCF!E10</f>
+        <v/>
+      </c>
+      <c r="H9" s="18">
+        <f>DCF!F10</f>
+        <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Change in working capital</t>
+          <t>Add back depreciation and amortisation</t>
         </is>
       </c>
       <c r="B10" s="28" t="inlineStr">
@@ -1439,102 +1597,152 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C10" s="28" t="n">
-        <v>-16840.00000000001</v>
-      </c>
-      <c r="D10" s="28" t="n">
-        <v>-19436.62605497414</v>
-      </c>
-      <c r="E10" s="28" t="n">
-        <v>-9882.022958880872</v>
-      </c>
-      <c r="F10" s="28" t="n">
-        <v>-7757.977564075773</v>
-      </c>
-      <c r="G10" s="28" t="n">
-        <v>-8041.998323039588</v>
-      </c>
-      <c r="H10" s="28" t="n">
-        <v>-8504.31209537806</v>
+      <c r="C10" s="28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D10" s="18">
+        <f>DCF!B11</f>
+        <v/>
+      </c>
+      <c r="E10" s="18">
+        <f>DCF!C11</f>
+        <v/>
+      </c>
+      <c r="F10" s="18">
+        <f>DCF!D11</f>
+        <v/>
+      </c>
+      <c r="G10" s="18">
+        <f>DCF!E11</f>
+        <v/>
+      </c>
+      <c r="H10" s="18">
+        <f>DCF!F11</f>
+        <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>NOPAT</t>
-        </is>
-      </c>
-      <c r="B11" s="28" t="inlineStr">
+          <t>Capital expenditure</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="n">
+        <v>-4830</v>
+      </c>
+      <c r="C11" s="22" t="n">
+        <v>-8765.700000000001</v>
+      </c>
+      <c r="D11" s="18">
+        <f>DCF!B12</f>
+        <v/>
+      </c>
+      <c r="E11" s="18">
+        <f>DCF!C12</f>
+        <v/>
+      </c>
+      <c r="F11" s="18">
+        <f>DCF!D12</f>
+        <v/>
+      </c>
+      <c r="G11" s="18">
+        <f>DCF!E12</f>
+        <v/>
+      </c>
+      <c r="H11" s="18">
+        <f>DCF!F12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Change in working capital</t>
+        </is>
+      </c>
+      <c r="B12" s="28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C11" s="28" t="inlineStr">
+      <c r="C12" s="28">
+        <f>-('Balance Sheet'!C16-'Balance Sheet'!B16)</f>
+        <v/>
+      </c>
+      <c r="D12" s="18">
+        <f>DCF!B13</f>
+        <v/>
+      </c>
+      <c r="E12" s="18">
+        <f>DCF!C13</f>
+        <v/>
+      </c>
+      <c r="F12" s="18">
+        <f>DCF!D13</f>
+        <v/>
+      </c>
+      <c r="G12" s="18">
+        <f>DCF!E13</f>
+        <v/>
+      </c>
+      <c r="H12" s="18">
+        <f>DCF!F13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t>Free cash flow to the firm</t>
+        </is>
+      </c>
+      <c r="B13" s="29" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D11" s="28" t="n">
-        <v>27941.92708878707</v>
-      </c>
-      <c r="E11" s="28" t="n">
-        <v>30488.46519190195</v>
-      </c>
-      <c r="F11" s="28" t="n">
-        <v>33203.08049064926</v>
-      </c>
-      <c r="G11" s="28" t="n">
-        <v>36172.11297719798</v>
-      </c>
-      <c r="H11" s="28" t="n">
-        <v>39362.57153671807</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="14" t="inlineStr">
-        <is>
-          <t>Free cash flow to the firm</t>
-        </is>
-      </c>
-      <c r="B12" s="29" t="inlineStr">
+      <c r="C13" s="29" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C12" s="29" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D12" s="29" t="n">
-        <v>1376.957672630335</v>
-      </c>
-      <c r="E12" s="29" t="n">
-        <v>13048.796573211</v>
-      </c>
-      <c r="F12" s="29" t="n">
-        <v>17705.69775216571</v>
-      </c>
-      <c r="G12" s="29" t="n">
-        <v>20733.25217170169</v>
-      </c>
-      <c r="H12" s="29" t="n">
-        <v>23916.66468285869</v>
-      </c>
-      <c r="I12" s="14" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="D13" s="29">
+        <f>D9+D10+D11+D12</f>
+        <v/>
+      </c>
+      <c r="E13" s="29">
+        <f>E9+E10+E11+E12</f>
+        <v/>
+      </c>
+      <c r="F13" s="29">
+        <f>F9+F10+F11+F12</f>
+        <v/>
+      </c>
+      <c r="G13" s="29">
+        <f>G9+G10+G11+G12</f>
+        <v/>
+      </c>
+      <c r="H13" s="29">
+        <f>H9+H10+H11+H12</f>
+        <v/>
+      </c>
+      <c r="I13" s="15" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>Cash conversion — operating cash flow as a share of EBITDA, FY2024</t>
         </is>
       </c>
-      <c r="C14" s="10" t="n">
-        <v>0.1259240038479064</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="C15" s="11">
+        <f>C8/C5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>This single ratio is the crux of the valuation: the company earned far more EBITDA than it converted to cash, because growth was funded through working capital.</t>
         </is>
@@ -1551,7 +1759,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1583,7 +1791,7 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>EGP mn unless stated</t>
+          <t>EGP mn unless stated. Every cell on this sheet is a link or a ratio; nothing is typed twice</t>
         </is>
       </c>
     </row>
@@ -1640,29 +1848,37 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B5" s="28" t="n">
-        <v>152186.2</v>
-      </c>
-      <c r="C5" s="28" t="n">
-        <v>231981.8</v>
-      </c>
-      <c r="D5" s="28" t="n">
-        <v>281049</v>
-      </c>
-      <c r="E5" s="28" t="n">
-        <v>365556.0698042354</v>
-      </c>
-      <c r="F5" s="28" t="n">
-        <v>408521.3870167609</v>
-      </c>
-      <c r="G5" s="28" t="n">
-        <v>442251.724251873</v>
-      </c>
-      <c r="H5" s="28" t="n">
-        <v>477216.9343520451</v>
-      </c>
-      <c r="I5" s="28" t="n">
-        <v>514192.2043319497</v>
+      <c r="B5" s="18">
+        <f>'Income Statement'!B5</f>
+        <v/>
+      </c>
+      <c r="C5" s="18">
+        <f>'Income Statement'!C5</f>
+        <v/>
+      </c>
+      <c r="D5" s="18">
+        <f>'Income Statement'!D5</f>
+        <v/>
+      </c>
+      <c r="E5" s="18">
+        <f>'Income Statement'!E5</f>
+        <v/>
+      </c>
+      <c r="F5" s="18">
+        <f>'Income Statement'!F5</f>
+        <v/>
+      </c>
+      <c r="G5" s="18">
+        <f>'Income Statement'!G5</f>
+        <v/>
+      </c>
+      <c r="H5" s="18">
+        <f>'Income Statement'!H5</f>
+        <v/>
+      </c>
+      <c r="I5" s="18">
+        <f>'Income Statement'!I5</f>
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -1671,31 +1887,38 @@
           <t>Revenue growth</t>
         </is>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C6" s="10" t="n">
-        <v>0.5243287499129354</v>
-      </c>
-      <c r="D6" s="10" t="n">
-        <v>0.2115131445656513</v>
-      </c>
-      <c r="E6" s="10" t="n">
-        <v>0.3006844706945602</v>
-      </c>
-      <c r="F6" s="10" t="n">
-        <v>0.1175341370628438</v>
-      </c>
-      <c r="G6" s="10" t="n">
-        <v>0.08256688219294661</v>
-      </c>
-      <c r="H6" s="10" t="n">
-        <v>0.07906178355623239</v>
-      </c>
-      <c r="I6" s="10" t="n">
-        <v>0.07748105173616437</v>
+      <c r="C6" s="11">
+        <f>C5/B5-1</f>
+        <v/>
+      </c>
+      <c r="D6" s="11">
+        <f>D5/C5-1</f>
+        <v/>
+      </c>
+      <c r="E6" s="11">
+        <f>E5/D5-1</f>
+        <v/>
+      </c>
+      <c r="F6" s="11">
+        <f>F5/E5-1</f>
+        <v/>
+      </c>
+      <c r="G6" s="11">
+        <f>G5/F5-1</f>
+        <v/>
+      </c>
+      <c r="H6" s="11">
+        <f>H5/G5-1</f>
+        <v/>
+      </c>
+      <c r="I6" s="11">
+        <f>I5/H5-1</f>
+        <v/>
       </c>
     </row>
     <row r="7">
@@ -1704,29 +1927,37 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B7" s="28" t="n">
-        <v>20035.1</v>
-      </c>
-      <c r="C7" s="28" t="n">
-        <v>31601.6</v>
-      </c>
-      <c r="D7" s="28" t="n">
-        <v>30622.08783333333</v>
-      </c>
-      <c r="E7" s="28" t="n">
-        <v>41094.2415179939</v>
-      </c>
-      <c r="F7" s="28" t="n">
-        <v>44940.76148621193</v>
-      </c>
-      <c r="G7" s="28" t="n">
-        <v>48914.41709217701</v>
-      </c>
-      <c r="H7" s="28" t="n">
-        <v>53240.26178029377</v>
-      </c>
-      <c r="I7" s="28" t="n">
-        <v>57882.44686110957</v>
+      <c r="B7" s="18">
+        <f>'Income Statement'!B7</f>
+        <v/>
+      </c>
+      <c r="C7" s="18">
+        <f>'Income Statement'!C7</f>
+        <v/>
+      </c>
+      <c r="D7" s="18">
+        <f>'Income Statement'!D7</f>
+        <v/>
+      </c>
+      <c r="E7" s="18">
+        <f>'Income Statement'!E7</f>
+        <v/>
+      </c>
+      <c r="F7" s="18">
+        <f>'Income Statement'!F7</f>
+        <v/>
+      </c>
+      <c r="G7" s="18">
+        <f>'Income Statement'!G7</f>
+        <v/>
+      </c>
+      <c r="H7" s="18">
+        <f>'Income Statement'!H7</f>
+        <v/>
+      </c>
+      <c r="I7" s="18">
+        <f>'Income Statement'!I7</f>
+        <v/>
       </c>
     </row>
     <row r="8">
@@ -1735,29 +1966,37 @@
           <t>EBITDA margin</t>
         </is>
       </c>
-      <c r="B8" s="10" t="n">
-        <v>0.1316485988874155</v>
-      </c>
-      <c r="C8" s="10" t="n">
-        <v>0.1362244796790093</v>
-      </c>
-      <c r="D8" s="10" t="n">
-        <v>0.1089564020271673</v>
-      </c>
-      <c r="E8" s="10" t="n">
-        <v>0.112415700114078</v>
-      </c>
-      <c r="F8" s="10" t="n">
-        <v>0.1100083445187365</v>
-      </c>
-      <c r="G8" s="10" t="n">
-        <v>0.1106031122318905</v>
-      </c>
-      <c r="H8" s="10" t="n">
-        <v>0.1115640664608482</v>
-      </c>
-      <c r="I8" s="10" t="n">
-        <v>0.1125696702000991</v>
+      <c r="B8" s="11">
+        <f>B7/B5</f>
+        <v/>
+      </c>
+      <c r="C8" s="11">
+        <f>C7/C5</f>
+        <v/>
+      </c>
+      <c r="D8" s="11">
+        <f>D7/D5</f>
+        <v/>
+      </c>
+      <c r="E8" s="11">
+        <f>E7/E5</f>
+        <v/>
+      </c>
+      <c r="F8" s="11">
+        <f>F7/F5</f>
+        <v/>
+      </c>
+      <c r="G8" s="11">
+        <f>G7/G5</f>
+        <v/>
+      </c>
+      <c r="H8" s="11">
+        <f>H7/H5</f>
+        <v/>
+      </c>
+      <c r="I8" s="11">
+        <f>I7/I5</f>
+        <v/>
       </c>
     </row>
     <row r="9">
@@ -1766,29 +2005,37 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B9" s="28" t="n">
-        <v>17739.1</v>
-      </c>
-      <c r="C9" s="28" t="n">
-        <v>29341.7</v>
-      </c>
-      <c r="D9" s="28" t="n">
-        <v>27671.07333333333</v>
-      </c>
-      <c r="E9" s="28" t="n">
-        <v>37255.90278504942</v>
-      </c>
-      <c r="F9" s="28" t="n">
-        <v>40651.28692253594</v>
-      </c>
-      <c r="G9" s="28" t="n">
-        <v>44270.77398753235</v>
-      </c>
-      <c r="H9" s="28" t="n">
-        <v>48229.4839695973</v>
-      </c>
-      <c r="I9" s="28" t="n">
-        <v>52483.42871562409</v>
+      <c r="B9" s="18">
+        <f>'Income Statement'!B10</f>
+        <v/>
+      </c>
+      <c r="C9" s="18">
+        <f>'Income Statement'!C10</f>
+        <v/>
+      </c>
+      <c r="D9" s="18">
+        <f>'Income Statement'!D10</f>
+        <v/>
+      </c>
+      <c r="E9" s="18">
+        <f>'Income Statement'!E10</f>
+        <v/>
+      </c>
+      <c r="F9" s="18">
+        <f>'Income Statement'!F10</f>
+        <v/>
+      </c>
+      <c r="G9" s="18">
+        <f>'Income Statement'!G10</f>
+        <v/>
+      </c>
+      <c r="H9" s="18">
+        <f>'Income Statement'!H10</f>
+        <v/>
+      </c>
+      <c r="I9" s="18">
+        <f>'Income Statement'!I10</f>
+        <v/>
       </c>
     </row>
     <row r="10">
@@ -1797,29 +2044,37 @@
           <t>Attributable profit</t>
         </is>
       </c>
-      <c r="B10" s="28" t="n">
-        <v>10115.7</v>
-      </c>
-      <c r="C10" s="28" t="n">
-        <v>17461.4</v>
-      </c>
-      <c r="D10" s="28" t="n">
-        <v>17330</v>
-      </c>
-      <c r="E10" s="28" t="n">
-        <v>23402.91492400461</v>
-      </c>
-      <c r="F10" s="28" t="n">
-        <v>25655.38637609128</v>
-      </c>
-      <c r="G10" s="28" t="n">
-        <v>28760.73212503701</v>
-      </c>
-      <c r="H10" s="28" t="n">
-        <v>32311.21619073199</v>
-      </c>
-      <c r="I10" s="28" t="n">
-        <v>36223.78337066263</v>
+      <c r="B10" s="18">
+        <f>'Income Statement'!B17</f>
+        <v/>
+      </c>
+      <c r="C10" s="18">
+        <f>'Income Statement'!C17</f>
+        <v/>
+      </c>
+      <c r="D10" s="18">
+        <f>'Income Statement'!D17</f>
+        <v/>
+      </c>
+      <c r="E10" s="18">
+        <f>'Income Statement'!E17</f>
+        <v/>
+      </c>
+      <c r="F10" s="18">
+        <f>'Income Statement'!F17</f>
+        <v/>
+      </c>
+      <c r="G10" s="18">
+        <f>'Income Statement'!G17</f>
+        <v/>
+      </c>
+      <c r="H10" s="18">
+        <f>'Income Statement'!H17</f>
+        <v/>
+      </c>
+      <c r="I10" s="18">
+        <f>'Income Statement'!I17</f>
+        <v/>
       </c>
     </row>
     <row r="11">
@@ -1843,20 +2098,25 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E11" s="28" t="n">
-        <v>1376.957672630335</v>
-      </c>
-      <c r="F11" s="28" t="n">
-        <v>13048.796573211</v>
-      </c>
-      <c r="G11" s="28" t="n">
-        <v>17705.69775216571</v>
-      </c>
-      <c r="H11" s="28" t="n">
-        <v>20733.25217170169</v>
-      </c>
-      <c r="I11" s="28" t="n">
-        <v>23916.66468285869</v>
+      <c r="E11" s="18">
+        <f>'Cash Flow'!D13</f>
+        <v/>
+      </c>
+      <c r="F11" s="18">
+        <f>'Cash Flow'!E13</f>
+        <v/>
+      </c>
+      <c r="G11" s="18">
+        <f>'Cash Flow'!F13</f>
+        <v/>
+      </c>
+      <c r="H11" s="18">
+        <f>'Cash Flow'!G13</f>
+        <v/>
+      </c>
+      <c r="I11" s="18">
+        <f>'Cash Flow'!H13</f>
+        <v/>
       </c>
     </row>
     <row r="12">
@@ -1865,29 +2125,37 @@
           <t>Net bank debt</t>
         </is>
       </c>
-      <c r="B12" s="28" t="n">
-        <v>14768</v>
-      </c>
-      <c r="C12" s="28" t="n">
-        <v>20028</v>
-      </c>
-      <c r="D12" s="28" t="n">
-        <v>19789</v>
-      </c>
-      <c r="E12" s="28" t="n">
-        <v>27358.32227038879</v>
-      </c>
-      <c r="F12" s="28" t="n">
-        <v>23956.92235029294</v>
-      </c>
-      <c r="G12" s="28" t="n">
-        <v>16043.86491166744</v>
-      </c>
-      <c r="H12" s="28" t="n">
-        <v>5128.832060029791</v>
-      </c>
-      <c r="I12" s="28" t="n">
-        <v>-9024.949133257413</v>
+      <c r="B12" s="18">
+        <f>'Balance Sheet'!B17</f>
+        <v/>
+      </c>
+      <c r="C12" s="18">
+        <f>'Balance Sheet'!C17</f>
+        <v/>
+      </c>
+      <c r="D12" s="18">
+        <f>'Balance Sheet'!D17</f>
+        <v/>
+      </c>
+      <c r="E12" s="18">
+        <f>'Balance Sheet'!E17</f>
+        <v/>
+      </c>
+      <c r="F12" s="18">
+        <f>'Balance Sheet'!F17</f>
+        <v/>
+      </c>
+      <c r="G12" s="18">
+        <f>'Balance Sheet'!G17</f>
+        <v/>
+      </c>
+      <c r="H12" s="18">
+        <f>'Balance Sheet'!H17</f>
+        <v/>
+      </c>
+      <c r="I12" s="18">
+        <f>'Balance Sheet'!I17</f>
+        <v/>
       </c>
     </row>
     <row r="13">
@@ -1906,25 +2174,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D13" s="28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E13" s="28" t="n">
-        <v>125689.6949161567</v>
-      </c>
-      <c r="F13" s="28" t="n">
-        <v>143129.3635348477</v>
-      </c>
-      <c r="G13" s="28" t="n">
-        <v>158626.7462733312</v>
-      </c>
-      <c r="H13" s="28" t="n">
-        <v>174065.6070788275</v>
-      </c>
-      <c r="I13" s="28" t="n">
-        <v>189511.5139326869</v>
+      <c r="D13" s="18">
+        <f>'Balance Sheet'!D16+'Balance Sheet'!D5+Assumptions!$C$52</f>
+        <v/>
+      </c>
+      <c r="E13" s="18">
+        <f>'Balance Sheet'!E16+'Balance Sheet'!E5+Assumptions!$C$52</f>
+        <v/>
+      </c>
+      <c r="F13" s="18">
+        <f>'Balance Sheet'!F16+'Balance Sheet'!F5+Assumptions!$C$52</f>
+        <v/>
+      </c>
+      <c r="G13" s="18">
+        <f>'Balance Sheet'!G16+'Balance Sheet'!G5+Assumptions!$C$52</f>
+        <v/>
+      </c>
+      <c r="H13" s="18">
+        <f>'Balance Sheet'!H16+'Balance Sheet'!H5+Assumptions!$C$52</f>
+        <v/>
+      </c>
+      <c r="I13" s="18">
+        <f>'Balance Sheet'!I16+'Balance Sheet'!I5+Assumptions!$C$52</f>
+        <v/>
       </c>
     </row>
     <row r="14">
@@ -1933,35 +2205,47 @@
           <t>Return on invested capital</t>
         </is>
       </c>
-      <c r="B14" s="10" t="inlineStr">
+      <c r="B14" s="11" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C14" s="10" t="inlineStr">
+      <c r="C14" s="11" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D14" s="10" t="inlineStr">
+      <c r="D14" s="11" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E14" s="10" t="n">
-        <v>0.2223088146361256</v>
-      </c>
-      <c r="F14" s="10" t="n">
-        <v>0.2130133498740734</v>
-      </c>
-      <c r="G14" s="10" t="n">
-        <v>0.2093157760005789</v>
-      </c>
-      <c r="H14" s="10" t="n">
-        <v>0.2078073525507945</v>
-      </c>
-      <c r="I14" s="10" t="n">
-        <v>0.2077054355161732</v>
+      <c r="E14" s="16">
+        <f>DCF!B10/E13</f>
+        <v/>
+      </c>
+      <c r="F14" s="16">
+        <f>DCF!C10/F13</f>
+        <v/>
+      </c>
+      <c r="G14" s="16">
+        <f>DCF!D10/G13</f>
+        <v/>
+      </c>
+      <c r="H14" s="16">
+        <f>DCF!E10/H13</f>
+        <v/>
+      </c>
+      <c r="I14" s="16">
+        <f>DCF!F10/I13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Return on invested capital is the DCF's NOPAT over the same year's invested capital, which is why the FY2025 column carries capital but no return: FY2025 NOPAT is struck on a different, post-financing basis and is reported in the terminal-growth reconciliation on the Per-Share &amp; Ratios sheet.</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -2005,7 +2289,7 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>A map of price dispersion. It carries no view on value and is never blended with the valuation.</t>
+          <t>A map of price dispersion. It carries no view on value and is never blended with the valuation. Each figure is an engine output, not a formula.</t>
         </is>
       </c>
     </row>
@@ -2052,22 +2336,22 @@
           <t>One month — to 2026-09-06</t>
         </is>
       </c>
-      <c r="B5" s="9" t="n">
+      <c r="B5" s="7" t="n">
         <v>87.47283768142248</v>
       </c>
-      <c r="C5" s="9" t="n">
+      <c r="C5" s="7" t="n">
         <v>99.10709529417855</v>
       </c>
-      <c r="D5" s="9" t="n">
+      <c r="D5" s="7" t="n">
         <v>106.6824907823649</v>
       </c>
-      <c r="E5" s="9" t="n">
+      <c r="E5" s="7" t="n">
         <v>114.8982326066757</v>
       </c>
-      <c r="F5" s="9" t="n">
+      <c r="F5" s="7" t="n">
         <v>130.1682181904347</v>
       </c>
-      <c r="G5" s="10" t="n">
+      <c r="G5" s="9" t="n">
         <v>0.55144</v>
       </c>
     </row>
@@ -2077,22 +2361,22 @@
           <t>Three months — to 2026-11-05</t>
         </is>
       </c>
-      <c r="B6" s="9" t="n">
+      <c r="B6" s="7" t="n">
         <v>78.29508034182929</v>
       </c>
-      <c r="C6" s="9" t="n">
+      <c r="C6" s="7" t="n">
         <v>96.93670208976819</v>
       </c>
-      <c r="D6" s="9" t="n">
+      <c r="D6" s="7" t="n">
         <v>109.9075824742194</v>
       </c>
-      <c r="E6" s="9" t="n">
+      <c r="E6" s="7" t="n">
         <v>124.4581193266816</v>
       </c>
-      <c r="F6" s="9" t="n">
+      <c r="F6" s="7" t="n">
         <v>154.1934203763022</v>
       </c>
-      <c r="G6" s="10" t="n">
+      <c r="G6" s="9" t="n">
         <v>0.59456</v>
       </c>
     </row>
@@ -2119,10 +2403,10 @@
           <t>Finishes 10% or more above spot</t>
         </is>
       </c>
-      <c r="B9" s="10" t="n">
+      <c r="B9" s="9" t="n">
         <v>0.23044</v>
       </c>
-      <c r="C9" s="10" t="n">
+      <c r="C9" s="9" t="n">
         <v>0.3878</v>
       </c>
     </row>
@@ -2132,10 +2416,10 @@
           <t>Finishes 10% or more below spot</t>
         </is>
       </c>
-      <c r="B10" s="10" t="n">
+      <c r="B10" s="9" t="n">
         <v>0.14414</v>
       </c>
-      <c r="C10" s="10" t="n">
+      <c r="C10" s="9" t="n">
         <v>0.21232</v>
       </c>
     </row>
@@ -2145,10 +2429,10 @@
           <t>Touches 10% above spot at any point</t>
         </is>
       </c>
-      <c r="B11" s="10" t="n">
+      <c r="B11" s="9" t="n">
         <v>0.36882</v>
       </c>
-      <c r="C11" s="10" t="n">
+      <c r="C11" s="9" t="n">
         <v>0.6306</v>
       </c>
     </row>
@@ -2158,10 +2442,10 @@
           <t>Touches 10% below spot at any point</t>
         </is>
       </c>
-      <c r="B12" s="10" t="n">
+      <c r="B12" s="9" t="n">
         <v>0.2549</v>
       </c>
-      <c r="C12" s="10" t="n">
+      <c r="C12" s="9" t="n">
         <v>0.446</v>
       </c>
     </row>
@@ -2183,7 +2467,7 @@
           <t>Simulated paths</t>
         </is>
       </c>
-      <c r="C15" s="28" t="n">
+      <c r="C15" s="22" t="n">
         <v>50000</v>
       </c>
     </row>
@@ -2193,7 +2477,7 @@
           <t>Annualised volatility (3-month anchor)</t>
         </is>
       </c>
-      <c r="C16" s="10" t="n">
+      <c r="C16" s="9" t="n">
         <v>0.4838094309558744</v>
       </c>
     </row>
@@ -2203,8 +2487,9 @@
           <t>Spot price (EGP)</t>
         </is>
       </c>
-      <c r="C17" s="9" t="n">
-        <v>105.2</v>
+      <c r="C17" s="8">
+        <f>Summary!C14</f>
+        <v/>
       </c>
     </row>
     <row r="18">
@@ -2213,7 +2498,7 @@
           <t>Anchor date</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C18" s="21" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
@@ -2260,7 +2545,7 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>EGP per share</t>
+          <t>EGP per share. Each cell is a complete re-run of the model, including the unit build, so these grids are engine outputs rather than formulas and do NOT redraw when a driver is changed.</t>
         </is>
       </c>
     </row>
@@ -2305,19 +2590,19 @@
           <t>13.1%</t>
         </is>
       </c>
-      <c r="B6" s="9" t="n">
+      <c r="B6" s="7" t="n">
         <v>71.48013737611937</v>
       </c>
-      <c r="C6" s="9" t="n">
+      <c r="C6" s="7" t="n">
         <v>75.158505958635</v>
       </c>
-      <c r="D6" s="9" t="n">
+      <c r="D6" s="7" t="n">
         <v>79.66249997898875</v>
       </c>
-      <c r="E6" s="9" t="n">
+      <c r="E6" s="7" t="n">
         <v>85.33897230281774</v>
       </c>
-      <c r="F6" s="9" t="n">
+      <c r="F6" s="7" t="n">
         <v>92.76070177891306</v>
       </c>
     </row>
@@ -2327,19 +2612,19 @@
           <t>14.1%</t>
         </is>
       </c>
-      <c r="B7" s="9" t="n">
+      <c r="B7" s="7" t="n">
         <v>64.51999723358476</v>
       </c>
-      <c r="C7" s="9" t="n">
+      <c r="C7" s="7" t="n">
         <v>67.23266415979741</v>
       </c>
-      <c r="D7" s="9" t="n">
+      <c r="D7" s="7" t="n">
         <v>70.47099233404454</v>
       </c>
-      <c r="E7" s="9" t="n">
+      <c r="E7" s="7" t="n">
         <v>74.42869060586594</v>
       </c>
-      <c r="F7" s="9" t="n">
+      <c r="F7" s="7" t="n">
         <v>79.40797299188714</v>
       </c>
     </row>
@@ -2349,19 +2634,19 @@
           <t>15.1%</t>
         </is>
       </c>
-      <c r="B8" s="9" t="n">
+      <c r="B8" s="7" t="n">
         <v>58.71390500851878</v>
       </c>
-      <c r="C8" s="9" t="n">
+      <c r="C8" s="7" t="n">
         <v>60.7356474116613</v>
       </c>
-      <c r="D8" s="9" t="n">
+      <c r="D8" s="7" t="n">
         <v>63.09639197519306</v>
       </c>
-      <c r="E8" s="9" t="n">
+      <c r="E8" s="7" t="n">
         <v>65.90739638220869</v>
       </c>
-      <c r="F8" s="9" t="n">
+      <c r="F8" s="7" t="n">
         <v>69.3345836803008</v>
       </c>
     </row>
@@ -2371,19 +2656,19 @@
           <t>16.1%</t>
         </is>
       </c>
-      <c r="B9" s="9" t="n">
+      <c r="B9" s="7" t="n">
         <v>53.79809034203993</v>
       </c>
-      <c r="C9" s="9" t="n">
+      <c r="C9" s="7" t="n">
         <v>55.314134925563</v>
       </c>
-      <c r="D9" s="9" t="n">
+      <c r="D9" s="7" t="n">
         <v>57.04924305755583</v>
       </c>
-      <c r="E9" s="9" t="n">
+      <c r="E9" s="7" t="n">
         <v>59.06822004769293</v>
       </c>
-      <c r="F9" s="9" t="n">
+      <c r="F9" s="7" t="n">
         <v>61.46422928886715</v>
       </c>
     </row>
@@ -2393,19 +2678,19 @@
           <t>17.1%</t>
         </is>
       </c>
-      <c r="B10" s="9" t="n">
+      <c r="B10" s="7" t="n">
         <v>49.58340787307901</v>
       </c>
-      <c r="C10" s="9" t="n">
+      <c r="C10" s="7" t="n">
         <v>50.72236517614795</v>
       </c>
-      <c r="D10" s="9" t="n">
+      <c r="D10" s="7" t="n">
         <v>52.00135637265844</v>
       </c>
-      <c r="E10" s="9" t="n">
+      <c r="E10" s="7" t="n">
         <v>53.45808918007977</v>
       </c>
-      <c r="F10" s="9" t="n">
+      <c r="F10" s="7" t="n">
         <v>55.14514468831749</v>
       </c>
     </row>
@@ -2450,19 +2735,19 @@
           <t>terminal 13.1%</t>
         </is>
       </c>
-      <c r="B14" s="9" t="n">
+      <c r="B14" s="7" t="n">
         <v>84.33728753089692</v>
       </c>
-      <c r="C14" s="9" t="n">
+      <c r="C14" s="7" t="n">
         <v>81.95820408756369</v>
       </c>
-      <c r="D14" s="9" t="n">
+      <c r="D14" s="7" t="n">
         <v>79.66249997898875</v>
       </c>
-      <c r="E14" s="9" t="n">
+      <c r="E14" s="7" t="n">
         <v>77.44651129819714</v>
       </c>
-      <c r="F14" s="9" t="n">
+      <c r="F14" s="7" t="n">
         <v>75.30676865150218</v>
       </c>
     </row>
@@ -2472,19 +2757,19 @@
           <t>terminal 14.1%</t>
         </is>
       </c>
-      <c r="B15" s="9" t="n">
+      <c r="B15" s="7" t="n">
         <v>74.62341007610547</v>
       </c>
-      <c r="C15" s="9" t="n">
+      <c r="C15" s="7" t="n">
         <v>72.51027129509237</v>
       </c>
-      <c r="D15" s="9" t="n">
+      <c r="D15" s="7" t="n">
         <v>70.47099233404454</v>
       </c>
-      <c r="E15" s="9" t="n">
+      <c r="E15" s="7" t="n">
         <v>68.50233381059978</v>
       </c>
-      <c r="F15" s="9" t="n">
+      <c r="F15" s="7" t="n">
         <v>66.60122807292484</v>
       </c>
     </row>
@@ -2494,19 +2779,19 @@
           <t>terminal 15.1%</t>
         </is>
       </c>
-      <c r="B16" s="9" t="n">
+      <c r="B16" s="7" t="n">
         <v>66.82989265057586</v>
       </c>
-      <c r="C16" s="9" t="n">
+      <c r="C16" s="7" t="n">
         <v>64.9300279088521</v>
       </c>
-      <c r="D16" s="9" t="n">
+      <c r="D16" s="7" t="n">
         <v>63.09639197519306</v>
       </c>
-      <c r="E16" s="9" t="n">
+      <c r="E16" s="7" t="n">
         <v>61.32608564835102</v>
       </c>
-      <c r="F16" s="9" t="n">
+      <c r="F16" s="7" t="n">
         <v>59.61636320712214</v>
       </c>
     </row>
@@ -2516,19 +2801,19 @@
           <t>terminal 16.1%</t>
         </is>
       </c>
-      <c r="B17" s="9" t="n">
+      <c r="B17" s="7" t="n">
         <v>60.43940513969982</v>
       </c>
-      <c r="C17" s="9" t="n">
+      <c r="C17" s="7" t="n">
         <v>58.71433541623137</v>
       </c>
-      <c r="D17" s="9" t="n">
+      <c r="D17" s="7" t="n">
         <v>57.04924305755583</v>
       </c>
-      <c r="E17" s="9" t="n">
+      <c r="E17" s="7" t="n">
         <v>55.44150743399135</v>
       </c>
-      <c r="F17" s="9" t="n">
+      <c r="F17" s="7" t="n">
         <v>53.88864645585161</v>
       </c>
     </row>
@@ -2538,19 +2823,19 @@
           <t>terminal 17.1%</t>
         </is>
       </c>
-      <c r="B18" s="9" t="n">
+      <c r="B18" s="7" t="n">
         <v>55.10506833536628</v>
       </c>
-      <c r="C18" s="9" t="n">
+      <c r="C18" s="7" t="n">
         <v>53.52583022982751</v>
       </c>
-      <c r="D18" s="9" t="n">
+      <c r="D18" s="7" t="n">
         <v>52.00135637265844</v>
       </c>
-      <c r="E18" s="9" t="n">
+      <c r="E18" s="7" t="n">
         <v>50.52925833918371</v>
       </c>
-      <c r="F18" s="9" t="n">
+      <c r="F18" s="7" t="n">
         <v>49.1072737958847</v>
       </c>
     </row>
@@ -2596,23 +2881,24 @@
           <t>Beta</t>
         </is>
       </c>
-      <c r="B22" s="9" t="n">
+      <c r="B22" s="7" t="n">
         <v>86.86398352810841</v>
       </c>
-      <c r="C22" s="9" t="n">
+      <c r="C22" s="7" t="n">
         <v>73.76938856958702</v>
       </c>
-      <c r="D22" s="9" t="n">
+      <c r="D22" s="7" t="n">
         <v>63.09639197519306</v>
       </c>
-      <c r="E22" s="9" t="n">
+      <c r="E22" s="7" t="n">
         <v>57.1692154119707</v>
       </c>
-      <c r="F22" s="9" t="n">
+      <c r="F22" s="7" t="n">
         <v>51.73397898456535</v>
       </c>
-      <c r="H22" s="9" t="n">
-        <v>35.13000454354306</v>
+      <c r="H22" s="10">
+        <f>MAX(B22:F22)-MIN(B22:F22)</f>
+        <v/>
       </c>
     </row>
     <row r="23">
@@ -2621,23 +2907,24 @@
           <t>Exchange-rate path multiplier</t>
         </is>
       </c>
-      <c r="B23" s="9" t="n">
+      <c r="B23" s="7" t="n">
         <v>71.93944315776433</v>
       </c>
-      <c r="C23" s="9" t="n">
+      <c r="C23" s="7" t="n">
         <v>63.09639197519306</v>
       </c>
-      <c r="D23" s="9" t="n">
+      <c r="D23" s="7" t="n">
         <v>45.41028961005051</v>
       </c>
-      <c r="E23" s="9" t="n">
+      <c r="E23" s="7" t="n">
         <v>23.30266165362228</v>
       </c>
-      <c r="F23" s="9" t="n">
+      <c r="F23" s="7" t="n">
         <v>1.195033697194072</v>
       </c>
-      <c r="H23" s="9" t="n">
-        <v>70.74440946057025</v>
+      <c r="H23" s="10">
+        <f>MAX(B23:F23)-MIN(B23:F23)</f>
+        <v/>
       </c>
     </row>
     <row r="24">
@@ -2646,23 +2933,24 @@
           <t>EBITDA margin shift</t>
         </is>
       </c>
-      <c r="B24" s="9" t="n">
+      <c r="B24" s="7" t="n">
         <v>42.21530497281732</v>
       </c>
-      <c r="C24" s="9" t="n">
+      <c r="C24" s="7" t="n">
         <v>52.6558484740052</v>
       </c>
-      <c r="D24" s="9" t="n">
+      <c r="D24" s="7" t="n">
         <v>63.09639197519306</v>
       </c>
-      <c r="E24" s="9" t="n">
+      <c r="E24" s="7" t="n">
         <v>73.53693547638095</v>
       </c>
-      <c r="F24" s="9" t="n">
+      <c r="F24" s="7" t="n">
         <v>83.97747897756886</v>
       </c>
-      <c r="H24" s="9" t="n">
-        <v>41.76217400475154</v>
+      <c r="H24" s="10">
+        <f>MAX(B24:F24)-MIN(B24:F24)</f>
+        <v/>
       </c>
     </row>
     <row r="25">
@@ -2671,23 +2959,24 @@
           <t>Working capital / revenue</t>
         </is>
       </c>
-      <c r="B25" s="9" t="n">
+      <c r="B25" s="7" t="n">
         <v>66.1820174425543</v>
       </c>
-      <c r="C25" s="9" t="n">
+      <c r="C25" s="7" t="n">
         <v>64.63920470887369</v>
       </c>
-      <c r="D25" s="9" t="n">
+      <c r="D25" s="7" t="n">
         <v>63.09639197519306</v>
       </c>
-      <c r="E25" s="9" t="n">
+      <c r="E25" s="7" t="n">
         <v>61.55357924151245</v>
       </c>
-      <c r="F25" s="9" t="n">
+      <c r="F25" s="7" t="n">
         <v>60.01076650783185</v>
       </c>
-      <c r="H25" s="9" t="n">
-        <v>6.171250934722451</v>
+      <c r="H25" s="10">
+        <f>MAX(B25:F25)-MIN(B25:F25)</f>
+        <v/>
       </c>
     </row>
     <row r="26">
@@ -2696,23 +2985,24 @@
           <t>Terminal return on invested capital</t>
         </is>
       </c>
-      <c r="B26" s="9" t="n">
+      <c r="B26" s="7" t="n">
         <v>55.97972245871841</v>
       </c>
-      <c r="C26" s="9" t="n">
+      <c r="C26" s="7" t="n">
         <v>59.77877118391308</v>
       </c>
-      <c r="D26" s="9" t="n">
+      <c r="D26" s="7" t="n">
         <v>63.09639197519306</v>
       </c>
-      <c r="E26" s="9" t="n">
+      <c r="E26" s="7" t="n">
         <v>65.62346153036643</v>
       </c>
-      <c r="F26" s="9" t="n">
+      <c r="F26" s="7" t="n">
         <v>67.37686863430243</v>
       </c>
-      <c r="H26" s="9" t="n">
-        <v>11.39714617558401</v>
+      <c r="H26" s="10">
+        <f>MAX(B26:F26)-MIN(B26:F26)</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -2758,7 +3048,7 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>The indicator set for a diversified industrial with a contracting arm</t>
+          <t>The indicator set for a diversified industrial with a contracting arm. Every ratio is a formula off the statements.</t>
         </is>
       </c>
     </row>
@@ -2815,29 +3105,37 @@
           <t>Earnings per share (EGP)</t>
         </is>
       </c>
-      <c r="B5" s="9" t="n">
-        <v>4.725245021170053</v>
-      </c>
-      <c r="C5" s="9" t="n">
-        <v>8.156567851227177</v>
-      </c>
-      <c r="D5" s="9" t="n">
-        <v>8.095188293136117</v>
-      </c>
-      <c r="E5" s="9" t="n">
-        <v>10.93196785447563</v>
-      </c>
-      <c r="F5" s="9" t="n">
-        <v>11.98414214931436</v>
-      </c>
-      <c r="G5" s="9" t="n">
-        <v>13.43471102138623</v>
-      </c>
-      <c r="H5" s="9" t="n">
-        <v>15.09321287040991</v>
-      </c>
-      <c r="I5" s="9" t="n">
-        <v>16.92085095645048</v>
+      <c r="B5" s="10">
+        <f>'Income Statement'!B18</f>
+        <v/>
+      </c>
+      <c r="C5" s="10">
+        <f>'Income Statement'!C18</f>
+        <v/>
+      </c>
+      <c r="D5" s="10">
+        <f>'Income Statement'!D18</f>
+        <v/>
+      </c>
+      <c r="E5" s="10">
+        <f>'Income Statement'!E18</f>
+        <v/>
+      </c>
+      <c r="F5" s="10">
+        <f>'Income Statement'!F18</f>
+        <v/>
+      </c>
+      <c r="G5" s="10">
+        <f>'Income Statement'!G18</f>
+        <v/>
+      </c>
+      <c r="H5" s="10">
+        <f>'Income Statement'!H18</f>
+        <v/>
+      </c>
+      <c r="I5" s="10">
+        <f>'Income Statement'!I18</f>
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -2846,29 +3144,37 @@
           <t>Book value per share (EGP)</t>
         </is>
       </c>
-      <c r="B6" s="9" t="n">
-        <v>16.68762574599776</v>
-      </c>
-      <c r="C6" s="9" t="n">
-        <v>25.82000711969241</v>
-      </c>
-      <c r="D6" s="9" t="n">
-        <v>32.91519541282852</v>
-      </c>
-      <c r="E6" s="9" t="n">
-        <v>41.11417130368525</v>
-      </c>
-      <c r="F6" s="9" t="n">
-        <v>50.10227791567102</v>
-      </c>
-      <c r="G6" s="9" t="n">
-        <v>60.17831118171069</v>
-      </c>
-      <c r="H6" s="9" t="n">
-        <v>71.49822083451812</v>
-      </c>
-      <c r="I6" s="9" t="n">
-        <v>84.18885905185599</v>
+      <c r="B6" s="10">
+        <f>'Balance Sheet'!B14/Assumptions!$C$6</f>
+        <v/>
+      </c>
+      <c r="C6" s="10">
+        <f>'Balance Sheet'!C14/Assumptions!$C$6</f>
+        <v/>
+      </c>
+      <c r="D6" s="10">
+        <f>'Balance Sheet'!D14/Assumptions!$C$6</f>
+        <v/>
+      </c>
+      <c r="E6" s="10">
+        <f>'Balance Sheet'!E14/Assumptions!$C$6</f>
+        <v/>
+      </c>
+      <c r="F6" s="10">
+        <f>'Balance Sheet'!F14/Assumptions!$C$6</f>
+        <v/>
+      </c>
+      <c r="G6" s="10">
+        <f>'Balance Sheet'!G14/Assumptions!$C$6</f>
+        <v/>
+      </c>
+      <c r="H6" s="10">
+        <f>'Balance Sheet'!H14/Assumptions!$C$6</f>
+        <v/>
+      </c>
+      <c r="I6" s="10">
+        <f>'Balance Sheet'!I14/Assumptions!$C$6</f>
+        <v/>
       </c>
     </row>
     <row r="7">
@@ -2877,35 +3183,40 @@
           <t>Free cash flow per share (EGP)</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="C7" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D7" s="9" t="inlineStr">
+      <c r="D7" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E7" s="9" t="n">
-        <v>0.6432043642020219</v>
-      </c>
-      <c r="F7" s="9" t="n">
-        <v>6.095352871262111</v>
-      </c>
-      <c r="G7" s="9" t="n">
-        <v>8.270684198796207</v>
-      </c>
-      <c r="H7" s="9" t="n">
-        <v>9.684915190940478</v>
-      </c>
-      <c r="I7" s="9" t="n">
-        <v>11.17195060308942</v>
+      <c r="E7" s="10">
+        <f>'Summary Financials'!E11/Assumptions!$C$6</f>
+        <v/>
+      </c>
+      <c r="F7" s="10">
+        <f>'Summary Financials'!F11/Assumptions!$C$6</f>
+        <v/>
+      </c>
+      <c r="G7" s="10">
+        <f>'Summary Financials'!G11/Assumptions!$C$6</f>
+        <v/>
+      </c>
+      <c r="H7" s="10">
+        <f>'Summary Financials'!H11/Assumptions!$C$6</f>
+        <v/>
+      </c>
+      <c r="I7" s="10">
+        <f>'Summary Financials'!I11/Assumptions!$C$6</f>
+        <v/>
       </c>
     </row>
     <row r="8">
@@ -2914,39 +3225,37 @@
           <t>Gross margin</t>
         </is>
       </c>
-      <c r="B8" s="10" t="n">
-        <v>0.191063972948927</v>
-      </c>
-      <c r="C8" s="10" t="n">
-        <v>0.1892325173785185</v>
-      </c>
-      <c r="D8" s="10" t="n">
-        <v>0.1448857672505506</v>
-      </c>
-      <c r="E8" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G8" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H8" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I8" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B8" s="11">
+        <f>'Income Statement'!B6/'Income Statement'!B5</f>
+        <v/>
+      </c>
+      <c r="C8" s="11">
+        <f>'Income Statement'!C6/'Income Statement'!C5</f>
+        <v/>
+      </c>
+      <c r="D8" s="11">
+        <f>'Income Statement'!D6/'Income Statement'!D5</f>
+        <v/>
+      </c>
+      <c r="E8" s="11">
+        <f>'Income Statement'!E6/'Income Statement'!E5</f>
+        <v/>
+      </c>
+      <c r="F8" s="11">
+        <f>'Income Statement'!F6/'Income Statement'!F5</f>
+        <v/>
+      </c>
+      <c r="G8" s="11">
+        <f>'Income Statement'!G6/'Income Statement'!G5</f>
+        <v/>
+      </c>
+      <c r="H8" s="11">
+        <f>'Income Statement'!H6/'Income Statement'!H5</f>
+        <v/>
+      </c>
+      <c r="I8" s="11">
+        <f>'Income Statement'!I6/'Income Statement'!I5</f>
+        <v/>
       </c>
     </row>
     <row r="9">
@@ -2955,29 +3264,37 @@
           <t>EBITDA margin</t>
         </is>
       </c>
-      <c r="B9" s="10" t="n">
-        <v>0.1316485988874155</v>
-      </c>
-      <c r="C9" s="10" t="n">
-        <v>0.1362244796790093</v>
-      </c>
-      <c r="D9" s="10" t="n">
-        <v>0.1089564020271673</v>
-      </c>
-      <c r="E9" s="10" t="n">
-        <v>0.112415700114078</v>
-      </c>
-      <c r="F9" s="10" t="n">
-        <v>0.1100083445187365</v>
-      </c>
-      <c r="G9" s="10" t="n">
-        <v>0.1106031122318905</v>
-      </c>
-      <c r="H9" s="10" t="n">
-        <v>0.1115640664608482</v>
-      </c>
-      <c r="I9" s="10" t="n">
-        <v>0.1125696702000991</v>
+      <c r="B9" s="11">
+        <f>'Income Statement'!B8</f>
+        <v/>
+      </c>
+      <c r="C9" s="11">
+        <f>'Income Statement'!C8</f>
+        <v/>
+      </c>
+      <c r="D9" s="11">
+        <f>'Income Statement'!D8</f>
+        <v/>
+      </c>
+      <c r="E9" s="11">
+        <f>'Income Statement'!E8</f>
+        <v/>
+      </c>
+      <c r="F9" s="11">
+        <f>'Income Statement'!F8</f>
+        <v/>
+      </c>
+      <c r="G9" s="11">
+        <f>'Income Statement'!G8</f>
+        <v/>
+      </c>
+      <c r="H9" s="11">
+        <f>'Income Statement'!H8</f>
+        <v/>
+      </c>
+      <c r="I9" s="11">
+        <f>'Income Statement'!I8</f>
+        <v/>
       </c>
     </row>
     <row r="10">
@@ -2986,29 +3303,37 @@
           <t>EBIT margin</t>
         </is>
       </c>
-      <c r="B10" s="10" t="n">
-        <v>0.1165618170372872</v>
-      </c>
-      <c r="C10" s="10" t="n">
-        <v>0.126482767182598</v>
-      </c>
-      <c r="D10" s="10" t="n">
-        <v>0.09845640202716727</v>
-      </c>
-      <c r="E10" s="10" t="n">
-        <v>0.101915700114078</v>
-      </c>
-      <c r="F10" s="10" t="n">
-        <v>0.09950834451873651</v>
-      </c>
-      <c r="G10" s="10" t="n">
-        <v>0.1001031122318905</v>
-      </c>
-      <c r="H10" s="10" t="n">
-        <v>0.1010640664608482</v>
-      </c>
-      <c r="I10" s="10" t="n">
-        <v>0.1020696702000991</v>
+      <c r="B10" s="11">
+        <f>'Income Statement'!B10/'Income Statement'!B5</f>
+        <v/>
+      </c>
+      <c r="C10" s="11">
+        <f>'Income Statement'!C10/'Income Statement'!C5</f>
+        <v/>
+      </c>
+      <c r="D10" s="11">
+        <f>'Income Statement'!D10/'Income Statement'!D5</f>
+        <v/>
+      </c>
+      <c r="E10" s="11">
+        <f>'Income Statement'!E10/'Income Statement'!E5</f>
+        <v/>
+      </c>
+      <c r="F10" s="11">
+        <f>'Income Statement'!F10/'Income Statement'!F5</f>
+        <v/>
+      </c>
+      <c r="G10" s="11">
+        <f>'Income Statement'!G10/'Income Statement'!G5</f>
+        <v/>
+      </c>
+      <c r="H10" s="11">
+        <f>'Income Statement'!H10/'Income Statement'!H5</f>
+        <v/>
+      </c>
+      <c r="I10" s="11">
+        <f>'Income Statement'!I10/'Income Statement'!I5</f>
+        <v/>
       </c>
     </row>
     <row r="11">
@@ -3017,29 +3342,37 @@
           <t>Net margin (attributable)</t>
         </is>
       </c>
-      <c r="B11" s="10" t="n">
-        <v>0.06646923308420868</v>
-      </c>
-      <c r="C11" s="10" t="n">
-        <v>0.07527056001807039</v>
-      </c>
-      <c r="D11" s="10" t="n">
-        <v>0.06166184544332127</v>
-      </c>
-      <c r="E11" s="10" t="n">
-        <v>0.06402004195016504</v>
-      </c>
-      <c r="F11" s="10" t="n">
-        <v>0.06280059549254072</v>
-      </c>
-      <c r="G11" s="10" t="n">
-        <v>0.06503249291721717</v>
-      </c>
-      <c r="H11" s="10" t="n">
-        <v>0.06770760604839697</v>
-      </c>
-      <c r="I11" s="10" t="n">
-        <v>0.07044794352284163</v>
+      <c r="B11" s="11">
+        <f>'Income Statement'!B17/'Income Statement'!B5</f>
+        <v/>
+      </c>
+      <c r="C11" s="11">
+        <f>'Income Statement'!C17/'Income Statement'!C5</f>
+        <v/>
+      </c>
+      <c r="D11" s="11">
+        <f>'Income Statement'!D17/'Income Statement'!D5</f>
+        <v/>
+      </c>
+      <c r="E11" s="11">
+        <f>'Income Statement'!E17/'Income Statement'!E5</f>
+        <v/>
+      </c>
+      <c r="F11" s="11">
+        <f>'Income Statement'!F17/'Income Statement'!F5</f>
+        <v/>
+      </c>
+      <c r="G11" s="11">
+        <f>'Income Statement'!G17/'Income Statement'!G5</f>
+        <v/>
+      </c>
+      <c r="H11" s="11">
+        <f>'Income Statement'!H17/'Income Statement'!H5</f>
+        <v/>
+      </c>
+      <c r="I11" s="11">
+        <f>'Income Statement'!I17/'Income Statement'!I5</f>
+        <v/>
       </c>
     </row>
     <row r="12">
@@ -3048,31 +3381,38 @@
           <t>Return on equity</t>
         </is>
       </c>
-      <c r="B12" s="10" t="inlineStr">
+      <c r="B12" s="11" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C12" s="10" t="n">
-        <v>0.3837695633158021</v>
-      </c>
-      <c r="D12" s="10" t="n">
-        <v>0.2756503065994848</v>
-      </c>
-      <c r="E12" s="10" t="n">
-        <v>0.2658929392916098</v>
-      </c>
-      <c r="F12" s="10" t="n">
-        <v>0.2391935586139479</v>
-      </c>
-      <c r="G12" s="10" t="n">
-        <v>0.2232483889556092</v>
-      </c>
-      <c r="H12" s="10" t="n">
-        <v>0.2110991391707913</v>
-      </c>
-      <c r="I12" s="10" t="n">
-        <v>0.2009868187669358</v>
+      <c r="C12" s="11">
+        <f>'Income Statement'!C17/(('Balance Sheet'!B14+'Balance Sheet'!C14)/2)</f>
+        <v/>
+      </c>
+      <c r="D12" s="11">
+        <f>'Income Statement'!D17/(('Balance Sheet'!C14+'Balance Sheet'!D14)/2)</f>
+        <v/>
+      </c>
+      <c r="E12" s="11">
+        <f>'Income Statement'!E17/(('Balance Sheet'!D14+'Balance Sheet'!E14)/2)</f>
+        <v/>
+      </c>
+      <c r="F12" s="11">
+        <f>'Income Statement'!F17/(('Balance Sheet'!E14+'Balance Sheet'!F14)/2)</f>
+        <v/>
+      </c>
+      <c r="G12" s="11">
+        <f>'Income Statement'!G17/(('Balance Sheet'!F14+'Balance Sheet'!G14)/2)</f>
+        <v/>
+      </c>
+      <c r="H12" s="11">
+        <f>'Income Statement'!H17/(('Balance Sheet'!G14+'Balance Sheet'!H14)/2)</f>
+        <v/>
+      </c>
+      <c r="I12" s="11">
+        <f>'Income Statement'!I17/(('Balance Sheet'!H14+'Balance Sheet'!I14)/2)</f>
+        <v/>
       </c>
     </row>
     <row r="13">
@@ -3081,29 +3421,40 @@
           <t>Return on invested capital</t>
         </is>
       </c>
-      <c r="B13" s="10" t="n">
-        <v>0.2229390349424942</v>
-      </c>
-      <c r="C13" s="10" t="n">
-        <v>0.2486105500867294</v>
-      </c>
-      <c r="D13" s="10" t="n">
-        <v>0.2093655734764178</v>
-      </c>
-      <c r="E13" s="10" t="n">
-        <v>0.2223088146361256</v>
-      </c>
-      <c r="F13" s="10" t="n">
-        <v>0.2130133498740734</v>
-      </c>
-      <c r="G13" s="10" t="n">
-        <v>0.2093157760005789</v>
-      </c>
-      <c r="H13" s="10" t="n">
-        <v>0.2078073525507945</v>
-      </c>
-      <c r="I13" s="10" t="n">
-        <v>0.2077054355161732</v>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E13" s="11">
+        <f>'Summary Financials'!E14</f>
+        <v/>
+      </c>
+      <c r="F13" s="11">
+        <f>'Summary Financials'!F14</f>
+        <v/>
+      </c>
+      <c r="G13" s="11">
+        <f>'Summary Financials'!G14</f>
+        <v/>
+      </c>
+      <c r="H13" s="11">
+        <f>'Summary Financials'!H14</f>
+        <v/>
+      </c>
+      <c r="I13" s="11">
+        <f>'Summary Financials'!I14</f>
+        <v/>
       </c>
     </row>
     <row r="14">
@@ -3112,29 +3463,37 @@
           <t>Net debt / EBITDA</t>
         </is>
       </c>
-      <c r="B14" s="33" t="n">
-        <v>0.7371063783060728</v>
-      </c>
-      <c r="C14" s="33" t="n">
-        <v>0.6337653789681534</v>
-      </c>
-      <c r="D14" s="33" t="n">
-        <v>0.6462328796032941</v>
-      </c>
-      <c r="E14" s="33" t="n">
-        <v>0.6657458870097267</v>
-      </c>
-      <c r="F14" s="33" t="n">
-        <v>0.53307780193362</v>
-      </c>
-      <c r="G14" s="33" t="n">
-        <v>0.3279986937477656</v>
-      </c>
-      <c r="H14" s="33" t="n">
-        <v>0.09633371227953212</v>
-      </c>
-      <c r="I14" s="33" t="n">
-        <v>-0.1559185836582377</v>
+      <c r="B14" s="34">
+        <f>'Balance Sheet'!B18</f>
+        <v/>
+      </c>
+      <c r="C14" s="34">
+        <f>'Balance Sheet'!C18</f>
+        <v/>
+      </c>
+      <c r="D14" s="34">
+        <f>'Balance Sheet'!D18</f>
+        <v/>
+      </c>
+      <c r="E14" s="34">
+        <f>'Balance Sheet'!E18</f>
+        <v/>
+      </c>
+      <c r="F14" s="34">
+        <f>'Balance Sheet'!F18</f>
+        <v/>
+      </c>
+      <c r="G14" s="34">
+        <f>'Balance Sheet'!G18</f>
+        <v/>
+      </c>
+      <c r="H14" s="34">
+        <f>'Balance Sheet'!H18</f>
+        <v/>
+      </c>
+      <c r="I14" s="34">
+        <f>'Balance Sheet'!I18</f>
+        <v/>
       </c>
     </row>
     <row r="15">
@@ -3143,41 +3502,38 @@
           <t>Interest cover (EBIT / net interest)</t>
         </is>
       </c>
-      <c r="B15" s="33" t="inlineStr">
+      <c r="B15" s="34" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C15" s="33" t="n">
-        <v>8.346617739090858</v>
-      </c>
-      <c r="D15" s="33" t="n">
-        <v>8.138550980392157</v>
-      </c>
-      <c r="E15" s="33" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F15" s="33" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G15" s="33" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H15" s="33" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I15" s="33" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C15" s="34">
+        <f>-'Income Statement'!C10/'Income Statement'!C11</f>
+        <v/>
+      </c>
+      <c r="D15" s="34">
+        <f>-'Income Statement'!D10/'Income Statement'!D11</f>
+        <v/>
+      </c>
+      <c r="E15" s="34">
+        <f>-'Income Statement'!E10/'Income Statement'!E11</f>
+        <v/>
+      </c>
+      <c r="F15" s="34">
+        <f>-'Income Statement'!F10/'Income Statement'!F11</f>
+        <v/>
+      </c>
+      <c r="G15" s="34">
+        <f>-'Income Statement'!G10/'Income Statement'!G11</f>
+        <v/>
+      </c>
+      <c r="H15" s="34">
+        <f>-'Income Statement'!H10/'Income Statement'!H11</f>
+        <v/>
+      </c>
+      <c r="I15" s="34">
+        <f>-'Income Statement'!I10/'Income Statement'!I11</f>
+        <v/>
       </c>
     </row>
     <row r="16">
@@ -3186,29 +3542,37 @@
           <t>Working capital / revenue</t>
         </is>
       </c>
-      <c r="B16" s="10" t="n">
-        <v>0.2408556097727652</v>
-      </c>
-      <c r="C16" s="10" t="n">
-        <v>0.2305995556547972</v>
-      </c>
-      <c r="D16" s="10" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="E16" s="10" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="F16" s="10" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="G16" s="10" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="H16" s="10" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="I16" s="10" t="n">
-        <v>0.23</v>
+      <c r="B16" s="11">
+        <f>'Balance Sheet'!B16/'Income Statement'!B5</f>
+        <v/>
+      </c>
+      <c r="C16" s="11">
+        <f>'Balance Sheet'!C16/'Income Statement'!C5</f>
+        <v/>
+      </c>
+      <c r="D16" s="11">
+        <f>'Balance Sheet'!D16/'Income Statement'!D5</f>
+        <v/>
+      </c>
+      <c r="E16" s="11">
+        <f>'Balance Sheet'!E16/'Income Statement'!E5</f>
+        <v/>
+      </c>
+      <c r="F16" s="11">
+        <f>'Balance Sheet'!F16/'Income Statement'!F5</f>
+        <v/>
+      </c>
+      <c r="G16" s="11">
+        <f>'Balance Sheet'!G16/'Income Statement'!G5</f>
+        <v/>
+      </c>
+      <c r="H16" s="11">
+        <f>'Balance Sheet'!H16/'Income Statement'!H5</f>
+        <v/>
+      </c>
+      <c r="I16" s="11">
+        <f>'Balance Sheet'!I16/'Income Statement'!I5</f>
+        <v/>
       </c>
     </row>
     <row r="17">
@@ -3217,31 +3581,38 @@
           <t>Capital expenditure / revenue</t>
         </is>
       </c>
-      <c r="B17" s="10" t="n">
-        <v>0.03173743742862362</v>
-      </c>
-      <c r="C17" s="10" t="n">
-        <v>0.03778615391379841</v>
-      </c>
-      <c r="D17" s="10" t="inlineStr">
+      <c r="B17" s="11">
+        <f>-'Cash Flow'!B11/'Income Statement'!B5</f>
+        <v/>
+      </c>
+      <c r="C17" s="11">
+        <f>-'Cash Flow'!C11/'Income Statement'!C5</f>
+        <v/>
+      </c>
+      <c r="D17" s="11" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E17" s="10" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="F17" s="10" t="n">
-        <v>0.029</v>
-      </c>
-      <c r="G17" s="10" t="n">
-        <v>0.028</v>
-      </c>
-      <c r="H17" s="10" t="n">
-        <v>0.026</v>
-      </c>
-      <c r="I17" s="10" t="n">
-        <v>0.024</v>
+      <c r="E17" s="11">
+        <f>-'Cash Flow'!D11/'Income Statement'!E5</f>
+        <v/>
+      </c>
+      <c r="F17" s="11">
+        <f>-'Cash Flow'!E11/'Income Statement'!F5</f>
+        <v/>
+      </c>
+      <c r="G17" s="11">
+        <f>-'Cash Flow'!F11/'Income Statement'!G5</f>
+        <v/>
+      </c>
+      <c r="H17" s="11">
+        <f>-'Cash Flow'!G11/'Income Statement'!H5</f>
+        <v/>
+      </c>
+      <c r="I17" s="11">
+        <f>-'Cash Flow'!H11/'Income Statement'!I5</f>
+        <v/>
       </c>
     </row>
     <row r="18">
@@ -3250,36 +3621,36 @@
           <t>Reinvestment rate</t>
         </is>
       </c>
-      <c r="B18" s="10" t="n">
+      <c r="B18" s="9" t="n">
         <v>0.2079305448304614</v>
       </c>
-      <c r="C18" s="10" t="n">
+      <c r="C18" s="9" t="n">
         <v>0.3172037113507076</v>
       </c>
-      <c r="D18" s="10" t="n">
+      <c r="D18" s="9" t="n">
         <v>0.2640762760437433</v>
       </c>
-      <c r="E18" s="10" t="inlineStr">
+      <c r="E18" s="11" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F18" s="10" t="inlineStr">
+      <c r="F18" s="11" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G18" s="10" t="inlineStr">
+      <c r="G18" s="11" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H18" s="10" t="inlineStr">
+      <c r="H18" s="11" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I18" s="10" t="inlineStr">
+      <c r="I18" s="11" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3291,36 +3662,36 @@
           <t>Implied growth (return on capital x reinvestment)</t>
         </is>
       </c>
-      <c r="B19" s="10" t="n">
+      <c r="B19" s="9" t="n">
         <v>0.04635583499957009</v>
       </c>
-      <c r="C19" s="10" t="n">
+      <c r="C19" s="9" t="n">
         <v>0.07886018916845154</v>
       </c>
-      <c r="D19" s="10" t="n">
+      <c r="D19" s="9" t="n">
         <v>0.05528848097541515</v>
       </c>
-      <c r="E19" s="10" t="inlineStr">
+      <c r="E19" s="11" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F19" s="10" t="inlineStr">
+      <c r="F19" s="11" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G19" s="10" t="inlineStr">
+      <c r="G19" s="11" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H19" s="10" t="inlineStr">
+      <c r="H19" s="11" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I19" s="10" t="inlineStr">
+      <c r="I19" s="11" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3407,12 +3778,12 @@
           <t>Saudi Arabia</t>
         </is>
       </c>
-      <c r="C5" s="36" t="inlineStr">
+      <c r="C5" s="40" t="inlineStr">
         <is>
           <t>nearest listed regional cable manufacturer</t>
         </is>
       </c>
-      <c r="D5" s="36" t="inlineStr">
+      <c r="D5" s="40" t="inlineStr">
         <is>
           <t>far smaller, no contracting arm, lighter balance sheet, pegged currency</t>
         </is>
@@ -3429,12 +3800,12 @@
           <t>Egypt</t>
         </is>
       </c>
-      <c r="C6" s="36" t="inlineStr">
+      <c r="C6" s="40" t="inlineStr">
         <is>
           <t>the only other listed Egyptian cable manufacturer</t>
         </is>
       </c>
-      <c r="D6" s="36" t="inlineStr">
+      <c r="D6" s="40" t="inlineStr">
         <is>
           <t>much smaller, domestic, heavily levered, currently loss-making</t>
         </is>
@@ -3451,12 +3822,12 @@
           <t>Europe</t>
         </is>
       </c>
-      <c r="C7" s="36" t="inlineStr">
+      <c r="C7" s="40" t="inlineStr">
         <is>
           <t>closest match on business model — cables plus projects</t>
         </is>
       </c>
-      <c r="D7" s="36" t="inlineStr">
+      <c r="D7" s="40" t="inlineStr">
         <is>
           <t>developed-market cost of capital; no convertibility risk</t>
         </is>
@@ -3473,12 +3844,12 @@
           <t>Gulf and North Africa</t>
         </is>
       </c>
-      <c r="C8" s="36" t="inlineStr">
+      <c r="C8" s="40" t="inlineStr">
         <is>
           <t>the right frame for the roughly 27% that is turnkey project work</t>
         </is>
       </c>
-      <c r="D8" s="36" t="inlineStr">
+      <c r="D8" s="40" t="inlineStr">
         <is>
           <t>project accounting and backlog quality are not comparable</t>
         </is>
@@ -3502,8 +3873,9 @@
           <t>Trailing enterprise value / EBITDA</t>
         </is>
       </c>
-      <c r="B11" s="33" t="n">
-        <v>8.000722677325394</v>
+      <c r="B11" s="32">
+        <f>'Relative &amp; Normalized'!C13</f>
+        <v/>
       </c>
     </row>
     <row r="12">
@@ -3512,8 +3884,9 @@
           <t>Trailing price / earnings</t>
         </is>
       </c>
-      <c r="B12" s="33" t="n">
-        <v>12.9953740655049</v>
+      <c r="B12" s="32">
+        <f>'Relative &amp; Normalized'!C14</f>
+        <v/>
       </c>
     </row>
     <row r="13">
@@ -3522,8 +3895,9 @@
           <t>Trailing price / book</t>
         </is>
       </c>
-      <c r="B13" s="33" t="n">
-        <v>3.196092220646482</v>
+      <c r="B13" s="32">
+        <f>'Relative &amp; Normalized'!C15</f>
+        <v/>
       </c>
     </row>
     <row r="14">
@@ -3532,8 +3906,9 @@
           <t>Justified enterprise value / EBITDA applied</t>
         </is>
       </c>
-      <c r="B14" s="33" t="n">
-        <v>6.5</v>
+      <c r="B14" s="32">
+        <f>'Relative &amp; Normalized'!C6</f>
+        <v/>
       </c>
     </row>
     <row r="15">
@@ -3542,8 +3917,9 @@
           <t>Justified price / earnings applied</t>
         </is>
       </c>
-      <c r="B15" s="33" t="n">
-        <v>9</v>
+      <c r="B15" s="32">
+        <f>'Relative &amp; Normalized'!C27</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -3635,20 +4011,21 @@
       <c r="B5" s="7" t="n">
         <v>35.37439268305282</v>
       </c>
-      <c r="C5" s="7" t="n">
-        <v>63.09639197519306</v>
+      <c r="C5" s="8">
+        <f>DCF!C31</f>
+        <v/>
       </c>
       <c r="D5" s="7" t="n">
         <v>110.3869768355961</v>
       </c>
-      <c r="E5" s="8" t="n">
+      <c r="E5" s="9" t="n">
         <v>0.45</v>
       </c>
-      <c r="F5" s="9">
+      <c r="F5" s="10">
         <f>C5*E5</f>
         <v/>
       </c>
-      <c r="G5" s="10">
+      <c r="G5" s="11">
         <f>C5/$C$14-1</f>
         <v/>
       </c>
@@ -3662,20 +4039,21 @@
       <c r="B6" s="7" t="n">
         <v>61.2294172643708</v>
       </c>
-      <c r="C6" s="7" t="n">
-        <v>73.38381725729656</v>
+      <c r="C6" s="8">
+        <f>'Relative &amp; Normalized'!C11</f>
+        <v/>
       </c>
       <c r="D6" s="7" t="n">
         <v>91.61541724668523</v>
       </c>
-      <c r="E6" s="8" t="n">
+      <c r="E6" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="F6" s="9">
+      <c r="F6" s="10">
         <f>C6*E6</f>
         <v/>
       </c>
-      <c r="G6" s="10">
+      <c r="G6" s="11">
         <f>C6/$C$14-1</f>
         <v/>
       </c>
@@ -3687,22 +4065,23 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>94.15599509791565</v>
-      </c>
-      <c r="C7" s="7" t="n">
-        <v>121.0577079830344</v>
+        <v>94.04297714970363</v>
+      </c>
+      <c r="C7" s="8">
+        <f>'Relative &amp; Normalized'!C28</f>
+        <v/>
       </c>
       <c r="D7" s="7" t="n">
-        <v>154.6848490894329</v>
-      </c>
-      <c r="E7" s="8" t="n">
+        <v>154.4991767459417</v>
+      </c>
+      <c r="E7" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="F7" s="9">
+      <c r="F7" s="10">
         <f>C7*E7</f>
         <v/>
       </c>
-      <c r="G7" s="10">
+      <c r="G7" s="11">
         <f>C7/$C$14-1</f>
         <v/>
       </c>
@@ -3716,48 +4095,49 @@
       <c r="B8" s="7" t="n">
         <v>33.76534925901321</v>
       </c>
-      <c r="C8" s="7" t="n">
-        <v>48.47019940598007</v>
+      <c r="C8" s="8">
+        <f>'Relative &amp; Normalized'!C36</f>
+        <v/>
       </c>
       <c r="D8" s="7" t="n">
         <v>53.71022096338332</v>
       </c>
-      <c r="E8" s="8" t="n">
+      <c r="E8" s="9" t="n">
         <v>0.15</v>
       </c>
-      <c r="F8" s="9">
+      <c r="F8" s="10">
         <f>C8*E8</f>
         <v/>
       </c>
-      <c r="G8" s="10">
+      <c r="G8" s="11">
         <f>C8/$C$14-1</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="11" t="inlineStr">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>Weighted central</t>
         </is>
       </c>
-      <c r="B9" s="12">
+      <c r="B9" s="13">
         <f>MIN(B5:B8)</f>
         <v/>
       </c>
-      <c r="C9" s="12">
+      <c r="C9" s="13">
         <f>SUM(F5:F8)</f>
         <v/>
       </c>
-      <c r="D9" s="12">
+      <c r="D9" s="13">
         <f>MAX(D5:D8)</f>
         <v/>
       </c>
-      <c r="E9" s="13">
+      <c r="E9" s="14">
         <f>SUM(E5:E8)</f>
         <v/>
       </c>
-      <c r="F9" s="14" t="n"/>
-      <c r="G9" s="13">
+      <c r="F9" s="15" t="n"/>
+      <c r="G9" s="14">
         <f>C9/$C$14-1</f>
         <v/>
       </c>
@@ -3765,14 +4145,14 @@
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Memo — currency-of-discounting alternative</t>
-        </is>
-      </c>
-      <c r="C11" s="7">
+          <t>Alternative reading — currency of discounting</t>
+        </is>
+      </c>
+      <c r="C11" s="8">
         <f>'Fundamental Valuation'!C18</f>
         <v/>
       </c>
-      <c r="G11" s="10">
+      <c r="G11" s="11">
         <f>C11/$C$14-1</f>
         <v/>
       </c>
@@ -3780,10 +4160,10 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Memo — terminal value share of DCF enterprise value</t>
-        </is>
-      </c>
-      <c r="C12" s="15">
+          <t>Terminal value share of DCF enterprise value</t>
+        </is>
+      </c>
+      <c r="C12" s="16">
         <f>DCF!C28</f>
         <v/>
       </c>
@@ -3791,32 +4171,32 @@
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>Memo — expert panel median</t>
-        </is>
-      </c>
-      <c r="C13" s="7">
+          <t>Expert panel median</t>
+        </is>
+      </c>
+      <c r="C13" s="8">
         <f>'Fundamental Valuation'!C26</f>
         <v/>
       </c>
-      <c r="G13" s="10">
+      <c r="G13" s="11">
         <f>C13/$C$14-1</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t>Market price (anchor)</t>
         </is>
       </c>
-      <c r="B14" s="14" t="n"/>
-      <c r="C14" s="16" t="n">
+      <c r="B14" s="15" t="n"/>
+      <c r="C14" s="17" t="n">
         <v>105.2</v>
       </c>
-      <c r="D14" s="14" t="n"/>
-      <c r="E14" s="14" t="n"/>
-      <c r="F14" s="14" t="n"/>
-      <c r="G14" s="14" t="n"/>
+      <c r="D14" s="15" t="n"/>
+      <c r="E14" s="15" t="n"/>
+      <c r="F14" s="15" t="n"/>
+      <c r="G14" s="15" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -3836,8 +4216,9 @@
           <t>Shares outstanding (mn)</t>
         </is>
       </c>
-      <c r="C17" s="17" t="n">
-        <v>2140.777876</v>
+      <c r="C17" s="18">
+        <f>Assumptions!$C$6</f>
+        <v/>
       </c>
     </row>
     <row r="18">
@@ -3857,8 +4238,9 @@
           <t>Net bank debt, FY2025 (EGP mn)</t>
         </is>
       </c>
-      <c r="C19" s="17" t="n">
-        <v>19789</v>
+      <c r="C19" s="18">
+        <f>'Balance Sheet'!D17</f>
+        <v/>
       </c>
     </row>
     <row r="20">
@@ -3867,8 +4249,9 @@
           <t>FY2025 revenue (EGP mn)</t>
         </is>
       </c>
-      <c r="C20" s="17" t="n">
-        <v>281049</v>
+      <c r="C20" s="18">
+        <f>'Income Statement'!D5</f>
+        <v/>
       </c>
     </row>
     <row r="21">
@@ -3877,8 +4260,9 @@
           <t>FY2025 EBITDA (EGP mn)</t>
         </is>
       </c>
-      <c r="C21" s="17" t="n">
-        <v>30622.08783333333</v>
+      <c r="C21" s="18">
+        <f>'Income Statement'!D7</f>
+        <v/>
       </c>
     </row>
     <row r="22">
@@ -3887,8 +4271,9 @@
           <t>FY2025 attributable profit (EGP mn)</t>
         </is>
       </c>
-      <c r="C22" s="17" t="n">
-        <v>17330</v>
+      <c r="C22" s="18">
+        <f>'Income Statement'!D17</f>
+        <v/>
       </c>
     </row>
     <row r="23">
@@ -3897,8 +4282,9 @@
           <t>Cost of capital — explicit window</t>
         </is>
       </c>
-      <c r="C23" s="8" t="n">
-        <v>0.2689791685924707</v>
+      <c r="C23" s="16">
+        <f>DCF!C46</f>
+        <v/>
       </c>
     </row>
     <row r="24">
@@ -3907,8 +4293,9 @@
           <t>Cost of capital — terminal</t>
         </is>
       </c>
-      <c r="C24" s="8" t="n">
-        <v>0.15141</v>
+      <c r="C24" s="16">
+        <f>DCF!C53</f>
+        <v/>
       </c>
     </row>
     <row r="25">
@@ -3917,8 +4304,9 @@
           <t>Terminal growth</t>
         </is>
       </c>
-      <c r="C25" s="8" t="n">
-        <v>0.05</v>
+      <c r="C25" s="16">
+        <f>DCF!C23</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -3983,7 +4371,7 @@
           <t>links to the DCF sheet</t>
         </is>
       </c>
-      <c r="C5" s="7">
+      <c r="C5" s="8">
         <f>DCF!C31</f>
         <v/>
       </c>
@@ -3999,7 +4387,7 @@
           <t>margin −1.5pp, weaker currency path, +2pp cost of capital, g 3%</t>
         </is>
       </c>
-      <c r="C6" s="9" t="n">
+      <c r="C6" s="7" t="n">
         <v>35.37439268305282</v>
       </c>
     </row>
@@ -4014,7 +4402,7 @@
           <t>margin +1.5pp, stronger currency path, −2pp cost of capital, g 6%</t>
         </is>
       </c>
-      <c r="C7" s="9" t="n">
+      <c r="C7" s="7" t="n">
         <v>110.3869768355961</v>
       </c>
     </row>
@@ -4029,7 +4417,7 @@
           <t>6.5x mid-cycle EV/EBITDA</t>
         </is>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="8">
         <f>'Relative &amp; Normalized'!C11</f>
         <v/>
       </c>
@@ -4045,8 +4433,8 @@
           <t>9.0x normalised earnings per share</t>
         </is>
       </c>
-      <c r="C9" s="7">
-        <f>'Relative &amp; Normalized'!C26</f>
+      <c r="C9" s="8">
+        <f>'Relative &amp; Normalized'!C28</f>
         <v/>
       </c>
     </row>
@@ -4061,18 +4449,18 @@
           <t>justified price-to-book on sustainable return on equity</t>
         </is>
       </c>
-      <c r="C10" s="7">
-        <f>'Relative &amp; Normalized'!C34</f>
+      <c r="C10" s="8">
+        <f>'Relative &amp; Normalized'!C36</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="A12" s="12" t="inlineStr">
         <is>
           <t>Weighted central</t>
         </is>
       </c>
-      <c r="B12" s="14" t="n"/>
+      <c r="B12" s="15" t="n"/>
       <c r="C12" s="19">
         <f>Summary!C9</f>
         <v/>
@@ -4091,7 +4479,7 @@
           <t>Share of forecast revenue earned in hard currency</t>
         </is>
       </c>
-      <c r="C15" s="8" t="n">
+      <c r="C15" s="9" t="n">
         <v>0.600860789848202</v>
       </c>
     </row>
@@ -4113,7 +4501,7 @@
           <t>Hard-currency cost of capital for the foreign leg</t>
         </is>
       </c>
-      <c r="C17" s="8" t="n">
+      <c r="C17" s="9" t="n">
         <v>0.10119375</v>
       </c>
     </row>
@@ -4123,7 +4511,7 @@
           <t>Fair value if the foreign leg is discounted at the hard-currency rate</t>
         </is>
       </c>
-      <c r="C18" s="22" t="n">
+      <c r="C18" s="7" t="n">
         <v>91.14622861923802</v>
       </c>
     </row>
@@ -4133,8 +4521,9 @@
           <t>Market price</t>
         </is>
       </c>
-      <c r="C19" s="22" t="n">
-        <v>105.2</v>
+      <c r="C19" s="8">
+        <f>Summary!C14</f>
+        <v/>
       </c>
     </row>
     <row r="21">
@@ -4182,13 +4571,13 @@
           <t>earnings power</t>
         </is>
       </c>
-      <c r="C23" s="9" t="n">
+      <c r="C23" s="7" t="n">
         <v>137.7034929664235</v>
       </c>
-      <c r="D23" s="9" t="n">
+      <c r="D23" s="7" t="n">
         <v>101.4657316594699</v>
       </c>
-      <c r="E23" s="9" t="n">
+      <c r="E23" s="7" t="n">
         <v>173.941254273377</v>
       </c>
     </row>
@@ -4203,13 +4592,13 @@
           <t>owner cash earnings</t>
         </is>
       </c>
-      <c r="C24" s="9" t="n">
+      <c r="C24" s="7" t="n">
         <v>66.19078084024615</v>
       </c>
-      <c r="D24" s="9" t="n">
+      <c r="D24" s="7" t="n">
         <v>40.8187533998155</v>
       </c>
-      <c r="E24" s="9" t="n">
+      <c r="E24" s="7" t="n">
         <v>72.60004748131544</v>
       </c>
     </row>
@@ -4224,29 +4613,29 @@
           <t>cash returns vs cost of capital</t>
         </is>
       </c>
-      <c r="C25" s="9" t="n">
+      <c r="C25" s="7" t="n">
         <v>60.72264310179215</v>
       </c>
-      <c r="D25" s="9" t="n">
+      <c r="D25" s="7" t="n">
         <v>49.99375810242254</v>
       </c>
-      <c r="E25" s="9" t="n">
+      <c r="E25" s="7" t="n">
         <v>91.14622861923802</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="11" t="inlineStr">
+      <c r="A26" s="12" t="inlineStr">
         <is>
           <t>Panel median</t>
         </is>
       </c>
-      <c r="B26" s="14" t="n"/>
-      <c r="C26" s="12">
+      <c r="B26" s="15" t="n"/>
+      <c r="C26" s="13">
         <f>MEDIAN(C23:C25)</f>
         <v/>
       </c>
-      <c r="D26" s="14" t="n"/>
-      <c r="E26" s="14" t="n"/>
+      <c r="D26" s="15" t="n"/>
+      <c r="E26" s="15" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4259,7 +4648,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H56"/>
+  <dimension ref="A1:H67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -4289,7 +4678,7 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>Blue cells are inputs. Change one and the model reprices.</t>
+          <t>Blue cells are inputs. Change one and the model reprices: everything downstream is a formula.</t>
         </is>
       </c>
     </row>
@@ -4326,18 +4715,18 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Anchors</t>
         </is>
       </c>
-      <c r="B4" s="14" t="n"/>
-      <c r="C4" s="14" t="n"/>
-      <c r="D4" s="14" t="n"/>
-      <c r="E4" s="14" t="n"/>
-      <c r="F4" s="14" t="n"/>
-      <c r="G4" s="14" t="n"/>
-      <c r="H4" s="14" t="n"/>
+      <c r="B4" s="15" t="n"/>
+      <c r="C4" s="15" t="n"/>
+      <c r="D4" s="15" t="n"/>
+      <c r="E4" s="15" t="n"/>
+      <c r="F4" s="15" t="n"/>
+      <c r="G4" s="15" t="n"/>
+      <c r="H4" s="15" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -4345,7 +4734,7 @@
           <t>Spot price (EGP)</t>
         </is>
       </c>
-      <c r="C5" s="22" t="n">
+      <c r="C5" s="7" t="n">
         <v>105.2</v>
       </c>
     </row>
@@ -4355,7 +4744,7 @@
           <t>Shares outstanding (mn)</t>
         </is>
       </c>
-      <c r="C6" s="17" t="n">
+      <c r="C6" s="22" t="n">
         <v>2140.777876</v>
       </c>
     </row>
@@ -4365,7 +4754,7 @@
           <t>Effective tax rate</t>
         </is>
       </c>
-      <c r="C7" s="8" t="n">
+      <c r="C7" s="9" t="n">
         <v>0.25</v>
       </c>
     </row>
@@ -4375,7 +4764,7 @@
           <t>Statutory corporate tax rate</t>
         </is>
       </c>
-      <c r="C8" s="8" t="n">
+      <c r="C8" s="9" t="n">
         <v>0.225</v>
       </c>
     </row>
@@ -4390,18 +4779,18 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="inlineStr">
+      <c r="A11" s="12" t="inlineStr">
         <is>
           <t>Revenue drivers — the unit build</t>
         </is>
       </c>
-      <c r="B11" s="14" t="n"/>
-      <c r="C11" s="14" t="n"/>
-      <c r="D11" s="14" t="n"/>
-      <c r="E11" s="14" t="n"/>
-      <c r="F11" s="14" t="n"/>
-      <c r="G11" s="14" t="n"/>
-      <c r="H11" s="14" t="n"/>
+      <c r="B11" s="15" t="n"/>
+      <c r="C11" s="15" t="n"/>
+      <c r="D11" s="15" t="n"/>
+      <c r="E11" s="15" t="n"/>
+      <c r="F11" s="15" t="n"/>
+      <c r="G11" s="15" t="n"/>
+      <c r="H11" s="15" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -4409,19 +4798,19 @@
           <t>Copper (USD/tonne)</t>
         </is>
       </c>
-      <c r="B12" s="17" t="n">
+      <c r="B12" s="22" t="n">
         <v>13400</v>
       </c>
-      <c r="C12" s="17" t="n">
+      <c r="C12" s="22" t="n">
         <v>14000</v>
       </c>
-      <c r="D12" s="17" t="n">
+      <c r="D12" s="22" t="n">
         <v>14000</v>
       </c>
-      <c r="E12" s="17" t="n">
+      <c r="E12" s="22" t="n">
         <v>14000</v>
       </c>
-      <c r="F12" s="17" t="n">
+      <c r="F12" s="22" t="n">
         <v>14000</v>
       </c>
     </row>
@@ -4453,19 +4842,19 @@
           <t>Cable volume growth</t>
         </is>
       </c>
-      <c r="B14" s="8" t="n">
+      <c r="B14" s="9" t="n">
         <v>0.06</v>
       </c>
-      <c r="C14" s="8" t="n">
+      <c r="C14" s="9" t="n">
         <v>0.05</v>
       </c>
-      <c r="D14" s="8" t="n">
+      <c r="D14" s="9" t="n">
         <v>0.04</v>
       </c>
-      <c r="E14" s="8" t="n">
+      <c r="E14" s="9" t="n">
         <v>0.04</v>
       </c>
-      <c r="F14" s="8" t="n">
+      <c r="F14" s="9" t="n">
         <v>0.04</v>
       </c>
     </row>
@@ -4497,19 +4886,19 @@
           <t>Raw-material volume growth</t>
         </is>
       </c>
-      <c r="B16" s="8" t="n">
+      <c r="B16" s="9" t="n">
         <v>0.04</v>
       </c>
-      <c r="C16" s="8" t="n">
+      <c r="C16" s="9" t="n">
         <v>0.04</v>
       </c>
-      <c r="D16" s="8" t="n">
+      <c r="D16" s="9" t="n">
         <v>0.03</v>
       </c>
-      <c r="E16" s="8" t="n">
+      <c r="E16" s="9" t="n">
         <v>0.03</v>
       </c>
-      <c r="F16" s="8" t="n">
+      <c r="F16" s="9" t="n">
         <v>0.03</v>
       </c>
     </row>
@@ -4519,19 +4908,19 @@
           <t>Transformer MVA growth</t>
         </is>
       </c>
-      <c r="B17" s="8" t="n">
+      <c r="B17" s="9" t="n">
         <v>0.08</v>
       </c>
-      <c r="C17" s="8" t="n">
+      <c r="C17" s="9" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="D17" s="8" t="n">
+      <c r="D17" s="9" t="n">
         <v>0.06</v>
       </c>
-      <c r="E17" s="8" t="n">
+      <c r="E17" s="9" t="n">
         <v>0.05</v>
       </c>
-      <c r="F17" s="8" t="n">
+      <c r="F17" s="9" t="n">
         <v>0.05</v>
       </c>
     </row>
@@ -4541,19 +4930,19 @@
           <t>Meter unit growth</t>
         </is>
       </c>
-      <c r="B18" s="8" t="n">
+      <c r="B18" s="9" t="n">
         <v>0.06</v>
       </c>
-      <c r="C18" s="8" t="n">
+      <c r="C18" s="9" t="n">
         <v>0.05</v>
       </c>
-      <c r="D18" s="8" t="n">
+      <c r="D18" s="9" t="n">
         <v>0.05</v>
       </c>
-      <c r="E18" s="8" t="n">
+      <c r="E18" s="9" t="n">
         <v>0.04</v>
       </c>
-      <c r="F18" s="8" t="n">
+      <c r="F18" s="9" t="n">
         <v>0.04</v>
       </c>
     </row>
@@ -4563,19 +4952,19 @@
           <t>Order-book conversion rate</t>
         </is>
       </c>
-      <c r="B19" s="8" t="n">
+      <c r="B19" s="9" t="n">
         <v>0.27</v>
       </c>
-      <c r="C19" s="8" t="n">
+      <c r="C19" s="9" t="n">
         <v>0.265</v>
       </c>
-      <c r="D19" s="8" t="n">
+      <c r="D19" s="9" t="n">
         <v>0.26</v>
       </c>
-      <c r="E19" s="8" t="n">
+      <c r="E19" s="9" t="n">
         <v>0.255</v>
       </c>
-      <c r="F19" s="8" t="n">
+      <c r="F19" s="9" t="n">
         <v>0.25</v>
       </c>
     </row>
@@ -4607,19 +4996,19 @@
           <t>Other-lines revenue growth</t>
         </is>
       </c>
-      <c r="B21" s="8" t="n">
+      <c r="B21" s="9" t="n">
         <v>0.12</v>
       </c>
-      <c r="C21" s="8" t="n">
+      <c r="C21" s="9" t="n">
         <v>0.11</v>
       </c>
-      <c r="D21" s="8" t="n">
+      <c r="D21" s="9" t="n">
         <v>0.1</v>
       </c>
-      <c r="E21" s="8" t="n">
+      <c r="E21" s="9" t="n">
         <v>0.09</v>
       </c>
-      <c r="F21" s="8" t="n">
+      <c r="F21" s="9" t="n">
         <v>0.08</v>
       </c>
     </row>
@@ -4629,35 +5018,35 @@
           <t>Meter price inflation</t>
         </is>
       </c>
-      <c r="B22" s="8" t="n">
+      <c r="B22" s="9" t="n">
         <v>0.08</v>
       </c>
-      <c r="C22" s="8" t="n">
+      <c r="C22" s="9" t="n">
         <v>0.075</v>
       </c>
-      <c r="D22" s="8" t="n">
+      <c r="D22" s="9" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="E22" s="8" t="n">
+      <c r="E22" s="9" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="F22" s="8" t="n">
+      <c r="F22" s="9" t="n">
         <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="11" t="inlineStr">
+      <c r="A24" s="12" t="inlineStr">
         <is>
           <t>Unit gross profit and cost load</t>
         </is>
       </c>
-      <c r="B24" s="14" t="n"/>
-      <c r="C24" s="14" t="n"/>
-      <c r="D24" s="14" t="n"/>
-      <c r="E24" s="14" t="n"/>
-      <c r="F24" s="14" t="n"/>
-      <c r="G24" s="14" t="n"/>
-      <c r="H24" s="14" t="n"/>
+      <c r="B24" s="15" t="n"/>
+      <c r="C24" s="15" t="n"/>
+      <c r="D24" s="15" t="n"/>
+      <c r="E24" s="15" t="n"/>
+      <c r="F24" s="15" t="n"/>
+      <c r="G24" s="15" t="n"/>
+      <c r="H24" s="15" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
@@ -4665,19 +5054,19 @@
           <t>Gross profit per unit — growth</t>
         </is>
       </c>
-      <c r="B25" s="8" t="n">
+      <c r="B25" s="9" t="n">
         <v>0.08500000000000001</v>
       </c>
-      <c r="C25" s="8" t="n">
+      <c r="C25" s="9" t="n">
         <v>0.08</v>
       </c>
-      <c r="D25" s="8" t="n">
+      <c r="D25" s="9" t="n">
         <v>0.075</v>
       </c>
-      <c r="E25" s="8" t="n">
+      <c r="E25" s="9" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="F25" s="8" t="n">
+      <c r="F25" s="9" t="n">
         <v>0.07000000000000001</v>
       </c>
     </row>
@@ -4709,19 +5098,19 @@
           <t>Operating load (% of revenue)</t>
         </is>
       </c>
-      <c r="B27" s="8" t="n">
+      <c r="B27" s="9" t="n">
         <v>0.04</v>
       </c>
-      <c r="C27" s="8" t="n">
+      <c r="C27" s="9" t="n">
         <v>0.043</v>
       </c>
-      <c r="D27" s="8" t="n">
+      <c r="D27" s="9" t="n">
         <v>0.046</v>
       </c>
-      <c r="E27" s="8" t="n">
+      <c r="E27" s="9" t="n">
         <v>0.048</v>
       </c>
-      <c r="F27" s="8" t="n">
+      <c r="F27" s="9" t="n">
         <v>0.05</v>
       </c>
     </row>
@@ -4731,7 +5120,7 @@
           <t>Cable gross profit per tonne, FY2025 (EGP)</t>
         </is>
       </c>
-      <c r="C28" s="17" t="n">
+      <c r="C28" s="22" t="n">
         <v>88173</v>
       </c>
     </row>
@@ -4741,23 +5130,23 @@
           <t>Order book at FY2025 (EGP mn)</t>
         </is>
       </c>
-      <c r="C29" s="17" t="n">
+      <c r="C29" s="22" t="n">
         <v>323700</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="11" t="inlineStr">
+      <c r="A31" s="12" t="inlineStr">
         <is>
           <t>Capital intensity</t>
         </is>
       </c>
-      <c r="B31" s="14" t="n"/>
-      <c r="C31" s="14" t="n"/>
-      <c r="D31" s="14" t="n"/>
-      <c r="E31" s="14" t="n"/>
-      <c r="F31" s="14" t="n"/>
-      <c r="G31" s="14" t="n"/>
-      <c r="H31" s="14" t="n"/>
+      <c r="B31" s="15" t="n"/>
+      <c r="C31" s="15" t="n"/>
+      <c r="D31" s="15" t="n"/>
+      <c r="E31" s="15" t="n"/>
+      <c r="F31" s="15" t="n"/>
+      <c r="G31" s="15" t="n"/>
+      <c r="H31" s="15" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
@@ -4765,7 +5154,7 @@
           <t>Working capital / revenue</t>
         </is>
       </c>
-      <c r="C32" s="8" t="n">
+      <c r="C32" s="9" t="n">
         <v>0.23</v>
       </c>
     </row>
@@ -4775,19 +5164,19 @@
           <t>Capital expenditure / revenue</t>
         </is>
       </c>
-      <c r="B33" s="8" t="n">
+      <c r="B33" s="9" t="n">
         <v>0.03</v>
       </c>
-      <c r="C33" s="8" t="n">
+      <c r="C33" s="9" t="n">
         <v>0.029</v>
       </c>
-      <c r="D33" s="8" t="n">
+      <c r="D33" s="9" t="n">
         <v>0.028</v>
       </c>
-      <c r="E33" s="8" t="n">
+      <c r="E33" s="9" t="n">
         <v>0.026</v>
       </c>
-      <c r="F33" s="8" t="n">
+      <c r="F33" s="9" t="n">
         <v>0.024</v>
       </c>
     </row>
@@ -4797,23 +5186,23 @@
           <t>Depreciation and amortisation / revenue</t>
         </is>
       </c>
-      <c r="C34" s="8" t="n">
+      <c r="C34" s="9" t="n">
         <v>0.0105</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="11" t="inlineStr">
+      <c r="A36" s="12" t="inlineStr">
         <is>
           <t>Cost of capital</t>
         </is>
       </c>
-      <c r="B36" s="14" t="n"/>
-      <c r="C36" s="14" t="n"/>
-      <c r="D36" s="14" t="n"/>
-      <c r="E36" s="14" t="n"/>
-      <c r="F36" s="14" t="n"/>
-      <c r="G36" s="14" t="n"/>
-      <c r="H36" s="14" t="n"/>
+      <c r="B36" s="15" t="n"/>
+      <c r="C36" s="15" t="n"/>
+      <c r="D36" s="15" t="n"/>
+      <c r="E36" s="15" t="n"/>
+      <c r="F36" s="15" t="n"/>
+      <c r="G36" s="15" t="n"/>
+      <c r="H36" s="15" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
@@ -4821,7 +5210,7 @@
           <t>Risk-free rate (10-year local currency)</t>
         </is>
       </c>
-      <c r="C37" s="8" t="n">
+      <c r="C37" s="9" t="n">
         <v>0.2231</v>
       </c>
     </row>
@@ -4831,7 +5220,7 @@
           <t>Sovereign default spread (netted out)</t>
         </is>
       </c>
-      <c r="C38" s="8" t="n">
+      <c r="C38" s="9" t="n">
         <v>0.034</v>
       </c>
     </row>
@@ -4841,7 +5230,7 @@
           <t>Equity risk premium</t>
         </is>
       </c>
-      <c r="C39" s="8" t="n">
+      <c r="C39" s="9" t="n">
         <v>0.0941</v>
       </c>
     </row>
@@ -4861,7 +5250,7 @@
           <t>Cost of debt, blended</t>
         </is>
       </c>
-      <c r="C41" s="8" t="n">
+      <c r="C41" s="9" t="n">
         <v>0.13</v>
       </c>
     </row>
@@ -4871,19 +5260,19 @@
           <t>Cost of debt path</t>
         </is>
       </c>
-      <c r="B42" s="8" t="n">
+      <c r="B42" s="9" t="n">
         <v>0.13</v>
       </c>
-      <c r="C42" s="8" t="n">
+      <c r="C42" s="9" t="n">
         <v>0.122</v>
       </c>
-      <c r="D42" s="8" t="n">
+      <c r="D42" s="9" t="n">
         <v>0.115</v>
       </c>
-      <c r="E42" s="8" t="n">
+      <c r="E42" s="9" t="n">
         <v>0.11</v>
       </c>
-      <c r="F42" s="8" t="n">
+      <c r="F42" s="9" t="n">
         <v>0.106</v>
       </c>
     </row>
@@ -4893,7 +5282,7 @@
           <t>Terminal risk-free rate</t>
         </is>
       </c>
-      <c r="C43" s="8" t="n">
+      <c r="C43" s="9" t="n">
         <v>0.105</v>
       </c>
     </row>
@@ -4903,7 +5292,7 @@
           <t>Terminal equity risk premium</t>
         </is>
       </c>
-      <c r="C44" s="8" t="n">
+      <c r="C44" s="9" t="n">
         <v>0.07000000000000001</v>
       </c>
     </row>
@@ -4913,7 +5302,7 @@
           <t>Terminal cost of debt</t>
         </is>
       </c>
-      <c r="C45" s="8" t="n">
+      <c r="C45" s="9" t="n">
         <v>0.105</v>
       </c>
     </row>
@@ -4923,7 +5312,7 @@
           <t>Terminal debt weight</t>
         </is>
       </c>
-      <c r="C46" s="8" t="n">
+      <c r="C46" s="9" t="n">
         <v>0.25</v>
       </c>
     </row>
@@ -4933,91 +5322,195 @@
           <t>Terminal growth</t>
         </is>
       </c>
-      <c r="C47" s="8" t="n">
+      <c r="C47" s="9" t="n">
         <v>0.05</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="11" t="inlineStr">
-        <is>
-          <t>Lens inputs</t>
-        </is>
-      </c>
-      <c r="B49" s="14" t="n"/>
-      <c r="C49" s="14" t="n"/>
-      <c r="D49" s="14" t="n"/>
-      <c r="E49" s="14" t="n"/>
-      <c r="F49" s="14" t="n"/>
-      <c r="G49" s="14" t="n"/>
-      <c r="H49" s="14" t="n"/>
+      <c r="A49" s="12" t="inlineStr">
+        <is>
+          <t>Balance-sheet and bridge anchors</t>
+        </is>
+      </c>
+      <c r="B49" s="15" t="n"/>
+      <c r="C49" s="15" t="n"/>
+      <c r="D49" s="15" t="n"/>
+      <c r="E49" s="15" t="n"/>
+      <c r="F49" s="15" t="n"/>
+      <c r="G49" s="15" t="n"/>
+      <c r="H49" s="15" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>Justified EV/EBITDA</t>
-        </is>
-      </c>
-      <c r="C50" s="24" t="n">
-        <v>6.5</v>
+          <t>Net bank debt at FY2025 (EGP mn, disclosed)</t>
+        </is>
+      </c>
+      <c r="C50" s="22" t="n">
+        <v>19789</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>Justified price/earnings</t>
-        </is>
-      </c>
-      <c r="C51" s="24" t="n">
-        <v>9</v>
+          <t>Equity-accounted investees at carrying value (EGP mn)</t>
+        </is>
+      </c>
+      <c r="C51" s="22" t="n">
+        <v>6474</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>Sustainable return on equity</t>
-        </is>
-      </c>
-      <c r="C52" s="8" t="n">
-        <v>0.235</v>
+          <t>Intangible assets and goodwill (EGP mn)</t>
+        </is>
+      </c>
+      <c r="C52" s="22" t="n">
+        <v>1459.2</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
         <is>
-          <t>Weight — discounted cash flow</t>
-        </is>
-      </c>
-      <c r="C53" s="8" t="n">
-        <v>0.45</v>
+          <t>FY2025 profit after tax (EGP mn, disclosed)</t>
+        </is>
+      </c>
+      <c r="C53" s="22" t="n">
+        <v>19180</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
         <is>
-          <t>Weight — relative</t>
-        </is>
-      </c>
-      <c r="C54" s="8" t="n">
-        <v>0.2</v>
+          <t>FY2025 profit after minority interests (EGP mn, disclosed)</t>
+        </is>
+      </c>
+      <c r="C54" s="22" t="n">
+        <v>17330</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="6" t="inlineStr">
         <is>
-          <t>Weight — normalised</t>
-        </is>
-      </c>
-      <c r="C55" s="8" t="n">
-        <v>0.2</v>
+          <t>FY2024 dividend per share (EGP)</t>
+        </is>
+      </c>
+      <c r="C55" s="7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
         <is>
+          <t>Forecast dividend payout ratio</t>
+        </is>
+      </c>
+      <c r="C56" s="9" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t>Growth in the share of equity-accounted investees</t>
+        </is>
+      </c>
+      <c r="C57" s="9" t="n">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>Yield assumed on surplus cash</t>
+        </is>
+      </c>
+      <c r="C58" s="9" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="12" t="inlineStr">
+        <is>
+          <t>Lens inputs</t>
+        </is>
+      </c>
+      <c r="B60" s="15" t="n"/>
+      <c r="C60" s="15" t="n"/>
+      <c r="D60" s="15" t="n"/>
+      <c r="E60" s="15" t="n"/>
+      <c r="F60" s="15" t="n"/>
+      <c r="G60" s="15" t="n"/>
+      <c r="H60" s="15" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>Justified EV/EBITDA</t>
+        </is>
+      </c>
+      <c r="C61" s="24" t="n">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t>Justified price/earnings</t>
+        </is>
+      </c>
+      <c r="C62" s="24" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>Sustainable return on equity</t>
+        </is>
+      </c>
+      <c r="C63" s="9" t="n">
+        <v>0.235</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t>Weight — discounted cash flow</t>
+        </is>
+      </c>
+      <c r="C64" s="9" t="n">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="6" t="inlineStr">
+        <is>
+          <t>Weight — relative</t>
+        </is>
+      </c>
+      <c r="C65" s="9" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t>Weight — normalised</t>
+        </is>
+      </c>
+      <c r="C66" s="9" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="6" t="inlineStr">
+        <is>
           <t>Weight — book</t>
         </is>
       </c>
-      <c r="C56" s="8" t="n">
+      <c r="C67" s="9" t="n">
         <v>0.15</v>
       </c>
     </row>
@@ -5080,8 +5573,8 @@
         <f>DCF!C26</f>
         <v/>
       </c>
-      <c r="D5" s="9">
-        <f>C5/2140.777876</f>
+      <c r="D5" s="10">
+        <f>C5/Assumptions!$C$6</f>
         <v/>
       </c>
     </row>
@@ -5095,8 +5588,8 @@
         <f>DCF!C27</f>
         <v/>
       </c>
-      <c r="D6" s="9">
-        <f>C6/2140.777876</f>
+      <c r="D6" s="10">
+        <f>C6/Assumptions!$C$6</f>
         <v/>
       </c>
     </row>
@@ -5111,7 +5604,7 @@
         <v/>
       </c>
       <c r="D7" s="27">
-        <f>C7/2140.777876</f>
+        <f>C7/Assumptions!$C$6</f>
         <v/>
       </c>
     </row>
@@ -5121,12 +5614,12 @@
           <t>Less net bank debt</t>
         </is>
       </c>
-      <c r="C8" s="28">
-        <f>-19789.0</f>
-        <v/>
-      </c>
-      <c r="D8" s="9">
-        <f>C8/2140.777876</f>
+      <c r="C8" s="18">
+        <f>-Assumptions!$C$50</f>
+        <v/>
+      </c>
+      <c r="D8" s="10">
+        <f>C8/Assumptions!$C$6</f>
         <v/>
       </c>
     </row>
@@ -5136,11 +5629,12 @@
           <t>Plus equity-accounted investees at carrying value</t>
         </is>
       </c>
-      <c r="C9" s="28" t="n">
-        <v>6474</v>
-      </c>
-      <c r="D9" s="9">
-        <f>C9/2140.777876</f>
+      <c r="C9" s="18">
+        <f>Assumptions!$C$51</f>
+        <v/>
+      </c>
+      <c r="D9" s="10">
+        <f>C9/Assumptions!$C$6</f>
         <v/>
       </c>
     </row>
@@ -5154,8 +5648,8 @@
         <f>C7+C8+C9</f>
         <v/>
       </c>
-      <c r="D10" s="9">
-        <f>C10/2140.777876</f>
+      <c r="D10" s="10">
+        <f>C10/Assumptions!$C$6</f>
         <v/>
       </c>
     </row>
@@ -5166,37 +5660,37 @@
         </is>
       </c>
       <c r="C11" s="28">
-        <f>-C10*0.09645464025026068</f>
-        <v/>
-      </c>
-      <c r="D11" s="9">
-        <f>C11/2140.777876</f>
+        <f>-C10*$C$15</f>
+        <v/>
+      </c>
+      <c r="D11" s="10">
+        <f>C11/Assumptions!$C$6</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="14" t="inlineStr">
+      <c r="A12" s="15" t="inlineStr">
         <is>
           <t>Equity attributable to shareholders</t>
         </is>
       </c>
-      <c r="B12" s="14" t="n"/>
+      <c r="B12" s="15" t="n"/>
       <c r="C12" s="29">
         <f>C10+C11</f>
         <v/>
       </c>
       <c r="D12" s="30">
-        <f>C12/2140.777876</f>
+        <f>C12/Assumptions!$C$6</f>
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Memo — terminal value as a share of enterprise value</t>
-        </is>
-      </c>
-      <c r="C14" s="15">
+          <t>Terminal value as a share of enterprise value</t>
+        </is>
+      </c>
+      <c r="C14" s="16">
         <f>DCF!C28</f>
         <v/>
       </c>
@@ -5204,11 +5698,12 @@
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>Memo — minority share of group profit</t>
-        </is>
-      </c>
-      <c r="C15" s="8" t="n">
-        <v>0.09645464025026068</v>
+          <t>Minority share of group profit</t>
+        </is>
+      </c>
+      <c r="C15" s="11">
+        <f>(Assumptions!$C$53-Assumptions!$C$54)/Assumptions!$C$53</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -5222,7 +5717,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5233,6 +5728,7 @@
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5248,11 +5744,12 @@
       <c r="F1" s="2" t="n"/>
       <c r="G1" s="2" t="n"/>
       <c r="H1" s="2" t="n"/>
+      <c r="I1" s="2" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>FY2025 disclosed shares and gross margins; forecast revenue and EBITDA by segment</t>
+          <t>FY2025 disclosed shares and gross margins; forecast revenue and gross profit come from the unit build, and EBITDA is computed from them</t>
         </is>
       </c>
     </row>
@@ -5309,28 +5806,29 @@
           <t>Cables</t>
         </is>
       </c>
-      <c r="B5" s="28" t="n">
+      <c r="B5" s="22" t="n">
         <v>92138.29685490194</v>
       </c>
-      <c r="C5" s="10" t="n">
-        <v>0.3278371275290143</v>
-      </c>
-      <c r="D5" s="8" t="n">
+      <c r="C5" s="11">
+        <f>B5/$B$12</f>
+        <v/>
+      </c>
+      <c r="D5" s="9" t="n">
         <v>0.1479665487953016</v>
       </c>
-      <c r="E5" s="28" t="n">
+      <c r="E5" s="22" t="n">
         <v>145610.3678770696</v>
       </c>
-      <c r="F5" s="28" t="n">
+      <c r="F5" s="22" t="n">
         <v>169133.0260767016</v>
       </c>
-      <c r="G5" s="28" t="n">
+      <c r="G5" s="22" t="n">
         <v>187299.1659145696</v>
       </c>
-      <c r="H5" s="28" t="n">
+      <c r="H5" s="22" t="n">
         <v>206647.9840977443</v>
       </c>
-      <c r="I5" s="28" t="n">
+      <c r="I5" s="22" t="n">
         <v>227245.0290701096</v>
       </c>
     </row>
@@ -5340,28 +5838,29 @@
           <t>Raw material (copper rod)</t>
         </is>
       </c>
-      <c r="B6" s="28" t="n">
+      <c r="B6" s="22" t="n">
         <v>60448.00314509805</v>
       </c>
-      <c r="C6" s="10" t="n">
-        <v>0.2150799438713465</v>
-      </c>
-      <c r="D6" s="8" t="n">
+      <c r="C6" s="11">
+        <f>B6/$B$12</f>
+        <v/>
+      </c>
+      <c r="D6" s="9" t="n">
         <v>0.1239697053155375</v>
       </c>
-      <c r="E6" s="28" t="n">
+      <c r="E6" s="22" t="n">
         <v>86793.07467340285</v>
       </c>
-      <c r="F6" s="28" t="n">
+      <c r="F6" s="22" t="n">
         <v>99853.94648992721</v>
       </c>
-      <c r="G6" s="28" t="n">
+      <c r="G6" s="22" t="n">
         <v>109515.7403864063</v>
       </c>
-      <c r="H6" s="28" t="n">
+      <c r="H6" s="22" t="n">
         <v>119667.3733648332</v>
       </c>
-      <c r="I6" s="28" t="n">
+      <c r="I6" s="22" t="n">
         <v>130329.5401556179</v>
       </c>
     </row>
@@ -5371,28 +5870,29 @@
           <t>Engineering &amp; construction</t>
         </is>
       </c>
-      <c r="B7" s="28" t="n">
+      <c r="B7" s="22" t="n">
         <v>87100.7</v>
       </c>
-      <c r="C7" s="10" t="n">
-        <v>0.3099128621699419</v>
-      </c>
-      <c r="D7" s="8" t="n">
+      <c r="C7" s="11">
+        <f>B7/$B$12</f>
+        <v/>
+      </c>
+      <c r="D7" s="9" t="n">
         <v>0.08991421158660849</v>
       </c>
-      <c r="E7" s="28" t="n">
+      <c r="E7" s="22" t="n">
         <v>87399</v>
       </c>
-      <c r="F7" s="28" t="n">
+      <c r="F7" s="22" t="n">
         <v>86938.53675000001</v>
       </c>
-      <c r="G7" s="28" t="n">
+      <c r="G7" s="22" t="n">
         <v>86428.38797775001</v>
       </c>
-      <c r="H7" s="28" t="n">
+      <c r="H7" s="22" t="n">
         <v>85427.48076159229</v>
       </c>
-      <c r="I7" s="28" t="n">
+      <c r="I7" s="22" t="n">
         <v>84179.56952301609</v>
       </c>
     </row>
@@ -5402,28 +5902,29 @@
           <t>Transformers</t>
         </is>
       </c>
-      <c r="B8" s="28" t="n">
+      <c r="B8" s="22" t="n">
         <v>17703.5</v>
       </c>
-      <c r="C8" s="10" t="n">
-        <v>0.06299079519941363</v>
-      </c>
-      <c r="D8" s="8" t="n">
+      <c r="C8" s="11">
+        <f>B8/$B$12</f>
+        <v/>
+      </c>
+      <c r="D8" s="9" t="n">
         <v>0.2769882639821222</v>
       </c>
-      <c r="E8" s="28" t="n">
+      <c r="E8" s="22" t="n">
         <v>20025.95817760357</v>
       </c>
-      <c r="F8" s="28" t="n">
+      <c r="F8" s="22" t="n">
         <v>23704.12363041715</v>
       </c>
-      <c r="G8" s="28" t="n">
+      <c r="G8" s="22" t="n">
         <v>26754.93213470232</v>
       </c>
-      <c r="H8" s="28" t="n">
+      <c r="H8" s="22" t="n">
         <v>29802.66788222058</v>
       </c>
-      <c r="I8" s="28" t="n">
+      <c r="I8" s="22" t="n">
         <v>33088.28987415392</v>
       </c>
     </row>
@@ -5433,28 +5934,29 @@
           <t>Meters &amp; digital</t>
         </is>
       </c>
-      <c r="B9" s="28" t="n">
+      <c r="B9" s="22" t="n">
         <v>16594.1</v>
       </c>
-      <c r="C9" s="10" t="n">
-        <v>0.05904344082348629</v>
-      </c>
-      <c r="D9" s="8" t="n">
+      <c r="C9" s="11">
+        <f>B9/$B$12</f>
+        <v/>
+      </c>
+      <c r="D9" s="9" t="n">
         <v>0.2190169964043364</v>
       </c>
-      <c r="E9" s="28" t="n">
+      <c r="E9" s="22" t="n">
         <v>17815.54107615941</v>
       </c>
-      <c r="F9" s="28" t="n">
+      <c r="F9" s="22" t="n">
         <v>20109.29198971493</v>
       </c>
-      <c r="G9" s="28" t="n">
+      <c r="G9" s="22" t="n">
         <v>22592.78955044473</v>
       </c>
-      <c r="H9" s="28" t="n">
+      <c r="H9" s="22" t="n">
         <v>25141.25621173489</v>
       </c>
-      <c r="I9" s="28" t="n">
+      <c r="I9" s="22" t="n">
         <v>27977.18991241859</v>
       </c>
     </row>
@@ -5464,28 +5966,29 @@
           <t>Other electrical products</t>
         </is>
       </c>
-      <c r="B10" s="28" t="n">
+      <c r="B10" s="22" t="n">
         <v>3206.5</v>
       </c>
-      <c r="C10" s="10" t="n">
-        <v>0.01140904255129888</v>
-      </c>
-      <c r="D10" s="8" t="n">
+      <c r="C10" s="11">
+        <f>B10/$B$12</f>
+        <v/>
+      </c>
+      <c r="D10" s="9" t="n">
         <v>0.4076827342682428</v>
       </c>
-      <c r="E10" s="28" t="n">
+      <c r="E10" s="22" t="n">
         <v>3591.28</v>
       </c>
-      <c r="F10" s="28" t="n">
+      <c r="F10" s="22" t="n">
         <v>3986.3208</v>
       </c>
-      <c r="G10" s="28" t="n">
+      <c r="G10" s="22" t="n">
         <v>4384.952880000001</v>
       </c>
-      <c r="H10" s="28" t="n">
+      <c r="H10" s="22" t="n">
         <v>4779.598639200001</v>
       </c>
-      <c r="I10" s="28" t="n">
+      <c r="I10" s="22" t="n">
         <v>5161.966530336002</v>
       </c>
     </row>
@@ -5495,33 +5998,34 @@
           <t>Infrastructure investment</t>
         </is>
       </c>
-      <c r="B11" s="28" t="n">
+      <c r="B11" s="22" t="n">
         <v>3857.9</v>
       </c>
-      <c r="C11" s="10" t="n">
-        <v>0.01372678785549851</v>
-      </c>
-      <c r="D11" s="8" t="n">
+      <c r="C11" s="11">
+        <f>B11/$B$12</f>
+        <v/>
+      </c>
+      <c r="D11" s="9" t="n">
         <v>0.4966473826898447</v>
       </c>
-      <c r="E11" s="28" t="n">
+      <c r="E11" s="22" t="n">
         <v>4320.848000000001</v>
       </c>
-      <c r="F11" s="28" t="n">
+      <c r="F11" s="22" t="n">
         <v>4796.141280000002</v>
       </c>
-      <c r="G11" s="28" t="n">
+      <c r="G11" s="22" t="n">
         <v>5275.755408000002</v>
       </c>
-      <c r="H11" s="28" t="n">
+      <c r="H11" s="22" t="n">
         <v>5750.573394720002</v>
       </c>
-      <c r="I11" s="28" t="n">
+      <c r="I11" s="22" t="n">
         <v>6210.619266297603</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="A12" s="12" t="inlineStr">
         <is>
           <t>Total revenue</t>
         </is>
@@ -5530,11 +6034,11 @@
         <f>SUM(B5:B11)</f>
         <v/>
       </c>
-      <c r="C12" s="13">
+      <c r="C12" s="14">
         <f>SUM(C5:C11)</f>
         <v/>
       </c>
-      <c r="D12" s="14" t="n"/>
+      <c r="D12" s="15" t="n"/>
       <c r="E12" s="31">
         <f>SUM(E5:E11)</f>
         <v/>
@@ -5559,7 +6063,7 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>Segment EBITDA</t>
+          <t>Gross profit by segment</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
@@ -5594,20 +6098,20 @@
           <t>Cables</t>
         </is>
       </c>
-      <c r="B15" s="28" t="n">
-        <v>20041.67909882659</v>
-      </c>
-      <c r="C15" s="28" t="n">
-        <v>22059.43026367506</v>
-      </c>
-      <c r="D15" s="28" t="n">
-        <v>24177.58249832987</v>
-      </c>
-      <c r="E15" s="28" t="n">
-        <v>26573.33011161748</v>
-      </c>
-      <c r="F15" s="28" t="n">
-        <v>29246.528376493</v>
+      <c r="B15" s="22" t="n">
+        <v>25866.09381390937</v>
+      </c>
+      <c r="C15" s="22" t="n">
+        <v>29332.15038497323</v>
+      </c>
+      <c r="D15" s="22" t="n">
+        <v>32793.34413040007</v>
+      </c>
+      <c r="E15" s="22" t="n">
+        <v>36492.43334830921</v>
+      </c>
+      <c r="F15" s="22" t="n">
+        <v>40608.77982999848</v>
       </c>
     </row>
     <row r="16">
@@ -5616,20 +6120,20 @@
           <t>Raw material (copper rod)</t>
         </is>
       </c>
-      <c r="B16" s="28" t="n">
-        <v>4984.191943840839</v>
-      </c>
-      <c r="C16" s="28" t="n">
-        <v>5203.963951181807</v>
-      </c>
-      <c r="D16" s="28" t="n">
-        <v>5478.586163963156</v>
-      </c>
-      <c r="E16" s="28" t="n">
-        <v>5845.99157386529</v>
-      </c>
-      <c r="F16" s="28" t="n">
-        <v>6256.890090674406</v>
+      <c r="B16" s="22" t="n">
+        <v>8455.914930776953</v>
+      </c>
+      <c r="C16" s="22" t="n">
+        <v>9497.683650248677</v>
+      </c>
+      <c r="D16" s="22" t="n">
+        <v>10516.31022173785</v>
+      </c>
+      <c r="E16" s="22" t="n">
+        <v>11590.02549537728</v>
+      </c>
+      <c r="F16" s="22" t="n">
+        <v>12773.3670984553</v>
       </c>
     </row>
     <row r="17">
@@ -5638,20 +6142,20 @@
           <t>Engineering &amp; construction</t>
         </is>
       </c>
-      <c r="B17" s="28" t="n">
-        <v>4362.452178457996</v>
-      </c>
-      <c r="C17" s="28" t="n">
-        <v>4391.333307654424</v>
-      </c>
-      <c r="D17" s="28" t="n">
-        <v>4339.414342204866</v>
-      </c>
-      <c r="E17" s="28" t="n">
-        <v>4271.928516198092</v>
-      </c>
-      <c r="F17" s="28" t="n">
-        <v>4116.855111747494</v>
+      <c r="B17" s="22" t="n">
+        <v>7858.412178457996</v>
+      </c>
+      <c r="C17" s="22" t="n">
+        <v>8129.690387904425</v>
+      </c>
+      <c r="D17" s="22" t="n">
+        <v>8315.120189181367</v>
+      </c>
+      <c r="E17" s="22" t="n">
+        <v>8372.447592754523</v>
+      </c>
+      <c r="F17" s="22" t="n">
+        <v>8325.833587898298</v>
       </c>
     </row>
     <row r="18">
@@ -5660,20 +6164,20 @@
           <t>Transformers</t>
         </is>
       </c>
-      <c r="B18" s="28" t="n">
-        <v>4945.072489759165</v>
-      </c>
-      <c r="C18" s="28" t="n">
-        <v>5620.928343859304</v>
-      </c>
-      <c r="D18" s="28" t="n">
-        <v>6335.787471336365</v>
-      </c>
-      <c r="E18" s="28" t="n">
-        <v>7070.450813353369</v>
-      </c>
-      <c r="F18" s="28" t="n">
-        <v>7896.435268647207</v>
+      <c r="B18" s="22" t="n">
+        <v>5746.110816863308</v>
+      </c>
+      <c r="C18" s="22" t="n">
+        <v>6640.205659967241</v>
+      </c>
+      <c r="D18" s="22" t="n">
+        <v>7566.514349532672</v>
+      </c>
+      <c r="E18" s="22" t="n">
+        <v>8500.978871699957</v>
+      </c>
+      <c r="F18" s="22" t="n">
+        <v>9550.849762354903</v>
       </c>
     </row>
     <row r="19">
@@ -5682,20 +6186,20 @@
           <t>Meters &amp; digital</t>
         </is>
       </c>
-      <c r="B19" s="28" t="n">
-        <v>3467.290226985804</v>
-      </c>
-      <c r="C19" s="28" t="n">
-        <v>3875.320505058752</v>
-      </c>
-      <c r="D19" s="28" t="n">
-        <v>4311.02932410041</v>
-      </c>
-      <c r="E19" s="28" t="n">
-        <v>4747.030919435468</v>
-      </c>
-      <c r="F19" s="28" t="n">
-        <v>5226.541627322952</v>
+      <c r="B19" s="22" t="n">
+        <v>4179.911870032181</v>
+      </c>
+      <c r="C19" s="22" t="n">
+        <v>4740.020060616494</v>
+      </c>
+      <c r="D19" s="22" t="n">
+        <v>5350.297643420868</v>
+      </c>
+      <c r="E19" s="22" t="n">
+        <v>5953.811217598743</v>
+      </c>
+      <c r="F19" s="22" t="n">
+        <v>6625.401122943882</v>
       </c>
     </row>
     <row r="20">
@@ -5704,20 +6208,20 @@
           <t>Other electrical products</t>
         </is>
       </c>
-      <c r="B20" s="28" t="n">
-        <v>1320.451649922855</v>
-      </c>
-      <c r="C20" s="28" t="n">
-        <v>1518.748535550944</v>
-      </c>
-      <c r="D20" s="28" t="n">
-        <v>1711.098617858713</v>
-      </c>
-      <c r="E20" s="28" t="n">
-        <v>1894.509493026274</v>
-      </c>
-      <c r="F20" s="28" t="n">
-        <v>2056.790765700589</v>
+      <c r="B20" s="22" t="n">
+        <v>1464.102849922855</v>
+      </c>
+      <c r="C20" s="22" t="n">
+        <v>1690.160329950944</v>
+      </c>
+      <c r="D20" s="22" t="n">
+        <v>1912.806450338713</v>
+      </c>
+      <c r="E20" s="22" t="n">
+        <v>2123.930227707874</v>
+      </c>
+      <c r="F20" s="22" t="n">
+        <v>2314.889092217389</v>
       </c>
     </row>
     <row r="21">
@@ -5726,26 +6230,26 @@
           <t>Infrastructure investment</t>
         </is>
       </c>
-      <c r="B21" s="28" t="n">
-        <v>1973.103930200651</v>
-      </c>
-      <c r="C21" s="28" t="n">
-        <v>2271.036579231632</v>
-      </c>
-      <c r="D21" s="28" t="n">
-        <v>2560.918674383644</v>
-      </c>
-      <c r="E21" s="28" t="n">
-        <v>2837.020352797803</v>
-      </c>
-      <c r="F21" s="28" t="n">
-        <v>3082.405620523931</v>
+      <c r="B21" s="22" t="n">
+        <v>2145.937850200651</v>
+      </c>
+      <c r="C21" s="22" t="n">
+        <v>2477.270654271631</v>
+      </c>
+      <c r="D21" s="22" t="n">
+        <v>2803.603423151645</v>
+      </c>
+      <c r="E21" s="22" t="n">
+        <v>3113.047875744363</v>
+      </c>
+      <c r="F21" s="22" t="n">
+        <v>3392.936583838811</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="11" t="inlineStr">
-        <is>
-          <t>Group EBITDA</t>
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>Group gross profit</t>
         </is>
       </c>
       <c r="B22" s="31">
@@ -5772,23 +6276,303 @@
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
+          <t>Group gross margin</t>
+        </is>
+      </c>
+      <c r="B23" s="11">
+        <f>B22/E$12</f>
+        <v/>
+      </c>
+      <c r="C23" s="11">
+        <f>C22/F$12</f>
+        <v/>
+      </c>
+      <c r="D23" s="11">
+        <f>D22/G$12</f>
+        <v/>
+      </c>
+      <c r="E23" s="11">
+        <f>E22/H$12</f>
+        <v/>
+      </c>
+      <c r="F23" s="11">
+        <f>F22/I$12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Segment EBITDA — gross profit less the operating load</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>FY26E</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>FY27E</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>FY28E</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>FY29E</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>FY30E</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>Cables</t>
+        </is>
+      </c>
+      <c r="B26" s="28">
+        <f>B15-Assumptions!$B$27*E5</f>
+        <v/>
+      </c>
+      <c r="C26" s="28">
+        <f>C15-Assumptions!$C$27*F5</f>
+        <v/>
+      </c>
+      <c r="D26" s="28">
+        <f>D15-Assumptions!$D$27*G5</f>
+        <v/>
+      </c>
+      <c r="E26" s="28">
+        <f>E15-Assumptions!$E$27*H5</f>
+        <v/>
+      </c>
+      <c r="F26" s="28">
+        <f>F15-Assumptions!$F$27*I5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>Raw material (copper rod)</t>
+        </is>
+      </c>
+      <c r="B27" s="28">
+        <f>B16-Assumptions!$B$27*E6</f>
+        <v/>
+      </c>
+      <c r="C27" s="28">
+        <f>C16-Assumptions!$C$27*F6</f>
+        <v/>
+      </c>
+      <c r="D27" s="28">
+        <f>D16-Assumptions!$D$27*G6</f>
+        <v/>
+      </c>
+      <c r="E27" s="28">
+        <f>E16-Assumptions!$E$27*H6</f>
+        <v/>
+      </c>
+      <c r="F27" s="28">
+        <f>F16-Assumptions!$F$27*I6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>Engineering &amp; construction</t>
+        </is>
+      </c>
+      <c r="B28" s="28">
+        <f>B17-Assumptions!$B$27*E7</f>
+        <v/>
+      </c>
+      <c r="C28" s="28">
+        <f>C17-Assumptions!$C$27*F7</f>
+        <v/>
+      </c>
+      <c r="D28" s="28">
+        <f>D17-Assumptions!$D$27*G7</f>
+        <v/>
+      </c>
+      <c r="E28" s="28">
+        <f>E17-Assumptions!$E$27*H7</f>
+        <v/>
+      </c>
+      <c r="F28" s="28">
+        <f>F17-Assumptions!$F$27*I7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>Transformers</t>
+        </is>
+      </c>
+      <c r="B29" s="28">
+        <f>B18-Assumptions!$B$27*E8</f>
+        <v/>
+      </c>
+      <c r="C29" s="28">
+        <f>C18-Assumptions!$C$27*F8</f>
+        <v/>
+      </c>
+      <c r="D29" s="28">
+        <f>D18-Assumptions!$D$27*G8</f>
+        <v/>
+      </c>
+      <c r="E29" s="28">
+        <f>E18-Assumptions!$E$27*H8</f>
+        <v/>
+      </c>
+      <c r="F29" s="28">
+        <f>F18-Assumptions!$F$27*I8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>Meters &amp; digital</t>
+        </is>
+      </c>
+      <c r="B30" s="28">
+        <f>B19-Assumptions!$B$27*E9</f>
+        <v/>
+      </c>
+      <c r="C30" s="28">
+        <f>C19-Assumptions!$C$27*F9</f>
+        <v/>
+      </c>
+      <c r="D30" s="28">
+        <f>D19-Assumptions!$D$27*G9</f>
+        <v/>
+      </c>
+      <c r="E30" s="28">
+        <f>E19-Assumptions!$E$27*H9</f>
+        <v/>
+      </c>
+      <c r="F30" s="28">
+        <f>F19-Assumptions!$F$27*I9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>Other electrical products</t>
+        </is>
+      </c>
+      <c r="B31" s="28">
+        <f>B20-Assumptions!$B$27*E10</f>
+        <v/>
+      </c>
+      <c r="C31" s="28">
+        <f>C20-Assumptions!$C$27*F10</f>
+        <v/>
+      </c>
+      <c r="D31" s="28">
+        <f>D20-Assumptions!$D$27*G10</f>
+        <v/>
+      </c>
+      <c r="E31" s="28">
+        <f>E20-Assumptions!$E$27*H10</f>
+        <v/>
+      </c>
+      <c r="F31" s="28">
+        <f>F20-Assumptions!$F$27*I10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>Infrastructure investment</t>
+        </is>
+      </c>
+      <c r="B32" s="28">
+        <f>B21-Assumptions!$B$27*E11</f>
+        <v/>
+      </c>
+      <c r="C32" s="28">
+        <f>C21-Assumptions!$C$27*F11</f>
+        <v/>
+      </c>
+      <c r="D32" s="28">
+        <f>D21-Assumptions!$D$27*G11</f>
+        <v/>
+      </c>
+      <c r="E32" s="28">
+        <f>E21-Assumptions!$E$27*H11</f>
+        <v/>
+      </c>
+      <c r="F32" s="28">
+        <f>F21-Assumptions!$F$27*I11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>Group EBITDA</t>
+        </is>
+      </c>
+      <c r="B33" s="31">
+        <f>SUM(B26:B32)</f>
+        <v/>
+      </c>
+      <c r="C33" s="31">
+        <f>SUM(C26:C32)</f>
+        <v/>
+      </c>
+      <c r="D33" s="31">
+        <f>SUM(D26:D32)</f>
+        <v/>
+      </c>
+      <c r="E33" s="31">
+        <f>SUM(E26:E32)</f>
+        <v/>
+      </c>
+      <c r="F33" s="31">
+        <f>SUM(F26:F32)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
           <t>Group EBITDA margin</t>
         </is>
       </c>
-      <c r="B23" s="10" t="n">
-        <v>0.112415700114078</v>
-      </c>
-      <c r="C23" s="10" t="n">
-        <v>0.1100083445187365</v>
-      </c>
-      <c r="D23" s="10" t="n">
-        <v>0.1106031122318905</v>
-      </c>
-      <c r="E23" s="10" t="n">
-        <v>0.1115640664608482</v>
-      </c>
-      <c r="F23" s="10" t="n">
-        <v>0.1125696702000991</v>
+      <c r="B34" s="11">
+        <f>B33/E$12</f>
+        <v/>
+      </c>
+      <c r="C34" s="11">
+        <f>C33/F$12</f>
+        <v/>
+      </c>
+      <c r="D34" s="11">
+        <f>D33/G$12</f>
+        <v/>
+      </c>
+      <c r="E34" s="11">
+        <f>E33/H$12</f>
+        <v/>
+      </c>
+      <c r="F34" s="11">
+        <f>F33/I$12</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -5802,7 +6586,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:E36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -5852,8 +6636,9 @@
           <t>Justified enterprise value / EBITDA</t>
         </is>
       </c>
-      <c r="C6" s="24" t="n">
-        <v>6.5</v>
+      <c r="C6" s="32">
+        <f>Assumptions!$C$61</f>
+        <v/>
       </c>
     </row>
     <row r="7">
@@ -5873,8 +6658,9 @@
           <t>Discount factor back to today (year-2)</t>
         </is>
       </c>
-      <c r="C8" s="32" t="n">
-        <v>0.6407885540320136</v>
+      <c r="C8" s="33">
+        <f>DCF!C16</f>
+        <v/>
       </c>
     </row>
     <row r="9">
@@ -5895,19 +6681,19 @@
         </is>
       </c>
       <c r="C10" s="28">
-        <f>-19789.0+6474.0</f>
+        <f>-Assumptions!$C$50+Assumptions!$C$51</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="14" t="inlineStr">
+      <c r="A11" s="15" t="inlineStr">
         <is>
           <t>Implied value per share (EGP)</t>
         </is>
       </c>
-      <c r="B11" s="14" t="n"/>
+      <c r="B11" s="15" t="n"/>
       <c r="C11" s="30">
-        <f>(C9+C10)*(1-0.09645464025026068)/2140.777876</f>
+        <f>(C9+C10)*(1-'SOTP Bridge'!$C$15)/Assumptions!$C$6</f>
         <v/>
       </c>
     </row>
@@ -5917,8 +6703,9 @@
           <t>Trailing enterprise value / EBITDA</t>
         </is>
       </c>
-      <c r="C13" s="33" t="n">
-        <v>8.000722677325394</v>
+      <c r="C13" s="34">
+        <f>((Assumptions!$C$5*Assumptions!$C$6)+Assumptions!$C$50)/'Income Statement'!D7</f>
+        <v/>
       </c>
     </row>
     <row r="14">
@@ -5927,8 +6714,9 @@
           <t>Trailing price / earnings</t>
         </is>
       </c>
-      <c r="C14" s="33" t="n">
-        <v>12.9953740655049</v>
+      <c r="C14" s="34">
+        <f>Assumptions!$C$5/'Income Statement'!D18</f>
+        <v/>
       </c>
     </row>
     <row r="15">
@@ -5937,8 +6725,9 @@
           <t>Trailing price / book</t>
         </is>
       </c>
-      <c r="C15" s="33" t="n">
-        <v>3.196092220646482</v>
+      <c r="C15" s="34">
+        <f>Assumptions!$C$5/C31</f>
+        <v/>
       </c>
     </row>
     <row r="16">
@@ -5947,14 +6736,15 @@
           <t>Net bank debt / EBITDA</t>
         </is>
       </c>
-      <c r="C16" s="33" t="n">
-        <v>0.6462328796032941</v>
+      <c r="C16" s="34">
+        <f>Assumptions!$C$50/'Income Statement'!D7</f>
+        <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>Normalised earnings lens</t>
+          <t>Normalised earnings lens — every component from the same year (FY2028E)</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
@@ -5969,8 +6759,9 @@
           <t>Mid-cycle revenue (EGP mn)</t>
         </is>
       </c>
-      <c r="C19" s="17" t="n">
-        <v>442251.724251873</v>
+      <c r="C19" s="18">
+        <f>DCF!D5</f>
+        <v/>
       </c>
     </row>
     <row r="20">
@@ -5979,143 +6770,176 @@
           <t>Mid-cycle EBITDA margin</t>
         </is>
       </c>
-      <c r="C20" s="8" t="n">
-        <v>0.1106031122318905</v>
+      <c r="C20" s="16">
+        <f>DCF!D7</f>
+        <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>Mid-cycle EBIT (EGP mn)</t>
-        </is>
-      </c>
-      <c r="C21" s="17" t="n">
-        <v>44270.77398753235</v>
+          <t>Mid-cycle EBITDA (EGP mn)</t>
+        </is>
+      </c>
+      <c r="C21" s="28">
+        <f>C19*C20</f>
+        <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Less net interest (EGP mn)</t>
-        </is>
-      </c>
-      <c r="C22" s="17" t="n">
-        <v>-3418.938394042807</v>
+          <t>Mid-cycle EBIT (EGP mn)</t>
+        </is>
+      </c>
+      <c r="C22" s="28">
+        <f>C21-C19*Assumptions!$C$34</f>
+        <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>Normalised attributable earnings (EGP mn)</t>
-        </is>
-      </c>
-      <c r="C23" s="17" t="n">
-        <v>28795.29588548318</v>
+          <t>Net finance cost (EGP mn)</t>
+        </is>
+      </c>
+      <c r="C23" s="18">
+        <f>'Income Statement'!G11</f>
+        <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Normalised earnings per share (EGP)</t>
-        </is>
-      </c>
-      <c r="C24" s="22" t="n">
-        <v>13.45085644255938</v>
+          <t>Share of equity-accounted investees (EGP mn)</t>
+        </is>
+      </c>
+      <c r="C24" s="18">
+        <f>'Income Statement'!G12</f>
+        <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
+          <t>Normalised attributable earnings (EGP mn)</t>
+        </is>
+      </c>
+      <c r="C25" s="28">
+        <f>(C22+C23+C24)*(1-Assumptions!$C$7)*(1-'SOTP Bridge'!$C$15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>Normalised earnings per share (EGP)</t>
+        </is>
+      </c>
+      <c r="C26" s="10">
+        <f>C25/Assumptions!$C$6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
           <t>Justified price / earnings</t>
         </is>
       </c>
-      <c r="C25" s="24" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="14" t="inlineStr">
+      <c r="C27" s="34">
+        <f>Assumptions!$C$62</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="15" t="inlineStr">
         <is>
           <t>Implied value per share (EGP)</t>
         </is>
       </c>
-      <c r="B26" s="14" t="n"/>
-      <c r="C26" s="30">
-        <f>C24*C25</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
+      <c r="B28" s="15" t="n"/>
+      <c r="C28" s="30">
+        <f>C26*C27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
         <is>
           <t>Book lens</t>
         </is>
       </c>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>Book value per share (EGP)</t>
-        </is>
-      </c>
-      <c r="C29" s="22" t="n">
-        <v>32.91519541282852</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="6" t="inlineStr">
-        <is>
-          <t>Sustainable return on equity</t>
-        </is>
-      </c>
-      <c r="C30" s="8" t="n">
-        <v>0.235</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>Trailing return on equity</t>
-        </is>
-      </c>
-      <c r="C31" s="8" t="n">
-        <v>0.2756503065994848</v>
+          <t>Book value per share (EGP)</t>
+        </is>
+      </c>
+      <c r="C31" s="8">
+        <f>'Balance Sheet'!D14/Assumptions!$C$6</f>
+        <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>Perpetual cost of equity</t>
-        </is>
-      </c>
-      <c r="C32" s="8" t="n">
-        <v>0.17563</v>
+          <t>Sustainable return on equity</t>
+        </is>
+      </c>
+      <c r="C32" s="11">
+        <f>Assumptions!$C$63</f>
+        <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
+          <t>Trailing return on equity</t>
+        </is>
+      </c>
+      <c r="C33" s="16">
+        <f>'Income Statement'!D17/(('Balance Sheet'!C14+'Balance Sheet'!D14)/2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>Perpetual cost of equity</t>
+        </is>
+      </c>
+      <c r="C34" s="16">
+        <f>DCF!C49</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
           <t>Justified price / book</t>
         </is>
       </c>
-      <c r="C33" s="24" t="n">
-        <v>1.472578205842553</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="14" t="inlineStr">
+      <c r="C35" s="34">
+        <f>(C32-Assumptions!$C$47)/(C34-Assumptions!$C$47)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="15" t="inlineStr">
         <is>
           <t>Implied value per share (EGP)</t>
         </is>
       </c>
-      <c r="B34" s="14" t="n"/>
-      <c r="C34" s="30">
-        <f>C29*C33</f>
+      <c r="B36" s="15" t="n"/>
+      <c r="C36" s="30">
+        <f>C31*C35</f>
         <v/>
       </c>
     </row>
@@ -6130,10 +6954,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
@@ -6156,7 +6980,7 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>Every line computed; the terminal value is capitalised at the terminal rate and discounted at the year-5 factor</t>
+          <t>Every line is a live formula: the cost of capital is built below, the glide is derived from the cost-of-debt path, and the terminal value is capitalised at the terminal rate and discounted at the year-5 factor</t>
         </is>
       </c>
     </row>
@@ -6198,20 +7022,25 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B5" s="28" t="n">
-        <v>365556.0698042354</v>
-      </c>
-      <c r="C5" s="28" t="n">
-        <v>408521.3870167609</v>
-      </c>
-      <c r="D5" s="28" t="n">
-        <v>442251.724251873</v>
-      </c>
-      <c r="E5" s="28" t="n">
-        <v>477216.9343520451</v>
-      </c>
-      <c r="F5" s="28" t="n">
-        <v>514192.2043319497</v>
+      <c r="B5" s="18">
+        <f>Segments!E12</f>
+        <v/>
+      </c>
+      <c r="C5" s="18">
+        <f>Segments!F12</f>
+        <v/>
+      </c>
+      <c r="D5" s="18">
+        <f>Segments!G12</f>
+        <v/>
+      </c>
+      <c r="E5" s="18">
+        <f>Segments!H12</f>
+        <v/>
+      </c>
+      <c r="F5" s="18">
+        <f>Segments!I12</f>
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -6220,20 +7049,25 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B6" s="28" t="n">
-        <v>41094.2415179939</v>
-      </c>
-      <c r="C6" s="28" t="n">
-        <v>44940.76148621193</v>
-      </c>
-      <c r="D6" s="28" t="n">
-        <v>48914.41709217701</v>
-      </c>
-      <c r="E6" s="28" t="n">
-        <v>53240.26178029377</v>
-      </c>
-      <c r="F6" s="28" t="n">
-        <v>57882.44686110957</v>
+      <c r="B6" s="18">
+        <f>Segments!B33</f>
+        <v/>
+      </c>
+      <c r="C6" s="18">
+        <f>Segments!C33</f>
+        <v/>
+      </c>
+      <c r="D6" s="18">
+        <f>Segments!D33</f>
+        <v/>
+      </c>
+      <c r="E6" s="18">
+        <f>Segments!E33</f>
+        <v/>
+      </c>
+      <c r="F6" s="18">
+        <f>Segments!F33</f>
+        <v/>
       </c>
     </row>
     <row r="7">
@@ -6242,20 +7076,25 @@
           <t>EBITDA margin</t>
         </is>
       </c>
-      <c r="B7" s="10" t="n">
-        <v>0.112415700114078</v>
-      </c>
-      <c r="C7" s="10" t="n">
-        <v>0.1100083445187365</v>
-      </c>
-      <c r="D7" s="10" t="n">
-        <v>0.1106031122318905</v>
-      </c>
-      <c r="E7" s="10" t="n">
-        <v>0.1115640664608482</v>
-      </c>
-      <c r="F7" s="10" t="n">
-        <v>0.1125696702000991</v>
+      <c r="B7" s="11">
+        <f>B6/B5</f>
+        <v/>
+      </c>
+      <c r="C7" s="11">
+        <f>C6/C5</f>
+        <v/>
+      </c>
+      <c r="D7" s="11">
+        <f>D6/D5</f>
+        <v/>
+      </c>
+      <c r="E7" s="11">
+        <f>E6/E5</f>
+        <v/>
+      </c>
+      <c r="F7" s="11">
+        <f>F6/F5</f>
+        <v/>
       </c>
     </row>
     <row r="8">
@@ -6264,42 +7103,52 @@
           <t>Less depreciation and amortisation</t>
         </is>
       </c>
-      <c r="B8" s="28" t="n">
-        <v>-3838.338732944472</v>
-      </c>
-      <c r="C8" s="28" t="n">
-        <v>-4289.47456367599</v>
-      </c>
-      <c r="D8" s="28" t="n">
-        <v>-4643.643104644667</v>
-      </c>
-      <c r="E8" s="28" t="n">
-        <v>-5010.777810696474</v>
-      </c>
-      <c r="F8" s="28" t="n">
-        <v>-5399.018145485472</v>
+      <c r="B8" s="28">
+        <f>-B5*Assumptions!$C$34</f>
+        <v/>
+      </c>
+      <c r="C8" s="28">
+        <f>-C5*Assumptions!$C$34</f>
+        <v/>
+      </c>
+      <c r="D8" s="28">
+        <f>-D5*Assumptions!$C$34</f>
+        <v/>
+      </c>
+      <c r="E8" s="28">
+        <f>-E5*Assumptions!$C$34</f>
+        <v/>
+      </c>
+      <c r="F8" s="28">
+        <f>-F5*Assumptions!$C$34</f>
+        <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="14" t="inlineStr">
+      <c r="A9" s="15" t="inlineStr">
         <is>
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B9" s="29" t="n">
-        <v>37255.90278504942</v>
-      </c>
-      <c r="C9" s="29" t="n">
-        <v>40651.28692253594</v>
-      </c>
-      <c r="D9" s="29" t="n">
-        <v>44270.77398753235</v>
-      </c>
-      <c r="E9" s="29" t="n">
-        <v>48229.4839695973</v>
-      </c>
-      <c r="F9" s="29" t="n">
-        <v>52483.42871562409</v>
+      <c r="B9" s="29">
+        <f>B6+B8</f>
+        <v/>
+      </c>
+      <c r="C9" s="29">
+        <f>C6+C8</f>
+        <v/>
+      </c>
+      <c r="D9" s="29">
+        <f>D6+D8</f>
+        <v/>
+      </c>
+      <c r="E9" s="29">
+        <f>E6+E8</f>
+        <v/>
+      </c>
+      <c r="F9" s="29">
+        <f>F6+F8</f>
+        <v/>
       </c>
     </row>
     <row r="10">
@@ -6308,20 +7157,25 @@
           <t>NOPAT — EBIT x (1 - 25%)</t>
         </is>
       </c>
-      <c r="B10" s="28" t="n">
-        <v>27941.92708878707</v>
-      </c>
-      <c r="C10" s="28" t="n">
-        <v>30488.46519190195</v>
-      </c>
-      <c r="D10" s="28" t="n">
-        <v>33203.08049064926</v>
-      </c>
-      <c r="E10" s="28" t="n">
-        <v>36172.11297719798</v>
-      </c>
-      <c r="F10" s="28" t="n">
-        <v>39362.57153671807</v>
+      <c r="B10" s="28">
+        <f>B9*(1-Assumptions!$C$7)</f>
+        <v/>
+      </c>
+      <c r="C10" s="28">
+        <f>C9*(1-Assumptions!$C$7)</f>
+        <v/>
+      </c>
+      <c r="D10" s="28">
+        <f>D9*(1-Assumptions!$C$7)</f>
+        <v/>
+      </c>
+      <c r="E10" s="28">
+        <f>E9*(1-Assumptions!$C$7)</f>
+        <v/>
+      </c>
+      <c r="F10" s="28">
+        <f>F9*(1-Assumptions!$C$7)</f>
+        <v/>
       </c>
     </row>
     <row r="11">
@@ -6330,20 +7184,25 @@
           <t>Add back depreciation and amortisation</t>
         </is>
       </c>
-      <c r="B11" s="28" t="n">
-        <v>3838.338732944472</v>
-      </c>
-      <c r="C11" s="28" t="n">
-        <v>4289.47456367599</v>
-      </c>
-      <c r="D11" s="28" t="n">
-        <v>4643.643104644667</v>
-      </c>
-      <c r="E11" s="28" t="n">
-        <v>5010.777810696474</v>
-      </c>
-      <c r="F11" s="28" t="n">
-        <v>5399.018145485472</v>
+      <c r="B11" s="28">
+        <f>-B8</f>
+        <v/>
+      </c>
+      <c r="C11" s="28">
+        <f>-C8</f>
+        <v/>
+      </c>
+      <c r="D11" s="28">
+        <f>-D8</f>
+        <v/>
+      </c>
+      <c r="E11" s="28">
+        <f>-E8</f>
+        <v/>
+      </c>
+      <c r="F11" s="28">
+        <f>-F8</f>
+        <v/>
       </c>
     </row>
     <row r="12">
@@ -6352,20 +7211,25 @@
           <t>Less capital expenditure</t>
         </is>
       </c>
-      <c r="B12" s="28" t="n">
-        <v>-10966.68209412706</v>
-      </c>
-      <c r="C12" s="28" t="n">
-        <v>-11847.12022348607</v>
-      </c>
-      <c r="D12" s="28" t="n">
-        <v>-12383.04827905244</v>
-      </c>
-      <c r="E12" s="28" t="n">
-        <v>-12407.64029315317</v>
-      </c>
-      <c r="F12" s="28" t="n">
-        <v>-12340.61290396679</v>
+      <c r="B12" s="28">
+        <f>-B5*Assumptions!$B$33</f>
+        <v/>
+      </c>
+      <c r="C12" s="28">
+        <f>-C5*Assumptions!$C$33</f>
+        <v/>
+      </c>
+      <c r="D12" s="28">
+        <f>-D5*Assumptions!$D$33</f>
+        <v/>
+      </c>
+      <c r="E12" s="28">
+        <f>-E5*Assumptions!$E$33</f>
+        <v/>
+      </c>
+      <c r="F12" s="28">
+        <f>-F5*Assumptions!$F$33</f>
+        <v/>
       </c>
     </row>
     <row r="13">
@@ -6374,42 +7238,52 @@
           <t>Less change in working capital</t>
         </is>
       </c>
-      <c r="B13" s="28" t="n">
-        <v>-19436.62605497414</v>
-      </c>
-      <c r="C13" s="28" t="n">
-        <v>-9882.022958880872</v>
-      </c>
-      <c r="D13" s="28" t="n">
-        <v>-7757.977564075773</v>
-      </c>
-      <c r="E13" s="28" t="n">
-        <v>-8041.998323039588</v>
-      </c>
-      <c r="F13" s="28" t="n">
-        <v>-8504.31209537806</v>
+      <c r="B13" s="28">
+        <f>-(B5-'Income Statement'!D5)*Assumptions!$C$32</f>
+        <v/>
+      </c>
+      <c r="C13" s="28">
+        <f>-(C5-B5)*Assumptions!$C$32</f>
+        <v/>
+      </c>
+      <c r="D13" s="28">
+        <f>-(D5-C5)*Assumptions!$C$32</f>
+        <v/>
+      </c>
+      <c r="E13" s="28">
+        <f>-(E5-D5)*Assumptions!$C$32</f>
+        <v/>
+      </c>
+      <c r="F13" s="28">
+        <f>-(F5-E5)*Assumptions!$C$32</f>
+        <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="14" t="inlineStr">
+      <c r="A14" s="15" t="inlineStr">
         <is>
           <t>Free cash flow to the firm</t>
         </is>
       </c>
-      <c r="B14" s="29" t="n">
-        <v>1376.957672630335</v>
-      </c>
-      <c r="C14" s="29" t="n">
-        <v>13048.796573211</v>
-      </c>
-      <c r="D14" s="29" t="n">
-        <v>17705.69775216571</v>
-      </c>
-      <c r="E14" s="29" t="n">
-        <v>20733.25217170169</v>
-      </c>
-      <c r="F14" s="29" t="n">
-        <v>23916.66468285869</v>
+      <c r="B14" s="29">
+        <f>B10+B11+B12+B13</f>
+        <v/>
+      </c>
+      <c r="C14" s="29">
+        <f>C10+C11+C12+C13</f>
+        <v/>
+      </c>
+      <c r="D14" s="29">
+        <f>D10+D11+D12+D13</f>
+        <v/>
+      </c>
+      <c r="E14" s="29">
+        <f>E10+E11+E12+E13</f>
+        <v/>
+      </c>
+      <c r="F14" s="29">
+        <f>F10+F11+F12+F13</f>
+        <v/>
       </c>
     </row>
     <row r="15">
@@ -6418,20 +7292,25 @@
           <t>Forward cost of capital</t>
         </is>
       </c>
-      <c r="B15" s="34" t="n">
-        <v>0.2689791685924707</v>
-      </c>
-      <c r="C15" s="34" t="n">
-        <v>0.2297894457283138</v>
-      </c>
-      <c r="D15" s="34" t="n">
-        <v>0.1954984382221766</v>
-      </c>
-      <c r="E15" s="34" t="n">
-        <v>0.1710048614320785</v>
-      </c>
-      <c r="F15" s="34" t="n">
-        <v>0.15141</v>
+      <c r="B15" s="35">
+        <f>$C$46-($C$46-$C$53)*B57</f>
+        <v/>
+      </c>
+      <c r="C15" s="35">
+        <f>$C$46-($C$46-$C$53)*C57</f>
+        <v/>
+      </c>
+      <c r="D15" s="35">
+        <f>$C$46-($C$46-$C$53)*D57</f>
+        <v/>
+      </c>
+      <c r="E15" s="35">
+        <f>$C$46-($C$46-$C$53)*E57</f>
+        <v/>
+      </c>
+      <c r="F15" s="35">
+        <f>$C$46-($C$46-$C$53)*F57</f>
+        <v/>
       </c>
     </row>
     <row r="16">
@@ -6440,42 +7319,52 @@
           <t>Discount factor</t>
         </is>
       </c>
-      <c r="B16" s="35" t="n">
-        <v>0.7880350006920778</v>
-      </c>
-      <c r="C16" s="35" t="n">
-        <v>0.6407885540320136</v>
-      </c>
-      <c r="D16" s="35" t="n">
-        <v>0.536001163652651</v>
-      </c>
-      <c r="E16" s="35" t="n">
-        <v>0.4577275306928695</v>
-      </c>
-      <c r="F16" s="35" t="n">
-        <v>0.3975365253844151</v>
+      <c r="B16" s="36">
+        <f>1/(1+B15)</f>
+        <v/>
+      </c>
+      <c r="C16" s="36">
+        <f>B16/(1+C15)</f>
+        <v/>
+      </c>
+      <c r="D16" s="36">
+        <f>C16/(1+D15)</f>
+        <v/>
+      </c>
+      <c r="E16" s="36">
+        <f>D16/(1+E15)</f>
+        <v/>
+      </c>
+      <c r="F16" s="36">
+        <f>E16/(1+F15)</f>
+        <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="14" t="inlineStr">
+      <c r="A17" s="15" t="inlineStr">
         <is>
           <t>Present value of FCFF</t>
         </is>
       </c>
-      <c r="B17" s="29" t="n">
-        <v>1085.090840504208</v>
-      </c>
-      <c r="C17" s="29" t="n">
-        <v>8361.519488005773</v>
-      </c>
-      <c r="D17" s="29" t="n">
-        <v>9490.274598442946</v>
-      </c>
-      <c r="E17" s="29" t="n">
-        <v>9490.18031978559</v>
-      </c>
-      <c r="F17" s="29" t="n">
-        <v>9507.747776807799</v>
+      <c r="B17" s="29">
+        <f>B14*B16</f>
+        <v/>
+      </c>
+      <c r="C17" s="29">
+        <f>C14*C16</f>
+        <v/>
+      </c>
+      <c r="D17" s="29">
+        <f>D14*D16</f>
+        <v/>
+      </c>
+      <c r="E17" s="29">
+        <f>E14*E16</f>
+        <v/>
+      </c>
+      <c r="F17" s="29">
+        <f>F14*F16</f>
+        <v/>
       </c>
     </row>
     <row r="19">
@@ -6491,8 +7380,9 @@
           <t>Terminal-year NOPAT grown one year (EGP mn)</t>
         </is>
       </c>
-      <c r="C20" s="17" t="n">
-        <v>41330.70011355398</v>
+      <c r="C20" s="28">
+        <f>F10*(1+C23)</f>
+        <v/>
       </c>
     </row>
     <row r="21">
@@ -6501,8 +7391,9 @@
           <t>Terminal return on invested capital</t>
         </is>
       </c>
-      <c r="C21" s="8" t="n">
-        <v>0.2180907072919819</v>
+      <c r="C21" s="16">
+        <f>F10*(1+C23)/'Summary Financials'!I13</f>
+        <v/>
       </c>
     </row>
     <row r="22">
@@ -6511,8 +7402,9 @@
           <t>Required reinvestment rate (g / return on capital)</t>
         </is>
       </c>
-      <c r="C22" s="8" t="n">
-        <v>0.2292624047161236</v>
+      <c r="C22" s="11">
+        <f>C23/C21</f>
+        <v/>
       </c>
     </row>
     <row r="23">
@@ -6521,8 +7413,9 @@
           <t>Terminal growth</t>
         </is>
       </c>
-      <c r="C23" s="8" t="n">
-        <v>0.05</v>
+      <c r="C23" s="16">
+        <f>Assumptions!$C$47</f>
+        <v/>
       </c>
     </row>
     <row r="24">
@@ -6531,8 +7424,9 @@
           <t>Terminal cost of capital</t>
         </is>
       </c>
-      <c r="C24" s="8" t="n">
-        <v>0.15141</v>
+      <c r="C24" s="11">
+        <f>C53</f>
+        <v/>
       </c>
     </row>
     <row r="25">
@@ -6541,8 +7435,9 @@
           <t>Terminal value (EGP mn)</t>
         </is>
       </c>
-      <c r="C25" s="17" t="n">
-        <v>314122.1222455342</v>
+      <c r="C25" s="28">
+        <f>C20*(1-C22)/(C24-C23)</f>
+        <v/>
       </c>
     </row>
     <row r="26">
@@ -6573,7 +7468,7 @@
           <t>Terminal value as a share of enterprise value</t>
         </is>
       </c>
-      <c r="C28" s="10">
+      <c r="C28" s="11">
         <f>C27/(C26+C27)</f>
         <v/>
       </c>
@@ -6601,17 +7496,341 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="14" t="inlineStr">
+      <c r="A31" s="15" t="inlineStr">
         <is>
           <t>Fair value per share (EGP)</t>
         </is>
       </c>
-      <c r="B31" s="14" t="n"/>
+      <c r="B31" s="15" t="n"/>
       <c r="C31" s="30">
-        <f>C30/2140.777876</f>
-        <v/>
-      </c>
-      <c r="D31" s="14" t="n"/>
+        <f>C30/Assumptions!$C$6</f>
+        <v/>
+      </c>
+      <c r="D31" s="15" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="20" t="inlineStr">
+        <is>
+          <t>COST OF CAPITAL — BUILT HERE, NOT ASSUMED</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>Risk-free rate, 10-year local currency</t>
+        </is>
+      </c>
+      <c r="C34" s="37">
+        <f>Assumptions!$C$37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>Less sovereign default spread (removed to avoid double-counting)</t>
+        </is>
+      </c>
+      <c r="C35" s="37">
+        <f>Assumptions!$C$38</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>Risk-free rate net of the sovereign spread</t>
+        </is>
+      </c>
+      <c r="C36" s="35">
+        <f>C34-C35</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="C37" s="38">
+        <f>Assumptions!$C$40</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>Equity risk premium</t>
+        </is>
+      </c>
+      <c r="C38" s="37">
+        <f>Assumptions!$C$39</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>Cost of equity, explicit window</t>
+        </is>
+      </c>
+      <c r="C39" s="35">
+        <f>C36+C37*C38</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>Cost of debt, blended</t>
+        </is>
+      </c>
+      <c r="C40" s="37">
+        <f>Assumptions!$C$41</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>Cost of debt after tax</t>
+        </is>
+      </c>
+      <c r="C41" s="35">
+        <f>C40*(1-Assumptions!$C$7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>Market capitalisation (EGP mn)</t>
+        </is>
+      </c>
+      <c r="C42" s="18">
+        <f>Assumptions!$C$5*Assumptions!$C$6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>Net bank debt (EGP mn)</t>
+        </is>
+      </c>
+      <c r="C43" s="18">
+        <f>Assumptions!$C$50</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>Debt weight (net debt / (net debt + market capitalisation))</t>
+        </is>
+      </c>
+      <c r="C44" s="35">
+        <f>C43/(C43+C42)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>Equity weight</t>
+        </is>
+      </c>
+      <c r="C45" s="35">
+        <f>1-C44</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="15" t="inlineStr">
+        <is>
+          <t>Cost of capital, explicit window</t>
+        </is>
+      </c>
+      <c r="B46" s="15" t="n"/>
+      <c r="C46" s="39">
+        <f>C45*C39+C44*C41</f>
+        <v/>
+      </c>
+      <c r="D46" s="15" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>Terminal risk-free rate</t>
+        </is>
+      </c>
+      <c r="C47" s="37">
+        <f>Assumptions!$C$43</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>Terminal equity risk premium</t>
+        </is>
+      </c>
+      <c r="C48" s="37">
+        <f>Assumptions!$C$44</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>Terminal cost of equity</t>
+        </is>
+      </c>
+      <c r="C49" s="35">
+        <f>C47+C37*C48</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>Terminal cost of debt</t>
+        </is>
+      </c>
+      <c r="C50" s="37">
+        <f>Assumptions!$C$45</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>Terminal cost of debt after tax</t>
+        </is>
+      </c>
+      <c r="C51" s="35">
+        <f>C50*(1-Assumptions!$C$7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>Terminal debt weight</t>
+        </is>
+      </c>
+      <c r="C52" s="37">
+        <f>Assumptions!$C$46</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="15" t="inlineStr">
+        <is>
+          <t>Terminal cost of capital</t>
+        </is>
+      </c>
+      <c r="B53" s="15" t="n"/>
+      <c r="C53" s="39">
+        <f>(1-C52)*C49+C52*C51</f>
+        <v/>
+      </c>
+      <c r="D53" s="15" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>The glide — inherited from the cost-of-debt path, not invented</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>FY26E</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>FY27E</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>FY28E</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>FY29E</t>
+        </is>
+      </c>
+      <c r="F55" s="5" t="inlineStr">
+        <is>
+          <t>FY30E</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>Cost of debt path</t>
+        </is>
+      </c>
+      <c r="B56" s="37">
+        <f>Assumptions!$B$42</f>
+        <v/>
+      </c>
+      <c r="C56" s="37">
+        <f>Assumptions!$C$42</f>
+        <v/>
+      </c>
+      <c r="D56" s="37">
+        <f>Assumptions!$D$42</f>
+        <v/>
+      </c>
+      <c r="E56" s="37">
+        <f>Assumptions!$E$42</f>
+        <v/>
+      </c>
+      <c r="F56" s="37">
+        <f>Assumptions!$F$42</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t>Glide fraction — cumulative progress of the easing</t>
+        </is>
+      </c>
+      <c r="B57" s="35">
+        <f>($B$56-B56)/($B$56-$F$56)</f>
+        <v/>
+      </c>
+      <c r="C57" s="35">
+        <f>($B$56-C56)/($B$56-$F$56)</f>
+        <v/>
+      </c>
+      <c r="D57" s="35">
+        <f>($B$56-D56)/($B$56-$F$56)</f>
+        <v/>
+      </c>
+      <c r="E57" s="35">
+        <f>($B$56-E56)/($B$56-$F$56)</f>
+        <v/>
+      </c>
+      <c r="F57" s="35">
+        <f>($B$56-F56)/($B$56-$F$56)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Note: row 15 above is the explicit-window cost of capital walked down to the terminal rate by the glide fraction on row 57, so the shape of the easing is inherited from the cost-of-debt path rather than being a second free parameter.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6656,7 +7875,7 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>EGP mn, consolidated</t>
+          <t>EGP mn, consolidated. History is the audited record; every forecast line is a formula</t>
         </is>
       </c>
     </row>
@@ -6708,7 +7927,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="14" t="inlineStr">
+      <c r="A5" s="15" t="inlineStr">
         <is>
           <t>Revenue</t>
         </is>
@@ -6722,20 +7941,25 @@
       <c r="D5" s="29" t="n">
         <v>281049</v>
       </c>
-      <c r="E5" s="29" t="n">
-        <v>365556.0698042354</v>
-      </c>
-      <c r="F5" s="29" t="n">
-        <v>408521.3870167609</v>
-      </c>
-      <c r="G5" s="29" t="n">
-        <v>442251.724251873</v>
-      </c>
-      <c r="H5" s="29" t="n">
-        <v>477216.9343520451</v>
-      </c>
-      <c r="I5" s="29" t="n">
-        <v>514192.2043319497</v>
+      <c r="E5" s="29">
+        <f>DCF!B5</f>
+        <v/>
+      </c>
+      <c r="F5" s="29">
+        <f>DCF!C5</f>
+        <v/>
+      </c>
+      <c r="G5" s="29">
+        <f>DCF!D5</f>
+        <v/>
+      </c>
+      <c r="H5" s="29">
+        <f>DCF!E5</f>
+        <v/>
+      </c>
+      <c r="I5" s="29">
+        <f>DCF!F5</f>
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -6744,18 +7968,38 @@
           <t>Gross profit</t>
         </is>
       </c>
-      <c r="B6" s="28" t="n">
+      <c r="B6" s="22" t="n">
         <v>29077.3</v>
       </c>
-      <c r="C6" s="28" t="n">
+      <c r="C6" s="22" t="n">
         <v>43898.5</v>
       </c>
-      <c r="D6" s="28" t="n">
+      <c r="D6" s="22" t="n">
         <v>40720</v>
       </c>
+      <c r="E6" s="18">
+        <f>Segments!B22</f>
+        <v/>
+      </c>
+      <c r="F6" s="18">
+        <f>Segments!C22</f>
+        <v/>
+      </c>
+      <c r="G6" s="18">
+        <f>Segments!D22</f>
+        <v/>
+      </c>
+      <c r="H6" s="18">
+        <f>Segments!E22</f>
+        <v/>
+      </c>
+      <c r="I6" s="18">
+        <f>Segments!F22</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="14" t="inlineStr">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>EBITDA</t>
         </is>
@@ -6769,20 +8013,25 @@
       <c r="D7" s="29" t="n">
         <v>30622.08783333333</v>
       </c>
-      <c r="E7" s="29" t="n">
-        <v>41094.2415179939</v>
-      </c>
-      <c r="F7" s="29" t="n">
-        <v>44940.76148621193</v>
-      </c>
-      <c r="G7" s="29" t="n">
-        <v>48914.41709217701</v>
-      </c>
-      <c r="H7" s="29" t="n">
-        <v>53240.26178029377</v>
-      </c>
-      <c r="I7" s="29" t="n">
-        <v>57882.44686110957</v>
+      <c r="E7" s="29">
+        <f>DCF!B6</f>
+        <v/>
+      </c>
+      <c r="F7" s="29">
+        <f>DCF!C6</f>
+        <v/>
+      </c>
+      <c r="G7" s="29">
+        <f>DCF!D6</f>
+        <v/>
+      </c>
+      <c r="H7" s="29">
+        <f>DCF!E6</f>
+        <v/>
+      </c>
+      <c r="I7" s="29">
+        <f>DCF!F6</f>
+        <v/>
       </c>
     </row>
     <row r="8">
@@ -6791,35 +8040,35 @@
           <t>EBITDA margin</t>
         </is>
       </c>
-      <c r="B8" s="10">
+      <c r="B8" s="11">
         <f>B7/B5</f>
         <v/>
       </c>
-      <c r="C8" s="10">
+      <c r="C8" s="11">
         <f>C7/C5</f>
         <v/>
       </c>
-      <c r="D8" s="10">
+      <c r="D8" s="11">
         <f>D7/D5</f>
         <v/>
       </c>
-      <c r="E8" s="10">
+      <c r="E8" s="11">
         <f>E7/E5</f>
         <v/>
       </c>
-      <c r="F8" s="10">
+      <c r="F8" s="11">
         <f>F7/F5</f>
         <v/>
       </c>
-      <c r="G8" s="10">
+      <c r="G8" s="11">
         <f>G7/G5</f>
         <v/>
       </c>
-      <c r="H8" s="10">
+      <c r="H8" s="11">
         <f>H7/H5</f>
         <v/>
       </c>
-      <c r="I8" s="10">
+      <c r="I8" s="11">
         <f>I7/I5</f>
         <v/>
       </c>
@@ -6830,60 +8079,73 @@
           <t>Depreciation and amortisation</t>
         </is>
       </c>
-      <c r="B9" s="28" t="n">
+      <c r="B9" s="22" t="n">
         <v>-2296</v>
       </c>
-      <c r="C9" s="28" t="n">
+      <c r="C9" s="22" t="n">
         <v>-2259.9</v>
       </c>
-      <c r="D9" s="28" t="n">
+      <c r="D9" s="22" t="n">
         <v>-2951.0145</v>
       </c>
-      <c r="E9" s="28" t="n">
-        <v>-3838.338732944472</v>
-      </c>
-      <c r="F9" s="28" t="n">
-        <v>-4289.47456367599</v>
-      </c>
-      <c r="G9" s="28" t="n">
-        <v>-4643.643104644667</v>
-      </c>
-      <c r="H9" s="28" t="n">
-        <v>-5010.777810696474</v>
-      </c>
-      <c r="I9" s="28" t="n">
-        <v>-5399.018145485472</v>
+      <c r="E9" s="18">
+        <f>DCF!B8</f>
+        <v/>
+      </c>
+      <c r="F9" s="18">
+        <f>DCF!C8</f>
+        <v/>
+      </c>
+      <c r="G9" s="18">
+        <f>DCF!D8</f>
+        <v/>
+      </c>
+      <c r="H9" s="18">
+        <f>DCF!E8</f>
+        <v/>
+      </c>
+      <c r="I9" s="18">
+        <f>DCF!F8</f>
+        <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="14" t="inlineStr">
+      <c r="A10" s="15" t="inlineStr">
         <is>
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B10" s="29" t="n">
-        <v>17739.1</v>
-      </c>
-      <c r="C10" s="29" t="n">
-        <v>29341.7</v>
-      </c>
-      <c r="D10" s="29" t="n">
-        <v>27671.07333333333</v>
-      </c>
-      <c r="E10" s="29" t="n">
-        <v>37255.90278504942</v>
-      </c>
-      <c r="F10" s="29" t="n">
-        <v>40651.28692253594</v>
-      </c>
-      <c r="G10" s="29" t="n">
-        <v>44270.77398753235</v>
-      </c>
-      <c r="H10" s="29" t="n">
-        <v>48229.4839695973</v>
-      </c>
-      <c r="I10" s="29" t="n">
-        <v>52483.42871562409</v>
+      <c r="B10" s="29">
+        <f>B7+B9</f>
+        <v/>
+      </c>
+      <c r="C10" s="29">
+        <f>C7+C9</f>
+        <v/>
+      </c>
+      <c r="D10" s="29">
+        <f>D7+D9</f>
+        <v/>
+      </c>
+      <c r="E10" s="29">
+        <f>E7+E9</f>
+        <v/>
+      </c>
+      <c r="F10" s="29">
+        <f>F7+F9</f>
+        <v/>
+      </c>
+      <c r="G10" s="29">
+        <f>G7+G9</f>
+        <v/>
+      </c>
+      <c r="H10" s="29">
+        <f>H7+H9</f>
+        <v/>
+      </c>
+      <c r="I10" s="29">
+        <f>I7+I9</f>
+        <v/>
       </c>
     </row>
     <row r="11">
@@ -6892,29 +8154,34 @@
           <t>Net finance costs</t>
         </is>
       </c>
-      <c r="B11" s="28" t="n">
+      <c r="B11" s="22" t="n">
         <v>-2124.4</v>
       </c>
-      <c r="C11" s="28" t="n">
+      <c r="C11" s="22" t="n">
         <v>-3515.4</v>
       </c>
-      <c r="D11" s="28" t="n">
+      <c r="D11" s="22" t="n">
         <v>-3400</v>
       </c>
-      <c r="E11" s="28" t="n">
-        <v>-4127.401616023958</v>
-      </c>
-      <c r="F11" s="28" t="n">
-        <v>-3554.467851750901</v>
-      </c>
-      <c r="G11" s="28" t="n">
-        <v>-3053.150808011979</v>
-      </c>
-      <c r="H11" s="28" t="n">
-        <v>-2695.067205341319</v>
-      </c>
-      <c r="I11" s="28" t="n">
-        <v>-2408.600323204791</v>
+      <c r="E11" s="28">
+        <f>-(Assumptions!$B$42*'Balance Sheet'!$D$11-Assumptions!$C$58*MAX('Balance Sheet'!$D$11-'Balance Sheet'!D17,0))</f>
+        <v/>
+      </c>
+      <c r="F11" s="28">
+        <f>-(Assumptions!$C$42*'Balance Sheet'!$D$11-Assumptions!$C$58*MAX('Balance Sheet'!$D$11-'Balance Sheet'!E17,0))</f>
+        <v/>
+      </c>
+      <c r="G11" s="28">
+        <f>-(Assumptions!$D$42*'Balance Sheet'!$D$11-Assumptions!$C$58*MAX('Balance Sheet'!$D$11-'Balance Sheet'!F17,0))</f>
+        <v/>
+      </c>
+      <c r="H11" s="28">
+        <f>-(Assumptions!$E$42*'Balance Sheet'!$D$11-Assumptions!$C$58*MAX('Balance Sheet'!$D$11-'Balance Sheet'!G17,0))</f>
+        <v/>
+      </c>
+      <c r="I11" s="28">
+        <f>-(Assumptions!$F$42*'Balance Sheet'!$D$11-Assumptions!$C$58*MAX('Balance Sheet'!$D$11-'Balance Sheet'!H17,0))</f>
+        <v/>
       </c>
     </row>
     <row r="12">
@@ -6923,29 +8190,34 @@
           <t>Share of equity-accounted investees</t>
         </is>
       </c>
-      <c r="B12" s="28" t="n">
+      <c r="B12" s="22" t="n">
         <v>603.6</v>
       </c>
-      <c r="C12" s="28" t="n">
+      <c r="C12" s="22" t="n">
         <v>1132.4</v>
       </c>
-      <c r="D12" s="28" t="n">
+      <c r="D12" s="22" t="n">
         <v>1302.26</v>
       </c>
-      <c r="E12" s="28" t="n">
-        <v>1406.4408</v>
-      </c>
-      <c r="F12" s="28" t="n">
-        <v>1518.956064</v>
-      </c>
-      <c r="G12" s="28" t="n">
-        <v>1640.47254912</v>
-      </c>
-      <c r="H12" s="28" t="n">
-        <v>1771.7103530496</v>
-      </c>
-      <c r="I12" s="28" t="n">
-        <v>1913.447181293569</v>
+      <c r="E12" s="28">
+        <f>D12*(1+Assumptions!$C$57)</f>
+        <v/>
+      </c>
+      <c r="F12" s="28">
+        <f>E12*(1+Assumptions!$C$57)</f>
+        <v/>
+      </c>
+      <c r="G12" s="28">
+        <f>F12*(1+Assumptions!$C$57)</f>
+        <v/>
+      </c>
+      <c r="H12" s="28">
+        <f>G12*(1+Assumptions!$C$57)</f>
+        <v/>
+      </c>
+      <c r="I12" s="28">
+        <f>H12*(1+Assumptions!$C$57)</f>
+        <v/>
       </c>
     </row>
     <row r="13">
@@ -6954,14 +8226,37 @@
           <t>Profit before tax</t>
         </is>
       </c>
-      <c r="B13" s="28" t="n">
-        <v>16218.3</v>
-      </c>
-      <c r="C13" s="28" t="n">
-        <v>26958.7</v>
-      </c>
-      <c r="D13" s="28" t="n">
-        <v>25573.33333333333</v>
+      <c r="B13" s="28">
+        <f>B10+B11+B12</f>
+        <v/>
+      </c>
+      <c r="C13" s="28">
+        <f>C10+C11+C12</f>
+        <v/>
+      </c>
+      <c r="D13" s="28">
+        <f>D10+D11+D12</f>
+        <v/>
+      </c>
+      <c r="E13" s="28">
+        <f>E10+E11+E12</f>
+        <v/>
+      </c>
+      <c r="F13" s="28">
+        <f>F10+F11+F12</f>
+        <v/>
+      </c>
+      <c r="G13" s="28">
+        <f>G10+G11+G12</f>
+        <v/>
+      </c>
+      <c r="H13" s="28">
+        <f>H10+H11+H12</f>
+        <v/>
+      </c>
+      <c r="I13" s="28">
+        <f>I10+I11+I12</f>
+        <v/>
       </c>
     </row>
     <row r="14">
@@ -6970,14 +8265,34 @@
           <t>Income tax</t>
         </is>
       </c>
-      <c r="B14" s="28" t="n">
+      <c r="B14" s="22" t="n">
         <v>-5080.4</v>
       </c>
-      <c r="C14" s="28" t="n">
+      <c r="C14" s="22" t="n">
         <v>-8121.5</v>
       </c>
-      <c r="D14" s="28" t="n">
+      <c r="D14" s="22" t="n">
         <v>-6393.333333333332</v>
+      </c>
+      <c r="E14" s="28">
+        <f>-E13*Assumptions!$C$7</f>
+        <v/>
+      </c>
+      <c r="F14" s="28">
+        <f>-F13*Assumptions!$C$7</f>
+        <v/>
+      </c>
+      <c r="G14" s="28">
+        <f>-G13*Assumptions!$C$7</f>
+        <v/>
+      </c>
+      <c r="H14" s="28">
+        <f>-H13*Assumptions!$C$7</f>
+        <v/>
+      </c>
+      <c r="I14" s="28">
+        <f>-I13*Assumptions!$C$7</f>
+        <v/>
       </c>
     </row>
     <row r="15">
@@ -6986,14 +8301,34 @@
           <t>Profit for the year</t>
         </is>
       </c>
-      <c r="B15" s="28" t="n">
+      <c r="B15" s="22" t="n">
         <v>11138</v>
       </c>
-      <c r="C15" s="28" t="n">
+      <c r="C15" s="22" t="n">
         <v>18837.2</v>
       </c>
-      <c r="D15" s="28" t="n">
+      <c r="D15" s="22" t="n">
         <v>19180</v>
+      </c>
+      <c r="E15" s="28">
+        <f>E13+E14</f>
+        <v/>
+      </c>
+      <c r="F15" s="28">
+        <f>F13+F14</f>
+        <v/>
+      </c>
+      <c r="G15" s="28">
+        <f>G13+G14</f>
+        <v/>
+      </c>
+      <c r="H15" s="28">
+        <f>H13+H14</f>
+        <v/>
+      </c>
+      <c r="I15" s="28">
+        <f>I13+I14</f>
+        <v/>
       </c>
     </row>
     <row r="16">
@@ -7002,18 +8337,38 @@
           <t>Non-controlling interests</t>
         </is>
       </c>
-      <c r="B16" s="28" t="n">
+      <c r="B16" s="22" t="n">
         <v>-1022.299999999999</v>
       </c>
-      <c r="C16" s="28" t="n">
+      <c r="C16" s="22" t="n">
         <v>-1375.799999999999</v>
       </c>
-      <c r="D16" s="28" t="n">
+      <c r="D16" s="22" t="n">
         <v>-1850</v>
       </c>
+      <c r="E16" s="28">
+        <f>-E15*'SOTP Bridge'!$C$15</f>
+        <v/>
+      </c>
+      <c r="F16" s="28">
+        <f>-F15*'SOTP Bridge'!$C$15</f>
+        <v/>
+      </c>
+      <c r="G16" s="28">
+        <f>-G15*'SOTP Bridge'!$C$15</f>
+        <v/>
+      </c>
+      <c r="H16" s="28">
+        <f>-H15*'SOTP Bridge'!$C$15</f>
+        <v/>
+      </c>
+      <c r="I16" s="28">
+        <f>-I15*'SOTP Bridge'!$C$15</f>
+        <v/>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="14" t="inlineStr">
+      <c r="A17" s="15" t="inlineStr">
         <is>
           <t>Profit attributable to shareholders</t>
         </is>
@@ -7027,20 +8382,25 @@
       <c r="D17" s="29" t="n">
         <v>17330</v>
       </c>
-      <c r="E17" s="29" t="n">
-        <v>23402.91492400461</v>
-      </c>
-      <c r="F17" s="29" t="n">
-        <v>25655.38637609128</v>
-      </c>
-      <c r="G17" s="29" t="n">
-        <v>28760.73212503701</v>
-      </c>
-      <c r="H17" s="29" t="n">
-        <v>32311.21619073199</v>
-      </c>
-      <c r="I17" s="29" t="n">
-        <v>36223.78337066263</v>
+      <c r="E17" s="29">
+        <f>E15+E16</f>
+        <v/>
+      </c>
+      <c r="F17" s="29">
+        <f>F15+F16</f>
+        <v/>
+      </c>
+      <c r="G17" s="29">
+        <f>G15+G16</f>
+        <v/>
+      </c>
+      <c r="H17" s="29">
+        <f>H15+H16</f>
+        <v/>
+      </c>
+      <c r="I17" s="29">
+        <f>I15+I16</f>
+        <v/>
       </c>
     </row>
     <row r="18">
@@ -7049,43 +8409,43 @@
           <t>Earnings per share (EGP)</t>
         </is>
       </c>
-      <c r="B18" s="9">
-        <f>B17/2140.777876</f>
-        <v/>
-      </c>
-      <c r="C18" s="9">
-        <f>C17/2140.777876</f>
-        <v/>
-      </c>
-      <c r="D18" s="9">
-        <f>D17/2140.777876</f>
-        <v/>
-      </c>
-      <c r="E18" s="9">
-        <f>E17/2140.777876</f>
-        <v/>
-      </c>
-      <c r="F18" s="9">
-        <f>F17/2140.777876</f>
-        <v/>
-      </c>
-      <c r="G18" s="9">
-        <f>G17/2140.777876</f>
-        <v/>
-      </c>
-      <c r="H18" s="9">
-        <f>H17/2140.777876</f>
-        <v/>
-      </c>
-      <c r="I18" s="9">
-        <f>I17/2140.777876</f>
+      <c r="B18" s="10">
+        <f>B17/Assumptions!$C$6</f>
+        <v/>
+      </c>
+      <c r="C18" s="10">
+        <f>C17/Assumptions!$C$6</f>
+        <v/>
+      </c>
+      <c r="D18" s="10">
+        <f>D17/Assumptions!$C$6</f>
+        <v/>
+      </c>
+      <c r="E18" s="10">
+        <f>E17/Assumptions!$C$6</f>
+        <v/>
+      </c>
+      <c r="F18" s="10">
+        <f>F17/Assumptions!$C$6</f>
+        <v/>
+      </c>
+      <c r="G18" s="10">
+        <f>G17/Assumptions!$C$6</f>
+        <v/>
+      </c>
+      <c r="H18" s="10">
+        <f>H17/Assumptions!$C$6</f>
+        <v/>
+      </c>
+      <c r="I18" s="10">
+        <f>I17/Assumptions!$C$6</f>
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>Note: FY2023 and FY2024 are audited. FY2025 revenue, profit after tax and profit after minority interests are disclosed; the intermediate lines are derived by closing the account to the reported profit. Forecast profit is struck after interest on the estimated debt and cash balances, so it differs from the pre-financing DCF waterfall by construction.</t>
+          <t>Note: FY2023 and FY2024 are audited. FY2025 revenue, profit after tax and profit after minority interests are disclosed; the intermediate lines are derived by closing the account to the reported profit. In the forecast the finance charge is computed on the gross debt book less the cash the business is accumulating, so it falls with net debt rather than being frozen at the FY2025 balance; profit is therefore struck after interest and differs from the pre-financing DCF waterfall by construction.</t>
         </is>
       </c>
     </row>

--- a/engine/swdy_study/SWDY_Valuation_Model_05082026_public.xlsx
+++ b/engine/swdy_study/SWDY_Valuation_Model_05082026_public.xlsx
@@ -36,8 +36,8 @@
     <numFmt numFmtId="165" formatCode="0.0%;(0.0%);&quot;-&quot;"/>
     <numFmt numFmtId="166" formatCode="#,##0;(#,##0);&quot;-&quot;"/>
     <numFmt numFmtId="167" formatCode="#,##0.0;(#,##0.0);&quot;-&quot;"/>
-    <numFmt numFmtId="168" formatCode="0.00x"/>
-    <numFmt numFmtId="169" formatCode="0.000"/>
+    <numFmt numFmtId="168" formatCode="0.000"/>
+    <numFmt numFmtId="169" formatCode="0.00x"/>
     <numFmt numFmtId="170" formatCode="0.0000"/>
   </numFmts>
   <fonts count="11">
@@ -153,13 +153,13 @@
     <xf numFmtId="166" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="8" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -529,7 +529,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I50"/>
+  <dimension ref="A1:I51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="112" customWidth="1" min="1" max="1"/>
@@ -626,233 +626,240 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>primary record, not a calculation. Second, the sub-segment unit build: revenue and gross profit per segment</t>
+          <t>primary record, not a calculation. Second, the segment build: revenue and profit for the three segments the</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>come from a seven-line tonnage, megavolt-ampere, meter-unit and order-book model, and only its OUTPUT is</t>
+          <t>company itself discloses (Cables and its accessories, Constructions and infrastructure, Electrical products</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>carried here; everything downstream of it is formula. Third, the Monte Carlo price map and the sensitivity</t>
+          <t>and digital solutions) are pasted for FY2025 and grown on their own drivers; only its OUTPUT is carried here</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>grids, where each individual cell is a complete re-run of the whole valuation and so cannot be a formula in</t>
+          <t>and everything downstream of it is formula. Third, the Monte Carlo price map and the sensitivity grids,</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>a grid. Changing a driver reprices the model but does NOT redraw those two grids.</t>
+          <t>where each individual cell is a complete re-run of the whole valuation and so cannot be a formula in a grid.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr"/>
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Changing a driver reprices the model but does NOT redraw those two grids.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>How revenue is built. Not as one growth rate. Revenue splits into a domestic Egyptian-pound leg and a</t>
-        </is>
-      </c>
+      <c r="A20" s="3" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>foreign leg forecast in US dollars and translated at an explicit exchange-rate path, because more than 70%</t>
+          <t>How revenue is built. Not as one growth rate. Each of the three disclosed segments is grown on its own</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>of this company's revenue is earned outside Egypt. Margins come from a segment build; group EBITDA margin</t>
+          <t>driver — Cables on copper-price growth times FX-translation growth times a modest real-volume assumption,</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>is an output of that build, not an input.</t>
+          <t>Constructions and Electrical products on a taper of their own recent revenue CAGR — because none of the</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="inlineStr"/>
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>audited filings discloses a tonnage, order-book or backlog figure to build a literal unit model from.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
+          <t>Margins come from the same segment build; group EBITDA margin is an OUTPUT of it, not an input.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
           <t>What it is not. It is not investment advice, a recommendation, or a price target. Values are model outputs</t>
         </is>
       </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>shown as ranges.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>Sourcing note, up front. FY2023 and FY2024 come from the company's audited consolidated statements and</t>
+          <t>shown as ranges.</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>earnings releases and are not estimated. For FY2025, revenue, profit after tax, profit after minority</t>
-        </is>
-      </c>
+      <c r="A29" s="3" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>interests, total assets and net bank debt are disclosed; the intermediate income-statement lines are</t>
+          <t>Sourcing note, up front. FY2023, FY2024 and FY2025 all come from the company's own audited consolidated</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>derived by closing the profit-and-loss account to the reported profit, and the balance sheet beyond total</t>
+          <t>financial statements — every income-statement, balance-sheet and segment line is the audited figure, not a</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>assets and net debt is triangulated by three methods, which are shown and averaged on the Balance Sheet</t>
+          <t>derivation or a triangulation. Segment revenue ties EXACTLY to consolidated revenue in every year (Note</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>sheet rather than asserted. Every derived line is annotated where it appears and listed with source and</t>
+          <t>5-3); segment profit reconciles to consolidated operating profit through an explicit, exactly-reconciling</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>date in the companion bibliography document.</t>
+          <t>corporate cost load (Note 16 less G&amp;A, net impairment, other expenses and other income). Every input is</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="inlineStr"/>
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>annotated where it appears and listed with source and date in the companion bibliography document.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t>Discount convention. Each explicit year is discounted at its own forward cost of capital, gliding</t>
-        </is>
-      </c>
+      <c r="A36" s="3" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>26.9% -&gt; 15.1% on the same easing calendar as the interest forecast; the terminal value is</t>
+          <t>Discount convention. Each explicit year is discounted at its own forward cost of capital, gliding</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>capitalised at the terminal rate and discounted at the year-5 cumulative factor. One date, one price of time.</t>
+          <t>26.6% -&gt; 14.8% on the same easing calendar as the interest forecast; the terminal value is</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>The glide fractions are not a free parameter: they are the cost-of-debt path's own cumulative progress, and</t>
+          <t>capitalised at the terminal rate and discounted at the year-5 cumulative factor. One date, one price of time.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
+          <t>The glide fractions are not a free parameter: they are the cost-of-debt path's own cumulative progress, and</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
           <t>the DCF sheet computes them in front of you.</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="3" t="inlineStr"/>
-    </row>
     <row r="42">
-      <c r="A42" s="3" t="inlineStr">
-        <is>
-          <t>The open question. This company earns most of its revenue in hard currency but reports, lists and borrows</t>
-        </is>
-      </c>
+      <c r="A42" s="3" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>in Egyptian pounds. The primary model charges the full Egyptian cost of capital. The Fundamental Valuation</t>
+          <t>The open question. This company earns just over half its revenue on a hard-currency-linked basis but</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>sheet also shows what the same cash flows are worth if the hard-currency leg is discounted at a</t>
+          <t>reports, lists and borrows in Egyptian pounds. The primary model charges the full Egyptian cost of capital.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>hard-currency rate. Both are shown; they are not averaged.</t>
+          <t>The Fundamental Valuation sheet also shows what the same cash flows are worth if the hard-currency leg is</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="inlineStr"/>
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>discounted at a hard-currency rate. Both are shown; they are not averaged.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t>Currency. EGP million unless stated. Spot EGP 105.20 (2026-08-05 close). Sheets: READ FIRST · Summary ·</t>
-        </is>
-      </c>
+      <c r="A47" s="3" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>Fundamental Valuation · Assumptions · SOTP Bridge · Segments · Relative &amp; Normalized · DCF · Income</t>
+          <t>Currency. EGP million unless stated. Spot EGP 105.20 (2026-08-05 close). Sheets: READ FIRST · Summary ·</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>Statement · Balance Sheet · Cash Flow · Summary Financials · Monte Carlo · Sensitivity · Per-Share &amp;</t>
+          <t>Fundamental Valuation · Assumptions · SOTP Bridge · Segments · Relative &amp; Normalized · DCF · Income</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>Statement · Balance Sheet · Cash Flow · Summary Financials · Monte Carlo · Sensitivity · Per-Share &amp;</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
         <is>
           <t>Ratios · Peer &amp; Sector.</t>
         </is>
@@ -869,7 +876,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -901,7 +908,7 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>EGP mn, consolidated. The FY2025 debt and cash lines are triangulated by three methods, shown and averaged below rather than asserted</t>
+          <t>EGP mn, consolidated. Every FY2023-25 line is the audited closing figure — no triangulation is needed for any year, including FY2025, because the full filing is in hand</t>
         </is>
       </c>
     </row>
@@ -959,14 +966,13 @@
         </is>
       </c>
       <c r="B5" s="22" t="n">
-        <v>18009.2</v>
+        <v>18009.166367</v>
       </c>
       <c r="C5" s="22" t="n">
-        <v>27543.8</v>
-      </c>
-      <c r="D5" s="28">
-        <f>C5+'Income Statement'!D5*(Assumptions!$B$33-Assumptions!$C$34)</f>
-        <v/>
+        <v>27543.762675</v>
+      </c>
+      <c r="D5" s="22" t="n">
+        <v>35961.076614</v>
       </c>
       <c r="E5" s="28">
         <f>D5-DCF!B12+DCF!B8</f>
@@ -996,15 +1002,13 @@
         </is>
       </c>
       <c r="B6" s="22" t="n">
-        <v>30881.8</v>
+        <v>30881.822082</v>
       </c>
       <c r="C6" s="22" t="n">
-        <v>56795.9</v>
-      </c>
-      <c r="D6" s="22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>56795.884068</v>
+      </c>
+      <c r="D6" s="22" t="n">
+        <v>59860.04457</v>
       </c>
     </row>
     <row r="7">
@@ -1014,15 +1018,13 @@
         </is>
       </c>
       <c r="B7" s="22" t="n">
-        <v>16179.6</v>
+        <v>16179.633722</v>
       </c>
       <c r="C7" s="22" t="n">
-        <v>18052</v>
-      </c>
-      <c r="D7" s="22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>18051.96657</v>
+      </c>
+      <c r="D7" s="22" t="n">
+        <v>29894.579591</v>
       </c>
     </row>
     <row r="8">
@@ -1032,15 +1034,13 @@
         </is>
       </c>
       <c r="B8" s="22" t="n">
-        <v>46591.9</v>
+        <v>46591.885092</v>
       </c>
       <c r="C8" s="22" t="n">
-        <v>86736.3</v>
-      </c>
-      <c r="D8" s="22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>86736.309423</v>
+      </c>
+      <c r="D8" s="22" t="n">
+        <v>116259.797169</v>
       </c>
     </row>
     <row r="9">
@@ -1050,10 +1050,10 @@
         </is>
       </c>
       <c r="B9" s="22" t="n">
-        <v>25552</v>
+        <v>25552.0448</v>
       </c>
       <c r="C9" s="22" t="n">
-        <v>38180</v>
+        <v>38180.002322</v>
       </c>
       <c r="D9" s="28">
         <f>D11-D17</f>
@@ -1067,13 +1067,13 @@
         </is>
       </c>
       <c r="B10" s="29" t="n">
-        <v>151448.7</v>
+        <v>151448.654828</v>
       </c>
       <c r="C10" s="29" t="n">
-        <v>249527.1</v>
+        <v>249527.138687</v>
       </c>
       <c r="D10" s="29" t="n">
-        <v>311090</v>
+        <v>311099.090775</v>
       </c>
       <c r="E10" s="15" t="n"/>
       <c r="F10" s="15" t="n"/>
@@ -1088,14 +1088,13 @@
         </is>
       </c>
       <c r="B11" s="22" t="n">
-        <v>41766.5</v>
+        <v>41766.492071</v>
       </c>
       <c r="C11" s="22" t="n">
-        <v>59082.9</v>
-      </c>
-      <c r="D11" s="28">
-        <f>AVERAGE(B23:B25)</f>
-        <v/>
+        <v>59082.941807</v>
+      </c>
+      <c r="D11" s="22" t="n">
+        <v>62509.211797</v>
       </c>
     </row>
     <row r="12">
@@ -1105,15 +1104,13 @@
         </is>
       </c>
       <c r="B12" s="22" t="n">
-        <v>31938.1</v>
+        <v>31938.12206</v>
       </c>
       <c r="C12" s="22" t="n">
-        <v>54808.2</v>
-      </c>
-      <c r="D12" s="22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>54808.185042</v>
+      </c>
+      <c r="D12" s="22" t="n">
+        <v>68895.662044</v>
       </c>
     </row>
     <row r="13">
@@ -1123,15 +1120,13 @@
         </is>
       </c>
       <c r="B13" s="22" t="n">
-        <v>25060.3</v>
+        <v>25060.328092</v>
       </c>
       <c r="C13" s="22" t="n">
-        <v>53281.1</v>
-      </c>
-      <c r="D13" s="22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>53281.056753</v>
+      </c>
+      <c r="D13" s="22" t="n">
+        <v>81266.224686</v>
       </c>
     </row>
     <row r="14">
@@ -1141,33 +1136,32 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>35724.5</v>
+        <v>35724.466132</v>
       </c>
       <c r="C14" s="29" t="n">
-        <v>55274.9</v>
-      </c>
-      <c r="D14" s="29">
-        <f>C14+'Income Statement'!D17-Assumptions!$C$55*Assumptions!$C$6</f>
-        <v/>
+        <v>55274.913356</v>
+      </c>
+      <c r="D14" s="29" t="n">
+        <v>66870.86655000001</v>
       </c>
       <c r="E14" s="29">
-        <f>D14+'Income Statement'!E17*(1-Assumptions!$C$56)</f>
+        <f>D14+'Income Statement'!E17*(1-Assumptions!$C$49)</f>
         <v/>
       </c>
       <c r="F14" s="29">
-        <f>E14+'Income Statement'!F17*(1-Assumptions!$C$56)</f>
+        <f>E14+'Income Statement'!F17*(1-Assumptions!$C$49)</f>
         <v/>
       </c>
       <c r="G14" s="29">
-        <f>F14+'Income Statement'!G17*(1-Assumptions!$C$56)</f>
+        <f>F14+'Income Statement'!G17*(1-Assumptions!$C$49)</f>
         <v/>
       </c>
       <c r="H14" s="29">
-        <f>G14+'Income Statement'!H17*(1-Assumptions!$C$56)</f>
+        <f>G14+'Income Statement'!H17*(1-Assumptions!$C$49)</f>
         <v/>
       </c>
       <c r="I14" s="29">
-        <f>H14+'Income Statement'!I17*(1-Assumptions!$C$56)</f>
+        <f>H14+'Income Statement'!I17*(1-Assumptions!$C$49)</f>
         <v/>
       </c>
     </row>
@@ -1178,13 +1172,13 @@
         </is>
       </c>
       <c r="B15" s="22" t="n">
-        <v>2384</v>
+        <v>2384.013396</v>
       </c>
       <c r="C15" s="22" t="n">
-        <v>4251.8</v>
+        <v>4251.7719</v>
       </c>
       <c r="D15" s="22" t="n">
-        <v>5851.8</v>
+        <v>5118.978381</v>
       </c>
     </row>
     <row r="16">
@@ -1194,33 +1188,32 @@
         </is>
       </c>
       <c r="B16" s="22" t="n">
-        <v>36654.90000000001</v>
+        <v>36654.89074399999</v>
       </c>
       <c r="C16" s="22" t="n">
-        <v>53494.90000000002</v>
-      </c>
-      <c r="D16" s="28">
-        <f>'Income Statement'!D5*Assumptions!$C$32</f>
-        <v/>
+        <v>53494.91826600001</v>
+      </c>
+      <c r="D16" s="22" t="n">
+        <v>55852.53459999998</v>
       </c>
       <c r="E16" s="28">
-        <f>'Income Statement'!E5*Assumptions!$C$32</f>
+        <f>'Income Statement'!E5*Assumptions!$C$25</f>
         <v/>
       </c>
       <c r="F16" s="28">
-        <f>'Income Statement'!F5*Assumptions!$C$32</f>
+        <f>'Income Statement'!F5*Assumptions!$C$25</f>
         <v/>
       </c>
       <c r="G16" s="28">
-        <f>'Income Statement'!G5*Assumptions!$C$32</f>
+        <f>'Income Statement'!G5*Assumptions!$C$25</f>
         <v/>
       </c>
       <c r="H16" s="28">
-        <f>'Income Statement'!H5*Assumptions!$C$32</f>
+        <f>'Income Statement'!H5*Assumptions!$C$25</f>
         <v/>
       </c>
       <c r="I16" s="28">
-        <f>'Income Statement'!I5*Assumptions!$C$32</f>
+        <f>'Income Statement'!I5*Assumptions!$C$25</f>
         <v/>
       </c>
     </row>
@@ -1231,33 +1224,33 @@
         </is>
       </c>
       <c r="B17" s="29" t="n">
-        <v>14768</v>
+        <v>16214.447271</v>
       </c>
       <c r="C17" s="29" t="n">
-        <v>20028</v>
+        <v>20902.939485</v>
       </c>
       <c r="D17" s="29">
-        <f>Assumptions!$C$50</f>
+        <f>Assumptions!$C$43</f>
         <v/>
       </c>
       <c r="E17" s="29">
-        <f>D17-DCF!B14-'Income Statement'!E11*(1-Assumptions!$C$7)+Assumptions!$C$56*'Income Statement'!E17</f>
+        <f>D17-DCF!B14-'Income Statement'!E11*(1-Assumptions!$C$7)+Assumptions!$C$49*'Income Statement'!E17</f>
         <v/>
       </c>
       <c r="F17" s="29">
-        <f>E17-DCF!C14-'Income Statement'!F11*(1-Assumptions!$C$7)+Assumptions!$C$56*'Income Statement'!F17</f>
+        <f>E17-DCF!C14-'Income Statement'!F11*(1-Assumptions!$C$7)+Assumptions!$C$49*'Income Statement'!F17</f>
         <v/>
       </c>
       <c r="G17" s="29">
-        <f>F17-DCF!D14-'Income Statement'!G11*(1-Assumptions!$C$7)+Assumptions!$C$56*'Income Statement'!G17</f>
+        <f>F17-DCF!D14-'Income Statement'!G11*(1-Assumptions!$C$7)+Assumptions!$C$49*'Income Statement'!G17</f>
         <v/>
       </c>
       <c r="H17" s="29">
-        <f>G17-DCF!E14-'Income Statement'!H11*(1-Assumptions!$C$7)+Assumptions!$C$56*'Income Statement'!H17</f>
+        <f>G17-DCF!E14-'Income Statement'!H11*(1-Assumptions!$C$7)+Assumptions!$C$49*'Income Statement'!H17</f>
         <v/>
       </c>
       <c r="I17" s="29">
-        <f>H17-DCF!F14-'Income Statement'!I11*(1-Assumptions!$C$7)+Assumptions!$C$56*'Income Statement'!I17</f>
+        <f>H17-DCF!F14-'Income Statement'!I11*(1-Assumptions!$C$7)+Assumptions!$C$49*'Income Statement'!I17</f>
         <v/>
       </c>
     </row>
@@ -1314,70 +1307,16 @@
         <f>C10-(C11+C12+C13+C14+C15)</f>
         <v/>
       </c>
-      <c r="D19" s="6" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
+      <c r="D19" s="28">
+        <f>D10-(D11+D12+D13+D14+D15)</f>
+        <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Note: this is a CONDENSED layout, so it does not foot to zero — the residual row above is the block of other liabilities, provisions, deferred tax and related-party balances that is not shown separately. For FY2024 that residual is 22,828, which reconciles to the audited statements (provisions 13,440 + 943, deferred tax 3,670, related parties 2,050 + 95, other liabilities 2,631 = 22,829). FY2025 shows only the disclosed lines (total assets, net bank debt) plus rolled-forward equity and triangulated debt and cash; the valuation bridge uses only the disclosed net bank debt.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>FY2025 gross debt — three independent triangulations</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>EGP mn</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>Balance-sheet residual (assets less equity and non-debt liabilities)</t>
-        </is>
-      </c>
-      <c r="B23" s="22" t="n">
-        <v>76165.80577232633</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>FY2024 debt scaled with revenue growth</t>
-        </is>
-      </c>
-      <c r="B24" s="22" t="n">
-        <v>71579.70996905792</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t>Implied from the cash balance and the disclosed net debt</t>
-        </is>
-      </c>
-      <c r="B25" s="22" t="n">
-        <v>67104.64586101151</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="15" t="inlineStr">
-        <is>
-          <t>Average — the figure carried on row 11</t>
-        </is>
-      </c>
-      <c r="B26" s="29">
-        <f>AVERAGE(B23:B25)</f>
-        <v/>
+          <t>Note: this is a CONDENSED layout, so it does not foot to zero — the residual row above is the block of other liabilities, provisions, deferred tax and related-party balances that is not shown separately. For FY2024 that residual is 22,828, which reconciles to the audited statements (provisions 13,440 + 943, deferred tax 3,670, related parties 2,050 + 95, other liabilities 2,631 = 22,829). Every line, including FY2025, is now the audited closing figure — no triangulation or roll-forward is used for any historical year.</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1435,12 +1374,12 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>FY2023</t>
+          <t>FY2024</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2025</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
@@ -1476,11 +1415,11 @@
         </is>
       </c>
       <c r="B5" s="18">
-        <f>'Income Statement'!B7</f>
+        <f>'Income Statement'!C7</f>
         <v/>
       </c>
       <c r="C5" s="18">
-        <f>'Income Statement'!C7</f>
+        <f>'Income Statement'!D7</f>
         <v/>
       </c>
       <c r="D5" s="18">
@@ -1516,7 +1455,7 @@
         </is>
       </c>
       <c r="C6" s="22" t="n">
-        <v>-7706.9</v>
+        <v>-5740.31242</v>
       </c>
     </row>
     <row r="7">
@@ -1531,7 +1470,7 @@
         </is>
       </c>
       <c r="C7" s="22" t="n">
-        <v>-4891</v>
+        <v>-8298.752112</v>
       </c>
     </row>
     <row r="8">
@@ -1546,7 +1485,7 @@
         </is>
       </c>
       <c r="C8" s="22" t="n">
-        <v>3979.4</v>
+        <v>12765.922545</v>
       </c>
     </row>
     <row r="9">
@@ -1630,10 +1569,10 @@
         </is>
       </c>
       <c r="B11" s="22" t="n">
-        <v>-4830</v>
+        <v>-8489.780912</v>
       </c>
       <c r="C11" s="22" t="n">
-        <v>-8765.700000000001</v>
+        <v>-13112.049791</v>
       </c>
       <c r="D11" s="18">
         <f>DCF!B12</f>
@@ -1668,7 +1607,7 @@
         </is>
       </c>
       <c r="C12" s="28">
-        <f>-('Balance Sheet'!C16-'Balance Sheet'!B16)</f>
+        <f>-('Balance Sheet'!D16-'Balance Sheet'!C16)</f>
         <v/>
       </c>
       <c r="D12" s="18">
@@ -1733,7 +1672,7 @@
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>Cash conversion — operating cash flow as a share of EBITDA, FY2024</t>
+          <t>Cash conversion — operating cash flow as a share of EBITDA, FY2025</t>
         </is>
       </c>
       <c r="C15" s="11">
@@ -2175,27 +2114,27 @@
         </is>
       </c>
       <c r="D13" s="18">
-        <f>'Balance Sheet'!D16+'Balance Sheet'!D5+Assumptions!$C$52</f>
+        <f>'Balance Sheet'!D16+'Balance Sheet'!D5+Assumptions!$C$45</f>
         <v/>
       </c>
       <c r="E13" s="18">
-        <f>'Balance Sheet'!E16+'Balance Sheet'!E5+Assumptions!$C$52</f>
+        <f>'Balance Sheet'!E16+'Balance Sheet'!E5+Assumptions!$C$45</f>
         <v/>
       </c>
       <c r="F13" s="18">
-        <f>'Balance Sheet'!F16+'Balance Sheet'!F5+Assumptions!$C$52</f>
+        <f>'Balance Sheet'!F16+'Balance Sheet'!F5+Assumptions!$C$45</f>
         <v/>
       </c>
       <c r="G13" s="18">
-        <f>'Balance Sheet'!G16+'Balance Sheet'!G5+Assumptions!$C$52</f>
+        <f>'Balance Sheet'!G16+'Balance Sheet'!G5+Assumptions!$C$45</f>
         <v/>
       </c>
       <c r="H13" s="18">
-        <f>'Balance Sheet'!H16+'Balance Sheet'!H5+Assumptions!$C$52</f>
+        <f>'Balance Sheet'!H16+'Balance Sheet'!H5+Assumptions!$C$45</f>
         <v/>
       </c>
       <c r="I13" s="18">
-        <f>'Balance Sheet'!I16+'Balance Sheet'!I5+Assumptions!$C$52</f>
+        <f>'Balance Sheet'!I16+'Balance Sheet'!I5+Assumptions!$C$45</f>
         <v/>
       </c>
     </row>
@@ -2587,111 +2526,111 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>13.1%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>71.48013737611937</v>
+        <v>65.73330536703199</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>75.158505958635</v>
+        <v>69.438436012762</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>79.66249997898875</v>
+        <v>74.00009362699467</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>85.33897230281774</v>
+        <v>79.79348988925979</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>92.76070177891306</v>
+        <v>87.45046385571818</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>64.51999723358476</v>
+        <v>58.46247949320996</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>67.23266415979741</v>
+        <v>61.14086920605202</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>70.47099233404454</v>
+        <v>64.34874750647396</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>74.42869060586594</v>
+        <v>68.28850926253585</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>79.40797299188714</v>
+        <v>73.28076460177508</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>15.1%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>58.71390500851878</v>
+        <v>52.43291506341599</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>60.7356474116613</v>
+        <v>54.38595651288955</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>63.09639197519306</v>
+        <v>56.66901991043024</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>65.90739638220869</v>
+        <v>59.3939979641928</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>69.3345836803008</v>
+        <v>62.72981076166899</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>16.1%</t>
+          <t>15.8%</t>
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>53.79809034203993</v>
+        <v>47.35430052698718</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>55.314134925563</v>
+        <v>48.78264840984675</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>57.04924305755583</v>
+        <v>50.41527431963544</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>59.06822004769293</v>
+        <v>52.31440533812709</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>61.46422928886715</v>
+        <v>54.57039902646127</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>17.1%</t>
+          <t>16.8%</t>
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>49.58340787307901</v>
+        <v>43.02019875229038</v>
       </c>
       <c r="C10" s="7" t="n">
-        <v>50.72236517614795</v>
+        <v>44.06165690563098</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>52.00135637265844</v>
+        <v>45.2260975498987</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>53.45808918007977</v>
+        <v>46.54753023242386</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>55.14514468831749</v>
+        <v>48.07377779812698</v>
       </c>
     </row>
     <row r="12">
@@ -2705,138 +2644,138 @@
       <c r="A13" s="5" t="inlineStr"/>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>23.9%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>25.4%</t>
+          <t>25.1%</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>26.6%</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>28.4%</t>
+          <t>28.1%</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>29.9%</t>
+          <t>29.6%</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>terminal 13.1%</t>
+          <t>terminal 12.8%</t>
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>84.33728753089692</v>
+        <v>78.52776396161002</v>
       </c>
       <c r="C14" s="7" t="n">
-        <v>81.95820408756369</v>
+        <v>76.2229422830915</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>79.66249997898875</v>
+        <v>74.00009362699467</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>77.44651129819714</v>
+        <v>71.85558212399256</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>75.30676865150218</v>
+        <v>69.78596622715773</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>terminal 14.1%</t>
+          <t>terminal 13.8%</t>
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>74.62341007610547</v>
+        <v>68.32365822883249</v>
       </c>
       <c r="C15" s="7" t="n">
-        <v>72.51027129509237</v>
+        <v>66.3002853062016</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>70.47099233404454</v>
+        <v>64.34874750647396</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>68.50233381059978</v>
+        <v>62.46586343952262</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>66.60122807292484</v>
+        <v>60.6486215398966</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>terminal 15.1%</t>
+          <t>terminal 14.8%</t>
         </is>
       </c>
       <c r="B16" s="7" t="n">
-        <v>66.82989265057586</v>
+        <v>60.20432618850818</v>
       </c>
       <c r="C16" s="7" t="n">
-        <v>64.9300279088521</v>
+        <v>58.40478484299483</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>63.09639197519306</v>
+        <v>56.66901991043024</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>61.32608564835102</v>
+        <v>54.99421111957988</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>59.61636320712214</v>
+        <v>53.37768856559438</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>terminal 16.1%</t>
+          <t>terminal 15.8%</t>
         </is>
       </c>
       <c r="B17" s="7" t="n">
-        <v>60.43940513969982</v>
+        <v>53.59280842300805</v>
       </c>
       <c r="C17" s="7" t="n">
-        <v>58.71433541623137</v>
+        <v>51.97543076855138</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>57.04924305755583</v>
+        <v>50.41527431963544</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>55.44150743399135</v>
+        <v>48.90981241909613</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>53.88864645585161</v>
+        <v>47.45665296136994</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>terminal 17.1%</t>
+          <t>terminal 16.8%</t>
         </is>
       </c>
       <c r="B18" s="7" t="n">
-        <v>55.10506833536628</v>
+        <v>48.1069447436003</v>
       </c>
       <c r="C18" s="7" t="n">
-        <v>53.52583022982751</v>
+        <v>46.6406270489659</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>52.00135637265844</v>
+        <v>45.2260975498987</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>50.52925833918371</v>
+        <v>43.86107282353094</v>
       </c>
       <c r="F18" s="7" t="n">
-        <v>49.1072737958847</v>
+        <v>42.543390902758</v>
       </c>
     </row>
     <row r="20">
@@ -2882,19 +2821,19 @@
         </is>
       </c>
       <c r="B22" s="7" t="n">
-        <v>86.86398352810841</v>
+        <v>81.10220410949162</v>
       </c>
       <c r="C22" s="7" t="n">
-        <v>73.76938856958702</v>
+        <v>67.57169350379721</v>
       </c>
       <c r="D22" s="7" t="n">
-        <v>63.09639197519306</v>
+        <v>56.66901991043024</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>57.1692154119707</v>
+        <v>50.66757021426321</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>51.73397898456535</v>
+        <v>45.20072232829303</v>
       </c>
       <c r="H22" s="10">
         <f>MAX(B22:F22)-MIN(B22:F22)</f>
@@ -2908,19 +2847,19 @@
         </is>
       </c>
       <c r="B23" s="7" t="n">
-        <v>71.93944315776433</v>
+        <v>53.01576059688728</v>
       </c>
       <c r="C23" s="7" t="n">
-        <v>63.09639197519306</v>
+        <v>56.66901991043024</v>
       </c>
       <c r="D23" s="7" t="n">
-        <v>45.41028961005051</v>
+        <v>63.97553853751615</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>23.30266165362228</v>
+        <v>73.10868682137352</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>1.195033697194072</v>
+        <v>82.2418351052309</v>
       </c>
       <c r="H23" s="10">
         <f>MAX(B23:F23)-MIN(B23:F23)</f>
@@ -2934,19 +2873,19 @@
         </is>
       </c>
       <c r="B24" s="7" t="n">
-        <v>42.21530497281732</v>
+        <v>32.20907967130833</v>
       </c>
       <c r="C24" s="7" t="n">
-        <v>52.6558484740052</v>
+        <v>44.43904979086927</v>
       </c>
       <c r="D24" s="7" t="n">
-        <v>63.09639197519306</v>
+        <v>56.66901991043024</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>73.53693547638095</v>
+        <v>68.89899002999118</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>83.97747897756886</v>
+        <v>81.12896014955211</v>
       </c>
       <c r="H24" s="10">
         <f>MAX(B24:F24)-MIN(B24:F24)</f>
@@ -2960,19 +2899,19 @@
         </is>
       </c>
       <c r="B25" s="7" t="n">
-        <v>66.1820174425543</v>
+        <v>62.80167783479418</v>
       </c>
       <c r="C25" s="7" t="n">
-        <v>64.63920470887369</v>
+        <v>59.62961339115767</v>
       </c>
       <c r="D25" s="7" t="n">
-        <v>63.09639197519306</v>
+        <v>56.66901991043024</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>61.55357924151245</v>
+        <v>53.28548450388462</v>
       </c>
       <c r="F25" s="7" t="n">
-        <v>60.01076650783185</v>
+        <v>50.11342006024807</v>
       </c>
       <c r="H25" s="10">
         <f>MAX(B25:F25)-MIN(B25:F25)</f>
@@ -2986,19 +2925,19 @@
         </is>
       </c>
       <c r="B26" s="7" t="n">
-        <v>55.97972245871841</v>
+        <v>50.38212331740489</v>
       </c>
       <c r="C26" s="7" t="n">
-        <v>59.77877118391308</v>
+        <v>54.34373888956956</v>
       </c>
       <c r="D26" s="7" t="n">
-        <v>63.09639197519306</v>
+        <v>56.66901991043024</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>65.62346153036643</v>
+        <v>60.43853207751521</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>67.37686863430243</v>
+        <v>62.26697003389888</v>
       </c>
       <c r="H26" s="10">
         <f>MAX(B26:F26)-MIN(B26:F26)</f>
@@ -3581,18 +3520,18 @@
           <t>Capital expenditure / revenue</t>
         </is>
       </c>
-      <c r="B17" s="11">
-        <f>-'Cash Flow'!B11/'Income Statement'!B5</f>
-        <v/>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C17" s="11">
-        <f>-'Cash Flow'!C11/'Income Statement'!C5</f>
-        <v/>
-      </c>
-      <c r="D17" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <f>-'Cash Flow'!B11/'Income Statement'!C5</f>
+        <v/>
+      </c>
+      <c r="D17" s="11">
+        <f>-'Cash Flow'!C11/'Income Statement'!D5</f>
+        <v/>
       </c>
       <c r="E17" s="11">
         <f>-'Cash Flow'!D11/'Income Statement'!E5</f>
@@ -3622,13 +3561,13 @@
         </is>
       </c>
       <c r="B18" s="9" t="n">
-        <v>0.2079305448304614</v>
+        <v>0.2012516504606288</v>
       </c>
       <c r="C18" s="9" t="n">
-        <v>0.3172037113507076</v>
+        <v>0.3037580263923543</v>
       </c>
       <c r="D18" s="9" t="n">
-        <v>0.2640762760437433</v>
+        <v>0.5146285136141233</v>
       </c>
       <c r="E18" s="11" t="inlineStr">
         <is>
@@ -3663,13 +3602,13 @@
         </is>
       </c>
       <c r="B19" s="9" t="n">
-        <v>0.04635583499957009</v>
+        <v>0.04486693009301836</v>
       </c>
       <c r="C19" s="9" t="n">
-        <v>0.07886018916845154</v>
+        <v>0.07551752174309861</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v>0.05528848097541515</v>
+        <v>0.1079821501300804</v>
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
@@ -3700,7 +3639,7 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Terminal growth reconciliation: actual NOPAT compound growth FY2023–FY2025 was 30.5%; the implied growth from stable years only (FY2024 excluded as a debt-funded capacity burst) is 5.1%; the adopted terminal growth is 5.0%, below the blended nominal ceiling of 10.5%.</t>
+          <t>Terminal growth reconciliation: actual NOPAT compound growth FY2023–FY2025 was 26.9%; the implied growth from stable years only (FY2024 excluded as a debt-funded capacity burst) is 7.6%; the adopted terminal growth is 5.0%, below the blended nominal ceiling of 11.1%.</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3785,7 @@
       </c>
       <c r="C8" s="40" t="inlineStr">
         <is>
-          <t>the right frame for the roughly 27% that is turnkey project work</t>
+          <t>the right frame for the roughly 32% that is the Constructions and infrastructure segment</t>
         </is>
       </c>
       <c r="D8" s="40" t="inlineStr">
@@ -4009,14 +3948,14 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>35.37439268305282</v>
+        <v>21.43294146720748</v>
       </c>
       <c r="C5" s="8">
         <f>DCF!C31</f>
         <v/>
       </c>
       <c r="D5" s="7" t="n">
-        <v>110.3869768355961</v>
+        <v>125.1947652327141</v>
       </c>
       <c r="E5" s="9" t="n">
         <v>0.45</v>
@@ -4037,14 +3976,14 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>61.2294172643708</v>
+        <v>56.37443764397884</v>
       </c>
       <c r="C6" s="8">
         <f>'Relative &amp; Normalized'!C11</f>
         <v/>
       </c>
       <c r="D6" s="7" t="n">
-        <v>91.61541724668523</v>
+        <v>84.64625944108809</v>
       </c>
       <c r="E6" s="9" t="n">
         <v>0.2</v>
@@ -4065,14 +4004,14 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>94.04297714970363</v>
+        <v>92.75547847378519</v>
       </c>
       <c r="C7" s="8">
         <f>'Relative &amp; Normalized'!C28</f>
         <v/>
       </c>
       <c r="D7" s="7" t="n">
-        <v>154.4991767459417</v>
+        <v>152.38400034979</v>
       </c>
       <c r="E7" s="9" t="n">
         <v>0.2</v>
@@ -4093,14 +4032,14 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>33.76534925901321</v>
+        <v>32.0435151429293</v>
       </c>
       <c r="C8" s="8">
         <f>'Relative &amp; Normalized'!C36</f>
         <v/>
       </c>
       <c r="D8" s="7" t="n">
-        <v>53.71022096338332</v>
+        <v>50.97131575829435</v>
       </c>
       <c r="E8" s="9" t="n">
         <v>0.15</v>
@@ -4388,7 +4327,7 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>35.37439268305282</v>
+        <v>21.43294146720748</v>
       </c>
     </row>
     <row r="7">
@@ -4403,7 +4342,7 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>110.3869768355961</v>
+        <v>125.1947652327141</v>
       </c>
     </row>
     <row r="8">
@@ -4480,7 +4419,7 @@
         </is>
       </c>
       <c r="C15" s="9" t="n">
-        <v>0.600860789848202</v>
+        <v>0.5254856747391311</v>
       </c>
     </row>
     <row r="16">
@@ -4491,7 +4430,7 @@
       </c>
       <c r="C16" s="21" t="inlineStr">
         <is>
-          <t>26.9% → 15.1%</t>
+          <t>26.6% → 14.8%</t>
         </is>
       </c>
     </row>
@@ -4502,7 +4441,7 @@
         </is>
       </c>
       <c r="C17" s="9" t="n">
-        <v>0.10119375</v>
+        <v>0.101275</v>
       </c>
     </row>
     <row r="18">
@@ -4512,7 +4451,7 @@
         </is>
       </c>
       <c r="C18" s="7" t="n">
-        <v>91.14622861923802</v>
+        <v>78.89124097524397</v>
       </c>
     </row>
     <row r="19">
@@ -4572,13 +4511,13 @@
         </is>
       </c>
       <c r="C23" s="7" t="n">
-        <v>137.7034929664235</v>
+        <v>127.9603292598724</v>
       </c>
       <c r="D23" s="7" t="n">
-        <v>101.4657316594699</v>
+        <v>94.28655840201122</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>173.941254273377</v>
+        <v>161.6341001177335</v>
       </c>
     </row>
     <row r="24">
@@ -4593,13 +4532,13 @@
         </is>
       </c>
       <c r="C24" s="7" t="n">
-        <v>66.19078084024615</v>
+        <v>54.95725953296358</v>
       </c>
       <c r="D24" s="7" t="n">
-        <v>40.8187533998155</v>
+        <v>33.89122768954719</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>72.60004748131544</v>
+        <v>60.2787820431655</v>
       </c>
     </row>
     <row r="25">
@@ -4614,13 +4553,13 @@
         </is>
       </c>
       <c r="C25" s="7" t="n">
-        <v>60.72264310179215</v>
+        <v>54.07311304584361</v>
       </c>
       <c r="D25" s="7" t="n">
-        <v>49.99375810242254</v>
+        <v>45.06525322726745</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>91.14622861923802</v>
+        <v>78.89124097524397</v>
       </c>
     </row>
     <row r="26">
@@ -4648,7 +4587,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H67"/>
+  <dimension ref="A1:H60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -4755,7 +4694,7 @@
         </is>
       </c>
       <c r="C7" s="9" t="n">
-        <v>0.25</v>
+        <v>0.245</v>
       </c>
     </row>
     <row r="8">
@@ -4781,7 +4720,7 @@
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>Revenue drivers — the unit build</t>
+          <t>Revenue drivers — the three disclosed segments</t>
         </is>
       </c>
       <c r="B11" s="15" t="n"/>
@@ -4839,205 +4778,175 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Cable volume growth</t>
+          <t>Cables — real (volume) growth over copper x FX</t>
         </is>
       </c>
       <c r="B14" s="9" t="n">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="C14" s="9" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="D14" s="9" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="E14" s="9" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="F14" s="9" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>Cable fabrication uplift over copper</t>
-        </is>
-      </c>
-      <c r="B15" s="24" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="C15" s="24" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="D15" s="24" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="E15" s="24" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="F15" s="24" t="n">
-        <v>1.3</v>
+          <t>Constructions and infrastructure — revenue growth</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="C15" s="9" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="D15" s="9" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="E15" s="9" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="F15" s="9" t="n">
+        <v>0.08</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Raw-material volume growth</t>
+          <t>Electrical products and digital solutions — revenue growth</t>
         </is>
       </c>
       <c r="B16" s="9" t="n">
-        <v>0.04</v>
+        <v>0.2</v>
       </c>
       <c r="C16" s="9" t="n">
-        <v>0.04</v>
+        <v>0.16</v>
       </c>
       <c r="D16" s="9" t="n">
-        <v>0.03</v>
+        <v>0.13</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>0.03</v>
+        <v>0.11</v>
       </c>
       <c r="F16" s="9" t="n">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>Transformer MVA growth</t>
-        </is>
-      </c>
-      <c r="B17" s="9" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="C17" s="9" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="D17" s="9" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="E17" s="9" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="F17" s="9" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>Meter unit growth</t>
-        </is>
-      </c>
-      <c r="B18" s="9" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="C18" s="9" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="D18" s="9" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="E18" s="9" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="F18" s="9" t="n">
-        <v>0.04</v>
-      </c>
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>Segment gross margins and corporate cost load</t>
+        </is>
+      </c>
+      <c r="B18" s="15" t="n"/>
+      <c r="C18" s="15" t="n"/>
+      <c r="D18" s="15" t="n"/>
+      <c r="E18" s="15" t="n"/>
+      <c r="F18" s="15" t="n"/>
+      <c r="G18" s="15" t="n"/>
+      <c r="H18" s="15" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>Order-book conversion rate</t>
+          <t>Cables — gross/segment margin</t>
         </is>
       </c>
       <c r="B19" s="9" t="n">
-        <v>0.27</v>
+        <v>0.14</v>
       </c>
       <c r="C19" s="9" t="n">
-        <v>0.265</v>
+        <v>0.145</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v>0.26</v>
+        <v>0.15</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>0.255</v>
+        <v>0.153</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>0.25</v>
+        <v>0.155</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Order-book book-to-bill</t>
-        </is>
-      </c>
-      <c r="B20" s="24" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="C20" s="24" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="D20" s="24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="E20" s="24" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="F20" s="24" t="n">
-        <v>1</v>
+          <t>Constructions and infrastructure — segment margin</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="n">
+        <v>0.068</v>
+      </c>
+      <c r="C20" s="9" t="n">
+        <v>0.07199999999999999</v>
+      </c>
+      <c r="D20" s="9" t="n">
+        <v>0.076</v>
+      </c>
+      <c r="E20" s="9" t="n">
+        <v>0.079</v>
+      </c>
+      <c r="F20" s="9" t="n">
+        <v>0.082</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>Other-lines revenue growth</t>
+          <t>Electrical products and digital solutions — segment margin</t>
         </is>
       </c>
       <c r="B21" s="9" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="C21" s="9" t="n">
-        <v>0.11</v>
+        <v>0.222</v>
       </c>
       <c r="D21" s="9" t="n">
-        <v>0.1</v>
+        <v>0.224</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>0.09</v>
+        <v>0.226</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>0.08</v>
+        <v>0.228</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Meter price inflation</t>
+          <t>Corporate cost load (% of revenue) — the bridge from segment profit to EBIT</t>
         </is>
       </c>
       <c r="B22" s="9" t="n">
-        <v>0.08</v>
+        <v>0.033</v>
       </c>
       <c r="C22" s="9" t="n">
-        <v>0.075</v>
+        <v>0.034</v>
       </c>
       <c r="D22" s="9" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.035</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.035</v>
       </c>
       <c r="F22" s="9" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.036</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>Unit gross profit and cost load</t>
+          <t>Capital intensity</t>
         </is>
       </c>
       <c r="B24" s="15" t="n"/>
@@ -5051,466 +4960,366 @@
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>Gross profit per unit — growth</t>
-        </is>
-      </c>
-      <c r="B25" s="9" t="n">
-        <v>0.08500000000000001</v>
+          <t>Working capital / revenue</t>
+        </is>
       </c>
       <c r="C25" s="9" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="D25" s="9" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="E25" s="9" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="F25" s="9" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.199</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>Non-cable margin recovery factor</t>
-        </is>
-      </c>
-      <c r="B26" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="C26" s="24" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="D26" s="24" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="E26" s="24" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="F26" s="24" t="n">
-        <v>1.1</v>
+          <t>Capital expenditure / revenue</t>
+        </is>
+      </c>
+      <c r="B26" s="9" t="n">
+        <v>0.044</v>
+      </c>
+      <c r="C26" s="9" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="D26" s="9" t="n">
+        <v>0.036</v>
+      </c>
+      <c r="E26" s="9" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="F26" s="9" t="n">
+        <v>0.031</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>Operating load (% of revenue)</t>
-        </is>
-      </c>
-      <c r="B27" s="9" t="n">
-        <v>0.04</v>
+          <t>Depreciation and amortisation / revenue</t>
+        </is>
       </c>
       <c r="C27" s="9" t="n">
-        <v>0.043</v>
-      </c>
-      <c r="D27" s="9" t="n">
-        <v>0.046</v>
-      </c>
-      <c r="E27" s="9" t="n">
-        <v>0.048</v>
-      </c>
-      <c r="F27" s="9" t="n">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t>Cable gross profit per tonne, FY2025 (EGP)</t>
-        </is>
-      </c>
-      <c r="C28" s="22" t="n">
-        <v>88173</v>
+        <v>0.0125</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>Order book at FY2025 (EGP mn)</t>
-        </is>
-      </c>
-      <c r="C29" s="22" t="n">
-        <v>323700</v>
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>Cost of capital</t>
+        </is>
+      </c>
+      <c r="B29" s="15" t="n"/>
+      <c r="C29" s="15" t="n"/>
+      <c r="D29" s="15" t="n"/>
+      <c r="E29" s="15" t="n"/>
+      <c r="F29" s="15" t="n"/>
+      <c r="G29" s="15" t="n"/>
+      <c r="H29" s="15" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>Risk-free rate (10-year local currency)</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="n">
+        <v>0.2231</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="12" t="inlineStr">
-        <is>
-          <t>Capital intensity</t>
-        </is>
-      </c>
-      <c r="B31" s="15" t="n"/>
-      <c r="C31" s="15" t="n"/>
-      <c r="D31" s="15" t="n"/>
-      <c r="E31" s="15" t="n"/>
-      <c r="F31" s="15" t="n"/>
-      <c r="G31" s="15" t="n"/>
-      <c r="H31" s="15" t="n"/>
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>Sovereign default spread (netted out)</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="n">
+        <v>0.034</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>Working capital / revenue</t>
+          <t>Equity risk premium</t>
         </is>
       </c>
       <c r="C32" s="9" t="n">
-        <v>0.23</v>
+        <v>0.0941</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>Capital expenditure / revenue</t>
-        </is>
-      </c>
-      <c r="B33" s="9" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="C33" s="9" t="n">
-        <v>0.029</v>
-      </c>
-      <c r="D33" s="9" t="n">
-        <v>0.028</v>
-      </c>
-      <c r="E33" s="9" t="n">
-        <v>0.026</v>
-      </c>
-      <c r="F33" s="9" t="n">
-        <v>0.024</v>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="C33" s="24" t="n">
+        <v>1.009</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>Depreciation and amortisation / revenue</t>
+          <t>Cost of debt, blended</t>
         </is>
       </c>
       <c r="C34" s="9" t="n">
-        <v>0.0105</v>
+        <v>0.095</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>Cost of debt path</t>
+        </is>
+      </c>
+      <c r="B35" s="9" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="C35" s="9" t="n">
+        <v>0.089</v>
+      </c>
+      <c r="D35" s="9" t="n">
+        <v>0.08400000000000001</v>
+      </c>
+      <c r="E35" s="9" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="F35" s="9" t="n">
+        <v>0.077</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="12" t="inlineStr">
-        <is>
-          <t>Cost of capital</t>
-        </is>
-      </c>
-      <c r="B36" s="15" t="n"/>
-      <c r="C36" s="15" t="n"/>
-      <c r="D36" s="15" t="n"/>
-      <c r="E36" s="15" t="n"/>
-      <c r="F36" s="15" t="n"/>
-      <c r="G36" s="15" t="n"/>
-      <c r="H36" s="15" t="n"/>
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>Terminal risk-free rate</t>
+        </is>
+      </c>
+      <c r="C36" s="9" t="n">
+        <v>0.105</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>Risk-free rate (10-year local currency)</t>
+          <t>Terminal equity risk premium</t>
         </is>
       </c>
       <c r="C37" s="9" t="n">
-        <v>0.2231</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>Sovereign default spread (netted out)</t>
+          <t>Terminal cost of debt</t>
         </is>
       </c>
       <c r="C38" s="9" t="n">
-        <v>0.034</v>
+        <v>0.0888</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>Equity risk premium</t>
+          <t>Terminal debt weight</t>
         </is>
       </c>
       <c r="C39" s="9" t="n">
-        <v>0.0941</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>Beta</t>
-        </is>
-      </c>
-      <c r="C40" s="25" t="n">
-        <v>1.009</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="6" t="inlineStr">
-        <is>
-          <t>Cost of debt, blended</t>
-        </is>
-      </c>
-      <c r="C41" s="9" t="n">
-        <v>0.13</v>
+          <t>Terminal growth</t>
+        </is>
+      </c>
+      <c r="C40" s="9" t="n">
+        <v>0.05</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="6" t="inlineStr">
-        <is>
-          <t>Cost of debt path</t>
-        </is>
-      </c>
-      <c r="B42" s="9" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="C42" s="9" t="n">
-        <v>0.122</v>
-      </c>
-      <c r="D42" s="9" t="n">
-        <v>0.115</v>
-      </c>
-      <c r="E42" s="9" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="F42" s="9" t="n">
-        <v>0.106</v>
-      </c>
+      <c r="A42" s="12" t="inlineStr">
+        <is>
+          <t>Balance-sheet and bridge anchors</t>
+        </is>
+      </c>
+      <c r="B42" s="15" t="n"/>
+      <c r="C42" s="15" t="n"/>
+      <c r="D42" s="15" t="n"/>
+      <c r="E42" s="15" t="n"/>
+      <c r="F42" s="15" t="n"/>
+      <c r="G42" s="15" t="n"/>
+      <c r="H42" s="15" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>Terminal risk-free rate</t>
-        </is>
-      </c>
-      <c r="C43" s="9" t="n">
-        <v>0.105</v>
+          <t>Net bank debt at FY2025 (EGP mn, disclosed)</t>
+        </is>
+      </c>
+      <c r="C43" s="22" t="n">
+        <v>20560.003173</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>Terminal equity risk premium</t>
-        </is>
-      </c>
-      <c r="C44" s="9" t="n">
-        <v>0.07000000000000001</v>
+          <t>Equity-accounted investees at carrying value (EGP mn)</t>
+        </is>
+      </c>
+      <c r="C44" s="22" t="n">
+        <v>6757.650507</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>Terminal cost of debt</t>
-        </is>
-      </c>
-      <c r="C45" s="9" t="n">
-        <v>0.105</v>
+          <t>Intangible assets and goodwill (EGP mn)</t>
+        </is>
+      </c>
+      <c r="C45" s="22" t="n">
+        <v>1748.816945</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>Terminal debt weight</t>
-        </is>
-      </c>
-      <c r="C46" s="9" t="n">
-        <v>0.25</v>
+          <t>FY2025 profit after tax (EGP mn, disclosed)</t>
+        </is>
+      </c>
+      <c r="C46" s="22" t="n">
+        <v>19186.550057</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>Terminal growth</t>
-        </is>
-      </c>
-      <c r="C47" s="9" t="n">
-        <v>0.05</v>
+          <t>FY2025 profit after minority interests (EGP mn, disclosed)</t>
+        </is>
+      </c>
+      <c r="C47" s="22" t="n">
+        <v>17330.24499</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>FY2024 dividend per share (EGP)</t>
+        </is>
+      </c>
+      <c r="C48" s="7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="12" t="inlineStr">
-        <is>
-          <t>Balance-sheet and bridge anchors</t>
-        </is>
-      </c>
-      <c r="B49" s="15" t="n"/>
-      <c r="C49" s="15" t="n"/>
-      <c r="D49" s="15" t="n"/>
-      <c r="E49" s="15" t="n"/>
-      <c r="F49" s="15" t="n"/>
-      <c r="G49" s="15" t="n"/>
-      <c r="H49" s="15" t="n"/>
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>Forecast dividend payout ratio</t>
+        </is>
+      </c>
+      <c r="C49" s="9" t="n">
+        <v>0.15</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>Net bank debt at FY2025 (EGP mn, disclosed)</t>
-        </is>
-      </c>
-      <c r="C50" s="22" t="n">
-        <v>19789</v>
+          <t>Growth in the share of equity-accounted investees</t>
+        </is>
+      </c>
+      <c r="C50" s="9" t="n">
+        <v>0.08</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>Equity-accounted investees at carrying value (EGP mn)</t>
-        </is>
-      </c>
-      <c r="C51" s="22" t="n">
-        <v>6474</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="6" t="inlineStr">
-        <is>
-          <t>Intangible assets and goodwill (EGP mn)</t>
-        </is>
-      </c>
-      <c r="C52" s="22" t="n">
-        <v>1459.2</v>
+          <t>Yield assumed on surplus cash</t>
+        </is>
+      </c>
+      <c r="C51" s="9" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="6" t="inlineStr">
-        <is>
-          <t>FY2025 profit after tax (EGP mn, disclosed)</t>
-        </is>
-      </c>
-      <c r="C53" s="22" t="n">
-        <v>19180</v>
-      </c>
+      <c r="A53" s="12" t="inlineStr">
+        <is>
+          <t>Lens inputs</t>
+        </is>
+      </c>
+      <c r="B53" s="15" t="n"/>
+      <c r="C53" s="15" t="n"/>
+      <c r="D53" s="15" t="n"/>
+      <c r="E53" s="15" t="n"/>
+      <c r="F53" s="15" t="n"/>
+      <c r="G53" s="15" t="n"/>
+      <c r="H53" s="15" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
         <is>
-          <t>FY2025 profit after minority interests (EGP mn, disclosed)</t>
-        </is>
-      </c>
-      <c r="C54" s="22" t="n">
-        <v>17330</v>
+          <t>Justified EV/EBITDA</t>
+        </is>
+      </c>
+      <c r="C54" s="25" t="n">
+        <v>6.5</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="6" t="inlineStr">
         <is>
-          <t>FY2024 dividend per share (EGP)</t>
-        </is>
-      </c>
-      <c r="C55" s="7" t="n">
-        <v>1</v>
+          <t>Justified price/earnings</t>
+        </is>
+      </c>
+      <c r="C55" s="25" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
         <is>
-          <t>Forecast dividend payout ratio</t>
+          <t>Sustainable return on equity</t>
         </is>
       </c>
       <c r="C56" s="9" t="n">
-        <v>0.25</v>
+        <v>0.235</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="6" t="inlineStr">
         <is>
-          <t>Growth in the share of equity-accounted investees</t>
+          <t>Weight — discounted cash flow</t>
         </is>
       </c>
       <c r="C57" s="9" t="n">
-        <v>0.08</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
         <is>
-          <t>Yield assumed on surplus cash</t>
+          <t>Weight — relative</t>
         </is>
       </c>
       <c r="C58" s="9" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>Weight — normalised</t>
+        </is>
+      </c>
+      <c r="C59" s="9" t="n">
+        <v>0.2</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="12" t="inlineStr">
-        <is>
-          <t>Lens inputs</t>
-        </is>
-      </c>
-      <c r="B60" s="15" t="n"/>
-      <c r="C60" s="15" t="n"/>
-      <c r="D60" s="15" t="n"/>
-      <c r="E60" s="15" t="n"/>
-      <c r="F60" s="15" t="n"/>
-      <c r="G60" s="15" t="n"/>
-      <c r="H60" s="15" t="n"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="6" t="inlineStr">
-        <is>
-          <t>Justified EV/EBITDA</t>
-        </is>
-      </c>
-      <c r="C61" s="24" t="n">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="6" t="inlineStr">
-        <is>
-          <t>Justified price/earnings</t>
-        </is>
-      </c>
-      <c r="C62" s="24" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="6" t="inlineStr">
-        <is>
-          <t>Sustainable return on equity</t>
-        </is>
-      </c>
-      <c r="C63" s="9" t="n">
-        <v>0.235</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="6" t="inlineStr">
-        <is>
-          <t>Weight — discounted cash flow</t>
-        </is>
-      </c>
-      <c r="C64" s="9" t="n">
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="6" t="inlineStr">
-        <is>
-          <t>Weight — relative</t>
-        </is>
-      </c>
-      <c r="C65" s="9" t="n">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="6" t="inlineStr">
-        <is>
-          <t>Weight — normalised</t>
-        </is>
-      </c>
-      <c r="C66" s="9" t="n">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="6" t="inlineStr">
+      <c r="A60" s="6" t="inlineStr">
         <is>
           <t>Weight — book</t>
         </is>
       </c>
-      <c r="C67" s="9" t="n">
+      <c r="C60" s="9" t="n">
         <v>0.15</v>
       </c>
     </row>
@@ -5615,7 +5424,7 @@
         </is>
       </c>
       <c r="C8" s="18">
-        <f>-Assumptions!$C$50</f>
+        <f>-Assumptions!$C$43</f>
         <v/>
       </c>
       <c r="D8" s="10">
@@ -5630,7 +5439,7 @@
         </is>
       </c>
       <c r="C9" s="18">
-        <f>Assumptions!$C$51</f>
+        <f>Assumptions!$C$44</f>
         <v/>
       </c>
       <c r="D9" s="10">
@@ -5702,7 +5511,7 @@
         </is>
       </c>
       <c r="C15" s="11">
-        <f>(Assumptions!$C$53-Assumptions!$C$54)/Assumptions!$C$53</f>
+        <f>(Assumptions!$C$46-Assumptions!$C$47)/Assumptions!$C$46</f>
         <v/>
       </c>
     </row>
@@ -5717,7 +5526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I34"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5803,775 +5612,451 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Cables</t>
+          <t>Cables and its accessories</t>
         </is>
       </c>
       <c r="B5" s="22" t="n">
-        <v>92138.29685490194</v>
+        <v>155792.929738</v>
       </c>
       <c r="C5" s="11">
-        <f>B5/$B$12</f>
+        <f>B5/$B$8</f>
         <v/>
       </c>
       <c r="D5" s="9" t="n">
-        <v>0.1479665487953016</v>
+        <v>0.134899552356732</v>
       </c>
       <c r="E5" s="22" t="n">
-        <v>145610.3678770696</v>
+        <v>221541.3228857327</v>
       </c>
       <c r="F5" s="22" t="n">
-        <v>169133.0260767016</v>
+        <v>252428.7347156312</v>
       </c>
       <c r="G5" s="22" t="n">
-        <v>187299.1659145696</v>
+        <v>276853.5521024677</v>
       </c>
       <c r="H5" s="22" t="n">
-        <v>206647.9840977443</v>
+        <v>302516.6726712704</v>
       </c>
       <c r="I5" s="22" t="n">
-        <v>227245.0290701096</v>
+        <v>329470.412277309</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Raw material (copper rod)</t>
+          <t>Constructions and infrastructure</t>
         </is>
       </c>
       <c r="B6" s="22" t="n">
-        <v>60448.00314509805</v>
+        <v>90958.55022799999</v>
       </c>
       <c r="C6" s="11">
-        <f>B6/$B$12</f>
+        <f>B6/$B$8</f>
         <v/>
       </c>
       <c r="D6" s="9" t="n">
-        <v>0.1239697053155375</v>
+        <v>0.06452269254829619</v>
       </c>
       <c r="E6" s="22" t="n">
-        <v>86793.07467340285</v>
+        <v>107331.08926904</v>
       </c>
       <c r="F6" s="22" t="n">
-        <v>99853.94648992721</v>
+        <v>122357.4417667056</v>
       </c>
       <c r="G6" s="22" t="n">
-        <v>109515.7403864063</v>
+        <v>135816.7603610432</v>
       </c>
       <c r="H6" s="22" t="n">
-        <v>119667.3733648332</v>
+        <v>148040.2687935371</v>
       </c>
       <c r="I6" s="22" t="n">
-        <v>130329.5401556179</v>
+        <v>159883.4902970201</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>Engineering &amp; construction</t>
+          <t>Electrical products and digital solutions</t>
         </is>
       </c>
       <c r="B7" s="22" t="n">
-        <v>87100.7</v>
+        <v>34297.601753</v>
       </c>
       <c r="C7" s="11">
-        <f>B7/$B$12</f>
+        <f>B7/$B$8</f>
         <v/>
       </c>
       <c r="D7" s="9" t="n">
-        <v>0.08991421158660849</v>
+        <v>0.2217300370961013</v>
       </c>
       <c r="E7" s="22" t="n">
-        <v>87399</v>
+        <v>41157.1221036</v>
       </c>
       <c r="F7" s="22" t="n">
-        <v>86938.53675000001</v>
+        <v>47742.261640176</v>
       </c>
       <c r="G7" s="22" t="n">
-        <v>86428.38797775001</v>
+        <v>53948.75565339887</v>
       </c>
       <c r="H7" s="22" t="n">
-        <v>85427.48076159229</v>
+        <v>59883.11877527275</v>
       </c>
       <c r="I7" s="22" t="n">
-        <v>84179.56952301609</v>
+        <v>65871.43065280003</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>Transformers</t>
-        </is>
-      </c>
-      <c r="B8" s="22" t="n">
-        <v>17703.5</v>
-      </c>
-      <c r="C8" s="11">
-        <f>B8/$B$12</f>
-        <v/>
-      </c>
-      <c r="D8" s="9" t="n">
-        <v>0.2769882639821222</v>
-      </c>
-      <c r="E8" s="22" t="n">
-        <v>20025.95817760357</v>
-      </c>
-      <c r="F8" s="22" t="n">
-        <v>23704.12363041715</v>
-      </c>
-      <c r="G8" s="22" t="n">
-        <v>26754.93213470232</v>
-      </c>
-      <c r="H8" s="22" t="n">
-        <v>29802.66788222058</v>
-      </c>
-      <c r="I8" s="22" t="n">
-        <v>33088.28987415392</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>Meters &amp; digital</t>
-        </is>
-      </c>
-      <c r="B9" s="22" t="n">
-        <v>16594.1</v>
-      </c>
-      <c r="C9" s="11">
-        <f>B9/$B$12</f>
-        <v/>
-      </c>
-      <c r="D9" s="9" t="n">
-        <v>0.2190169964043364</v>
-      </c>
-      <c r="E9" s="22" t="n">
-        <v>17815.54107615941</v>
-      </c>
-      <c r="F9" s="22" t="n">
-        <v>20109.29198971493</v>
-      </c>
-      <c r="G9" s="22" t="n">
-        <v>22592.78955044473</v>
-      </c>
-      <c r="H9" s="22" t="n">
-        <v>25141.25621173489</v>
-      </c>
-      <c r="I9" s="22" t="n">
-        <v>27977.18991241859</v>
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>Total revenue</t>
+        </is>
+      </c>
+      <c r="B8" s="31">
+        <f>SUM(B5:B7)</f>
+        <v/>
+      </c>
+      <c r="C8" s="14">
+        <f>SUM(C5:C7)</f>
+        <v/>
+      </c>
+      <c r="D8" s="15" t="n"/>
+      <c r="E8" s="31">
+        <f>SUM(E5:E7)</f>
+        <v/>
+      </c>
+      <c r="F8" s="31">
+        <f>SUM(F5:F7)</f>
+        <v/>
+      </c>
+      <c r="G8" s="31">
+        <f>SUM(G5:G7)</f>
+        <v/>
+      </c>
+      <c r="H8" s="31">
+        <f>SUM(H5:H7)</f>
+        <v/>
+      </c>
+      <c r="I8" s="31">
+        <f>SUM(I5:I7)</f>
+        <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>Other electrical products</t>
-        </is>
-      </c>
-      <c r="B10" s="22" t="n">
-        <v>3206.5</v>
-      </c>
-      <c r="C10" s="11">
-        <f>B10/$B$12</f>
-        <v/>
-      </c>
-      <c r="D10" s="9" t="n">
-        <v>0.4076827342682428</v>
-      </c>
-      <c r="E10" s="22" t="n">
-        <v>3591.28</v>
-      </c>
-      <c r="F10" s="22" t="n">
-        <v>3986.3208</v>
-      </c>
-      <c r="G10" s="22" t="n">
-        <v>4384.952880000001</v>
-      </c>
-      <c r="H10" s="22" t="n">
-        <v>4779.598639200001</v>
-      </c>
-      <c r="I10" s="22" t="n">
-        <v>5161.966530336002</v>
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Gross profit by segment</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>FY26E</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>FY27E</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>FY28E</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>FY29E</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>FY30E</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Infrastructure investment</t>
+          <t>Cables and its accessories</t>
         </is>
       </c>
       <c r="B11" s="22" t="n">
-        <v>3857.9</v>
-      </c>
-      <c r="C11" s="11">
-        <f>B11/$B$12</f>
-        <v/>
-      </c>
-      <c r="D11" s="9" t="n">
-        <v>0.4966473826898447</v>
+        <v>31015.78520400258</v>
+      </c>
+      <c r="C11" s="22" t="n">
+        <v>36602.16653376652</v>
+      </c>
+      <c r="D11" s="22" t="n">
+        <v>41528.03281537016</v>
       </c>
       <c r="E11" s="22" t="n">
-        <v>4320.848000000001</v>
+        <v>46285.05091870438</v>
       </c>
       <c r="F11" s="22" t="n">
-        <v>4796.141280000002</v>
-      </c>
-      <c r="G11" s="22" t="n">
-        <v>5275.755408000002</v>
-      </c>
-      <c r="H11" s="22" t="n">
-        <v>5750.573394720002</v>
-      </c>
-      <c r="I11" s="22" t="n">
-        <v>6210.619266297603</v>
+        <v>51067.91390298289</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="12" t="inlineStr">
-        <is>
-          <t>Total revenue</t>
-        </is>
-      </c>
-      <c r="B12" s="31">
-        <f>SUM(B5:B11)</f>
-        <v/>
-      </c>
-      <c r="C12" s="14">
-        <f>SUM(C5:C11)</f>
-        <v/>
-      </c>
-      <c r="D12" s="15" t="n"/>
-      <c r="E12" s="31">
-        <f>SUM(E5:E11)</f>
-        <v/>
-      </c>
-      <c r="F12" s="31">
-        <f>SUM(F5:F11)</f>
-        <v/>
-      </c>
-      <c r="G12" s="31">
-        <f>SUM(G5:G11)</f>
-        <v/>
-      </c>
-      <c r="H12" s="31">
-        <f>SUM(H5:H11)</f>
-        <v/>
-      </c>
-      <c r="I12" s="31">
-        <f>SUM(I5:I11)</f>
-        <v/>
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Constructions and infrastructure</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="n">
+        <v>7298.51407029472</v>
+      </c>
+      <c r="C12" s="22" t="n">
+        <v>8809.735807202804</v>
+      </c>
+      <c r="D12" s="22" t="n">
+        <v>10322.07378743929</v>
+      </c>
+      <c r="E12" s="22" t="n">
+        <v>11695.18123468943</v>
+      </c>
+      <c r="F12" s="22" t="n">
+        <v>13110.44620435565</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Electrical products and digital solutions</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="n">
+        <v>9054.566862792</v>
+      </c>
+      <c r="C13" s="22" t="n">
+        <v>10598.78208411907</v>
+      </c>
+      <c r="D13" s="22" t="n">
+        <v>12084.52126636135</v>
+      </c>
+      <c r="E13" s="22" t="n">
+        <v>13533.58484321164</v>
+      </c>
+      <c r="F13" s="22" t="n">
+        <v>15018.68618883841</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>Gross profit by segment</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>FY26E</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>FY27E</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>FY28E</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>FY29E</t>
-        </is>
-      </c>
-      <c r="F14" s="5" t="inlineStr">
-        <is>
-          <t>FY30E</t>
-        </is>
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>Group gross profit</t>
+        </is>
+      </c>
+      <c r="B14" s="31">
+        <f>SUM(B11:B13)</f>
+        <v/>
+      </c>
+      <c r="C14" s="31">
+        <f>SUM(C11:C13)</f>
+        <v/>
+      </c>
+      <c r="D14" s="31">
+        <f>SUM(D11:D13)</f>
+        <v/>
+      </c>
+      <c r="E14" s="31">
+        <f>SUM(E11:E13)</f>
+        <v/>
+      </c>
+      <c r="F14" s="31">
+        <f>SUM(F11:F13)</f>
+        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>Cables</t>
-        </is>
-      </c>
-      <c r="B15" s="22" t="n">
-        <v>25866.09381390937</v>
-      </c>
-      <c r="C15" s="22" t="n">
-        <v>29332.15038497323</v>
-      </c>
-      <c r="D15" s="22" t="n">
-        <v>32793.34413040007</v>
-      </c>
-      <c r="E15" s="22" t="n">
-        <v>36492.43334830921</v>
-      </c>
-      <c r="F15" s="22" t="n">
-        <v>40608.77982999848</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>Raw material (copper rod)</t>
-        </is>
-      </c>
-      <c r="B16" s="22" t="n">
-        <v>8455.914930776953</v>
-      </c>
-      <c r="C16" s="22" t="n">
-        <v>9497.683650248677</v>
-      </c>
-      <c r="D16" s="22" t="n">
-        <v>10516.31022173785</v>
-      </c>
-      <c r="E16" s="22" t="n">
-        <v>11590.02549537728</v>
-      </c>
-      <c r="F16" s="22" t="n">
-        <v>12773.3670984553</v>
+          <t>Group gross margin</t>
+        </is>
+      </c>
+      <c r="B15" s="11">
+        <f>B14/E$8</f>
+        <v/>
+      </c>
+      <c r="C15" s="11">
+        <f>C14/F$8</f>
+        <v/>
+      </c>
+      <c r="D15" s="11">
+        <f>D14/G$8</f>
+        <v/>
+      </c>
+      <c r="E15" s="11">
+        <f>E14/H$8</f>
+        <v/>
+      </c>
+      <c r="F15" s="11">
+        <f>F14/I$8</f>
+        <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>Engineering &amp; construction</t>
-        </is>
-      </c>
-      <c r="B17" s="22" t="n">
-        <v>7858.412178457996</v>
-      </c>
-      <c r="C17" s="22" t="n">
-        <v>8129.690387904425</v>
-      </c>
-      <c r="D17" s="22" t="n">
-        <v>8315.120189181367</v>
-      </c>
-      <c r="E17" s="22" t="n">
-        <v>8372.447592754523</v>
-      </c>
-      <c r="F17" s="22" t="n">
-        <v>8325.833587898298</v>
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Segment EBITDA — gross profit less the operating load</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>FY26E</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>FY27E</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>FY28E</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>FY29E</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>FY30E</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Transformers</t>
-        </is>
-      </c>
-      <c r="B18" s="22" t="n">
-        <v>5746.110816863308</v>
-      </c>
-      <c r="C18" s="22" t="n">
-        <v>6640.205659967241</v>
-      </c>
-      <c r="D18" s="22" t="n">
-        <v>7566.514349532672</v>
-      </c>
-      <c r="E18" s="22" t="n">
-        <v>8500.978871699957</v>
-      </c>
-      <c r="F18" s="22" t="n">
-        <v>9550.849762354903</v>
+          <t>Cables and its accessories</t>
+        </is>
+      </c>
+      <c r="B18" s="28">
+        <f>B11-Assumptions!$B$22*E5</f>
+        <v/>
+      </c>
+      <c r="C18" s="28">
+        <f>C11-Assumptions!$C$22*F5</f>
+        <v/>
+      </c>
+      <c r="D18" s="28">
+        <f>D11-Assumptions!$D$22*G5</f>
+        <v/>
+      </c>
+      <c r="E18" s="28">
+        <f>E11-Assumptions!$E$22*H5</f>
+        <v/>
+      </c>
+      <c r="F18" s="28">
+        <f>F11-Assumptions!$F$22*I5</f>
+        <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>Meters &amp; digital</t>
-        </is>
-      </c>
-      <c r="B19" s="22" t="n">
-        <v>4179.911870032181</v>
-      </c>
-      <c r="C19" s="22" t="n">
-        <v>4740.020060616494</v>
-      </c>
-      <c r="D19" s="22" t="n">
-        <v>5350.297643420868</v>
-      </c>
-      <c r="E19" s="22" t="n">
-        <v>5953.811217598743</v>
-      </c>
-      <c r="F19" s="22" t="n">
-        <v>6625.401122943882</v>
+          <t>Constructions and infrastructure</t>
+        </is>
+      </c>
+      <c r="B19" s="28">
+        <f>B12-Assumptions!$B$22*E6</f>
+        <v/>
+      </c>
+      <c r="C19" s="28">
+        <f>C12-Assumptions!$C$22*F6</f>
+        <v/>
+      </c>
+      <c r="D19" s="28">
+        <f>D12-Assumptions!$D$22*G6</f>
+        <v/>
+      </c>
+      <c r="E19" s="28">
+        <f>E12-Assumptions!$E$22*H6</f>
+        <v/>
+      </c>
+      <c r="F19" s="28">
+        <f>F12-Assumptions!$F$22*I6</f>
+        <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Other electrical products</t>
-        </is>
-      </c>
-      <c r="B20" s="22" t="n">
-        <v>1464.102849922855</v>
-      </c>
-      <c r="C20" s="22" t="n">
-        <v>1690.160329950944</v>
-      </c>
-      <c r="D20" s="22" t="n">
-        <v>1912.806450338713</v>
-      </c>
-      <c r="E20" s="22" t="n">
-        <v>2123.930227707874</v>
-      </c>
-      <c r="F20" s="22" t="n">
-        <v>2314.889092217389</v>
+          <t>Electrical products and digital solutions</t>
+        </is>
+      </c>
+      <c r="B20" s="28">
+        <f>B13-Assumptions!$B$22*E7</f>
+        <v/>
+      </c>
+      <c r="C20" s="28">
+        <f>C13-Assumptions!$C$22*F7</f>
+        <v/>
+      </c>
+      <c r="D20" s="28">
+        <f>D13-Assumptions!$D$22*G7</f>
+        <v/>
+      </c>
+      <c r="E20" s="28">
+        <f>E13-Assumptions!$E$22*H7</f>
+        <v/>
+      </c>
+      <c r="F20" s="28">
+        <f>F13-Assumptions!$F$22*I7</f>
+        <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>Infrastructure investment</t>
-        </is>
-      </c>
-      <c r="B21" s="22" t="n">
-        <v>2145.937850200651</v>
-      </c>
-      <c r="C21" s="22" t="n">
-        <v>2477.270654271631</v>
-      </c>
-      <c r="D21" s="22" t="n">
-        <v>2803.603423151645</v>
-      </c>
-      <c r="E21" s="22" t="n">
-        <v>3113.047875744363</v>
-      </c>
-      <c r="F21" s="22" t="n">
-        <v>3392.936583838811</v>
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>Group EBITDA</t>
+        </is>
+      </c>
+      <c r="B21" s="31">
+        <f>SUM(B18:B20)</f>
+        <v/>
+      </c>
+      <c r="C21" s="31">
+        <f>SUM(C18:C20)</f>
+        <v/>
+      </c>
+      <c r="D21" s="31">
+        <f>SUM(D18:D20)</f>
+        <v/>
+      </c>
+      <c r="E21" s="31">
+        <f>SUM(E18:E20)</f>
+        <v/>
+      </c>
+      <c r="F21" s="31">
+        <f>SUM(F18:F20)</f>
+        <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="12" t="inlineStr">
-        <is>
-          <t>Group gross profit</t>
-        </is>
-      </c>
-      <c r="B22" s="31">
-        <f>SUM(B15:B21)</f>
-        <v/>
-      </c>
-      <c r="C22" s="31">
-        <f>SUM(C15:C21)</f>
-        <v/>
-      </c>
-      <c r="D22" s="31">
-        <f>SUM(D15:D21)</f>
-        <v/>
-      </c>
-      <c r="E22" s="31">
-        <f>SUM(E15:E21)</f>
-        <v/>
-      </c>
-      <c r="F22" s="31">
-        <f>SUM(F15:F21)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>Group gross margin</t>
-        </is>
-      </c>
-      <c r="B23" s="11">
-        <f>B22/E$12</f>
-        <v/>
-      </c>
-      <c r="C23" s="11">
-        <f>C22/F$12</f>
-        <v/>
-      </c>
-      <c r="D23" s="11">
-        <f>D22/G$12</f>
-        <v/>
-      </c>
-      <c r="E23" s="11">
-        <f>E22/H$12</f>
-        <v/>
-      </c>
-      <c r="F23" s="11">
-        <f>F22/I$12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>Segment EBITDA — gross profit less the operating load</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>FY26E</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>FY27E</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>FY28E</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>FY29E</t>
-        </is>
-      </c>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>FY30E</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t>Cables</t>
-        </is>
-      </c>
-      <c r="B26" s="28">
-        <f>B15-Assumptions!$B$27*E5</f>
-        <v/>
-      </c>
-      <c r="C26" s="28">
-        <f>C15-Assumptions!$C$27*F5</f>
-        <v/>
-      </c>
-      <c r="D26" s="28">
-        <f>D15-Assumptions!$D$27*G5</f>
-        <v/>
-      </c>
-      <c r="E26" s="28">
-        <f>E15-Assumptions!$E$27*H5</f>
-        <v/>
-      </c>
-      <c r="F26" s="28">
-        <f>F15-Assumptions!$F$27*I5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>Raw material (copper rod)</t>
-        </is>
-      </c>
-      <c r="B27" s="28">
-        <f>B16-Assumptions!$B$27*E6</f>
-        <v/>
-      </c>
-      <c r="C27" s="28">
-        <f>C16-Assumptions!$C$27*F6</f>
-        <v/>
-      </c>
-      <c r="D27" s="28">
-        <f>D16-Assumptions!$D$27*G6</f>
-        <v/>
-      </c>
-      <c r="E27" s="28">
-        <f>E16-Assumptions!$E$27*H6</f>
-        <v/>
-      </c>
-      <c r="F27" s="28">
-        <f>F16-Assumptions!$F$27*I6</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t>Engineering &amp; construction</t>
-        </is>
-      </c>
-      <c r="B28" s="28">
-        <f>B17-Assumptions!$B$27*E7</f>
-        <v/>
-      </c>
-      <c r="C28" s="28">
-        <f>C17-Assumptions!$C$27*F7</f>
-        <v/>
-      </c>
-      <c r="D28" s="28">
-        <f>D17-Assumptions!$D$27*G7</f>
-        <v/>
-      </c>
-      <c r="E28" s="28">
-        <f>E17-Assumptions!$E$27*H7</f>
-        <v/>
-      </c>
-      <c r="F28" s="28">
-        <f>F17-Assumptions!$F$27*I7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>Transformers</t>
-        </is>
-      </c>
-      <c r="B29" s="28">
-        <f>B18-Assumptions!$B$27*E8</f>
-        <v/>
-      </c>
-      <c r="C29" s="28">
-        <f>C18-Assumptions!$C$27*F8</f>
-        <v/>
-      </c>
-      <c r="D29" s="28">
-        <f>D18-Assumptions!$D$27*G8</f>
-        <v/>
-      </c>
-      <c r="E29" s="28">
-        <f>E18-Assumptions!$E$27*H8</f>
-        <v/>
-      </c>
-      <c r="F29" s="28">
-        <f>F18-Assumptions!$F$27*I8</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="6" t="inlineStr">
-        <is>
-          <t>Meters &amp; digital</t>
-        </is>
-      </c>
-      <c r="B30" s="28">
-        <f>B19-Assumptions!$B$27*E9</f>
-        <v/>
-      </c>
-      <c r="C30" s="28">
-        <f>C19-Assumptions!$C$27*F9</f>
-        <v/>
-      </c>
-      <c r="D30" s="28">
-        <f>D19-Assumptions!$D$27*G9</f>
-        <v/>
-      </c>
-      <c r="E30" s="28">
-        <f>E19-Assumptions!$E$27*H9</f>
-        <v/>
-      </c>
-      <c r="F30" s="28">
-        <f>F19-Assumptions!$F$27*I9</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="6" t="inlineStr">
-        <is>
-          <t>Other electrical products</t>
-        </is>
-      </c>
-      <c r="B31" s="28">
-        <f>B20-Assumptions!$B$27*E10</f>
-        <v/>
-      </c>
-      <c r="C31" s="28">
-        <f>C20-Assumptions!$C$27*F10</f>
-        <v/>
-      </c>
-      <c r="D31" s="28">
-        <f>D20-Assumptions!$D$27*G10</f>
-        <v/>
-      </c>
-      <c r="E31" s="28">
-        <f>E20-Assumptions!$E$27*H10</f>
-        <v/>
-      </c>
-      <c r="F31" s="28">
-        <f>F20-Assumptions!$F$27*I10</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t>Infrastructure investment</t>
-        </is>
-      </c>
-      <c r="B32" s="28">
-        <f>B21-Assumptions!$B$27*E11</f>
-        <v/>
-      </c>
-      <c r="C32" s="28">
-        <f>C21-Assumptions!$C$27*F11</f>
-        <v/>
-      </c>
-      <c r="D32" s="28">
-        <f>D21-Assumptions!$D$27*G11</f>
-        <v/>
-      </c>
-      <c r="E32" s="28">
-        <f>E21-Assumptions!$E$27*H11</f>
-        <v/>
-      </c>
-      <c r="F32" s="28">
-        <f>F21-Assumptions!$F$27*I11</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="12" t="inlineStr">
-        <is>
-          <t>Group EBITDA</t>
-        </is>
-      </c>
-      <c r="B33" s="31">
-        <f>SUM(B26:B32)</f>
-        <v/>
-      </c>
-      <c r="C33" s="31">
-        <f>SUM(C26:C32)</f>
-        <v/>
-      </c>
-      <c r="D33" s="31">
-        <f>SUM(D26:D32)</f>
-        <v/>
-      </c>
-      <c r="E33" s="31">
-        <f>SUM(E26:E32)</f>
-        <v/>
-      </c>
-      <c r="F33" s="31">
-        <f>SUM(F26:F32)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="6" t="inlineStr">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>Group EBITDA margin</t>
         </is>
       </c>
-      <c r="B34" s="11">
-        <f>B33/E$12</f>
-        <v/>
-      </c>
-      <c r="C34" s="11">
-        <f>C33/F$12</f>
-        <v/>
-      </c>
-      <c r="D34" s="11">
-        <f>D33/G$12</f>
-        <v/>
-      </c>
-      <c r="E34" s="11">
-        <f>E33/H$12</f>
-        <v/>
-      </c>
-      <c r="F34" s="11">
-        <f>F33/I$12</f>
+      <c r="B22" s="11">
+        <f>B21/E$8</f>
+        <v/>
+      </c>
+      <c r="C22" s="11">
+        <f>C21/F$8</f>
+        <v/>
+      </c>
+      <c r="D22" s="11">
+        <f>D21/G$8</f>
+        <v/>
+      </c>
+      <c r="E22" s="11">
+        <f>E21/H$8</f>
+        <v/>
+      </c>
+      <c r="F22" s="11">
+        <f>F21/I$8</f>
         <v/>
       </c>
     </row>
@@ -6637,7 +6122,7 @@
         </is>
       </c>
       <c r="C6" s="32">
-        <f>Assumptions!$C$61</f>
+        <f>Assumptions!$C$54</f>
         <v/>
       </c>
     </row>
@@ -6681,7 +6166,7 @@
         </is>
       </c>
       <c r="C10" s="28">
-        <f>-Assumptions!$C$50+Assumptions!$C$51</f>
+        <f>-Assumptions!$C$43+Assumptions!$C$44</f>
         <v/>
       </c>
     </row>
@@ -6704,7 +6189,7 @@
         </is>
       </c>
       <c r="C13" s="34">
-        <f>((Assumptions!$C$5*Assumptions!$C$6)+Assumptions!$C$50)/'Income Statement'!D7</f>
+        <f>((Assumptions!$C$5*Assumptions!$C$6)+Assumptions!$C$43)/'Income Statement'!D7</f>
         <v/>
       </c>
     </row>
@@ -6737,7 +6222,7 @@
         </is>
       </c>
       <c r="C16" s="34">
-        <f>Assumptions!$C$50/'Income Statement'!D7</f>
+        <f>Assumptions!$C$43/'Income Statement'!D7</f>
         <v/>
       </c>
     </row>
@@ -6793,7 +6278,7 @@
         </is>
       </c>
       <c r="C22" s="28">
-        <f>C21-C19*Assumptions!$C$34</f>
+        <f>C21-C19*Assumptions!$C$27</f>
         <v/>
       </c>
     </row>
@@ -6848,7 +6333,7 @@
         </is>
       </c>
       <c r="C27" s="34">
-        <f>Assumptions!$C$62</f>
+        <f>Assumptions!$C$55</f>
         <v/>
       </c>
     </row>
@@ -6894,7 +6379,7 @@
         </is>
       </c>
       <c r="C32" s="11">
-        <f>Assumptions!$C$63</f>
+        <f>Assumptions!$C$56</f>
         <v/>
       </c>
     </row>
@@ -6927,7 +6412,7 @@
         </is>
       </c>
       <c r="C35" s="34">
-        <f>(C32-Assumptions!$C$47)/(C34-Assumptions!$C$47)</f>
+        <f>(C32-Assumptions!$C$40)/(C34-Assumptions!$C$40)</f>
         <v/>
       </c>
     </row>
@@ -7023,23 +6508,23 @@
         </is>
       </c>
       <c r="B5" s="18">
-        <f>Segments!E12</f>
+        <f>Segments!E8</f>
         <v/>
       </c>
       <c r="C5" s="18">
-        <f>Segments!F12</f>
+        <f>Segments!F8</f>
         <v/>
       </c>
       <c r="D5" s="18">
-        <f>Segments!G12</f>
+        <f>Segments!G8</f>
         <v/>
       </c>
       <c r="E5" s="18">
-        <f>Segments!H12</f>
+        <f>Segments!H8</f>
         <v/>
       </c>
       <c r="F5" s="18">
-        <f>Segments!I12</f>
+        <f>Segments!I8</f>
         <v/>
       </c>
     </row>
@@ -7050,23 +6535,23 @@
         </is>
       </c>
       <c r="B6" s="18">
-        <f>Segments!B33</f>
+        <f>Segments!B21</f>
         <v/>
       </c>
       <c r="C6" s="18">
-        <f>Segments!C33</f>
+        <f>Segments!C21</f>
         <v/>
       </c>
       <c r="D6" s="18">
-        <f>Segments!D33</f>
+        <f>Segments!D21</f>
         <v/>
       </c>
       <c r="E6" s="18">
-        <f>Segments!E33</f>
+        <f>Segments!E21</f>
         <v/>
       </c>
       <c r="F6" s="18">
-        <f>Segments!F33</f>
+        <f>Segments!F21</f>
         <v/>
       </c>
     </row>
@@ -7104,23 +6589,23 @@
         </is>
       </c>
       <c r="B8" s="28">
-        <f>-B5*Assumptions!$C$34</f>
+        <f>-B5*Assumptions!$C$27</f>
         <v/>
       </c>
       <c r="C8" s="28">
-        <f>-C5*Assumptions!$C$34</f>
+        <f>-C5*Assumptions!$C$27</f>
         <v/>
       </c>
       <c r="D8" s="28">
-        <f>-D5*Assumptions!$C$34</f>
+        <f>-D5*Assumptions!$C$27</f>
         <v/>
       </c>
       <c r="E8" s="28">
-        <f>-E5*Assumptions!$C$34</f>
+        <f>-E5*Assumptions!$C$27</f>
         <v/>
       </c>
       <c r="F8" s="28">
-        <f>-F5*Assumptions!$C$34</f>
+        <f>-F5*Assumptions!$C$27</f>
         <v/>
       </c>
     </row>
@@ -7154,7 +6639,7 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>NOPAT — EBIT x (1 - 25%)</t>
+          <t>NOPAT — EBIT x (1 - 24%)</t>
         </is>
       </c>
       <c r="B10" s="28">
@@ -7212,23 +6697,23 @@
         </is>
       </c>
       <c r="B12" s="28">
-        <f>-B5*Assumptions!$B$33</f>
+        <f>-B5*Assumptions!$B$26</f>
         <v/>
       </c>
       <c r="C12" s="28">
-        <f>-C5*Assumptions!$C$33</f>
+        <f>-C5*Assumptions!$C$26</f>
         <v/>
       </c>
       <c r="D12" s="28">
-        <f>-D5*Assumptions!$D$33</f>
+        <f>-D5*Assumptions!$D$26</f>
         <v/>
       </c>
       <c r="E12" s="28">
-        <f>-E5*Assumptions!$E$33</f>
+        <f>-E5*Assumptions!$E$26</f>
         <v/>
       </c>
       <c r="F12" s="28">
-        <f>-F5*Assumptions!$F$33</f>
+        <f>-F5*Assumptions!$F$26</f>
         <v/>
       </c>
     </row>
@@ -7239,23 +6724,23 @@
         </is>
       </c>
       <c r="B13" s="28">
-        <f>-(B5-'Income Statement'!D5)*Assumptions!$C$32</f>
+        <f>-(B5*Assumptions!$C$25-'Balance Sheet'!D16)</f>
         <v/>
       </c>
       <c r="C13" s="28">
-        <f>-(C5-B5)*Assumptions!$C$32</f>
+        <f>-(C5-B5)*Assumptions!$C$25</f>
         <v/>
       </c>
       <c r="D13" s="28">
-        <f>-(D5-C5)*Assumptions!$C$32</f>
+        <f>-(D5-C5)*Assumptions!$C$25</f>
         <v/>
       </c>
       <c r="E13" s="28">
-        <f>-(E5-D5)*Assumptions!$C$32</f>
+        <f>-(E5-D5)*Assumptions!$C$25</f>
         <v/>
       </c>
       <c r="F13" s="28">
-        <f>-(F5-E5)*Assumptions!$C$32</f>
+        <f>-(F5-E5)*Assumptions!$C$25</f>
         <v/>
       </c>
     </row>
@@ -7414,7 +6899,7 @@
         </is>
       </c>
       <c r="C23" s="16">
-        <f>Assumptions!$C$47</f>
+        <f>Assumptions!$C$40</f>
         <v/>
       </c>
     </row>
@@ -7522,7 +7007,7 @@
         </is>
       </c>
       <c r="C34" s="37">
-        <f>Assumptions!$C$37</f>
+        <f>Assumptions!$C$30</f>
         <v/>
       </c>
     </row>
@@ -7533,7 +7018,7 @@
         </is>
       </c>
       <c r="C35" s="37">
-        <f>Assumptions!$C$38</f>
+        <f>Assumptions!$C$31</f>
         <v/>
       </c>
     </row>
@@ -7555,7 +7040,7 @@
         </is>
       </c>
       <c r="C37" s="38">
-        <f>Assumptions!$C$40</f>
+        <f>Assumptions!$C$33</f>
         <v/>
       </c>
     </row>
@@ -7566,7 +7051,7 @@
         </is>
       </c>
       <c r="C38" s="37">
-        <f>Assumptions!$C$39</f>
+        <f>Assumptions!$C$32</f>
         <v/>
       </c>
     </row>
@@ -7588,7 +7073,7 @@
         </is>
       </c>
       <c r="C40" s="37">
-        <f>Assumptions!$C$41</f>
+        <f>Assumptions!$C$34</f>
         <v/>
       </c>
     </row>
@@ -7621,7 +7106,7 @@
         </is>
       </c>
       <c r="C43" s="18">
-        <f>Assumptions!$C$50</f>
+        <f>Assumptions!$C$43</f>
         <v/>
       </c>
     </row>
@@ -7667,7 +7152,7 @@
         </is>
       </c>
       <c r="C47" s="37">
-        <f>Assumptions!$C$43</f>
+        <f>Assumptions!$C$36</f>
         <v/>
       </c>
     </row>
@@ -7678,7 +7163,7 @@
         </is>
       </c>
       <c r="C48" s="37">
-        <f>Assumptions!$C$44</f>
+        <f>Assumptions!$C$37</f>
         <v/>
       </c>
     </row>
@@ -7700,7 +7185,7 @@
         </is>
       </c>
       <c r="C50" s="37">
-        <f>Assumptions!$C$45</f>
+        <f>Assumptions!$C$38</f>
         <v/>
       </c>
     </row>
@@ -7722,7 +7207,7 @@
         </is>
       </c>
       <c r="C52" s="37">
-        <f>Assumptions!$C$46</f>
+        <f>Assumptions!$C$39</f>
         <v/>
       </c>
     </row>
@@ -7778,23 +7263,23 @@
         </is>
       </c>
       <c r="B56" s="37">
-        <f>Assumptions!$B$42</f>
+        <f>Assumptions!$B$35</f>
         <v/>
       </c>
       <c r="C56" s="37">
-        <f>Assumptions!$C$42</f>
+        <f>Assumptions!$C$35</f>
         <v/>
       </c>
       <c r="D56" s="37">
-        <f>Assumptions!$D$42</f>
+        <f>Assumptions!$D$35</f>
         <v/>
       </c>
       <c r="E56" s="37">
-        <f>Assumptions!$E$42</f>
+        <f>Assumptions!$E$35</f>
         <v/>
       </c>
       <c r="F56" s="37">
-        <f>Assumptions!$F$42</f>
+        <f>Assumptions!$F$35</f>
         <v/>
       </c>
     </row>
@@ -7933,13 +7418,13 @@
         </is>
       </c>
       <c r="B5" s="29" t="n">
-        <v>152186.2</v>
+        <v>152186.247545</v>
       </c>
       <c r="C5" s="29" t="n">
-        <v>231981.8</v>
+        <v>231981.835577</v>
       </c>
       <c r="D5" s="29" t="n">
-        <v>281049</v>
+        <v>281049.081719</v>
       </c>
       <c r="E5" s="29">
         <f>DCF!B5</f>
@@ -7969,32 +7454,32 @@
         </is>
       </c>
       <c r="B6" s="22" t="n">
-        <v>29077.3</v>
+        <v>29077.288803</v>
       </c>
       <c r="C6" s="22" t="n">
-        <v>43898.5</v>
+        <v>43898.520903</v>
       </c>
       <c r="D6" s="22" t="n">
-        <v>40720</v>
+        <v>40762.108187</v>
       </c>
       <c r="E6" s="18">
-        <f>Segments!B22</f>
+        <f>Segments!B14</f>
         <v/>
       </c>
       <c r="F6" s="18">
-        <f>Segments!C22</f>
+        <f>Segments!C14</f>
         <v/>
       </c>
       <c r="G6" s="18">
-        <f>Segments!D22</f>
+        <f>Segments!D14</f>
         <v/>
       </c>
       <c r="H6" s="18">
-        <f>Segments!E22</f>
+        <f>Segments!E14</f>
         <v/>
       </c>
       <c r="I6" s="18">
-        <f>Segments!F22</f>
+        <f>Segments!F14</f>
         <v/>
       </c>
     </row>
@@ -8005,13 +7490,13 @@
         </is>
       </c>
       <c r="B7" s="29" t="n">
-        <v>20035.1</v>
+        <v>20035.105205</v>
       </c>
       <c r="C7" s="29" t="n">
-        <v>31601.6</v>
+        <v>31601.46495</v>
       </c>
       <c r="D7" s="29" t="n">
-        <v>30622.08783333333</v>
+        <v>28363.203246</v>
       </c>
       <c r="E7" s="29">
         <f>DCF!B6</f>
@@ -8080,13 +7565,13 @@
         </is>
       </c>
       <c r="B9" s="22" t="n">
-        <v>-2296</v>
+        <v>-2295.986956</v>
       </c>
       <c r="C9" s="22" t="n">
-        <v>-2259.9</v>
+        <v>-2259.745806</v>
       </c>
       <c r="D9" s="22" t="n">
-        <v>-2951.0145</v>
+        <v>-3008.977627</v>
       </c>
       <c r="E9" s="18">
         <f>DCF!B8</f>
@@ -8155,32 +7640,32 @@
         </is>
       </c>
       <c r="B11" s="22" t="n">
-        <v>-2124.4</v>
+        <v>-2124.362277</v>
       </c>
       <c r="C11" s="22" t="n">
-        <v>-3515.4</v>
+        <v>-3515.365946</v>
       </c>
       <c r="D11" s="22" t="n">
-        <v>-3400</v>
+        <v>-2145.438755</v>
       </c>
       <c r="E11" s="28">
-        <f>-(Assumptions!$B$42*'Balance Sheet'!$D$11-Assumptions!$C$58*MAX('Balance Sheet'!$D$11-'Balance Sheet'!D17,0))</f>
+        <f>-(Assumptions!$B$35*'Balance Sheet'!$D$11-Assumptions!$C$51*MAX('Balance Sheet'!$D$11-'Balance Sheet'!D17,0))</f>
         <v/>
       </c>
       <c r="F11" s="28">
-        <f>-(Assumptions!$C$42*'Balance Sheet'!$D$11-Assumptions!$C$58*MAX('Balance Sheet'!$D$11-'Balance Sheet'!E17,0))</f>
+        <f>-(Assumptions!$C$35*'Balance Sheet'!$D$11-Assumptions!$C$51*MAX('Balance Sheet'!$D$11-'Balance Sheet'!E17,0))</f>
         <v/>
       </c>
       <c r="G11" s="28">
-        <f>-(Assumptions!$D$42*'Balance Sheet'!$D$11-Assumptions!$C$58*MAX('Balance Sheet'!$D$11-'Balance Sheet'!F17,0))</f>
+        <f>-(Assumptions!$D$35*'Balance Sheet'!$D$11-Assumptions!$C$51*MAX('Balance Sheet'!$D$11-'Balance Sheet'!F17,0))</f>
         <v/>
       </c>
       <c r="H11" s="28">
-        <f>-(Assumptions!$E$42*'Balance Sheet'!$D$11-Assumptions!$C$58*MAX('Balance Sheet'!$D$11-'Balance Sheet'!G17,0))</f>
+        <f>-(Assumptions!$E$35*'Balance Sheet'!$D$11-Assumptions!$C$51*MAX('Balance Sheet'!$D$11-'Balance Sheet'!G17,0))</f>
         <v/>
       </c>
       <c r="I11" s="28">
-        <f>-(Assumptions!$F$42*'Balance Sheet'!$D$11-Assumptions!$C$58*MAX('Balance Sheet'!$D$11-'Balance Sheet'!H17,0))</f>
+        <f>-(Assumptions!$F$35*'Balance Sheet'!$D$11-Assumptions!$C$51*MAX('Balance Sheet'!$D$11-'Balance Sheet'!H17,0))</f>
         <v/>
       </c>
     </row>
@@ -8191,32 +7676,32 @@
         </is>
       </c>
       <c r="B12" s="22" t="n">
-        <v>603.6</v>
+        <v>603.624972</v>
       </c>
       <c r="C12" s="22" t="n">
-        <v>1132.4</v>
+        <v>1132.366257</v>
       </c>
       <c r="D12" s="22" t="n">
-        <v>1302.26</v>
+        <v>1568.902975</v>
       </c>
       <c r="E12" s="28">
-        <f>D12*(1+Assumptions!$C$57)</f>
+        <f>D12*(1+Assumptions!$C$50)</f>
         <v/>
       </c>
       <c r="F12" s="28">
-        <f>E12*(1+Assumptions!$C$57)</f>
+        <f>E12*(1+Assumptions!$C$50)</f>
         <v/>
       </c>
       <c r="G12" s="28">
-        <f>F12*(1+Assumptions!$C$57)</f>
+        <f>F12*(1+Assumptions!$C$50)</f>
         <v/>
       </c>
       <c r="H12" s="28">
-        <f>G12*(1+Assumptions!$C$57)</f>
+        <f>G12*(1+Assumptions!$C$50)</f>
         <v/>
       </c>
       <c r="I12" s="28">
-        <f>H12*(1+Assumptions!$C$57)</f>
+        <f>H12*(1+Assumptions!$C$50)</f>
         <v/>
       </c>
     </row>
@@ -8266,13 +7751,13 @@
         </is>
       </c>
       <c r="B14" s="22" t="n">
-        <v>-5080.4</v>
+        <v>-5080.406688</v>
       </c>
       <c r="C14" s="22" t="n">
-        <v>-8121.5</v>
+        <v>-8121.510082</v>
       </c>
       <c r="D14" s="22" t="n">
-        <v>-6393.333333333332</v>
+        <v>-5591.139782</v>
       </c>
       <c r="E14" s="28">
         <f>-E13*Assumptions!$C$7</f>
@@ -8302,13 +7787,13 @@
         </is>
       </c>
       <c r="B15" s="22" t="n">
-        <v>11138</v>
+        <v>11137.974256</v>
       </c>
       <c r="C15" s="22" t="n">
-        <v>18837.2</v>
+        <v>18837.209373</v>
       </c>
       <c r="D15" s="22" t="n">
-        <v>19180</v>
+        <v>19186.550057</v>
       </c>
       <c r="E15" s="28">
         <f>E13+E14</f>
@@ -8338,13 +7823,13 @@
         </is>
       </c>
       <c r="B16" s="22" t="n">
-        <v>-1022.299999999999</v>
+        <v>-1022.272478999999</v>
       </c>
       <c r="C16" s="22" t="n">
-        <v>-1375.799999999999</v>
+        <v>-1375.850659</v>
       </c>
       <c r="D16" s="22" t="n">
-        <v>-1850</v>
+        <v>-1856.305067000001</v>
       </c>
       <c r="E16" s="28">
         <f>-E15*'SOTP Bridge'!$C$15</f>
@@ -8374,13 +7859,13 @@
         </is>
       </c>
       <c r="B17" s="29" t="n">
-        <v>10115.7</v>
+        <v>10115.701777</v>
       </c>
       <c r="C17" s="29" t="n">
-        <v>17461.4</v>
+        <v>17461.358714</v>
       </c>
       <c r="D17" s="29" t="n">
-        <v>17330</v>
+        <v>17330.24499</v>
       </c>
       <c r="E17" s="29">
         <f>E15+E16</f>

--- a/engine/swdy_study/SWDY_Valuation_Model_05082026_public.xlsx
+++ b/engine/swdy_study/SWDY_Valuation_Model_05082026_public.xlsx
@@ -143,6 +143,7 @@
     <xf numFmtId="164" fontId="10" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -158,7 +159,6 @@
     <xf numFmtId="169" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -529,7 +529,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I51"/>
+  <dimension ref="A1:I55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="112" customWidth="1" min="1" max="1"/>
@@ -619,247 +619,275 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>THREE THINGS ARE PASTED VALUES, and it is worth knowing which. First, audited and disclosed history — the</t>
+          <t>THREE THINGS ARE PASTED VALUES, and it is worth knowing exactly which. First, audited and disclosed history</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>primary record, not a calculation. Second, the segment build: revenue and profit for the three segments the</t>
+          <t>— the primary record, not a calculation. Second, the segment build: revenue and profit for the three</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>company itself discloses (Cables and its accessories, Constructions and infrastructure, Electrical products</t>
+          <t>segments the company itself discloses (Cables and its accessories, Constructions and infrastructure,</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>and digital solutions) are pasted for FY2025 and grown on their own drivers; only its OUTPUT is carried here</t>
+          <t>Electrical products and digital solutions) are pasted for FY2025 and grown on their own drivers; only its</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>and everything downstream of it is formula. Third, the Monte Carlo price map and the sensitivity grids,</t>
+          <t>OUTPUT is carried here and everything downstream of it is formula. Third, whole-model engine outputs, where</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>where each individual cell is a complete re-run of the whole valuation and so cannot be a formula in a grid.</t>
+          <t>each figure is a complete re-run of the entire valuation and so cannot be a single formula: the Monte Carlo</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Changing a driver reprices the model but does NOT redraw those two grids.</t>
+          <t>price map, the sensitivity grids, the DCF scenario bear/bull bounds, the multi-leg currency-of-discounting</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr"/>
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>alternative (its USD cost of capital IS a live formula; the leg-by-leg USD discounting is the engine's),</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>How revenue is built. Not as one growth rate. Each of the three disclosed segments is grown on its own</t>
+          <t>and the expert-panel legs. Everything else — including every lens base value, the relative/normalised/book</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>driver — Cables on copper-price growth times FX-translation growth times a modest real-volume assumption,</t>
+          <t>bear and bull bounds, and the anchor-date roll — is a live formula. Changing a driver reprices the model</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Constructions and Electrical products on a taper of their own recent revenue CAGR — because none of the</t>
+          <t>but does NOT redraw the engine outputs.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>audited filings discloses a tonnage, order-book or backlog figure to build a literal unit model from.</t>
-        </is>
-      </c>
+      <c r="A24" s="3" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Margins come from the same segment build; group EBITDA margin is an OUTPUT of it, not an input.</t>
+          <t>How revenue is built. Not as one growth rate. Each of the three disclosed segments is grown on its own</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="inlineStr"/>
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>driver — Cables on copper-price growth times FX-translation growth times a modest real-volume assumption,</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>What it is not. It is not investment advice, a recommendation, or a price target. Values are model outputs</t>
+          <t>Constructions and Electrical products on a taper of their own recent revenue CAGR — because none of the</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>shown as ranges.</t>
+          <t>audited filings discloses a tonnage, order-book or backlog figure to build a literal unit model from.</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="inlineStr"/>
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Margins come from the same segment build; group EBITDA margin is an OUTPUT of it, not an input.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>Sourcing note, up front. FY2023, FY2024 and FY2025 all come from the company's own audited consolidated</t>
-        </is>
-      </c>
+      <c r="A30" s="3" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>financial statements — every income-statement, balance-sheet and segment line is the audited figure, not a</t>
+          <t>What it is not. It is not investment advice, a recommendation, or a price target. Values are model outputs</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>derivation or a triangulation. Segment revenue ties EXACTLY to consolidated revenue in every year (Note</t>
+          <t>shown as ranges.</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>5-3); segment profit reconciles to consolidated operating profit through an explicit, exactly-reconciling</t>
-        </is>
-      </c>
+      <c r="A33" s="3" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>corporate cost load (Note 16 less G&amp;A, net impairment, other expenses and other income). Every input is</t>
+          <t>Sourcing note, up front. FY2023, FY2024 and FY2025 all come from the company's own audited consolidated</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>annotated where it appears and listed with source and date in the companion bibliography document.</t>
+          <t>financial statements — every income-statement, balance-sheet and segment line is the audited figure, not a</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="inlineStr"/>
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>derivation or a triangulation. Segment revenue ties EXACTLY to consolidated revenue in every year (Note</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>Discount convention. Each explicit year is discounted at its own forward cost of capital, gliding</t>
+          <t>5-3); segment profit reconciles to consolidated operating profit through an explicit, exactly-reconciling</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>26.6% -&gt; 14.8% on the same easing calendar as the interest forecast; the terminal value is</t>
+          <t>corporate cost load (Note 16 less G&amp;A, net impairment, other expenses and other income). Every input is</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>capitalised at the terminal rate and discounted at the year-5 cumulative factor. One date, one price of time.</t>
+          <t>annotated where it appears and listed with source and date in the companion bibliography document.</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t>The glide fractions are not a free parameter: they are the cost-of-debt path's own cumulative progress, and</t>
-        </is>
-      </c>
+      <c r="A40" s="3" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>the DCF sheet computes them in front of you.</t>
+          <t>Discount convention. Each explicit year is discounted at its own forward cost of capital, gliding</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="inlineStr"/>
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>26.6% -&gt; 15.9% on the same easing calendar as the interest forecast; the terminal value is</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>The open question. This company earns just over half its revenue on a hard-currency-linked basis but</t>
+          <t>capitalised at the terminal rate and discounted at the year-5 cumulative factor. One date, one price of time.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>reports, lists and borrows in Egyptian pounds. The primary model charges the full Egyptian cost of capital.</t>
+          <t>The glide fractions are not a free parameter: they are the cost-of-debt path's own cumulative progress, and</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>The Fundamental Valuation sheet also shows what the same cash flows are worth if the hard-currency leg is</t>
+          <t>the DCF sheet computes them in front of you.</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="inlineStr">
-        <is>
-          <t>discounted at a hard-currency rate. Both are shown; they are not averaged.</t>
-        </is>
-      </c>
+      <c r="A46" s="3" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="inlineStr"/>
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>The open question. This company earns just over half its revenue on a hard-currency-linked basis but</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>Currency. EGP million unless stated. Spot EGP 105.20 (2026-08-05 close). Sheets: READ FIRST · Summary ·</t>
+          <t>reports, lists and borrows in Egyptian pounds. The primary model charges the full Egyptian cost of capital.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>Fundamental Valuation · Assumptions · SOTP Bridge · Segments · Relative &amp; Normalized · DCF · Income</t>
+          <t>The Fundamental Valuation sheet also shows what the same cash flows are worth if the hard-currency leg is</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
+          <t>discounted at a hard-currency rate. Both are shown; they are not averaged.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>Currency. EGP million unless stated. Spot EGP 105.20 (2026-08-05 close). Sheets: READ FIRST · Summary ·</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>Fundamental Valuation · Assumptions · SOTP Bridge · Segments · Relative &amp; Normalized · DCF · Income</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
           <t>Statement · Balance Sheet · Cash Flow · Summary Financials · Monte Carlo · Sensitivity · Per-Share &amp;</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="3" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
         <is>
           <t>Ratios · Peer &amp; Sector.</t>
         </is>
@@ -965,32 +993,32 @@
           <t>Property, plant and equipment</t>
         </is>
       </c>
-      <c r="B5" s="22" t="n">
+      <c r="B5" s="23" t="n">
         <v>18009.166367</v>
       </c>
-      <c r="C5" s="22" t="n">
+      <c r="C5" s="23" t="n">
         <v>27543.762675</v>
       </c>
-      <c r="D5" s="22" t="n">
+      <c r="D5" s="23" t="n">
         <v>35961.076614</v>
       </c>
-      <c r="E5" s="28">
+      <c r="E5" s="29">
         <f>D5-DCF!B12+DCF!B8</f>
         <v/>
       </c>
-      <c r="F5" s="28">
+      <c r="F5" s="29">
         <f>E5-DCF!C12+DCF!C8</f>
         <v/>
       </c>
-      <c r="G5" s="28">
+      <c r="G5" s="29">
         <f>F5-DCF!D12+DCF!D8</f>
         <v/>
       </c>
-      <c r="H5" s="28">
+      <c r="H5" s="29">
         <f>G5-DCF!E12+DCF!E8</f>
         <v/>
       </c>
-      <c r="I5" s="28">
+      <c r="I5" s="29">
         <f>H5-DCF!F12+DCF!F8</f>
         <v/>
       </c>
@@ -1001,13 +1029,13 @@
           <t>Inventories</t>
         </is>
       </c>
-      <c r="B6" s="22" t="n">
+      <c r="B6" s="23" t="n">
         <v>30881.822082</v>
       </c>
-      <c r="C6" s="22" t="n">
+      <c r="C6" s="23" t="n">
         <v>56795.884068</v>
       </c>
-      <c r="D6" s="22" t="n">
+      <c r="D6" s="23" t="n">
         <v>59860.04457</v>
       </c>
     </row>
@@ -1017,13 +1045,13 @@
           <t>Contract assets</t>
         </is>
       </c>
-      <c r="B7" s="22" t="n">
+      <c r="B7" s="23" t="n">
         <v>16179.633722</v>
       </c>
-      <c r="C7" s="22" t="n">
+      <c r="C7" s="23" t="n">
         <v>18051.96657</v>
       </c>
-      <c r="D7" s="22" t="n">
+      <c r="D7" s="23" t="n">
         <v>29894.579591</v>
       </c>
     </row>
@@ -1033,13 +1061,13 @@
           <t>Trade and other receivables</t>
         </is>
       </c>
-      <c r="B8" s="22" t="n">
+      <c r="B8" s="23" t="n">
         <v>46591.885092</v>
       </c>
-      <c r="C8" s="22" t="n">
+      <c r="C8" s="23" t="n">
         <v>86736.309423</v>
       </c>
-      <c r="D8" s="22" t="n">
+      <c r="D8" s="23" t="n">
         <v>116259.797169</v>
       </c>
     </row>
@@ -1049,13 +1077,13 @@
           <t>Cash and cash equivalents</t>
         </is>
       </c>
-      <c r="B9" s="22" t="n">
+      <c r="B9" s="23" t="n">
         <v>25552.0448</v>
       </c>
-      <c r="C9" s="22" t="n">
+      <c r="C9" s="23" t="n">
         <v>38180.002322</v>
       </c>
-      <c r="D9" s="28">
+      <c r="D9" s="29">
         <f>D11-D17</f>
         <v/>
       </c>
@@ -1066,13 +1094,13 @@
           <t>Total assets</t>
         </is>
       </c>
-      <c r="B10" s="29" t="n">
+      <c r="B10" s="30" t="n">
         <v>151448.654828</v>
       </c>
-      <c r="C10" s="29" t="n">
+      <c r="C10" s="30" t="n">
         <v>249527.138687</v>
       </c>
-      <c r="D10" s="29" t="n">
+      <c r="D10" s="30" t="n">
         <v>311099.090775</v>
       </c>
       <c r="E10" s="15" t="n"/>
@@ -1087,13 +1115,13 @@
           <t>Loans and borrowings</t>
         </is>
       </c>
-      <c r="B11" s="22" t="n">
+      <c r="B11" s="23" t="n">
         <v>41766.492071</v>
       </c>
-      <c r="C11" s="22" t="n">
+      <c r="C11" s="23" t="n">
         <v>59082.941807</v>
       </c>
-      <c r="D11" s="22" t="n">
+      <c r="D11" s="23" t="n">
         <v>62509.211797</v>
       </c>
     </row>
@@ -1103,13 +1131,13 @@
           <t>Trade and other payables</t>
         </is>
       </c>
-      <c r="B12" s="22" t="n">
+      <c r="B12" s="23" t="n">
         <v>31938.12206</v>
       </c>
-      <c r="C12" s="22" t="n">
+      <c r="C12" s="23" t="n">
         <v>54808.185042</v>
       </c>
-      <c r="D12" s="22" t="n">
+      <c r="D12" s="23" t="n">
         <v>68895.662044</v>
       </c>
     </row>
@@ -1119,13 +1147,13 @@
           <t>Contract liabilities</t>
         </is>
       </c>
-      <c r="B13" s="22" t="n">
+      <c r="B13" s="23" t="n">
         <v>25060.328092</v>
       </c>
-      <c r="C13" s="22" t="n">
+      <c r="C13" s="23" t="n">
         <v>53281.056753</v>
       </c>
-      <c r="D13" s="22" t="n">
+      <c r="D13" s="23" t="n">
         <v>81266.224686</v>
       </c>
     </row>
@@ -1135,33 +1163,33 @@
           <t>Equity attributable to shareholders</t>
         </is>
       </c>
-      <c r="B14" s="29" t="n">
+      <c r="B14" s="30" t="n">
         <v>35724.466132</v>
       </c>
-      <c r="C14" s="29" t="n">
+      <c r="C14" s="30" t="n">
         <v>55274.913356</v>
       </c>
-      <c r="D14" s="29" t="n">
+      <c r="D14" s="30" t="n">
         <v>66870.86655000001</v>
       </c>
-      <c r="E14" s="29">
-        <f>D14+'Income Statement'!E17*(1-Assumptions!$C$49)</f>
-        <v/>
-      </c>
-      <c r="F14" s="29">
-        <f>E14+'Income Statement'!F17*(1-Assumptions!$C$49)</f>
-        <v/>
-      </c>
-      <c r="G14" s="29">
-        <f>F14+'Income Statement'!G17*(1-Assumptions!$C$49)</f>
-        <v/>
-      </c>
-      <c r="H14" s="29">
-        <f>G14+'Income Statement'!H17*(1-Assumptions!$C$49)</f>
-        <v/>
-      </c>
-      <c r="I14" s="29">
-        <f>H14+'Income Statement'!I17*(1-Assumptions!$C$49)</f>
+      <c r="E14" s="30">
+        <f>D14+'Income Statement'!E17*(1-Assumptions!$C$50)</f>
+        <v/>
+      </c>
+      <c r="F14" s="30">
+        <f>E14+'Income Statement'!F17*(1-Assumptions!$C$50)</f>
+        <v/>
+      </c>
+      <c r="G14" s="30">
+        <f>F14+'Income Statement'!G17*(1-Assumptions!$C$50)</f>
+        <v/>
+      </c>
+      <c r="H14" s="30">
+        <f>G14+'Income Statement'!H17*(1-Assumptions!$C$50)</f>
+        <v/>
+      </c>
+      <c r="I14" s="30">
+        <f>H14+'Income Statement'!I17*(1-Assumptions!$C$50)</f>
         <v/>
       </c>
     </row>
@@ -1171,13 +1199,13 @@
           <t>Non-controlling interests</t>
         </is>
       </c>
-      <c r="B15" s="22" t="n">
+      <c r="B15" s="23" t="n">
         <v>2384.013396</v>
       </c>
-      <c r="C15" s="22" t="n">
+      <c r="C15" s="23" t="n">
         <v>4251.7719</v>
       </c>
-      <c r="D15" s="22" t="n">
+      <c r="D15" s="23" t="n">
         <v>5118.978381</v>
       </c>
     </row>
@@ -1187,32 +1215,32 @@
           <t>Net working capital</t>
         </is>
       </c>
-      <c r="B16" s="22" t="n">
+      <c r="B16" s="23" t="n">
         <v>36654.89074399999</v>
       </c>
-      <c r="C16" s="22" t="n">
+      <c r="C16" s="23" t="n">
         <v>53494.91826600001</v>
       </c>
-      <c r="D16" s="22" t="n">
+      <c r="D16" s="23" t="n">
         <v>55852.53459999998</v>
       </c>
-      <c r="E16" s="28">
+      <c r="E16" s="29">
         <f>'Income Statement'!E5*Assumptions!$C$25</f>
         <v/>
       </c>
-      <c r="F16" s="28">
+      <c r="F16" s="29">
         <f>'Income Statement'!F5*Assumptions!$C$25</f>
         <v/>
       </c>
-      <c r="G16" s="28">
+      <c r="G16" s="29">
         <f>'Income Statement'!G5*Assumptions!$C$25</f>
         <v/>
       </c>
-      <c r="H16" s="28">
+      <c r="H16" s="29">
         <f>'Income Statement'!H5*Assumptions!$C$25</f>
         <v/>
       </c>
-      <c r="I16" s="28">
+      <c r="I16" s="29">
         <f>'Income Statement'!I5*Assumptions!$C$25</f>
         <v/>
       </c>
@@ -1223,34 +1251,34 @@
           <t>Net bank debt</t>
         </is>
       </c>
-      <c r="B17" s="29" t="n">
+      <c r="B17" s="30" t="n">
         <v>16214.447271</v>
       </c>
-      <c r="C17" s="29" t="n">
+      <c r="C17" s="30" t="n">
         <v>20902.939485</v>
       </c>
-      <c r="D17" s="29">
+      <c r="D17" s="30">
         <f>Assumptions!$C$43</f>
         <v/>
       </c>
-      <c r="E17" s="29">
-        <f>D17-DCF!B14-'Income Statement'!E11*(1-Assumptions!$C$7)+Assumptions!$C$49*'Income Statement'!E17</f>
-        <v/>
-      </c>
-      <c r="F17" s="29">
-        <f>E17-DCF!C14-'Income Statement'!F11*(1-Assumptions!$C$7)+Assumptions!$C$49*'Income Statement'!F17</f>
-        <v/>
-      </c>
-      <c r="G17" s="29">
-        <f>F17-DCF!D14-'Income Statement'!G11*(1-Assumptions!$C$7)+Assumptions!$C$49*'Income Statement'!G17</f>
-        <v/>
-      </c>
-      <c r="H17" s="29">
-        <f>G17-DCF!E14-'Income Statement'!H11*(1-Assumptions!$C$7)+Assumptions!$C$49*'Income Statement'!H17</f>
-        <v/>
-      </c>
-      <c r="I17" s="29">
-        <f>H17-DCF!F14-'Income Statement'!I11*(1-Assumptions!$C$7)+Assumptions!$C$49*'Income Statement'!I17</f>
+      <c r="E17" s="30">
+        <f>D17-DCF!B14-'Income Statement'!E11*(1-Assumptions!$C$7)+Assumptions!$C$50*'Income Statement'!E17</f>
+        <v/>
+      </c>
+      <c r="F17" s="30">
+        <f>E17-DCF!C14-'Income Statement'!F11*(1-Assumptions!$C$7)+Assumptions!$C$50*'Income Statement'!F17</f>
+        <v/>
+      </c>
+      <c r="G17" s="30">
+        <f>F17-DCF!D14-'Income Statement'!G11*(1-Assumptions!$C$7)+Assumptions!$C$50*'Income Statement'!G17</f>
+        <v/>
+      </c>
+      <c r="H17" s="30">
+        <f>G17-DCF!E14-'Income Statement'!H11*(1-Assumptions!$C$7)+Assumptions!$C$50*'Income Statement'!H17</f>
+        <v/>
+      </c>
+      <c r="I17" s="30">
+        <f>H17-DCF!F14-'Income Statement'!I11*(1-Assumptions!$C$7)+Assumptions!$C$50*'Income Statement'!I17</f>
         <v/>
       </c>
     </row>
@@ -1260,35 +1288,35 @@
           <t>Net debt / EBITDA</t>
         </is>
       </c>
-      <c r="B18" s="34">
+      <c r="B18" s="35">
         <f>B17/'Income Statement'!B7</f>
         <v/>
       </c>
-      <c r="C18" s="34">
+      <c r="C18" s="35">
         <f>C17/'Income Statement'!C7</f>
         <v/>
       </c>
-      <c r="D18" s="34">
+      <c r="D18" s="35">
         <f>D17/'Income Statement'!D7</f>
         <v/>
       </c>
-      <c r="E18" s="34">
+      <c r="E18" s="35">
         <f>E17/'Income Statement'!E7</f>
         <v/>
       </c>
-      <c r="F18" s="34">
+      <c r="F18" s="35">
         <f>F17/'Income Statement'!F7</f>
         <v/>
       </c>
-      <c r="G18" s="34">
+      <c r="G18" s="35">
         <f>G17/'Income Statement'!G7</f>
         <v/>
       </c>
-      <c r="H18" s="34">
+      <c r="H18" s="35">
         <f>H17/'Income Statement'!H7</f>
         <v/>
       </c>
-      <c r="I18" s="34">
+      <c r="I18" s="35">
         <f>I17/'Income Statement'!I7</f>
         <v/>
       </c>
@@ -1299,15 +1327,15 @@
           <t>Residual: other liabilities, provisions and deferred tax not shown separately (total assets less the lines above)</t>
         </is>
       </c>
-      <c r="B19" s="28">
+      <c r="B19" s="29">
         <f>B10-(B11+B12+B13+B14+B15)</f>
         <v/>
       </c>
-      <c r="C19" s="28">
+      <c r="C19" s="29">
         <f>C10-(C11+C12+C13+C14+C15)</f>
         <v/>
       </c>
-      <c r="D19" s="28">
+      <c r="D19" s="29">
         <f>D10-(D11+D12+D13+D14+D15)</f>
         <v/>
       </c>
@@ -1449,12 +1477,12 @@
           <t>Interest paid</t>
         </is>
       </c>
-      <c r="B6" s="28" t="inlineStr">
+      <c r="B6" s="29" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C6" s="22" t="n">
+      <c r="C6" s="23" t="n">
         <v>-5740.31242</v>
       </c>
     </row>
@@ -1464,12 +1492,12 @@
           <t>Income tax paid</t>
         </is>
       </c>
-      <c r="B7" s="28" t="inlineStr">
+      <c r="B7" s="29" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C7" s="22" t="n">
+      <c r="C7" s="23" t="n">
         <v>-8298.752112</v>
       </c>
     </row>
@@ -1479,12 +1507,12 @@
           <t>Operating cash flow after interest and tax</t>
         </is>
       </c>
-      <c r="B8" s="28" t="inlineStr">
+      <c r="B8" s="29" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C8" s="22" t="n">
+      <c r="C8" s="23" t="n">
         <v>12765.922545</v>
       </c>
     </row>
@@ -1494,12 +1522,12 @@
           <t>NOPAT</t>
         </is>
       </c>
-      <c r="B9" s="28" t="inlineStr">
+      <c r="B9" s="29" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C9" s="28" t="inlineStr">
+      <c r="C9" s="29" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1531,12 +1559,12 @@
           <t>Add back depreciation and amortisation</t>
         </is>
       </c>
-      <c r="B10" s="28" t="inlineStr">
+      <c r="B10" s="29" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C10" s="28" t="inlineStr">
+      <c r="C10" s="29" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1568,10 +1596,10 @@
           <t>Capital expenditure</t>
         </is>
       </c>
-      <c r="B11" s="22" t="n">
+      <c r="B11" s="23" t="n">
         <v>-8489.780912</v>
       </c>
-      <c r="C11" s="22" t="n">
+      <c r="C11" s="23" t="n">
         <v>-13112.049791</v>
       </c>
       <c r="D11" s="18">
@@ -1601,12 +1629,12 @@
           <t>Change in working capital</t>
         </is>
       </c>
-      <c r="B12" s="28" t="inlineStr">
+      <c r="B12" s="29" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C12" s="28">
+      <c r="C12" s="29">
         <f>-('Balance Sheet'!D16-'Balance Sheet'!C16)</f>
         <v/>
       </c>
@@ -1637,33 +1665,33 @@
           <t>Free cash flow to the firm</t>
         </is>
       </c>
-      <c r="B13" s="29" t="inlineStr">
+      <c r="B13" s="30" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C13" s="29" t="inlineStr">
+      <c r="C13" s="30" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D13" s="29">
+      <c r="D13" s="30">
         <f>D9+D10+D11+D12</f>
         <v/>
       </c>
-      <c r="E13" s="29">
+      <c r="E13" s="30">
         <f>E9+E10+E11+E12</f>
         <v/>
       </c>
-      <c r="F13" s="29">
+      <c r="F13" s="30">
         <f>F9+F10+F11+F12</f>
         <v/>
       </c>
-      <c r="G13" s="29">
+      <c r="G13" s="30">
         <f>G9+G10+G11+G12</f>
         <v/>
       </c>
-      <c r="H13" s="29">
+      <c r="H13" s="30">
         <f>H9+H10+H11+H12</f>
         <v/>
       </c>
@@ -2022,17 +2050,17 @@
           <t>Free cash flow to the firm</t>
         </is>
       </c>
-      <c r="B11" s="28" t="inlineStr">
+      <c r="B11" s="29" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C11" s="28" t="inlineStr">
+      <c r="C11" s="29" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D11" s="28" t="inlineStr">
+      <c r="D11" s="29" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2103,12 +2131,12 @@
           <t>Invested capital</t>
         </is>
       </c>
-      <c r="B13" s="28" t="inlineStr">
+      <c r="B13" s="29" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C13" s="28" t="inlineStr">
+      <c r="C13" s="29" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2406,7 +2434,7 @@
           <t>Simulated paths</t>
         </is>
       </c>
-      <c r="C15" s="22" t="n">
+      <c r="C15" s="23" t="n">
         <v>50000</v>
       </c>
     </row>
@@ -2454,10 +2482,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
@@ -2526,111 +2554,111 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>65.73330536703199</v>
+        <v>65.329844401984</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>69.438436012762</v>
+        <v>68.35354257523431</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>74.00009362699467</v>
+        <v>71.9670712933261</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>79.79348988925979</v>
+        <v>76.39345107557055</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>87.45046385571818</v>
+        <v>81.98435185876774</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>14.9%</t>
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>58.46247949320996</v>
+        <v>58.4402879098668</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>61.14086920605202</v>
+        <v>60.6461755538821</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>64.34874750647396</v>
+        <v>63.21971152566643</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>68.28850926253585</v>
+        <v>66.28434770102153</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>73.28076460177508</v>
+        <v>70.02577372147603</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>15.9%</t>
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>52.43291506341599</v>
+        <v>52.6302713847032</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>54.38595651288955</v>
+        <v>54.24351203947743</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>56.66901991043024</v>
+        <v>56.08399377388404</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>59.3939979641928</v>
+        <v>58.22034038779206</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>62.72981076166899</v>
+        <v>60.75189974055389</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>15.8%</t>
+          <t>16.9%</t>
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>47.35430052698718</v>
+        <v>47.66687793345727</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>48.78264840984675</v>
+        <v>48.84248007666995</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>50.41527431963544</v>
+        <v>50.15437928765454</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>52.31440533812709</v>
+        <v>51.63997115359249</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>54.57039902646127</v>
+        <v>53.35170855849378</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>16.8%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>43.02019875229038</v>
+        <v>43.37959572111903</v>
       </c>
       <c r="C10" s="7" t="n">
-        <v>44.06165690563098</v>
+        <v>44.22702715685592</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>45.2260975498987</v>
+        <v>45.15076181775254</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>46.54753023242386</v>
+        <v>46.16998066974453</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>48.07377779812698</v>
+        <v>47.31088154269673</v>
       </c>
     </row>
     <row r="12">
@@ -2671,144 +2699,133 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>terminal 12.8%</t>
+          <t>terminal 13.9%</t>
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>78.52776396161002</v>
+        <v>76.53066395732843</v>
       </c>
       <c r="C14" s="7" t="n">
-        <v>76.2229422830915</v>
+        <v>74.20763706152702</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>74.00009362699467</v>
+        <v>71.9670712933261</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>71.85558212399256</v>
+        <v>69.80531513594863</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>69.78596622715773</v>
+        <v>67.71891197265076</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>terminal 13.8%</t>
+          <t>terminal 14.9%</t>
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>68.32365822883249</v>
+        <v>67.28261009519261</v>
       </c>
       <c r="C15" s="7" t="n">
-        <v>66.3002853062016</v>
+        <v>65.21451934442834</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>64.34874750647396</v>
+        <v>63.21971152566643</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>62.46586343952262</v>
+        <v>61.29494639096928</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>60.6486215398966</v>
+        <v>59.4371564326104</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>terminal 14.8%</t>
+          <t>terminal 15.9%</t>
         </is>
       </c>
       <c r="B16" s="7" t="n">
-        <v>60.20432618850818</v>
+        <v>59.73868410008669</v>
       </c>
       <c r="C16" s="7" t="n">
-        <v>58.40478484299483</v>
+        <v>57.87843695583718</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>56.66901991043024</v>
+        <v>56.08399377388404</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>54.99421111957988</v>
+        <v>54.35244928326305</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>53.37768856559438</v>
+        <v>52.68105291114693</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>terminal 15.8%</t>
+          <t>terminal 16.9%</t>
         </is>
       </c>
       <c r="B17" s="7" t="n">
-        <v>53.59280842300805</v>
+        <v>53.47006721636905</v>
       </c>
       <c r="C17" s="7" t="n">
-        <v>51.97543076855138</v>
+        <v>51.78242507173835</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>50.41527431963544</v>
+        <v>50.15437928765454</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>48.90981241909613</v>
+        <v>48.58330249404308</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>47.45665296136994</v>
+        <v>47.06670705720629</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>terminal 16.8%</t>
+          <t>terminal 17.9%</t>
         </is>
       </c>
       <c r="B18" s="7" t="n">
-        <v>48.1069447436003</v>
+        <v>48.18057399728519</v>
       </c>
       <c r="C18" s="7" t="n">
-        <v>46.6406270489659</v>
+        <v>46.63848559892643</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>45.2260975498987</v>
+        <v>45.15076181775254</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>43.86107282353094</v>
+        <v>43.71500938002328</v>
       </c>
       <c r="F18" s="7" t="n">
-        <v>42.543390902758</v>
+        <v>42.32896215043171</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="20" t="inlineStr">
         <is>
-          <t>Single-driver sensitivities</t>
+          <t>Single-driver sensitivities — five engine re-runs per row; the parameter grid for each row is shown beside its name</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>Driver</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+          <t>Driver (parameter grid)</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr"/>
       <c r="C21" s="5" t="inlineStr"/>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>Base</t>
-        </is>
-      </c>
+      <c r="D21" s="5" t="inlineStr"/>
       <c r="E21" s="5" t="inlineStr"/>
-      <c r="F21" s="5" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G21" s="5" t="inlineStr">
+      <c r="F21" s="5" t="inlineStr"/>
+      <c r="G21" s="5" t="inlineStr"/>
+      <c r="H21" s="5" t="inlineStr">
         <is>
           <t>Swing</t>
         </is>
@@ -2817,23 +2834,23 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Beta</t>
+          <t>Beta  (0.60 / 0.80 / 1.01 / 1.15 / 1.30)</t>
         </is>
       </c>
       <c r="B22" s="7" t="n">
-        <v>81.10220410949162</v>
+        <v>82.1040695099194</v>
       </c>
       <c r="C22" s="7" t="n">
-        <v>67.57169350379721</v>
+        <v>67.65449935590391</v>
       </c>
       <c r="D22" s="7" t="n">
-        <v>56.66901991043024</v>
+        <v>56.08399377388404</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>50.66757021426321</v>
+        <v>49.74342393917833</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>45.20072232829303</v>
+        <v>43.98578978959206</v>
       </c>
       <c r="H22" s="10">
         <f>MAX(B22:F22)-MIN(B22:F22)</f>
@@ -2843,23 +2860,23 @@
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>Exchange-rate path multiplier</t>
+          <t>Exchange-rate path multiplier  (0.90x / 1.00x / 1.20x / 1.45x / 1.70x)</t>
         </is>
       </c>
       <c r="B23" s="7" t="n">
-        <v>53.01576059688728</v>
+        <v>52.41845656686412</v>
       </c>
       <c r="C23" s="7" t="n">
-        <v>56.66901991043024</v>
+        <v>56.08399377388404</v>
       </c>
       <c r="D23" s="7" t="n">
-        <v>63.97553853751615</v>
+        <v>63.41506818792391</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>73.10868682137352</v>
+        <v>72.57891120547374</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>82.2418351052309</v>
+        <v>81.74275422302357</v>
       </c>
       <c r="H23" s="10">
         <f>MAX(B23:F23)-MIN(B23:F23)</f>
@@ -2869,23 +2886,23 @@
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>EBITDA margin shift</t>
+          <t>Segment margins, multiplicative  (0.850x / 0.925x / 1.000x / 1.075x / 1.150x)</t>
         </is>
       </c>
       <c r="B24" s="7" t="n">
-        <v>32.20907967130833</v>
+        <v>30.09596871603819</v>
       </c>
       <c r="C24" s="7" t="n">
-        <v>44.43904979086927</v>
+        <v>43.08998124496109</v>
       </c>
       <c r="D24" s="7" t="n">
-        <v>56.66901991043024</v>
+        <v>56.08399377388404</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>68.89899002999118</v>
+        <v>69.078006302807</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>81.12896014955211</v>
+        <v>82.07201883172988</v>
       </c>
       <c r="H24" s="10">
         <f>MAX(B24:F24)-MIN(B24:F24)</f>
@@ -2895,23 +2912,23 @@
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>Working capital / revenue</t>
+          <t>Copper price multiplier  (0.850x / 0.925x / 1.000x / 1.075x / 1.150x)</t>
         </is>
       </c>
       <c r="B25" s="7" t="n">
-        <v>62.80167783479418</v>
+        <v>50.58568796335414</v>
       </c>
       <c r="C25" s="7" t="n">
-        <v>59.62961339115767</v>
+        <v>53.33484086861908</v>
       </c>
       <c r="D25" s="7" t="n">
-        <v>56.66901991043024</v>
+        <v>56.08399377388404</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>53.28548450388462</v>
+        <v>58.83314667914899</v>
       </c>
       <c r="F25" s="7" t="n">
-        <v>50.11342006024807</v>
+        <v>61.58229958441391</v>
       </c>
       <c r="H25" s="10">
         <f>MAX(B25:F25)-MIN(B25:F25)</f>
@@ -2921,26 +2938,78 @@
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>Terminal return on invested capital</t>
+          <t>Working capital / revenue  (17.0% / 18.5% / 19.9% / 21.5% / 23.0%)</t>
         </is>
       </c>
       <c r="B26" s="7" t="n">
-        <v>50.38212331740489</v>
+        <v>62.98785448545478</v>
       </c>
       <c r="C26" s="7" t="n">
-        <v>54.34373888956956</v>
+        <v>59.41689204843545</v>
       </c>
       <c r="D26" s="7" t="n">
-        <v>56.66901991043024</v>
+        <v>56.08399377388404</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>60.43853207751521</v>
+        <v>52.27496717439674</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>62.26697003389888</v>
+        <v>48.70400473737737</v>
       </c>
       <c r="H26" s="10">
         <f>MAX(B26:F26)-MIN(B26:F26)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>Terminal return on invested capital  (15.0% / 18.0% / 20.4% / 26.0% / 30.0%)</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="n">
+        <v>49.68012825683863</v>
+      </c>
+      <c r="C27" s="7" t="n">
+        <v>53.7154504510227</v>
+      </c>
+      <c r="D27" s="7" t="n">
+        <v>56.08399377388404</v>
+      </c>
+      <c r="E27" s="7" t="n">
+        <v>59.92363844207513</v>
+      </c>
+      <c r="F27" s="7" t="n">
+        <v>61.78609483939085</v>
+      </c>
+      <c r="H27" s="10">
+        <f>MAX(B27:F27)-MIN(B27:F27)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>Terminal growth (at base cost of capital)  (3% / 4% / 5% / 6% / 7%)</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="n">
+        <v>52.6302713847032</v>
+      </c>
+      <c r="C28" s="7" t="n">
+        <v>54.24351203947743</v>
+      </c>
+      <c r="D28" s="7" t="n">
+        <v>56.08399377388404</v>
+      </c>
+      <c r="E28" s="7" t="n">
+        <v>58.22034038779206</v>
+      </c>
+      <c r="F28" s="7" t="n">
+        <v>60.75189974055389</v>
+      </c>
+      <c r="H28" s="10">
+        <f>MAX(B28:F28)-MIN(B28:F28)</f>
         <v/>
       </c>
     </row>
@@ -3402,35 +3471,35 @@
           <t>Net debt / EBITDA</t>
         </is>
       </c>
-      <c r="B14" s="34">
+      <c r="B14" s="35">
         <f>'Balance Sheet'!B18</f>
         <v/>
       </c>
-      <c r="C14" s="34">
+      <c r="C14" s="35">
         <f>'Balance Sheet'!C18</f>
         <v/>
       </c>
-      <c r="D14" s="34">
+      <c r="D14" s="35">
         <f>'Balance Sheet'!D18</f>
         <v/>
       </c>
-      <c r="E14" s="34">
+      <c r="E14" s="35">
         <f>'Balance Sheet'!E18</f>
         <v/>
       </c>
-      <c r="F14" s="34">
+      <c r="F14" s="35">
         <f>'Balance Sheet'!F18</f>
         <v/>
       </c>
-      <c r="G14" s="34">
+      <c r="G14" s="35">
         <f>'Balance Sheet'!G18</f>
         <v/>
       </c>
-      <c r="H14" s="34">
+      <c r="H14" s="35">
         <f>'Balance Sheet'!H18</f>
         <v/>
       </c>
-      <c r="I14" s="34">
+      <c r="I14" s="35">
         <f>'Balance Sheet'!I18</f>
         <v/>
       </c>
@@ -3441,36 +3510,36 @@
           <t>Interest cover (EBIT / net interest)</t>
         </is>
       </c>
-      <c r="B15" s="34" t="inlineStr">
+      <c r="B15" s="35" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C15" s="34">
+      <c r="C15" s="35">
         <f>-'Income Statement'!C10/'Income Statement'!C11</f>
         <v/>
       </c>
-      <c r="D15" s="34">
+      <c r="D15" s="35">
         <f>-'Income Statement'!D10/'Income Statement'!D11</f>
         <v/>
       </c>
-      <c r="E15" s="34">
+      <c r="E15" s="35">
         <f>-'Income Statement'!E10/'Income Statement'!E11</f>
         <v/>
       </c>
-      <c r="F15" s="34">
+      <c r="F15" s="35">
         <f>-'Income Statement'!F10/'Income Statement'!F11</f>
         <v/>
       </c>
-      <c r="G15" s="34">
+      <c r="G15" s="35">
         <f>-'Income Statement'!G10/'Income Statement'!G11</f>
         <v/>
       </c>
-      <c r="H15" s="34">
+      <c r="H15" s="35">
         <f>-'Income Statement'!H10/'Income Statement'!H11</f>
         <v/>
       </c>
-      <c r="I15" s="34">
+      <c r="I15" s="35">
         <f>-'Income Statement'!I10/'Income Statement'!I11</f>
         <v/>
       </c>
@@ -3812,7 +3881,7 @@
           <t>Trailing enterprise value / EBITDA</t>
         </is>
       </c>
-      <c r="B11" s="32">
+      <c r="B11" s="33">
         <f>'Relative &amp; Normalized'!C13</f>
         <v/>
       </c>
@@ -3823,7 +3892,7 @@
           <t>Trailing price / earnings</t>
         </is>
       </c>
-      <c r="B12" s="32">
+      <c r="B12" s="33">
         <f>'Relative &amp; Normalized'!C14</f>
         <v/>
       </c>
@@ -3834,7 +3903,7 @@
           <t>Trailing price / book</t>
         </is>
       </c>
-      <c r="B13" s="32">
+      <c r="B13" s="33">
         <f>'Relative &amp; Normalized'!C15</f>
         <v/>
       </c>
@@ -3845,7 +3914,7 @@
           <t>Justified enterprise value / EBITDA applied</t>
         </is>
       </c>
-      <c r="B14" s="32">
+      <c r="B14" s="33">
         <f>'Relative &amp; Normalized'!C6</f>
         <v/>
       </c>
@@ -3856,7 +3925,7 @@
           <t>Justified price / earnings applied</t>
         </is>
       </c>
-      <c r="B15" s="32">
+      <c r="B15" s="33">
         <f>'Relative &amp; Normalized'!C27</f>
         <v/>
       </c>
@@ -3948,14 +4017,14 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>21.43294146720748</v>
+        <v>19.945090316451</v>
       </c>
       <c r="C5" s="8">
-        <f>DCF!C31</f>
+        <f>DCF!C62</f>
         <v/>
       </c>
       <c r="D5" s="7" t="n">
-        <v>125.1947652327141</v>
+        <v>122.3348933382508</v>
       </c>
       <c r="E5" s="9" t="n">
         <v>0.45</v>
@@ -3975,15 +4044,17 @@
           <t>Relative multiples</t>
         </is>
       </c>
-      <c r="B6" s="7" t="n">
-        <v>56.37443764397884</v>
+      <c r="B6" s="8">
+        <f>'Relative &amp; Normalized'!C12</f>
+        <v/>
       </c>
       <c r="C6" s="8">
         <f>'Relative &amp; Normalized'!C11</f>
         <v/>
       </c>
-      <c r="D6" s="7" t="n">
-        <v>84.64625944108809</v>
+      <c r="D6" s="8">
+        <f>'Relative &amp; Normalized'!D12</f>
+        <v/>
       </c>
       <c r="E6" s="9" t="n">
         <v>0.2</v>
@@ -4003,15 +4074,17 @@
           <t>Normalised earnings power</t>
         </is>
       </c>
-      <c r="B7" s="7" t="n">
-        <v>92.75547847378519</v>
+      <c r="B7" s="8">
+        <f>'Relative &amp; Normalized'!E28</f>
+        <v/>
       </c>
       <c r="C7" s="8">
         <f>'Relative &amp; Normalized'!C28</f>
         <v/>
       </c>
-      <c r="D7" s="7" t="n">
-        <v>152.38400034979</v>
+      <c r="D7" s="8">
+        <f>'Relative &amp; Normalized'!F28</f>
+        <v/>
       </c>
       <c r="E7" s="9" t="n">
         <v>0.2</v>
@@ -4031,15 +4104,17 @@
           <t>Book value and sustainable return</t>
         </is>
       </c>
-      <c r="B8" s="7" t="n">
-        <v>32.0435151429293</v>
+      <c r="B8" s="8">
+        <f>'Relative &amp; Normalized'!E36</f>
+        <v/>
       </c>
       <c r="C8" s="8">
         <f>'Relative &amp; Normalized'!C36</f>
         <v/>
       </c>
-      <c r="D8" s="7" t="n">
-        <v>50.97131575829435</v>
+      <c r="D8" s="8">
+        <f>'Relative &amp; Normalized'!F36</f>
+        <v/>
       </c>
       <c r="E8" s="9" t="n">
         <v>0.15</v>
@@ -4311,7 +4386,7 @@
         </is>
       </c>
       <c r="C5" s="8">
-        <f>DCF!C31</f>
+        <f>DCF!C62</f>
         <v/>
       </c>
     </row>
@@ -4327,7 +4402,7 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>21.43294146720748</v>
+        <v>19.945090316451</v>
       </c>
     </row>
     <row r="7">
@@ -4342,7 +4417,7 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>125.1947652327141</v>
+        <v>122.3348933382508</v>
       </c>
     </row>
     <row r="8">
@@ -4430,7 +4505,7 @@
       </c>
       <c r="C16" s="21" t="inlineStr">
         <is>
-          <t>26.6% → 14.8%</t>
+          <t>26.6% → 15.9%</t>
         </is>
       </c>
     </row>
@@ -4440,8 +4515,9 @@
           <t>Hard-currency cost of capital for the foreign leg</t>
         </is>
       </c>
-      <c r="C17" s="9" t="n">
-        <v>0.101275</v>
+      <c r="C17" s="22">
+        <f>(1-Assumptions!$C$59)*(Assumptions!$C$56+Assumptions!$C$33*Assumptions!$C$57)+Assumptions!$C$59*Assumptions!$C$58*(1-Assumptions!$C$7)</f>
+        <v/>
       </c>
     </row>
     <row r="18">
@@ -4451,7 +4527,7 @@
         </is>
       </c>
       <c r="C18" s="7" t="n">
-        <v>78.89124097524397</v>
+        <v>85.97488545126602</v>
       </c>
     </row>
     <row r="19">
@@ -4511,13 +4587,13 @@
         </is>
       </c>
       <c r="C23" s="7" t="n">
-        <v>127.9603292598724</v>
+        <v>146.6166527148279</v>
       </c>
       <c r="D23" s="7" t="n">
-        <v>94.28655840201122</v>
+        <v>107.5464809477679</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>161.6341001177335</v>
+        <v>185.6868244818879</v>
       </c>
     </row>
     <row r="24">
@@ -4532,13 +4608,13 @@
         </is>
       </c>
       <c r="C24" s="7" t="n">
-        <v>54.95725953296358</v>
+        <v>61.91445272087842</v>
       </c>
       <c r="D24" s="7" t="n">
-        <v>33.89122768954719</v>
+        <v>37.47247721279566</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>60.2787820431655</v>
+        <v>68.08877752143243</v>
       </c>
     </row>
     <row r="25">
@@ -4553,13 +4629,13 @@
         </is>
       </c>
       <c r="C25" s="7" t="n">
-        <v>54.07311304584361</v>
+        <v>53.24641887790025</v>
       </c>
       <c r="D25" s="7" t="n">
-        <v>45.06525322726745</v>
+        <v>46.17387104421569</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>78.89124097524397</v>
+        <v>85.97488545126602</v>
       </c>
     </row>
     <row r="26">
@@ -4587,7 +4663,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H60"/>
+  <dimension ref="A1:H69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -4683,7 +4759,7 @@
           <t>Shares outstanding (mn)</t>
         </is>
       </c>
-      <c r="C6" s="22" t="n">
+      <c r="C6" s="23" t="n">
         <v>2140.777876</v>
       </c>
     </row>
@@ -4713,7 +4789,7 @@
           <t>FY2025 average USD/EGP</t>
         </is>
       </c>
-      <c r="C9" s="23" t="n">
+      <c r="C9" s="24" t="n">
         <v>49.5</v>
       </c>
     </row>
@@ -4737,19 +4813,19 @@
           <t>Copper (USD/tonne)</t>
         </is>
       </c>
-      <c r="B12" s="22" t="n">
+      <c r="B12" s="23" t="n">
         <v>13400</v>
       </c>
-      <c r="C12" s="22" t="n">
+      <c r="C12" s="23" t="n">
         <v>14000</v>
       </c>
-      <c r="D12" s="22" t="n">
+      <c r="D12" s="23" t="n">
         <v>14000</v>
       </c>
-      <c r="E12" s="22" t="n">
+      <c r="E12" s="23" t="n">
         <v>14000</v>
       </c>
-      <c r="F12" s="22" t="n">
+      <c r="F12" s="23" t="n">
         <v>14000</v>
       </c>
     </row>
@@ -4759,19 +4835,19 @@
           <t>USD/EGP path</t>
         </is>
       </c>
-      <c r="B13" s="23" t="n">
+      <c r="B13" s="24" t="n">
         <v>51</v>
       </c>
-      <c r="C13" s="23" t="n">
+      <c r="C13" s="24" t="n">
         <v>54</v>
       </c>
-      <c r="D13" s="23" t="n">
+      <c r="D13" s="24" t="n">
         <v>57.5</v>
       </c>
-      <c r="E13" s="23" t="n">
+      <c r="E13" s="24" t="n">
         <v>61</v>
       </c>
-      <c r="F13" s="23" t="n">
+      <c r="F13" s="24" t="n">
         <v>64.5</v>
       </c>
     </row>
@@ -4928,19 +5004,19 @@
         </is>
       </c>
       <c r="B22" s="9" t="n">
-        <v>0.033</v>
+        <v>0.0455</v>
       </c>
       <c r="C22" s="9" t="n">
-        <v>0.034</v>
+        <v>0.0465</v>
       </c>
       <c r="D22" s="9" t="n">
-        <v>0.035</v>
+        <v>0.0475</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>0.035</v>
+        <v>0.0475</v>
       </c>
       <c r="F22" s="9" t="n">
-        <v>0.036</v>
+        <v>0.0485</v>
       </c>
     </row>
     <row r="24">
@@ -5049,7 +5125,7 @@
           <t>Beta</t>
         </is>
       </c>
-      <c r="C33" s="24" t="n">
+      <c r="C33" s="25" t="n">
         <v>1.009</v>
       </c>
     </row>
@@ -5122,7 +5198,7 @@
         </is>
       </c>
       <c r="C39" s="9" t="n">
-        <v>0.25</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="40">
@@ -5155,7 +5231,7 @@
           <t>Net bank debt at FY2025 (EGP mn, disclosed)</t>
         </is>
       </c>
-      <c r="C43" s="22" t="n">
+      <c r="C43" s="23" t="n">
         <v>20560.003173</v>
       </c>
     </row>
@@ -5165,7 +5241,7 @@
           <t>Equity-accounted investees at carrying value (EGP mn)</t>
         </is>
       </c>
-      <c r="C44" s="22" t="n">
+      <c r="C44" s="23" t="n">
         <v>6757.650507</v>
       </c>
     </row>
@@ -5175,7 +5251,7 @@
           <t>Intangible assets and goodwill (EGP mn)</t>
         </is>
       </c>
-      <c r="C45" s="22" t="n">
+      <c r="C45" s="23" t="n">
         <v>1748.816945</v>
       </c>
     </row>
@@ -5185,7 +5261,7 @@
           <t>FY2025 profit after tax (EGP mn, disclosed)</t>
         </is>
       </c>
-      <c r="C46" s="22" t="n">
+      <c r="C46" s="23" t="n">
         <v>19186.550057</v>
       </c>
     </row>
@@ -5195,7 +5271,7 @@
           <t>FY2025 profit after minority interests (EGP mn, disclosed)</t>
         </is>
       </c>
-      <c r="C47" s="22" t="n">
+      <c r="C47" s="23" t="n">
         <v>17330.24499</v>
       </c>
     </row>
@@ -5212,114 +5288,198 @@
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>Forecast dividend payout ratio</t>
-        </is>
-      </c>
-      <c r="C49" s="9" t="n">
-        <v>0.15</v>
+          <t>FY2025 dividend per share (EGP, ratified 6 May 2026, paid 4 June 2026)</t>
+        </is>
+      </c>
+      <c r="C49" s="7" t="n">
+        <v>1.85</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>Growth in the share of equity-accounted investees</t>
+          <t>Forecast dividend payout ratio (struck at the actual FY2025 rate)</t>
         </is>
       </c>
       <c r="C50" s="9" t="n">
-        <v>0.08</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>Yield assumed on surplus cash</t>
+          <t>Growth in the share of equity-accounted investees</t>
         </is>
       </c>
       <c r="C51" s="9" t="n">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>Yield assumed on surplus cash (blend of EGP deposit and hard-currency rates)</t>
+        </is>
+      </c>
+      <c r="C52" s="9" t="n">
         <v>0.1</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="12" t="inlineStr">
-        <is>
-          <t>Lens inputs</t>
-        </is>
-      </c>
-      <c r="B53" s="15" t="n"/>
-      <c r="C53" s="15" t="n"/>
-      <c r="D53" s="15" t="n"/>
-      <c r="E53" s="15" t="n"/>
-      <c r="F53" s="15" t="n"/>
-      <c r="G53" s="15" t="n"/>
-      <c r="H53" s="15" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="6" t="inlineStr">
-        <is>
-          <t>Justified EV/EBITDA</t>
-        </is>
-      </c>
-      <c r="C54" s="25" t="n">
-        <v>6.5</v>
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>Days from the 31-Dec-2025 valuation date to the 5-Aug-2026 anchor</t>
+        </is>
+      </c>
+      <c r="C53" s="23" t="n">
+        <v>217</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="6" t="inlineStr">
-        <is>
-          <t>Justified price/earnings</t>
-        </is>
-      </c>
-      <c r="C55" s="25" t="n">
-        <v>9</v>
-      </c>
+      <c r="A55" s="12" t="inlineStr">
+        <is>
+          <t>Currency-of-discounting alternative</t>
+        </is>
+      </c>
+      <c r="B55" s="15" t="n"/>
+      <c r="C55" s="15" t="n"/>
+      <c r="D55" s="15" t="n"/>
+      <c r="E55" s="15" t="n"/>
+      <c r="F55" s="15" t="n"/>
+      <c r="G55" s="15" t="n"/>
+      <c r="H55" s="15" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
         <is>
-          <t>Sustainable return on equity</t>
+          <t>US dollar risk-free rate</t>
         </is>
       </c>
       <c r="C56" s="9" t="n">
-        <v>0.235</v>
+        <v>0.043</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="6" t="inlineStr">
         <is>
-          <t>Weight — discounted cash flow</t>
+          <t>Hard-currency-leg equity risk premium</t>
         </is>
       </c>
       <c r="C57" s="9" t="n">
-        <v>0.45</v>
+        <v>0.075</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
         <is>
-          <t>Weight — relative</t>
+          <t>US dollar cost of debt</t>
         </is>
       </c>
       <c r="C58" s="9" t="n">
-        <v>0.2</v>
+        <v>0.065</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="6" t="inlineStr">
         <is>
-          <t>Weight — normalised</t>
+          <t>Debt weight, USD leg</t>
         </is>
       </c>
       <c r="C59" s="9" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
         <is>
+          <t>Terminal growth of the USD leg</t>
+        </is>
+      </c>
+      <c r="C60" s="9" t="n">
+        <v>0.035</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="12" t="inlineStr">
+        <is>
+          <t>Lens inputs</t>
+        </is>
+      </c>
+      <c r="B62" s="15" t="n"/>
+      <c r="C62" s="15" t="n"/>
+      <c r="D62" s="15" t="n"/>
+      <c r="E62" s="15" t="n"/>
+      <c r="F62" s="15" t="n"/>
+      <c r="G62" s="15" t="n"/>
+      <c r="H62" s="15" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>Justified EV/EBITDA</t>
+        </is>
+      </c>
+      <c r="C63" s="26" t="n">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t>Justified price/earnings</t>
+        </is>
+      </c>
+      <c r="C64" s="26" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="6" t="inlineStr">
+        <is>
+          <t>Sustainable return on equity</t>
+        </is>
+      </c>
+      <c r="C65" s="9" t="n">
+        <v>0.235</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t>Weight — discounted cash flow</t>
+        </is>
+      </c>
+      <c r="C66" s="9" t="n">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="6" t="inlineStr">
+        <is>
+          <t>Weight — relative</t>
+        </is>
+      </c>
+      <c r="C67" s="9" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="6" t="inlineStr">
+        <is>
+          <t>Weight — normalised</t>
+        </is>
+      </c>
+      <c r="C68" s="9" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="6" t="inlineStr">
+        <is>
           <t>Weight — book</t>
         </is>
       </c>
-      <c r="C60" s="9" t="n">
+      <c r="C69" s="9" t="n">
         <v>0.15</v>
       </c>
     </row>
@@ -5408,11 +5568,11 @@
           <t>Enterprise value</t>
         </is>
       </c>
-      <c r="C7" s="26">
+      <c r="C7" s="27">
         <f>C5+C6</f>
         <v/>
       </c>
-      <c r="D7" s="27">
+      <c r="D7" s="28">
         <f>C7/Assumptions!$C$6</f>
         <v/>
       </c>
@@ -5453,7 +5613,7 @@
           <t>Equity before minority interests</t>
         </is>
       </c>
-      <c r="C10" s="28">
+      <c r="C10" s="29">
         <f>C7+C8+C9</f>
         <v/>
       </c>
@@ -5468,7 +5628,7 @@
           <t>Less minority interests at their share of group profit</t>
         </is>
       </c>
-      <c r="C11" s="28">
+      <c r="C11" s="29">
         <f>-C10*$C$15</f>
         <v/>
       </c>
@@ -5484,11 +5644,11 @@
         </is>
       </c>
       <c r="B12" s="15" t="n"/>
-      <c r="C12" s="29">
+      <c r="C12" s="30">
         <f>C10+C11</f>
         <v/>
       </c>
-      <c r="D12" s="30">
+      <c r="D12" s="31">
         <f>C12/Assumptions!$C$6</f>
         <v/>
       </c>
@@ -5526,7 +5686,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5580,7 +5740,7 @@
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>Gross margin</t>
+          <t>Segment margin</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -5615,7 +5775,7 @@
           <t>Cables and its accessories</t>
         </is>
       </c>
-      <c r="B5" s="22" t="n">
+      <c r="B5" s="23" t="n">
         <v>155792.929738</v>
       </c>
       <c r="C5" s="11">
@@ -5625,19 +5785,19 @@
       <c r="D5" s="9" t="n">
         <v>0.134899552356732</v>
       </c>
-      <c r="E5" s="22" t="n">
+      <c r="E5" s="23" t="n">
         <v>221541.3228857327</v>
       </c>
-      <c r="F5" s="22" t="n">
+      <c r="F5" s="23" t="n">
         <v>252428.7347156312</v>
       </c>
-      <c r="G5" s="22" t="n">
+      <c r="G5" s="23" t="n">
         <v>276853.5521024677</v>
       </c>
-      <c r="H5" s="22" t="n">
+      <c r="H5" s="23" t="n">
         <v>302516.6726712704</v>
       </c>
-      <c r="I5" s="22" t="n">
+      <c r="I5" s="23" t="n">
         <v>329470.412277309</v>
       </c>
     </row>
@@ -5647,7 +5807,7 @@
           <t>Constructions and infrastructure</t>
         </is>
       </c>
-      <c r="B6" s="22" t="n">
+      <c r="B6" s="23" t="n">
         <v>90958.55022799999</v>
       </c>
       <c r="C6" s="11">
@@ -5657,19 +5817,19 @@
       <c r="D6" s="9" t="n">
         <v>0.06452269254829619</v>
       </c>
-      <c r="E6" s="22" t="n">
+      <c r="E6" s="23" t="n">
         <v>107331.08926904</v>
       </c>
-      <c r="F6" s="22" t="n">
+      <c r="F6" s="23" t="n">
         <v>122357.4417667056</v>
       </c>
-      <c r="G6" s="22" t="n">
+      <c r="G6" s="23" t="n">
         <v>135816.7603610432</v>
       </c>
-      <c r="H6" s="22" t="n">
+      <c r="H6" s="23" t="n">
         <v>148040.2687935371</v>
       </c>
-      <c r="I6" s="22" t="n">
+      <c r="I6" s="23" t="n">
         <v>159883.4902970201</v>
       </c>
     </row>
@@ -5679,7 +5839,7 @@
           <t>Electrical products and digital solutions</t>
         </is>
       </c>
-      <c r="B7" s="22" t="n">
+      <c r="B7" s="23" t="n">
         <v>34297.601753</v>
       </c>
       <c r="C7" s="11">
@@ -5689,19 +5849,19 @@
       <c r="D7" s="9" t="n">
         <v>0.2217300370961013</v>
       </c>
-      <c r="E7" s="22" t="n">
+      <c r="E7" s="23" t="n">
         <v>41157.1221036</v>
       </c>
-      <c r="F7" s="22" t="n">
+      <c r="F7" s="23" t="n">
         <v>47742.261640176</v>
       </c>
-      <c r="G7" s="22" t="n">
+      <c r="G7" s="23" t="n">
         <v>53948.75565339887</v>
       </c>
-      <c r="H7" s="22" t="n">
+      <c r="H7" s="23" t="n">
         <v>59883.11877527275</v>
       </c>
-      <c r="I7" s="22" t="n">
+      <c r="I7" s="23" t="n">
         <v>65871.43065280003</v>
       </c>
     </row>
@@ -5711,7 +5871,7 @@
           <t>Total revenue</t>
         </is>
       </c>
-      <c r="B8" s="31">
+      <c r="B8" s="32">
         <f>SUM(B5:B7)</f>
         <v/>
       </c>
@@ -5720,23 +5880,23 @@
         <v/>
       </c>
       <c r="D8" s="15" t="n"/>
-      <c r="E8" s="31">
+      <c r="E8" s="32">
         <f>SUM(E5:E7)</f>
         <v/>
       </c>
-      <c r="F8" s="31">
+      <c r="F8" s="32">
         <f>SUM(F5:F7)</f>
         <v/>
       </c>
-      <c r="G8" s="31">
+      <c r="G8" s="32">
         <f>SUM(G5:G7)</f>
         <v/>
       </c>
-      <c r="H8" s="31">
+      <c r="H8" s="32">
         <f>SUM(H5:H7)</f>
         <v/>
       </c>
-      <c r="I8" s="31">
+      <c r="I8" s="32">
         <f>SUM(I5:I7)</f>
         <v/>
       </c>
@@ -5744,7 +5904,7 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>Gross profit by segment</t>
+          <t>Segment profit by segment (Note 16 basis)</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
@@ -5779,19 +5939,19 @@
           <t>Cables and its accessories</t>
         </is>
       </c>
-      <c r="B11" s="22" t="n">
+      <c r="B11" s="23" t="n">
         <v>31015.78520400258</v>
       </c>
-      <c r="C11" s="22" t="n">
+      <c r="C11" s="23" t="n">
         <v>36602.16653376652</v>
       </c>
-      <c r="D11" s="22" t="n">
+      <c r="D11" s="23" t="n">
         <v>41528.03281537016</v>
       </c>
-      <c r="E11" s="22" t="n">
+      <c r="E11" s="23" t="n">
         <v>46285.05091870438</v>
       </c>
-      <c r="F11" s="22" t="n">
+      <c r="F11" s="23" t="n">
         <v>51067.91390298289</v>
       </c>
     </row>
@@ -5801,19 +5961,19 @@
           <t>Constructions and infrastructure</t>
         </is>
       </c>
-      <c r="B12" s="22" t="n">
+      <c r="B12" s="23" t="n">
         <v>7298.51407029472</v>
       </c>
-      <c r="C12" s="22" t="n">
+      <c r="C12" s="23" t="n">
         <v>8809.735807202804</v>
       </c>
-      <c r="D12" s="22" t="n">
+      <c r="D12" s="23" t="n">
         <v>10322.07378743929</v>
       </c>
-      <c r="E12" s="22" t="n">
+      <c r="E12" s="23" t="n">
         <v>11695.18123468943</v>
       </c>
-      <c r="F12" s="22" t="n">
+      <c r="F12" s="23" t="n">
         <v>13110.44620435565</v>
       </c>
     </row>
@@ -5823,45 +5983,45 @@
           <t>Electrical products and digital solutions</t>
         </is>
       </c>
-      <c r="B13" s="22" t="n">
+      <c r="B13" s="23" t="n">
         <v>9054.566862792</v>
       </c>
-      <c r="C13" s="22" t="n">
+      <c r="C13" s="23" t="n">
         <v>10598.78208411907</v>
       </c>
-      <c r="D13" s="22" t="n">
+      <c r="D13" s="23" t="n">
         <v>12084.52126636135</v>
       </c>
-      <c r="E13" s="22" t="n">
+      <c r="E13" s="23" t="n">
         <v>13533.58484321164</v>
       </c>
-      <c r="F13" s="22" t="n">
+      <c r="F13" s="23" t="n">
         <v>15018.68618883841</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>Group gross profit</t>
-        </is>
-      </c>
-      <c r="B14" s="31">
+          <t>Group segment profit</t>
+        </is>
+      </c>
+      <c r="B14" s="32">
         <f>SUM(B11:B13)</f>
         <v/>
       </c>
-      <c r="C14" s="31">
+      <c r="C14" s="32">
         <f>SUM(C11:C13)</f>
         <v/>
       </c>
-      <c r="D14" s="31">
+      <c r="D14" s="32">
         <f>SUM(D11:D13)</f>
         <v/>
       </c>
-      <c r="E14" s="31">
+      <c r="E14" s="32">
         <f>SUM(E11:E13)</f>
         <v/>
       </c>
-      <c r="F14" s="31">
+      <c r="F14" s="32">
         <f>SUM(F11:F13)</f>
         <v/>
       </c>
@@ -5869,7 +6029,7 @@
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>Group gross margin</t>
+          <t>Group segment-profit margin</t>
         </is>
       </c>
       <c r="B15" s="11">
@@ -5896,7 +6056,7 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>Segment EBITDA — gross profit less the operating load</t>
+          <t>Segment EBIT contribution — segment profit less the pro-rata corporate load</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
@@ -5931,23 +6091,23 @@
           <t>Cables and its accessories</t>
         </is>
       </c>
-      <c r="B18" s="28">
+      <c r="B18" s="29">
         <f>B11-Assumptions!$B$22*E5</f>
         <v/>
       </c>
-      <c r="C18" s="28">
+      <c r="C18" s="29">
         <f>C11-Assumptions!$C$22*F5</f>
         <v/>
       </c>
-      <c r="D18" s="28">
+      <c r="D18" s="29">
         <f>D11-Assumptions!$D$22*G5</f>
         <v/>
       </c>
-      <c r="E18" s="28">
+      <c r="E18" s="29">
         <f>E11-Assumptions!$E$22*H5</f>
         <v/>
       </c>
-      <c r="F18" s="28">
+      <c r="F18" s="29">
         <f>F11-Assumptions!$F$22*I5</f>
         <v/>
       </c>
@@ -5958,23 +6118,23 @@
           <t>Constructions and infrastructure</t>
         </is>
       </c>
-      <c r="B19" s="28">
+      <c r="B19" s="29">
         <f>B12-Assumptions!$B$22*E6</f>
         <v/>
       </c>
-      <c r="C19" s="28">
+      <c r="C19" s="29">
         <f>C12-Assumptions!$C$22*F6</f>
         <v/>
       </c>
-      <c r="D19" s="28">
+      <c r="D19" s="29">
         <f>D12-Assumptions!$D$22*G6</f>
         <v/>
       </c>
-      <c r="E19" s="28">
+      <c r="E19" s="29">
         <f>E12-Assumptions!$E$22*H6</f>
         <v/>
       </c>
-      <c r="F19" s="28">
+      <c r="F19" s="29">
         <f>F12-Assumptions!$F$22*I6</f>
         <v/>
       </c>
@@ -5985,23 +6145,23 @@
           <t>Electrical products and digital solutions</t>
         </is>
       </c>
-      <c r="B20" s="28">
+      <c r="B20" s="29">
         <f>B13-Assumptions!$B$22*E7</f>
         <v/>
       </c>
-      <c r="C20" s="28">
+      <c r="C20" s="29">
         <f>C13-Assumptions!$C$22*F7</f>
         <v/>
       </c>
-      <c r="D20" s="28">
+      <c r="D20" s="29">
         <f>D13-Assumptions!$D$22*G7</f>
         <v/>
       </c>
-      <c r="E20" s="28">
+      <c r="E20" s="29">
         <f>E13-Assumptions!$E$22*H7</f>
         <v/>
       </c>
-      <c r="F20" s="28">
+      <c r="F20" s="29">
         <f>F13-Assumptions!$F$22*I7</f>
         <v/>
       </c>
@@ -6009,26 +6169,26 @@
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>Group EBITDA</t>
-        </is>
-      </c>
-      <c r="B21" s="31">
+          <t>Group EBIT</t>
+        </is>
+      </c>
+      <c r="B21" s="32">
         <f>SUM(B18:B20)</f>
         <v/>
       </c>
-      <c r="C21" s="31">
+      <c r="C21" s="32">
         <f>SUM(C18:C20)</f>
         <v/>
       </c>
-      <c r="D21" s="31">
+      <c r="D21" s="32">
         <f>SUM(D18:D20)</f>
         <v/>
       </c>
-      <c r="E21" s="31">
+      <c r="E21" s="32">
         <f>SUM(E18:E20)</f>
         <v/>
       </c>
-      <c r="F21" s="31">
+      <c r="F21" s="32">
         <f>SUM(F18:F20)</f>
         <v/>
       </c>
@@ -6036,28 +6196,89 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
+          <t>Add back depreciation and amortisation</t>
+        </is>
+      </c>
+      <c r="B22" s="29">
+        <f>Assumptions!$C$27*E8</f>
+        <v/>
+      </c>
+      <c r="C22" s="29">
+        <f>Assumptions!$C$27*F8</f>
+        <v/>
+      </c>
+      <c r="D22" s="29">
+        <f>Assumptions!$C$27*G8</f>
+        <v/>
+      </c>
+      <c r="E22" s="29">
+        <f>Assumptions!$C$27*H8</f>
+        <v/>
+      </c>
+      <c r="F22" s="29">
+        <f>Assumptions!$C$27*I8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>Group EBITDA</t>
+        </is>
+      </c>
+      <c r="B23" s="32">
+        <f>B21+B22</f>
+        <v/>
+      </c>
+      <c r="C23" s="32">
+        <f>C21+C22</f>
+        <v/>
+      </c>
+      <c r="D23" s="32">
+        <f>D21+D22</f>
+        <v/>
+      </c>
+      <c r="E23" s="32">
+        <f>E21+E22</f>
+        <v/>
+      </c>
+      <c r="F23" s="32">
+        <f>F21+F22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
           <t>Group EBITDA margin</t>
         </is>
       </c>
-      <c r="B22" s="11">
-        <f>B21/E$8</f>
-        <v/>
-      </c>
-      <c r="C22" s="11">
-        <f>C21/F$8</f>
-        <v/>
-      </c>
-      <c r="D22" s="11">
-        <f>D21/G$8</f>
-        <v/>
-      </c>
-      <c r="E22" s="11">
-        <f>E21/H$8</f>
-        <v/>
-      </c>
-      <c r="F22" s="11">
-        <f>F21/I$8</f>
-        <v/>
+      <c r="B24" s="11">
+        <f>B23/E$8</f>
+        <v/>
+      </c>
+      <c r="C24" s="11">
+        <f>C23/F$8</f>
+        <v/>
+      </c>
+      <c r="D24" s="11">
+        <f>D23/G$8</f>
+        <v/>
+      </c>
+      <c r="E24" s="11">
+        <f>E23/H$8</f>
+        <v/>
+      </c>
+      <c r="F24" s="11">
+        <f>F23/I$8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>The corporate load is stated on the segment-profit-to-EBIT basis — the same basis as the audited historical bridge — so EBIT falls out first and EBITDA is EBIT plus D&amp;A, not the other way round.</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -6071,7 +6292,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -6121,8 +6342,8 @@
           <t>Justified enterprise value / EBITDA</t>
         </is>
       </c>
-      <c r="C6" s="32">
-        <f>Assumptions!$C$54</f>
+      <c r="C6" s="33">
+        <f>Assumptions!$C$63</f>
         <v/>
       </c>
     </row>
@@ -6132,7 +6353,7 @@
           <t>Implied enterprise value AS AT end-FY2027 (EGP mn)</t>
         </is>
       </c>
-      <c r="C7" s="28">
+      <c r="C7" s="29">
         <f>C5*C6</f>
         <v/>
       </c>
@@ -6140,10 +6361,10 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Discount factor back to today (year-2)</t>
-        </is>
-      </c>
-      <c r="C8" s="33">
+          <t>Discount factor back to the valuation date (year-2)</t>
+        </is>
+      </c>
+      <c r="C8" s="34">
         <f>DCF!C16</f>
         <v/>
       </c>
@@ -6151,34 +6372,49 @@
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>Implied enterprise value TODAY (EGP mn)</t>
-        </is>
-      </c>
-      <c r="C9" s="28">
-        <f>C7*C8</f>
+          <t>Plus present value of the interim FY26-27 free cash flows (EGP mn)</t>
+        </is>
+      </c>
+      <c r="C9" s="18">
+        <f>DCF!B17+DCF!C17</f>
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Less net bank debt, plus associates (EGP mn)</t>
-        </is>
-      </c>
-      <c r="C10" s="28">
-        <f>-Assumptions!$C$43+Assumptions!$C$44</f>
+          <t>Implied enterprise value at 31-Dec-2025 (EGP mn)</t>
+        </is>
+      </c>
+      <c r="C10" s="29">
+        <f>C7*C8+C9</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>Implied value per share (EGP)</t>
+          <t>Implied value per share, rolled to the anchor (EGP)</t>
         </is>
       </c>
       <c r="B11" s="15" t="n"/>
-      <c r="C11" s="30">
-        <f>(C9+C10)*(1-'SOTP Bridge'!$C$15)/Assumptions!$C$6</f>
+      <c r="C11" s="31">
+        <f>((C10-Assumptions!$C$43+Assumptions!$C$44)*(1-'SOTP Bridge'!$C$15)/Assumptions!$C$6)*DCF!$C$61-Assumptions!$C$49</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Bear at 5.5× (C) / bull at 8.0× (D), same construction</t>
+        </is>
+      </c>
+      <c r="C12" s="10">
+        <f>((5.5*C5*C8+C9-Assumptions!$C$43+Assumptions!$C$44)*(1-'SOTP Bridge'!$C$15)/Assumptions!$C$6)*DCF!$C$61-Assumptions!$C$49</f>
+        <v/>
+      </c>
+      <c r="D12" s="10">
+        <f>((8.0*C5*C8+C9-Assumptions!$C$43+Assumptions!$C$44)*(1-'SOTP Bridge'!$C$15)/Assumptions!$C$6)*DCF!$C$61-Assumptions!$C$49</f>
         <v/>
       </c>
     </row>
@@ -6188,7 +6424,7 @@
           <t>Trailing enterprise value / EBITDA</t>
         </is>
       </c>
-      <c r="C13" s="34">
+      <c r="C13" s="35">
         <f>((Assumptions!$C$5*Assumptions!$C$6)+Assumptions!$C$43)/'Income Statement'!D7</f>
         <v/>
       </c>
@@ -6199,7 +6435,7 @@
           <t>Trailing price / earnings</t>
         </is>
       </c>
-      <c r="C14" s="34">
+      <c r="C14" s="35">
         <f>Assumptions!$C$5/'Income Statement'!D18</f>
         <v/>
       </c>
@@ -6210,7 +6446,7 @@
           <t>Trailing price / book</t>
         </is>
       </c>
-      <c r="C15" s="34">
+      <c r="C15" s="35">
         <f>Assumptions!$C$5/C31</f>
         <v/>
       </c>
@@ -6221,7 +6457,7 @@
           <t>Net bank debt / EBITDA</t>
         </is>
       </c>
-      <c r="C16" s="34">
+      <c r="C16" s="35">
         <f>Assumptions!$C$43/'Income Statement'!D7</f>
         <v/>
       </c>
@@ -6229,7 +6465,7 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>Normalised earnings lens — every component from the same year (FY2028E)</t>
+          <t>Normalised earnings lens — mid-cycle margin (FY2028E) at current (FY2026E) scale</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
@@ -6241,18 +6477,18 @@
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>Mid-cycle revenue (EGP mn)</t>
+          <t>Current-scale revenue (FY2026E, EGP mn)</t>
         </is>
       </c>
       <c r="C19" s="18">
-        <f>DCF!D5</f>
+        <f>DCF!B5</f>
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Mid-cycle EBITDA margin</t>
+          <t>Mid-cycle EBITDA margin (FY2028E)</t>
         </is>
       </c>
       <c r="C20" s="16">
@@ -6263,10 +6499,10 @@
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>Mid-cycle EBITDA (EGP mn)</t>
-        </is>
-      </c>
-      <c r="C21" s="28">
+          <t>Normalised EBITDA (EGP mn)</t>
+        </is>
+      </c>
+      <c r="C21" s="29">
         <f>C19*C20</f>
         <v/>
       </c>
@@ -6274,10 +6510,10 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Mid-cycle EBIT (EGP mn)</t>
-        </is>
-      </c>
-      <c r="C22" s="28">
+          <t>Normalised EBIT (EGP mn)</t>
+        </is>
+      </c>
+      <c r="C22" s="29">
         <f>C21-C19*Assumptions!$C$27</f>
         <v/>
       </c>
@@ -6285,22 +6521,22 @@
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>Net finance cost (EGP mn)</t>
+          <t>Net finance cost (FY2026E, EGP mn)</t>
         </is>
       </c>
       <c r="C23" s="18">
-        <f>'Income Statement'!G11</f>
+        <f>'Income Statement'!E11</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Share of equity-accounted investees (EGP mn)</t>
+          <t>Share of equity-accounted investees (FY2026E, EGP mn)</t>
         </is>
       </c>
       <c r="C24" s="18">
-        <f>'Income Statement'!G12</f>
+        <f>'Income Statement'!E12</f>
         <v/>
       </c>
     </row>
@@ -6310,7 +6546,7 @@
           <t>Normalised attributable earnings (EGP mn)</t>
         </is>
       </c>
-      <c r="C25" s="28">
+      <c r="C25" s="29">
         <f>(C22+C23+C24)*(1-Assumptions!$C$7)*(1-'SOTP Bridge'!$C$15)</f>
         <v/>
       </c>
@@ -6332,20 +6568,33 @@
           <t>Justified price / earnings</t>
         </is>
       </c>
-      <c r="C27" s="34">
-        <f>Assumptions!$C$55</f>
+      <c r="C27" s="35">
+        <f>Assumptions!$C$64</f>
         <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="15" t="inlineStr">
         <is>
-          <t>Implied value per share (EGP)</t>
+          <t>Implied value per share, rolled to the anchor (EGP)</t>
         </is>
       </c>
       <c r="B28" s="15" t="n"/>
-      <c r="C28" s="30">
-        <f>C26*C27</f>
+      <c r="C28" s="31">
+        <f>C26*C27*DCF!$C$61-Assumptions!$C$49</f>
+        <v/>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>bear 7.0× (E) / bull 11.5× (F):</t>
+        </is>
+      </c>
+      <c r="E28" s="10">
+        <f>C26*7*DCF!$C$61-Assumptions!$C$49</f>
+        <v/>
+      </c>
+      <c r="F28" s="10">
+        <f>C26*11.5*DCF!$C$61-Assumptions!$C$49</f>
         <v/>
       </c>
     </row>
@@ -6379,7 +6628,7 @@
         </is>
       </c>
       <c r="C32" s="11">
-        <f>Assumptions!$C$56</f>
+        <f>Assumptions!$C$65</f>
         <v/>
       </c>
     </row>
@@ -6397,7 +6646,7 @@
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>Perpetual cost of equity</t>
+          <t>Perpetual (terminal) cost of equity — a steady-state multiple takes a steady-state rate</t>
         </is>
       </c>
       <c r="C34" s="16">
@@ -6411,7 +6660,7 @@
           <t>Justified price / book</t>
         </is>
       </c>
-      <c r="C35" s="34">
+      <c r="C35" s="35">
         <f>(C32-Assumptions!$C$40)/(C34-Assumptions!$C$40)</f>
         <v/>
       </c>
@@ -6419,12 +6668,25 @@
     <row r="36">
       <c r="A36" s="15" t="inlineStr">
         <is>
-          <t>Implied value per share (EGP)</t>
+          <t>Implied value per share, rolled to the anchor (EGP)</t>
         </is>
       </c>
       <c r="B36" s="15" t="n"/>
-      <c r="C36" s="30">
-        <f>C31*C35</f>
+      <c r="C36" s="31">
+        <f>C31*C35*DCF!$C$61-Assumptions!$C$49</f>
+        <v/>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>bear / bull constructions (E / F):</t>
+        </is>
+      </c>
+      <c r="E36" s="10">
+        <f>((Assumptions!$C$65-0.03)/((DCF!C39+DCF!C49)/2-0.03))*C31*DCF!$C$61-Assumptions!$C$49</f>
+        <v/>
+      </c>
+      <c r="F36" s="10">
+        <f>((Assumptions!$C$65+0.02-Assumptions!$C$40)/(DCF!C49-Assumptions!$C$40))*C31*DCF!$C$61-Assumptions!$C$49</f>
         <v/>
       </c>
     </row>
@@ -6439,7 +6701,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F58"/>
+  <dimension ref="A1:F63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -6535,23 +6797,23 @@
         </is>
       </c>
       <c r="B6" s="18">
-        <f>Segments!B21</f>
+        <f>Segments!B23</f>
         <v/>
       </c>
       <c r="C6" s="18">
-        <f>Segments!C21</f>
+        <f>Segments!C23</f>
         <v/>
       </c>
       <c r="D6" s="18">
-        <f>Segments!D21</f>
+        <f>Segments!D23</f>
         <v/>
       </c>
       <c r="E6" s="18">
-        <f>Segments!E21</f>
+        <f>Segments!E23</f>
         <v/>
       </c>
       <c r="F6" s="18">
-        <f>Segments!F21</f>
+        <f>Segments!F23</f>
         <v/>
       </c>
     </row>
@@ -6588,23 +6850,23 @@
           <t>Less depreciation and amortisation</t>
         </is>
       </c>
-      <c r="B8" s="28">
+      <c r="B8" s="29">
         <f>-B5*Assumptions!$C$27</f>
         <v/>
       </c>
-      <c r="C8" s="28">
+      <c r="C8" s="29">
         <f>-C5*Assumptions!$C$27</f>
         <v/>
       </c>
-      <c r="D8" s="28">
+      <c r="D8" s="29">
         <f>-D5*Assumptions!$C$27</f>
         <v/>
       </c>
-      <c r="E8" s="28">
+      <c r="E8" s="29">
         <f>-E5*Assumptions!$C$27</f>
         <v/>
       </c>
-      <c r="F8" s="28">
+      <c r="F8" s="29">
         <f>-F5*Assumptions!$C$27</f>
         <v/>
       </c>
@@ -6615,23 +6877,23 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B9" s="29">
+      <c r="B9" s="30">
         <f>B6+B8</f>
         <v/>
       </c>
-      <c r="C9" s="29">
+      <c r="C9" s="30">
         <f>C6+C8</f>
         <v/>
       </c>
-      <c r="D9" s="29">
+      <c r="D9" s="30">
         <f>D6+D8</f>
         <v/>
       </c>
-      <c r="E9" s="29">
+      <c r="E9" s="30">
         <f>E6+E8</f>
         <v/>
       </c>
-      <c r="F9" s="29">
+      <c r="F9" s="30">
         <f>F6+F8</f>
         <v/>
       </c>
@@ -6642,23 +6904,23 @@
           <t>NOPAT — EBIT x (1 - 24%)</t>
         </is>
       </c>
-      <c r="B10" s="28">
+      <c r="B10" s="29">
         <f>B9*(1-Assumptions!$C$7)</f>
         <v/>
       </c>
-      <c r="C10" s="28">
+      <c r="C10" s="29">
         <f>C9*(1-Assumptions!$C$7)</f>
         <v/>
       </c>
-      <c r="D10" s="28">
+      <c r="D10" s="29">
         <f>D9*(1-Assumptions!$C$7)</f>
         <v/>
       </c>
-      <c r="E10" s="28">
+      <c r="E10" s="29">
         <f>E9*(1-Assumptions!$C$7)</f>
         <v/>
       </c>
-      <c r="F10" s="28">
+      <c r="F10" s="29">
         <f>F9*(1-Assumptions!$C$7)</f>
         <v/>
       </c>
@@ -6669,23 +6931,23 @@
           <t>Add back depreciation and amortisation</t>
         </is>
       </c>
-      <c r="B11" s="28">
+      <c r="B11" s="29">
         <f>-B8</f>
         <v/>
       </c>
-      <c r="C11" s="28">
+      <c r="C11" s="29">
         <f>-C8</f>
         <v/>
       </c>
-      <c r="D11" s="28">
+      <c r="D11" s="29">
         <f>-D8</f>
         <v/>
       </c>
-      <c r="E11" s="28">
+      <c r="E11" s="29">
         <f>-E8</f>
         <v/>
       </c>
-      <c r="F11" s="28">
+      <c r="F11" s="29">
         <f>-F8</f>
         <v/>
       </c>
@@ -6696,23 +6958,23 @@
           <t>Less capital expenditure</t>
         </is>
       </c>
-      <c r="B12" s="28">
+      <c r="B12" s="29">
         <f>-B5*Assumptions!$B$26</f>
         <v/>
       </c>
-      <c r="C12" s="28">
+      <c r="C12" s="29">
         <f>-C5*Assumptions!$C$26</f>
         <v/>
       </c>
-      <c r="D12" s="28">
+      <c r="D12" s="29">
         <f>-D5*Assumptions!$D$26</f>
         <v/>
       </c>
-      <c r="E12" s="28">
+      <c r="E12" s="29">
         <f>-E5*Assumptions!$E$26</f>
         <v/>
       </c>
-      <c r="F12" s="28">
+      <c r="F12" s="29">
         <f>-F5*Assumptions!$F$26</f>
         <v/>
       </c>
@@ -6723,23 +6985,23 @@
           <t>Less change in working capital</t>
         </is>
       </c>
-      <c r="B13" s="28">
+      <c r="B13" s="29">
         <f>-(B5*Assumptions!$C$25-'Balance Sheet'!D16)</f>
         <v/>
       </c>
-      <c r="C13" s="28">
+      <c r="C13" s="29">
         <f>-(C5-B5)*Assumptions!$C$25</f>
         <v/>
       </c>
-      <c r="D13" s="28">
+      <c r="D13" s="29">
         <f>-(D5-C5)*Assumptions!$C$25</f>
         <v/>
       </c>
-      <c r="E13" s="28">
+      <c r="E13" s="29">
         <f>-(E5-D5)*Assumptions!$C$25</f>
         <v/>
       </c>
-      <c r="F13" s="28">
+      <c r="F13" s="29">
         <f>-(F5-E5)*Assumptions!$C$25</f>
         <v/>
       </c>
@@ -6750,23 +7012,23 @@
           <t>Free cash flow to the firm</t>
         </is>
       </c>
-      <c r="B14" s="29">
+      <c r="B14" s="30">
         <f>B10+B11+B12+B13</f>
         <v/>
       </c>
-      <c r="C14" s="29">
+      <c r="C14" s="30">
         <f>C10+C11+C12+C13</f>
         <v/>
       </c>
-      <c r="D14" s="29">
+      <c r="D14" s="30">
         <f>D10+D11+D12+D13</f>
         <v/>
       </c>
-      <c r="E14" s="29">
+      <c r="E14" s="30">
         <f>E10+E11+E12+E13</f>
         <v/>
       </c>
-      <c r="F14" s="29">
+      <c r="F14" s="30">
         <f>F10+F11+F12+F13</f>
         <v/>
       </c>
@@ -6777,23 +7039,23 @@
           <t>Forward cost of capital</t>
         </is>
       </c>
-      <c r="B15" s="35">
+      <c r="B15" s="36">
         <f>$C$46-($C$46-$C$53)*B57</f>
         <v/>
       </c>
-      <c r="C15" s="35">
+      <c r="C15" s="36">
         <f>$C$46-($C$46-$C$53)*C57</f>
         <v/>
       </c>
-      <c r="D15" s="35">
+      <c r="D15" s="36">
         <f>$C$46-($C$46-$C$53)*D57</f>
         <v/>
       </c>
-      <c r="E15" s="35">
+      <c r="E15" s="36">
         <f>$C$46-($C$46-$C$53)*E57</f>
         <v/>
       </c>
-      <c r="F15" s="35">
+      <c r="F15" s="36">
         <f>$C$46-($C$46-$C$53)*F57</f>
         <v/>
       </c>
@@ -6804,23 +7066,23 @@
           <t>Discount factor</t>
         </is>
       </c>
-      <c r="B16" s="36">
+      <c r="B16" s="37">
         <f>1/(1+B15)</f>
         <v/>
       </c>
-      <c r="C16" s="36">
+      <c r="C16" s="37">
         <f>B16/(1+C15)</f>
         <v/>
       </c>
-      <c r="D16" s="36">
+      <c r="D16" s="37">
         <f>C16/(1+D15)</f>
         <v/>
       </c>
-      <c r="E16" s="36">
+      <c r="E16" s="37">
         <f>D16/(1+E15)</f>
         <v/>
       </c>
-      <c r="F16" s="36">
+      <c r="F16" s="37">
         <f>E16/(1+F15)</f>
         <v/>
       </c>
@@ -6831,23 +7093,23 @@
           <t>Present value of FCFF</t>
         </is>
       </c>
-      <c r="B17" s="29">
+      <c r="B17" s="30">
         <f>B14*B16</f>
         <v/>
       </c>
-      <c r="C17" s="29">
+      <c r="C17" s="30">
         <f>C14*C16</f>
         <v/>
       </c>
-      <c r="D17" s="29">
+      <c r="D17" s="30">
         <f>D14*D16</f>
         <v/>
       </c>
-      <c r="E17" s="29">
+      <c r="E17" s="30">
         <f>E14*E16</f>
         <v/>
       </c>
-      <c r="F17" s="29">
+      <c r="F17" s="30">
         <f>F14*F16</f>
         <v/>
       </c>
@@ -6855,7 +7117,7 @@
     <row r="19">
       <c r="A19" s="20" t="inlineStr">
         <is>
-          <t>TERMINAL VALUE AND BRIDGE</t>
+          <t>TERMINAL VALUE, BRIDGE AND THE ANCHOR ROLL</t>
         </is>
       </c>
     </row>
@@ -6865,7 +7127,7 @@
           <t>Terminal-year NOPAT grown one year (EGP mn)</t>
         </is>
       </c>
-      <c r="C20" s="28">
+      <c r="C20" s="29">
         <f>F10*(1+C23)</f>
         <v/>
       </c>
@@ -6917,10 +7179,10 @@
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>Terminal value (EGP mn)</t>
-        </is>
-      </c>
-      <c r="C25" s="28">
+          <t>Terminal value — terminal-year FCFF C20×(1−C22), capitalised (EGP mn)</t>
+        </is>
+      </c>
+      <c r="C25" s="29">
         <f>C20*(1-C22)/(C24-C23)</f>
         <v/>
       </c>
@@ -6931,7 +7193,7 @@
           <t>Present value of the five forecast years (EGP mn)</t>
         </is>
       </c>
-      <c r="C26" s="28">
+      <c r="C26" s="29">
         <f>SUM(B17:F17)</f>
         <v/>
       </c>
@@ -6942,7 +7204,7 @@
           <t>Present value of the terminal value (EGP mn)</t>
         </is>
       </c>
-      <c r="C27" s="28">
+      <c r="C27" s="29">
         <f>C25*F16</f>
         <v/>
       </c>
@@ -6964,7 +7226,7 @@
           <t>Enterprise value (EGP mn)</t>
         </is>
       </c>
-      <c r="C29" s="28">
+      <c r="C29" s="29">
         <f>C26+C27</f>
         <v/>
       </c>
@@ -6983,11 +7245,11 @@
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>Fair value per share (EGP)</t>
+          <t>Fair value per share at 31-Dec-2025 (EGP)</t>
         </is>
       </c>
       <c r="B31" s="15" t="n"/>
-      <c r="C31" s="30">
+      <c r="C31" s="31">
         <f>C30/Assumptions!$C$6</f>
         <v/>
       </c>
@@ -7006,7 +7268,7 @@
           <t>Risk-free rate, 10-year local currency</t>
         </is>
       </c>
-      <c r="C34" s="37">
+      <c r="C34" s="22">
         <f>Assumptions!$C$30</f>
         <v/>
       </c>
@@ -7017,7 +7279,7 @@
           <t>Less sovereign default spread (removed to avoid double-counting)</t>
         </is>
       </c>
-      <c r="C35" s="37">
+      <c r="C35" s="22">
         <f>Assumptions!$C$31</f>
         <v/>
       </c>
@@ -7028,7 +7290,7 @@
           <t>Risk-free rate net of the sovereign spread</t>
         </is>
       </c>
-      <c r="C36" s="35">
+      <c r="C36" s="36">
         <f>C34-C35</f>
         <v/>
       </c>
@@ -7050,7 +7312,7 @@
           <t>Equity risk premium</t>
         </is>
       </c>
-      <c r="C38" s="37">
+      <c r="C38" s="22">
         <f>Assumptions!$C$32</f>
         <v/>
       </c>
@@ -7061,7 +7323,7 @@
           <t>Cost of equity, explicit window</t>
         </is>
       </c>
-      <c r="C39" s="35">
+      <c r="C39" s="36">
         <f>C36+C37*C38</f>
         <v/>
       </c>
@@ -7072,7 +7334,7 @@
           <t>Cost of debt, blended</t>
         </is>
       </c>
-      <c r="C40" s="37">
+      <c r="C40" s="22">
         <f>Assumptions!$C$34</f>
         <v/>
       </c>
@@ -7083,7 +7345,7 @@
           <t>Cost of debt after tax</t>
         </is>
       </c>
-      <c r="C41" s="35">
+      <c r="C41" s="36">
         <f>C40*(1-Assumptions!$C$7)</f>
         <v/>
       </c>
@@ -7116,7 +7378,7 @@
           <t>Debt weight (net debt / (net debt + market capitalisation))</t>
         </is>
       </c>
-      <c r="C44" s="35">
+      <c r="C44" s="36">
         <f>C43/(C43+C42)</f>
         <v/>
       </c>
@@ -7127,7 +7389,7 @@
           <t>Equity weight</t>
         </is>
       </c>
-      <c r="C45" s="35">
+      <c r="C45" s="36">
         <f>1-C44</f>
         <v/>
       </c>
@@ -7151,7 +7413,7 @@
           <t>Terminal risk-free rate</t>
         </is>
       </c>
-      <c r="C47" s="37">
+      <c r="C47" s="22">
         <f>Assumptions!$C$36</f>
         <v/>
       </c>
@@ -7162,7 +7424,7 @@
           <t>Terminal equity risk premium</t>
         </is>
       </c>
-      <c r="C48" s="37">
+      <c r="C48" s="22">
         <f>Assumptions!$C$37</f>
         <v/>
       </c>
@@ -7173,7 +7435,7 @@
           <t>Terminal cost of equity</t>
         </is>
       </c>
-      <c r="C49" s="35">
+      <c r="C49" s="36">
         <f>C47+C37*C48</f>
         <v/>
       </c>
@@ -7184,7 +7446,7 @@
           <t>Terminal cost of debt</t>
         </is>
       </c>
-      <c r="C50" s="37">
+      <c r="C50" s="22">
         <f>Assumptions!$C$38</f>
         <v/>
       </c>
@@ -7195,7 +7457,7 @@
           <t>Terminal cost of debt after tax</t>
         </is>
       </c>
-      <c r="C51" s="35">
+      <c r="C51" s="36">
         <f>C50*(1-Assumptions!$C$7)</f>
         <v/>
       </c>
@@ -7206,7 +7468,7 @@
           <t>Terminal debt weight</t>
         </is>
       </c>
-      <c r="C52" s="37">
+      <c r="C52" s="22">
         <f>Assumptions!$C$39</f>
         <v/>
       </c>
@@ -7262,23 +7524,23 @@
           <t>Cost of debt path</t>
         </is>
       </c>
-      <c r="B56" s="37">
+      <c r="B56" s="22">
         <f>Assumptions!$B$35</f>
         <v/>
       </c>
-      <c r="C56" s="37">
+      <c r="C56" s="22">
         <f>Assumptions!$C$35</f>
         <v/>
       </c>
-      <c r="D56" s="37">
+      <c r="D56" s="22">
         <f>Assumptions!$D$35</f>
         <v/>
       </c>
-      <c r="E56" s="37">
+      <c r="E56" s="22">
         <f>Assumptions!$E$35</f>
         <v/>
       </c>
-      <c r="F56" s="37">
+      <c r="F56" s="22">
         <f>Assumptions!$F$35</f>
         <v/>
       </c>
@@ -7289,23 +7551,23 @@
           <t>Glide fraction — cumulative progress of the easing</t>
         </is>
       </c>
-      <c r="B57" s="35">
+      <c r="B57" s="36">
         <f>($B$56-B56)/($B$56-$F$56)</f>
         <v/>
       </c>
-      <c r="C57" s="35">
+      <c r="C57" s="36">
         <f>($B$56-C56)/($B$56-$F$56)</f>
         <v/>
       </c>
-      <c r="D57" s="35">
+      <c r="D57" s="36">
         <f>($B$56-D56)/($B$56-$F$56)</f>
         <v/>
       </c>
-      <c r="E57" s="35">
+      <c r="E57" s="36">
         <f>($B$56-E56)/($B$56-$F$56)</f>
         <v/>
       </c>
-      <c r="F57" s="35">
+      <c r="F57" s="36">
         <f>($B$56-F56)/($B$56-$F$56)</f>
         <v/>
       </c>
@@ -7314,6 +7576,44 @@
       <c r="A58" s="4" t="inlineStr">
         <is>
           <t>Note: row 15 above is the explicit-window cost of capital walked down to the terminal rate by the glide fraction on row 57, so the shape of the easing is inherited from the cost-of-debt path rather than being a second free parameter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="20" t="inlineStr">
+        <is>
+          <t>THE ANCHOR ROLL — one date, one price of time</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>Anchor accretion factor — (1 + cost of equity)^(days to anchor / 365)</t>
+        </is>
+      </c>
+      <c r="C61" s="37">
+        <f>(1+C39)^(Assumptions!$C$53/365)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="15" t="inlineStr">
+        <is>
+          <t>Fair value per share at the 5-Aug-2026 anchor (EGP)</t>
+        </is>
+      </c>
+      <c r="B62" s="15" t="n"/>
+      <c r="C62" s="31">
+        <f>C31*C61-Assumptions!$C$49</f>
+        <v/>
+      </c>
+      <c r="D62" s="15" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>The bridge on row 31 is dated 31-Dec-2025 (the audited balance-sheet date it subtracts net debt at). Row 62 rolls it to the anchor at the cost of equity, net of the EGP 1.85 FY2025 dividend paid in the window. Every lens on every sheet is rolled the same way.</t>
         </is>
       </c>
     </row>
@@ -7417,32 +7717,32 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B5" s="29" t="n">
+      <c r="B5" s="30" t="n">
         <v>152186.247545</v>
       </c>
-      <c r="C5" s="29" t="n">
+      <c r="C5" s="30" t="n">
         <v>231981.835577</v>
       </c>
-      <c r="D5" s="29" t="n">
+      <c r="D5" s="30" t="n">
         <v>281049.081719</v>
       </c>
-      <c r="E5" s="29">
+      <c r="E5" s="30">
         <f>DCF!B5</f>
         <v/>
       </c>
-      <c r="F5" s="29">
+      <c r="F5" s="30">
         <f>DCF!C5</f>
         <v/>
       </c>
-      <c r="G5" s="29">
+      <c r="G5" s="30">
         <f>DCF!D5</f>
         <v/>
       </c>
-      <c r="H5" s="29">
+      <c r="H5" s="30">
         <f>DCF!E5</f>
         <v/>
       </c>
-      <c r="I5" s="29">
+      <c r="I5" s="30">
         <f>DCF!F5</f>
         <v/>
       </c>
@@ -7453,13 +7753,13 @@
           <t>Gross profit</t>
         </is>
       </c>
-      <c r="B6" s="22" t="n">
+      <c r="B6" s="23" t="n">
         <v>29077.288803</v>
       </c>
-      <c r="C6" s="22" t="n">
+      <c r="C6" s="23" t="n">
         <v>43898.520903</v>
       </c>
-      <c r="D6" s="22" t="n">
+      <c r="D6" s="23" t="n">
         <v>40762.108187</v>
       </c>
       <c r="E6" s="18">
@@ -7489,32 +7789,32 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B7" s="29" t="n">
+      <c r="B7" s="30" t="n">
         <v>20035.105205</v>
       </c>
-      <c r="C7" s="29" t="n">
+      <c r="C7" s="30" t="n">
         <v>31601.46495</v>
       </c>
-      <c r="D7" s="29" t="n">
+      <c r="D7" s="30" t="n">
         <v>28363.203246</v>
       </c>
-      <c r="E7" s="29">
+      <c r="E7" s="30">
         <f>DCF!B6</f>
         <v/>
       </c>
-      <c r="F7" s="29">
+      <c r="F7" s="30">
         <f>DCF!C6</f>
         <v/>
       </c>
-      <c r="G7" s="29">
+      <c r="G7" s="30">
         <f>DCF!D6</f>
         <v/>
       </c>
-      <c r="H7" s="29">
+      <c r="H7" s="30">
         <f>DCF!E6</f>
         <v/>
       </c>
-      <c r="I7" s="29">
+      <c r="I7" s="30">
         <f>DCF!F6</f>
         <v/>
       </c>
@@ -7564,13 +7864,13 @@
           <t>Depreciation and amortisation</t>
         </is>
       </c>
-      <c r="B9" s="22" t="n">
+      <c r="B9" s="23" t="n">
         <v>-2295.986956</v>
       </c>
-      <c r="C9" s="22" t="n">
+      <c r="C9" s="23" t="n">
         <v>-2259.745806</v>
       </c>
-      <c r="D9" s="22" t="n">
+      <c r="D9" s="23" t="n">
         <v>-3008.977627</v>
       </c>
       <c r="E9" s="18">
@@ -7600,35 +7900,35 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B10" s="29">
+      <c r="B10" s="30">
         <f>B7+B9</f>
         <v/>
       </c>
-      <c r="C10" s="29">
+      <c r="C10" s="30">
         <f>C7+C9</f>
         <v/>
       </c>
-      <c r="D10" s="29">
+      <c r="D10" s="30">
         <f>D7+D9</f>
         <v/>
       </c>
-      <c r="E10" s="29">
+      <c r="E10" s="30">
         <f>E7+E9</f>
         <v/>
       </c>
-      <c r="F10" s="29">
+      <c r="F10" s="30">
         <f>F7+F9</f>
         <v/>
       </c>
-      <c r="G10" s="29">
+      <c r="G10" s="30">
         <f>G7+G9</f>
         <v/>
       </c>
-      <c r="H10" s="29">
+      <c r="H10" s="30">
         <f>H7+H9</f>
         <v/>
       </c>
-      <c r="I10" s="29">
+      <c r="I10" s="30">
         <f>I7+I9</f>
         <v/>
       </c>
@@ -7639,33 +7939,33 @@
           <t>Net finance costs</t>
         </is>
       </c>
-      <c r="B11" s="22" t="n">
+      <c r="B11" s="23" t="n">
         <v>-2124.362277</v>
       </c>
-      <c r="C11" s="22" t="n">
+      <c r="C11" s="23" t="n">
         <v>-3515.365946</v>
       </c>
-      <c r="D11" s="22" t="n">
+      <c r="D11" s="23" t="n">
         <v>-2145.438755</v>
       </c>
-      <c r="E11" s="28">
-        <f>-(Assumptions!$B$35*'Balance Sheet'!$D$11-Assumptions!$C$51*MAX('Balance Sheet'!$D$11-'Balance Sheet'!D17,0))</f>
-        <v/>
-      </c>
-      <c r="F11" s="28">
-        <f>-(Assumptions!$C$35*'Balance Sheet'!$D$11-Assumptions!$C$51*MAX('Balance Sheet'!$D$11-'Balance Sheet'!E17,0))</f>
-        <v/>
-      </c>
-      <c r="G11" s="28">
-        <f>-(Assumptions!$D$35*'Balance Sheet'!$D$11-Assumptions!$C$51*MAX('Balance Sheet'!$D$11-'Balance Sheet'!F17,0))</f>
-        <v/>
-      </c>
-      <c r="H11" s="28">
-        <f>-(Assumptions!$E$35*'Balance Sheet'!$D$11-Assumptions!$C$51*MAX('Balance Sheet'!$D$11-'Balance Sheet'!G17,0))</f>
-        <v/>
-      </c>
-      <c r="I11" s="28">
-        <f>-(Assumptions!$F$35*'Balance Sheet'!$D$11-Assumptions!$C$51*MAX('Balance Sheet'!$D$11-'Balance Sheet'!H17,0))</f>
+      <c r="E11" s="29">
+        <f>-(Assumptions!$B$35*'Balance Sheet'!$D$11-Assumptions!$C$52*MAX('Balance Sheet'!$D$11-'Balance Sheet'!D17,0))</f>
+        <v/>
+      </c>
+      <c r="F11" s="29">
+        <f>-(Assumptions!$C$35*'Balance Sheet'!$D$11-Assumptions!$C$52*MAX('Balance Sheet'!$D$11-'Balance Sheet'!E17,0))</f>
+        <v/>
+      </c>
+      <c r="G11" s="29">
+        <f>-(Assumptions!$D$35*'Balance Sheet'!$D$11-Assumptions!$C$52*MAX('Balance Sheet'!$D$11-'Balance Sheet'!F17,0))</f>
+        <v/>
+      </c>
+      <c r="H11" s="29">
+        <f>-(Assumptions!$E$35*'Balance Sheet'!$D$11-Assumptions!$C$52*MAX('Balance Sheet'!$D$11-'Balance Sheet'!G17,0))</f>
+        <v/>
+      </c>
+      <c r="I11" s="29">
+        <f>-(Assumptions!$F$35*'Balance Sheet'!$D$11-Assumptions!$C$52*MAX('Balance Sheet'!$D$11-'Balance Sheet'!H17,0))</f>
         <v/>
       </c>
     </row>
@@ -7675,33 +7975,33 @@
           <t>Share of equity-accounted investees</t>
         </is>
       </c>
-      <c r="B12" s="22" t="n">
+      <c r="B12" s="23" t="n">
         <v>603.624972</v>
       </c>
-      <c r="C12" s="22" t="n">
+      <c r="C12" s="23" t="n">
         <v>1132.366257</v>
       </c>
-      <c r="D12" s="22" t="n">
+      <c r="D12" s="23" t="n">
         <v>1568.902975</v>
       </c>
-      <c r="E12" s="28">
-        <f>D12*(1+Assumptions!$C$50)</f>
-        <v/>
-      </c>
-      <c r="F12" s="28">
-        <f>E12*(1+Assumptions!$C$50)</f>
-        <v/>
-      </c>
-      <c r="G12" s="28">
-        <f>F12*(1+Assumptions!$C$50)</f>
-        <v/>
-      </c>
-      <c r="H12" s="28">
-        <f>G12*(1+Assumptions!$C$50)</f>
-        <v/>
-      </c>
-      <c r="I12" s="28">
-        <f>H12*(1+Assumptions!$C$50)</f>
+      <c r="E12" s="29">
+        <f>D12*(1+Assumptions!$C$51)</f>
+        <v/>
+      </c>
+      <c r="F12" s="29">
+        <f>E12*(1+Assumptions!$C$51)</f>
+        <v/>
+      </c>
+      <c r="G12" s="29">
+        <f>F12*(1+Assumptions!$C$51)</f>
+        <v/>
+      </c>
+      <c r="H12" s="29">
+        <f>G12*(1+Assumptions!$C$51)</f>
+        <v/>
+      </c>
+      <c r="I12" s="29">
+        <f>H12*(1+Assumptions!$C$51)</f>
         <v/>
       </c>
     </row>
@@ -7711,35 +8011,35 @@
           <t>Profit before tax</t>
         </is>
       </c>
-      <c r="B13" s="28">
+      <c r="B13" s="29">
         <f>B10+B11+B12</f>
         <v/>
       </c>
-      <c r="C13" s="28">
+      <c r="C13" s="29">
         <f>C10+C11+C12</f>
         <v/>
       </c>
-      <c r="D13" s="28">
+      <c r="D13" s="29">
         <f>D10+D11+D12</f>
         <v/>
       </c>
-      <c r="E13" s="28">
+      <c r="E13" s="29">
         <f>E10+E11+E12</f>
         <v/>
       </c>
-      <c r="F13" s="28">
+      <c r="F13" s="29">
         <f>F10+F11+F12</f>
         <v/>
       </c>
-      <c r="G13" s="28">
+      <c r="G13" s="29">
         <f>G10+G11+G12</f>
         <v/>
       </c>
-      <c r="H13" s="28">
+      <c r="H13" s="29">
         <f>H10+H11+H12</f>
         <v/>
       </c>
-      <c r="I13" s="28">
+      <c r="I13" s="29">
         <f>I10+I11+I12</f>
         <v/>
       </c>
@@ -7750,32 +8050,32 @@
           <t>Income tax</t>
         </is>
       </c>
-      <c r="B14" s="22" t="n">
+      <c r="B14" s="23" t="n">
         <v>-5080.406688</v>
       </c>
-      <c r="C14" s="22" t="n">
+      <c r="C14" s="23" t="n">
         <v>-8121.510082</v>
       </c>
-      <c r="D14" s="22" t="n">
+      <c r="D14" s="23" t="n">
         <v>-5591.139782</v>
       </c>
-      <c r="E14" s="28">
+      <c r="E14" s="29">
         <f>-E13*Assumptions!$C$7</f>
         <v/>
       </c>
-      <c r="F14" s="28">
+      <c r="F14" s="29">
         <f>-F13*Assumptions!$C$7</f>
         <v/>
       </c>
-      <c r="G14" s="28">
+      <c r="G14" s="29">
         <f>-G13*Assumptions!$C$7</f>
         <v/>
       </c>
-      <c r="H14" s="28">
+      <c r="H14" s="29">
         <f>-H13*Assumptions!$C$7</f>
         <v/>
       </c>
-      <c r="I14" s="28">
+      <c r="I14" s="29">
         <f>-I13*Assumptions!$C$7</f>
         <v/>
       </c>
@@ -7786,32 +8086,32 @@
           <t>Profit for the year</t>
         </is>
       </c>
-      <c r="B15" s="22" t="n">
+      <c r="B15" s="23" t="n">
         <v>11137.974256</v>
       </c>
-      <c r="C15" s="22" t="n">
+      <c r="C15" s="23" t="n">
         <v>18837.209373</v>
       </c>
-      <c r="D15" s="22" t="n">
+      <c r="D15" s="23" t="n">
         <v>19186.550057</v>
       </c>
-      <c r="E15" s="28">
+      <c r="E15" s="29">
         <f>E13+E14</f>
         <v/>
       </c>
-      <c r="F15" s="28">
+      <c r="F15" s="29">
         <f>F13+F14</f>
         <v/>
       </c>
-      <c r="G15" s="28">
+      <c r="G15" s="29">
         <f>G13+G14</f>
         <v/>
       </c>
-      <c r="H15" s="28">
+      <c r="H15" s="29">
         <f>H13+H14</f>
         <v/>
       </c>
-      <c r="I15" s="28">
+      <c r="I15" s="29">
         <f>I13+I14</f>
         <v/>
       </c>
@@ -7822,32 +8122,32 @@
           <t>Non-controlling interests</t>
         </is>
       </c>
-      <c r="B16" s="22" t="n">
+      <c r="B16" s="23" t="n">
         <v>-1022.272478999999</v>
       </c>
-      <c r="C16" s="22" t="n">
+      <c r="C16" s="23" t="n">
         <v>-1375.850659</v>
       </c>
-      <c r="D16" s="22" t="n">
+      <c r="D16" s="23" t="n">
         <v>-1856.305067000001</v>
       </c>
-      <c r="E16" s="28">
+      <c r="E16" s="29">
         <f>-E15*'SOTP Bridge'!$C$15</f>
         <v/>
       </c>
-      <c r="F16" s="28">
+      <c r="F16" s="29">
         <f>-F15*'SOTP Bridge'!$C$15</f>
         <v/>
       </c>
-      <c r="G16" s="28">
+      <c r="G16" s="29">
         <f>-G15*'SOTP Bridge'!$C$15</f>
         <v/>
       </c>
-      <c r="H16" s="28">
+      <c r="H16" s="29">
         <f>-H15*'SOTP Bridge'!$C$15</f>
         <v/>
       </c>
-      <c r="I16" s="28">
+      <c r="I16" s="29">
         <f>-I15*'SOTP Bridge'!$C$15</f>
         <v/>
       </c>
@@ -7858,32 +8158,32 @@
           <t>Profit attributable to shareholders</t>
         </is>
       </c>
-      <c r="B17" s="29" t="n">
+      <c r="B17" s="30" t="n">
         <v>10115.701777</v>
       </c>
-      <c r="C17" s="29" t="n">
+      <c r="C17" s="30" t="n">
         <v>17461.358714</v>
       </c>
-      <c r="D17" s="29" t="n">
+      <c r="D17" s="30" t="n">
         <v>17330.24499</v>
       </c>
-      <c r="E17" s="29">
+      <c r="E17" s="30">
         <f>E15+E16</f>
         <v/>
       </c>
-      <c r="F17" s="29">
+      <c r="F17" s="30">
         <f>F15+F16</f>
         <v/>
       </c>
-      <c r="G17" s="29">
+      <c r="G17" s="30">
         <f>G15+G16</f>
         <v/>
       </c>
-      <c r="H17" s="29">
+      <c r="H17" s="30">
         <f>H15+H16</f>
         <v/>
       </c>
-      <c r="I17" s="29">
+      <c r="I17" s="30">
         <f>I15+I16</f>
         <v/>
       </c>
@@ -7930,7 +8230,7 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>Note: FY2023 and FY2024 are audited. FY2025 revenue, profit after tax and profit after minority interests are disclosed; the intermediate lines are derived by closing the account to the reported profit. In the forecast the finance charge is computed on the gross debt book less the cash the business is accumulating, so it falls with net debt rather than being frozen at the FY2025 balance; profit is therefore struck after interest and differs from the pre-financing DCF waterfall by construction.</t>
+          <t>Note: every FY2023-25 statement line is the audited figure — no closure or derivation is used for any historical year (the EBITDA and EPS rows are labelled house derivations). In the forecast the finance charge is computed on the gross debt book less the cash the business is accumulating, so it moves with net debt rather than being frozen at the FY2025 balance; profit is therefore struck after interest and differs from the pre-financing DCF waterfall by construction.</t>
         </is>
       </c>
     </row>

--- a/engine/swdy_study/SWDY_Valuation_Model_05082026_public.xlsx
+++ b/engine/swdy_study/SWDY_Valuation_Model_05082026_public.xlsx
@@ -36,8 +36,8 @@
     <numFmt numFmtId="165" formatCode="0.0%;(0.0%);&quot;-&quot;"/>
     <numFmt numFmtId="166" formatCode="#,##0;(#,##0);&quot;-&quot;"/>
     <numFmt numFmtId="167" formatCode="#,##0.0;(#,##0.0);&quot;-&quot;"/>
-    <numFmt numFmtId="168" formatCode="0.00x"/>
-    <numFmt numFmtId="169" formatCode="0.000"/>
+    <numFmt numFmtId="168" formatCode="0.000"/>
+    <numFmt numFmtId="169" formatCode="0.00x"/>
     <numFmt numFmtId="170" formatCode="0.0000"/>
   </numFmts>
   <fonts count="11">
@@ -143,6 +143,7 @@
     <xf numFmtId="164" fontId="10" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -153,13 +154,12 @@
     <xf numFmtId="166" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="8" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -529,7 +529,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I50"/>
+  <dimension ref="A1:I55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="112" customWidth="1" min="1" max="1"/>
@@ -619,73 +619,77 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>THREE THINGS ARE PASTED VALUES, and it is worth knowing which. First, audited and disclosed history — the</t>
+          <t>THREE THINGS ARE PASTED VALUES, and it is worth knowing exactly which. First, audited and disclosed history</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>primary record, not a calculation. Second, the sub-segment unit build: revenue and gross profit per segment</t>
+          <t>— the primary record, not a calculation. Second, the segment build: revenue and profit for the three</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>come from a seven-line tonnage, megavolt-ampere, meter-unit and order-book model, and only its OUTPUT is</t>
+          <t>segments the company itself discloses (Cables and its accessories, Constructions and infrastructure,</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>carried here; everything downstream of it is formula. Third, the Monte Carlo price map and the sensitivity</t>
+          <t>Electrical products and digital solutions) are pasted for FY2025 and grown on their own drivers; only its</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>grids, where each individual cell is a complete re-run of the whole valuation and so cannot be a formula in</t>
+          <t>OUTPUT is carried here and everything downstream of it is formula. Third, whole-model engine outputs, where</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>a grid. Changing a driver reprices the model but does NOT redraw those two grids.</t>
+          <t>each figure is a complete re-run of the entire valuation and so cannot be a single formula: the Monte Carlo</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr"/>
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>price map, the sensitivity grids, the DCF scenario bear/bull bounds, the multi-leg currency-of-discounting</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>How revenue is built. Not as one growth rate. Revenue splits into a domestic Egyptian-pound leg and a</t>
+          <t>alternative (its USD cost of capital IS a live formula; the leg-by-leg USD discounting is the engine's),</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>foreign leg forecast in US dollars and translated at an explicit exchange-rate path, because more than 70%</t>
+          <t>and the expert-panel legs. Everything else — including every lens base value, the relative/normalised/book</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>of this company's revenue is earned outside Egypt. Margins come from a segment build; group EBITDA margin</t>
+          <t>bear and bull bounds, and the anchor-date roll — is a live formula. Changing a driver reprices the model</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>is an output of that build, not an input.</t>
+          <t>but does NOT redraw the engine outputs.</t>
         </is>
       </c>
     </row>
@@ -695,135 +699,135 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>What it is not. It is not investment advice, a recommendation, or a price target. Values are model outputs</t>
+          <t>How revenue is built. Not as one growth rate. Each of the three disclosed segments is grown on its own</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>shown as ranges.</t>
+          <t>driver — Cables on copper-price growth times FX-translation growth times a modest real-volume assumption,</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="inlineStr"/>
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Constructions and Electrical products on a taper of their own recent revenue CAGR — because none of the</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>Sourcing note, up front. FY2023 and FY2024 come from the company's audited consolidated statements and</t>
+          <t>audited filings discloses a tonnage, order-book or backlog figure to build a literal unit model from.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>earnings releases and are not estimated. For FY2025, revenue, profit after tax, profit after minority</t>
+          <t>Margins come from the same segment build; group EBITDA margin is an OUTPUT of it, not an input.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>interests, total assets and net bank debt are disclosed; the intermediate income-statement lines are</t>
-        </is>
-      </c>
+      <c r="A30" s="3" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>derived by closing the profit-and-loss account to the reported profit, and the balance sheet beyond total</t>
+          <t>What it is not. It is not investment advice, a recommendation, or a price target. Values are model outputs</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>assets and net debt is triangulated by three methods, which are shown and averaged on the Balance Sheet</t>
+          <t>shown as ranges.</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>sheet rather than asserted. Every derived line is annotated where it appears and listed with source and</t>
-        </is>
-      </c>
+      <c r="A33" s="3" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>date in the companion bibliography document.</t>
+          <t>Sourcing note, up front. FY2023, FY2024 and FY2025 all come from the company's own audited consolidated</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="inlineStr"/>
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>financial statements — every income-statement, balance-sheet and segment line is the audited figure, not a</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>Discount convention. Each explicit year is discounted at its own forward cost of capital, gliding</t>
+          <t>derivation or a triangulation. Segment revenue ties EXACTLY to consolidated revenue in every year (Note</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>26.9% -&gt; 15.1% on the same easing calendar as the interest forecast; the terminal value is</t>
+          <t>5-3); segment profit reconciles to consolidated operating profit through an explicit, exactly-reconciling</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>capitalised at the terminal rate and discounted at the year-5 cumulative factor. One date, one price of time.</t>
+          <t>corporate cost load (Note 16 less G&amp;A, net impairment, other expenses and other income). Every input is</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>The glide fractions are not a free parameter: they are the cost-of-debt path's own cumulative progress, and</t>
+          <t>annotated where it appears and listed with source and date in the companion bibliography document.</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t>the DCF sheet computes them in front of you.</t>
-        </is>
-      </c>
+      <c r="A40" s="3" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="inlineStr"/>
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>Discount convention. Each explicit year is discounted at its own forward cost of capital, gliding</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>The open question. This company earns most of its revenue in hard currency but reports, lists and borrows</t>
+          <t>26.6% -&gt; 15.9% on the same easing calendar as the interest forecast; the terminal value is</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>in Egyptian pounds. The primary model charges the full Egyptian cost of capital. The Fundamental Valuation</t>
+          <t>capitalised at the terminal rate and discounted at the year-5 cumulative factor. One date, one price of time.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>sheet also shows what the same cash flows are worth if the hard-currency leg is discounted at a</t>
+          <t>The glide fractions are not a free parameter: they are the cost-of-debt path's own cumulative progress, and</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>hard-currency rate. Both are shown; they are not averaged.</t>
+          <t>the DCF sheet computes them in front of you.</t>
         </is>
       </c>
     </row>
@@ -833,26 +837,57 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>Currency. EGP million unless stated. Spot EGP 105.20 (2026-08-05 close). Sheets: READ FIRST · Summary ·</t>
+          <t>The open question. This company earns just over half its revenue on a hard-currency-linked basis but</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>Fundamental Valuation · Assumptions · SOTP Bridge · Segments · Relative &amp; Normalized · DCF · Income</t>
+          <t>reports, lists and borrows in Egyptian pounds. The primary model charges the full Egyptian cost of capital.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>Statement · Balance Sheet · Cash Flow · Summary Financials · Monte Carlo · Sensitivity · Per-Share &amp;</t>
+          <t>The Fundamental Valuation sheet also shows what the same cash flows are worth if the hard-currency leg is</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>discounted at a hard-currency rate. Both are shown; they are not averaged.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>Currency. EGP million unless stated. Spot EGP 105.20 (2026-08-05 close). Sheets: READ FIRST · Summary ·</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>Fundamental Valuation · Assumptions · SOTP Bridge · Segments · Relative &amp; Normalized · DCF · Income</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>Statement · Balance Sheet · Cash Flow · Summary Financials · Monte Carlo · Sensitivity · Per-Share &amp;</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
         <is>
           <t>Ratios · Peer &amp; Sector.</t>
         </is>
@@ -869,7 +904,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -901,7 +936,7 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>EGP mn, consolidated. The FY2025 debt and cash lines are triangulated by three methods, shown and averaged below rather than asserted</t>
+          <t>EGP mn, consolidated. Every FY2023-25 line is the audited closing figure — no triangulation is needed for any year, including FY2025, because the full filing is in hand</t>
         </is>
       </c>
     </row>
@@ -958,33 +993,32 @@
           <t>Property, plant and equipment</t>
         </is>
       </c>
-      <c r="B5" s="22" t="n">
-        <v>18009.2</v>
-      </c>
-      <c r="C5" s="22" t="n">
-        <v>27543.8</v>
-      </c>
-      <c r="D5" s="28">
-        <f>C5+'Income Statement'!D5*(Assumptions!$B$33-Assumptions!$C$34)</f>
-        <v/>
-      </c>
-      <c r="E5" s="28">
+      <c r="B5" s="23" t="n">
+        <v>18009.166367</v>
+      </c>
+      <c r="C5" s="23" t="n">
+        <v>27543.762675</v>
+      </c>
+      <c r="D5" s="23" t="n">
+        <v>35961.076614</v>
+      </c>
+      <c r="E5" s="29">
         <f>D5-DCF!B12+DCF!B8</f>
         <v/>
       </c>
-      <c r="F5" s="28">
+      <c r="F5" s="29">
         <f>E5-DCF!C12+DCF!C8</f>
         <v/>
       </c>
-      <c r="G5" s="28">
+      <c r="G5" s="29">
         <f>F5-DCF!D12+DCF!D8</f>
         <v/>
       </c>
-      <c r="H5" s="28">
+      <c r="H5" s="29">
         <f>G5-DCF!E12+DCF!E8</f>
         <v/>
       </c>
-      <c r="I5" s="28">
+      <c r="I5" s="29">
         <f>H5-DCF!F12+DCF!F8</f>
         <v/>
       </c>
@@ -995,16 +1029,14 @@
           <t>Inventories</t>
         </is>
       </c>
-      <c r="B6" s="22" t="n">
-        <v>30881.8</v>
-      </c>
-      <c r="C6" s="22" t="n">
-        <v>56795.9</v>
-      </c>
-      <c r="D6" s="22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B6" s="23" t="n">
+        <v>30881.822082</v>
+      </c>
+      <c r="C6" s="23" t="n">
+        <v>56795.884068</v>
+      </c>
+      <c r="D6" s="23" t="n">
+        <v>59860.04457</v>
       </c>
     </row>
     <row r="7">
@@ -1013,16 +1045,14 @@
           <t>Contract assets</t>
         </is>
       </c>
-      <c r="B7" s="22" t="n">
-        <v>16179.6</v>
-      </c>
-      <c r="C7" s="22" t="n">
-        <v>18052</v>
-      </c>
-      <c r="D7" s="22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B7" s="23" t="n">
+        <v>16179.633722</v>
+      </c>
+      <c r="C7" s="23" t="n">
+        <v>18051.96657</v>
+      </c>
+      <c r="D7" s="23" t="n">
+        <v>29894.579591</v>
       </c>
     </row>
     <row r="8">
@@ -1031,16 +1061,14 @@
           <t>Trade and other receivables</t>
         </is>
       </c>
-      <c r="B8" s="22" t="n">
-        <v>46591.9</v>
-      </c>
-      <c r="C8" s="22" t="n">
-        <v>86736.3</v>
-      </c>
-      <c r="D8" s="22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B8" s="23" t="n">
+        <v>46591.885092</v>
+      </c>
+      <c r="C8" s="23" t="n">
+        <v>86736.309423</v>
+      </c>
+      <c r="D8" s="23" t="n">
+        <v>116259.797169</v>
       </c>
     </row>
     <row r="9">
@@ -1049,13 +1077,13 @@
           <t>Cash and cash equivalents</t>
         </is>
       </c>
-      <c r="B9" s="22" t="n">
-        <v>25552</v>
-      </c>
-      <c r="C9" s="22" t="n">
-        <v>38180</v>
-      </c>
-      <c r="D9" s="28">
+      <c r="B9" s="23" t="n">
+        <v>25552.0448</v>
+      </c>
+      <c r="C9" s="23" t="n">
+        <v>38180.002322</v>
+      </c>
+      <c r="D9" s="29">
         <f>D11-D17</f>
         <v/>
       </c>
@@ -1066,14 +1094,14 @@
           <t>Total assets</t>
         </is>
       </c>
-      <c r="B10" s="29" t="n">
-        <v>151448.7</v>
-      </c>
-      <c r="C10" s="29" t="n">
-        <v>249527.1</v>
-      </c>
-      <c r="D10" s="29" t="n">
-        <v>311090</v>
+      <c r="B10" s="30" t="n">
+        <v>151448.654828</v>
+      </c>
+      <c r="C10" s="30" t="n">
+        <v>249527.138687</v>
+      </c>
+      <c r="D10" s="30" t="n">
+        <v>311099.090775</v>
       </c>
       <c r="E10" s="15" t="n"/>
       <c r="F10" s="15" t="n"/>
@@ -1087,15 +1115,14 @@
           <t>Loans and borrowings</t>
         </is>
       </c>
-      <c r="B11" s="22" t="n">
-        <v>41766.5</v>
-      </c>
-      <c r="C11" s="22" t="n">
-        <v>59082.9</v>
-      </c>
-      <c r="D11" s="28">
-        <f>AVERAGE(B23:B25)</f>
-        <v/>
+      <c r="B11" s="23" t="n">
+        <v>41766.492071</v>
+      </c>
+      <c r="C11" s="23" t="n">
+        <v>59082.941807</v>
+      </c>
+      <c r="D11" s="23" t="n">
+        <v>62509.211797</v>
       </c>
     </row>
     <row r="12">
@@ -1104,16 +1131,14 @@
           <t>Trade and other payables</t>
         </is>
       </c>
-      <c r="B12" s="22" t="n">
-        <v>31938.1</v>
-      </c>
-      <c r="C12" s="22" t="n">
-        <v>54808.2</v>
-      </c>
-      <c r="D12" s="22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B12" s="23" t="n">
+        <v>31938.12206</v>
+      </c>
+      <c r="C12" s="23" t="n">
+        <v>54808.185042</v>
+      </c>
+      <c r="D12" s="23" t="n">
+        <v>68895.662044</v>
       </c>
     </row>
     <row r="13">
@@ -1122,16 +1147,14 @@
           <t>Contract liabilities</t>
         </is>
       </c>
-      <c r="B13" s="22" t="n">
-        <v>25060.3</v>
-      </c>
-      <c r="C13" s="22" t="n">
-        <v>53281.1</v>
-      </c>
-      <c r="D13" s="22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B13" s="23" t="n">
+        <v>25060.328092</v>
+      </c>
+      <c r="C13" s="23" t="n">
+        <v>53281.056753</v>
+      </c>
+      <c r="D13" s="23" t="n">
+        <v>81266.224686</v>
       </c>
     </row>
     <row r="14">
@@ -1140,34 +1163,33 @@
           <t>Equity attributable to shareholders</t>
         </is>
       </c>
-      <c r="B14" s="29" t="n">
-        <v>35724.5</v>
-      </c>
-      <c r="C14" s="29" t="n">
-        <v>55274.9</v>
-      </c>
-      <c r="D14" s="29">
-        <f>C14+'Income Statement'!D17-Assumptions!$C$55*Assumptions!$C$6</f>
-        <v/>
-      </c>
-      <c r="E14" s="29">
-        <f>D14+'Income Statement'!E17*(1-Assumptions!$C$56)</f>
-        <v/>
-      </c>
-      <c r="F14" s="29">
-        <f>E14+'Income Statement'!F17*(1-Assumptions!$C$56)</f>
-        <v/>
-      </c>
-      <c r="G14" s="29">
-        <f>F14+'Income Statement'!G17*(1-Assumptions!$C$56)</f>
-        <v/>
-      </c>
-      <c r="H14" s="29">
-        <f>G14+'Income Statement'!H17*(1-Assumptions!$C$56)</f>
-        <v/>
-      </c>
-      <c r="I14" s="29">
-        <f>H14+'Income Statement'!I17*(1-Assumptions!$C$56)</f>
+      <c r="B14" s="30" t="n">
+        <v>35724.466132</v>
+      </c>
+      <c r="C14" s="30" t="n">
+        <v>55274.913356</v>
+      </c>
+      <c r="D14" s="30" t="n">
+        <v>66870.86655000001</v>
+      </c>
+      <c r="E14" s="30">
+        <f>D14+'Income Statement'!E17*(1-Assumptions!$C$50)</f>
+        <v/>
+      </c>
+      <c r="F14" s="30">
+        <f>E14+'Income Statement'!F17*(1-Assumptions!$C$50)</f>
+        <v/>
+      </c>
+      <c r="G14" s="30">
+        <f>F14+'Income Statement'!G17*(1-Assumptions!$C$50)</f>
+        <v/>
+      </c>
+      <c r="H14" s="30">
+        <f>G14+'Income Statement'!H17*(1-Assumptions!$C$50)</f>
+        <v/>
+      </c>
+      <c r="I14" s="30">
+        <f>H14+'Income Statement'!I17*(1-Assumptions!$C$50)</f>
         <v/>
       </c>
     </row>
@@ -1177,14 +1199,14 @@
           <t>Non-controlling interests</t>
         </is>
       </c>
-      <c r="B15" s="22" t="n">
-        <v>2384</v>
-      </c>
-      <c r="C15" s="22" t="n">
-        <v>4251.8</v>
-      </c>
-      <c r="D15" s="22" t="n">
-        <v>5851.8</v>
+      <c r="B15" s="23" t="n">
+        <v>2384.013396</v>
+      </c>
+      <c r="C15" s="23" t="n">
+        <v>4251.7719</v>
+      </c>
+      <c r="D15" s="23" t="n">
+        <v>5118.978381</v>
       </c>
     </row>
     <row r="16">
@@ -1193,34 +1215,33 @@
           <t>Net working capital</t>
         </is>
       </c>
-      <c r="B16" s="22" t="n">
-        <v>36654.90000000001</v>
-      </c>
-      <c r="C16" s="22" t="n">
-        <v>53494.90000000002</v>
-      </c>
-      <c r="D16" s="28">
-        <f>'Income Statement'!D5*Assumptions!$C$32</f>
-        <v/>
-      </c>
-      <c r="E16" s="28">
-        <f>'Income Statement'!E5*Assumptions!$C$32</f>
-        <v/>
-      </c>
-      <c r="F16" s="28">
-        <f>'Income Statement'!F5*Assumptions!$C$32</f>
-        <v/>
-      </c>
-      <c r="G16" s="28">
-        <f>'Income Statement'!G5*Assumptions!$C$32</f>
-        <v/>
-      </c>
-      <c r="H16" s="28">
-        <f>'Income Statement'!H5*Assumptions!$C$32</f>
-        <v/>
-      </c>
-      <c r="I16" s="28">
-        <f>'Income Statement'!I5*Assumptions!$C$32</f>
+      <c r="B16" s="23" t="n">
+        <v>36654.89074399999</v>
+      </c>
+      <c r="C16" s="23" t="n">
+        <v>53494.91826600001</v>
+      </c>
+      <c r="D16" s="23" t="n">
+        <v>55852.53459999998</v>
+      </c>
+      <c r="E16" s="29">
+        <f>'Income Statement'!E5*Assumptions!$C$25</f>
+        <v/>
+      </c>
+      <c r="F16" s="29">
+        <f>'Income Statement'!F5*Assumptions!$C$25</f>
+        <v/>
+      </c>
+      <c r="G16" s="29">
+        <f>'Income Statement'!G5*Assumptions!$C$25</f>
+        <v/>
+      </c>
+      <c r="H16" s="29">
+        <f>'Income Statement'!H5*Assumptions!$C$25</f>
+        <v/>
+      </c>
+      <c r="I16" s="29">
+        <f>'Income Statement'!I5*Assumptions!$C$25</f>
         <v/>
       </c>
     </row>
@@ -1230,34 +1251,34 @@
           <t>Net bank debt</t>
         </is>
       </c>
-      <c r="B17" s="29" t="n">
-        <v>14768</v>
-      </c>
-      <c r="C17" s="29" t="n">
-        <v>20028</v>
-      </c>
-      <c r="D17" s="29">
-        <f>Assumptions!$C$50</f>
-        <v/>
-      </c>
-      <c r="E17" s="29">
-        <f>D17-DCF!B14-'Income Statement'!E11*(1-Assumptions!$C$7)+Assumptions!$C$56*'Income Statement'!E17</f>
-        <v/>
-      </c>
-      <c r="F17" s="29">
-        <f>E17-DCF!C14-'Income Statement'!F11*(1-Assumptions!$C$7)+Assumptions!$C$56*'Income Statement'!F17</f>
-        <v/>
-      </c>
-      <c r="G17" s="29">
-        <f>F17-DCF!D14-'Income Statement'!G11*(1-Assumptions!$C$7)+Assumptions!$C$56*'Income Statement'!G17</f>
-        <v/>
-      </c>
-      <c r="H17" s="29">
-        <f>G17-DCF!E14-'Income Statement'!H11*(1-Assumptions!$C$7)+Assumptions!$C$56*'Income Statement'!H17</f>
-        <v/>
-      </c>
-      <c r="I17" s="29">
-        <f>H17-DCF!F14-'Income Statement'!I11*(1-Assumptions!$C$7)+Assumptions!$C$56*'Income Statement'!I17</f>
+      <c r="B17" s="30" t="n">
+        <v>16214.447271</v>
+      </c>
+      <c r="C17" s="30" t="n">
+        <v>20902.939485</v>
+      </c>
+      <c r="D17" s="30">
+        <f>Assumptions!$C$43</f>
+        <v/>
+      </c>
+      <c r="E17" s="30">
+        <f>D17-DCF!B14-'Income Statement'!E11*(1-Assumptions!$C$7)+Assumptions!$C$50*'Income Statement'!E17</f>
+        <v/>
+      </c>
+      <c r="F17" s="30">
+        <f>E17-DCF!C14-'Income Statement'!F11*(1-Assumptions!$C$7)+Assumptions!$C$50*'Income Statement'!F17</f>
+        <v/>
+      </c>
+      <c r="G17" s="30">
+        <f>F17-DCF!D14-'Income Statement'!G11*(1-Assumptions!$C$7)+Assumptions!$C$50*'Income Statement'!G17</f>
+        <v/>
+      </c>
+      <c r="H17" s="30">
+        <f>G17-DCF!E14-'Income Statement'!H11*(1-Assumptions!$C$7)+Assumptions!$C$50*'Income Statement'!H17</f>
+        <v/>
+      </c>
+      <c r="I17" s="30">
+        <f>H17-DCF!F14-'Income Statement'!I11*(1-Assumptions!$C$7)+Assumptions!$C$50*'Income Statement'!I17</f>
         <v/>
       </c>
     </row>
@@ -1267,35 +1288,35 @@
           <t>Net debt / EBITDA</t>
         </is>
       </c>
-      <c r="B18" s="34">
+      <c r="B18" s="35">
         <f>B17/'Income Statement'!B7</f>
         <v/>
       </c>
-      <c r="C18" s="34">
+      <c r="C18" s="35">
         <f>C17/'Income Statement'!C7</f>
         <v/>
       </c>
-      <c r="D18" s="34">
+      <c r="D18" s="35">
         <f>D17/'Income Statement'!D7</f>
         <v/>
       </c>
-      <c r="E18" s="34">
+      <c r="E18" s="35">
         <f>E17/'Income Statement'!E7</f>
         <v/>
       </c>
-      <c r="F18" s="34">
+      <c r="F18" s="35">
         <f>F17/'Income Statement'!F7</f>
         <v/>
       </c>
-      <c r="G18" s="34">
+      <c r="G18" s="35">
         <f>G17/'Income Statement'!G7</f>
         <v/>
       </c>
-      <c r="H18" s="34">
+      <c r="H18" s="35">
         <f>H17/'Income Statement'!H7</f>
         <v/>
       </c>
-      <c r="I18" s="34">
+      <c r="I18" s="35">
         <f>I17/'Income Statement'!I7</f>
         <v/>
       </c>
@@ -1306,78 +1327,24 @@
           <t>Residual: other liabilities, provisions and deferred tax not shown separately (total assets less the lines above)</t>
         </is>
       </c>
-      <c r="B19" s="28">
+      <c r="B19" s="29">
         <f>B10-(B11+B12+B13+B14+B15)</f>
         <v/>
       </c>
-      <c r="C19" s="28">
+      <c r="C19" s="29">
         <f>C10-(C11+C12+C13+C14+C15)</f>
         <v/>
       </c>
-      <c r="D19" s="6" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
+      <c r="D19" s="29">
+        <f>D10-(D11+D12+D13+D14+D15)</f>
+        <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Note: this is a CONDENSED layout, so it does not foot to zero — the residual row above is the block of other liabilities, provisions, deferred tax and related-party balances that is not shown separately. For FY2024 that residual is 22,828, which reconciles to the audited statements (provisions 13,440 + 943, deferred tax 3,670, related parties 2,050 + 95, other liabilities 2,631 = 22,829). FY2025 shows only the disclosed lines (total assets, net bank debt) plus rolled-forward equity and triangulated debt and cash; the valuation bridge uses only the disclosed net bank debt.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>FY2025 gross debt — three independent triangulations</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>EGP mn</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>Balance-sheet residual (assets less equity and non-debt liabilities)</t>
-        </is>
-      </c>
-      <c r="B23" s="22" t="n">
-        <v>76165.80577232633</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>FY2024 debt scaled with revenue growth</t>
-        </is>
-      </c>
-      <c r="B24" s="22" t="n">
-        <v>71579.70996905792</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t>Implied from the cash balance and the disclosed net debt</t>
-        </is>
-      </c>
-      <c r="B25" s="22" t="n">
-        <v>67104.64586101151</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="15" t="inlineStr">
-        <is>
-          <t>Average — the figure carried on row 11</t>
-        </is>
-      </c>
-      <c r="B26" s="29">
-        <f>AVERAGE(B23:B25)</f>
-        <v/>
+          <t>Note: this is a CONDENSED layout, so it does not foot to zero — the residual row above is the block of other liabilities, provisions, deferred tax and related-party balances that is not shown separately. For FY2024 that residual is 22,828, which reconciles to the audited statements (provisions 13,440 + 943, deferred tax 3,670, related parties 2,050 + 95, other liabilities 2,631 = 22,829). Every line, including FY2025, is now the audited closing figure — no triangulation or roll-forward is used for any historical year.</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1435,12 +1402,12 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>FY2023</t>
+          <t>FY2024</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2025</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
@@ -1476,11 +1443,11 @@
         </is>
       </c>
       <c r="B5" s="18">
-        <f>'Income Statement'!B7</f>
+        <f>'Income Statement'!C7</f>
         <v/>
       </c>
       <c r="C5" s="18">
-        <f>'Income Statement'!C7</f>
+        <f>'Income Statement'!D7</f>
         <v/>
       </c>
       <c r="D5" s="18">
@@ -1510,13 +1477,13 @@
           <t>Interest paid</t>
         </is>
       </c>
-      <c r="B6" s="28" t="inlineStr">
+      <c r="B6" s="29" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C6" s="22" t="n">
-        <v>-7706.9</v>
+      <c r="C6" s="23" t="n">
+        <v>-5740.31242</v>
       </c>
     </row>
     <row r="7">
@@ -1525,13 +1492,13 @@
           <t>Income tax paid</t>
         </is>
       </c>
-      <c r="B7" s="28" t="inlineStr">
+      <c r="B7" s="29" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C7" s="22" t="n">
-        <v>-4891</v>
+      <c r="C7" s="23" t="n">
+        <v>-8298.752112</v>
       </c>
     </row>
     <row r="8">
@@ -1540,13 +1507,13 @@
           <t>Operating cash flow after interest and tax</t>
         </is>
       </c>
-      <c r="B8" s="28" t="inlineStr">
+      <c r="B8" s="29" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C8" s="22" t="n">
-        <v>3979.4</v>
+      <c r="C8" s="23" t="n">
+        <v>12765.922545</v>
       </c>
     </row>
     <row r="9">
@@ -1555,12 +1522,12 @@
           <t>NOPAT</t>
         </is>
       </c>
-      <c r="B9" s="28" t="inlineStr">
+      <c r="B9" s="29" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C9" s="28" t="inlineStr">
+      <c r="C9" s="29" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1592,12 +1559,12 @@
           <t>Add back depreciation and amortisation</t>
         </is>
       </c>
-      <c r="B10" s="28" t="inlineStr">
+      <c r="B10" s="29" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C10" s="28" t="inlineStr">
+      <c r="C10" s="29" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1629,11 +1596,11 @@
           <t>Capital expenditure</t>
         </is>
       </c>
-      <c r="B11" s="22" t="n">
-        <v>-4830</v>
-      </c>
-      <c r="C11" s="22" t="n">
-        <v>-8765.700000000001</v>
+      <c r="B11" s="23" t="n">
+        <v>-8489.780912</v>
+      </c>
+      <c r="C11" s="23" t="n">
+        <v>-13112.049791</v>
       </c>
       <c r="D11" s="18">
         <f>DCF!B12</f>
@@ -1662,13 +1629,13 @@
           <t>Change in working capital</t>
         </is>
       </c>
-      <c r="B12" s="28" t="inlineStr">
+      <c r="B12" s="29" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C12" s="28">
-        <f>-('Balance Sheet'!C16-'Balance Sheet'!B16)</f>
+      <c r="C12" s="29">
+        <f>-('Balance Sheet'!D16-'Balance Sheet'!C16)</f>
         <v/>
       </c>
       <c r="D12" s="18">
@@ -1698,33 +1665,33 @@
           <t>Free cash flow to the firm</t>
         </is>
       </c>
-      <c r="B13" s="29" t="inlineStr">
+      <c r="B13" s="30" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C13" s="29" t="inlineStr">
+      <c r="C13" s="30" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D13" s="29">
+      <c r="D13" s="30">
         <f>D9+D10+D11+D12</f>
         <v/>
       </c>
-      <c r="E13" s="29">
+      <c r="E13" s="30">
         <f>E9+E10+E11+E12</f>
         <v/>
       </c>
-      <c r="F13" s="29">
+      <c r="F13" s="30">
         <f>F9+F10+F11+F12</f>
         <v/>
       </c>
-      <c r="G13" s="29">
+      <c r="G13" s="30">
         <f>G9+G10+G11+G12</f>
         <v/>
       </c>
-      <c r="H13" s="29">
+      <c r="H13" s="30">
         <f>H9+H10+H11+H12</f>
         <v/>
       </c>
@@ -1733,7 +1700,7 @@
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>Cash conversion — operating cash flow as a share of EBITDA, FY2024</t>
+          <t>Cash conversion — operating cash flow as a share of EBITDA, FY2025</t>
         </is>
       </c>
       <c r="C15" s="11">
@@ -2083,17 +2050,17 @@
           <t>Free cash flow to the firm</t>
         </is>
       </c>
-      <c r="B11" s="28" t="inlineStr">
+      <c r="B11" s="29" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C11" s="28" t="inlineStr">
+      <c r="C11" s="29" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D11" s="28" t="inlineStr">
+      <c r="D11" s="29" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2164,38 +2131,38 @@
           <t>Invested capital</t>
         </is>
       </c>
-      <c r="B13" s="28" t="inlineStr">
+      <c r="B13" s="29" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C13" s="28" t="inlineStr">
+      <c r="C13" s="29" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="D13" s="18">
-        <f>'Balance Sheet'!D16+'Balance Sheet'!D5+Assumptions!$C$52</f>
+        <f>'Balance Sheet'!D16+'Balance Sheet'!D5+Assumptions!$C$45</f>
         <v/>
       </c>
       <c r="E13" s="18">
-        <f>'Balance Sheet'!E16+'Balance Sheet'!E5+Assumptions!$C$52</f>
+        <f>'Balance Sheet'!E16+'Balance Sheet'!E5+Assumptions!$C$45</f>
         <v/>
       </c>
       <c r="F13" s="18">
-        <f>'Balance Sheet'!F16+'Balance Sheet'!F5+Assumptions!$C$52</f>
+        <f>'Balance Sheet'!F16+'Balance Sheet'!F5+Assumptions!$C$45</f>
         <v/>
       </c>
       <c r="G13" s="18">
-        <f>'Balance Sheet'!G16+'Balance Sheet'!G5+Assumptions!$C$52</f>
+        <f>'Balance Sheet'!G16+'Balance Sheet'!G5+Assumptions!$C$45</f>
         <v/>
       </c>
       <c r="H13" s="18">
-        <f>'Balance Sheet'!H16+'Balance Sheet'!H5+Assumptions!$C$52</f>
+        <f>'Balance Sheet'!H16+'Balance Sheet'!H5+Assumptions!$C$45</f>
         <v/>
       </c>
       <c r="I13" s="18">
-        <f>'Balance Sheet'!I16+'Balance Sheet'!I5+Assumptions!$C$52</f>
+        <f>'Balance Sheet'!I16+'Balance Sheet'!I5+Assumptions!$C$45</f>
         <v/>
       </c>
     </row>
@@ -2467,7 +2434,7 @@
           <t>Simulated paths</t>
         </is>
       </c>
-      <c r="C15" s="22" t="n">
+      <c r="C15" s="23" t="n">
         <v>50000</v>
       </c>
     </row>
@@ -2515,10 +2482,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
@@ -2587,111 +2554,111 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>13.1%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>71.48013737611937</v>
+        <v>65.329844401984</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>75.158505958635</v>
+        <v>68.35354257523431</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>79.66249997898875</v>
+        <v>71.9670712933261</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>85.33897230281774</v>
+        <v>76.39345107557055</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>92.76070177891306</v>
+        <v>81.98435185876774</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>14.9%</t>
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>64.51999723358476</v>
+        <v>58.4402879098668</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>67.23266415979741</v>
+        <v>60.6461755538821</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>70.47099233404454</v>
+        <v>63.21971152566643</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>74.42869060586594</v>
+        <v>66.28434770102153</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>79.40797299188714</v>
+        <v>70.02577372147603</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>15.1%</t>
+          <t>15.9%</t>
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>58.71390500851878</v>
+        <v>52.6302713847032</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>60.7356474116613</v>
+        <v>54.24351203947743</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>63.09639197519306</v>
+        <v>56.08399377388404</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>65.90739638220869</v>
+        <v>58.22034038779206</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>69.3345836803008</v>
+        <v>60.75189974055389</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>16.1%</t>
+          <t>16.9%</t>
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>53.79809034203993</v>
+        <v>47.66687793345727</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>55.314134925563</v>
+        <v>48.84248007666995</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>57.04924305755583</v>
+        <v>50.15437928765454</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>59.06822004769293</v>
+        <v>51.63997115359249</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>61.46422928886715</v>
+        <v>53.35170855849378</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>17.1%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>49.58340787307901</v>
+        <v>43.37959572111903</v>
       </c>
       <c r="C10" s="7" t="n">
-        <v>50.72236517614795</v>
+        <v>44.22702715685592</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>52.00135637265844</v>
+        <v>45.15076181775254</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>53.45808918007977</v>
+        <v>46.16998066974453</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>55.14514468831749</v>
+        <v>47.31088154269673</v>
       </c>
     </row>
     <row r="12">
@@ -2705,171 +2672,160 @@
       <c r="A13" s="5" t="inlineStr"/>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>23.9%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>25.4%</t>
+          <t>25.1%</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>26.6%</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>28.4%</t>
+          <t>28.1%</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>29.9%</t>
+          <t>29.6%</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>terminal 13.1%</t>
+          <t>terminal 13.9%</t>
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>84.33728753089692</v>
+        <v>76.53066395732843</v>
       </c>
       <c r="C14" s="7" t="n">
-        <v>81.95820408756369</v>
+        <v>74.20763706152702</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>79.66249997898875</v>
+        <v>71.9670712933261</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>77.44651129819714</v>
+        <v>69.80531513594863</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>75.30676865150218</v>
+        <v>67.71891197265076</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>terminal 14.1%</t>
+          <t>terminal 14.9%</t>
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>74.62341007610547</v>
+        <v>67.28261009519261</v>
       </c>
       <c r="C15" s="7" t="n">
-        <v>72.51027129509237</v>
+        <v>65.21451934442834</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>70.47099233404454</v>
+        <v>63.21971152566643</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>68.50233381059978</v>
+        <v>61.29494639096928</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>66.60122807292484</v>
+        <v>59.4371564326104</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>terminal 15.1%</t>
+          <t>terminal 15.9%</t>
         </is>
       </c>
       <c r="B16" s="7" t="n">
-        <v>66.82989265057586</v>
+        <v>59.73868410008669</v>
       </c>
       <c r="C16" s="7" t="n">
-        <v>64.9300279088521</v>
+        <v>57.87843695583718</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>63.09639197519306</v>
+        <v>56.08399377388404</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>61.32608564835102</v>
+        <v>54.35244928326305</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>59.61636320712214</v>
+        <v>52.68105291114693</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>terminal 16.1%</t>
+          <t>terminal 16.9%</t>
         </is>
       </c>
       <c r="B17" s="7" t="n">
-        <v>60.43940513969982</v>
+        <v>53.47006721636905</v>
       </c>
       <c r="C17" s="7" t="n">
-        <v>58.71433541623137</v>
+        <v>51.78242507173835</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>57.04924305755583</v>
+        <v>50.15437928765454</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>55.44150743399135</v>
+        <v>48.58330249404308</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>53.88864645585161</v>
+        <v>47.06670705720629</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>terminal 17.1%</t>
+          <t>terminal 17.9%</t>
         </is>
       </c>
       <c r="B18" s="7" t="n">
-        <v>55.10506833536628</v>
+        <v>48.18057399728519</v>
       </c>
       <c r="C18" s="7" t="n">
-        <v>53.52583022982751</v>
+        <v>46.63848559892643</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>52.00135637265844</v>
+        <v>45.15076181775254</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>50.52925833918371</v>
+        <v>43.71500938002328</v>
       </c>
       <c r="F18" s="7" t="n">
-        <v>49.1072737958847</v>
+        <v>42.32896215043171</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="20" t="inlineStr">
         <is>
-          <t>Single-driver sensitivities</t>
+          <t>Single-driver sensitivities — five engine re-runs per row; the parameter grid for each row is shown beside its name</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>Driver</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+          <t>Driver (parameter grid)</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr"/>
       <c r="C21" s="5" t="inlineStr"/>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>Base</t>
-        </is>
-      </c>
+      <c r="D21" s="5" t="inlineStr"/>
       <c r="E21" s="5" t="inlineStr"/>
-      <c r="F21" s="5" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G21" s="5" t="inlineStr">
+      <c r="F21" s="5" t="inlineStr"/>
+      <c r="G21" s="5" t="inlineStr"/>
+      <c r="H21" s="5" t="inlineStr">
         <is>
           <t>Swing</t>
         </is>
@@ -2878,23 +2834,23 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Beta</t>
+          <t>Beta  (0.60 / 0.80 / 1.01 / 1.15 / 1.30)</t>
         </is>
       </c>
       <c r="B22" s="7" t="n">
-        <v>86.86398352810841</v>
+        <v>82.1040695099194</v>
       </c>
       <c r="C22" s="7" t="n">
-        <v>73.76938856958702</v>
+        <v>67.65449935590391</v>
       </c>
       <c r="D22" s="7" t="n">
-        <v>63.09639197519306</v>
+        <v>56.08399377388404</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>57.1692154119707</v>
+        <v>49.74342393917833</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>51.73397898456535</v>
+        <v>43.98578978959206</v>
       </c>
       <c r="H22" s="10">
         <f>MAX(B22:F22)-MIN(B22:F22)</f>
@@ -2904,23 +2860,23 @@
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>Exchange-rate path multiplier</t>
+          <t>Exchange-rate path multiplier  (0.90x / 1.00x / 1.20x / 1.45x / 1.70x)</t>
         </is>
       </c>
       <c r="B23" s="7" t="n">
-        <v>71.93944315776433</v>
+        <v>52.41845656686412</v>
       </c>
       <c r="C23" s="7" t="n">
-        <v>63.09639197519306</v>
+        <v>56.08399377388404</v>
       </c>
       <c r="D23" s="7" t="n">
-        <v>45.41028961005051</v>
+        <v>63.41506818792391</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>23.30266165362228</v>
+        <v>72.57891120547374</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>1.195033697194072</v>
+        <v>81.74275422302357</v>
       </c>
       <c r="H23" s="10">
         <f>MAX(B23:F23)-MIN(B23:F23)</f>
@@ -2930,23 +2886,23 @@
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>EBITDA margin shift</t>
+          <t>Segment margins, multiplicative  (0.850x / 0.925x / 1.000x / 1.075x / 1.150x)</t>
         </is>
       </c>
       <c r="B24" s="7" t="n">
-        <v>42.21530497281732</v>
+        <v>30.09596871603819</v>
       </c>
       <c r="C24" s="7" t="n">
-        <v>52.6558484740052</v>
+        <v>43.08998124496109</v>
       </c>
       <c r="D24" s="7" t="n">
-        <v>63.09639197519306</v>
+        <v>56.08399377388404</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>73.53693547638095</v>
+        <v>69.078006302807</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>83.97747897756886</v>
+        <v>82.07201883172988</v>
       </c>
       <c r="H24" s="10">
         <f>MAX(B24:F24)-MIN(B24:F24)</f>
@@ -2956,23 +2912,23 @@
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>Working capital / revenue</t>
+          <t>Copper price multiplier  (0.850x / 0.925x / 1.000x / 1.075x / 1.150x)</t>
         </is>
       </c>
       <c r="B25" s="7" t="n">
-        <v>66.1820174425543</v>
+        <v>50.58568796335414</v>
       </c>
       <c r="C25" s="7" t="n">
-        <v>64.63920470887369</v>
+        <v>53.33484086861908</v>
       </c>
       <c r="D25" s="7" t="n">
-        <v>63.09639197519306</v>
+        <v>56.08399377388404</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>61.55357924151245</v>
+        <v>58.83314667914899</v>
       </c>
       <c r="F25" s="7" t="n">
-        <v>60.01076650783185</v>
+        <v>61.58229958441391</v>
       </c>
       <c r="H25" s="10">
         <f>MAX(B25:F25)-MIN(B25:F25)</f>
@@ -2982,26 +2938,78 @@
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>Terminal return on invested capital</t>
+          <t>Working capital / revenue  (17.0% / 18.5% / 19.9% / 21.5% / 23.0%)</t>
         </is>
       </c>
       <c r="B26" s="7" t="n">
-        <v>55.97972245871841</v>
+        <v>62.98785448545478</v>
       </c>
       <c r="C26" s="7" t="n">
-        <v>59.77877118391308</v>
+        <v>59.41689204843545</v>
       </c>
       <c r="D26" s="7" t="n">
-        <v>63.09639197519306</v>
+        <v>56.08399377388404</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>65.62346153036643</v>
+        <v>52.27496717439674</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>67.37686863430243</v>
+        <v>48.70400473737737</v>
       </c>
       <c r="H26" s="10">
         <f>MAX(B26:F26)-MIN(B26:F26)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>Terminal return on invested capital  (15.0% / 18.0% / 20.4% / 26.0% / 30.0%)</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="n">
+        <v>49.68012825683863</v>
+      </c>
+      <c r="C27" s="7" t="n">
+        <v>53.7154504510227</v>
+      </c>
+      <c r="D27" s="7" t="n">
+        <v>56.08399377388404</v>
+      </c>
+      <c r="E27" s="7" t="n">
+        <v>59.92363844207513</v>
+      </c>
+      <c r="F27" s="7" t="n">
+        <v>61.78609483939085</v>
+      </c>
+      <c r="H27" s="10">
+        <f>MAX(B27:F27)-MIN(B27:F27)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>Terminal growth (at base cost of capital)  (3% / 4% / 5% / 6% / 7%)</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="n">
+        <v>52.6302713847032</v>
+      </c>
+      <c r="C28" s="7" t="n">
+        <v>54.24351203947743</v>
+      </c>
+      <c r="D28" s="7" t="n">
+        <v>56.08399377388404</v>
+      </c>
+      <c r="E28" s="7" t="n">
+        <v>58.22034038779206</v>
+      </c>
+      <c r="F28" s="7" t="n">
+        <v>60.75189974055389</v>
+      </c>
+      <c r="H28" s="10">
+        <f>MAX(B28:F28)-MIN(B28:F28)</f>
         <v/>
       </c>
     </row>
@@ -3463,35 +3471,35 @@
           <t>Net debt / EBITDA</t>
         </is>
       </c>
-      <c r="B14" s="34">
+      <c r="B14" s="35">
         <f>'Balance Sheet'!B18</f>
         <v/>
       </c>
-      <c r="C14" s="34">
+      <c r="C14" s="35">
         <f>'Balance Sheet'!C18</f>
         <v/>
       </c>
-      <c r="D14" s="34">
+      <c r="D14" s="35">
         <f>'Balance Sheet'!D18</f>
         <v/>
       </c>
-      <c r="E14" s="34">
+      <c r="E14" s="35">
         <f>'Balance Sheet'!E18</f>
         <v/>
       </c>
-      <c r="F14" s="34">
+      <c r="F14" s="35">
         <f>'Balance Sheet'!F18</f>
         <v/>
       </c>
-      <c r="G14" s="34">
+      <c r="G14" s="35">
         <f>'Balance Sheet'!G18</f>
         <v/>
       </c>
-      <c r="H14" s="34">
+      <c r="H14" s="35">
         <f>'Balance Sheet'!H18</f>
         <v/>
       </c>
-      <c r="I14" s="34">
+      <c r="I14" s="35">
         <f>'Balance Sheet'!I18</f>
         <v/>
       </c>
@@ -3502,36 +3510,36 @@
           <t>Interest cover (EBIT / net interest)</t>
         </is>
       </c>
-      <c r="B15" s="34" t="inlineStr">
+      <c r="B15" s="35" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C15" s="34">
+      <c r="C15" s="35">
         <f>-'Income Statement'!C10/'Income Statement'!C11</f>
         <v/>
       </c>
-      <c r="D15" s="34">
+      <c r="D15" s="35">
         <f>-'Income Statement'!D10/'Income Statement'!D11</f>
         <v/>
       </c>
-      <c r="E15" s="34">
+      <c r="E15" s="35">
         <f>-'Income Statement'!E10/'Income Statement'!E11</f>
         <v/>
       </c>
-      <c r="F15" s="34">
+      <c r="F15" s="35">
         <f>-'Income Statement'!F10/'Income Statement'!F11</f>
         <v/>
       </c>
-      <c r="G15" s="34">
+      <c r="G15" s="35">
         <f>-'Income Statement'!G10/'Income Statement'!G11</f>
         <v/>
       </c>
-      <c r="H15" s="34">
+      <c r="H15" s="35">
         <f>-'Income Statement'!H10/'Income Statement'!H11</f>
         <v/>
       </c>
-      <c r="I15" s="34">
+      <c r="I15" s="35">
         <f>-'Income Statement'!I10/'Income Statement'!I11</f>
         <v/>
       </c>
@@ -3581,18 +3589,18 @@
           <t>Capital expenditure / revenue</t>
         </is>
       </c>
-      <c r="B17" s="11">
-        <f>-'Cash Flow'!B11/'Income Statement'!B5</f>
-        <v/>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C17" s="11">
-        <f>-'Cash Flow'!C11/'Income Statement'!C5</f>
-        <v/>
-      </c>
-      <c r="D17" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <f>-'Cash Flow'!B11/'Income Statement'!C5</f>
+        <v/>
+      </c>
+      <c r="D17" s="11">
+        <f>-'Cash Flow'!C11/'Income Statement'!D5</f>
+        <v/>
       </c>
       <c r="E17" s="11">
         <f>-'Cash Flow'!D11/'Income Statement'!E5</f>
@@ -3622,13 +3630,13 @@
         </is>
       </c>
       <c r="B18" s="9" t="n">
-        <v>0.2079305448304614</v>
+        <v>0.2012516504606288</v>
       </c>
       <c r="C18" s="9" t="n">
-        <v>0.3172037113507076</v>
+        <v>0.3037580263923543</v>
       </c>
       <c r="D18" s="9" t="n">
-        <v>0.2640762760437433</v>
+        <v>0.5146285136141233</v>
       </c>
       <c r="E18" s="11" t="inlineStr">
         <is>
@@ -3663,13 +3671,13 @@
         </is>
       </c>
       <c r="B19" s="9" t="n">
-        <v>0.04635583499957009</v>
+        <v>0.04486693009301836</v>
       </c>
       <c r="C19" s="9" t="n">
-        <v>0.07886018916845154</v>
+        <v>0.07551752174309861</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v>0.05528848097541515</v>
+        <v>0.1079821501300804</v>
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
@@ -3700,7 +3708,7 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Terminal growth reconciliation: actual NOPAT compound growth FY2023–FY2025 was 30.5%; the implied growth from stable years only (FY2024 excluded as a debt-funded capacity burst) is 5.1%; the adopted terminal growth is 5.0%, below the blended nominal ceiling of 10.5%.</t>
+          <t>Terminal growth reconciliation: actual NOPAT compound growth FY2023–FY2025 was 26.9%; the implied growth from stable years only (FY2024 excluded as a debt-funded capacity burst) is 7.6%; the adopted terminal growth is 5.0%, below the blended nominal ceiling of 11.1%.</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3854,7 @@
       </c>
       <c r="C8" s="40" t="inlineStr">
         <is>
-          <t>the right frame for the roughly 27% that is turnkey project work</t>
+          <t>the right frame for the roughly 32% that is the Constructions and infrastructure segment</t>
         </is>
       </c>
       <c r="D8" s="40" t="inlineStr">
@@ -3873,7 +3881,7 @@
           <t>Trailing enterprise value / EBITDA</t>
         </is>
       </c>
-      <c r="B11" s="32">
+      <c r="B11" s="33">
         <f>'Relative &amp; Normalized'!C13</f>
         <v/>
       </c>
@@ -3884,7 +3892,7 @@
           <t>Trailing price / earnings</t>
         </is>
       </c>
-      <c r="B12" s="32">
+      <c r="B12" s="33">
         <f>'Relative &amp; Normalized'!C14</f>
         <v/>
       </c>
@@ -3895,7 +3903,7 @@
           <t>Trailing price / book</t>
         </is>
       </c>
-      <c r="B13" s="32">
+      <c r="B13" s="33">
         <f>'Relative &amp; Normalized'!C15</f>
         <v/>
       </c>
@@ -3906,7 +3914,7 @@
           <t>Justified enterprise value / EBITDA applied</t>
         </is>
       </c>
-      <c r="B14" s="32">
+      <c r="B14" s="33">
         <f>'Relative &amp; Normalized'!C6</f>
         <v/>
       </c>
@@ -3917,7 +3925,7 @@
           <t>Justified price / earnings applied</t>
         </is>
       </c>
-      <c r="B15" s="32">
+      <c r="B15" s="33">
         <f>'Relative &amp; Normalized'!C27</f>
         <v/>
       </c>
@@ -4009,14 +4017,14 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>35.37439268305282</v>
+        <v>19.945090316451</v>
       </c>
       <c r="C5" s="8">
-        <f>DCF!C31</f>
+        <f>DCF!C62</f>
         <v/>
       </c>
       <c r="D5" s="7" t="n">
-        <v>110.3869768355961</v>
+        <v>122.3348933382508</v>
       </c>
       <c r="E5" s="9" t="n">
         <v>0.45</v>
@@ -4036,15 +4044,17 @@
           <t>Relative multiples</t>
         </is>
       </c>
-      <c r="B6" s="7" t="n">
-        <v>61.2294172643708</v>
+      <c r="B6" s="8">
+        <f>'Relative &amp; Normalized'!C12</f>
+        <v/>
       </c>
       <c r="C6" s="8">
         <f>'Relative &amp; Normalized'!C11</f>
         <v/>
       </c>
-      <c r="D6" s="7" t="n">
-        <v>91.61541724668523</v>
+      <c r="D6" s="8">
+        <f>'Relative &amp; Normalized'!D12</f>
+        <v/>
       </c>
       <c r="E6" s="9" t="n">
         <v>0.2</v>
@@ -4064,15 +4074,17 @@
           <t>Normalised earnings power</t>
         </is>
       </c>
-      <c r="B7" s="7" t="n">
-        <v>94.04297714970363</v>
+      <c r="B7" s="8">
+        <f>'Relative &amp; Normalized'!E28</f>
+        <v/>
       </c>
       <c r="C7" s="8">
         <f>'Relative &amp; Normalized'!C28</f>
         <v/>
       </c>
-      <c r="D7" s="7" t="n">
-        <v>154.4991767459417</v>
+      <c r="D7" s="8">
+        <f>'Relative &amp; Normalized'!F28</f>
+        <v/>
       </c>
       <c r="E7" s="9" t="n">
         <v>0.2</v>
@@ -4092,15 +4104,17 @@
           <t>Book value and sustainable return</t>
         </is>
       </c>
-      <c r="B8" s="7" t="n">
-        <v>33.76534925901321</v>
+      <c r="B8" s="8">
+        <f>'Relative &amp; Normalized'!E36</f>
+        <v/>
       </c>
       <c r="C8" s="8">
         <f>'Relative &amp; Normalized'!C36</f>
         <v/>
       </c>
-      <c r="D8" s="7" t="n">
-        <v>53.71022096338332</v>
+      <c r="D8" s="8">
+        <f>'Relative &amp; Normalized'!F36</f>
+        <v/>
       </c>
       <c r="E8" s="9" t="n">
         <v>0.15</v>
@@ -4372,7 +4386,7 @@
         </is>
       </c>
       <c r="C5" s="8">
-        <f>DCF!C31</f>
+        <f>DCF!C62</f>
         <v/>
       </c>
     </row>
@@ -4388,7 +4402,7 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>35.37439268305282</v>
+        <v>19.945090316451</v>
       </c>
     </row>
     <row r="7">
@@ -4403,7 +4417,7 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>110.3869768355961</v>
+        <v>122.3348933382508</v>
       </c>
     </row>
     <row r="8">
@@ -4480,7 +4494,7 @@
         </is>
       </c>
       <c r="C15" s="9" t="n">
-        <v>0.600860789848202</v>
+        <v>0.5254856747391311</v>
       </c>
     </row>
     <row r="16">
@@ -4491,7 +4505,7 @@
       </c>
       <c r="C16" s="21" t="inlineStr">
         <is>
-          <t>26.9% → 15.1%</t>
+          <t>26.6% → 15.9%</t>
         </is>
       </c>
     </row>
@@ -4501,8 +4515,9 @@
           <t>Hard-currency cost of capital for the foreign leg</t>
         </is>
       </c>
-      <c r="C17" s="9" t="n">
-        <v>0.10119375</v>
+      <c r="C17" s="22">
+        <f>(1-Assumptions!$C$59)*(Assumptions!$C$56+Assumptions!$C$33*Assumptions!$C$57)+Assumptions!$C$59*Assumptions!$C$58*(1-Assumptions!$C$7)</f>
+        <v/>
       </c>
     </row>
     <row r="18">
@@ -4512,7 +4527,7 @@
         </is>
       </c>
       <c r="C18" s="7" t="n">
-        <v>91.14622861923802</v>
+        <v>85.97488545126602</v>
       </c>
     </row>
     <row r="19">
@@ -4572,13 +4587,13 @@
         </is>
       </c>
       <c r="C23" s="7" t="n">
-        <v>137.7034929664235</v>
+        <v>146.6166527148279</v>
       </c>
       <c r="D23" s="7" t="n">
-        <v>101.4657316594699</v>
+        <v>107.5464809477679</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>173.941254273377</v>
+        <v>185.6868244818879</v>
       </c>
     </row>
     <row r="24">
@@ -4593,13 +4608,13 @@
         </is>
       </c>
       <c r="C24" s="7" t="n">
-        <v>66.19078084024615</v>
+        <v>61.91445272087842</v>
       </c>
       <c r="D24" s="7" t="n">
-        <v>40.8187533998155</v>
+        <v>37.47247721279566</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>72.60004748131544</v>
+        <v>68.08877752143243</v>
       </c>
     </row>
     <row r="25">
@@ -4614,13 +4629,13 @@
         </is>
       </c>
       <c r="C25" s="7" t="n">
-        <v>60.72264310179215</v>
+        <v>53.24641887790025</v>
       </c>
       <c r="D25" s="7" t="n">
-        <v>49.99375810242254</v>
+        <v>46.17387104421569</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>91.14622861923802</v>
+        <v>85.97488545126602</v>
       </c>
     </row>
     <row r="26">
@@ -4648,7 +4663,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H67"/>
+  <dimension ref="A1:H69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -4744,7 +4759,7 @@
           <t>Shares outstanding (mn)</t>
         </is>
       </c>
-      <c r="C6" s="22" t="n">
+      <c r="C6" s="23" t="n">
         <v>2140.777876</v>
       </c>
     </row>
@@ -4755,7 +4770,7 @@
         </is>
       </c>
       <c r="C7" s="9" t="n">
-        <v>0.25</v>
+        <v>0.245</v>
       </c>
     </row>
     <row r="8">
@@ -4774,14 +4789,14 @@
           <t>FY2025 average USD/EGP</t>
         </is>
       </c>
-      <c r="C9" s="23" t="n">
+      <c r="C9" s="24" t="n">
         <v>49.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>Revenue drivers — the unit build</t>
+          <t>Revenue drivers — the three disclosed segments</t>
         </is>
       </c>
       <c r="B11" s="15" t="n"/>
@@ -4798,19 +4813,19 @@
           <t>Copper (USD/tonne)</t>
         </is>
       </c>
-      <c r="B12" s="22" t="n">
+      <c r="B12" s="23" t="n">
         <v>13400</v>
       </c>
-      <c r="C12" s="22" t="n">
+      <c r="C12" s="23" t="n">
         <v>14000</v>
       </c>
-      <c r="D12" s="22" t="n">
+      <c r="D12" s="23" t="n">
         <v>14000</v>
       </c>
-      <c r="E12" s="22" t="n">
+      <c r="E12" s="23" t="n">
         <v>14000</v>
       </c>
-      <c r="F12" s="22" t="n">
+      <c r="F12" s="23" t="n">
         <v>14000</v>
       </c>
     </row>
@@ -4820,224 +4835,194 @@
           <t>USD/EGP path</t>
         </is>
       </c>
-      <c r="B13" s="23" t="n">
+      <c r="B13" s="24" t="n">
         <v>51</v>
       </c>
-      <c r="C13" s="23" t="n">
+      <c r="C13" s="24" t="n">
         <v>54</v>
       </c>
-      <c r="D13" s="23" t="n">
+      <c r="D13" s="24" t="n">
         <v>57.5</v>
       </c>
-      <c r="E13" s="23" t="n">
+      <c r="E13" s="24" t="n">
         <v>61</v>
       </c>
-      <c r="F13" s="23" t="n">
+      <c r="F13" s="24" t="n">
         <v>64.5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Cable volume growth</t>
+          <t>Cables — real (volume) growth over copper x FX</t>
         </is>
       </c>
       <c r="B14" s="9" t="n">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="C14" s="9" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="D14" s="9" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="E14" s="9" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="F14" s="9" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>Cable fabrication uplift over copper</t>
-        </is>
-      </c>
-      <c r="B15" s="24" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="C15" s="24" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="D15" s="24" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="E15" s="24" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="F15" s="24" t="n">
-        <v>1.3</v>
+          <t>Constructions and infrastructure — revenue growth</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="C15" s="9" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="D15" s="9" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="E15" s="9" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="F15" s="9" t="n">
+        <v>0.08</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Raw-material volume growth</t>
+          <t>Electrical products and digital solutions — revenue growth</t>
         </is>
       </c>
       <c r="B16" s="9" t="n">
-        <v>0.04</v>
+        <v>0.2</v>
       </c>
       <c r="C16" s="9" t="n">
-        <v>0.04</v>
+        <v>0.16</v>
       </c>
       <c r="D16" s="9" t="n">
-        <v>0.03</v>
+        <v>0.13</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>0.03</v>
+        <v>0.11</v>
       </c>
       <c r="F16" s="9" t="n">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>Transformer MVA growth</t>
-        </is>
-      </c>
-      <c r="B17" s="9" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="C17" s="9" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="D17" s="9" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="E17" s="9" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="F17" s="9" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>Meter unit growth</t>
-        </is>
-      </c>
-      <c r="B18" s="9" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="C18" s="9" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="D18" s="9" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="E18" s="9" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="F18" s="9" t="n">
-        <v>0.04</v>
-      </c>
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>Segment gross margins and corporate cost load</t>
+        </is>
+      </c>
+      <c r="B18" s="15" t="n"/>
+      <c r="C18" s="15" t="n"/>
+      <c r="D18" s="15" t="n"/>
+      <c r="E18" s="15" t="n"/>
+      <c r="F18" s="15" t="n"/>
+      <c r="G18" s="15" t="n"/>
+      <c r="H18" s="15" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>Order-book conversion rate</t>
+          <t>Cables — gross/segment margin</t>
         </is>
       </c>
       <c r="B19" s="9" t="n">
-        <v>0.27</v>
+        <v>0.14</v>
       </c>
       <c r="C19" s="9" t="n">
-        <v>0.265</v>
+        <v>0.145</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v>0.26</v>
+        <v>0.15</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>0.255</v>
+        <v>0.153</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>0.25</v>
+        <v>0.155</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Order-book book-to-bill</t>
-        </is>
-      </c>
-      <c r="B20" s="24" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="C20" s="24" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="D20" s="24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="E20" s="24" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="F20" s="24" t="n">
-        <v>1</v>
+          <t>Constructions and infrastructure — segment margin</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="n">
+        <v>0.068</v>
+      </c>
+      <c r="C20" s="9" t="n">
+        <v>0.07199999999999999</v>
+      </c>
+      <c r="D20" s="9" t="n">
+        <v>0.076</v>
+      </c>
+      <c r="E20" s="9" t="n">
+        <v>0.079</v>
+      </c>
+      <c r="F20" s="9" t="n">
+        <v>0.082</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>Other-lines revenue growth</t>
+          <t>Electrical products and digital solutions — segment margin</t>
         </is>
       </c>
       <c r="B21" s="9" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="C21" s="9" t="n">
-        <v>0.11</v>
+        <v>0.222</v>
       </c>
       <c r="D21" s="9" t="n">
-        <v>0.1</v>
+        <v>0.224</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>0.09</v>
+        <v>0.226</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>0.08</v>
+        <v>0.228</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Meter price inflation</t>
+          <t>Corporate cost load (% of revenue) — the bridge from segment profit to EBIT</t>
         </is>
       </c>
       <c r="B22" s="9" t="n">
-        <v>0.08</v>
+        <v>0.0455</v>
       </c>
       <c r="C22" s="9" t="n">
-        <v>0.075</v>
+        <v>0.0465</v>
       </c>
       <c r="D22" s="9" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.0475</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.0475</v>
       </c>
       <c r="F22" s="9" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.0485</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>Unit gross profit and cost load</t>
+          <t>Capital intensity</t>
         </is>
       </c>
       <c r="B24" s="15" t="n"/>
@@ -5051,466 +5036,450 @@
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>Gross profit per unit — growth</t>
-        </is>
-      </c>
-      <c r="B25" s="9" t="n">
-        <v>0.08500000000000001</v>
+          <t>Working capital / revenue</t>
+        </is>
       </c>
       <c r="C25" s="9" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="D25" s="9" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="E25" s="9" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="F25" s="9" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.199</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>Non-cable margin recovery factor</t>
-        </is>
-      </c>
-      <c r="B26" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="C26" s="24" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="D26" s="24" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="E26" s="24" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="F26" s="24" t="n">
-        <v>1.1</v>
+          <t>Capital expenditure / revenue</t>
+        </is>
+      </c>
+      <c r="B26" s="9" t="n">
+        <v>0.044</v>
+      </c>
+      <c r="C26" s="9" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="D26" s="9" t="n">
+        <v>0.036</v>
+      </c>
+      <c r="E26" s="9" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="F26" s="9" t="n">
+        <v>0.031</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>Operating load (% of revenue)</t>
-        </is>
-      </c>
-      <c r="B27" s="9" t="n">
-        <v>0.04</v>
+          <t>Depreciation and amortisation / revenue</t>
+        </is>
       </c>
       <c r="C27" s="9" t="n">
-        <v>0.043</v>
-      </c>
-      <c r="D27" s="9" t="n">
-        <v>0.046</v>
-      </c>
-      <c r="E27" s="9" t="n">
-        <v>0.048</v>
-      </c>
-      <c r="F27" s="9" t="n">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t>Cable gross profit per tonne, FY2025 (EGP)</t>
-        </is>
-      </c>
-      <c r="C28" s="22" t="n">
-        <v>88173</v>
+        <v>0.0125</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>Order book at FY2025 (EGP mn)</t>
-        </is>
-      </c>
-      <c r="C29" s="22" t="n">
-        <v>323700</v>
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>Cost of capital</t>
+        </is>
+      </c>
+      <c r="B29" s="15" t="n"/>
+      <c r="C29" s="15" t="n"/>
+      <c r="D29" s="15" t="n"/>
+      <c r="E29" s="15" t="n"/>
+      <c r="F29" s="15" t="n"/>
+      <c r="G29" s="15" t="n"/>
+      <c r="H29" s="15" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>Risk-free rate (10-year local currency)</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="n">
+        <v>0.2231</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="12" t="inlineStr">
-        <is>
-          <t>Capital intensity</t>
-        </is>
-      </c>
-      <c r="B31" s="15" t="n"/>
-      <c r="C31" s="15" t="n"/>
-      <c r="D31" s="15" t="n"/>
-      <c r="E31" s="15" t="n"/>
-      <c r="F31" s="15" t="n"/>
-      <c r="G31" s="15" t="n"/>
-      <c r="H31" s="15" t="n"/>
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>Sovereign default spread (netted out)</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="n">
+        <v>0.034</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>Working capital / revenue</t>
+          <t>Equity risk premium</t>
         </is>
       </c>
       <c r="C32" s="9" t="n">
-        <v>0.23</v>
+        <v>0.0941</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>Capital expenditure / revenue</t>
-        </is>
-      </c>
-      <c r="B33" s="9" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="C33" s="9" t="n">
-        <v>0.029</v>
-      </c>
-      <c r="D33" s="9" t="n">
-        <v>0.028</v>
-      </c>
-      <c r="E33" s="9" t="n">
-        <v>0.026</v>
-      </c>
-      <c r="F33" s="9" t="n">
-        <v>0.024</v>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="C33" s="25" t="n">
+        <v>1.009</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>Depreciation and amortisation / revenue</t>
+          <t>Cost of debt, blended</t>
         </is>
       </c>
       <c r="C34" s="9" t="n">
-        <v>0.0105</v>
+        <v>0.095</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>Cost of debt path</t>
+        </is>
+      </c>
+      <c r="B35" s="9" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="C35" s="9" t="n">
+        <v>0.089</v>
+      </c>
+      <c r="D35" s="9" t="n">
+        <v>0.08400000000000001</v>
+      </c>
+      <c r="E35" s="9" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="F35" s="9" t="n">
+        <v>0.077</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="12" t="inlineStr">
-        <is>
-          <t>Cost of capital</t>
-        </is>
-      </c>
-      <c r="B36" s="15" t="n"/>
-      <c r="C36" s="15" t="n"/>
-      <c r="D36" s="15" t="n"/>
-      <c r="E36" s="15" t="n"/>
-      <c r="F36" s="15" t="n"/>
-      <c r="G36" s="15" t="n"/>
-      <c r="H36" s="15" t="n"/>
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>Terminal risk-free rate</t>
+        </is>
+      </c>
+      <c r="C36" s="9" t="n">
+        <v>0.105</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>Risk-free rate (10-year local currency)</t>
+          <t>Terminal equity risk premium</t>
         </is>
       </c>
       <c r="C37" s="9" t="n">
-        <v>0.2231</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>Sovereign default spread (netted out)</t>
+          <t>Terminal cost of debt</t>
         </is>
       </c>
       <c r="C38" s="9" t="n">
-        <v>0.034</v>
+        <v>0.0888</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>Equity risk premium</t>
+          <t>Terminal debt weight</t>
         </is>
       </c>
       <c r="C39" s="9" t="n">
-        <v>0.0941</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>Beta</t>
-        </is>
-      </c>
-      <c r="C40" s="25" t="n">
-        <v>1.009</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="6" t="inlineStr">
-        <is>
-          <t>Cost of debt, blended</t>
-        </is>
-      </c>
-      <c r="C41" s="9" t="n">
-        <v>0.13</v>
+          <t>Terminal growth</t>
+        </is>
+      </c>
+      <c r="C40" s="9" t="n">
+        <v>0.05</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="6" t="inlineStr">
-        <is>
-          <t>Cost of debt path</t>
-        </is>
-      </c>
-      <c r="B42" s="9" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="C42" s="9" t="n">
-        <v>0.122</v>
-      </c>
-      <c r="D42" s="9" t="n">
-        <v>0.115</v>
-      </c>
-      <c r="E42" s="9" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="F42" s="9" t="n">
-        <v>0.106</v>
-      </c>
+      <c r="A42" s="12" t="inlineStr">
+        <is>
+          <t>Balance-sheet and bridge anchors</t>
+        </is>
+      </c>
+      <c r="B42" s="15" t="n"/>
+      <c r="C42" s="15" t="n"/>
+      <c r="D42" s="15" t="n"/>
+      <c r="E42" s="15" t="n"/>
+      <c r="F42" s="15" t="n"/>
+      <c r="G42" s="15" t="n"/>
+      <c r="H42" s="15" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>Terminal risk-free rate</t>
-        </is>
-      </c>
-      <c r="C43" s="9" t="n">
-        <v>0.105</v>
+          <t>Net bank debt at FY2025 (EGP mn, disclosed)</t>
+        </is>
+      </c>
+      <c r="C43" s="23" t="n">
+        <v>20560.003173</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>Terminal equity risk premium</t>
-        </is>
-      </c>
-      <c r="C44" s="9" t="n">
-        <v>0.07000000000000001</v>
+          <t>Equity-accounted investees at carrying value (EGP mn)</t>
+        </is>
+      </c>
+      <c r="C44" s="23" t="n">
+        <v>6757.650507</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>Terminal cost of debt</t>
-        </is>
-      </c>
-      <c r="C45" s="9" t="n">
-        <v>0.105</v>
+          <t>Intangible assets and goodwill (EGP mn)</t>
+        </is>
+      </c>
+      <c r="C45" s="23" t="n">
+        <v>1748.816945</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>Terminal debt weight</t>
-        </is>
-      </c>
-      <c r="C46" s="9" t="n">
-        <v>0.25</v>
+          <t>FY2025 profit after tax (EGP mn, disclosed)</t>
+        </is>
+      </c>
+      <c r="C46" s="23" t="n">
+        <v>19186.550057</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>Terminal growth</t>
-        </is>
-      </c>
-      <c r="C47" s="9" t="n">
-        <v>0.05</v>
+          <t>FY2025 profit after minority interests (EGP mn, disclosed)</t>
+        </is>
+      </c>
+      <c r="C47" s="23" t="n">
+        <v>17330.24499</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>FY2024 dividend per share (EGP)</t>
+        </is>
+      </c>
+      <c r="C48" s="7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="12" t="inlineStr">
-        <is>
-          <t>Balance-sheet and bridge anchors</t>
-        </is>
-      </c>
-      <c r="B49" s="15" t="n"/>
-      <c r="C49" s="15" t="n"/>
-      <c r="D49" s="15" t="n"/>
-      <c r="E49" s="15" t="n"/>
-      <c r="F49" s="15" t="n"/>
-      <c r="G49" s="15" t="n"/>
-      <c r="H49" s="15" t="n"/>
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>FY2025 dividend per share (EGP, ratified 6 May 2026, paid 4 June 2026)</t>
+        </is>
+      </c>
+      <c r="C49" s="7" t="n">
+        <v>1.85</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>Net bank debt at FY2025 (EGP mn, disclosed)</t>
-        </is>
-      </c>
-      <c r="C50" s="22" t="n">
-        <v>19789</v>
+          <t>Forecast dividend payout ratio (struck at the actual FY2025 rate)</t>
+        </is>
+      </c>
+      <c r="C50" s="9" t="n">
+        <v>0.25</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>Equity-accounted investees at carrying value (EGP mn)</t>
-        </is>
-      </c>
-      <c r="C51" s="22" t="n">
-        <v>6474</v>
+          <t>Growth in the share of equity-accounted investees</t>
+        </is>
+      </c>
+      <c r="C51" s="9" t="n">
+        <v>0.08</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>Intangible assets and goodwill (EGP mn)</t>
-        </is>
-      </c>
-      <c r="C52" s="22" t="n">
-        <v>1459.2</v>
+          <t>Yield assumed on surplus cash (blend of EGP deposit and hard-currency rates)</t>
+        </is>
+      </c>
+      <c r="C52" s="9" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
         <is>
-          <t>FY2025 profit after tax (EGP mn, disclosed)</t>
-        </is>
-      </c>
-      <c r="C53" s="22" t="n">
-        <v>19180</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="6" t="inlineStr">
-        <is>
-          <t>FY2025 profit after minority interests (EGP mn, disclosed)</t>
-        </is>
-      </c>
-      <c r="C54" s="22" t="n">
-        <v>17330</v>
+          <t>Days from the 31-Dec-2025 valuation date to the 5-Aug-2026 anchor</t>
+        </is>
+      </c>
+      <c r="C53" s="23" t="n">
+        <v>217</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="6" t="inlineStr">
-        <is>
-          <t>FY2024 dividend per share (EGP)</t>
-        </is>
-      </c>
-      <c r="C55" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="A55" s="12" t="inlineStr">
+        <is>
+          <t>Currency-of-discounting alternative</t>
+        </is>
+      </c>
+      <c r="B55" s="15" t="n"/>
+      <c r="C55" s="15" t="n"/>
+      <c r="D55" s="15" t="n"/>
+      <c r="E55" s="15" t="n"/>
+      <c r="F55" s="15" t="n"/>
+      <c r="G55" s="15" t="n"/>
+      <c r="H55" s="15" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
         <is>
-          <t>Forecast dividend payout ratio</t>
+          <t>US dollar risk-free rate</t>
         </is>
       </c>
       <c r="C56" s="9" t="n">
-        <v>0.25</v>
+        <v>0.043</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="6" t="inlineStr">
         <is>
-          <t>Growth in the share of equity-accounted investees</t>
+          <t>Hard-currency-leg equity risk premium</t>
         </is>
       </c>
       <c r="C57" s="9" t="n">
-        <v>0.08</v>
+        <v>0.075</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
         <is>
-          <t>Yield assumed on surplus cash</t>
+          <t>US dollar cost of debt</t>
         </is>
       </c>
       <c r="C58" s="9" t="n">
-        <v>0.1</v>
+        <v>0.065</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>Debt weight, USD leg</t>
+        </is>
+      </c>
+      <c r="C59" s="9" t="n">
+        <v>0.25</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="12" t="inlineStr">
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t>Terminal growth of the USD leg</t>
+        </is>
+      </c>
+      <c r="C60" s="9" t="n">
+        <v>0.035</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="12" t="inlineStr">
         <is>
           <t>Lens inputs</t>
         </is>
       </c>
-      <c r="B60" s="15" t="n"/>
-      <c r="C60" s="15" t="n"/>
-      <c r="D60" s="15" t="n"/>
-      <c r="E60" s="15" t="n"/>
-      <c r="F60" s="15" t="n"/>
-      <c r="G60" s="15" t="n"/>
-      <c r="H60" s="15" t="n"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="6" t="inlineStr">
-        <is>
-          <t>Justified EV/EBITDA</t>
-        </is>
-      </c>
-      <c r="C61" s="24" t="n">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="6" t="inlineStr">
-        <is>
-          <t>Justified price/earnings</t>
-        </is>
-      </c>
-      <c r="C62" s="24" t="n">
-        <v>9</v>
-      </c>
+      <c r="B62" s="15" t="n"/>
+      <c r="C62" s="15" t="n"/>
+      <c r="D62" s="15" t="n"/>
+      <c r="E62" s="15" t="n"/>
+      <c r="F62" s="15" t="n"/>
+      <c r="G62" s="15" t="n"/>
+      <c r="H62" s="15" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="6" t="inlineStr">
         <is>
-          <t>Sustainable return on equity</t>
-        </is>
-      </c>
-      <c r="C63" s="9" t="n">
-        <v>0.235</v>
+          <t>Justified EV/EBITDA</t>
+        </is>
+      </c>
+      <c r="C63" s="26" t="n">
+        <v>6.5</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="6" t="inlineStr">
         <is>
-          <t>Weight — discounted cash flow</t>
-        </is>
-      </c>
-      <c r="C64" s="9" t="n">
-        <v>0.45</v>
+          <t>Justified price/earnings</t>
+        </is>
+      </c>
+      <c r="C64" s="26" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="6" t="inlineStr">
         <is>
-          <t>Weight — relative</t>
+          <t>Sustainable return on equity</t>
         </is>
       </c>
       <c r="C65" s="9" t="n">
-        <v>0.2</v>
+        <v>0.235</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="6" t="inlineStr">
         <is>
-          <t>Weight — normalised</t>
+          <t>Weight — discounted cash flow</t>
         </is>
       </c>
       <c r="C66" s="9" t="n">
-        <v>0.2</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="6" t="inlineStr">
         <is>
+          <t>Weight — relative</t>
+        </is>
+      </c>
+      <c r="C67" s="9" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="6" t="inlineStr">
+        <is>
+          <t>Weight — normalised</t>
+        </is>
+      </c>
+      <c r="C68" s="9" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="6" t="inlineStr">
+        <is>
           <t>Weight — book</t>
         </is>
       </c>
-      <c r="C67" s="9" t="n">
+      <c r="C69" s="9" t="n">
         <v>0.15</v>
       </c>
     </row>
@@ -5599,11 +5568,11 @@
           <t>Enterprise value</t>
         </is>
       </c>
-      <c r="C7" s="26">
+      <c r="C7" s="27">
         <f>C5+C6</f>
         <v/>
       </c>
-      <c r="D7" s="27">
+      <c r="D7" s="28">
         <f>C7/Assumptions!$C$6</f>
         <v/>
       </c>
@@ -5615,7 +5584,7 @@
         </is>
       </c>
       <c r="C8" s="18">
-        <f>-Assumptions!$C$50</f>
+        <f>-Assumptions!$C$43</f>
         <v/>
       </c>
       <c r="D8" s="10">
@@ -5630,7 +5599,7 @@
         </is>
       </c>
       <c r="C9" s="18">
-        <f>Assumptions!$C$51</f>
+        <f>Assumptions!$C$44</f>
         <v/>
       </c>
       <c r="D9" s="10">
@@ -5644,7 +5613,7 @@
           <t>Equity before minority interests</t>
         </is>
       </c>
-      <c r="C10" s="28">
+      <c r="C10" s="29">
         <f>C7+C8+C9</f>
         <v/>
       </c>
@@ -5659,7 +5628,7 @@
           <t>Less minority interests at their share of group profit</t>
         </is>
       </c>
-      <c r="C11" s="28">
+      <c r="C11" s="29">
         <f>-C10*$C$15</f>
         <v/>
       </c>
@@ -5675,11 +5644,11 @@
         </is>
       </c>
       <c r="B12" s="15" t="n"/>
-      <c r="C12" s="29">
+      <c r="C12" s="30">
         <f>C10+C11</f>
         <v/>
       </c>
-      <c r="D12" s="30">
+      <c r="D12" s="31">
         <f>C12/Assumptions!$C$6</f>
         <v/>
       </c>
@@ -5702,7 +5671,7 @@
         </is>
       </c>
       <c r="C15" s="11">
-        <f>(Assumptions!$C$53-Assumptions!$C$54)/Assumptions!$C$53</f>
+        <f>(Assumptions!$C$46-Assumptions!$C$47)/Assumptions!$C$46</f>
         <v/>
       </c>
     </row>
@@ -5717,7 +5686,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I34"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5771,7 +5740,7 @@
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>Gross margin</t>
+          <t>Segment margin</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -5803,776 +5772,513 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Cables</t>
-        </is>
-      </c>
-      <c r="B5" s="22" t="n">
-        <v>92138.29685490194</v>
+          <t>Cables and its accessories</t>
+        </is>
+      </c>
+      <c r="B5" s="23" t="n">
+        <v>155792.929738</v>
       </c>
       <c r="C5" s="11">
-        <f>B5/$B$12</f>
+        <f>B5/$B$8</f>
         <v/>
       </c>
       <c r="D5" s="9" t="n">
-        <v>0.1479665487953016</v>
-      </c>
-      <c r="E5" s="22" t="n">
-        <v>145610.3678770696</v>
-      </c>
-      <c r="F5" s="22" t="n">
-        <v>169133.0260767016</v>
-      </c>
-      <c r="G5" s="22" t="n">
-        <v>187299.1659145696</v>
-      </c>
-      <c r="H5" s="22" t="n">
-        <v>206647.9840977443</v>
-      </c>
-      <c r="I5" s="22" t="n">
-        <v>227245.0290701096</v>
+        <v>0.134899552356732</v>
+      </c>
+      <c r="E5" s="23" t="n">
+        <v>221541.3228857327</v>
+      </c>
+      <c r="F5" s="23" t="n">
+        <v>252428.7347156312</v>
+      </c>
+      <c r="G5" s="23" t="n">
+        <v>276853.5521024677</v>
+      </c>
+      <c r="H5" s="23" t="n">
+        <v>302516.6726712704</v>
+      </c>
+      <c r="I5" s="23" t="n">
+        <v>329470.412277309</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Raw material (copper rod)</t>
-        </is>
-      </c>
-      <c r="B6" s="22" t="n">
-        <v>60448.00314509805</v>
+          <t>Constructions and infrastructure</t>
+        </is>
+      </c>
+      <c r="B6" s="23" t="n">
+        <v>90958.55022799999</v>
       </c>
       <c r="C6" s="11">
-        <f>B6/$B$12</f>
+        <f>B6/$B$8</f>
         <v/>
       </c>
       <c r="D6" s="9" t="n">
-        <v>0.1239697053155375</v>
-      </c>
-      <c r="E6" s="22" t="n">
-        <v>86793.07467340285</v>
-      </c>
-      <c r="F6" s="22" t="n">
-        <v>99853.94648992721</v>
-      </c>
-      <c r="G6" s="22" t="n">
-        <v>109515.7403864063</v>
-      </c>
-      <c r="H6" s="22" t="n">
-        <v>119667.3733648332</v>
-      </c>
-      <c r="I6" s="22" t="n">
-        <v>130329.5401556179</v>
+        <v>0.06452269254829619</v>
+      </c>
+      <c r="E6" s="23" t="n">
+        <v>107331.08926904</v>
+      </c>
+      <c r="F6" s="23" t="n">
+        <v>122357.4417667056</v>
+      </c>
+      <c r="G6" s="23" t="n">
+        <v>135816.7603610432</v>
+      </c>
+      <c r="H6" s="23" t="n">
+        <v>148040.2687935371</v>
+      </c>
+      <c r="I6" s="23" t="n">
+        <v>159883.4902970201</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>Engineering &amp; construction</t>
-        </is>
-      </c>
-      <c r="B7" s="22" t="n">
-        <v>87100.7</v>
+          <t>Electrical products and digital solutions</t>
+        </is>
+      </c>
+      <c r="B7" s="23" t="n">
+        <v>34297.601753</v>
       </c>
       <c r="C7" s="11">
-        <f>B7/$B$12</f>
+        <f>B7/$B$8</f>
         <v/>
       </c>
       <c r="D7" s="9" t="n">
-        <v>0.08991421158660849</v>
-      </c>
-      <c r="E7" s="22" t="n">
-        <v>87399</v>
-      </c>
-      <c r="F7" s="22" t="n">
-        <v>86938.53675000001</v>
-      </c>
-      <c r="G7" s="22" t="n">
-        <v>86428.38797775001</v>
-      </c>
-      <c r="H7" s="22" t="n">
-        <v>85427.48076159229</v>
-      </c>
-      <c r="I7" s="22" t="n">
-        <v>84179.56952301609</v>
+        <v>0.2217300370961013</v>
+      </c>
+      <c r="E7" s="23" t="n">
+        <v>41157.1221036</v>
+      </c>
+      <c r="F7" s="23" t="n">
+        <v>47742.261640176</v>
+      </c>
+      <c r="G7" s="23" t="n">
+        <v>53948.75565339887</v>
+      </c>
+      <c r="H7" s="23" t="n">
+        <v>59883.11877527275</v>
+      </c>
+      <c r="I7" s="23" t="n">
+        <v>65871.43065280003</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>Transformers</t>
-        </is>
-      </c>
-      <c r="B8" s="22" t="n">
-        <v>17703.5</v>
-      </c>
-      <c r="C8" s="11">
-        <f>B8/$B$12</f>
-        <v/>
-      </c>
-      <c r="D8" s="9" t="n">
-        <v>0.2769882639821222</v>
-      </c>
-      <c r="E8" s="22" t="n">
-        <v>20025.95817760357</v>
-      </c>
-      <c r="F8" s="22" t="n">
-        <v>23704.12363041715</v>
-      </c>
-      <c r="G8" s="22" t="n">
-        <v>26754.93213470232</v>
-      </c>
-      <c r="H8" s="22" t="n">
-        <v>29802.66788222058</v>
-      </c>
-      <c r="I8" s="22" t="n">
-        <v>33088.28987415392</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>Meters &amp; digital</t>
-        </is>
-      </c>
-      <c r="B9" s="22" t="n">
-        <v>16594.1</v>
-      </c>
-      <c r="C9" s="11">
-        <f>B9/$B$12</f>
-        <v/>
-      </c>
-      <c r="D9" s="9" t="n">
-        <v>0.2190169964043364</v>
-      </c>
-      <c r="E9" s="22" t="n">
-        <v>17815.54107615941</v>
-      </c>
-      <c r="F9" s="22" t="n">
-        <v>20109.29198971493</v>
-      </c>
-      <c r="G9" s="22" t="n">
-        <v>22592.78955044473</v>
-      </c>
-      <c r="H9" s="22" t="n">
-        <v>25141.25621173489</v>
-      </c>
-      <c r="I9" s="22" t="n">
-        <v>27977.18991241859</v>
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>Total revenue</t>
+        </is>
+      </c>
+      <c r="B8" s="32">
+        <f>SUM(B5:B7)</f>
+        <v/>
+      </c>
+      <c r="C8" s="14">
+        <f>SUM(C5:C7)</f>
+        <v/>
+      </c>
+      <c r="D8" s="15" t="n"/>
+      <c r="E8" s="32">
+        <f>SUM(E5:E7)</f>
+        <v/>
+      </c>
+      <c r="F8" s="32">
+        <f>SUM(F5:F7)</f>
+        <v/>
+      </c>
+      <c r="G8" s="32">
+        <f>SUM(G5:G7)</f>
+        <v/>
+      </c>
+      <c r="H8" s="32">
+        <f>SUM(H5:H7)</f>
+        <v/>
+      </c>
+      <c r="I8" s="32">
+        <f>SUM(I5:I7)</f>
+        <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>Other electrical products</t>
-        </is>
-      </c>
-      <c r="B10" s="22" t="n">
-        <v>3206.5</v>
-      </c>
-      <c r="C10" s="11">
-        <f>B10/$B$12</f>
-        <v/>
-      </c>
-      <c r="D10" s="9" t="n">
-        <v>0.4076827342682428</v>
-      </c>
-      <c r="E10" s="22" t="n">
-        <v>3591.28</v>
-      </c>
-      <c r="F10" s="22" t="n">
-        <v>3986.3208</v>
-      </c>
-      <c r="G10" s="22" t="n">
-        <v>4384.952880000001</v>
-      </c>
-      <c r="H10" s="22" t="n">
-        <v>4779.598639200001</v>
-      </c>
-      <c r="I10" s="22" t="n">
-        <v>5161.966530336002</v>
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Segment profit by segment (Note 16 basis)</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>FY26E</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>FY27E</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>FY28E</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>FY29E</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>FY30E</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Infrastructure investment</t>
-        </is>
-      </c>
-      <c r="B11" s="22" t="n">
-        <v>3857.9</v>
-      </c>
-      <c r="C11" s="11">
-        <f>B11/$B$12</f>
-        <v/>
-      </c>
-      <c r="D11" s="9" t="n">
-        <v>0.4966473826898447</v>
-      </c>
-      <c r="E11" s="22" t="n">
-        <v>4320.848000000001</v>
-      </c>
-      <c r="F11" s="22" t="n">
-        <v>4796.141280000002</v>
-      </c>
-      <c r="G11" s="22" t="n">
-        <v>5275.755408000002</v>
-      </c>
-      <c r="H11" s="22" t="n">
-        <v>5750.573394720002</v>
-      </c>
-      <c r="I11" s="22" t="n">
-        <v>6210.619266297603</v>
+          <t>Cables and its accessories</t>
+        </is>
+      </c>
+      <c r="B11" s="23" t="n">
+        <v>31015.78520400258</v>
+      </c>
+      <c r="C11" s="23" t="n">
+        <v>36602.16653376652</v>
+      </c>
+      <c r="D11" s="23" t="n">
+        <v>41528.03281537016</v>
+      </c>
+      <c r="E11" s="23" t="n">
+        <v>46285.05091870438</v>
+      </c>
+      <c r="F11" s="23" t="n">
+        <v>51067.91390298289</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="12" t="inlineStr">
-        <is>
-          <t>Total revenue</t>
-        </is>
-      </c>
-      <c r="B12" s="31">
-        <f>SUM(B5:B11)</f>
-        <v/>
-      </c>
-      <c r="C12" s="14">
-        <f>SUM(C5:C11)</f>
-        <v/>
-      </c>
-      <c r="D12" s="15" t="n"/>
-      <c r="E12" s="31">
-        <f>SUM(E5:E11)</f>
-        <v/>
-      </c>
-      <c r="F12" s="31">
-        <f>SUM(F5:F11)</f>
-        <v/>
-      </c>
-      <c r="G12" s="31">
-        <f>SUM(G5:G11)</f>
-        <v/>
-      </c>
-      <c r="H12" s="31">
-        <f>SUM(H5:H11)</f>
-        <v/>
-      </c>
-      <c r="I12" s="31">
-        <f>SUM(I5:I11)</f>
-        <v/>
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Constructions and infrastructure</t>
+        </is>
+      </c>
+      <c r="B12" s="23" t="n">
+        <v>7298.51407029472</v>
+      </c>
+      <c r="C12" s="23" t="n">
+        <v>8809.735807202804</v>
+      </c>
+      <c r="D12" s="23" t="n">
+        <v>10322.07378743929</v>
+      </c>
+      <c r="E12" s="23" t="n">
+        <v>11695.18123468943</v>
+      </c>
+      <c r="F12" s="23" t="n">
+        <v>13110.44620435565</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Electrical products and digital solutions</t>
+        </is>
+      </c>
+      <c r="B13" s="23" t="n">
+        <v>9054.566862792</v>
+      </c>
+      <c r="C13" s="23" t="n">
+        <v>10598.78208411907</v>
+      </c>
+      <c r="D13" s="23" t="n">
+        <v>12084.52126636135</v>
+      </c>
+      <c r="E13" s="23" t="n">
+        <v>13533.58484321164</v>
+      </c>
+      <c r="F13" s="23" t="n">
+        <v>15018.68618883841</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>Gross profit by segment</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>FY26E</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>FY27E</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>FY28E</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>FY29E</t>
-        </is>
-      </c>
-      <c r="F14" s="5" t="inlineStr">
-        <is>
-          <t>FY30E</t>
-        </is>
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>Group segment profit</t>
+        </is>
+      </c>
+      <c r="B14" s="32">
+        <f>SUM(B11:B13)</f>
+        <v/>
+      </c>
+      <c r="C14" s="32">
+        <f>SUM(C11:C13)</f>
+        <v/>
+      </c>
+      <c r="D14" s="32">
+        <f>SUM(D11:D13)</f>
+        <v/>
+      </c>
+      <c r="E14" s="32">
+        <f>SUM(E11:E13)</f>
+        <v/>
+      </c>
+      <c r="F14" s="32">
+        <f>SUM(F11:F13)</f>
+        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>Cables</t>
-        </is>
-      </c>
-      <c r="B15" s="22" t="n">
-        <v>25866.09381390937</v>
-      </c>
-      <c r="C15" s="22" t="n">
-        <v>29332.15038497323</v>
-      </c>
-      <c r="D15" s="22" t="n">
-        <v>32793.34413040007</v>
-      </c>
-      <c r="E15" s="22" t="n">
-        <v>36492.43334830921</v>
-      </c>
-      <c r="F15" s="22" t="n">
-        <v>40608.77982999848</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>Raw material (copper rod)</t>
-        </is>
-      </c>
-      <c r="B16" s="22" t="n">
-        <v>8455.914930776953</v>
-      </c>
-      <c r="C16" s="22" t="n">
-        <v>9497.683650248677</v>
-      </c>
-      <c r="D16" s="22" t="n">
-        <v>10516.31022173785</v>
-      </c>
-      <c r="E16" s="22" t="n">
-        <v>11590.02549537728</v>
-      </c>
-      <c r="F16" s="22" t="n">
-        <v>12773.3670984553</v>
+          <t>Group segment-profit margin</t>
+        </is>
+      </c>
+      <c r="B15" s="11">
+        <f>B14/E$8</f>
+        <v/>
+      </c>
+      <c r="C15" s="11">
+        <f>C14/F$8</f>
+        <v/>
+      </c>
+      <c r="D15" s="11">
+        <f>D14/G$8</f>
+        <v/>
+      </c>
+      <c r="E15" s="11">
+        <f>E14/H$8</f>
+        <v/>
+      </c>
+      <c r="F15" s="11">
+        <f>F14/I$8</f>
+        <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>Engineering &amp; construction</t>
-        </is>
-      </c>
-      <c r="B17" s="22" t="n">
-        <v>7858.412178457996</v>
-      </c>
-      <c r="C17" s="22" t="n">
-        <v>8129.690387904425</v>
-      </c>
-      <c r="D17" s="22" t="n">
-        <v>8315.120189181367</v>
-      </c>
-      <c r="E17" s="22" t="n">
-        <v>8372.447592754523</v>
-      </c>
-      <c r="F17" s="22" t="n">
-        <v>8325.833587898298</v>
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Segment EBIT contribution — segment profit less the pro-rata corporate load</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>FY26E</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>FY27E</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>FY28E</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>FY29E</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>FY30E</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Transformers</t>
-        </is>
-      </c>
-      <c r="B18" s="22" t="n">
-        <v>5746.110816863308</v>
-      </c>
-      <c r="C18" s="22" t="n">
-        <v>6640.205659967241</v>
-      </c>
-      <c r="D18" s="22" t="n">
-        <v>7566.514349532672</v>
-      </c>
-      <c r="E18" s="22" t="n">
-        <v>8500.978871699957</v>
-      </c>
-      <c r="F18" s="22" t="n">
-        <v>9550.849762354903</v>
+          <t>Cables and its accessories</t>
+        </is>
+      </c>
+      <c r="B18" s="29">
+        <f>B11-Assumptions!$B$22*E5</f>
+        <v/>
+      </c>
+      <c r="C18" s="29">
+        <f>C11-Assumptions!$C$22*F5</f>
+        <v/>
+      </c>
+      <c r="D18" s="29">
+        <f>D11-Assumptions!$D$22*G5</f>
+        <v/>
+      </c>
+      <c r="E18" s="29">
+        <f>E11-Assumptions!$E$22*H5</f>
+        <v/>
+      </c>
+      <c r="F18" s="29">
+        <f>F11-Assumptions!$F$22*I5</f>
+        <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>Meters &amp; digital</t>
-        </is>
-      </c>
-      <c r="B19" s="22" t="n">
-        <v>4179.911870032181</v>
-      </c>
-      <c r="C19" s="22" t="n">
-        <v>4740.020060616494</v>
-      </c>
-      <c r="D19" s="22" t="n">
-        <v>5350.297643420868</v>
-      </c>
-      <c r="E19" s="22" t="n">
-        <v>5953.811217598743</v>
-      </c>
-      <c r="F19" s="22" t="n">
-        <v>6625.401122943882</v>
+          <t>Constructions and infrastructure</t>
+        </is>
+      </c>
+      <c r="B19" s="29">
+        <f>B12-Assumptions!$B$22*E6</f>
+        <v/>
+      </c>
+      <c r="C19" s="29">
+        <f>C12-Assumptions!$C$22*F6</f>
+        <v/>
+      </c>
+      <c r="D19" s="29">
+        <f>D12-Assumptions!$D$22*G6</f>
+        <v/>
+      </c>
+      <c r="E19" s="29">
+        <f>E12-Assumptions!$E$22*H6</f>
+        <v/>
+      </c>
+      <c r="F19" s="29">
+        <f>F12-Assumptions!$F$22*I6</f>
+        <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Other electrical products</t>
-        </is>
-      </c>
-      <c r="B20" s="22" t="n">
-        <v>1464.102849922855</v>
-      </c>
-      <c r="C20" s="22" t="n">
-        <v>1690.160329950944</v>
-      </c>
-      <c r="D20" s="22" t="n">
-        <v>1912.806450338713</v>
-      </c>
-      <c r="E20" s="22" t="n">
-        <v>2123.930227707874</v>
-      </c>
-      <c r="F20" s="22" t="n">
-        <v>2314.889092217389</v>
+          <t>Electrical products and digital solutions</t>
+        </is>
+      </c>
+      <c r="B20" s="29">
+        <f>B13-Assumptions!$B$22*E7</f>
+        <v/>
+      </c>
+      <c r="C20" s="29">
+        <f>C13-Assumptions!$C$22*F7</f>
+        <v/>
+      </c>
+      <c r="D20" s="29">
+        <f>D13-Assumptions!$D$22*G7</f>
+        <v/>
+      </c>
+      <c r="E20" s="29">
+        <f>E13-Assumptions!$E$22*H7</f>
+        <v/>
+      </c>
+      <c r="F20" s="29">
+        <f>F13-Assumptions!$F$22*I7</f>
+        <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>Infrastructure investment</t>
-        </is>
-      </c>
-      <c r="B21" s="22" t="n">
-        <v>2145.937850200651</v>
-      </c>
-      <c r="C21" s="22" t="n">
-        <v>2477.270654271631</v>
-      </c>
-      <c r="D21" s="22" t="n">
-        <v>2803.603423151645</v>
-      </c>
-      <c r="E21" s="22" t="n">
-        <v>3113.047875744363</v>
-      </c>
-      <c r="F21" s="22" t="n">
-        <v>3392.936583838811</v>
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>Group EBIT</t>
+        </is>
+      </c>
+      <c r="B21" s="32">
+        <f>SUM(B18:B20)</f>
+        <v/>
+      </c>
+      <c r="C21" s="32">
+        <f>SUM(C18:C20)</f>
+        <v/>
+      </c>
+      <c r="D21" s="32">
+        <f>SUM(D18:D20)</f>
+        <v/>
+      </c>
+      <c r="E21" s="32">
+        <f>SUM(E18:E20)</f>
+        <v/>
+      </c>
+      <c r="F21" s="32">
+        <f>SUM(F18:F20)</f>
+        <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="12" t="inlineStr">
-        <is>
-          <t>Group gross profit</t>
-        </is>
-      </c>
-      <c r="B22" s="31">
-        <f>SUM(B15:B21)</f>
-        <v/>
-      </c>
-      <c r="C22" s="31">
-        <f>SUM(C15:C21)</f>
-        <v/>
-      </c>
-      <c r="D22" s="31">
-        <f>SUM(D15:D21)</f>
-        <v/>
-      </c>
-      <c r="E22" s="31">
-        <f>SUM(E15:E21)</f>
-        <v/>
-      </c>
-      <c r="F22" s="31">
-        <f>SUM(F15:F21)</f>
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>Add back depreciation and amortisation</t>
+        </is>
+      </c>
+      <c r="B22" s="29">
+        <f>Assumptions!$C$27*E8</f>
+        <v/>
+      </c>
+      <c r="C22" s="29">
+        <f>Assumptions!$C$27*F8</f>
+        <v/>
+      </c>
+      <c r="D22" s="29">
+        <f>Assumptions!$C$27*G8</f>
+        <v/>
+      </c>
+      <c r="E22" s="29">
+        <f>Assumptions!$C$27*H8</f>
+        <v/>
+      </c>
+      <c r="F22" s="29">
+        <f>Assumptions!$C$27*I8</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>Group gross margin</t>
-        </is>
-      </c>
-      <c r="B23" s="11">
-        <f>B22/E$12</f>
-        <v/>
-      </c>
-      <c r="C23" s="11">
-        <f>C22/F$12</f>
-        <v/>
-      </c>
-      <c r="D23" s="11">
-        <f>D22/G$12</f>
-        <v/>
-      </c>
-      <c r="E23" s="11">
-        <f>E22/H$12</f>
-        <v/>
-      </c>
-      <c r="F23" s="11">
-        <f>F22/I$12</f>
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>Group EBITDA</t>
+        </is>
+      </c>
+      <c r="B23" s="32">
+        <f>B21+B22</f>
+        <v/>
+      </c>
+      <c r="C23" s="32">
+        <f>C21+C22</f>
+        <v/>
+      </c>
+      <c r="D23" s="32">
+        <f>D21+D22</f>
+        <v/>
+      </c>
+      <c r="E23" s="32">
+        <f>E21+E22</f>
+        <v/>
+      </c>
+      <c r="F23" s="32">
+        <f>F21+F22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>Group EBITDA margin</t>
+        </is>
+      </c>
+      <c r="B24" s="11">
+        <f>B23/E$8</f>
+        <v/>
+      </c>
+      <c r="C24" s="11">
+        <f>C23/F$8</f>
+        <v/>
+      </c>
+      <c r="D24" s="11">
+        <f>D23/G$8</f>
+        <v/>
+      </c>
+      <c r="E24" s="11">
+        <f>E23/H$8</f>
+        <v/>
+      </c>
+      <c r="F24" s="11">
+        <f>F23/I$8</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>Segment EBITDA — gross profit less the operating load</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>FY26E</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>FY27E</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>FY28E</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>FY29E</t>
-        </is>
-      </c>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>FY30E</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t>Cables</t>
-        </is>
-      </c>
-      <c r="B26" s="28">
-        <f>B15-Assumptions!$B$27*E5</f>
-        <v/>
-      </c>
-      <c r="C26" s="28">
-        <f>C15-Assumptions!$C$27*F5</f>
-        <v/>
-      </c>
-      <c r="D26" s="28">
-        <f>D15-Assumptions!$D$27*G5</f>
-        <v/>
-      </c>
-      <c r="E26" s="28">
-        <f>E15-Assumptions!$E$27*H5</f>
-        <v/>
-      </c>
-      <c r="F26" s="28">
-        <f>F15-Assumptions!$F$27*I5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>Raw material (copper rod)</t>
-        </is>
-      </c>
-      <c r="B27" s="28">
-        <f>B16-Assumptions!$B$27*E6</f>
-        <v/>
-      </c>
-      <c r="C27" s="28">
-        <f>C16-Assumptions!$C$27*F6</f>
-        <v/>
-      </c>
-      <c r="D27" s="28">
-        <f>D16-Assumptions!$D$27*G6</f>
-        <v/>
-      </c>
-      <c r="E27" s="28">
-        <f>E16-Assumptions!$E$27*H6</f>
-        <v/>
-      </c>
-      <c r="F27" s="28">
-        <f>F16-Assumptions!$F$27*I6</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t>Engineering &amp; construction</t>
-        </is>
-      </c>
-      <c r="B28" s="28">
-        <f>B17-Assumptions!$B$27*E7</f>
-        <v/>
-      </c>
-      <c r="C28" s="28">
-        <f>C17-Assumptions!$C$27*F7</f>
-        <v/>
-      </c>
-      <c r="D28" s="28">
-        <f>D17-Assumptions!$D$27*G7</f>
-        <v/>
-      </c>
-      <c r="E28" s="28">
-        <f>E17-Assumptions!$E$27*H7</f>
-        <v/>
-      </c>
-      <c r="F28" s="28">
-        <f>F17-Assumptions!$F$27*I7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>Transformers</t>
-        </is>
-      </c>
-      <c r="B29" s="28">
-        <f>B18-Assumptions!$B$27*E8</f>
-        <v/>
-      </c>
-      <c r="C29" s="28">
-        <f>C18-Assumptions!$C$27*F8</f>
-        <v/>
-      </c>
-      <c r="D29" s="28">
-        <f>D18-Assumptions!$D$27*G8</f>
-        <v/>
-      </c>
-      <c r="E29" s="28">
-        <f>E18-Assumptions!$E$27*H8</f>
-        <v/>
-      </c>
-      <c r="F29" s="28">
-        <f>F18-Assumptions!$F$27*I8</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="6" t="inlineStr">
-        <is>
-          <t>Meters &amp; digital</t>
-        </is>
-      </c>
-      <c r="B30" s="28">
-        <f>B19-Assumptions!$B$27*E9</f>
-        <v/>
-      </c>
-      <c r="C30" s="28">
-        <f>C19-Assumptions!$C$27*F9</f>
-        <v/>
-      </c>
-      <c r="D30" s="28">
-        <f>D19-Assumptions!$D$27*G9</f>
-        <v/>
-      </c>
-      <c r="E30" s="28">
-        <f>E19-Assumptions!$E$27*H9</f>
-        <v/>
-      </c>
-      <c r="F30" s="28">
-        <f>F19-Assumptions!$F$27*I9</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="6" t="inlineStr">
-        <is>
-          <t>Other electrical products</t>
-        </is>
-      </c>
-      <c r="B31" s="28">
-        <f>B20-Assumptions!$B$27*E10</f>
-        <v/>
-      </c>
-      <c r="C31" s="28">
-        <f>C20-Assumptions!$C$27*F10</f>
-        <v/>
-      </c>
-      <c r="D31" s="28">
-        <f>D20-Assumptions!$D$27*G10</f>
-        <v/>
-      </c>
-      <c r="E31" s="28">
-        <f>E20-Assumptions!$E$27*H10</f>
-        <v/>
-      </c>
-      <c r="F31" s="28">
-        <f>F20-Assumptions!$F$27*I10</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t>Infrastructure investment</t>
-        </is>
-      </c>
-      <c r="B32" s="28">
-        <f>B21-Assumptions!$B$27*E11</f>
-        <v/>
-      </c>
-      <c r="C32" s="28">
-        <f>C21-Assumptions!$C$27*F11</f>
-        <v/>
-      </c>
-      <c r="D32" s="28">
-        <f>D21-Assumptions!$D$27*G11</f>
-        <v/>
-      </c>
-      <c r="E32" s="28">
-        <f>E21-Assumptions!$E$27*H11</f>
-        <v/>
-      </c>
-      <c r="F32" s="28">
-        <f>F21-Assumptions!$F$27*I11</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="12" t="inlineStr">
-        <is>
-          <t>Group EBITDA</t>
-        </is>
-      </c>
-      <c r="B33" s="31">
-        <f>SUM(B26:B32)</f>
-        <v/>
-      </c>
-      <c r="C33" s="31">
-        <f>SUM(C26:C32)</f>
-        <v/>
-      </c>
-      <c r="D33" s="31">
-        <f>SUM(D26:D32)</f>
-        <v/>
-      </c>
-      <c r="E33" s="31">
-        <f>SUM(E26:E32)</f>
-        <v/>
-      </c>
-      <c r="F33" s="31">
-        <f>SUM(F26:F32)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="6" t="inlineStr">
-        <is>
-          <t>Group EBITDA margin</t>
-        </is>
-      </c>
-      <c r="B34" s="11">
-        <f>B33/E$12</f>
-        <v/>
-      </c>
-      <c r="C34" s="11">
-        <f>C33/F$12</f>
-        <v/>
-      </c>
-      <c r="D34" s="11">
-        <f>D33/G$12</f>
-        <v/>
-      </c>
-      <c r="E34" s="11">
-        <f>E33/H$12</f>
-        <v/>
-      </c>
-      <c r="F34" s="11">
-        <f>F33/I$12</f>
-        <v/>
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>The corporate load is stated on the segment-profit-to-EBIT basis — the same basis as the audited historical bridge — so EBIT falls out first and EBITDA is EBIT plus D&amp;A, not the other way round.</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -6586,7 +6292,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -6636,8 +6342,8 @@
           <t>Justified enterprise value / EBITDA</t>
         </is>
       </c>
-      <c r="C6" s="32">
-        <f>Assumptions!$C$61</f>
+      <c r="C6" s="33">
+        <f>Assumptions!$C$63</f>
         <v/>
       </c>
     </row>
@@ -6647,7 +6353,7 @@
           <t>Implied enterprise value AS AT end-FY2027 (EGP mn)</t>
         </is>
       </c>
-      <c r="C7" s="28">
+      <c r="C7" s="29">
         <f>C5*C6</f>
         <v/>
       </c>
@@ -6655,10 +6361,10 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Discount factor back to today (year-2)</t>
-        </is>
-      </c>
-      <c r="C8" s="33">
+          <t>Discount factor back to the valuation date (year-2)</t>
+        </is>
+      </c>
+      <c r="C8" s="34">
         <f>DCF!C16</f>
         <v/>
       </c>
@@ -6666,34 +6372,49 @@
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>Implied enterprise value TODAY (EGP mn)</t>
-        </is>
-      </c>
-      <c r="C9" s="28">
-        <f>C7*C8</f>
+          <t>Plus present value of the interim FY26-27 free cash flows (EGP mn)</t>
+        </is>
+      </c>
+      <c r="C9" s="18">
+        <f>DCF!B17+DCF!C17</f>
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Less net bank debt, plus associates (EGP mn)</t>
-        </is>
-      </c>
-      <c r="C10" s="28">
-        <f>-Assumptions!$C$50+Assumptions!$C$51</f>
+          <t>Implied enterprise value at 31-Dec-2025 (EGP mn)</t>
+        </is>
+      </c>
+      <c r="C10" s="29">
+        <f>C7*C8+C9</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>Implied value per share (EGP)</t>
+          <t>Implied value per share, rolled to the anchor (EGP)</t>
         </is>
       </c>
       <c r="B11" s="15" t="n"/>
-      <c r="C11" s="30">
-        <f>(C9+C10)*(1-'SOTP Bridge'!$C$15)/Assumptions!$C$6</f>
+      <c r="C11" s="31">
+        <f>((C10-Assumptions!$C$43+Assumptions!$C$44)*(1-'SOTP Bridge'!$C$15)/Assumptions!$C$6)*DCF!$C$61-Assumptions!$C$49</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Bear at 5.5× (C) / bull at 8.0× (D), same construction</t>
+        </is>
+      </c>
+      <c r="C12" s="10">
+        <f>((5.5*C5*C8+C9-Assumptions!$C$43+Assumptions!$C$44)*(1-'SOTP Bridge'!$C$15)/Assumptions!$C$6)*DCF!$C$61-Assumptions!$C$49</f>
+        <v/>
+      </c>
+      <c r="D12" s="10">
+        <f>((8.0*C5*C8+C9-Assumptions!$C$43+Assumptions!$C$44)*(1-'SOTP Bridge'!$C$15)/Assumptions!$C$6)*DCF!$C$61-Assumptions!$C$49</f>
         <v/>
       </c>
     </row>
@@ -6703,8 +6424,8 @@
           <t>Trailing enterprise value / EBITDA</t>
         </is>
       </c>
-      <c r="C13" s="34">
-        <f>((Assumptions!$C$5*Assumptions!$C$6)+Assumptions!$C$50)/'Income Statement'!D7</f>
+      <c r="C13" s="35">
+        <f>((Assumptions!$C$5*Assumptions!$C$6)+Assumptions!$C$43)/'Income Statement'!D7</f>
         <v/>
       </c>
     </row>
@@ -6714,7 +6435,7 @@
           <t>Trailing price / earnings</t>
         </is>
       </c>
-      <c r="C14" s="34">
+      <c r="C14" s="35">
         <f>Assumptions!$C$5/'Income Statement'!D18</f>
         <v/>
       </c>
@@ -6725,7 +6446,7 @@
           <t>Trailing price / book</t>
         </is>
       </c>
-      <c r="C15" s="34">
+      <c r="C15" s="35">
         <f>Assumptions!$C$5/C31</f>
         <v/>
       </c>
@@ -6736,15 +6457,15 @@
           <t>Net bank debt / EBITDA</t>
         </is>
       </c>
-      <c r="C16" s="34">
-        <f>Assumptions!$C$50/'Income Statement'!D7</f>
+      <c r="C16" s="35">
+        <f>Assumptions!$C$43/'Income Statement'!D7</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>Normalised earnings lens — every component from the same year (FY2028E)</t>
+          <t>Normalised earnings lens — mid-cycle margin (FY2028E) at current (FY2026E) scale</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
@@ -6756,18 +6477,18 @@
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>Mid-cycle revenue (EGP mn)</t>
+          <t>Current-scale revenue (FY2026E, EGP mn)</t>
         </is>
       </c>
       <c r="C19" s="18">
-        <f>DCF!D5</f>
+        <f>DCF!B5</f>
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Mid-cycle EBITDA margin</t>
+          <t>Mid-cycle EBITDA margin (FY2028E)</t>
         </is>
       </c>
       <c r="C20" s="16">
@@ -6778,10 +6499,10 @@
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>Mid-cycle EBITDA (EGP mn)</t>
-        </is>
-      </c>
-      <c r="C21" s="28">
+          <t>Normalised EBITDA (EGP mn)</t>
+        </is>
+      </c>
+      <c r="C21" s="29">
         <f>C19*C20</f>
         <v/>
       </c>
@@ -6789,33 +6510,33 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Mid-cycle EBIT (EGP mn)</t>
-        </is>
-      </c>
-      <c r="C22" s="28">
-        <f>C21-C19*Assumptions!$C$34</f>
+          <t>Normalised EBIT (EGP mn)</t>
+        </is>
+      </c>
+      <c r="C22" s="29">
+        <f>C21-C19*Assumptions!$C$27</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>Net finance cost (EGP mn)</t>
+          <t>Net finance cost (FY2026E, EGP mn)</t>
         </is>
       </c>
       <c r="C23" s="18">
-        <f>'Income Statement'!G11</f>
+        <f>'Income Statement'!E11</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Share of equity-accounted investees (EGP mn)</t>
+          <t>Share of equity-accounted investees (FY2026E, EGP mn)</t>
         </is>
       </c>
       <c r="C24" s="18">
-        <f>'Income Statement'!G12</f>
+        <f>'Income Statement'!E12</f>
         <v/>
       </c>
     </row>
@@ -6825,7 +6546,7 @@
           <t>Normalised attributable earnings (EGP mn)</t>
         </is>
       </c>
-      <c r="C25" s="28">
+      <c r="C25" s="29">
         <f>(C22+C23+C24)*(1-Assumptions!$C$7)*(1-'SOTP Bridge'!$C$15)</f>
         <v/>
       </c>
@@ -6847,20 +6568,33 @@
           <t>Justified price / earnings</t>
         </is>
       </c>
-      <c r="C27" s="34">
-        <f>Assumptions!$C$62</f>
+      <c r="C27" s="35">
+        <f>Assumptions!$C$64</f>
         <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="15" t="inlineStr">
         <is>
-          <t>Implied value per share (EGP)</t>
+          <t>Implied value per share, rolled to the anchor (EGP)</t>
         </is>
       </c>
       <c r="B28" s="15" t="n"/>
-      <c r="C28" s="30">
-        <f>C26*C27</f>
+      <c r="C28" s="31">
+        <f>C26*C27*DCF!$C$61-Assumptions!$C$49</f>
+        <v/>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>bear 7.0× (E) / bull 11.5× (F):</t>
+        </is>
+      </c>
+      <c r="E28" s="10">
+        <f>C26*7*DCF!$C$61-Assumptions!$C$49</f>
+        <v/>
+      </c>
+      <c r="F28" s="10">
+        <f>C26*11.5*DCF!$C$61-Assumptions!$C$49</f>
         <v/>
       </c>
     </row>
@@ -6894,7 +6628,7 @@
         </is>
       </c>
       <c r="C32" s="11">
-        <f>Assumptions!$C$63</f>
+        <f>Assumptions!$C$65</f>
         <v/>
       </c>
     </row>
@@ -6912,7 +6646,7 @@
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>Perpetual cost of equity</t>
+          <t>Perpetual (terminal) cost of equity — a steady-state multiple takes a steady-state rate</t>
         </is>
       </c>
       <c r="C34" s="16">
@@ -6926,20 +6660,33 @@
           <t>Justified price / book</t>
         </is>
       </c>
-      <c r="C35" s="34">
-        <f>(C32-Assumptions!$C$47)/(C34-Assumptions!$C$47)</f>
+      <c r="C35" s="35">
+        <f>(C32-Assumptions!$C$40)/(C34-Assumptions!$C$40)</f>
         <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="15" t="inlineStr">
         <is>
-          <t>Implied value per share (EGP)</t>
+          <t>Implied value per share, rolled to the anchor (EGP)</t>
         </is>
       </c>
       <c r="B36" s="15" t="n"/>
-      <c r="C36" s="30">
-        <f>C31*C35</f>
+      <c r="C36" s="31">
+        <f>C31*C35*DCF!$C$61-Assumptions!$C$49</f>
+        <v/>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>bear / bull constructions (E / F):</t>
+        </is>
+      </c>
+      <c r="E36" s="10">
+        <f>((Assumptions!$C$65-0.03)/((DCF!C39+DCF!C49)/2-0.03))*C31*DCF!$C$61-Assumptions!$C$49</f>
+        <v/>
+      </c>
+      <c r="F36" s="10">
+        <f>((Assumptions!$C$65+0.02-Assumptions!$C$40)/(DCF!C49-Assumptions!$C$40))*C31*DCF!$C$61-Assumptions!$C$49</f>
         <v/>
       </c>
     </row>
@@ -6954,7 +6701,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F58"/>
+  <dimension ref="A1:F63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -7023,23 +6770,23 @@
         </is>
       </c>
       <c r="B5" s="18">
-        <f>Segments!E12</f>
+        <f>Segments!E8</f>
         <v/>
       </c>
       <c r="C5" s="18">
-        <f>Segments!F12</f>
+        <f>Segments!F8</f>
         <v/>
       </c>
       <c r="D5" s="18">
-        <f>Segments!G12</f>
+        <f>Segments!G8</f>
         <v/>
       </c>
       <c r="E5" s="18">
-        <f>Segments!H12</f>
+        <f>Segments!H8</f>
         <v/>
       </c>
       <c r="F5" s="18">
-        <f>Segments!I12</f>
+        <f>Segments!I8</f>
         <v/>
       </c>
     </row>
@@ -7050,23 +6797,23 @@
         </is>
       </c>
       <c r="B6" s="18">
-        <f>Segments!B33</f>
+        <f>Segments!B23</f>
         <v/>
       </c>
       <c r="C6" s="18">
-        <f>Segments!C33</f>
+        <f>Segments!C23</f>
         <v/>
       </c>
       <c r="D6" s="18">
-        <f>Segments!D33</f>
+        <f>Segments!D23</f>
         <v/>
       </c>
       <c r="E6" s="18">
-        <f>Segments!E33</f>
+        <f>Segments!E23</f>
         <v/>
       </c>
       <c r="F6" s="18">
-        <f>Segments!F33</f>
+        <f>Segments!F23</f>
         <v/>
       </c>
     </row>
@@ -7103,24 +6850,24 @@
           <t>Less depreciation and amortisation</t>
         </is>
       </c>
-      <c r="B8" s="28">
-        <f>-B5*Assumptions!$C$34</f>
-        <v/>
-      </c>
-      <c r="C8" s="28">
-        <f>-C5*Assumptions!$C$34</f>
-        <v/>
-      </c>
-      <c r="D8" s="28">
-        <f>-D5*Assumptions!$C$34</f>
-        <v/>
-      </c>
-      <c r="E8" s="28">
-        <f>-E5*Assumptions!$C$34</f>
-        <v/>
-      </c>
-      <c r="F8" s="28">
-        <f>-F5*Assumptions!$C$34</f>
+      <c r="B8" s="29">
+        <f>-B5*Assumptions!$C$27</f>
+        <v/>
+      </c>
+      <c r="C8" s="29">
+        <f>-C5*Assumptions!$C$27</f>
+        <v/>
+      </c>
+      <c r="D8" s="29">
+        <f>-D5*Assumptions!$C$27</f>
+        <v/>
+      </c>
+      <c r="E8" s="29">
+        <f>-E5*Assumptions!$C$27</f>
+        <v/>
+      </c>
+      <c r="F8" s="29">
+        <f>-F5*Assumptions!$C$27</f>
         <v/>
       </c>
     </row>
@@ -7130,23 +6877,23 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B9" s="29">
+      <c r="B9" s="30">
         <f>B6+B8</f>
         <v/>
       </c>
-      <c r="C9" s="29">
+      <c r="C9" s="30">
         <f>C6+C8</f>
         <v/>
       </c>
-      <c r="D9" s="29">
+      <c r="D9" s="30">
         <f>D6+D8</f>
         <v/>
       </c>
-      <c r="E9" s="29">
+      <c r="E9" s="30">
         <f>E6+E8</f>
         <v/>
       </c>
-      <c r="F9" s="29">
+      <c r="F9" s="30">
         <f>F6+F8</f>
         <v/>
       </c>
@@ -7154,26 +6901,26 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>NOPAT — EBIT x (1 - 25%)</t>
-        </is>
-      </c>
-      <c r="B10" s="28">
+          <t>NOPAT — EBIT x (1 - 24%)</t>
+        </is>
+      </c>
+      <c r="B10" s="29">
         <f>B9*(1-Assumptions!$C$7)</f>
         <v/>
       </c>
-      <c r="C10" s="28">
+      <c r="C10" s="29">
         <f>C9*(1-Assumptions!$C$7)</f>
         <v/>
       </c>
-      <c r="D10" s="28">
+      <c r="D10" s="29">
         <f>D9*(1-Assumptions!$C$7)</f>
         <v/>
       </c>
-      <c r="E10" s="28">
+      <c r="E10" s="29">
         <f>E9*(1-Assumptions!$C$7)</f>
         <v/>
       </c>
-      <c r="F10" s="28">
+      <c r="F10" s="29">
         <f>F9*(1-Assumptions!$C$7)</f>
         <v/>
       </c>
@@ -7184,23 +6931,23 @@
           <t>Add back depreciation and amortisation</t>
         </is>
       </c>
-      <c r="B11" s="28">
+      <c r="B11" s="29">
         <f>-B8</f>
         <v/>
       </c>
-      <c r="C11" s="28">
+      <c r="C11" s="29">
         <f>-C8</f>
         <v/>
       </c>
-      <c r="D11" s="28">
+      <c r="D11" s="29">
         <f>-D8</f>
         <v/>
       </c>
-      <c r="E11" s="28">
+      <c r="E11" s="29">
         <f>-E8</f>
         <v/>
       </c>
-      <c r="F11" s="28">
+      <c r="F11" s="29">
         <f>-F8</f>
         <v/>
       </c>
@@ -7211,24 +6958,24 @@
           <t>Less capital expenditure</t>
         </is>
       </c>
-      <c r="B12" s="28">
-        <f>-B5*Assumptions!$B$33</f>
-        <v/>
-      </c>
-      <c r="C12" s="28">
-        <f>-C5*Assumptions!$C$33</f>
-        <v/>
-      </c>
-      <c r="D12" s="28">
-        <f>-D5*Assumptions!$D$33</f>
-        <v/>
-      </c>
-      <c r="E12" s="28">
-        <f>-E5*Assumptions!$E$33</f>
-        <v/>
-      </c>
-      <c r="F12" s="28">
-        <f>-F5*Assumptions!$F$33</f>
+      <c r="B12" s="29">
+        <f>-B5*Assumptions!$B$26</f>
+        <v/>
+      </c>
+      <c r="C12" s="29">
+        <f>-C5*Assumptions!$C$26</f>
+        <v/>
+      </c>
+      <c r="D12" s="29">
+        <f>-D5*Assumptions!$D$26</f>
+        <v/>
+      </c>
+      <c r="E12" s="29">
+        <f>-E5*Assumptions!$E$26</f>
+        <v/>
+      </c>
+      <c r="F12" s="29">
+        <f>-F5*Assumptions!$F$26</f>
         <v/>
       </c>
     </row>
@@ -7238,24 +6985,24 @@
           <t>Less change in working capital</t>
         </is>
       </c>
-      <c r="B13" s="28">
-        <f>-(B5-'Income Statement'!D5)*Assumptions!$C$32</f>
-        <v/>
-      </c>
-      <c r="C13" s="28">
-        <f>-(C5-B5)*Assumptions!$C$32</f>
-        <v/>
-      </c>
-      <c r="D13" s="28">
-        <f>-(D5-C5)*Assumptions!$C$32</f>
-        <v/>
-      </c>
-      <c r="E13" s="28">
-        <f>-(E5-D5)*Assumptions!$C$32</f>
-        <v/>
-      </c>
-      <c r="F13" s="28">
-        <f>-(F5-E5)*Assumptions!$C$32</f>
+      <c r="B13" s="29">
+        <f>-(B5*Assumptions!$C$25-'Balance Sheet'!D16)</f>
+        <v/>
+      </c>
+      <c r="C13" s="29">
+        <f>-(C5-B5)*Assumptions!$C$25</f>
+        <v/>
+      </c>
+      <c r="D13" s="29">
+        <f>-(D5-C5)*Assumptions!$C$25</f>
+        <v/>
+      </c>
+      <c r="E13" s="29">
+        <f>-(E5-D5)*Assumptions!$C$25</f>
+        <v/>
+      </c>
+      <c r="F13" s="29">
+        <f>-(F5-E5)*Assumptions!$C$25</f>
         <v/>
       </c>
     </row>
@@ -7265,23 +7012,23 @@
           <t>Free cash flow to the firm</t>
         </is>
       </c>
-      <c r="B14" s="29">
+      <c r="B14" s="30">
         <f>B10+B11+B12+B13</f>
         <v/>
       </c>
-      <c r="C14" s="29">
+      <c r="C14" s="30">
         <f>C10+C11+C12+C13</f>
         <v/>
       </c>
-      <c r="D14" s="29">
+      <c r="D14" s="30">
         <f>D10+D11+D12+D13</f>
         <v/>
       </c>
-      <c r="E14" s="29">
+      <c r="E14" s="30">
         <f>E10+E11+E12+E13</f>
         <v/>
       </c>
-      <c r="F14" s="29">
+      <c r="F14" s="30">
         <f>F10+F11+F12+F13</f>
         <v/>
       </c>
@@ -7292,23 +7039,23 @@
           <t>Forward cost of capital</t>
         </is>
       </c>
-      <c r="B15" s="35">
+      <c r="B15" s="36">
         <f>$C$46-($C$46-$C$53)*B57</f>
         <v/>
       </c>
-      <c r="C15" s="35">
+      <c r="C15" s="36">
         <f>$C$46-($C$46-$C$53)*C57</f>
         <v/>
       </c>
-      <c r="D15" s="35">
+      <c r="D15" s="36">
         <f>$C$46-($C$46-$C$53)*D57</f>
         <v/>
       </c>
-      <c r="E15" s="35">
+      <c r="E15" s="36">
         <f>$C$46-($C$46-$C$53)*E57</f>
         <v/>
       </c>
-      <c r="F15" s="35">
+      <c r="F15" s="36">
         <f>$C$46-($C$46-$C$53)*F57</f>
         <v/>
       </c>
@@ -7319,23 +7066,23 @@
           <t>Discount factor</t>
         </is>
       </c>
-      <c r="B16" s="36">
+      <c r="B16" s="37">
         <f>1/(1+B15)</f>
         <v/>
       </c>
-      <c r="C16" s="36">
+      <c r="C16" s="37">
         <f>B16/(1+C15)</f>
         <v/>
       </c>
-      <c r="D16" s="36">
+      <c r="D16" s="37">
         <f>C16/(1+D15)</f>
         <v/>
       </c>
-      <c r="E16" s="36">
+      <c r="E16" s="37">
         <f>D16/(1+E15)</f>
         <v/>
       </c>
-      <c r="F16" s="36">
+      <c r="F16" s="37">
         <f>E16/(1+F15)</f>
         <v/>
       </c>
@@ -7346,23 +7093,23 @@
           <t>Present value of FCFF</t>
         </is>
       </c>
-      <c r="B17" s="29">
+      <c r="B17" s="30">
         <f>B14*B16</f>
         <v/>
       </c>
-      <c r="C17" s="29">
+      <c r="C17" s="30">
         <f>C14*C16</f>
         <v/>
       </c>
-      <c r="D17" s="29">
+      <c r="D17" s="30">
         <f>D14*D16</f>
         <v/>
       </c>
-      <c r="E17" s="29">
+      <c r="E17" s="30">
         <f>E14*E16</f>
         <v/>
       </c>
-      <c r="F17" s="29">
+      <c r="F17" s="30">
         <f>F14*F16</f>
         <v/>
       </c>
@@ -7370,7 +7117,7 @@
     <row r="19">
       <c r="A19" s="20" t="inlineStr">
         <is>
-          <t>TERMINAL VALUE AND BRIDGE</t>
+          <t>TERMINAL VALUE, BRIDGE AND THE ANCHOR ROLL</t>
         </is>
       </c>
     </row>
@@ -7380,7 +7127,7 @@
           <t>Terminal-year NOPAT grown one year (EGP mn)</t>
         </is>
       </c>
-      <c r="C20" s="28">
+      <c r="C20" s="29">
         <f>F10*(1+C23)</f>
         <v/>
       </c>
@@ -7414,7 +7161,7 @@
         </is>
       </c>
       <c r="C23" s="16">
-        <f>Assumptions!$C$47</f>
+        <f>Assumptions!$C$40</f>
         <v/>
       </c>
     </row>
@@ -7432,10 +7179,10 @@
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>Terminal value (EGP mn)</t>
-        </is>
-      </c>
-      <c r="C25" s="28">
+          <t>Terminal value — terminal-year FCFF C20×(1−C22), capitalised (EGP mn)</t>
+        </is>
+      </c>
+      <c r="C25" s="29">
         <f>C20*(1-C22)/(C24-C23)</f>
         <v/>
       </c>
@@ -7446,7 +7193,7 @@
           <t>Present value of the five forecast years (EGP mn)</t>
         </is>
       </c>
-      <c r="C26" s="28">
+      <c r="C26" s="29">
         <f>SUM(B17:F17)</f>
         <v/>
       </c>
@@ -7457,7 +7204,7 @@
           <t>Present value of the terminal value (EGP mn)</t>
         </is>
       </c>
-      <c r="C27" s="28">
+      <c r="C27" s="29">
         <f>C25*F16</f>
         <v/>
       </c>
@@ -7479,7 +7226,7 @@
           <t>Enterprise value (EGP mn)</t>
         </is>
       </c>
-      <c r="C29" s="28">
+      <c r="C29" s="29">
         <f>C26+C27</f>
         <v/>
       </c>
@@ -7498,11 +7245,11 @@
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>Fair value per share (EGP)</t>
+          <t>Fair value per share at 31-Dec-2025 (EGP)</t>
         </is>
       </c>
       <c r="B31" s="15" t="n"/>
-      <c r="C31" s="30">
+      <c r="C31" s="31">
         <f>C30/Assumptions!$C$6</f>
         <v/>
       </c>
@@ -7521,8 +7268,8 @@
           <t>Risk-free rate, 10-year local currency</t>
         </is>
       </c>
-      <c r="C34" s="37">
-        <f>Assumptions!$C$37</f>
+      <c r="C34" s="22">
+        <f>Assumptions!$C$30</f>
         <v/>
       </c>
     </row>
@@ -7532,8 +7279,8 @@
           <t>Less sovereign default spread (removed to avoid double-counting)</t>
         </is>
       </c>
-      <c r="C35" s="37">
-        <f>Assumptions!$C$38</f>
+      <c r="C35" s="22">
+        <f>Assumptions!$C$31</f>
         <v/>
       </c>
     </row>
@@ -7543,7 +7290,7 @@
           <t>Risk-free rate net of the sovereign spread</t>
         </is>
       </c>
-      <c r="C36" s="35">
+      <c r="C36" s="36">
         <f>C34-C35</f>
         <v/>
       </c>
@@ -7555,7 +7302,7 @@
         </is>
       </c>
       <c r="C37" s="38">
-        <f>Assumptions!$C$40</f>
+        <f>Assumptions!$C$33</f>
         <v/>
       </c>
     </row>
@@ -7565,8 +7312,8 @@
           <t>Equity risk premium</t>
         </is>
       </c>
-      <c r="C38" s="37">
-        <f>Assumptions!$C$39</f>
+      <c r="C38" s="22">
+        <f>Assumptions!$C$32</f>
         <v/>
       </c>
     </row>
@@ -7576,7 +7323,7 @@
           <t>Cost of equity, explicit window</t>
         </is>
       </c>
-      <c r="C39" s="35">
+      <c r="C39" s="36">
         <f>C36+C37*C38</f>
         <v/>
       </c>
@@ -7587,8 +7334,8 @@
           <t>Cost of debt, blended</t>
         </is>
       </c>
-      <c r="C40" s="37">
-        <f>Assumptions!$C$41</f>
+      <c r="C40" s="22">
+        <f>Assumptions!$C$34</f>
         <v/>
       </c>
     </row>
@@ -7598,7 +7345,7 @@
           <t>Cost of debt after tax</t>
         </is>
       </c>
-      <c r="C41" s="35">
+      <c r="C41" s="36">
         <f>C40*(1-Assumptions!$C$7)</f>
         <v/>
       </c>
@@ -7621,7 +7368,7 @@
         </is>
       </c>
       <c r="C43" s="18">
-        <f>Assumptions!$C$50</f>
+        <f>Assumptions!$C$43</f>
         <v/>
       </c>
     </row>
@@ -7631,7 +7378,7 @@
           <t>Debt weight (net debt / (net debt + market capitalisation))</t>
         </is>
       </c>
-      <c r="C44" s="35">
+      <c r="C44" s="36">
         <f>C43/(C43+C42)</f>
         <v/>
       </c>
@@ -7642,7 +7389,7 @@
           <t>Equity weight</t>
         </is>
       </c>
-      <c r="C45" s="35">
+      <c r="C45" s="36">
         <f>1-C44</f>
         <v/>
       </c>
@@ -7666,8 +7413,8 @@
           <t>Terminal risk-free rate</t>
         </is>
       </c>
-      <c r="C47" s="37">
-        <f>Assumptions!$C$43</f>
+      <c r="C47" s="22">
+        <f>Assumptions!$C$36</f>
         <v/>
       </c>
     </row>
@@ -7677,8 +7424,8 @@
           <t>Terminal equity risk premium</t>
         </is>
       </c>
-      <c r="C48" s="37">
-        <f>Assumptions!$C$44</f>
+      <c r="C48" s="22">
+        <f>Assumptions!$C$37</f>
         <v/>
       </c>
     </row>
@@ -7688,7 +7435,7 @@
           <t>Terminal cost of equity</t>
         </is>
       </c>
-      <c r="C49" s="35">
+      <c r="C49" s="36">
         <f>C47+C37*C48</f>
         <v/>
       </c>
@@ -7699,8 +7446,8 @@
           <t>Terminal cost of debt</t>
         </is>
       </c>
-      <c r="C50" s="37">
-        <f>Assumptions!$C$45</f>
+      <c r="C50" s="22">
+        <f>Assumptions!$C$38</f>
         <v/>
       </c>
     </row>
@@ -7710,7 +7457,7 @@
           <t>Terminal cost of debt after tax</t>
         </is>
       </c>
-      <c r="C51" s="35">
+      <c r="C51" s="36">
         <f>C50*(1-Assumptions!$C$7)</f>
         <v/>
       </c>
@@ -7721,8 +7468,8 @@
           <t>Terminal debt weight</t>
         </is>
       </c>
-      <c r="C52" s="37">
-        <f>Assumptions!$C$46</f>
+      <c r="C52" s="22">
+        <f>Assumptions!$C$39</f>
         <v/>
       </c>
     </row>
@@ -7777,24 +7524,24 @@
           <t>Cost of debt path</t>
         </is>
       </c>
-      <c r="B56" s="37">
-        <f>Assumptions!$B$42</f>
-        <v/>
-      </c>
-      <c r="C56" s="37">
-        <f>Assumptions!$C$42</f>
-        <v/>
-      </c>
-      <c r="D56" s="37">
-        <f>Assumptions!$D$42</f>
-        <v/>
-      </c>
-      <c r="E56" s="37">
-        <f>Assumptions!$E$42</f>
-        <v/>
-      </c>
-      <c r="F56" s="37">
-        <f>Assumptions!$F$42</f>
+      <c r="B56" s="22">
+        <f>Assumptions!$B$35</f>
+        <v/>
+      </c>
+      <c r="C56" s="22">
+        <f>Assumptions!$C$35</f>
+        <v/>
+      </c>
+      <c r="D56" s="22">
+        <f>Assumptions!$D$35</f>
+        <v/>
+      </c>
+      <c r="E56" s="22">
+        <f>Assumptions!$E$35</f>
+        <v/>
+      </c>
+      <c r="F56" s="22">
+        <f>Assumptions!$F$35</f>
         <v/>
       </c>
     </row>
@@ -7804,23 +7551,23 @@
           <t>Glide fraction — cumulative progress of the easing</t>
         </is>
       </c>
-      <c r="B57" s="35">
+      <c r="B57" s="36">
         <f>($B$56-B56)/($B$56-$F$56)</f>
         <v/>
       </c>
-      <c r="C57" s="35">
+      <c r="C57" s="36">
         <f>($B$56-C56)/($B$56-$F$56)</f>
         <v/>
       </c>
-      <c r="D57" s="35">
+      <c r="D57" s="36">
         <f>($B$56-D56)/($B$56-$F$56)</f>
         <v/>
       </c>
-      <c r="E57" s="35">
+      <c r="E57" s="36">
         <f>($B$56-E56)/($B$56-$F$56)</f>
         <v/>
       </c>
-      <c r="F57" s="35">
+      <c r="F57" s="36">
         <f>($B$56-F56)/($B$56-$F$56)</f>
         <v/>
       </c>
@@ -7829,6 +7576,44 @@
       <c r="A58" s="4" t="inlineStr">
         <is>
           <t>Note: row 15 above is the explicit-window cost of capital walked down to the terminal rate by the glide fraction on row 57, so the shape of the easing is inherited from the cost-of-debt path rather than being a second free parameter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="20" t="inlineStr">
+        <is>
+          <t>THE ANCHOR ROLL — one date, one price of time</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>Anchor accretion factor — (1 + cost of equity)^(days to anchor / 365)</t>
+        </is>
+      </c>
+      <c r="C61" s="37">
+        <f>(1+C39)^(Assumptions!$C$53/365)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="15" t="inlineStr">
+        <is>
+          <t>Fair value per share at the 5-Aug-2026 anchor (EGP)</t>
+        </is>
+      </c>
+      <c r="B62" s="15" t="n"/>
+      <c r="C62" s="31">
+        <f>C31*C61-Assumptions!$C$49</f>
+        <v/>
+      </c>
+      <c r="D62" s="15" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>The bridge on row 31 is dated 31-Dec-2025 (the audited balance-sheet date it subtracts net debt at). Row 62 rolls it to the anchor at the cost of equity, net of the EGP 1.85 FY2025 dividend paid in the window. Every lens on every sheet is rolled the same way.</t>
         </is>
       </c>
     </row>
@@ -7932,32 +7717,32 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B5" s="29" t="n">
-        <v>152186.2</v>
-      </c>
-      <c r="C5" s="29" t="n">
-        <v>231981.8</v>
-      </c>
-      <c r="D5" s="29" t="n">
-        <v>281049</v>
-      </c>
-      <c r="E5" s="29">
+      <c r="B5" s="30" t="n">
+        <v>152186.247545</v>
+      </c>
+      <c r="C5" s="30" t="n">
+        <v>231981.835577</v>
+      </c>
+      <c r="D5" s="30" t="n">
+        <v>281049.081719</v>
+      </c>
+      <c r="E5" s="30">
         <f>DCF!B5</f>
         <v/>
       </c>
-      <c r="F5" s="29">
+      <c r="F5" s="30">
         <f>DCF!C5</f>
         <v/>
       </c>
-      <c r="G5" s="29">
+      <c r="G5" s="30">
         <f>DCF!D5</f>
         <v/>
       </c>
-      <c r="H5" s="29">
+      <c r="H5" s="30">
         <f>DCF!E5</f>
         <v/>
       </c>
-      <c r="I5" s="29">
+      <c r="I5" s="30">
         <f>DCF!F5</f>
         <v/>
       </c>
@@ -7968,33 +7753,33 @@
           <t>Gross profit</t>
         </is>
       </c>
-      <c r="B6" s="22" t="n">
-        <v>29077.3</v>
-      </c>
-      <c r="C6" s="22" t="n">
-        <v>43898.5</v>
-      </c>
-      <c r="D6" s="22" t="n">
-        <v>40720</v>
+      <c r="B6" s="23" t="n">
+        <v>29077.288803</v>
+      </c>
+      <c r="C6" s="23" t="n">
+        <v>43898.520903</v>
+      </c>
+      <c r="D6" s="23" t="n">
+        <v>40762.108187</v>
       </c>
       <c r="E6" s="18">
-        <f>Segments!B22</f>
+        <f>Segments!B14</f>
         <v/>
       </c>
       <c r="F6" s="18">
-        <f>Segments!C22</f>
+        <f>Segments!C14</f>
         <v/>
       </c>
       <c r="G6" s="18">
-        <f>Segments!D22</f>
+        <f>Segments!D14</f>
         <v/>
       </c>
       <c r="H6" s="18">
-        <f>Segments!E22</f>
+        <f>Segments!E14</f>
         <v/>
       </c>
       <c r="I6" s="18">
-        <f>Segments!F22</f>
+        <f>Segments!F14</f>
         <v/>
       </c>
     </row>
@@ -8004,32 +7789,32 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B7" s="29" t="n">
-        <v>20035.1</v>
-      </c>
-      <c r="C7" s="29" t="n">
-        <v>31601.6</v>
-      </c>
-      <c r="D7" s="29" t="n">
-        <v>30622.08783333333</v>
-      </c>
-      <c r="E7" s="29">
+      <c r="B7" s="30" t="n">
+        <v>20035.105205</v>
+      </c>
+      <c r="C7" s="30" t="n">
+        <v>31601.46495</v>
+      </c>
+      <c r="D7" s="30" t="n">
+        <v>28363.203246</v>
+      </c>
+      <c r="E7" s="30">
         <f>DCF!B6</f>
         <v/>
       </c>
-      <c r="F7" s="29">
+      <c r="F7" s="30">
         <f>DCF!C6</f>
         <v/>
       </c>
-      <c r="G7" s="29">
+      <c r="G7" s="30">
         <f>DCF!D6</f>
         <v/>
       </c>
-      <c r="H7" s="29">
+      <c r="H7" s="30">
         <f>DCF!E6</f>
         <v/>
       </c>
-      <c r="I7" s="29">
+      <c r="I7" s="30">
         <f>DCF!F6</f>
         <v/>
       </c>
@@ -8079,14 +7864,14 @@
           <t>Depreciation and amortisation</t>
         </is>
       </c>
-      <c r="B9" s="22" t="n">
-        <v>-2296</v>
-      </c>
-      <c r="C9" s="22" t="n">
-        <v>-2259.9</v>
-      </c>
-      <c r="D9" s="22" t="n">
-        <v>-2951.0145</v>
+      <c r="B9" s="23" t="n">
+        <v>-2295.986956</v>
+      </c>
+      <c r="C9" s="23" t="n">
+        <v>-2259.745806</v>
+      </c>
+      <c r="D9" s="23" t="n">
+        <v>-3008.977627</v>
       </c>
       <c r="E9" s="18">
         <f>DCF!B8</f>
@@ -8115,35 +7900,35 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B10" s="29">
+      <c r="B10" s="30">
         <f>B7+B9</f>
         <v/>
       </c>
-      <c r="C10" s="29">
+      <c r="C10" s="30">
         <f>C7+C9</f>
         <v/>
       </c>
-      <c r="D10" s="29">
+      <c r="D10" s="30">
         <f>D7+D9</f>
         <v/>
       </c>
-      <c r="E10" s="29">
+      <c r="E10" s="30">
         <f>E7+E9</f>
         <v/>
       </c>
-      <c r="F10" s="29">
+      <c r="F10" s="30">
         <f>F7+F9</f>
         <v/>
       </c>
-      <c r="G10" s="29">
+      <c r="G10" s="30">
         <f>G7+G9</f>
         <v/>
       </c>
-      <c r="H10" s="29">
+      <c r="H10" s="30">
         <f>H7+H9</f>
         <v/>
       </c>
-      <c r="I10" s="29">
+      <c r="I10" s="30">
         <f>I7+I9</f>
         <v/>
       </c>
@@ -8154,33 +7939,33 @@
           <t>Net finance costs</t>
         </is>
       </c>
-      <c r="B11" s="22" t="n">
-        <v>-2124.4</v>
-      </c>
-      <c r="C11" s="22" t="n">
-        <v>-3515.4</v>
-      </c>
-      <c r="D11" s="22" t="n">
-        <v>-3400</v>
-      </c>
-      <c r="E11" s="28">
-        <f>-(Assumptions!$B$42*'Balance Sheet'!$D$11-Assumptions!$C$58*MAX('Balance Sheet'!$D$11-'Balance Sheet'!D17,0))</f>
-        <v/>
-      </c>
-      <c r="F11" s="28">
-        <f>-(Assumptions!$C$42*'Balance Sheet'!$D$11-Assumptions!$C$58*MAX('Balance Sheet'!$D$11-'Balance Sheet'!E17,0))</f>
-        <v/>
-      </c>
-      <c r="G11" s="28">
-        <f>-(Assumptions!$D$42*'Balance Sheet'!$D$11-Assumptions!$C$58*MAX('Balance Sheet'!$D$11-'Balance Sheet'!F17,0))</f>
-        <v/>
-      </c>
-      <c r="H11" s="28">
-        <f>-(Assumptions!$E$42*'Balance Sheet'!$D$11-Assumptions!$C$58*MAX('Balance Sheet'!$D$11-'Balance Sheet'!G17,0))</f>
-        <v/>
-      </c>
-      <c r="I11" s="28">
-        <f>-(Assumptions!$F$42*'Balance Sheet'!$D$11-Assumptions!$C$58*MAX('Balance Sheet'!$D$11-'Balance Sheet'!H17,0))</f>
+      <c r="B11" s="23" t="n">
+        <v>-2124.362277</v>
+      </c>
+      <c r="C11" s="23" t="n">
+        <v>-3515.365946</v>
+      </c>
+      <c r="D11" s="23" t="n">
+        <v>-2145.438755</v>
+      </c>
+      <c r="E11" s="29">
+        <f>-(Assumptions!$B$35*'Balance Sheet'!$D$11-Assumptions!$C$52*MAX('Balance Sheet'!$D$11-'Balance Sheet'!D17,0))</f>
+        <v/>
+      </c>
+      <c r="F11" s="29">
+        <f>-(Assumptions!$C$35*'Balance Sheet'!$D$11-Assumptions!$C$52*MAX('Balance Sheet'!$D$11-'Balance Sheet'!E17,0))</f>
+        <v/>
+      </c>
+      <c r="G11" s="29">
+        <f>-(Assumptions!$D$35*'Balance Sheet'!$D$11-Assumptions!$C$52*MAX('Balance Sheet'!$D$11-'Balance Sheet'!F17,0))</f>
+        <v/>
+      </c>
+      <c r="H11" s="29">
+        <f>-(Assumptions!$E$35*'Balance Sheet'!$D$11-Assumptions!$C$52*MAX('Balance Sheet'!$D$11-'Balance Sheet'!G17,0))</f>
+        <v/>
+      </c>
+      <c r="I11" s="29">
+        <f>-(Assumptions!$F$35*'Balance Sheet'!$D$11-Assumptions!$C$52*MAX('Balance Sheet'!$D$11-'Balance Sheet'!H17,0))</f>
         <v/>
       </c>
     </row>
@@ -8190,33 +7975,33 @@
           <t>Share of equity-accounted investees</t>
         </is>
       </c>
-      <c r="B12" s="22" t="n">
-        <v>603.6</v>
-      </c>
-      <c r="C12" s="22" t="n">
-        <v>1132.4</v>
-      </c>
-      <c r="D12" s="22" t="n">
-        <v>1302.26</v>
-      </c>
-      <c r="E12" s="28">
-        <f>D12*(1+Assumptions!$C$57)</f>
-        <v/>
-      </c>
-      <c r="F12" s="28">
-        <f>E12*(1+Assumptions!$C$57)</f>
-        <v/>
-      </c>
-      <c r="G12" s="28">
-        <f>F12*(1+Assumptions!$C$57)</f>
-        <v/>
-      </c>
-      <c r="H12" s="28">
-        <f>G12*(1+Assumptions!$C$57)</f>
-        <v/>
-      </c>
-      <c r="I12" s="28">
-        <f>H12*(1+Assumptions!$C$57)</f>
+      <c r="B12" s="23" t="n">
+        <v>603.624972</v>
+      </c>
+      <c r="C12" s="23" t="n">
+        <v>1132.366257</v>
+      </c>
+      <c r="D12" s="23" t="n">
+        <v>1568.902975</v>
+      </c>
+      <c r="E12" s="29">
+        <f>D12*(1+Assumptions!$C$51)</f>
+        <v/>
+      </c>
+      <c r="F12" s="29">
+        <f>E12*(1+Assumptions!$C$51)</f>
+        <v/>
+      </c>
+      <c r="G12" s="29">
+        <f>F12*(1+Assumptions!$C$51)</f>
+        <v/>
+      </c>
+      <c r="H12" s="29">
+        <f>G12*(1+Assumptions!$C$51)</f>
+        <v/>
+      </c>
+      <c r="I12" s="29">
+        <f>H12*(1+Assumptions!$C$51)</f>
         <v/>
       </c>
     </row>
@@ -8226,35 +8011,35 @@
           <t>Profit before tax</t>
         </is>
       </c>
-      <c r="B13" s="28">
+      <c r="B13" s="29">
         <f>B10+B11+B12</f>
         <v/>
       </c>
-      <c r="C13" s="28">
+      <c r="C13" s="29">
         <f>C10+C11+C12</f>
         <v/>
       </c>
-      <c r="D13" s="28">
+      <c r="D13" s="29">
         <f>D10+D11+D12</f>
         <v/>
       </c>
-      <c r="E13" s="28">
+      <c r="E13" s="29">
         <f>E10+E11+E12</f>
         <v/>
       </c>
-      <c r="F13" s="28">
+      <c r="F13" s="29">
         <f>F10+F11+F12</f>
         <v/>
       </c>
-      <c r="G13" s="28">
+      <c r="G13" s="29">
         <f>G10+G11+G12</f>
         <v/>
       </c>
-      <c r="H13" s="28">
+      <c r="H13" s="29">
         <f>H10+H11+H12</f>
         <v/>
       </c>
-      <c r="I13" s="28">
+      <c r="I13" s="29">
         <f>I10+I11+I12</f>
         <v/>
       </c>
@@ -8265,32 +8050,32 @@
           <t>Income tax</t>
         </is>
       </c>
-      <c r="B14" s="22" t="n">
-        <v>-5080.4</v>
-      </c>
-      <c r="C14" s="22" t="n">
-        <v>-8121.5</v>
-      </c>
-      <c r="D14" s="22" t="n">
-        <v>-6393.333333333332</v>
-      </c>
-      <c r="E14" s="28">
+      <c r="B14" s="23" t="n">
+        <v>-5080.406688</v>
+      </c>
+      <c r="C14" s="23" t="n">
+        <v>-8121.510082</v>
+      </c>
+      <c r="D14" s="23" t="n">
+        <v>-5591.139782</v>
+      </c>
+      <c r="E14" s="29">
         <f>-E13*Assumptions!$C$7</f>
         <v/>
       </c>
-      <c r="F14" s="28">
+      <c r="F14" s="29">
         <f>-F13*Assumptions!$C$7</f>
         <v/>
       </c>
-      <c r="G14" s="28">
+      <c r="G14" s="29">
         <f>-G13*Assumptions!$C$7</f>
         <v/>
       </c>
-      <c r="H14" s="28">
+      <c r="H14" s="29">
         <f>-H13*Assumptions!$C$7</f>
         <v/>
       </c>
-      <c r="I14" s="28">
+      <c r="I14" s="29">
         <f>-I13*Assumptions!$C$7</f>
         <v/>
       </c>
@@ -8301,32 +8086,32 @@
           <t>Profit for the year</t>
         </is>
       </c>
-      <c r="B15" s="22" t="n">
-        <v>11138</v>
-      </c>
-      <c r="C15" s="22" t="n">
-        <v>18837.2</v>
-      </c>
-      <c r="D15" s="22" t="n">
-        <v>19180</v>
-      </c>
-      <c r="E15" s="28">
+      <c r="B15" s="23" t="n">
+        <v>11137.974256</v>
+      </c>
+      <c r="C15" s="23" t="n">
+        <v>18837.209373</v>
+      </c>
+      <c r="D15" s="23" t="n">
+        <v>19186.550057</v>
+      </c>
+      <c r="E15" s="29">
         <f>E13+E14</f>
         <v/>
       </c>
-      <c r="F15" s="28">
+      <c r="F15" s="29">
         <f>F13+F14</f>
         <v/>
       </c>
-      <c r="G15" s="28">
+      <c r="G15" s="29">
         <f>G13+G14</f>
         <v/>
       </c>
-      <c r="H15" s="28">
+      <c r="H15" s="29">
         <f>H13+H14</f>
         <v/>
       </c>
-      <c r="I15" s="28">
+      <c r="I15" s="29">
         <f>I13+I14</f>
         <v/>
       </c>
@@ -8337,32 +8122,32 @@
           <t>Non-controlling interests</t>
         </is>
       </c>
-      <c r="B16" s="22" t="n">
-        <v>-1022.299999999999</v>
-      </c>
-      <c r="C16" s="22" t="n">
-        <v>-1375.799999999999</v>
-      </c>
-      <c r="D16" s="22" t="n">
-        <v>-1850</v>
-      </c>
-      <c r="E16" s="28">
+      <c r="B16" s="23" t="n">
+        <v>-1022.272478999999</v>
+      </c>
+      <c r="C16" s="23" t="n">
+        <v>-1375.850659</v>
+      </c>
+      <c r="D16" s="23" t="n">
+        <v>-1856.305067000001</v>
+      </c>
+      <c r="E16" s="29">
         <f>-E15*'SOTP Bridge'!$C$15</f>
         <v/>
       </c>
-      <c r="F16" s="28">
+      <c r="F16" s="29">
         <f>-F15*'SOTP Bridge'!$C$15</f>
         <v/>
       </c>
-      <c r="G16" s="28">
+      <c r="G16" s="29">
         <f>-G15*'SOTP Bridge'!$C$15</f>
         <v/>
       </c>
-      <c r="H16" s="28">
+      <c r="H16" s="29">
         <f>-H15*'SOTP Bridge'!$C$15</f>
         <v/>
       </c>
-      <c r="I16" s="28">
+      <c r="I16" s="29">
         <f>-I15*'SOTP Bridge'!$C$15</f>
         <v/>
       </c>
@@ -8373,32 +8158,32 @@
           <t>Profit attributable to shareholders</t>
         </is>
       </c>
-      <c r="B17" s="29" t="n">
-        <v>10115.7</v>
-      </c>
-      <c r="C17" s="29" t="n">
-        <v>17461.4</v>
-      </c>
-      <c r="D17" s="29" t="n">
-        <v>17330</v>
-      </c>
-      <c r="E17" s="29">
+      <c r="B17" s="30" t="n">
+        <v>10115.701777</v>
+      </c>
+      <c r="C17" s="30" t="n">
+        <v>17461.358714</v>
+      </c>
+      <c r="D17" s="30" t="n">
+        <v>17330.24499</v>
+      </c>
+      <c r="E17" s="30">
         <f>E15+E16</f>
         <v/>
       </c>
-      <c r="F17" s="29">
+      <c r="F17" s="30">
         <f>F15+F16</f>
         <v/>
       </c>
-      <c r="G17" s="29">
+      <c r="G17" s="30">
         <f>G15+G16</f>
         <v/>
       </c>
-      <c r="H17" s="29">
+      <c r="H17" s="30">
         <f>H15+H16</f>
         <v/>
       </c>
-      <c r="I17" s="29">
+      <c r="I17" s="30">
         <f>I15+I16</f>
         <v/>
       </c>
@@ -8445,7 +8230,7 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>Note: FY2023 and FY2024 are audited. FY2025 revenue, profit after tax and profit after minority interests are disclosed; the intermediate lines are derived by closing the account to the reported profit. In the forecast the finance charge is computed on the gross debt book less the cash the business is accumulating, so it falls with net debt rather than being frozen at the FY2025 balance; profit is therefore struck after interest and differs from the pre-financing DCF waterfall by construction.</t>
+          <t>Note: every FY2023-25 statement line is the audited figure — no closure or derivation is used for any historical year (the EBITDA and EPS rows are labelled house derivations). In the forecast the finance charge is computed on the gross debt book less the cash the business is accumulating, so it moves with net debt rather than being frozen at the FY2025 balance; profit is therefore struck after interest and differs from the pre-financing DCF waterfall by construction.</t>
         </is>
       </c>
     </row>

--- a/engine/swdy_study/SWDY_Valuation_Model_05082026_public.xlsx
+++ b/engine/swdy_study/SWDY_Valuation_Model_05082026_public.xlsx
@@ -120,7 +120,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -130,18 +130,19 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="8" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="8" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="9" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="10" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -993,32 +994,32 @@
           <t>Property, plant and equipment</t>
         </is>
       </c>
-      <c r="B5" s="23" t="n">
+      <c r="B5" s="24" t="n">
         <v>18009.166367</v>
       </c>
-      <c r="C5" s="23" t="n">
+      <c r="C5" s="24" t="n">
         <v>27543.762675</v>
       </c>
-      <c r="D5" s="23" t="n">
+      <c r="D5" s="24" t="n">
         <v>35961.076614</v>
       </c>
-      <c r="E5" s="29">
+      <c r="E5" s="30">
         <f>D5-DCF!B12+DCF!B8</f>
         <v/>
       </c>
-      <c r="F5" s="29">
+      <c r="F5" s="30">
         <f>E5-DCF!C12+DCF!C8</f>
         <v/>
       </c>
-      <c r="G5" s="29">
+      <c r="G5" s="30">
         <f>F5-DCF!D12+DCF!D8</f>
         <v/>
       </c>
-      <c r="H5" s="29">
+      <c r="H5" s="30">
         <f>G5-DCF!E12+DCF!E8</f>
         <v/>
       </c>
-      <c r="I5" s="29">
+      <c r="I5" s="30">
         <f>H5-DCF!F12+DCF!F8</f>
         <v/>
       </c>
@@ -1029,13 +1030,13 @@
           <t>Inventories</t>
         </is>
       </c>
-      <c r="B6" s="23" t="n">
+      <c r="B6" s="24" t="n">
         <v>30881.822082</v>
       </c>
-      <c r="C6" s="23" t="n">
+      <c r="C6" s="24" t="n">
         <v>56795.884068</v>
       </c>
-      <c r="D6" s="23" t="n">
+      <c r="D6" s="24" t="n">
         <v>59860.04457</v>
       </c>
     </row>
@@ -1045,13 +1046,13 @@
           <t>Contract assets</t>
         </is>
       </c>
-      <c r="B7" s="23" t="n">
+      <c r="B7" s="24" t="n">
         <v>16179.633722</v>
       </c>
-      <c r="C7" s="23" t="n">
+      <c r="C7" s="24" t="n">
         <v>18051.96657</v>
       </c>
-      <c r="D7" s="23" t="n">
+      <c r="D7" s="24" t="n">
         <v>29894.579591</v>
       </c>
     </row>
@@ -1061,13 +1062,13 @@
           <t>Trade and other receivables</t>
         </is>
       </c>
-      <c r="B8" s="23" t="n">
+      <c r="B8" s="24" t="n">
         <v>46591.885092</v>
       </c>
-      <c r="C8" s="23" t="n">
+      <c r="C8" s="24" t="n">
         <v>86736.309423</v>
       </c>
-      <c r="D8" s="23" t="n">
+      <c r="D8" s="24" t="n">
         <v>116259.797169</v>
       </c>
     </row>
@@ -1077,37 +1078,37 @@
           <t>Cash and cash equivalents</t>
         </is>
       </c>
-      <c r="B9" s="23" t="n">
+      <c r="B9" s="24" t="n">
         <v>25552.0448</v>
       </c>
-      <c r="C9" s="23" t="n">
+      <c r="C9" s="24" t="n">
         <v>38180.002322</v>
       </c>
-      <c r="D9" s="29">
+      <c r="D9" s="30">
         <f>D11-D17</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="13" t="inlineStr">
         <is>
           <t>Total assets</t>
         </is>
       </c>
-      <c r="B10" s="30" t="n">
+      <c r="B10" s="31" t="n">
         <v>151448.654828</v>
       </c>
-      <c r="C10" s="30" t="n">
+      <c r="C10" s="31" t="n">
         <v>249527.138687</v>
       </c>
-      <c r="D10" s="30" t="n">
+      <c r="D10" s="31" t="n">
         <v>311099.090775</v>
       </c>
-      <c r="E10" s="15" t="n"/>
-      <c r="F10" s="15" t="n"/>
-      <c r="G10" s="15" t="n"/>
-      <c r="H10" s="15" t="n"/>
-      <c r="I10" s="15" t="n"/>
+      <c r="E10" s="13" t="n"/>
+      <c r="F10" s="13" t="n"/>
+      <c r="G10" s="13" t="n"/>
+      <c r="H10" s="13" t="n"/>
+      <c r="I10" s="13" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -1115,13 +1116,13 @@
           <t>Loans and borrowings</t>
         </is>
       </c>
-      <c r="B11" s="23" t="n">
+      <c r="B11" s="24" t="n">
         <v>41766.492071</v>
       </c>
-      <c r="C11" s="23" t="n">
+      <c r="C11" s="24" t="n">
         <v>59082.941807</v>
       </c>
-      <c r="D11" s="23" t="n">
+      <c r="D11" s="24" t="n">
         <v>62509.211797</v>
       </c>
     </row>
@@ -1131,13 +1132,13 @@
           <t>Trade and other payables</t>
         </is>
       </c>
-      <c r="B12" s="23" t="n">
+      <c r="B12" s="24" t="n">
         <v>31938.12206</v>
       </c>
-      <c r="C12" s="23" t="n">
+      <c r="C12" s="24" t="n">
         <v>54808.185042</v>
       </c>
-      <c r="D12" s="23" t="n">
+      <c r="D12" s="24" t="n">
         <v>68895.662044</v>
       </c>
     </row>
@@ -1147,48 +1148,48 @@
           <t>Contract liabilities</t>
         </is>
       </c>
-      <c r="B13" s="23" t="n">
+      <c r="B13" s="24" t="n">
         <v>25060.328092</v>
       </c>
-      <c r="C13" s="23" t="n">
+      <c r="C13" s="24" t="n">
         <v>53281.056753</v>
       </c>
-      <c r="D13" s="23" t="n">
+      <c r="D13" s="24" t="n">
         <v>81266.224686</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="inlineStr">
+      <c r="A14" s="13" t="inlineStr">
         <is>
           <t>Equity attributable to shareholders</t>
         </is>
       </c>
-      <c r="B14" s="30" t="n">
+      <c r="B14" s="31" t="n">
         <v>35724.466132</v>
       </c>
-      <c r="C14" s="30" t="n">
+      <c r="C14" s="31" t="n">
         <v>55274.913356</v>
       </c>
-      <c r="D14" s="30" t="n">
+      <c r="D14" s="31" t="n">
         <v>66870.86655000001</v>
       </c>
-      <c r="E14" s="30">
+      <c r="E14" s="31">
         <f>D14+'Income Statement'!E17*(1-Assumptions!$C$50)</f>
         <v/>
       </c>
-      <c r="F14" s="30">
+      <c r="F14" s="31">
         <f>E14+'Income Statement'!F17*(1-Assumptions!$C$50)</f>
         <v/>
       </c>
-      <c r="G14" s="30">
+      <c r="G14" s="31">
         <f>F14+'Income Statement'!G17*(1-Assumptions!$C$50)</f>
         <v/>
       </c>
-      <c r="H14" s="30">
+      <c r="H14" s="31">
         <f>G14+'Income Statement'!H17*(1-Assumptions!$C$50)</f>
         <v/>
       </c>
-      <c r="I14" s="30">
+      <c r="I14" s="31">
         <f>H14+'Income Statement'!I17*(1-Assumptions!$C$50)</f>
         <v/>
       </c>
@@ -1199,13 +1200,13 @@
           <t>Non-controlling interests</t>
         </is>
       </c>
-      <c r="B15" s="23" t="n">
+      <c r="B15" s="24" t="n">
         <v>2384.013396</v>
       </c>
-      <c r="C15" s="23" t="n">
+      <c r="C15" s="24" t="n">
         <v>4251.7719</v>
       </c>
-      <c r="D15" s="23" t="n">
+      <c r="D15" s="24" t="n">
         <v>5118.978381</v>
       </c>
     </row>
@@ -1215,69 +1216,69 @@
           <t>Net working capital</t>
         </is>
       </c>
-      <c r="B16" s="23" t="n">
+      <c r="B16" s="24" t="n">
         <v>36654.89074399999</v>
       </c>
-      <c r="C16" s="23" t="n">
+      <c r="C16" s="24" t="n">
         <v>53494.91826600001</v>
       </c>
-      <c r="D16" s="23" t="n">
+      <c r="D16" s="24" t="n">
         <v>55852.53459999998</v>
       </c>
-      <c r="E16" s="29">
+      <c r="E16" s="30">
         <f>'Income Statement'!E5*Assumptions!$C$25</f>
         <v/>
       </c>
-      <c r="F16" s="29">
+      <c r="F16" s="30">
         <f>'Income Statement'!F5*Assumptions!$C$25</f>
         <v/>
       </c>
-      <c r="G16" s="29">
+      <c r="G16" s="30">
         <f>'Income Statement'!G5*Assumptions!$C$25</f>
         <v/>
       </c>
-      <c r="H16" s="29">
+      <c r="H16" s="30">
         <f>'Income Statement'!H5*Assumptions!$C$25</f>
         <v/>
       </c>
-      <c r="I16" s="29">
+      <c r="I16" s="30">
         <f>'Income Statement'!I5*Assumptions!$C$25</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="13" t="inlineStr">
         <is>
           <t>Net bank debt</t>
         </is>
       </c>
-      <c r="B17" s="30" t="n">
+      <c r="B17" s="31" t="n">
         <v>16214.447271</v>
       </c>
-      <c r="C17" s="30" t="n">
+      <c r="C17" s="31" t="n">
         <v>20902.939485</v>
       </c>
-      <c r="D17" s="30">
+      <c r="D17" s="31">
         <f>Assumptions!$C$43</f>
         <v/>
       </c>
-      <c r="E17" s="30">
+      <c r="E17" s="31">
         <f>D17-DCF!B14-'Income Statement'!E11*(1-Assumptions!$C$7)+Assumptions!$C$50*'Income Statement'!E17</f>
         <v/>
       </c>
-      <c r="F17" s="30">
+      <c r="F17" s="31">
         <f>E17-DCF!C14-'Income Statement'!F11*(1-Assumptions!$C$7)+Assumptions!$C$50*'Income Statement'!F17</f>
         <v/>
       </c>
-      <c r="G17" s="30">
+      <c r="G17" s="31">
         <f>F17-DCF!D14-'Income Statement'!G11*(1-Assumptions!$C$7)+Assumptions!$C$50*'Income Statement'!G17</f>
         <v/>
       </c>
-      <c r="H17" s="30">
+      <c r="H17" s="31">
         <f>G17-DCF!E14-'Income Statement'!H11*(1-Assumptions!$C$7)+Assumptions!$C$50*'Income Statement'!H17</f>
         <v/>
       </c>
-      <c r="I17" s="30">
+      <c r="I17" s="31">
         <f>H17-DCF!F14-'Income Statement'!I11*(1-Assumptions!$C$7)+Assumptions!$C$50*'Income Statement'!I17</f>
         <v/>
       </c>
@@ -1288,35 +1289,35 @@
           <t>Net debt / EBITDA</t>
         </is>
       </c>
-      <c r="B18" s="35">
+      <c r="B18" s="36">
         <f>B17/'Income Statement'!B7</f>
         <v/>
       </c>
-      <c r="C18" s="35">
+      <c r="C18" s="36">
         <f>C17/'Income Statement'!C7</f>
         <v/>
       </c>
-      <c r="D18" s="35">
+      <c r="D18" s="36">
         <f>D17/'Income Statement'!D7</f>
         <v/>
       </c>
-      <c r="E18" s="35">
+      <c r="E18" s="36">
         <f>E17/'Income Statement'!E7</f>
         <v/>
       </c>
-      <c r="F18" s="35">
+      <c r="F18" s="36">
         <f>F17/'Income Statement'!F7</f>
         <v/>
       </c>
-      <c r="G18" s="35">
+      <c r="G18" s="36">
         <f>G17/'Income Statement'!G7</f>
         <v/>
       </c>
-      <c r="H18" s="35">
+      <c r="H18" s="36">
         <f>H17/'Income Statement'!H7</f>
         <v/>
       </c>
-      <c r="I18" s="35">
+      <c r="I18" s="36">
         <f>I17/'Income Statement'!I7</f>
         <v/>
       </c>
@@ -1327,15 +1328,15 @@
           <t>Residual: other liabilities, provisions and deferred tax not shown separately (total assets less the lines above)</t>
         </is>
       </c>
-      <c r="B19" s="29">
+      <c r="B19" s="30">
         <f>B10-(B11+B12+B13+B14+B15)</f>
         <v/>
       </c>
-      <c r="C19" s="29">
+      <c r="C19" s="30">
         <f>C10-(C11+C12+C13+C14+C15)</f>
         <v/>
       </c>
-      <c r="D19" s="29">
+      <c r="D19" s="30">
         <f>D10-(D11+D12+D13+D14+D15)</f>
         <v/>
       </c>
@@ -1442,31 +1443,31 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B5" s="18">
+      <c r="B5" s="19">
         <f>'Income Statement'!C7</f>
         <v/>
       </c>
-      <c r="C5" s="18">
+      <c r="C5" s="19">
         <f>'Income Statement'!D7</f>
         <v/>
       </c>
-      <c r="D5" s="18">
+      <c r="D5" s="19">
         <f>'Income Statement'!E7</f>
         <v/>
       </c>
-      <c r="E5" s="18">
+      <c r="E5" s="19">
         <f>'Income Statement'!F7</f>
         <v/>
       </c>
-      <c r="F5" s="18">
+      <c r="F5" s="19">
         <f>'Income Statement'!G7</f>
         <v/>
       </c>
-      <c r="G5" s="18">
+      <c r="G5" s="19">
         <f>'Income Statement'!H7</f>
         <v/>
       </c>
-      <c r="H5" s="18">
+      <c r="H5" s="19">
         <f>'Income Statement'!I7</f>
         <v/>
       </c>
@@ -1477,12 +1478,12 @@
           <t>Interest paid</t>
         </is>
       </c>
-      <c r="B6" s="29" t="inlineStr">
+      <c r="B6" s="30" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C6" s="23" t="n">
+      <c r="C6" s="24" t="n">
         <v>-5740.31242</v>
       </c>
     </row>
@@ -1492,12 +1493,12 @@
           <t>Income tax paid</t>
         </is>
       </c>
-      <c r="B7" s="29" t="inlineStr">
+      <c r="B7" s="30" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C7" s="23" t="n">
+      <c r="C7" s="24" t="n">
         <v>-8298.752112</v>
       </c>
     </row>
@@ -1507,12 +1508,12 @@
           <t>Operating cash flow after interest and tax</t>
         </is>
       </c>
-      <c r="B8" s="29" t="inlineStr">
+      <c r="B8" s="30" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C8" s="23" t="n">
+      <c r="C8" s="24" t="n">
         <v>12765.922545</v>
       </c>
     </row>
@@ -1522,33 +1523,33 @@
           <t>NOPAT</t>
         </is>
       </c>
-      <c r="B9" s="29" t="inlineStr">
+      <c r="B9" s="30" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C9" s="29" t="inlineStr">
+      <c r="C9" s="30" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D9" s="18">
+      <c r="D9" s="19">
         <f>DCF!B10</f>
         <v/>
       </c>
-      <c r="E9" s="18">
+      <c r="E9" s="19">
         <f>DCF!C10</f>
         <v/>
       </c>
-      <c r="F9" s="18">
+      <c r="F9" s="19">
         <f>DCF!D10</f>
         <v/>
       </c>
-      <c r="G9" s="18">
+      <c r="G9" s="19">
         <f>DCF!E10</f>
         <v/>
       </c>
-      <c r="H9" s="18">
+      <c r="H9" s="19">
         <f>DCF!F10</f>
         <v/>
       </c>
@@ -1559,33 +1560,33 @@
           <t>Add back depreciation and amortisation</t>
         </is>
       </c>
-      <c r="B10" s="29" t="inlineStr">
+      <c r="B10" s="30" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C10" s="29" t="inlineStr">
+      <c r="C10" s="30" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D10" s="18">
+      <c r="D10" s="19">
         <f>DCF!B11</f>
         <v/>
       </c>
-      <c r="E10" s="18">
+      <c r="E10" s="19">
         <f>DCF!C11</f>
         <v/>
       </c>
-      <c r="F10" s="18">
+      <c r="F10" s="19">
         <f>DCF!D11</f>
         <v/>
       </c>
-      <c r="G10" s="18">
+      <c r="G10" s="19">
         <f>DCF!E11</f>
         <v/>
       </c>
-      <c r="H10" s="18">
+      <c r="H10" s="19">
         <f>DCF!F11</f>
         <v/>
       </c>
@@ -1596,29 +1597,29 @@
           <t>Capital expenditure</t>
         </is>
       </c>
-      <c r="B11" s="23" t="n">
+      <c r="B11" s="24" t="n">
         <v>-8489.780912</v>
       </c>
-      <c r="C11" s="23" t="n">
+      <c r="C11" s="24" t="n">
         <v>-13112.049791</v>
       </c>
-      <c r="D11" s="18">
+      <c r="D11" s="19">
         <f>DCF!B12</f>
         <v/>
       </c>
-      <c r="E11" s="18">
+      <c r="E11" s="19">
         <f>DCF!C12</f>
         <v/>
       </c>
-      <c r="F11" s="18">
+      <c r="F11" s="19">
         <f>DCF!D12</f>
         <v/>
       </c>
-      <c r="G11" s="18">
+      <c r="G11" s="19">
         <f>DCF!E12</f>
         <v/>
       </c>
-      <c r="H11" s="18">
+      <c r="H11" s="19">
         <f>DCF!F12</f>
         <v/>
       </c>
@@ -1629,73 +1630,73 @@
           <t>Change in working capital</t>
         </is>
       </c>
-      <c r="B12" s="29" t="inlineStr">
+      <c r="B12" s="30" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C12" s="29">
+      <c r="C12" s="30">
         <f>-('Balance Sheet'!D16-'Balance Sheet'!C16)</f>
         <v/>
       </c>
-      <c r="D12" s="18">
+      <c r="D12" s="19">
         <f>DCF!B13</f>
         <v/>
       </c>
-      <c r="E12" s="18">
+      <c r="E12" s="19">
         <f>DCF!C13</f>
         <v/>
       </c>
-      <c r="F12" s="18">
+      <c r="F12" s="19">
         <f>DCF!D13</f>
         <v/>
       </c>
-      <c r="G12" s="18">
+      <c r="G12" s="19">
         <f>DCF!E13</f>
         <v/>
       </c>
-      <c r="H12" s="18">
+      <c r="H12" s="19">
         <f>DCF!F13</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="13" t="inlineStr">
         <is>
           <t>Free cash flow to the firm</t>
         </is>
       </c>
-      <c r="B13" s="30" t="inlineStr">
+      <c r="B13" s="31" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C13" s="30" t="inlineStr">
+      <c r="C13" s="31" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D13" s="30">
+      <c r="D13" s="31">
         <f>D9+D10+D11+D12</f>
         <v/>
       </c>
-      <c r="E13" s="30">
+      <c r="E13" s="31">
         <f>E9+E10+E11+E12</f>
         <v/>
       </c>
-      <c r="F13" s="30">
+      <c r="F13" s="31">
         <f>F9+F10+F11+F12</f>
         <v/>
       </c>
-      <c r="G13" s="30">
+      <c r="G13" s="31">
         <f>G9+G10+G11+G12</f>
         <v/>
       </c>
-      <c r="H13" s="30">
+      <c r="H13" s="31">
         <f>H9+H10+H11+H12</f>
         <v/>
       </c>
-      <c r="I13" s="15" t="n"/>
+      <c r="I13" s="13" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -1703,7 +1704,7 @@
           <t>Cash conversion — operating cash flow as a share of EBITDA, FY2025</t>
         </is>
       </c>
-      <c r="C15" s="11">
+      <c r="C15" s="9">
         <f>C8/C5</f>
         <v/>
       </c>
@@ -1815,35 +1816,35 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B5" s="18">
+      <c r="B5" s="19">
         <f>'Income Statement'!B5</f>
         <v/>
       </c>
-      <c r="C5" s="18">
+      <c r="C5" s="19">
         <f>'Income Statement'!C5</f>
         <v/>
       </c>
-      <c r="D5" s="18">
+      <c r="D5" s="19">
         <f>'Income Statement'!D5</f>
         <v/>
       </c>
-      <c r="E5" s="18">
+      <c r="E5" s="19">
         <f>'Income Statement'!E5</f>
         <v/>
       </c>
-      <c r="F5" s="18">
+      <c r="F5" s="19">
         <f>'Income Statement'!F5</f>
         <v/>
       </c>
-      <c r="G5" s="18">
+      <c r="G5" s="19">
         <f>'Income Statement'!G5</f>
         <v/>
       </c>
-      <c r="H5" s="18">
+      <c r="H5" s="19">
         <f>'Income Statement'!H5</f>
         <v/>
       </c>
-      <c r="I5" s="18">
+      <c r="I5" s="19">
         <f>'Income Statement'!I5</f>
         <v/>
       </c>
@@ -1854,36 +1855,36 @@
           <t>Revenue growth</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C6" s="11">
+      <c r="C6" s="9">
         <f>C5/B5-1</f>
         <v/>
       </c>
-      <c r="D6" s="11">
+      <c r="D6" s="9">
         <f>D5/C5-1</f>
         <v/>
       </c>
-      <c r="E6" s="11">
+      <c r="E6" s="9">
         <f>E5/D5-1</f>
         <v/>
       </c>
-      <c r="F6" s="11">
+      <c r="F6" s="9">
         <f>F5/E5-1</f>
         <v/>
       </c>
-      <c r="G6" s="11">
+      <c r="G6" s="9">
         <f>G5/F5-1</f>
         <v/>
       </c>
-      <c r="H6" s="11">
+      <c r="H6" s="9">
         <f>H5/G5-1</f>
         <v/>
       </c>
-      <c r="I6" s="11">
+      <c r="I6" s="9">
         <f>I5/H5-1</f>
         <v/>
       </c>
@@ -1894,35 +1895,35 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B7" s="18">
+      <c r="B7" s="19">
         <f>'Income Statement'!B7</f>
         <v/>
       </c>
-      <c r="C7" s="18">
+      <c r="C7" s="19">
         <f>'Income Statement'!C7</f>
         <v/>
       </c>
-      <c r="D7" s="18">
+      <c r="D7" s="19">
         <f>'Income Statement'!D7</f>
         <v/>
       </c>
-      <c r="E7" s="18">
+      <c r="E7" s="19">
         <f>'Income Statement'!E7</f>
         <v/>
       </c>
-      <c r="F7" s="18">
+      <c r="F7" s="19">
         <f>'Income Statement'!F7</f>
         <v/>
       </c>
-      <c r="G7" s="18">
+      <c r="G7" s="19">
         <f>'Income Statement'!G7</f>
         <v/>
       </c>
-      <c r="H7" s="18">
+      <c r="H7" s="19">
         <f>'Income Statement'!H7</f>
         <v/>
       </c>
-      <c r="I7" s="18">
+      <c r="I7" s="19">
         <f>'Income Statement'!I7</f>
         <v/>
       </c>
@@ -1933,35 +1934,35 @@
           <t>EBITDA margin</t>
         </is>
       </c>
-      <c r="B8" s="11">
+      <c r="B8" s="9">
         <f>B7/B5</f>
         <v/>
       </c>
-      <c r="C8" s="11">
+      <c r="C8" s="9">
         <f>C7/C5</f>
         <v/>
       </c>
-      <c r="D8" s="11">
+      <c r="D8" s="9">
         <f>D7/D5</f>
         <v/>
       </c>
-      <c r="E8" s="11">
+      <c r="E8" s="9">
         <f>E7/E5</f>
         <v/>
       </c>
-      <c r="F8" s="11">
+      <c r="F8" s="9">
         <f>F7/F5</f>
         <v/>
       </c>
-      <c r="G8" s="11">
+      <c r="G8" s="9">
         <f>G7/G5</f>
         <v/>
       </c>
-      <c r="H8" s="11">
+      <c r="H8" s="9">
         <f>H7/H5</f>
         <v/>
       </c>
-      <c r="I8" s="11">
+      <c r="I8" s="9">
         <f>I7/I5</f>
         <v/>
       </c>
@@ -1972,35 +1973,35 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B9" s="18">
+      <c r="B9" s="19">
         <f>'Income Statement'!B10</f>
         <v/>
       </c>
-      <c r="C9" s="18">
+      <c r="C9" s="19">
         <f>'Income Statement'!C10</f>
         <v/>
       </c>
-      <c r="D9" s="18">
+      <c r="D9" s="19">
         <f>'Income Statement'!D10</f>
         <v/>
       </c>
-      <c r="E9" s="18">
+      <c r="E9" s="19">
         <f>'Income Statement'!E10</f>
         <v/>
       </c>
-      <c r="F9" s="18">
+      <c r="F9" s="19">
         <f>'Income Statement'!F10</f>
         <v/>
       </c>
-      <c r="G9" s="18">
+      <c r="G9" s="19">
         <f>'Income Statement'!G10</f>
         <v/>
       </c>
-      <c r="H9" s="18">
+      <c r="H9" s="19">
         <f>'Income Statement'!H10</f>
         <v/>
       </c>
-      <c r="I9" s="18">
+      <c r="I9" s="19">
         <f>'Income Statement'!I10</f>
         <v/>
       </c>
@@ -2011,35 +2012,35 @@
           <t>Attributable profit</t>
         </is>
       </c>
-      <c r="B10" s="18">
+      <c r="B10" s="19">
         <f>'Income Statement'!B17</f>
         <v/>
       </c>
-      <c r="C10" s="18">
+      <c r="C10" s="19">
         <f>'Income Statement'!C17</f>
         <v/>
       </c>
-      <c r="D10" s="18">
+      <c r="D10" s="19">
         <f>'Income Statement'!D17</f>
         <v/>
       </c>
-      <c r="E10" s="18">
+      <c r="E10" s="19">
         <f>'Income Statement'!E17</f>
         <v/>
       </c>
-      <c r="F10" s="18">
+      <c r="F10" s="19">
         <f>'Income Statement'!F17</f>
         <v/>
       </c>
-      <c r="G10" s="18">
+      <c r="G10" s="19">
         <f>'Income Statement'!G17</f>
         <v/>
       </c>
-      <c r="H10" s="18">
+      <c r="H10" s="19">
         <f>'Income Statement'!H17</f>
         <v/>
       </c>
-      <c r="I10" s="18">
+      <c r="I10" s="19">
         <f>'Income Statement'!I17</f>
         <v/>
       </c>
@@ -2050,38 +2051,38 @@
           <t>Free cash flow to the firm</t>
         </is>
       </c>
-      <c r="B11" s="29" t="inlineStr">
+      <c r="B11" s="30" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C11" s="29" t="inlineStr">
+      <c r="C11" s="30" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D11" s="29" t="inlineStr">
+      <c r="D11" s="30" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E11" s="18">
+      <c r="E11" s="19">
         <f>'Cash Flow'!D13</f>
         <v/>
       </c>
-      <c r="F11" s="18">
+      <c r="F11" s="19">
         <f>'Cash Flow'!E13</f>
         <v/>
       </c>
-      <c r="G11" s="18">
+      <c r="G11" s="19">
         <f>'Cash Flow'!F13</f>
         <v/>
       </c>
-      <c r="H11" s="18">
+      <c r="H11" s="19">
         <f>'Cash Flow'!G13</f>
         <v/>
       </c>
-      <c r="I11" s="18">
+      <c r="I11" s="19">
         <f>'Cash Flow'!H13</f>
         <v/>
       </c>
@@ -2092,35 +2093,35 @@
           <t>Net bank debt</t>
         </is>
       </c>
-      <c r="B12" s="18">
+      <c r="B12" s="19">
         <f>'Balance Sheet'!B17</f>
         <v/>
       </c>
-      <c r="C12" s="18">
+      <c r="C12" s="19">
         <f>'Balance Sheet'!C17</f>
         <v/>
       </c>
-      <c r="D12" s="18">
+      <c r="D12" s="19">
         <f>'Balance Sheet'!D17</f>
         <v/>
       </c>
-      <c r="E12" s="18">
+      <c r="E12" s="19">
         <f>'Balance Sheet'!E17</f>
         <v/>
       </c>
-      <c r="F12" s="18">
+      <c r="F12" s="19">
         <f>'Balance Sheet'!F17</f>
         <v/>
       </c>
-      <c r="G12" s="18">
+      <c r="G12" s="19">
         <f>'Balance Sheet'!G17</f>
         <v/>
       </c>
-      <c r="H12" s="18">
+      <c r="H12" s="19">
         <f>'Balance Sheet'!H17</f>
         <v/>
       </c>
-      <c r="I12" s="18">
+      <c r="I12" s="19">
         <f>'Balance Sheet'!I17</f>
         <v/>
       </c>
@@ -2131,37 +2132,37 @@
           <t>Invested capital</t>
         </is>
       </c>
-      <c r="B13" s="29" t="inlineStr">
+      <c r="B13" s="30" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C13" s="29" t="inlineStr">
+      <c r="C13" s="30" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D13" s="18">
+      <c r="D13" s="19">
         <f>'Balance Sheet'!D16+'Balance Sheet'!D5+Assumptions!$C$45</f>
         <v/>
       </c>
-      <c r="E13" s="18">
+      <c r="E13" s="19">
         <f>'Balance Sheet'!E16+'Balance Sheet'!E5+Assumptions!$C$45</f>
         <v/>
       </c>
-      <c r="F13" s="18">
+      <c r="F13" s="19">
         <f>'Balance Sheet'!F16+'Balance Sheet'!F5+Assumptions!$C$45</f>
         <v/>
       </c>
-      <c r="G13" s="18">
+      <c r="G13" s="19">
         <f>'Balance Sheet'!G16+'Balance Sheet'!G5+Assumptions!$C$45</f>
         <v/>
       </c>
-      <c r="H13" s="18">
+      <c r="H13" s="19">
         <f>'Balance Sheet'!H16+'Balance Sheet'!H5+Assumptions!$C$45</f>
         <v/>
       </c>
-      <c r="I13" s="18">
+      <c r="I13" s="19">
         <f>'Balance Sheet'!I16+'Balance Sheet'!I5+Assumptions!$C$45</f>
         <v/>
       </c>
@@ -2172,38 +2173,38 @@
           <t>Return on invested capital</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B14" s="9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C14" s="11" t="inlineStr">
+      <c r="C14" s="9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D14" s="11" t="inlineStr">
+      <c r="D14" s="9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E14" s="16">
+      <c r="E14" s="17">
         <f>DCF!B10/E13</f>
         <v/>
       </c>
-      <c r="F14" s="16">
+      <c r="F14" s="17">
         <f>DCF!C10/F13</f>
         <v/>
       </c>
-      <c r="G14" s="16">
+      <c r="G14" s="17">
         <f>DCF!D10/G13</f>
         <v/>
       </c>
-      <c r="H14" s="16">
+      <c r="H14" s="17">
         <f>DCF!E10/H13</f>
         <v/>
       </c>
-      <c r="I14" s="16">
+      <c r="I14" s="17">
         <f>DCF!F10/I13</f>
         <v/>
       </c>
@@ -2318,7 +2319,7 @@
       <c r="F5" s="7" t="n">
         <v>130.1682181904347</v>
       </c>
-      <c r="G5" s="9" t="n">
+      <c r="G5" s="21" t="n">
         <v>0.55144</v>
       </c>
     </row>
@@ -2343,7 +2344,7 @@
       <c r="F6" s="7" t="n">
         <v>154.1934203763022</v>
       </c>
-      <c r="G6" s="9" t="n">
+      <c r="G6" s="21" t="n">
         <v>0.59456</v>
       </c>
     </row>
@@ -2370,10 +2371,10 @@
           <t>Finishes 10% or more above spot</t>
         </is>
       </c>
-      <c r="B9" s="9" t="n">
+      <c r="B9" s="21" t="n">
         <v>0.23044</v>
       </c>
-      <c r="C9" s="9" t="n">
+      <c r="C9" s="21" t="n">
         <v>0.3878</v>
       </c>
     </row>
@@ -2383,10 +2384,10 @@
           <t>Finishes 10% or more below spot</t>
         </is>
       </c>
-      <c r="B10" s="9" t="n">
+      <c r="B10" s="21" t="n">
         <v>0.14414</v>
       </c>
-      <c r="C10" s="9" t="n">
+      <c r="C10" s="21" t="n">
         <v>0.21232</v>
       </c>
     </row>
@@ -2396,10 +2397,10 @@
           <t>Touches 10% above spot at any point</t>
         </is>
       </c>
-      <c r="B11" s="9" t="n">
+      <c r="B11" s="21" t="n">
         <v>0.36882</v>
       </c>
-      <c r="C11" s="9" t="n">
+      <c r="C11" s="21" t="n">
         <v>0.6306</v>
       </c>
     </row>
@@ -2409,10 +2410,10 @@
           <t>Touches 10% below spot at any point</t>
         </is>
       </c>
-      <c r="B12" s="9" t="n">
+      <c r="B12" s="21" t="n">
         <v>0.2549</v>
       </c>
-      <c r="C12" s="9" t="n">
+      <c r="C12" s="21" t="n">
         <v>0.446</v>
       </c>
     </row>
@@ -2434,7 +2435,7 @@
           <t>Simulated paths</t>
         </is>
       </c>
-      <c r="C15" s="23" t="n">
+      <c r="C15" s="24" t="n">
         <v>50000</v>
       </c>
     </row>
@@ -2444,7 +2445,7 @@
           <t>Annualised volatility (3-month anchor)</t>
         </is>
       </c>
-      <c r="C16" s="9" t="n">
+      <c r="C16" s="21" t="n">
         <v>0.4838094309558744</v>
       </c>
     </row>
@@ -2455,7 +2456,7 @@
         </is>
       </c>
       <c r="C17" s="8">
-        <f>Summary!C14</f>
+        <f>Summary!C16</f>
         <v/>
       </c>
     </row>
@@ -2465,7 +2466,7 @@
           <t>Anchor date</t>
         </is>
       </c>
-      <c r="C18" s="21" t="inlineStr">
+      <c r="C18" s="22" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
@@ -2517,7 +2518,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="20" t="inlineStr">
+      <c r="A4" s="15" t="inlineStr">
         <is>
           <t>Terminal cost of capital (rows) x terminal growth (columns)</t>
         </is>
@@ -2558,19 +2559,19 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>65.329844401984</v>
+        <v>64.02326653453551</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>68.35354257523431</v>
+        <v>66.87332082657952</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>71.9670712933261</v>
+        <v>70.27596109226505</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>76.39345107557055</v>
+        <v>74.4401253255354</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>81.98435185876774</v>
+        <v>79.69527743111146</v>
       </c>
     </row>
     <row r="7">
@@ -2580,19 +2581,19 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>58.4402879098668</v>
+        <v>57.37629801344737</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>60.6461755538821</v>
+        <v>59.44490839625706</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>63.21971152566643</v>
+        <v>61.85495881829012</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>66.28434770102153</v>
+        <v>64.7211007280429</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>70.02577372147603</v>
+        <v>68.21578663977438</v>
       </c>
     </row>
     <row r="8">
@@ -2602,19 +2603,19 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>52.6302713847032</v>
+        <v>51.7708075360223</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>54.24351203947743</v>
+        <v>53.27390215434404</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>56.08399377388404</v>
+        <v>54.98535884474298</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>58.22034038779206</v>
+        <v>56.96810019655753</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>60.75189974055389</v>
+        <v>59.31322032826569</v>
       </c>
     </row>
     <row r="9">
@@ -2624,19 +2625,19 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>47.66687793345727</v>
+        <v>46.98207982326851</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>48.84248007666995</v>
+        <v>48.06820632030645</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>50.15437928765454</v>
+        <v>49.27676996088003</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>51.63997115359249</v>
+        <v>50.64136360909256</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>53.35170855849378</v>
+        <v>52.20910626312477</v>
       </c>
     </row>
     <row r="10">
@@ -2646,23 +2647,23 @@
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>43.37959572111903</v>
+        <v>42.84560782729903</v>
       </c>
       <c r="C10" s="7" t="n">
-        <v>44.22702715685592</v>
+        <v>43.61959366674767</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>45.15076181775254</v>
+        <v>44.45954899997528</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>46.16998066974453</v>
+        <v>45.3820571183214</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>47.31088154269673</v>
+        <v>46.40976788449724</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="20" t="inlineStr">
+      <c r="A12" s="15" t="inlineStr">
         <is>
           <t>Explicit-window cost of capital (columns) x terminal cost of capital (rows)</t>
         </is>
@@ -2703,19 +2704,19 @@
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>76.53066395732843</v>
+        <v>84.65984646706161</v>
       </c>
       <c r="C14" s="7" t="n">
-        <v>74.20763706152702</v>
+        <v>82.13279721284205</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>71.9670712933261</v>
+        <v>79.69527743111146</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>69.80531513594863</v>
+        <v>77.34332590623208</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>67.71891197265076</v>
+        <v>75.07319276143608</v>
       </c>
     </row>
     <row r="15">
@@ -2725,19 +2726,19 @@
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>67.28261009519261</v>
+        <v>72.52574844266042</v>
       </c>
       <c r="C15" s="7" t="n">
-        <v>65.21451934442834</v>
+        <v>70.3319852695824</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>63.21971152566643</v>
+        <v>68.21578663977438</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>61.29494639096928</v>
+        <v>66.17372628576796</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>59.4371564326104</v>
+        <v>64.20256050533408</v>
       </c>
     </row>
     <row r="16">
@@ -2747,19 +2748,19 @@
         </is>
       </c>
       <c r="B16" s="7" t="n">
-        <v>59.73868410008669</v>
+        <v>63.11573867848826</v>
       </c>
       <c r="C16" s="7" t="n">
-        <v>57.87843695583718</v>
+        <v>61.18033295945634</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>56.08399377388404</v>
+        <v>59.31322032826569</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>54.35244928326305</v>
+        <v>57.51138889928905</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>52.68105291114693</v>
+        <v>55.77198707016157</v>
       </c>
     </row>
     <row r="17">
@@ -2769,19 +2770,19 @@
         </is>
       </c>
       <c r="B17" s="7" t="n">
-        <v>53.47006721636905</v>
+        <v>55.60688154053267</v>
       </c>
       <c r="C17" s="7" t="n">
-        <v>51.78242507173835</v>
+        <v>53.87754330288151</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>50.15437928765454</v>
+        <v>52.20910626312477</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>48.58330249404308</v>
+        <v>50.59888878852414</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>47.06670705720629</v>
+        <v>49.04435177713601</v>
       </c>
     </row>
     <row r="18">
@@ -2791,23 +2792,23 @@
         </is>
       </c>
       <c r="B18" s="7" t="n">
-        <v>48.18057399728519</v>
+        <v>49.47730377942706</v>
       </c>
       <c r="C18" s="7" t="n">
-        <v>46.63848559892643</v>
+        <v>47.91609946481731</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>45.15076181775254</v>
+        <v>46.40976788449724</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>43.71500938002328</v>
+        <v>44.95589663617206</v>
       </c>
       <c r="F18" s="7" t="n">
-        <v>42.32896215043171</v>
+        <v>43.55220138111397</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="20" t="inlineStr">
+      <c r="A20" s="15" t="inlineStr">
         <is>
           <t>Single-driver sensitivities — five engine re-runs per row; the parameter grid for each row is shown beside its name</t>
         </is>
@@ -2838,21 +2839,21 @@
         </is>
       </c>
       <c r="B22" s="7" t="n">
-        <v>82.1040695099194</v>
+        <v>92.05706087886328</v>
       </c>
       <c r="C22" s="7" t="n">
-        <v>67.65449935590391</v>
+        <v>73.37265613726478</v>
       </c>
       <c r="D22" s="7" t="n">
-        <v>56.08399377388404</v>
+        <v>59.31322032826569</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>49.74342393917833</v>
+        <v>51.92216787250401</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>43.98578978959206</v>
-      </c>
-      <c r="H22" s="10">
+        <v>45.39154463312268</v>
+      </c>
+      <c r="H22" s="16">
         <f>MAX(B22:F22)-MIN(B22:F22)</f>
         <v/>
       </c>
@@ -2864,21 +2865,21 @@
         </is>
       </c>
       <c r="B23" s="7" t="n">
-        <v>52.41845656686412</v>
+        <v>53.41908966035297</v>
       </c>
       <c r="C23" s="7" t="n">
-        <v>56.08399377388404</v>
+        <v>55.48217612662315</v>
       </c>
       <c r="D23" s="7" t="n">
-        <v>63.41506818792391</v>
+        <v>59.60834905916349</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>72.57891120547374</v>
+        <v>64.76606522483894</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>81.74275422302357</v>
-      </c>
-      <c r="H23" s="10">
+        <v>69.92378139051441</v>
+      </c>
+      <c r="H23" s="16">
         <f>MAX(B23:F23)-MIN(B23:F23)</f>
         <v/>
       </c>
@@ -2890,21 +2891,21 @@
         </is>
       </c>
       <c r="B24" s="7" t="n">
-        <v>30.09596871603819</v>
+        <v>31.52261532145548</v>
       </c>
       <c r="C24" s="7" t="n">
-        <v>43.08998124496109</v>
+        <v>43.50239572403932</v>
       </c>
       <c r="D24" s="7" t="n">
-        <v>56.08399377388404</v>
+        <v>55.48217612662315</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>69.078006302807</v>
+        <v>67.46195652920696</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>82.07201883172988</v>
-      </c>
-      <c r="H24" s="10">
+        <v>79.4417369317908</v>
+      </c>
+      <c r="H24" s="16">
         <f>MAX(B24:F24)-MIN(B24:F24)</f>
         <v/>
       </c>
@@ -2916,21 +2917,21 @@
         </is>
       </c>
       <c r="B25" s="7" t="n">
-        <v>50.58568796335414</v>
+        <v>52.3875464272179</v>
       </c>
       <c r="C25" s="7" t="n">
-        <v>53.33484086861908</v>
+        <v>53.9348612769205</v>
       </c>
       <c r="D25" s="7" t="n">
-        <v>56.08399377388404</v>
+        <v>55.48217612662315</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>58.83314667914899</v>
+        <v>57.02949097632575</v>
       </c>
       <c r="F25" s="7" t="n">
-        <v>61.58229958441391</v>
-      </c>
-      <c r="H25" s="10">
+        <v>58.57680582602841</v>
+      </c>
+      <c r="H25" s="16">
         <f>MAX(B25:F25)-MIN(B25:F25)</f>
         <v/>
       </c>
@@ -2942,21 +2943,21 @@
         </is>
       </c>
       <c r="B26" s="7" t="n">
-        <v>62.98785448545478</v>
+        <v>62.73597456572764</v>
       </c>
       <c r="C26" s="7" t="n">
-        <v>59.41689204843545</v>
+        <v>58.98400985584599</v>
       </c>
       <c r="D26" s="7" t="n">
-        <v>56.08399377388404</v>
+        <v>55.48217612662315</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>52.27496717439674</v>
+        <v>51.48008043608273</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>48.70400473737737</v>
-      </c>
-      <c r="H26" s="10">
+        <v>47.72811572620108</v>
+      </c>
+      <c r="H26" s="16">
         <f>MAX(B26:F26)-MIN(B26:F26)</f>
         <v/>
       </c>
@@ -2964,25 +2965,25 @@
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>Terminal return on invested capital  (15.0% / 18.0% / 20.4% / 26.0% / 30.0%)</t>
+          <t>Terminal return on invested capital  (15.0% / 18.0% / 20.1% / 26.0% / 30.0%)</t>
         </is>
       </c>
       <c r="B27" s="7" t="n">
-        <v>49.68012825683863</v>
+        <v>48.93607870871411</v>
       </c>
       <c r="C27" s="7" t="n">
-        <v>53.7154504510227</v>
+        <v>55.75099900441143</v>
       </c>
       <c r="D27" s="7" t="n">
-        <v>56.08399377388404</v>
+        <v>59.31322032826569</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>59.92363844207513</v>
+        <v>66.23549176702268</v>
       </c>
       <c r="F27" s="7" t="n">
-        <v>61.78609483939085</v>
-      </c>
-      <c r="H27" s="10">
+        <v>69.38083959580605</v>
+      </c>
+      <c r="H27" s="16">
         <f>MAX(B27:F27)-MIN(B27:F27)</f>
         <v/>
       </c>
@@ -2994,21 +2995,21 @@
         </is>
       </c>
       <c r="B28" s="7" t="n">
-        <v>52.6302713847032</v>
+        <v>51.7708075360223</v>
       </c>
       <c r="C28" s="7" t="n">
-        <v>54.24351203947743</v>
+        <v>53.27390215434404</v>
       </c>
       <c r="D28" s="7" t="n">
-        <v>56.08399377388404</v>
+        <v>54.98535884474298</v>
       </c>
       <c r="E28" s="7" t="n">
-        <v>58.22034038779206</v>
+        <v>56.96810019655753</v>
       </c>
       <c r="F28" s="7" t="n">
-        <v>60.75189974055389</v>
-      </c>
-      <c r="H28" s="10">
+        <v>59.31322032826569</v>
+      </c>
+      <c r="H28" s="16">
         <f>MAX(B28:F28)-MIN(B28:F28)</f>
         <v/>
       </c>
@@ -3113,35 +3114,35 @@
           <t>Earnings per share (EGP)</t>
         </is>
       </c>
-      <c r="B5" s="10">
+      <c r="B5" s="16">
         <f>'Income Statement'!B18</f>
         <v/>
       </c>
-      <c r="C5" s="10">
+      <c r="C5" s="16">
         <f>'Income Statement'!C18</f>
         <v/>
       </c>
-      <c r="D5" s="10">
+      <c r="D5" s="16">
         <f>'Income Statement'!D18</f>
         <v/>
       </c>
-      <c r="E5" s="10">
+      <c r="E5" s="16">
         <f>'Income Statement'!E18</f>
         <v/>
       </c>
-      <c r="F5" s="10">
+      <c r="F5" s="16">
         <f>'Income Statement'!F18</f>
         <v/>
       </c>
-      <c r="G5" s="10">
+      <c r="G5" s="16">
         <f>'Income Statement'!G18</f>
         <v/>
       </c>
-      <c r="H5" s="10">
+      <c r="H5" s="16">
         <f>'Income Statement'!H18</f>
         <v/>
       </c>
-      <c r="I5" s="10">
+      <c r="I5" s="16">
         <f>'Income Statement'!I18</f>
         <v/>
       </c>
@@ -3152,35 +3153,35 @@
           <t>Book value per share (EGP)</t>
         </is>
       </c>
-      <c r="B6" s="10">
+      <c r="B6" s="16">
         <f>'Balance Sheet'!B14/Assumptions!$C$6</f>
         <v/>
       </c>
-      <c r="C6" s="10">
+      <c r="C6" s="16">
         <f>'Balance Sheet'!C14/Assumptions!$C$6</f>
         <v/>
       </c>
-      <c r="D6" s="10">
+      <c r="D6" s="16">
         <f>'Balance Sheet'!D14/Assumptions!$C$6</f>
         <v/>
       </c>
-      <c r="E6" s="10">
+      <c r="E6" s="16">
         <f>'Balance Sheet'!E14/Assumptions!$C$6</f>
         <v/>
       </c>
-      <c r="F6" s="10">
+      <c r="F6" s="16">
         <f>'Balance Sheet'!F14/Assumptions!$C$6</f>
         <v/>
       </c>
-      <c r="G6" s="10">
+      <c r="G6" s="16">
         <f>'Balance Sheet'!G14/Assumptions!$C$6</f>
         <v/>
       </c>
-      <c r="H6" s="10">
+      <c r="H6" s="16">
         <f>'Balance Sheet'!H14/Assumptions!$C$6</f>
         <v/>
       </c>
-      <c r="I6" s="10">
+      <c r="I6" s="16">
         <f>'Balance Sheet'!I14/Assumptions!$C$6</f>
         <v/>
       </c>
@@ -3191,38 +3192,38 @@
           <t>Free cash flow per share (EGP)</t>
         </is>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="16" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C7" s="10" t="inlineStr">
+      <c r="C7" s="16" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D7" s="10" t="inlineStr">
+      <c r="D7" s="16" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E7" s="10">
+      <c r="E7" s="16">
         <f>'Summary Financials'!E11/Assumptions!$C$6</f>
         <v/>
       </c>
-      <c r="F7" s="10">
+      <c r="F7" s="16">
         <f>'Summary Financials'!F11/Assumptions!$C$6</f>
         <v/>
       </c>
-      <c r="G7" s="10">
+      <c r="G7" s="16">
         <f>'Summary Financials'!G11/Assumptions!$C$6</f>
         <v/>
       </c>
-      <c r="H7" s="10">
+      <c r="H7" s="16">
         <f>'Summary Financials'!H11/Assumptions!$C$6</f>
         <v/>
       </c>
-      <c r="I7" s="10">
+      <c r="I7" s="16">
         <f>'Summary Financials'!I11/Assumptions!$C$6</f>
         <v/>
       </c>
@@ -3233,35 +3234,35 @@
           <t>Gross margin</t>
         </is>
       </c>
-      <c r="B8" s="11">
+      <c r="B8" s="9">
         <f>'Income Statement'!B6/'Income Statement'!B5</f>
         <v/>
       </c>
-      <c r="C8" s="11">
+      <c r="C8" s="9">
         <f>'Income Statement'!C6/'Income Statement'!C5</f>
         <v/>
       </c>
-      <c r="D8" s="11">
+      <c r="D8" s="9">
         <f>'Income Statement'!D6/'Income Statement'!D5</f>
         <v/>
       </c>
-      <c r="E8" s="11">
+      <c r="E8" s="9">
         <f>'Income Statement'!E6/'Income Statement'!E5</f>
         <v/>
       </c>
-      <c r="F8" s="11">
+      <c r="F8" s="9">
         <f>'Income Statement'!F6/'Income Statement'!F5</f>
         <v/>
       </c>
-      <c r="G8" s="11">
+      <c r="G8" s="9">
         <f>'Income Statement'!G6/'Income Statement'!G5</f>
         <v/>
       </c>
-      <c r="H8" s="11">
+      <c r="H8" s="9">
         <f>'Income Statement'!H6/'Income Statement'!H5</f>
         <v/>
       </c>
-      <c r="I8" s="11">
+      <c r="I8" s="9">
         <f>'Income Statement'!I6/'Income Statement'!I5</f>
         <v/>
       </c>
@@ -3272,35 +3273,35 @@
           <t>EBITDA margin</t>
         </is>
       </c>
-      <c r="B9" s="11">
+      <c r="B9" s="9">
         <f>'Income Statement'!B8</f>
         <v/>
       </c>
-      <c r="C9" s="11">
+      <c r="C9" s="9">
         <f>'Income Statement'!C8</f>
         <v/>
       </c>
-      <c r="D9" s="11">
+      <c r="D9" s="9">
         <f>'Income Statement'!D8</f>
         <v/>
       </c>
-      <c r="E9" s="11">
+      <c r="E9" s="9">
         <f>'Income Statement'!E8</f>
         <v/>
       </c>
-      <c r="F9" s="11">
+      <c r="F9" s="9">
         <f>'Income Statement'!F8</f>
         <v/>
       </c>
-      <c r="G9" s="11">
+      <c r="G9" s="9">
         <f>'Income Statement'!G8</f>
         <v/>
       </c>
-      <c r="H9" s="11">
+      <c r="H9" s="9">
         <f>'Income Statement'!H8</f>
         <v/>
       </c>
-      <c r="I9" s="11">
+      <c r="I9" s="9">
         <f>'Income Statement'!I8</f>
         <v/>
       </c>
@@ -3311,35 +3312,35 @@
           <t>EBIT margin</t>
         </is>
       </c>
-      <c r="B10" s="11">
+      <c r="B10" s="9">
         <f>'Income Statement'!B10/'Income Statement'!B5</f>
         <v/>
       </c>
-      <c r="C10" s="11">
+      <c r="C10" s="9">
         <f>'Income Statement'!C10/'Income Statement'!C5</f>
         <v/>
       </c>
-      <c r="D10" s="11">
+      <c r="D10" s="9">
         <f>'Income Statement'!D10/'Income Statement'!D5</f>
         <v/>
       </c>
-      <c r="E10" s="11">
+      <c r="E10" s="9">
         <f>'Income Statement'!E10/'Income Statement'!E5</f>
         <v/>
       </c>
-      <c r="F10" s="11">
+      <c r="F10" s="9">
         <f>'Income Statement'!F10/'Income Statement'!F5</f>
         <v/>
       </c>
-      <c r="G10" s="11">
+      <c r="G10" s="9">
         <f>'Income Statement'!G10/'Income Statement'!G5</f>
         <v/>
       </c>
-      <c r="H10" s="11">
+      <c r="H10" s="9">
         <f>'Income Statement'!H10/'Income Statement'!H5</f>
         <v/>
       </c>
-      <c r="I10" s="11">
+      <c r="I10" s="9">
         <f>'Income Statement'!I10/'Income Statement'!I5</f>
         <v/>
       </c>
@@ -3350,35 +3351,35 @@
           <t>Net margin (attributable)</t>
         </is>
       </c>
-      <c r="B11" s="11">
+      <c r="B11" s="9">
         <f>'Income Statement'!B17/'Income Statement'!B5</f>
         <v/>
       </c>
-      <c r="C11" s="11">
+      <c r="C11" s="9">
         <f>'Income Statement'!C17/'Income Statement'!C5</f>
         <v/>
       </c>
-      <c r="D11" s="11">
+      <c r="D11" s="9">
         <f>'Income Statement'!D17/'Income Statement'!D5</f>
         <v/>
       </c>
-      <c r="E11" s="11">
+      <c r="E11" s="9">
         <f>'Income Statement'!E17/'Income Statement'!E5</f>
         <v/>
       </c>
-      <c r="F11" s="11">
+      <c r="F11" s="9">
         <f>'Income Statement'!F17/'Income Statement'!F5</f>
         <v/>
       </c>
-      <c r="G11" s="11">
+      <c r="G11" s="9">
         <f>'Income Statement'!G17/'Income Statement'!G5</f>
         <v/>
       </c>
-      <c r="H11" s="11">
+      <c r="H11" s="9">
         <f>'Income Statement'!H17/'Income Statement'!H5</f>
         <v/>
       </c>
-      <c r="I11" s="11">
+      <c r="I11" s="9">
         <f>'Income Statement'!I17/'Income Statement'!I5</f>
         <v/>
       </c>
@@ -3389,36 +3390,36 @@
           <t>Return on equity</t>
         </is>
       </c>
-      <c r="B12" s="11" t="inlineStr">
+      <c r="B12" s="9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C12" s="11">
+      <c r="C12" s="9">
         <f>'Income Statement'!C17/(('Balance Sheet'!B14+'Balance Sheet'!C14)/2)</f>
         <v/>
       </c>
-      <c r="D12" s="11">
+      <c r="D12" s="9">
         <f>'Income Statement'!D17/(('Balance Sheet'!C14+'Balance Sheet'!D14)/2)</f>
         <v/>
       </c>
-      <c r="E12" s="11">
+      <c r="E12" s="9">
         <f>'Income Statement'!E17/(('Balance Sheet'!D14+'Balance Sheet'!E14)/2)</f>
         <v/>
       </c>
-      <c r="F12" s="11">
+      <c r="F12" s="9">
         <f>'Income Statement'!F17/(('Balance Sheet'!E14+'Balance Sheet'!F14)/2)</f>
         <v/>
       </c>
-      <c r="G12" s="11">
+      <c r="G12" s="9">
         <f>'Income Statement'!G17/(('Balance Sheet'!F14+'Balance Sheet'!G14)/2)</f>
         <v/>
       </c>
-      <c r="H12" s="11">
+      <c r="H12" s="9">
         <f>'Income Statement'!H17/(('Balance Sheet'!G14+'Balance Sheet'!H14)/2)</f>
         <v/>
       </c>
-      <c r="I12" s="11">
+      <c r="I12" s="9">
         <f>'Income Statement'!I17/(('Balance Sheet'!H14+'Balance Sheet'!I14)/2)</f>
         <v/>
       </c>
@@ -3429,38 +3430,38 @@
           <t>Return on invested capital</t>
         </is>
       </c>
-      <c r="B13" s="11" t="inlineStr">
+      <c r="B13" s="9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C13" s="11" t="inlineStr">
+      <c r="C13" s="9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D13" s="11" t="inlineStr">
+      <c r="D13" s="9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E13" s="11">
+      <c r="E13" s="9">
         <f>'Summary Financials'!E14</f>
         <v/>
       </c>
-      <c r="F13" s="11">
+      <c r="F13" s="9">
         <f>'Summary Financials'!F14</f>
         <v/>
       </c>
-      <c r="G13" s="11">
+      <c r="G13" s="9">
         <f>'Summary Financials'!G14</f>
         <v/>
       </c>
-      <c r="H13" s="11">
+      <c r="H13" s="9">
         <f>'Summary Financials'!H14</f>
         <v/>
       </c>
-      <c r="I13" s="11">
+      <c r="I13" s="9">
         <f>'Summary Financials'!I14</f>
         <v/>
       </c>
@@ -3471,35 +3472,35 @@
           <t>Net debt / EBITDA</t>
         </is>
       </c>
-      <c r="B14" s="35">
+      <c r="B14" s="36">
         <f>'Balance Sheet'!B18</f>
         <v/>
       </c>
-      <c r="C14" s="35">
+      <c r="C14" s="36">
         <f>'Balance Sheet'!C18</f>
         <v/>
       </c>
-      <c r="D14" s="35">
+      <c r="D14" s="36">
         <f>'Balance Sheet'!D18</f>
         <v/>
       </c>
-      <c r="E14" s="35">
+      <c r="E14" s="36">
         <f>'Balance Sheet'!E18</f>
         <v/>
       </c>
-      <c r="F14" s="35">
+      <c r="F14" s="36">
         <f>'Balance Sheet'!F18</f>
         <v/>
       </c>
-      <c r="G14" s="35">
+      <c r="G14" s="36">
         <f>'Balance Sheet'!G18</f>
         <v/>
       </c>
-      <c r="H14" s="35">
+      <c r="H14" s="36">
         <f>'Balance Sheet'!H18</f>
         <v/>
       </c>
-      <c r="I14" s="35">
+      <c r="I14" s="36">
         <f>'Balance Sheet'!I18</f>
         <v/>
       </c>
@@ -3510,36 +3511,36 @@
           <t>Interest cover (EBIT / net interest)</t>
         </is>
       </c>
-      <c r="B15" s="35" t="inlineStr">
+      <c r="B15" s="36" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C15" s="35">
+      <c r="C15" s="36">
         <f>-'Income Statement'!C10/'Income Statement'!C11</f>
         <v/>
       </c>
-      <c r="D15" s="35">
+      <c r="D15" s="36">
         <f>-'Income Statement'!D10/'Income Statement'!D11</f>
         <v/>
       </c>
-      <c r="E15" s="35">
+      <c r="E15" s="36">
         <f>-'Income Statement'!E10/'Income Statement'!E11</f>
         <v/>
       </c>
-      <c r="F15" s="35">
+      <c r="F15" s="36">
         <f>-'Income Statement'!F10/'Income Statement'!F11</f>
         <v/>
       </c>
-      <c r="G15" s="35">
+      <c r="G15" s="36">
         <f>-'Income Statement'!G10/'Income Statement'!G11</f>
         <v/>
       </c>
-      <c r="H15" s="35">
+      <c r="H15" s="36">
         <f>-'Income Statement'!H10/'Income Statement'!H11</f>
         <v/>
       </c>
-      <c r="I15" s="35">
+      <c r="I15" s="36">
         <f>-'Income Statement'!I10/'Income Statement'!I11</f>
         <v/>
       </c>
@@ -3550,35 +3551,35 @@
           <t>Working capital / revenue</t>
         </is>
       </c>
-      <c r="B16" s="11">
+      <c r="B16" s="9">
         <f>'Balance Sheet'!B16/'Income Statement'!B5</f>
         <v/>
       </c>
-      <c r="C16" s="11">
+      <c r="C16" s="9">
         <f>'Balance Sheet'!C16/'Income Statement'!C5</f>
         <v/>
       </c>
-      <c r="D16" s="11">
+      <c r="D16" s="9">
         <f>'Balance Sheet'!D16/'Income Statement'!D5</f>
         <v/>
       </c>
-      <c r="E16" s="11">
+      <c r="E16" s="9">
         <f>'Balance Sheet'!E16/'Income Statement'!E5</f>
         <v/>
       </c>
-      <c r="F16" s="11">
+      <c r="F16" s="9">
         <f>'Balance Sheet'!F16/'Income Statement'!F5</f>
         <v/>
       </c>
-      <c r="G16" s="11">
+      <c r="G16" s="9">
         <f>'Balance Sheet'!G16/'Income Statement'!G5</f>
         <v/>
       </c>
-      <c r="H16" s="11">
+      <c r="H16" s="9">
         <f>'Balance Sheet'!H16/'Income Statement'!H5</f>
         <v/>
       </c>
-      <c r="I16" s="11">
+      <c r="I16" s="9">
         <f>'Balance Sheet'!I16/'Income Statement'!I5</f>
         <v/>
       </c>
@@ -3589,36 +3590,36 @@
           <t>Capital expenditure / revenue</t>
         </is>
       </c>
-      <c r="B17" s="11" t="inlineStr">
+      <c r="B17" s="9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C17" s="11">
+      <c r="C17" s="9">
         <f>-'Cash Flow'!B11/'Income Statement'!C5</f>
         <v/>
       </c>
-      <c r="D17" s="11">
+      <c r="D17" s="9">
         <f>-'Cash Flow'!C11/'Income Statement'!D5</f>
         <v/>
       </c>
-      <c r="E17" s="11">
+      <c r="E17" s="9">
         <f>-'Cash Flow'!D11/'Income Statement'!E5</f>
         <v/>
       </c>
-      <c r="F17" s="11">
+      <c r="F17" s="9">
         <f>-'Cash Flow'!E11/'Income Statement'!F5</f>
         <v/>
       </c>
-      <c r="G17" s="11">
+      <c r="G17" s="9">
         <f>-'Cash Flow'!F11/'Income Statement'!G5</f>
         <v/>
       </c>
-      <c r="H17" s="11">
+      <c r="H17" s="9">
         <f>-'Cash Flow'!G11/'Income Statement'!H5</f>
         <v/>
       </c>
-      <c r="I17" s="11">
+      <c r="I17" s="9">
         <f>-'Cash Flow'!H11/'Income Statement'!I5</f>
         <v/>
       </c>
@@ -3629,36 +3630,36 @@
           <t>Reinvestment rate</t>
         </is>
       </c>
-      <c r="B18" s="9" t="n">
+      <c r="B18" s="21" t="n">
         <v>0.2012516504606288</v>
       </c>
-      <c r="C18" s="9" t="n">
+      <c r="C18" s="21" t="n">
         <v>0.3037580263923543</v>
       </c>
-      <c r="D18" s="9" t="n">
+      <c r="D18" s="21" t="n">
         <v>0.5146285136141233</v>
       </c>
-      <c r="E18" s="11" t="inlineStr">
+      <c r="E18" s="9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F18" s="11" t="inlineStr">
+      <c r="F18" s="9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G18" s="11" t="inlineStr">
+      <c r="G18" s="9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H18" s="11" t="inlineStr">
+      <c r="H18" s="9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I18" s="11" t="inlineStr">
+      <c r="I18" s="9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3670,36 +3671,36 @@
           <t>Implied growth (return on capital x reinvestment)</t>
         </is>
       </c>
-      <c r="B19" s="9" t="n">
+      <c r="B19" s="21" t="n">
         <v>0.04486693009301836</v>
       </c>
-      <c r="C19" s="9" t="n">
+      <c r="C19" s="21" t="n">
         <v>0.07551752174309861</v>
       </c>
-      <c r="D19" s="9" t="n">
+      <c r="D19" s="21" t="n">
         <v>0.1079821501300804</v>
       </c>
-      <c r="E19" s="11" t="inlineStr">
+      <c r="E19" s="9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F19" s="11" t="inlineStr">
+      <c r="F19" s="9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G19" s="11" t="inlineStr">
+      <c r="G19" s="9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H19" s="11" t="inlineStr">
+      <c r="H19" s="9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I19" s="11" t="inlineStr">
+      <c r="I19" s="9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3708,7 +3709,7 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Terminal growth reconciliation: actual NOPAT compound growth FY2023–FY2025 was 26.9%; the implied growth from stable years only (FY2024 excluded as a debt-funded capacity burst) is 7.6%; the adopted terminal growth is 5.0%, below the blended nominal ceiling of 11.1%.</t>
+          <t>Terminal growth reconciliation: actual NOPAT compound growth FY2023–FY2025 was 26.9%; the implied growth from stable years only (FY2024 excluded as a debt-funded capacity burst) is 7.6%; the adopted terminal growth is 7.0%, below the blended nominal ceiling of 11.1%.</t>
         </is>
       </c>
     </row>
@@ -3786,12 +3787,12 @@
           <t>Saudi Arabia</t>
         </is>
       </c>
-      <c r="C5" s="40" t="inlineStr">
+      <c r="C5" s="41" t="inlineStr">
         <is>
           <t>nearest listed regional cable manufacturer</t>
         </is>
       </c>
-      <c r="D5" s="40" t="inlineStr">
+      <c r="D5" s="41" t="inlineStr">
         <is>
           <t>far smaller, no contracting arm, lighter balance sheet, pegged currency</t>
         </is>
@@ -3808,12 +3809,12 @@
           <t>Egypt</t>
         </is>
       </c>
-      <c r="C6" s="40" t="inlineStr">
+      <c r="C6" s="41" t="inlineStr">
         <is>
           <t>the only other listed Egyptian cable manufacturer</t>
         </is>
       </c>
-      <c r="D6" s="40" t="inlineStr">
+      <c r="D6" s="41" t="inlineStr">
         <is>
           <t>much smaller, domestic, heavily levered, currently loss-making</t>
         </is>
@@ -3830,12 +3831,12 @@
           <t>Europe</t>
         </is>
       </c>
-      <c r="C7" s="40" t="inlineStr">
+      <c r="C7" s="41" t="inlineStr">
         <is>
           <t>closest match on business model — cables plus projects</t>
         </is>
       </c>
-      <c r="D7" s="40" t="inlineStr">
+      <c r="D7" s="41" t="inlineStr">
         <is>
           <t>developed-market cost of capital; no convertibility risk</t>
         </is>
@@ -3852,12 +3853,12 @@
           <t>Gulf and North Africa</t>
         </is>
       </c>
-      <c r="C8" s="40" t="inlineStr">
+      <c r="C8" s="41" t="inlineStr">
         <is>
           <t>the right frame for the roughly 32% that is the Constructions and infrastructure segment</t>
         </is>
       </c>
-      <c r="D8" s="40" t="inlineStr">
+      <c r="D8" s="41" t="inlineStr">
         <is>
           <t>project accounting and backlog quality are not comparable</t>
         </is>
@@ -3881,7 +3882,7 @@
           <t>Trailing enterprise value / EBITDA</t>
         </is>
       </c>
-      <c r="B11" s="33">
+      <c r="B11" s="34">
         <f>'Relative &amp; Normalized'!C13</f>
         <v/>
       </c>
@@ -3892,7 +3893,7 @@
           <t>Trailing price / earnings</t>
         </is>
       </c>
-      <c r="B12" s="33">
+      <c r="B12" s="34">
         <f>'Relative &amp; Normalized'!C14</f>
         <v/>
       </c>
@@ -3903,7 +3904,7 @@
           <t>Trailing price / book</t>
         </is>
       </c>
-      <c r="B13" s="33">
+      <c r="B13" s="34">
         <f>'Relative &amp; Normalized'!C15</f>
         <v/>
       </c>
@@ -3914,7 +3915,7 @@
           <t>Justified enterprise value / EBITDA applied</t>
         </is>
       </c>
-      <c r="B14" s="33">
+      <c r="B14" s="34">
         <f>'Relative &amp; Normalized'!C6</f>
         <v/>
       </c>
@@ -3925,7 +3926,7 @@
           <t>Justified price / earnings applied</t>
         </is>
       </c>
-      <c r="B15" s="33">
+      <c r="B15" s="34">
         <f>'Relative &amp; Normalized'!C27</f>
         <v/>
       </c>
@@ -3941,7 +3942,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -3996,45 +3997,39 @@
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>Weight</t>
-        </is>
-      </c>
-      <c r="F4" s="5" t="inlineStr">
-        <is>
-          <t>Contribution</t>
-        </is>
-      </c>
+          <t>Role</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr"/>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>vs spot</t>
+          <t>vs price</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Discounted cash flow (primary)</t>
+          <t>Discounted cash flow (the answer)</t>
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>19.945090316451</v>
+        <v>19.89441449632232</v>
       </c>
       <c r="C5" s="8">
         <f>DCF!C62</f>
         <v/>
       </c>
       <c r="D5" s="7" t="n">
-        <v>122.3348933382508</v>
-      </c>
-      <c r="E5" s="9" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="F5" s="10">
-        <f>C5*E5</f>
-        <v/>
-      </c>
-      <c r="G5" s="11">
-        <f>C5/$C$14-1</f>
+        <v>104.9620537972264</v>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>THE CENTRAL — the class primary</t>
+        </is>
+      </c>
+      <c r="G5" s="9">
+        <f>C5/$C$16-1</f>
         <v/>
       </c>
     </row>
@@ -4056,15 +4051,13 @@
         <f>'Relative &amp; Normalized'!D12</f>
         <v/>
       </c>
-      <c r="E6" s="9" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F6" s="10">
-        <f>C6*E6</f>
-        <v/>
-      </c>
-      <c r="G6" s="11">
-        <f>C6/$C$14-1</f>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>cross-check</t>
+        </is>
+      </c>
+      <c r="G6" s="9">
+        <f>C6/$C$16-1</f>
         <v/>
       </c>
     </row>
@@ -4086,15 +4079,13 @@
         <f>'Relative &amp; Normalized'!F28</f>
         <v/>
       </c>
-      <c r="E7" s="9" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F7" s="10">
-        <f>C7*E7</f>
-        <v/>
-      </c>
-      <c r="G7" s="11">
-        <f>C7/$C$14-1</f>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>REMOVED — not a lens this class publishes</t>
+        </is>
+      </c>
+      <c r="G7" s="9">
+        <f>C7/$C$16-1</f>
         <v/>
       </c>
     </row>
@@ -4116,209 +4107,243 @@
         <f>'Relative &amp; Normalized'!F36</f>
         <v/>
       </c>
-      <c r="E8" s="9" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="F8" s="10">
-        <f>C8*E8</f>
-        <v/>
-      </c>
-      <c r="G8" s="11">
-        <f>C8/$C$14-1</f>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>a disclosed floor, never weighted</t>
+        </is>
+      </c>
+      <c r="G8" s="9">
+        <f>C8/$C$16-1</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>Weighted central</t>
-        </is>
-      </c>
-      <c r="B9" s="13">
-        <f>MIN(B5:B8)</f>
-        <v/>
-      </c>
-      <c r="C9" s="13">
-        <f>SUM(F5:F8)</f>
-        <v/>
-      </c>
-      <c r="D9" s="13">
-        <f>MAX(D5:D8)</f>
-        <v/>
-      </c>
-      <c r="E9" s="14">
-        <f>SUM(E5:E8)</f>
-        <v/>
-      </c>
-      <c r="F9" s="15" t="n"/>
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>THE CENTRAL — the cash-flow lens, not an average</t>
+        </is>
+      </c>
+      <c r="B9" s="11">
+        <f>B5</f>
+        <v/>
+      </c>
+      <c r="C9" s="11">
+        <f>C5</f>
+        <v/>
+      </c>
+      <c r="D9" s="11">
+        <f>D5</f>
+        <v/>
+      </c>
+      <c r="E9" s="12" t="inlineStr">
+        <is>
+          <t>the class primary</t>
+        </is>
+      </c>
+      <c r="F9" s="13" t="n"/>
       <c r="G9" s="14">
-        <f>C9/$C$14-1</f>
+        <f>C9/$C$16-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>NOT AVERAGED — the retired 45/20/20/15 blend, published unused</t>
+        </is>
+      </c>
+      <c r="C10" s="16">
+        <f>C5*0.45+C6*0.2+C7*0.2+C8*0.15</f>
+        <v/>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>retired 04-Sep-2026</t>
+        </is>
+      </c>
+      <c r="G10" s="9">
+        <f>C10/$C$16-1</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Alternative reading — currency of discounting</t>
-        </is>
-      </c>
-      <c r="C11" s="8">
-        <f>'Fundamental Valuation'!C18</f>
-        <v/>
-      </c>
-      <c r="G11" s="11">
-        <f>C11/$C$14-1</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>Terminal value share of DCF enterprise value</t>
-        </is>
-      </c>
-      <c r="C12" s="16">
-        <f>DCF!C28</f>
+          <t>Span across the lenses (min/max) — a spread between METHODS, not a range around the answer</t>
+        </is>
+      </c>
+      <c r="B11" s="16">
+        <f>MIN(B5:B8)</f>
+        <v/>
+      </c>
+      <c r="D11" s="16">
+        <f>MAX(D5:D8)</f>
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
+          <t>Alternative reading — currency of discounting</t>
+        </is>
+      </c>
+      <c r="C13" s="8">
+        <f>'Fundamental Valuation'!C18</f>
+        <v/>
+      </c>
+      <c r="G13" s="9">
+        <f>C13/$C$16-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Terminal value share of DCF enterprise value</t>
+        </is>
+      </c>
+      <c r="C14" s="17">
+        <f>DCF!C28</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
           <t>Expert panel median</t>
         </is>
       </c>
-      <c r="C13" s="8">
+      <c r="C15" s="8">
         <f>'Fundamental Valuation'!C26</f>
         <v/>
       </c>
-      <c r="G13" s="11">
-        <f>C13/$C$14-1</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="12" t="inlineStr">
+      <c r="G15" s="9">
+        <f>C15/$C$16-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="inlineStr">
         <is>
           <t>Market price (anchor)</t>
         </is>
       </c>
-      <c r="B14" s="15" t="n"/>
-      <c r="C14" s="17" t="n">
+      <c r="B16" s="13" t="n"/>
+      <c r="C16" s="18" t="n">
         <v>105.2</v>
       </c>
-      <c r="D14" s="15" t="n"/>
-      <c r="E14" s="15" t="n"/>
-      <c r="F14" s="15" t="n"/>
-      <c r="G14" s="15" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="D16" s="13" t="n"/>
+      <c r="E16" s="13" t="n"/>
+      <c r="F16" s="13" t="n"/>
+      <c r="G16" s="13" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>Key figure</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>Shares outstanding (mn)</t>
-        </is>
-      </c>
-      <c r="C17" s="18">
-        <f>Assumptions!$C$6</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>Market capitalisation (EGP mn)</t>
-        </is>
-      </c>
-      <c r="C18" s="18">
-        <f>$C$14*C17</f>
-        <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>Net bank debt, FY2025 (EGP mn)</t>
-        </is>
-      </c>
-      <c r="C19" s="18">
-        <f>'Balance Sheet'!D17</f>
+          <t>Shares outstanding (mn)</t>
+        </is>
+      </c>
+      <c r="C19" s="19">
+        <f>Assumptions!$C$6</f>
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>FY2025 revenue (EGP mn)</t>
-        </is>
-      </c>
-      <c r="C20" s="18">
-        <f>'Income Statement'!D5</f>
+          <t>Market capitalisation (EGP mn)</t>
+        </is>
+      </c>
+      <c r="C20" s="19">
+        <f>$C$16*C19</f>
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>FY2025 EBITDA (EGP mn)</t>
-        </is>
-      </c>
-      <c r="C21" s="18">
-        <f>'Income Statement'!D7</f>
+          <t>Net bank debt, FY2025 (EGP mn)</t>
+        </is>
+      </c>
+      <c r="C21" s="19">
+        <f>'Balance Sheet'!D17</f>
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>FY2025 attributable profit (EGP mn)</t>
-        </is>
-      </c>
-      <c r="C22" s="18">
-        <f>'Income Statement'!D17</f>
+          <t>FY2025 revenue (EGP mn)</t>
+        </is>
+      </c>
+      <c r="C22" s="19">
+        <f>'Income Statement'!D5</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>Cost of capital — explicit window</t>
-        </is>
-      </c>
-      <c r="C23" s="16">
-        <f>DCF!C46</f>
+          <t>FY2025 EBITDA (EGP mn)</t>
+        </is>
+      </c>
+      <c r="C23" s="19">
+        <f>'Income Statement'!D7</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Cost of capital — terminal</t>
-        </is>
-      </c>
-      <c r="C24" s="16">
-        <f>DCF!C53</f>
+          <t>FY2025 attributable profit (EGP mn)</t>
+        </is>
+      </c>
+      <c r="C24" s="19">
+        <f>'Income Statement'!D17</f>
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
+          <t>Cost of capital — explicit window</t>
+        </is>
+      </c>
+      <c r="C25" s="17">
+        <f>DCF!C46</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>Cost of capital — terminal</t>
+        </is>
+      </c>
+      <c r="C26" s="17">
+        <f>DCF!C53</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
           <t>Terminal growth</t>
         </is>
       </c>
-      <c r="C25" s="16">
+      <c r="C27" s="17">
         <f>DCF!C23</f>
         <v/>
       </c>
@@ -4402,7 +4427,7 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>19.945090316451</v>
+        <v>19.89441449632232</v>
       </c>
     </row>
     <row r="7">
@@ -4417,7 +4442,7 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>122.3348933382508</v>
+        <v>104.9620537972264</v>
       </c>
     </row>
     <row r="8">
@@ -4469,19 +4494,19 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="12" t="inlineStr">
-        <is>
-          <t>Weighted central</t>
-        </is>
-      </c>
-      <c r="B12" s="15" t="n"/>
-      <c r="C12" s="19">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>THE CENTRAL — the cash-flow lens itself, not an average of the four</t>
+        </is>
+      </c>
+      <c r="B12" s="13" t="n"/>
+      <c r="C12" s="20">
         <f>Summary!C9</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="20" t="inlineStr">
+      <c r="A14" s="15" t="inlineStr">
         <is>
           <t>THE CURRENCY-OF-DISCOUNTING QUESTION</t>
         </is>
@@ -4493,7 +4518,7 @@
           <t>Share of forecast revenue earned in hard currency</t>
         </is>
       </c>
-      <c r="C15" s="9" t="n">
+      <c r="C15" s="21" t="n">
         <v>0.5254856747391311</v>
       </c>
     </row>
@@ -4503,7 +4528,7 @@
           <t>Cost of capital applied in the primary model (explicit → terminal)</t>
         </is>
       </c>
-      <c r="C16" s="21" t="inlineStr">
+      <c r="C16" s="22" t="inlineStr">
         <is>
           <t>26.6% → 15.9%</t>
         </is>
@@ -4515,7 +4540,7 @@
           <t>Hard-currency cost of capital for the foreign leg</t>
         </is>
       </c>
-      <c r="C17" s="22">
+      <c r="C17" s="23">
         <f>(1-Assumptions!$C$59)*(Assumptions!$C$56+Assumptions!$C$33*Assumptions!$C$57)+Assumptions!$C$59*Assumptions!$C$58*(1-Assumptions!$C$7)</f>
         <v/>
       </c>
@@ -4527,7 +4552,7 @@
         </is>
       </c>
       <c r="C18" s="7" t="n">
-        <v>85.97488545126602</v>
+        <v>69.57809227740921</v>
       </c>
     </row>
     <row r="19">
@@ -4537,12 +4562,12 @@
         </is>
       </c>
       <c r="C19" s="8">
-        <f>Summary!C14</f>
+        <f>Summary!C16</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="20" t="inlineStr">
+      <c r="A21" s="15" t="inlineStr">
         <is>
           <t>EXPERT PANEL</t>
         </is>
@@ -4587,13 +4612,13 @@
         </is>
       </c>
       <c r="C23" s="7" t="n">
-        <v>146.6166527148279</v>
+        <v>148.4077409306208</v>
       </c>
       <c r="D23" s="7" t="n">
-        <v>107.5464809477679</v>
+        <v>108.8662301594048</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>185.6868244818879</v>
+        <v>187.9492517018369</v>
       </c>
     </row>
     <row r="24">
@@ -4608,13 +4633,13 @@
         </is>
       </c>
       <c r="C24" s="7" t="n">
-        <v>61.91445272087842</v>
+        <v>72.81006662300985</v>
       </c>
       <c r="D24" s="7" t="n">
-        <v>37.47247721279566</v>
+        <v>36.13831647623267</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>68.08877752143243</v>
+        <v>65.71584535779077</v>
       </c>
     </row>
     <row r="25">
@@ -4629,28 +4654,28 @@
         </is>
       </c>
       <c r="C25" s="7" t="n">
-        <v>53.24641887790025</v>
+        <v>54.45131359842825</v>
       </c>
       <c r="D25" s="7" t="n">
-        <v>46.17387104421569</v>
+        <v>46.88400987822836</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>85.97488545126602</v>
+        <v>69.57809227740921</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="12" t="inlineStr">
+      <c r="A26" s="10" t="inlineStr">
         <is>
           <t>Panel median</t>
         </is>
       </c>
-      <c r="B26" s="15" t="n"/>
-      <c r="C26" s="13">
+      <c r="B26" s="13" t="n"/>
+      <c r="C26" s="11">
         <f>MEDIAN(C23:C25)</f>
         <v/>
       </c>
-      <c r="D26" s="15" t="n"/>
-      <c r="E26" s="15" t="n"/>
+      <c r="D26" s="13" t="n"/>
+      <c r="E26" s="13" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4663,7 +4688,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H69"/>
+  <dimension ref="A1:H65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -4730,18 +4755,18 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>Anchors</t>
         </is>
       </c>
-      <c r="B4" s="15" t="n"/>
-      <c r="C4" s="15" t="n"/>
-      <c r="D4" s="15" t="n"/>
-      <c r="E4" s="15" t="n"/>
-      <c r="F4" s="15" t="n"/>
-      <c r="G4" s="15" t="n"/>
-      <c r="H4" s="15" t="n"/>
+      <c r="B4" s="13" t="n"/>
+      <c r="C4" s="13" t="n"/>
+      <c r="D4" s="13" t="n"/>
+      <c r="E4" s="13" t="n"/>
+      <c r="F4" s="13" t="n"/>
+      <c r="G4" s="13" t="n"/>
+      <c r="H4" s="13" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -4759,7 +4784,7 @@
           <t>Shares outstanding (mn)</t>
         </is>
       </c>
-      <c r="C6" s="23" t="n">
+      <c r="C6" s="24" t="n">
         <v>2140.777876</v>
       </c>
     </row>
@@ -4769,7 +4794,7 @@
           <t>Effective tax rate</t>
         </is>
       </c>
-      <c r="C7" s="9" t="n">
+      <c r="C7" s="21" t="n">
         <v>0.245</v>
       </c>
     </row>
@@ -4779,7 +4804,7 @@
           <t>Statutory corporate tax rate</t>
         </is>
       </c>
-      <c r="C8" s="9" t="n">
+      <c r="C8" s="21" t="n">
         <v>0.225</v>
       </c>
     </row>
@@ -4789,23 +4814,23 @@
           <t>FY2025 average USD/EGP</t>
         </is>
       </c>
-      <c r="C9" s="24" t="n">
+      <c r="C9" s="25" t="n">
         <v>49.5</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="12" t="inlineStr">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>Revenue drivers — the three disclosed segments</t>
         </is>
       </c>
-      <c r="B11" s="15" t="n"/>
-      <c r="C11" s="15" t="n"/>
-      <c r="D11" s="15" t="n"/>
-      <c r="E11" s="15" t="n"/>
-      <c r="F11" s="15" t="n"/>
-      <c r="G11" s="15" t="n"/>
-      <c r="H11" s="15" t="n"/>
+      <c r="B11" s="13" t="n"/>
+      <c r="C11" s="13" t="n"/>
+      <c r="D11" s="13" t="n"/>
+      <c r="E11" s="13" t="n"/>
+      <c r="F11" s="13" t="n"/>
+      <c r="G11" s="13" t="n"/>
+      <c r="H11" s="13" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -4813,19 +4838,19 @@
           <t>Copper (USD/tonne)</t>
         </is>
       </c>
-      <c r="B12" s="23" t="n">
+      <c r="B12" s="24" t="n">
         <v>13400</v>
       </c>
-      <c r="C12" s="23" t="n">
+      <c r="C12" s="24" t="n">
         <v>14000</v>
       </c>
-      <c r="D12" s="23" t="n">
+      <c r="D12" s="24" t="n">
         <v>14000</v>
       </c>
-      <c r="E12" s="23" t="n">
+      <c r="E12" s="24" t="n">
         <v>14000</v>
       </c>
-      <c r="F12" s="23" t="n">
+      <c r="F12" s="24" t="n">
         <v>14000</v>
       </c>
     </row>
@@ -4835,19 +4860,19 @@
           <t>USD/EGP path</t>
         </is>
       </c>
-      <c r="B13" s="24" t="n">
+      <c r="B13" s="25" t="n">
         <v>51</v>
       </c>
-      <c r="C13" s="24" t="n">
+      <c r="C13" s="25" t="n">
         <v>54</v>
       </c>
-      <c r="D13" s="24" t="n">
+      <c r="D13" s="25" t="n">
         <v>57.5</v>
       </c>
-      <c r="E13" s="24" t="n">
+      <c r="E13" s="25" t="n">
         <v>61</v>
       </c>
-      <c r="F13" s="24" t="n">
+      <c r="F13" s="25" t="n">
         <v>64.5</v>
       </c>
     </row>
@@ -4857,19 +4882,19 @@
           <t>Cables — real (volume) growth over copper x FX</t>
         </is>
       </c>
-      <c r="B14" s="9" t="n">
+      <c r="B14" s="21" t="n">
         <v>0.03</v>
       </c>
-      <c r="C14" s="9" t="n">
+      <c r="C14" s="21" t="n">
         <v>0.03</v>
       </c>
-      <c r="D14" s="9" t="n">
+      <c r="D14" s="21" t="n">
         <v>0.03</v>
       </c>
-      <c r="E14" s="9" t="n">
+      <c r="E14" s="21" t="n">
         <v>0.03</v>
       </c>
-      <c r="F14" s="9" t="n">
+      <c r="F14" s="21" t="n">
         <v>0.03</v>
       </c>
     </row>
@@ -4879,19 +4904,19 @@
           <t>Constructions and infrastructure — revenue growth</t>
         </is>
       </c>
-      <c r="B15" s="9" t="n">
+      <c r="B15" s="21" t="n">
         <v>0.18</v>
       </c>
-      <c r="C15" s="9" t="n">
+      <c r="C15" s="21" t="n">
         <v>0.14</v>
       </c>
-      <c r="D15" s="9" t="n">
+      <c r="D15" s="21" t="n">
         <v>0.11</v>
       </c>
-      <c r="E15" s="9" t="n">
+      <c r="E15" s="21" t="n">
         <v>0.09</v>
       </c>
-      <c r="F15" s="9" t="n">
+      <c r="F15" s="21" t="n">
         <v>0.08</v>
       </c>
     </row>
@@ -4901,35 +4926,35 @@
           <t>Electrical products and digital solutions — revenue growth</t>
         </is>
       </c>
-      <c r="B16" s="9" t="n">
+      <c r="B16" s="21" t="n">
         <v>0.2</v>
       </c>
-      <c r="C16" s="9" t="n">
+      <c r="C16" s="21" t="n">
         <v>0.16</v>
       </c>
-      <c r="D16" s="9" t="n">
+      <c r="D16" s="21" t="n">
         <v>0.13</v>
       </c>
-      <c r="E16" s="9" t="n">
+      <c r="E16" s="21" t="n">
         <v>0.11</v>
       </c>
-      <c r="F16" s="9" t="n">
+      <c r="F16" s="21" t="n">
         <v>0.1</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="12" t="inlineStr">
+      <c r="A18" s="10" t="inlineStr">
         <is>
           <t>Segment gross margins and corporate cost load</t>
         </is>
       </c>
-      <c r="B18" s="15" t="n"/>
-      <c r="C18" s="15" t="n"/>
-      <c r="D18" s="15" t="n"/>
-      <c r="E18" s="15" t="n"/>
-      <c r="F18" s="15" t="n"/>
-      <c r="G18" s="15" t="n"/>
-      <c r="H18" s="15" t="n"/>
+      <c r="B18" s="13" t="n"/>
+      <c r="C18" s="13" t="n"/>
+      <c r="D18" s="13" t="n"/>
+      <c r="E18" s="13" t="n"/>
+      <c r="F18" s="13" t="n"/>
+      <c r="G18" s="13" t="n"/>
+      <c r="H18" s="13" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -4937,20 +4962,20 @@
           <t>Cables — gross/segment margin</t>
         </is>
       </c>
-      <c r="B19" s="9" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="C19" s="9" t="n">
-        <v>0.145</v>
-      </c>
-      <c r="D19" s="9" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="E19" s="9" t="n">
-        <v>0.153</v>
-      </c>
-      <c r="F19" s="9" t="n">
-        <v>0.155</v>
+      <c r="B19" s="21" t="n">
+        <v>0.114341</v>
+      </c>
+      <c r="C19" s="21" t="n">
+        <v>0.114341</v>
+      </c>
+      <c r="D19" s="21" t="n">
+        <v>0.114341</v>
+      </c>
+      <c r="E19" s="21" t="n">
+        <v>0.114341</v>
+      </c>
+      <c r="F19" s="21" t="n">
+        <v>0.114341</v>
       </c>
     </row>
     <row r="20">
@@ -4959,20 +4984,20 @@
           <t>Constructions and infrastructure — segment margin</t>
         </is>
       </c>
-      <c r="B20" s="9" t="n">
-        <v>0.068</v>
-      </c>
-      <c r="C20" s="9" t="n">
-        <v>0.07199999999999999</v>
-      </c>
-      <c r="D20" s="9" t="n">
-        <v>0.076</v>
-      </c>
-      <c r="E20" s="9" t="n">
-        <v>0.079</v>
-      </c>
-      <c r="F20" s="9" t="n">
-        <v>0.082</v>
+      <c r="B20" s="21" t="n">
+        <v>0.08987100000000001</v>
+      </c>
+      <c r="C20" s="21" t="n">
+        <v>0.08987100000000001</v>
+      </c>
+      <c r="D20" s="21" t="n">
+        <v>0.08987100000000001</v>
+      </c>
+      <c r="E20" s="21" t="n">
+        <v>0.08987100000000001</v>
+      </c>
+      <c r="F20" s="21" t="n">
+        <v>0.08987100000000001</v>
       </c>
     </row>
     <row r="21">
@@ -4981,20 +5006,20 @@
           <t>Electrical products and digital solutions — segment margin</t>
         </is>
       </c>
-      <c r="B21" s="9" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="C21" s="9" t="n">
-        <v>0.222</v>
-      </c>
-      <c r="D21" s="9" t="n">
-        <v>0.224</v>
-      </c>
-      <c r="E21" s="9" t="n">
-        <v>0.226</v>
-      </c>
-      <c r="F21" s="9" t="n">
-        <v>0.228</v>
+      <c r="B21" s="21" t="n">
+        <v>0.236221</v>
+      </c>
+      <c r="C21" s="21" t="n">
+        <v>0.236221</v>
+      </c>
+      <c r="D21" s="21" t="n">
+        <v>0.236221</v>
+      </c>
+      <c r="E21" s="21" t="n">
+        <v>0.236221</v>
+      </c>
+      <c r="F21" s="21" t="n">
+        <v>0.236221</v>
       </c>
     </row>
     <row r="22">
@@ -5003,35 +5028,35 @@
           <t>Corporate cost load (% of revenue) — the bridge from segment profit to EBIT</t>
         </is>
       </c>
-      <c r="B22" s="9" t="n">
-        <v>0.0455</v>
-      </c>
-      <c r="C22" s="9" t="n">
-        <v>0.0465</v>
-      </c>
-      <c r="D22" s="9" t="n">
-        <v>0.0475</v>
-      </c>
-      <c r="E22" s="9" t="n">
-        <v>0.0475</v>
-      </c>
-      <c r="F22" s="9" t="n">
-        <v>0.0485</v>
+      <c r="B22" s="21" t="n">
+        <v>0.0307</v>
+      </c>
+      <c r="C22" s="21" t="n">
+        <v>0.0307</v>
+      </c>
+      <c r="D22" s="21" t="n">
+        <v>0.0307</v>
+      </c>
+      <c r="E22" s="21" t="n">
+        <v>0.0307</v>
+      </c>
+      <c r="F22" s="21" t="n">
+        <v>0.0307</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="12" t="inlineStr">
+      <c r="A24" s="10" t="inlineStr">
         <is>
           <t>Capital intensity</t>
         </is>
       </c>
-      <c r="B24" s="15" t="n"/>
-      <c r="C24" s="15" t="n"/>
-      <c r="D24" s="15" t="n"/>
-      <c r="E24" s="15" t="n"/>
-      <c r="F24" s="15" t="n"/>
-      <c r="G24" s="15" t="n"/>
-      <c r="H24" s="15" t="n"/>
+      <c r="B24" s="13" t="n"/>
+      <c r="C24" s="13" t="n"/>
+      <c r="D24" s="13" t="n"/>
+      <c r="E24" s="13" t="n"/>
+      <c r="F24" s="13" t="n"/>
+      <c r="G24" s="13" t="n"/>
+      <c r="H24" s="13" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
@@ -5039,7 +5064,7 @@
           <t>Working capital / revenue</t>
         </is>
       </c>
-      <c r="C25" s="9" t="n">
+      <c r="C25" s="21" t="n">
         <v>0.199</v>
       </c>
     </row>
@@ -5049,19 +5074,19 @@
           <t>Capital expenditure / revenue</t>
         </is>
       </c>
-      <c r="B26" s="9" t="n">
+      <c r="B26" s="21" t="n">
         <v>0.044</v>
       </c>
-      <c r="C26" s="9" t="n">
+      <c r="C26" s="21" t="n">
         <v>0.04</v>
       </c>
-      <c r="D26" s="9" t="n">
+      <c r="D26" s="21" t="n">
         <v>0.036</v>
       </c>
-      <c r="E26" s="9" t="n">
+      <c r="E26" s="21" t="n">
         <v>0.033</v>
       </c>
-      <c r="F26" s="9" t="n">
+      <c r="F26" s="21" t="n">
         <v>0.031</v>
       </c>
     </row>
@@ -5071,23 +5096,23 @@
           <t>Depreciation and amortisation / revenue</t>
         </is>
       </c>
-      <c r="C27" s="9" t="n">
+      <c r="C27" s="21" t="n">
         <v>0.0125</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="12" t="inlineStr">
+      <c r="A29" s="10" t="inlineStr">
         <is>
           <t>Cost of capital</t>
         </is>
       </c>
-      <c r="B29" s="15" t="n"/>
-      <c r="C29" s="15" t="n"/>
-      <c r="D29" s="15" t="n"/>
-      <c r="E29" s="15" t="n"/>
-      <c r="F29" s="15" t="n"/>
-      <c r="G29" s="15" t="n"/>
-      <c r="H29" s="15" t="n"/>
+      <c r="B29" s="13" t="n"/>
+      <c r="C29" s="13" t="n"/>
+      <c r="D29" s="13" t="n"/>
+      <c r="E29" s="13" t="n"/>
+      <c r="F29" s="13" t="n"/>
+      <c r="G29" s="13" t="n"/>
+      <c r="H29" s="13" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
@@ -5095,7 +5120,7 @@
           <t>Risk-free rate (10-year local currency)</t>
         </is>
       </c>
-      <c r="C30" s="9" t="n">
+      <c r="C30" s="21" t="n">
         <v>0.2231</v>
       </c>
     </row>
@@ -5105,7 +5130,7 @@
           <t>Sovereign default spread (netted out)</t>
         </is>
       </c>
-      <c r="C31" s="9" t="n">
+      <c r="C31" s="21" t="n">
         <v>0.034</v>
       </c>
     </row>
@@ -5115,7 +5140,7 @@
           <t>Equity risk premium</t>
         </is>
       </c>
-      <c r="C32" s="9" t="n">
+      <c r="C32" s="21" t="n">
         <v>0.0941</v>
       </c>
     </row>
@@ -5125,7 +5150,7 @@
           <t>Beta</t>
         </is>
       </c>
-      <c r="C33" s="25" t="n">
+      <c r="C33" s="26" t="n">
         <v>1.009</v>
       </c>
     </row>
@@ -5135,7 +5160,7 @@
           <t>Cost of debt, blended</t>
         </is>
       </c>
-      <c r="C34" s="9" t="n">
+      <c r="C34" s="21" t="n">
         <v>0.095</v>
       </c>
     </row>
@@ -5145,19 +5170,19 @@
           <t>Cost of debt path</t>
         </is>
       </c>
-      <c r="B35" s="9" t="n">
+      <c r="B35" s="21" t="n">
         <v>0.095</v>
       </c>
-      <c r="C35" s="9" t="n">
+      <c r="C35" s="21" t="n">
         <v>0.089</v>
       </c>
-      <c r="D35" s="9" t="n">
+      <c r="D35" s="21" t="n">
         <v>0.08400000000000001</v>
       </c>
-      <c r="E35" s="9" t="n">
+      <c r="E35" s="21" t="n">
         <v>0.08</v>
       </c>
-      <c r="F35" s="9" t="n">
+      <c r="F35" s="21" t="n">
         <v>0.077</v>
       </c>
     </row>
@@ -5167,7 +5192,7 @@
           <t>Terminal risk-free rate</t>
         </is>
       </c>
-      <c r="C36" s="9" t="n">
+      <c r="C36" s="21" t="n">
         <v>0.105</v>
       </c>
     </row>
@@ -5177,7 +5202,7 @@
           <t>Terminal equity risk premium</t>
         </is>
       </c>
-      <c r="C37" s="9" t="n">
+      <c r="C37" s="21" t="n">
         <v>0.07000000000000001</v>
       </c>
     </row>
@@ -5187,7 +5212,7 @@
           <t>Terminal cost of debt</t>
         </is>
       </c>
-      <c r="C38" s="9" t="n">
+      <c r="C38" s="21" t="n">
         <v>0.0888</v>
       </c>
     </row>
@@ -5197,7 +5222,7 @@
           <t>Terminal debt weight</t>
         </is>
       </c>
-      <c r="C39" s="9" t="n">
+      <c r="C39" s="21" t="n">
         <v>0.15</v>
       </c>
     </row>
@@ -5207,23 +5232,23 @@
           <t>Terminal growth</t>
         </is>
       </c>
-      <c r="C40" s="9" t="n">
-        <v>0.05</v>
+      <c r="C40" s="21" t="n">
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="12" t="inlineStr">
+      <c r="A42" s="10" t="inlineStr">
         <is>
           <t>Balance-sheet and bridge anchors</t>
         </is>
       </c>
-      <c r="B42" s="15" t="n"/>
-      <c r="C42" s="15" t="n"/>
-      <c r="D42" s="15" t="n"/>
-      <c r="E42" s="15" t="n"/>
-      <c r="F42" s="15" t="n"/>
-      <c r="G42" s="15" t="n"/>
-      <c r="H42" s="15" t="n"/>
+      <c r="B42" s="13" t="n"/>
+      <c r="C42" s="13" t="n"/>
+      <c r="D42" s="13" t="n"/>
+      <c r="E42" s="13" t="n"/>
+      <c r="F42" s="13" t="n"/>
+      <c r="G42" s="13" t="n"/>
+      <c r="H42" s="13" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
@@ -5231,7 +5256,7 @@
           <t>Net bank debt at FY2025 (EGP mn, disclosed)</t>
         </is>
       </c>
-      <c r="C43" s="23" t="n">
+      <c r="C43" s="24" t="n">
         <v>20560.003173</v>
       </c>
     </row>
@@ -5241,7 +5266,7 @@
           <t>Equity-accounted investees at carrying value (EGP mn)</t>
         </is>
       </c>
-      <c r="C44" s="23" t="n">
+      <c r="C44" s="24" t="n">
         <v>6757.650507</v>
       </c>
     </row>
@@ -5251,7 +5276,7 @@
           <t>Intangible assets and goodwill (EGP mn)</t>
         </is>
       </c>
-      <c r="C45" s="23" t="n">
+      <c r="C45" s="24" t="n">
         <v>1748.816945</v>
       </c>
     </row>
@@ -5261,7 +5286,7 @@
           <t>FY2025 profit after tax (EGP mn, disclosed)</t>
         </is>
       </c>
-      <c r="C46" s="23" t="n">
+      <c r="C46" s="24" t="n">
         <v>19186.550057</v>
       </c>
     </row>
@@ -5271,7 +5296,7 @@
           <t>FY2025 profit after minority interests (EGP mn, disclosed)</t>
         </is>
       </c>
-      <c r="C47" s="23" t="n">
+      <c r="C47" s="24" t="n">
         <v>17330.24499</v>
       </c>
     </row>
@@ -5301,7 +5326,7 @@
           <t>Forecast dividend payout ratio (struck at the actual FY2025 rate)</t>
         </is>
       </c>
-      <c r="C50" s="9" t="n">
+      <c r="C50" s="21" t="n">
         <v>0.25</v>
       </c>
     </row>
@@ -5311,7 +5336,7 @@
           <t>Growth in the share of equity-accounted investees</t>
         </is>
       </c>
-      <c r="C51" s="9" t="n">
+      <c r="C51" s="21" t="n">
         <v>0.08</v>
       </c>
     </row>
@@ -5321,7 +5346,7 @@
           <t>Yield assumed on surplus cash (blend of EGP deposit and hard-currency rates)</t>
         </is>
       </c>
-      <c r="C52" s="9" t="n">
+      <c r="C52" s="21" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -5331,23 +5356,23 @@
           <t>Days from the 31-Dec-2025 valuation date to the 5-Aug-2026 anchor</t>
         </is>
       </c>
-      <c r="C53" s="23" t="n">
+      <c r="C53" s="24" t="n">
         <v>217</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="12" t="inlineStr">
+      <c r="A55" s="10" t="inlineStr">
         <is>
           <t>Currency-of-discounting alternative</t>
         </is>
       </c>
-      <c r="B55" s="15" t="n"/>
-      <c r="C55" s="15" t="n"/>
-      <c r="D55" s="15" t="n"/>
-      <c r="E55" s="15" t="n"/>
-      <c r="F55" s="15" t="n"/>
-      <c r="G55" s="15" t="n"/>
-      <c r="H55" s="15" t="n"/>
+      <c r="B55" s="13" t="n"/>
+      <c r="C55" s="13" t="n"/>
+      <c r="D55" s="13" t="n"/>
+      <c r="E55" s="13" t="n"/>
+      <c r="F55" s="13" t="n"/>
+      <c r="G55" s="13" t="n"/>
+      <c r="H55" s="13" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
@@ -5355,7 +5380,7 @@
           <t>US dollar risk-free rate</t>
         </is>
       </c>
-      <c r="C56" s="9" t="n">
+      <c r="C56" s="21" t="n">
         <v>0.043</v>
       </c>
     </row>
@@ -5365,7 +5390,7 @@
           <t>Hard-currency-leg equity risk premium</t>
         </is>
       </c>
-      <c r="C57" s="9" t="n">
+      <c r="C57" s="21" t="n">
         <v>0.075</v>
       </c>
     </row>
@@ -5375,7 +5400,7 @@
           <t>US dollar cost of debt</t>
         </is>
       </c>
-      <c r="C58" s="9" t="n">
+      <c r="C58" s="21" t="n">
         <v>0.065</v>
       </c>
     </row>
@@ -5385,7 +5410,7 @@
           <t>Debt weight, USD leg</t>
         </is>
       </c>
-      <c r="C59" s="9" t="n">
+      <c r="C59" s="21" t="n">
         <v>0.25</v>
       </c>
     </row>
@@ -5395,23 +5420,23 @@
           <t>Terminal growth of the USD leg</t>
         </is>
       </c>
-      <c r="C60" s="9" t="n">
+      <c r="C60" s="21" t="n">
         <v>0.035</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="12" t="inlineStr">
+      <c r="A62" s="10" t="inlineStr">
         <is>
           <t>Lens inputs</t>
         </is>
       </c>
-      <c r="B62" s="15" t="n"/>
-      <c r="C62" s="15" t="n"/>
-      <c r="D62" s="15" t="n"/>
-      <c r="E62" s="15" t="n"/>
-      <c r="F62" s="15" t="n"/>
-      <c r="G62" s="15" t="n"/>
-      <c r="H62" s="15" t="n"/>
+      <c r="B62" s="13" t="n"/>
+      <c r="C62" s="13" t="n"/>
+      <c r="D62" s="13" t="n"/>
+      <c r="E62" s="13" t="n"/>
+      <c r="F62" s="13" t="n"/>
+      <c r="G62" s="13" t="n"/>
+      <c r="H62" s="13" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="6" t="inlineStr">
@@ -5419,7 +5444,7 @@
           <t>Justified EV/EBITDA</t>
         </is>
       </c>
-      <c r="C63" s="26" t="n">
+      <c r="C63" s="27" t="n">
         <v>6.5</v>
       </c>
     </row>
@@ -5429,7 +5454,7 @@
           <t>Justified price/earnings</t>
         </is>
       </c>
-      <c r="C64" s="26" t="n">
+      <c r="C64" s="27" t="n">
         <v>9</v>
       </c>
     </row>
@@ -5439,48 +5464,8 @@
           <t>Sustainable return on equity</t>
         </is>
       </c>
-      <c r="C65" s="9" t="n">
+      <c r="C65" s="21" t="n">
         <v>0.235</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="6" t="inlineStr">
-        <is>
-          <t>Weight — discounted cash flow</t>
-        </is>
-      </c>
-      <c r="C66" s="9" t="n">
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="6" t="inlineStr">
-        <is>
-          <t>Weight — relative</t>
-        </is>
-      </c>
-      <c r="C67" s="9" t="n">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="6" t="inlineStr">
-        <is>
-          <t>Weight — normalised</t>
-        </is>
-      </c>
-      <c r="C68" s="9" t="n">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="6" t="inlineStr">
-        <is>
-          <t>Weight — book</t>
-        </is>
-      </c>
-      <c r="C69" s="9" t="n">
-        <v>0.15</v>
       </c>
     </row>
   </sheetData>
@@ -5538,11 +5523,11 @@
           <t>Present value of the five forecast years</t>
         </is>
       </c>
-      <c r="C5" s="18">
+      <c r="C5" s="19">
         <f>DCF!C26</f>
         <v/>
       </c>
-      <c r="D5" s="10">
+      <c r="D5" s="16">
         <f>C5/Assumptions!$C$6</f>
         <v/>
       </c>
@@ -5553,11 +5538,11 @@
           <t>Present value of the terminal value</t>
         </is>
       </c>
-      <c r="C6" s="18">
+      <c r="C6" s="19">
         <f>DCF!C27</f>
         <v/>
       </c>
-      <c r="D6" s="10">
+      <c r="D6" s="16">
         <f>C6/Assumptions!$C$6</f>
         <v/>
       </c>
@@ -5568,11 +5553,11 @@
           <t>Enterprise value</t>
         </is>
       </c>
-      <c r="C7" s="27">
+      <c r="C7" s="28">
         <f>C5+C6</f>
         <v/>
       </c>
-      <c r="D7" s="28">
+      <c r="D7" s="29">
         <f>C7/Assumptions!$C$6</f>
         <v/>
       </c>
@@ -5583,11 +5568,11 @@
           <t>Less net bank debt</t>
         </is>
       </c>
-      <c r="C8" s="18">
+      <c r="C8" s="19">
         <f>-Assumptions!$C$43</f>
         <v/>
       </c>
-      <c r="D8" s="10">
+      <c r="D8" s="16">
         <f>C8/Assumptions!$C$6</f>
         <v/>
       </c>
@@ -5598,11 +5583,11 @@
           <t>Plus equity-accounted investees at carrying value</t>
         </is>
       </c>
-      <c r="C9" s="18">
+      <c r="C9" s="19">
         <f>Assumptions!$C$44</f>
         <v/>
       </c>
-      <c r="D9" s="10">
+      <c r="D9" s="16">
         <f>C9/Assumptions!$C$6</f>
         <v/>
       </c>
@@ -5613,11 +5598,11 @@
           <t>Equity before minority interests</t>
         </is>
       </c>
-      <c r="C10" s="29">
+      <c r="C10" s="30">
         <f>C7+C8+C9</f>
         <v/>
       </c>
-      <c r="D10" s="10">
+      <c r="D10" s="16">
         <f>C10/Assumptions!$C$6</f>
         <v/>
       </c>
@@ -5628,27 +5613,27 @@
           <t>Less minority interests at their share of group profit</t>
         </is>
       </c>
-      <c r="C11" s="29">
+      <c r="C11" s="30">
         <f>-C10*$C$15</f>
         <v/>
       </c>
-      <c r="D11" s="10">
+      <c r="D11" s="16">
         <f>C11/Assumptions!$C$6</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="13" t="inlineStr">
         <is>
           <t>Equity attributable to shareholders</t>
         </is>
       </c>
-      <c r="B12" s="15" t="n"/>
-      <c r="C12" s="30">
+      <c r="B12" s="13" t="n"/>
+      <c r="C12" s="31">
         <f>C10+C11</f>
         <v/>
       </c>
-      <c r="D12" s="31">
+      <c r="D12" s="32">
         <f>C12/Assumptions!$C$6</f>
         <v/>
       </c>
@@ -5659,7 +5644,7 @@
           <t>Terminal value as a share of enterprise value</t>
         </is>
       </c>
-      <c r="C14" s="16">
+      <c r="C14" s="17">
         <f>DCF!C28</f>
         <v/>
       </c>
@@ -5670,7 +5655,7 @@
           <t>Minority share of group profit</t>
         </is>
       </c>
-      <c r="C15" s="11">
+      <c r="C15" s="9">
         <f>(Assumptions!$C$46-Assumptions!$C$47)/Assumptions!$C$46</f>
         <v/>
       </c>
@@ -5775,29 +5760,29 @@
           <t>Cables and its accessories</t>
         </is>
       </c>
-      <c r="B5" s="23" t="n">
+      <c r="B5" s="24" t="n">
         <v>155792.929738</v>
       </c>
-      <c r="C5" s="11">
+      <c r="C5" s="9">
         <f>B5/$B$8</f>
         <v/>
       </c>
-      <c r="D5" s="9" t="n">
+      <c r="D5" s="21" t="n">
         <v>0.134899552356732</v>
       </c>
-      <c r="E5" s="23" t="n">
+      <c r="E5" s="24" t="n">
         <v>221541.3228857327</v>
       </c>
-      <c r="F5" s="23" t="n">
+      <c r="F5" s="24" t="n">
         <v>252428.7347156312</v>
       </c>
-      <c r="G5" s="23" t="n">
+      <c r="G5" s="24" t="n">
         <v>276853.5521024677</v>
       </c>
-      <c r="H5" s="23" t="n">
+      <c r="H5" s="24" t="n">
         <v>302516.6726712704</v>
       </c>
-      <c r="I5" s="23" t="n">
+      <c r="I5" s="24" t="n">
         <v>329470.412277309</v>
       </c>
     </row>
@@ -5807,29 +5792,29 @@
           <t>Constructions and infrastructure</t>
         </is>
       </c>
-      <c r="B6" s="23" t="n">
+      <c r="B6" s="24" t="n">
         <v>90958.55022799999</v>
       </c>
-      <c r="C6" s="11">
+      <c r="C6" s="9">
         <f>B6/$B$8</f>
         <v/>
       </c>
-      <c r="D6" s="9" t="n">
+      <c r="D6" s="21" t="n">
         <v>0.06452269254829619</v>
       </c>
-      <c r="E6" s="23" t="n">
+      <c r="E6" s="24" t="n">
         <v>107331.08926904</v>
       </c>
-      <c r="F6" s="23" t="n">
+      <c r="F6" s="24" t="n">
         <v>122357.4417667056</v>
       </c>
-      <c r="G6" s="23" t="n">
+      <c r="G6" s="24" t="n">
         <v>135816.7603610432</v>
       </c>
-      <c r="H6" s="23" t="n">
+      <c r="H6" s="24" t="n">
         <v>148040.2687935371</v>
       </c>
-      <c r="I6" s="23" t="n">
+      <c r="I6" s="24" t="n">
         <v>159883.4902970201</v>
       </c>
     </row>
@@ -5839,39 +5824,39 @@
           <t>Electrical products and digital solutions</t>
         </is>
       </c>
-      <c r="B7" s="23" t="n">
+      <c r="B7" s="24" t="n">
         <v>34297.601753</v>
       </c>
-      <c r="C7" s="11">
+      <c r="C7" s="9">
         <f>B7/$B$8</f>
         <v/>
       </c>
-      <c r="D7" s="9" t="n">
+      <c r="D7" s="21" t="n">
         <v>0.2217300370961013</v>
       </c>
-      <c r="E7" s="23" t="n">
+      <c r="E7" s="24" t="n">
         <v>41157.1221036</v>
       </c>
-      <c r="F7" s="23" t="n">
+      <c r="F7" s="24" t="n">
         <v>47742.261640176</v>
       </c>
-      <c r="G7" s="23" t="n">
+      <c r="G7" s="24" t="n">
         <v>53948.75565339887</v>
       </c>
-      <c r="H7" s="23" t="n">
+      <c r="H7" s="24" t="n">
         <v>59883.11877527275</v>
       </c>
-      <c r="I7" s="23" t="n">
+      <c r="I7" s="24" t="n">
         <v>65871.43065280003</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>Total revenue</t>
         </is>
       </c>
-      <c r="B8" s="32">
+      <c r="B8" s="33">
         <f>SUM(B5:B7)</f>
         <v/>
       </c>
@@ -5879,24 +5864,24 @@
         <f>SUM(C5:C7)</f>
         <v/>
       </c>
-      <c r="D8" s="15" t="n"/>
-      <c r="E8" s="32">
+      <c r="D8" s="13" t="n"/>
+      <c r="E8" s="33">
         <f>SUM(E5:E7)</f>
         <v/>
       </c>
-      <c r="F8" s="32">
+      <c r="F8" s="33">
         <f>SUM(F5:F7)</f>
         <v/>
       </c>
-      <c r="G8" s="32">
+      <c r="G8" s="33">
         <f>SUM(G5:G7)</f>
         <v/>
       </c>
-      <c r="H8" s="32">
+      <c r="H8" s="33">
         <f>SUM(H5:H7)</f>
         <v/>
       </c>
-      <c r="I8" s="32">
+      <c r="I8" s="33">
         <f>SUM(I5:I7)</f>
         <v/>
       </c>
@@ -5939,20 +5924,20 @@
           <t>Cables and its accessories</t>
         </is>
       </c>
-      <c r="B11" s="23" t="n">
-        <v>31015.78520400258</v>
-      </c>
-      <c r="C11" s="23" t="n">
-        <v>36602.16653376652</v>
-      </c>
-      <c r="D11" s="23" t="n">
-        <v>41528.03281537016</v>
-      </c>
-      <c r="E11" s="23" t="n">
-        <v>46285.05091870438</v>
-      </c>
-      <c r="F11" s="23" t="n">
-        <v>51067.91390298289</v>
+      <c r="B11" s="24" t="n">
+        <v>25331.25640007756</v>
+      </c>
+      <c r="C11" s="24" t="n">
+        <v>28862.95395611998</v>
+      </c>
+      <c r="D11" s="24" t="n">
+        <v>31655.71200094826</v>
+      </c>
+      <c r="E11" s="24" t="n">
+        <v>34590.05886990573</v>
+      </c>
+      <c r="F11" s="24" t="n">
+        <v>37671.97641019979</v>
       </c>
     </row>
     <row r="12">
@@ -5961,20 +5946,20 @@
           <t>Constructions and infrastructure</t>
         </is>
       </c>
-      <c r="B12" s="23" t="n">
-        <v>7298.51407029472</v>
-      </c>
-      <c r="C12" s="23" t="n">
-        <v>8809.735807202804</v>
-      </c>
-      <c r="D12" s="23" t="n">
-        <v>10322.07378743929</v>
-      </c>
-      <c r="E12" s="23" t="n">
-        <v>11695.18123468943</v>
-      </c>
-      <c r="F12" s="23" t="n">
-        <v>13110.44620435565</v>
+      <c r="B12" s="24" t="n">
+        <v>9645.952323697893</v>
+      </c>
+      <c r="C12" s="24" t="n">
+        <v>10996.3856490156</v>
+      </c>
+      <c r="D12" s="24" t="n">
+        <v>12205.98807040732</v>
+      </c>
+      <c r="E12" s="24" t="n">
+        <v>13304.52699674398</v>
+      </c>
+      <c r="F12" s="24" t="n">
+        <v>14368.8891564835</v>
       </c>
     </row>
     <row r="13">
@@ -5983,45 +5968,45 @@
           <t>Electrical products and digital solutions</t>
         </is>
       </c>
-      <c r="B13" s="23" t="n">
-        <v>9054.566862792</v>
-      </c>
-      <c r="C13" s="23" t="n">
-        <v>10598.78208411907</v>
-      </c>
-      <c r="D13" s="23" t="n">
-        <v>12084.52126636135</v>
-      </c>
-      <c r="E13" s="23" t="n">
-        <v>13533.58484321164</v>
-      </c>
-      <c r="F13" s="23" t="n">
-        <v>15018.68618883841</v>
+      <c r="B13" s="24" t="n">
+        <v>9722.176540434495</v>
+      </c>
+      <c r="C13" s="24" t="n">
+        <v>11277.72478690401</v>
+      </c>
+      <c r="D13" s="24" t="n">
+        <v>12743.82900920153</v>
+      </c>
+      <c r="E13" s="24" t="n">
+        <v>14145.6502002137</v>
+      </c>
+      <c r="F13" s="24" t="n">
+        <v>15560.21522023508</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="12" t="inlineStr">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t>Group segment profit</t>
         </is>
       </c>
-      <c r="B14" s="32">
+      <c r="B14" s="33">
         <f>SUM(B11:B13)</f>
         <v/>
       </c>
-      <c r="C14" s="32">
+      <c r="C14" s="33">
         <f>SUM(C11:C13)</f>
         <v/>
       </c>
-      <c r="D14" s="32">
+      <c r="D14" s="33">
         <f>SUM(D11:D13)</f>
         <v/>
       </c>
-      <c r="E14" s="32">
+      <c r="E14" s="33">
         <f>SUM(E11:E13)</f>
         <v/>
       </c>
-      <c r="F14" s="32">
+      <c r="F14" s="33">
         <f>SUM(F11:F13)</f>
         <v/>
       </c>
@@ -6032,23 +6017,23 @@
           <t>Group segment-profit margin</t>
         </is>
       </c>
-      <c r="B15" s="11">
+      <c r="B15" s="9">
         <f>B14/E$8</f>
         <v/>
       </c>
-      <c r="C15" s="11">
+      <c r="C15" s="9">
         <f>C14/F$8</f>
         <v/>
       </c>
-      <c r="D15" s="11">
+      <c r="D15" s="9">
         <f>D14/G$8</f>
         <v/>
       </c>
-      <c r="E15" s="11">
+      <c r="E15" s="9">
         <f>E14/H$8</f>
         <v/>
       </c>
-      <c r="F15" s="11">
+      <c r="F15" s="9">
         <f>F14/I$8</f>
         <v/>
       </c>
@@ -6091,23 +6076,23 @@
           <t>Cables and its accessories</t>
         </is>
       </c>
-      <c r="B18" s="29">
+      <c r="B18" s="30">
         <f>B11-Assumptions!$B$22*E5</f>
         <v/>
       </c>
-      <c r="C18" s="29">
+      <c r="C18" s="30">
         <f>C11-Assumptions!$C$22*F5</f>
         <v/>
       </c>
-      <c r="D18" s="29">
+      <c r="D18" s="30">
         <f>D11-Assumptions!$D$22*G5</f>
         <v/>
       </c>
-      <c r="E18" s="29">
+      <c r="E18" s="30">
         <f>E11-Assumptions!$E$22*H5</f>
         <v/>
       </c>
-      <c r="F18" s="29">
+      <c r="F18" s="30">
         <f>F11-Assumptions!$F$22*I5</f>
         <v/>
       </c>
@@ -6118,23 +6103,23 @@
           <t>Constructions and infrastructure</t>
         </is>
       </c>
-      <c r="B19" s="29">
+      <c r="B19" s="30">
         <f>B12-Assumptions!$B$22*E6</f>
         <v/>
       </c>
-      <c r="C19" s="29">
+      <c r="C19" s="30">
         <f>C12-Assumptions!$C$22*F6</f>
         <v/>
       </c>
-      <c r="D19" s="29">
+      <c r="D19" s="30">
         <f>D12-Assumptions!$D$22*G6</f>
         <v/>
       </c>
-      <c r="E19" s="29">
+      <c r="E19" s="30">
         <f>E12-Assumptions!$E$22*H6</f>
         <v/>
       </c>
-      <c r="F19" s="29">
+      <c r="F19" s="30">
         <f>F12-Assumptions!$F$22*I6</f>
         <v/>
       </c>
@@ -6145,50 +6130,50 @@
           <t>Electrical products and digital solutions</t>
         </is>
       </c>
-      <c r="B20" s="29">
+      <c r="B20" s="30">
         <f>B13-Assumptions!$B$22*E7</f>
         <v/>
       </c>
-      <c r="C20" s="29">
+      <c r="C20" s="30">
         <f>C13-Assumptions!$C$22*F7</f>
         <v/>
       </c>
-      <c r="D20" s="29">
+      <c r="D20" s="30">
         <f>D13-Assumptions!$D$22*G7</f>
         <v/>
       </c>
-      <c r="E20" s="29">
+      <c r="E20" s="30">
         <f>E13-Assumptions!$E$22*H7</f>
         <v/>
       </c>
-      <c r="F20" s="29">
+      <c r="F20" s="30">
         <f>F13-Assumptions!$F$22*I7</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="12" t="inlineStr">
+      <c r="A21" s="10" t="inlineStr">
         <is>
           <t>Group EBIT</t>
         </is>
       </c>
-      <c r="B21" s="32">
+      <c r="B21" s="33">
         <f>SUM(B18:B20)</f>
         <v/>
       </c>
-      <c r="C21" s="32">
+      <c r="C21" s="33">
         <f>SUM(C18:C20)</f>
         <v/>
       </c>
-      <c r="D21" s="32">
+      <c r="D21" s="33">
         <f>SUM(D18:D20)</f>
         <v/>
       </c>
-      <c r="E21" s="32">
+      <c r="E21" s="33">
         <f>SUM(E18:E20)</f>
         <v/>
       </c>
-      <c r="F21" s="32">
+      <c r="F21" s="33">
         <f>SUM(F18:F20)</f>
         <v/>
       </c>
@@ -6199,50 +6184,50 @@
           <t>Add back depreciation and amortisation</t>
         </is>
       </c>
-      <c r="B22" s="29">
+      <c r="B22" s="30">
         <f>Assumptions!$C$27*E8</f>
         <v/>
       </c>
-      <c r="C22" s="29">
+      <c r="C22" s="30">
         <f>Assumptions!$C$27*F8</f>
         <v/>
       </c>
-      <c r="D22" s="29">
+      <c r="D22" s="30">
         <f>Assumptions!$C$27*G8</f>
         <v/>
       </c>
-      <c r="E22" s="29">
+      <c r="E22" s="30">
         <f>Assumptions!$C$27*H8</f>
         <v/>
       </c>
-      <c r="F22" s="29">
+      <c r="F22" s="30">
         <f>Assumptions!$C$27*I8</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="12" t="inlineStr">
+      <c r="A23" s="10" t="inlineStr">
         <is>
           <t>Group EBITDA</t>
         </is>
       </c>
-      <c r="B23" s="32">
+      <c r="B23" s="33">
         <f>B21+B22</f>
         <v/>
       </c>
-      <c r="C23" s="32">
+      <c r="C23" s="33">
         <f>C21+C22</f>
         <v/>
       </c>
-      <c r="D23" s="32">
+      <c r="D23" s="33">
         <f>D21+D22</f>
         <v/>
       </c>
-      <c r="E23" s="32">
+      <c r="E23" s="33">
         <f>E21+E22</f>
         <v/>
       </c>
-      <c r="F23" s="32">
+      <c r="F23" s="33">
         <f>F21+F22</f>
         <v/>
       </c>
@@ -6253,23 +6238,23 @@
           <t>Group EBITDA margin</t>
         </is>
       </c>
-      <c r="B24" s="11">
+      <c r="B24" s="9">
         <f>B23/E$8</f>
         <v/>
       </c>
-      <c r="C24" s="11">
+      <c r="C24" s="9">
         <f>C23/F$8</f>
         <v/>
       </c>
-      <c r="D24" s="11">
+      <c r="D24" s="9">
         <f>D23/G$8</f>
         <v/>
       </c>
-      <c r="E24" s="11">
+      <c r="E24" s="9">
         <f>E23/H$8</f>
         <v/>
       </c>
-      <c r="F24" s="11">
+      <c r="F24" s="9">
         <f>F23/I$8</f>
         <v/>
       </c>
@@ -6331,7 +6316,7 @@
           <t>FY2027E EBITDA (EGP mn)</t>
         </is>
       </c>
-      <c r="C5" s="18">
+      <c r="C5" s="19">
         <f>DCF!C6</f>
         <v/>
       </c>
@@ -6342,7 +6327,7 @@
           <t>Justified enterprise value / EBITDA</t>
         </is>
       </c>
-      <c r="C6" s="33">
+      <c r="C6" s="34">
         <f>Assumptions!$C$63</f>
         <v/>
       </c>
@@ -6353,7 +6338,7 @@
           <t>Implied enterprise value AS AT end-FY2027 (EGP mn)</t>
         </is>
       </c>
-      <c r="C7" s="29">
+      <c r="C7" s="30">
         <f>C5*C6</f>
         <v/>
       </c>
@@ -6364,7 +6349,7 @@
           <t>Discount factor back to the valuation date (year-2)</t>
         </is>
       </c>
-      <c r="C8" s="34">
+      <c r="C8" s="35">
         <f>DCF!C16</f>
         <v/>
       </c>
@@ -6375,7 +6360,7 @@
           <t>Plus present value of the interim FY26-27 free cash flows (EGP mn)</t>
         </is>
       </c>
-      <c r="C9" s="18">
+      <c r="C9" s="19">
         <f>DCF!B17+DCF!C17</f>
         <v/>
       </c>
@@ -6386,19 +6371,19 @@
           <t>Implied enterprise value at 31-Dec-2025 (EGP mn)</t>
         </is>
       </c>
-      <c r="C10" s="29">
+      <c r="C10" s="30">
         <f>C7*C8+C9</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="13" t="inlineStr">
         <is>
           <t>Implied value per share, rolled to the anchor (EGP)</t>
         </is>
       </c>
-      <c r="B11" s="15" t="n"/>
-      <c r="C11" s="31">
+      <c r="B11" s="13" t="n"/>
+      <c r="C11" s="32">
         <f>((C10-Assumptions!$C$43+Assumptions!$C$44)*(1-'SOTP Bridge'!$C$15)/Assumptions!$C$6)*DCF!$C$61-Assumptions!$C$49</f>
         <v/>
       </c>
@@ -6409,11 +6394,11 @@
           <t>Bear at 5.5× (C) / bull at 8.0× (D), same construction</t>
         </is>
       </c>
-      <c r="C12" s="10">
+      <c r="C12" s="16">
         <f>((5.5*C5*C8+C9-Assumptions!$C$43+Assumptions!$C$44)*(1-'SOTP Bridge'!$C$15)/Assumptions!$C$6)*DCF!$C$61-Assumptions!$C$49</f>
         <v/>
       </c>
-      <c r="D12" s="10">
+      <c r="D12" s="16">
         <f>((8.0*C5*C8+C9-Assumptions!$C$43+Assumptions!$C$44)*(1-'SOTP Bridge'!$C$15)/Assumptions!$C$6)*DCF!$C$61-Assumptions!$C$49</f>
         <v/>
       </c>
@@ -6424,7 +6409,7 @@
           <t>Trailing enterprise value / EBITDA</t>
         </is>
       </c>
-      <c r="C13" s="35">
+      <c r="C13" s="36">
         <f>((Assumptions!$C$5*Assumptions!$C$6)+Assumptions!$C$43)/'Income Statement'!D7</f>
         <v/>
       </c>
@@ -6435,7 +6420,7 @@
           <t>Trailing price / earnings</t>
         </is>
       </c>
-      <c r="C14" s="35">
+      <c r="C14" s="36">
         <f>Assumptions!$C$5/'Income Statement'!D18</f>
         <v/>
       </c>
@@ -6446,7 +6431,7 @@
           <t>Trailing price / book</t>
         </is>
       </c>
-      <c r="C15" s="35">
+      <c r="C15" s="36">
         <f>Assumptions!$C$5/C31</f>
         <v/>
       </c>
@@ -6457,7 +6442,7 @@
           <t>Net bank debt / EBITDA</t>
         </is>
       </c>
-      <c r="C16" s="35">
+      <c r="C16" s="36">
         <f>Assumptions!$C$43/'Income Statement'!D7</f>
         <v/>
       </c>
@@ -6480,7 +6465,7 @@
           <t>Current-scale revenue (FY2026E, EGP mn)</t>
         </is>
       </c>
-      <c r="C19" s="18">
+      <c r="C19" s="19">
         <f>DCF!B5</f>
         <v/>
       </c>
@@ -6491,7 +6476,7 @@
           <t>Mid-cycle EBITDA margin (FY2028E)</t>
         </is>
       </c>
-      <c r="C20" s="16">
+      <c r="C20" s="17">
         <f>DCF!D7</f>
         <v/>
       </c>
@@ -6502,7 +6487,7 @@
           <t>Normalised EBITDA (EGP mn)</t>
         </is>
       </c>
-      <c r="C21" s="29">
+      <c r="C21" s="30">
         <f>C19*C20</f>
         <v/>
       </c>
@@ -6513,7 +6498,7 @@
           <t>Normalised EBIT (EGP mn)</t>
         </is>
       </c>
-      <c r="C22" s="29">
+      <c r="C22" s="30">
         <f>C21-C19*Assumptions!$C$27</f>
         <v/>
       </c>
@@ -6524,7 +6509,7 @@
           <t>Net finance cost (FY2026E, EGP mn)</t>
         </is>
       </c>
-      <c r="C23" s="18">
+      <c r="C23" s="19">
         <f>'Income Statement'!E11</f>
         <v/>
       </c>
@@ -6535,7 +6520,7 @@
           <t>Share of equity-accounted investees (FY2026E, EGP mn)</t>
         </is>
       </c>
-      <c r="C24" s="18">
+      <c r="C24" s="19">
         <f>'Income Statement'!E12</f>
         <v/>
       </c>
@@ -6546,7 +6531,7 @@
           <t>Normalised attributable earnings (EGP mn)</t>
         </is>
       </c>
-      <c r="C25" s="29">
+      <c r="C25" s="30">
         <f>(C22+C23+C24)*(1-Assumptions!$C$7)*(1-'SOTP Bridge'!$C$15)</f>
         <v/>
       </c>
@@ -6557,7 +6542,7 @@
           <t>Normalised earnings per share (EGP)</t>
         </is>
       </c>
-      <c r="C26" s="10">
+      <c r="C26" s="16">
         <f>C25/Assumptions!$C$6</f>
         <v/>
       </c>
@@ -6568,19 +6553,19 @@
           <t>Justified price / earnings</t>
         </is>
       </c>
-      <c r="C27" s="35">
+      <c r="C27" s="36">
         <f>Assumptions!$C$64</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="15" t="inlineStr">
+      <c r="A28" s="13" t="inlineStr">
         <is>
           <t>Implied value per share, rolled to the anchor (EGP)</t>
         </is>
       </c>
-      <c r="B28" s="15" t="n"/>
-      <c r="C28" s="31">
+      <c r="B28" s="13" t="n"/>
+      <c r="C28" s="32">
         <f>C26*C27*DCF!$C$61-Assumptions!$C$49</f>
         <v/>
       </c>
@@ -6589,11 +6574,11 @@
           <t>bear 7.0× (E) / bull 11.5× (F):</t>
         </is>
       </c>
-      <c r="E28" s="10">
+      <c r="E28" s="16">
         <f>C26*7*DCF!$C$61-Assumptions!$C$49</f>
         <v/>
       </c>
-      <c r="F28" s="10">
+      <c r="F28" s="16">
         <f>C26*11.5*DCF!$C$61-Assumptions!$C$49</f>
         <v/>
       </c>
@@ -6627,7 +6612,7 @@
           <t>Sustainable return on equity</t>
         </is>
       </c>
-      <c r="C32" s="11">
+      <c r="C32" s="9">
         <f>Assumptions!$C$65</f>
         <v/>
       </c>
@@ -6638,7 +6623,7 @@
           <t>Trailing return on equity</t>
         </is>
       </c>
-      <c r="C33" s="16">
+      <c r="C33" s="17">
         <f>'Income Statement'!D17/(('Balance Sheet'!C14+'Balance Sheet'!D14)/2)</f>
         <v/>
       </c>
@@ -6649,7 +6634,7 @@
           <t>Perpetual (terminal) cost of equity — a steady-state multiple takes a steady-state rate</t>
         </is>
       </c>
-      <c r="C34" s="16">
+      <c r="C34" s="17">
         <f>DCF!C49</f>
         <v/>
       </c>
@@ -6660,19 +6645,19 @@
           <t>Justified price / book</t>
         </is>
       </c>
-      <c r="C35" s="35">
+      <c r="C35" s="36">
         <f>(C32-Assumptions!$C$40)/(C34-Assumptions!$C$40)</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="15" t="inlineStr">
+      <c r="A36" s="13" t="inlineStr">
         <is>
           <t>Implied value per share, rolled to the anchor (EGP)</t>
         </is>
       </c>
-      <c r="B36" s="15" t="n"/>
-      <c r="C36" s="31">
+      <c r="B36" s="13" t="n"/>
+      <c r="C36" s="32">
         <f>C31*C35*DCF!$C$61-Assumptions!$C$49</f>
         <v/>
       </c>
@@ -6681,11 +6666,11 @@
           <t>bear / bull constructions (E / F):</t>
         </is>
       </c>
-      <c r="E36" s="10">
+      <c r="E36" s="16">
         <f>((Assumptions!$C$65-0.03)/((DCF!C39+DCF!C49)/2-0.03))*C31*DCF!$C$61-Assumptions!$C$49</f>
         <v/>
       </c>
-      <c r="F36" s="10">
+      <c r="F36" s="16">
         <f>((Assumptions!$C$65+0.02-Assumptions!$C$40)/(DCF!C49-Assumptions!$C$40))*C31*DCF!$C$61-Assumptions!$C$49</f>
         <v/>
       </c>
@@ -6769,23 +6754,23 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B5" s="18">
+      <c r="B5" s="19">
         <f>Segments!E8</f>
         <v/>
       </c>
-      <c r="C5" s="18">
+      <c r="C5" s="19">
         <f>Segments!F8</f>
         <v/>
       </c>
-      <c r="D5" s="18">
+      <c r="D5" s="19">
         <f>Segments!G8</f>
         <v/>
       </c>
-      <c r="E5" s="18">
+      <c r="E5" s="19">
         <f>Segments!H8</f>
         <v/>
       </c>
-      <c r="F5" s="18">
+      <c r="F5" s="19">
         <f>Segments!I8</f>
         <v/>
       </c>
@@ -6796,23 +6781,23 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B6" s="18">
+      <c r="B6" s="19">
         <f>Segments!B23</f>
         <v/>
       </c>
-      <c r="C6" s="18">
+      <c r="C6" s="19">
         <f>Segments!C23</f>
         <v/>
       </c>
-      <c r="D6" s="18">
+      <c r="D6" s="19">
         <f>Segments!D23</f>
         <v/>
       </c>
-      <c r="E6" s="18">
+      <c r="E6" s="19">
         <f>Segments!E23</f>
         <v/>
       </c>
-      <c r="F6" s="18">
+      <c r="F6" s="19">
         <f>Segments!F23</f>
         <v/>
       </c>
@@ -6823,23 +6808,23 @@
           <t>EBITDA margin</t>
         </is>
       </c>
-      <c r="B7" s="11">
+      <c r="B7" s="9">
         <f>B6/B5</f>
         <v/>
       </c>
-      <c r="C7" s="11">
+      <c r="C7" s="9">
         <f>C6/C5</f>
         <v/>
       </c>
-      <c r="D7" s="11">
+      <c r="D7" s="9">
         <f>D6/D5</f>
         <v/>
       </c>
-      <c r="E7" s="11">
+      <c r="E7" s="9">
         <f>E6/E5</f>
         <v/>
       </c>
-      <c r="F7" s="11">
+      <c r="F7" s="9">
         <f>F6/F5</f>
         <v/>
       </c>
@@ -6850,50 +6835,50 @@
           <t>Less depreciation and amortisation</t>
         </is>
       </c>
-      <c r="B8" s="29">
+      <c r="B8" s="30">
         <f>-B5*Assumptions!$C$27</f>
         <v/>
       </c>
-      <c r="C8" s="29">
+      <c r="C8" s="30">
         <f>-C5*Assumptions!$C$27</f>
         <v/>
       </c>
-      <c r="D8" s="29">
+      <c r="D8" s="30">
         <f>-D5*Assumptions!$C$27</f>
         <v/>
       </c>
-      <c r="E8" s="29">
+      <c r="E8" s="30">
         <f>-E5*Assumptions!$C$27</f>
         <v/>
       </c>
-      <c r="F8" s="29">
+      <c r="F8" s="30">
         <f>-F5*Assumptions!$C$27</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B9" s="30">
+      <c r="B9" s="31">
         <f>B6+B8</f>
         <v/>
       </c>
-      <c r="C9" s="30">
+      <c r="C9" s="31">
         <f>C6+C8</f>
         <v/>
       </c>
-      <c r="D9" s="30">
+      <c r="D9" s="31">
         <f>D6+D8</f>
         <v/>
       </c>
-      <c r="E9" s="30">
+      <c r="E9" s="31">
         <f>E6+E8</f>
         <v/>
       </c>
-      <c r="F9" s="30">
+      <c r="F9" s="31">
         <f>F6+F8</f>
         <v/>
       </c>
@@ -6904,23 +6889,23 @@
           <t>NOPAT — EBIT x (1 - 24%)</t>
         </is>
       </c>
-      <c r="B10" s="29">
+      <c r="B10" s="30">
         <f>B9*(1-Assumptions!$C$7)</f>
         <v/>
       </c>
-      <c r="C10" s="29">
+      <c r="C10" s="30">
         <f>C9*(1-Assumptions!$C$7)</f>
         <v/>
       </c>
-      <c r="D10" s="29">
+      <c r="D10" s="30">
         <f>D9*(1-Assumptions!$C$7)</f>
         <v/>
       </c>
-      <c r="E10" s="29">
+      <c r="E10" s="30">
         <f>E9*(1-Assumptions!$C$7)</f>
         <v/>
       </c>
-      <c r="F10" s="29">
+      <c r="F10" s="30">
         <f>F9*(1-Assumptions!$C$7)</f>
         <v/>
       </c>
@@ -6931,23 +6916,23 @@
           <t>Add back depreciation and amortisation</t>
         </is>
       </c>
-      <c r="B11" s="29">
+      <c r="B11" s="30">
         <f>-B8</f>
         <v/>
       </c>
-      <c r="C11" s="29">
+      <c r="C11" s="30">
         <f>-C8</f>
         <v/>
       </c>
-      <c r="D11" s="29">
+      <c r="D11" s="30">
         <f>-D8</f>
         <v/>
       </c>
-      <c r="E11" s="29">
+      <c r="E11" s="30">
         <f>-E8</f>
         <v/>
       </c>
-      <c r="F11" s="29">
+      <c r="F11" s="30">
         <f>-F8</f>
         <v/>
       </c>
@@ -6958,23 +6943,23 @@
           <t>Less capital expenditure</t>
         </is>
       </c>
-      <c r="B12" s="29">
+      <c r="B12" s="30">
         <f>-B5*Assumptions!$B$26</f>
         <v/>
       </c>
-      <c r="C12" s="29">
+      <c r="C12" s="30">
         <f>-C5*Assumptions!$C$26</f>
         <v/>
       </c>
-      <c r="D12" s="29">
+      <c r="D12" s="30">
         <f>-D5*Assumptions!$D$26</f>
         <v/>
       </c>
-      <c r="E12" s="29">
+      <c r="E12" s="30">
         <f>-E5*Assumptions!$E$26</f>
         <v/>
       </c>
-      <c r="F12" s="29">
+      <c r="F12" s="30">
         <f>-F5*Assumptions!$F$26</f>
         <v/>
       </c>
@@ -6985,50 +6970,50 @@
           <t>Less change in working capital</t>
         </is>
       </c>
-      <c r="B13" s="29">
+      <c r="B13" s="30">
         <f>-(B5*Assumptions!$C$25-'Balance Sheet'!D16)</f>
         <v/>
       </c>
-      <c r="C13" s="29">
+      <c r="C13" s="30">
         <f>-(C5-B5)*Assumptions!$C$25</f>
         <v/>
       </c>
-      <c r="D13" s="29">
+      <c r="D13" s="30">
         <f>-(D5-C5)*Assumptions!$C$25</f>
         <v/>
       </c>
-      <c r="E13" s="29">
+      <c r="E13" s="30">
         <f>-(E5-D5)*Assumptions!$C$25</f>
         <v/>
       </c>
-      <c r="F13" s="29">
+      <c r="F13" s="30">
         <f>-(F5-E5)*Assumptions!$C$25</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="inlineStr">
+      <c r="A14" s="13" t="inlineStr">
         <is>
           <t>Free cash flow to the firm</t>
         </is>
       </c>
-      <c r="B14" s="30">
+      <c r="B14" s="31">
         <f>B10+B11+B12+B13</f>
         <v/>
       </c>
-      <c r="C14" s="30">
+      <c r="C14" s="31">
         <f>C10+C11+C12+C13</f>
         <v/>
       </c>
-      <c r="D14" s="30">
+      <c r="D14" s="31">
         <f>D10+D11+D12+D13</f>
         <v/>
       </c>
-      <c r="E14" s="30">
+      <c r="E14" s="31">
         <f>E10+E11+E12+E13</f>
         <v/>
       </c>
-      <c r="F14" s="30">
+      <c r="F14" s="31">
         <f>F10+F11+F12+F13</f>
         <v/>
       </c>
@@ -7039,23 +7024,23 @@
           <t>Forward cost of capital</t>
         </is>
       </c>
-      <c r="B15" s="36">
+      <c r="B15" s="37">
         <f>$C$46-($C$46-$C$53)*B57</f>
         <v/>
       </c>
-      <c r="C15" s="36">
+      <c r="C15" s="37">
         <f>$C$46-($C$46-$C$53)*C57</f>
         <v/>
       </c>
-      <c r="D15" s="36">
+      <c r="D15" s="37">
         <f>$C$46-($C$46-$C$53)*D57</f>
         <v/>
       </c>
-      <c r="E15" s="36">
+      <c r="E15" s="37">
         <f>$C$46-($C$46-$C$53)*E57</f>
         <v/>
       </c>
-      <c r="F15" s="36">
+      <c r="F15" s="37">
         <f>$C$46-($C$46-$C$53)*F57</f>
         <v/>
       </c>
@@ -7066,56 +7051,56 @@
           <t>Discount factor</t>
         </is>
       </c>
-      <c r="B16" s="37">
+      <c r="B16" s="38">
         <f>1/(1+B15)</f>
         <v/>
       </c>
-      <c r="C16" s="37">
+      <c r="C16" s="38">
         <f>B16/(1+C15)</f>
         <v/>
       </c>
-      <c r="D16" s="37">
+      <c r="D16" s="38">
         <f>C16/(1+D15)</f>
         <v/>
       </c>
-      <c r="E16" s="37">
+      <c r="E16" s="38">
         <f>D16/(1+E15)</f>
         <v/>
       </c>
-      <c r="F16" s="37">
+      <c r="F16" s="38">
         <f>E16/(1+F15)</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="13" t="inlineStr">
         <is>
           <t>Present value of FCFF</t>
         </is>
       </c>
-      <c r="B17" s="30">
+      <c r="B17" s="31">
         <f>B14*B16</f>
         <v/>
       </c>
-      <c r="C17" s="30">
+      <c r="C17" s="31">
         <f>C14*C16</f>
         <v/>
       </c>
-      <c r="D17" s="30">
+      <c r="D17" s="31">
         <f>D14*D16</f>
         <v/>
       </c>
-      <c r="E17" s="30">
+      <c r="E17" s="31">
         <f>E14*E16</f>
         <v/>
       </c>
-      <c r="F17" s="30">
+      <c r="F17" s="31">
         <f>F14*F16</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="20" t="inlineStr">
+      <c r="A19" s="15" t="inlineStr">
         <is>
           <t>TERMINAL VALUE, BRIDGE AND THE ANCHOR ROLL</t>
         </is>
@@ -7127,7 +7112,7 @@
           <t>Terminal-year NOPAT grown one year (EGP mn)</t>
         </is>
       </c>
-      <c r="C20" s="29">
+      <c r="C20" s="30">
         <f>F10*(1+C23)</f>
         <v/>
       </c>
@@ -7138,7 +7123,7 @@
           <t>Terminal return on invested capital</t>
         </is>
       </c>
-      <c r="C21" s="16">
+      <c r="C21" s="17">
         <f>F10*(1+C23)/'Summary Financials'!I13</f>
         <v/>
       </c>
@@ -7149,7 +7134,7 @@
           <t>Required reinvestment rate (g / return on capital)</t>
         </is>
       </c>
-      <c r="C22" s="11">
+      <c r="C22" s="9">
         <f>C23/C21</f>
         <v/>
       </c>
@@ -7160,7 +7145,7 @@
           <t>Terminal growth</t>
         </is>
       </c>
-      <c r="C23" s="16">
+      <c r="C23" s="17">
         <f>Assumptions!$C$40</f>
         <v/>
       </c>
@@ -7171,7 +7156,7 @@
           <t>Terminal cost of capital</t>
         </is>
       </c>
-      <c r="C24" s="11">
+      <c r="C24" s="9">
         <f>C53</f>
         <v/>
       </c>
@@ -7182,7 +7167,7 @@
           <t>Terminal value — terminal-year FCFF C20×(1−C22), capitalised (EGP mn)</t>
         </is>
       </c>
-      <c r="C25" s="29">
+      <c r="C25" s="30">
         <f>C20*(1-C22)/(C24-C23)</f>
         <v/>
       </c>
@@ -7193,7 +7178,7 @@
           <t>Present value of the five forecast years (EGP mn)</t>
         </is>
       </c>
-      <c r="C26" s="29">
+      <c r="C26" s="30">
         <f>SUM(B17:F17)</f>
         <v/>
       </c>
@@ -7204,7 +7189,7 @@
           <t>Present value of the terminal value (EGP mn)</t>
         </is>
       </c>
-      <c r="C27" s="29">
+      <c r="C27" s="30">
         <f>C25*F16</f>
         <v/>
       </c>
@@ -7215,7 +7200,7 @@
           <t>Terminal value as a share of enterprise value</t>
         </is>
       </c>
-      <c r="C28" s="11">
+      <c r="C28" s="9">
         <f>C27/(C26+C27)</f>
         <v/>
       </c>
@@ -7226,7 +7211,7 @@
           <t>Enterprise value (EGP mn)</t>
         </is>
       </c>
-      <c r="C29" s="29">
+      <c r="C29" s="30">
         <f>C26+C27</f>
         <v/>
       </c>
@@ -7237,26 +7222,26 @@
           <t>Equity attributable to shareholders (EGP mn)</t>
         </is>
       </c>
-      <c r="C30" s="18">
+      <c r="C30" s="19">
         <f>'SOTP Bridge'!C12</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="15" t="inlineStr">
+      <c r="A31" s="13" t="inlineStr">
         <is>
           <t>Fair value per share at 31-Dec-2025 (EGP)</t>
         </is>
       </c>
-      <c r="B31" s="15" t="n"/>
-      <c r="C31" s="31">
+      <c r="B31" s="13" t="n"/>
+      <c r="C31" s="32">
         <f>C30/Assumptions!$C$6</f>
         <v/>
       </c>
-      <c r="D31" s="15" t="n"/>
+      <c r="D31" s="13" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="20" t="inlineStr">
+      <c r="A33" s="15" t="inlineStr">
         <is>
           <t>COST OF CAPITAL — BUILT HERE, NOT ASSUMED</t>
         </is>
@@ -7268,7 +7253,7 @@
           <t>Risk-free rate, 10-year local currency</t>
         </is>
       </c>
-      <c r="C34" s="22">
+      <c r="C34" s="23">
         <f>Assumptions!$C$30</f>
         <v/>
       </c>
@@ -7279,7 +7264,7 @@
           <t>Less sovereign default spread (removed to avoid double-counting)</t>
         </is>
       </c>
-      <c r="C35" s="22">
+      <c r="C35" s="23">
         <f>Assumptions!$C$31</f>
         <v/>
       </c>
@@ -7290,7 +7275,7 @@
           <t>Risk-free rate net of the sovereign spread</t>
         </is>
       </c>
-      <c r="C36" s="36">
+      <c r="C36" s="37">
         <f>C34-C35</f>
         <v/>
       </c>
@@ -7301,7 +7286,7 @@
           <t>Beta</t>
         </is>
       </c>
-      <c r="C37" s="38">
+      <c r="C37" s="39">
         <f>Assumptions!$C$33</f>
         <v/>
       </c>
@@ -7312,7 +7297,7 @@
           <t>Equity risk premium</t>
         </is>
       </c>
-      <c r="C38" s="22">
+      <c r="C38" s="23">
         <f>Assumptions!$C$32</f>
         <v/>
       </c>
@@ -7323,7 +7308,7 @@
           <t>Cost of equity, explicit window</t>
         </is>
       </c>
-      <c r="C39" s="36">
+      <c r="C39" s="37">
         <f>C36+C37*C38</f>
         <v/>
       </c>
@@ -7334,7 +7319,7 @@
           <t>Cost of debt, blended</t>
         </is>
       </c>
-      <c r="C40" s="22">
+      <c r="C40" s="23">
         <f>Assumptions!$C$34</f>
         <v/>
       </c>
@@ -7345,7 +7330,7 @@
           <t>Cost of debt after tax</t>
         </is>
       </c>
-      <c r="C41" s="36">
+      <c r="C41" s="37">
         <f>C40*(1-Assumptions!$C$7)</f>
         <v/>
       </c>
@@ -7356,7 +7341,7 @@
           <t>Market capitalisation (EGP mn)</t>
         </is>
       </c>
-      <c r="C42" s="18">
+      <c r="C42" s="19">
         <f>Assumptions!$C$5*Assumptions!$C$6</f>
         <v/>
       </c>
@@ -7367,7 +7352,7 @@
           <t>Net bank debt (EGP mn)</t>
         </is>
       </c>
-      <c r="C43" s="18">
+      <c r="C43" s="19">
         <f>Assumptions!$C$43</f>
         <v/>
       </c>
@@ -7378,7 +7363,7 @@
           <t>Debt weight (net debt / (net debt + market capitalisation))</t>
         </is>
       </c>
-      <c r="C44" s="36">
+      <c r="C44" s="37">
         <f>C43/(C43+C42)</f>
         <v/>
       </c>
@@ -7389,23 +7374,23 @@
           <t>Equity weight</t>
         </is>
       </c>
-      <c r="C45" s="36">
+      <c r="C45" s="37">
         <f>1-C44</f>
         <v/>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="15" t="inlineStr">
+      <c r="A46" s="13" t="inlineStr">
         <is>
           <t>Cost of capital, explicit window</t>
         </is>
       </c>
-      <c r="B46" s="15" t="n"/>
-      <c r="C46" s="39">
+      <c r="B46" s="13" t="n"/>
+      <c r="C46" s="40">
         <f>C45*C39+C44*C41</f>
         <v/>
       </c>
-      <c r="D46" s="15" t="n"/>
+      <c r="D46" s="13" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
@@ -7413,7 +7398,7 @@
           <t>Terminal risk-free rate</t>
         </is>
       </c>
-      <c r="C47" s="22">
+      <c r="C47" s="23">
         <f>Assumptions!$C$36</f>
         <v/>
       </c>
@@ -7424,7 +7409,7 @@
           <t>Terminal equity risk premium</t>
         </is>
       </c>
-      <c r="C48" s="22">
+      <c r="C48" s="23">
         <f>Assumptions!$C$37</f>
         <v/>
       </c>
@@ -7435,7 +7420,7 @@
           <t>Terminal cost of equity</t>
         </is>
       </c>
-      <c r="C49" s="36">
+      <c r="C49" s="37">
         <f>C47+C37*C48</f>
         <v/>
       </c>
@@ -7446,7 +7431,7 @@
           <t>Terminal cost of debt</t>
         </is>
       </c>
-      <c r="C50" s="22">
+      <c r="C50" s="23">
         <f>Assumptions!$C$38</f>
         <v/>
       </c>
@@ -7457,7 +7442,7 @@
           <t>Terminal cost of debt after tax</t>
         </is>
       </c>
-      <c r="C51" s="36">
+      <c r="C51" s="37">
         <f>C50*(1-Assumptions!$C$7)</f>
         <v/>
       </c>
@@ -7468,23 +7453,23 @@
           <t>Terminal debt weight</t>
         </is>
       </c>
-      <c r="C52" s="22">
+      <c r="C52" s="23">
         <f>Assumptions!$C$39</f>
         <v/>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="15" t="inlineStr">
+      <c r="A53" s="13" t="inlineStr">
         <is>
           <t>Terminal cost of capital</t>
         </is>
       </c>
-      <c r="B53" s="15" t="n"/>
-      <c r="C53" s="39">
+      <c r="B53" s="13" t="n"/>
+      <c r="C53" s="40">
         <f>(1-C52)*C49+C52*C51</f>
         <v/>
       </c>
-      <c r="D53" s="15" t="n"/>
+      <c r="D53" s="13" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
@@ -7524,23 +7509,23 @@
           <t>Cost of debt path</t>
         </is>
       </c>
-      <c r="B56" s="22">
+      <c r="B56" s="23">
         <f>Assumptions!$B$35</f>
         <v/>
       </c>
-      <c r="C56" s="22">
+      <c r="C56" s="23">
         <f>Assumptions!$C$35</f>
         <v/>
       </c>
-      <c r="D56" s="22">
+      <c r="D56" s="23">
         <f>Assumptions!$D$35</f>
         <v/>
       </c>
-      <c r="E56" s="22">
+      <c r="E56" s="23">
         <f>Assumptions!$E$35</f>
         <v/>
       </c>
-      <c r="F56" s="22">
+      <c r="F56" s="23">
         <f>Assumptions!$F$35</f>
         <v/>
       </c>
@@ -7551,23 +7536,23 @@
           <t>Glide fraction — cumulative progress of the easing</t>
         </is>
       </c>
-      <c r="B57" s="36">
+      <c r="B57" s="37">
         <f>($B$56-B56)/($B$56-$F$56)</f>
         <v/>
       </c>
-      <c r="C57" s="36">
+      <c r="C57" s="37">
         <f>($B$56-C56)/($B$56-$F$56)</f>
         <v/>
       </c>
-      <c r="D57" s="36">
+      <c r="D57" s="37">
         <f>($B$56-D56)/($B$56-$F$56)</f>
         <v/>
       </c>
-      <c r="E57" s="36">
+      <c r="E57" s="37">
         <f>($B$56-E56)/($B$56-$F$56)</f>
         <v/>
       </c>
-      <c r="F57" s="36">
+      <c r="F57" s="37">
         <f>($B$56-F56)/($B$56-$F$56)</f>
         <v/>
       </c>
@@ -7580,7 +7565,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="20" t="inlineStr">
+      <c r="A60" s="15" t="inlineStr">
         <is>
           <t>THE ANCHOR ROLL — one date, one price of time</t>
         </is>
@@ -7592,23 +7577,23 @@
           <t>Anchor accretion factor — (1 + cost of equity)^(days to anchor / 365)</t>
         </is>
       </c>
-      <c r="C61" s="37">
+      <c r="C61" s="38">
         <f>(1+C39)^(Assumptions!$C$53/365)</f>
         <v/>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="15" t="inlineStr">
+      <c r="A62" s="13" t="inlineStr">
         <is>
           <t>Fair value per share at the 5-Aug-2026 anchor (EGP)</t>
         </is>
       </c>
-      <c r="B62" s="15" t="n"/>
-      <c r="C62" s="31">
+      <c r="B62" s="13" t="n"/>
+      <c r="C62" s="32">
         <f>C31*C61-Assumptions!$C$49</f>
         <v/>
       </c>
-      <c r="D62" s="15" t="n"/>
+      <c r="D62" s="13" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
@@ -7712,37 +7697,37 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B5" s="30" t="n">
+      <c r="B5" s="31" t="n">
         <v>152186.247545</v>
       </c>
-      <c r="C5" s="30" t="n">
+      <c r="C5" s="31" t="n">
         <v>231981.835577</v>
       </c>
-      <c r="D5" s="30" t="n">
+      <c r="D5" s="31" t="n">
         <v>281049.081719</v>
       </c>
-      <c r="E5" s="30">
+      <c r="E5" s="31">
         <f>DCF!B5</f>
         <v/>
       </c>
-      <c r="F5" s="30">
+      <c r="F5" s="31">
         <f>DCF!C5</f>
         <v/>
       </c>
-      <c r="G5" s="30">
+      <c r="G5" s="31">
         <f>DCF!D5</f>
         <v/>
       </c>
-      <c r="H5" s="30">
+      <c r="H5" s="31">
         <f>DCF!E5</f>
         <v/>
       </c>
-      <c r="I5" s="30">
+      <c r="I5" s="31">
         <f>DCF!F5</f>
         <v/>
       </c>
@@ -7753,68 +7738,68 @@
           <t>Gross profit</t>
         </is>
       </c>
-      <c r="B6" s="23" t="n">
+      <c r="B6" s="24" t="n">
         <v>29077.288803</v>
       </c>
-      <c r="C6" s="23" t="n">
+      <c r="C6" s="24" t="n">
         <v>43898.520903</v>
       </c>
-      <c r="D6" s="23" t="n">
+      <c r="D6" s="24" t="n">
         <v>40762.108187</v>
       </c>
-      <c r="E6" s="18">
+      <c r="E6" s="19">
         <f>Segments!B14</f>
         <v/>
       </c>
-      <c r="F6" s="18">
+      <c r="F6" s="19">
         <f>Segments!C14</f>
         <v/>
       </c>
-      <c r="G6" s="18">
+      <c r="G6" s="19">
         <f>Segments!D14</f>
         <v/>
       </c>
-      <c r="H6" s="18">
+      <c r="H6" s="19">
         <f>Segments!E14</f>
         <v/>
       </c>
-      <c r="I6" s="18">
+      <c r="I6" s="19">
         <f>Segments!F14</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B7" s="30" t="n">
+      <c r="B7" s="31" t="n">
         <v>20035.105205</v>
       </c>
-      <c r="C7" s="30" t="n">
+      <c r="C7" s="31" t="n">
         <v>31601.46495</v>
       </c>
-      <c r="D7" s="30" t="n">
+      <c r="D7" s="31" t="n">
         <v>28363.203246</v>
       </c>
-      <c r="E7" s="30">
+      <c r="E7" s="31">
         <f>DCF!B6</f>
         <v/>
       </c>
-      <c r="F7" s="30">
+      <c r="F7" s="31">
         <f>DCF!C6</f>
         <v/>
       </c>
-      <c r="G7" s="30">
+      <c r="G7" s="31">
         <f>DCF!D6</f>
         <v/>
       </c>
-      <c r="H7" s="30">
+      <c r="H7" s="31">
         <f>DCF!E6</f>
         <v/>
       </c>
-      <c r="I7" s="30">
+      <c r="I7" s="31">
         <f>DCF!F6</f>
         <v/>
       </c>
@@ -7825,35 +7810,35 @@
           <t>EBITDA margin</t>
         </is>
       </c>
-      <c r="B8" s="11">
+      <c r="B8" s="9">
         <f>B7/B5</f>
         <v/>
       </c>
-      <c r="C8" s="11">
+      <c r="C8" s="9">
         <f>C7/C5</f>
         <v/>
       </c>
-      <c r="D8" s="11">
+      <c r="D8" s="9">
         <f>D7/D5</f>
         <v/>
       </c>
-      <c r="E8" s="11">
+      <c r="E8" s="9">
         <f>E7/E5</f>
         <v/>
       </c>
-      <c r="F8" s="11">
+      <c r="F8" s="9">
         <f>F7/F5</f>
         <v/>
       </c>
-      <c r="G8" s="11">
+      <c r="G8" s="9">
         <f>G7/G5</f>
         <v/>
       </c>
-      <c r="H8" s="11">
+      <c r="H8" s="9">
         <f>H7/H5</f>
         <v/>
       </c>
-      <c r="I8" s="11">
+      <c r="I8" s="9">
         <f>I7/I5</f>
         <v/>
       </c>
@@ -7864,71 +7849,71 @@
           <t>Depreciation and amortisation</t>
         </is>
       </c>
-      <c r="B9" s="23" t="n">
+      <c r="B9" s="24" t="n">
         <v>-2295.986956</v>
       </c>
-      <c r="C9" s="23" t="n">
+      <c r="C9" s="24" t="n">
         <v>-2259.745806</v>
       </c>
-      <c r="D9" s="23" t="n">
+      <c r="D9" s="24" t="n">
         <v>-3008.977627</v>
       </c>
-      <c r="E9" s="18">
+      <c r="E9" s="19">
         <f>DCF!B8</f>
         <v/>
       </c>
-      <c r="F9" s="18">
+      <c r="F9" s="19">
         <f>DCF!C8</f>
         <v/>
       </c>
-      <c r="G9" s="18">
+      <c r="G9" s="19">
         <f>DCF!D8</f>
         <v/>
       </c>
-      <c r="H9" s="18">
+      <c r="H9" s="19">
         <f>DCF!E8</f>
         <v/>
       </c>
-      <c r="I9" s="18">
+      <c r="I9" s="19">
         <f>DCF!F8</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="13" t="inlineStr">
         <is>
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B10" s="30">
+      <c r="B10" s="31">
         <f>B7+B9</f>
         <v/>
       </c>
-      <c r="C10" s="30">
+      <c r="C10" s="31">
         <f>C7+C9</f>
         <v/>
       </c>
-      <c r="D10" s="30">
+      <c r="D10" s="31">
         <f>D7+D9</f>
         <v/>
       </c>
-      <c r="E10" s="30">
+      <c r="E10" s="31">
         <f>E7+E9</f>
         <v/>
       </c>
-      <c r="F10" s="30">
+      <c r="F10" s="31">
         <f>F7+F9</f>
         <v/>
       </c>
-      <c r="G10" s="30">
+      <c r="G10" s="31">
         <f>G7+G9</f>
         <v/>
       </c>
-      <c r="H10" s="30">
+      <c r="H10" s="31">
         <f>H7+H9</f>
         <v/>
       </c>
-      <c r="I10" s="30">
+      <c r="I10" s="31">
         <f>I7+I9</f>
         <v/>
       </c>
@@ -7939,32 +7924,32 @@
           <t>Net finance costs</t>
         </is>
       </c>
-      <c r="B11" s="23" t="n">
+      <c r="B11" s="24" t="n">
         <v>-2124.362277</v>
       </c>
-      <c r="C11" s="23" t="n">
+      <c r="C11" s="24" t="n">
         <v>-3515.365946</v>
       </c>
-      <c r="D11" s="23" t="n">
+      <c r="D11" s="24" t="n">
         <v>-2145.438755</v>
       </c>
-      <c r="E11" s="29">
+      <c r="E11" s="30">
         <f>-(Assumptions!$B$35*'Balance Sheet'!$D$11-Assumptions!$C$52*MAX('Balance Sheet'!$D$11-'Balance Sheet'!D17,0))</f>
         <v/>
       </c>
-      <c r="F11" s="29">
+      <c r="F11" s="30">
         <f>-(Assumptions!$C$35*'Balance Sheet'!$D$11-Assumptions!$C$52*MAX('Balance Sheet'!$D$11-'Balance Sheet'!E17,0))</f>
         <v/>
       </c>
-      <c r="G11" s="29">
+      <c r="G11" s="30">
         <f>-(Assumptions!$D$35*'Balance Sheet'!$D$11-Assumptions!$C$52*MAX('Balance Sheet'!$D$11-'Balance Sheet'!F17,0))</f>
         <v/>
       </c>
-      <c r="H11" s="29">
+      <c r="H11" s="30">
         <f>-(Assumptions!$E$35*'Balance Sheet'!$D$11-Assumptions!$C$52*MAX('Balance Sheet'!$D$11-'Balance Sheet'!G17,0))</f>
         <v/>
       </c>
-      <c r="I11" s="29">
+      <c r="I11" s="30">
         <f>-(Assumptions!$F$35*'Balance Sheet'!$D$11-Assumptions!$C$52*MAX('Balance Sheet'!$D$11-'Balance Sheet'!H17,0))</f>
         <v/>
       </c>
@@ -7975,32 +7960,32 @@
           <t>Share of equity-accounted investees</t>
         </is>
       </c>
-      <c r="B12" s="23" t="n">
+      <c r="B12" s="24" t="n">
         <v>603.624972</v>
       </c>
-      <c r="C12" s="23" t="n">
+      <c r="C12" s="24" t="n">
         <v>1132.366257</v>
       </c>
-      <c r="D12" s="23" t="n">
+      <c r="D12" s="24" t="n">
         <v>1568.902975</v>
       </c>
-      <c r="E12" s="29">
+      <c r="E12" s="30">
         <f>D12*(1+Assumptions!$C$51)</f>
         <v/>
       </c>
-      <c r="F12" s="29">
+      <c r="F12" s="30">
         <f>E12*(1+Assumptions!$C$51)</f>
         <v/>
       </c>
-      <c r="G12" s="29">
+      <c r="G12" s="30">
         <f>F12*(1+Assumptions!$C$51)</f>
         <v/>
       </c>
-      <c r="H12" s="29">
+      <c r="H12" s="30">
         <f>G12*(1+Assumptions!$C$51)</f>
         <v/>
       </c>
-      <c r="I12" s="29">
+      <c r="I12" s="30">
         <f>H12*(1+Assumptions!$C$51)</f>
         <v/>
       </c>
@@ -8011,35 +7996,35 @@
           <t>Profit before tax</t>
         </is>
       </c>
-      <c r="B13" s="29">
+      <c r="B13" s="30">
         <f>B10+B11+B12</f>
         <v/>
       </c>
-      <c r="C13" s="29">
+      <c r="C13" s="30">
         <f>C10+C11+C12</f>
         <v/>
       </c>
-      <c r="D13" s="29">
+      <c r="D13" s="30">
         <f>D10+D11+D12</f>
         <v/>
       </c>
-      <c r="E13" s="29">
+      <c r="E13" s="30">
         <f>E10+E11+E12</f>
         <v/>
       </c>
-      <c r="F13" s="29">
+      <c r="F13" s="30">
         <f>F10+F11+F12</f>
         <v/>
       </c>
-      <c r="G13" s="29">
+      <c r="G13" s="30">
         <f>G10+G11+G12</f>
         <v/>
       </c>
-      <c r="H13" s="29">
+      <c r="H13" s="30">
         <f>H10+H11+H12</f>
         <v/>
       </c>
-      <c r="I13" s="29">
+      <c r="I13" s="30">
         <f>I10+I11+I12</f>
         <v/>
       </c>
@@ -8050,32 +8035,32 @@
           <t>Income tax</t>
         </is>
       </c>
-      <c r="B14" s="23" t="n">
+      <c r="B14" s="24" t="n">
         <v>-5080.406688</v>
       </c>
-      <c r="C14" s="23" t="n">
+      <c r="C14" s="24" t="n">
         <v>-8121.510082</v>
       </c>
-      <c r="D14" s="23" t="n">
+      <c r="D14" s="24" t="n">
         <v>-5591.139782</v>
       </c>
-      <c r="E14" s="29">
+      <c r="E14" s="30">
         <f>-E13*Assumptions!$C$7</f>
         <v/>
       </c>
-      <c r="F14" s="29">
+      <c r="F14" s="30">
         <f>-F13*Assumptions!$C$7</f>
         <v/>
       </c>
-      <c r="G14" s="29">
+      <c r="G14" s="30">
         <f>-G13*Assumptions!$C$7</f>
         <v/>
       </c>
-      <c r="H14" s="29">
+      <c r="H14" s="30">
         <f>-H13*Assumptions!$C$7</f>
         <v/>
       </c>
-      <c r="I14" s="29">
+      <c r="I14" s="30">
         <f>-I13*Assumptions!$C$7</f>
         <v/>
       </c>
@@ -8086,32 +8071,32 @@
           <t>Profit for the year</t>
         </is>
       </c>
-      <c r="B15" s="23" t="n">
+      <c r="B15" s="24" t="n">
         <v>11137.974256</v>
       </c>
-      <c r="C15" s="23" t="n">
+      <c r="C15" s="24" t="n">
         <v>18837.209373</v>
       </c>
-      <c r="D15" s="23" t="n">
+      <c r="D15" s="24" t="n">
         <v>19186.550057</v>
       </c>
-      <c r="E15" s="29">
+      <c r="E15" s="30">
         <f>E13+E14</f>
         <v/>
       </c>
-      <c r="F15" s="29">
+      <c r="F15" s="30">
         <f>F13+F14</f>
         <v/>
       </c>
-      <c r="G15" s="29">
+      <c r="G15" s="30">
         <f>G13+G14</f>
         <v/>
       </c>
-      <c r="H15" s="29">
+      <c r="H15" s="30">
         <f>H13+H14</f>
         <v/>
       </c>
-      <c r="I15" s="29">
+      <c r="I15" s="30">
         <f>I13+I14</f>
         <v/>
       </c>
@@ -8122,68 +8107,68 @@
           <t>Non-controlling interests</t>
         </is>
       </c>
-      <c r="B16" s="23" t="n">
+      <c r="B16" s="24" t="n">
         <v>-1022.272478999999</v>
       </c>
-      <c r="C16" s="23" t="n">
+      <c r="C16" s="24" t="n">
         <v>-1375.850659</v>
       </c>
-      <c r="D16" s="23" t="n">
+      <c r="D16" s="24" t="n">
         <v>-1856.305067000001</v>
       </c>
-      <c r="E16" s="29">
+      <c r="E16" s="30">
         <f>-E15*'SOTP Bridge'!$C$15</f>
         <v/>
       </c>
-      <c r="F16" s="29">
+      <c r="F16" s="30">
         <f>-F15*'SOTP Bridge'!$C$15</f>
         <v/>
       </c>
-      <c r="G16" s="29">
+      <c r="G16" s="30">
         <f>-G15*'SOTP Bridge'!$C$15</f>
         <v/>
       </c>
-      <c r="H16" s="29">
+      <c r="H16" s="30">
         <f>-H15*'SOTP Bridge'!$C$15</f>
         <v/>
       </c>
-      <c r="I16" s="29">
+      <c r="I16" s="30">
         <f>-I15*'SOTP Bridge'!$C$15</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="13" t="inlineStr">
         <is>
           <t>Profit attributable to shareholders</t>
         </is>
       </c>
-      <c r="B17" s="30" t="n">
+      <c r="B17" s="31" t="n">
         <v>10115.701777</v>
       </c>
-      <c r="C17" s="30" t="n">
+      <c r="C17" s="31" t="n">
         <v>17461.358714</v>
       </c>
-      <c r="D17" s="30" t="n">
+      <c r="D17" s="31" t="n">
         <v>17330.24499</v>
       </c>
-      <c r="E17" s="30">
+      <c r="E17" s="31">
         <f>E15+E16</f>
         <v/>
       </c>
-      <c r="F17" s="30">
+      <c r="F17" s="31">
         <f>F15+F16</f>
         <v/>
       </c>
-      <c r="G17" s="30">
+      <c r="G17" s="31">
         <f>G15+G16</f>
         <v/>
       </c>
-      <c r="H17" s="30">
+      <c r="H17" s="31">
         <f>H15+H16</f>
         <v/>
       </c>
-      <c r="I17" s="30">
+      <c r="I17" s="31">
         <f>I15+I16</f>
         <v/>
       </c>
@@ -8194,35 +8179,35 @@
           <t>Earnings per share (EGP)</t>
         </is>
       </c>
-      <c r="B18" s="10">
+      <c r="B18" s="16">
         <f>B17/Assumptions!$C$6</f>
         <v/>
       </c>
-      <c r="C18" s="10">
+      <c r="C18" s="16">
         <f>C17/Assumptions!$C$6</f>
         <v/>
       </c>
-      <c r="D18" s="10">
+      <c r="D18" s="16">
         <f>D17/Assumptions!$C$6</f>
         <v/>
       </c>
-      <c r="E18" s="10">
+      <c r="E18" s="16">
         <f>E17/Assumptions!$C$6</f>
         <v/>
       </c>
-      <c r="F18" s="10">
+      <c r="F18" s="16">
         <f>F17/Assumptions!$C$6</f>
         <v/>
       </c>
-      <c r="G18" s="10">
+      <c r="G18" s="16">
         <f>G17/Assumptions!$C$6</f>
         <v/>
       </c>
-      <c r="H18" s="10">
+      <c r="H18" s="16">
         <f>H17/Assumptions!$C$6</f>
         <v/>
       </c>
-      <c r="I18" s="10">
+      <c r="I18" s="16">
         <f>I17/Assumptions!$C$6</f>
         <v/>
       </c>

--- a/engine/swdy_study/SWDY_Valuation_Model_05082026_public.xlsx
+++ b/engine/swdy_study/SWDY_Valuation_Model_05082026_public.xlsx
@@ -37,8 +37,8 @@
     <numFmt numFmtId="166" formatCode="#,##0;(#,##0);&quot;-&quot;"/>
     <numFmt numFmtId="167" formatCode="#,##0.0;(#,##0.0);&quot;-&quot;"/>
     <numFmt numFmtId="168" formatCode="0.000"/>
-    <numFmt numFmtId="169" formatCode="0.00x"/>
-    <numFmt numFmtId="170" formatCode="0.0000"/>
+    <numFmt numFmtId="169" formatCode="0.0000"/>
+    <numFmt numFmtId="170" formatCode="0.00x"/>
   </numFmts>
   <fonts count="11">
     <font>
@@ -120,7 +120,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -149,17 +149,18 @@
     <xf numFmtId="167" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="8" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="170" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="170" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -807,7 +808,7 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>26.6% -&gt; 15.9% on the same easing calendar as the interest forecast; the terminal value is</t>
+          <t>26.9% -&gt; 15.9% on the same easing calendar as the interest forecast; the terminal value is</t>
         </is>
       </c>
     </row>
@@ -869,7 +870,7 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>Currency. EGP million unless stated. Spot EGP 105.20 (2026-08-05 close). Sheets: READ FIRST · Summary ·</t>
+          <t>Currency. EGP million unless stated. Spot EGP 130.00 (2026-09-03 close). Sheets: READ FIRST · Summary ·</t>
         </is>
       </c>
     </row>
@@ -1003,23 +1004,23 @@
       <c r="D5" s="24" t="n">
         <v>35961.076614</v>
       </c>
-      <c r="E5" s="30">
+      <c r="E5" s="31">
         <f>D5-DCF!B12+DCF!B8</f>
         <v/>
       </c>
-      <c r="F5" s="30">
+      <c r="F5" s="31">
         <f>E5-DCF!C12+DCF!C8</f>
         <v/>
       </c>
-      <c r="G5" s="30">
+      <c r="G5" s="31">
         <f>F5-DCF!D12+DCF!D8</f>
         <v/>
       </c>
-      <c r="H5" s="30">
+      <c r="H5" s="31">
         <f>G5-DCF!E12+DCF!E8</f>
         <v/>
       </c>
-      <c r="I5" s="30">
+      <c r="I5" s="31">
         <f>H5-DCF!F12+DCF!F8</f>
         <v/>
       </c>
@@ -1084,7 +1085,7 @@
       <c r="C9" s="24" t="n">
         <v>38180.002322</v>
       </c>
-      <c r="D9" s="30">
+      <c r="D9" s="31">
         <f>D11-D17</f>
         <v/>
       </c>
@@ -1095,13 +1096,13 @@
           <t>Total assets</t>
         </is>
       </c>
-      <c r="B10" s="31" t="n">
+      <c r="B10" s="32" t="n">
         <v>151448.654828</v>
       </c>
-      <c r="C10" s="31" t="n">
+      <c r="C10" s="32" t="n">
         <v>249527.138687</v>
       </c>
-      <c r="D10" s="31" t="n">
+      <c r="D10" s="32" t="n">
         <v>311099.090775</v>
       </c>
       <c r="E10" s="13" t="n"/>
@@ -1164,32 +1165,32 @@
           <t>Equity attributable to shareholders</t>
         </is>
       </c>
-      <c r="B14" s="31" t="n">
+      <c r="B14" s="32" t="n">
         <v>35724.466132</v>
       </c>
-      <c r="C14" s="31" t="n">
+      <c r="C14" s="32" t="n">
         <v>55274.913356</v>
       </c>
-      <c r="D14" s="31" t="n">
+      <c r="D14" s="32" t="n">
         <v>66870.86655000001</v>
       </c>
-      <c r="E14" s="31">
+      <c r="E14" s="32">
         <f>D14+'Income Statement'!E17*(1-Assumptions!$C$50)</f>
         <v/>
       </c>
-      <c r="F14" s="31">
+      <c r="F14" s="32">
         <f>E14+'Income Statement'!F17*(1-Assumptions!$C$50)</f>
         <v/>
       </c>
-      <c r="G14" s="31">
+      <c r="G14" s="32">
         <f>F14+'Income Statement'!G17*(1-Assumptions!$C$50)</f>
         <v/>
       </c>
-      <c r="H14" s="31">
+      <c r="H14" s="32">
         <f>G14+'Income Statement'!H17*(1-Assumptions!$C$50)</f>
         <v/>
       </c>
-      <c r="I14" s="31">
+      <c r="I14" s="32">
         <f>H14+'Income Statement'!I17*(1-Assumptions!$C$50)</f>
         <v/>
       </c>
@@ -1225,23 +1226,23 @@
       <c r="D16" s="24" t="n">
         <v>55852.53459999998</v>
       </c>
-      <c r="E16" s="30">
+      <c r="E16" s="31">
         <f>'Income Statement'!E5*Assumptions!$C$25</f>
         <v/>
       </c>
-      <c r="F16" s="30">
+      <c r="F16" s="31">
         <f>'Income Statement'!F5*Assumptions!$C$25</f>
         <v/>
       </c>
-      <c r="G16" s="30">
+      <c r="G16" s="31">
         <f>'Income Statement'!G5*Assumptions!$C$25</f>
         <v/>
       </c>
-      <c r="H16" s="30">
+      <c r="H16" s="31">
         <f>'Income Statement'!H5*Assumptions!$C$25</f>
         <v/>
       </c>
-      <c r="I16" s="30">
+      <c r="I16" s="31">
         <f>'Income Statement'!I5*Assumptions!$C$25</f>
         <v/>
       </c>
@@ -1252,33 +1253,33 @@
           <t>Net bank debt</t>
         </is>
       </c>
-      <c r="B17" s="31" t="n">
+      <c r="B17" s="32" t="n">
         <v>16214.447271</v>
       </c>
-      <c r="C17" s="31" t="n">
+      <c r="C17" s="32" t="n">
         <v>20902.939485</v>
       </c>
-      <c r="D17" s="31">
+      <c r="D17" s="32">
         <f>Assumptions!$C$43</f>
         <v/>
       </c>
-      <c r="E17" s="31">
+      <c r="E17" s="32">
         <f>D17-DCF!B14-'Income Statement'!E11*(1-Assumptions!$C$7)+Assumptions!$C$50*'Income Statement'!E17</f>
         <v/>
       </c>
-      <c r="F17" s="31">
+      <c r="F17" s="32">
         <f>E17-DCF!C14-'Income Statement'!F11*(1-Assumptions!$C$7)+Assumptions!$C$50*'Income Statement'!F17</f>
         <v/>
       </c>
-      <c r="G17" s="31">
+      <c r="G17" s="32">
         <f>F17-DCF!D14-'Income Statement'!G11*(1-Assumptions!$C$7)+Assumptions!$C$50*'Income Statement'!G17</f>
         <v/>
       </c>
-      <c r="H17" s="31">
+      <c r="H17" s="32">
         <f>G17-DCF!E14-'Income Statement'!H11*(1-Assumptions!$C$7)+Assumptions!$C$50*'Income Statement'!H17</f>
         <v/>
       </c>
-      <c r="I17" s="31">
+      <c r="I17" s="32">
         <f>H17-DCF!F14-'Income Statement'!I11*(1-Assumptions!$C$7)+Assumptions!$C$50*'Income Statement'!I17</f>
         <v/>
       </c>
@@ -1289,35 +1290,35 @@
           <t>Net debt / EBITDA</t>
         </is>
       </c>
-      <c r="B18" s="36">
+      <c r="B18" s="37">
         <f>B17/'Income Statement'!B7</f>
         <v/>
       </c>
-      <c r="C18" s="36">
+      <c r="C18" s="37">
         <f>C17/'Income Statement'!C7</f>
         <v/>
       </c>
-      <c r="D18" s="36">
+      <c r="D18" s="37">
         <f>D17/'Income Statement'!D7</f>
         <v/>
       </c>
-      <c r="E18" s="36">
+      <c r="E18" s="37">
         <f>E17/'Income Statement'!E7</f>
         <v/>
       </c>
-      <c r="F18" s="36">
+      <c r="F18" s="37">
         <f>F17/'Income Statement'!F7</f>
         <v/>
       </c>
-      <c r="G18" s="36">
+      <c r="G18" s="37">
         <f>G17/'Income Statement'!G7</f>
         <v/>
       </c>
-      <c r="H18" s="36">
+      <c r="H18" s="37">
         <f>H17/'Income Statement'!H7</f>
         <v/>
       </c>
-      <c r="I18" s="36">
+      <c r="I18" s="37">
         <f>I17/'Income Statement'!I7</f>
         <v/>
       </c>
@@ -1328,15 +1329,15 @@
           <t>Residual: other liabilities, provisions and deferred tax not shown separately (total assets less the lines above)</t>
         </is>
       </c>
-      <c r="B19" s="30">
+      <c r="B19" s="31">
         <f>B10-(B11+B12+B13+B14+B15)</f>
         <v/>
       </c>
-      <c r="C19" s="30">
+      <c r="C19" s="31">
         <f>C10-(C11+C12+C13+C14+C15)</f>
         <v/>
       </c>
-      <c r="D19" s="30">
+      <c r="D19" s="31">
         <f>D10-(D11+D12+D13+D14+D15)</f>
         <v/>
       </c>
@@ -1478,7 +1479,7 @@
           <t>Interest paid</t>
         </is>
       </c>
-      <c r="B6" s="30" t="inlineStr">
+      <c r="B6" s="31" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1493,7 +1494,7 @@
           <t>Income tax paid</t>
         </is>
       </c>
-      <c r="B7" s="30" t="inlineStr">
+      <c r="B7" s="31" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1508,7 +1509,7 @@
           <t>Operating cash flow after interest and tax</t>
         </is>
       </c>
-      <c r="B8" s="30" t="inlineStr">
+      <c r="B8" s="31" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1523,12 +1524,12 @@
           <t>NOPAT</t>
         </is>
       </c>
-      <c r="B9" s="30" t="inlineStr">
+      <c r="B9" s="31" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C9" s="30" t="inlineStr">
+      <c r="C9" s="31" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1560,12 +1561,12 @@
           <t>Add back depreciation and amortisation</t>
         </is>
       </c>
-      <c r="B10" s="30" t="inlineStr">
+      <c r="B10" s="31" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C10" s="30" t="inlineStr">
+      <c r="C10" s="31" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1630,12 +1631,12 @@
           <t>Change in working capital</t>
         </is>
       </c>
-      <c r="B12" s="30" t="inlineStr">
+      <c r="B12" s="31" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C12" s="30">
+      <c r="C12" s="31">
         <f>-('Balance Sheet'!D16-'Balance Sheet'!C16)</f>
         <v/>
       </c>
@@ -1666,33 +1667,33 @@
           <t>Free cash flow to the firm</t>
         </is>
       </c>
-      <c r="B13" s="31" t="inlineStr">
+      <c r="B13" s="32" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C13" s="31" t="inlineStr">
+      <c r="C13" s="32" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D13" s="31">
+      <c r="D13" s="32">
         <f>D9+D10+D11+D12</f>
         <v/>
       </c>
-      <c r="E13" s="31">
+      <c r="E13" s="32">
         <f>E9+E10+E11+E12</f>
         <v/>
       </c>
-      <c r="F13" s="31">
+      <c r="F13" s="32">
         <f>F9+F10+F11+F12</f>
         <v/>
       </c>
-      <c r="G13" s="31">
+      <c r="G13" s="32">
         <f>G9+G10+G11+G12</f>
         <v/>
       </c>
-      <c r="H13" s="31">
+      <c r="H13" s="32">
         <f>H9+H10+H11+H12</f>
         <v/>
       </c>
@@ -2051,17 +2052,17 @@
           <t>Free cash flow to the firm</t>
         </is>
       </c>
-      <c r="B11" s="30" t="inlineStr">
+      <c r="B11" s="31" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C11" s="30" t="inlineStr">
+      <c r="C11" s="31" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D11" s="30" t="inlineStr">
+      <c r="D11" s="31" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2132,12 +2133,12 @@
           <t>Invested capital</t>
         </is>
       </c>
-      <c r="B13" s="30" t="inlineStr">
+      <c r="B13" s="31" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C13" s="30" t="inlineStr">
+      <c r="C13" s="31" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2559,19 +2560,19 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>64.02326653453551</v>
+        <v>64.92380553045649</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>66.87332082657952</v>
+        <v>67.81454330477681</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>70.27596109226505</v>
+        <v>71.2657550153391</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>74.4401253255354</v>
+        <v>75.48936116950645</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>79.69527743111146</v>
+        <v>80.81952864869957</v>
       </c>
     </row>
     <row r="7">
@@ -2581,19 +2582,19 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>57.37629801344737</v>
+        <v>58.18280778459938</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>59.44490839625706</v>
+        <v>60.28097444263505</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>61.85495881829012</v>
+        <v>62.7254596302354</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>64.7211007280429</v>
+        <v>65.6325529341344</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>68.21578663977438</v>
+        <v>69.17717086762013</v>
       </c>
     </row>
     <row r="8">
@@ -2603,19 +2604,19 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>51.7708075360223</v>
+        <v>52.49799810153853</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>53.27390215434404</v>
+        <v>54.02258879276857</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>54.98535884474298</v>
+        <v>55.75852138598012</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>56.96810019655753</v>
+        <v>57.76961833972243</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>59.31322032826569</v>
+        <v>60.14827652865958</v>
       </c>
     </row>
     <row r="9">
@@ -2625,19 +2626,19 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>46.98207982326851</v>
+        <v>47.64148809789273</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>48.06820632030645</v>
+        <v>48.74316174823518</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>49.27676996088003</v>
+        <v>49.96902514555856</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>50.64136360909256</v>
+        <v>51.3531520126963</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>52.20910626312477</v>
+        <v>52.94333582385958</v>
       </c>
     </row>
     <row r="10">
@@ -2647,19 +2648,19 @@
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>42.84560782729903</v>
+        <v>43.44644775731468</v>
       </c>
       <c r="C10" s="7" t="n">
-        <v>43.61959366674767</v>
+        <v>44.23152271678764</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>44.45954899997528</v>
+        <v>45.08351233414617</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>45.3820571183214</v>
+        <v>46.01923749436355</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>46.40976788449724</v>
+        <v>47.06167257131559</v>
       </c>
     </row>
     <row r="12">
@@ -2673,27 +2674,27 @@
       <c r="A13" s="5" t="inlineStr"/>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>23.9%</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>25.1%</t>
+          <t>25.4%</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>26.6%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>28.1%</t>
+          <t>28.4%</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>29.9%</t>
         </is>
       </c>
     </row>
@@ -2704,19 +2705,19 @@
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>84.65984646706161</v>
+        <v>85.84545509208399</v>
       </c>
       <c r="C14" s="7" t="n">
-        <v>82.13279721284205</v>
+        <v>83.28726331486288</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>79.69527743111146</v>
+        <v>80.81952864869957</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>77.34332590623208</v>
+        <v>78.43825692508688</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>75.07319276143608</v>
+        <v>76.13966662860086</v>
       </c>
     </row>
     <row r="15">
@@ -2726,19 +2727,19 @@
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>72.52574844266042</v>
+        <v>73.5404678355972</v>
       </c>
       <c r="C15" s="7" t="n">
-        <v>70.3319852695824</v>
+        <v>71.31963462621358</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>68.21578663977438</v>
+        <v>69.17717086762013</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>66.17372628576796</v>
+        <v>67.10962173729665</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>64.20256050533408</v>
+        <v>65.11371611583073</v>
       </c>
     </row>
     <row r="16">
@@ -2748,19 +2749,19 @@
         </is>
       </c>
       <c r="B16" s="7" t="n">
-        <v>63.11573867848826</v>
+        <v>63.99790976465807</v>
       </c>
       <c r="C16" s="7" t="n">
-        <v>61.18033295945634</v>
+        <v>62.03859171613212</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>59.31322032826569</v>
+        <v>60.14827652865958</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>57.51138889928905</v>
+        <v>58.32392716970243</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>55.77198707016157</v>
+        <v>56.56266789121253</v>
       </c>
     </row>
     <row r="17">
@@ -2770,19 +2771,19 @@
         </is>
       </c>
       <c r="B17" s="7" t="n">
-        <v>55.60688154053267</v>
+        <v>56.3832632823887</v>
       </c>
       <c r="C17" s="7" t="n">
-        <v>53.87754330288151</v>
+        <v>54.63253200536953</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>52.20910626312477</v>
+        <v>52.94333582385958</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>50.59888878852414</v>
+        <v>51.31297067571722</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>49.04435177713601</v>
+        <v>49.73887592188827</v>
       </c>
     </row>
     <row r="18">
@@ -2792,19 +2793,19 @@
         </is>
       </c>
       <c r="B18" s="7" t="n">
-        <v>49.47730377942706</v>
+        <v>50.16731028865568</v>
       </c>
       <c r="C18" s="7" t="n">
-        <v>47.91609946481731</v>
+        <v>48.58676906627794</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>46.40976788449724</v>
+        <v>47.06167257131559</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>44.95589663617206</v>
+        <v>45.58958818858307</v>
       </c>
       <c r="F18" s="7" t="n">
-        <v>43.55220138111397</v>
+        <v>44.16821216991782</v>
       </c>
     </row>
     <row r="20">
@@ -2839,19 +2840,19 @@
         </is>
       </c>
       <c r="B22" s="7" t="n">
-        <v>92.05706087886328</v>
+        <v>93.45277355246162</v>
       </c>
       <c r="C22" s="7" t="n">
-        <v>73.37265613726478</v>
+        <v>74.44674244752112</v>
       </c>
       <c r="D22" s="7" t="n">
-        <v>59.31322032826569</v>
+        <v>60.14827652865958</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>51.92216787250401</v>
+        <v>52.63301422037497</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>45.39154463312268</v>
+        <v>45.99373037705359</v>
       </c>
       <c r="H22" s="16">
         <f>MAX(B22:F22)-MIN(B22:F22)</f>
@@ -2865,19 +2866,19 @@
         </is>
       </c>
       <c r="B23" s="7" t="n">
-        <v>53.41908966035297</v>
+        <v>50.79365382947766</v>
       </c>
       <c r="C23" s="7" t="n">
-        <v>55.48217612662315</v>
+        <v>52.69688996099238</v>
       </c>
       <c r="D23" s="7" t="n">
-        <v>59.60834905916349</v>
+        <v>56.50336222402186</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>64.76606522483894</v>
+        <v>61.26145255280872</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>69.92378139051441</v>
+        <v>66.01954288159557</v>
       </c>
       <c r="H23" s="16">
         <f>MAX(B23:F23)-MIN(B23:F23)</f>
@@ -2891,19 +2892,19 @@
         </is>
       </c>
       <c r="B24" s="7" t="n">
-        <v>31.52261532145548</v>
+        <v>29.48174706762489</v>
       </c>
       <c r="C24" s="7" t="n">
-        <v>43.50239572403932</v>
+        <v>41.08931851430866</v>
       </c>
       <c r="D24" s="7" t="n">
-        <v>55.48217612662315</v>
+        <v>52.69688996099238</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>67.46195652920696</v>
+        <v>64.30446140767616</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>79.4417369317908</v>
+        <v>75.91203285435989</v>
       </c>
       <c r="H24" s="16">
         <f>MAX(B24:F24)-MIN(B24:F24)</f>
@@ -2917,19 +2918,19 @@
         </is>
       </c>
       <c r="B25" s="7" t="n">
-        <v>52.3875464272179</v>
+        <v>49.8420357637203</v>
       </c>
       <c r="C25" s="7" t="n">
-        <v>53.9348612769205</v>
+        <v>51.26946286235632</v>
       </c>
       <c r="D25" s="7" t="n">
-        <v>55.48217612662315</v>
+        <v>52.69688996099238</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>57.02949097632575</v>
+        <v>54.12431705962842</v>
       </c>
       <c r="F25" s="7" t="n">
-        <v>58.57680582602841</v>
+        <v>55.55174415826449</v>
       </c>
       <c r="H25" s="16">
         <f>MAX(B25:F25)-MIN(B25:F25)</f>
@@ -2943,19 +2944,19 @@
         </is>
       </c>
       <c r="B26" s="7" t="n">
-        <v>62.73597456572764</v>
+        <v>59.90563209825564</v>
       </c>
       <c r="C26" s="7" t="n">
-        <v>58.98400985584599</v>
+        <v>56.17697237208499</v>
       </c>
       <c r="D26" s="7" t="n">
-        <v>55.48217612662315</v>
+        <v>52.69688996099238</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>51.48008043608273</v>
+        <v>48.71965291974369</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>47.72811572620108</v>
+        <v>44.99099319357304</v>
       </c>
       <c r="H26" s="16">
         <f>MAX(B26:F26)-MIN(B26:F26)</f>
@@ -2969,19 +2970,19 @@
         </is>
       </c>
       <c r="B27" s="7" t="n">
-        <v>48.93607870871411</v>
+        <v>49.62272921986233</v>
       </c>
       <c r="C27" s="7" t="n">
-        <v>55.75099900441143</v>
+        <v>56.53511112692783</v>
       </c>
       <c r="D27" s="7" t="n">
-        <v>59.31322032826569</v>
+        <v>60.14827652865958</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>66.23549176702268</v>
+        <v>67.16954483010554</v>
       </c>
       <c r="F27" s="7" t="n">
-        <v>69.38083959580605</v>
+        <v>70.35987494105883</v>
       </c>
       <c r="H27" s="16">
         <f>MAX(B27:F27)-MIN(B27:F27)</f>
@@ -2995,19 +2996,19 @@
         </is>
       </c>
       <c r="B28" s="7" t="n">
-        <v>51.7708075360223</v>
+        <v>52.49799810153853</v>
       </c>
       <c r="C28" s="7" t="n">
-        <v>53.27390215434404</v>
+        <v>54.02258879276857</v>
       </c>
       <c r="D28" s="7" t="n">
-        <v>54.98535884474298</v>
+        <v>55.75852138598012</v>
       </c>
       <c r="E28" s="7" t="n">
-        <v>56.96810019655753</v>
+        <v>57.76961833972243</v>
       </c>
       <c r="F28" s="7" t="n">
-        <v>59.31322032826569</v>
+        <v>60.14827652865958</v>
       </c>
       <c r="H28" s="16">
         <f>MAX(B28:F28)-MIN(B28:F28)</f>
@@ -3472,35 +3473,35 @@
           <t>Net debt / EBITDA</t>
         </is>
       </c>
-      <c r="B14" s="36">
+      <c r="B14" s="37">
         <f>'Balance Sheet'!B18</f>
         <v/>
       </c>
-      <c r="C14" s="36">
+      <c r="C14" s="37">
         <f>'Balance Sheet'!C18</f>
         <v/>
       </c>
-      <c r="D14" s="36">
+      <c r="D14" s="37">
         <f>'Balance Sheet'!D18</f>
         <v/>
       </c>
-      <c r="E14" s="36">
+      <c r="E14" s="37">
         <f>'Balance Sheet'!E18</f>
         <v/>
       </c>
-      <c r="F14" s="36">
+      <c r="F14" s="37">
         <f>'Balance Sheet'!F18</f>
         <v/>
       </c>
-      <c r="G14" s="36">
+      <c r="G14" s="37">
         <f>'Balance Sheet'!G18</f>
         <v/>
       </c>
-      <c r="H14" s="36">
+      <c r="H14" s="37">
         <f>'Balance Sheet'!H18</f>
         <v/>
       </c>
-      <c r="I14" s="36">
+      <c r="I14" s="37">
         <f>'Balance Sheet'!I18</f>
         <v/>
       </c>
@@ -3511,36 +3512,36 @@
           <t>Interest cover (EBIT / net interest)</t>
         </is>
       </c>
-      <c r="B15" s="36" t="inlineStr">
+      <c r="B15" s="37" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C15" s="36">
+      <c r="C15" s="37">
         <f>-'Income Statement'!C10/'Income Statement'!C11</f>
         <v/>
       </c>
-      <c r="D15" s="36">
+      <c r="D15" s="37">
         <f>-'Income Statement'!D10/'Income Statement'!D11</f>
         <v/>
       </c>
-      <c r="E15" s="36">
+      <c r="E15" s="37">
         <f>-'Income Statement'!E10/'Income Statement'!E11</f>
         <v/>
       </c>
-      <c r="F15" s="36">
+      <c r="F15" s="37">
         <f>-'Income Statement'!F10/'Income Statement'!F11</f>
         <v/>
       </c>
-      <c r="G15" s="36">
+      <c r="G15" s="37">
         <f>-'Income Statement'!G10/'Income Statement'!G11</f>
         <v/>
       </c>
-      <c r="H15" s="36">
+      <c r="H15" s="37">
         <f>-'Income Statement'!H10/'Income Statement'!H11</f>
         <v/>
       </c>
-      <c r="I15" s="36">
+      <c r="I15" s="37">
         <f>-'Income Statement'!I10/'Income Statement'!I11</f>
         <v/>
       </c>
@@ -3787,12 +3788,12 @@
           <t>Saudi Arabia</t>
         </is>
       </c>
-      <c r="C5" s="41" t="inlineStr">
+      <c r="C5" s="42" t="inlineStr">
         <is>
           <t>nearest listed regional cable manufacturer</t>
         </is>
       </c>
-      <c r="D5" s="41" t="inlineStr">
+      <c r="D5" s="42" t="inlineStr">
         <is>
           <t>far smaller, no contracting arm, lighter balance sheet, pegged currency</t>
         </is>
@@ -3809,12 +3810,12 @@
           <t>Egypt</t>
         </is>
       </c>
-      <c r="C6" s="41" t="inlineStr">
+      <c r="C6" s="42" t="inlineStr">
         <is>
           <t>the only other listed Egyptian cable manufacturer</t>
         </is>
       </c>
-      <c r="D6" s="41" t="inlineStr">
+      <c r="D6" s="42" t="inlineStr">
         <is>
           <t>much smaller, domestic, heavily levered, currently loss-making</t>
         </is>
@@ -3831,12 +3832,12 @@
           <t>Europe</t>
         </is>
       </c>
-      <c r="C7" s="41" t="inlineStr">
+      <c r="C7" s="42" t="inlineStr">
         <is>
           <t>closest match on business model — cables plus projects</t>
         </is>
       </c>
-      <c r="D7" s="41" t="inlineStr">
+      <c r="D7" s="42" t="inlineStr">
         <is>
           <t>developed-market cost of capital; no convertibility risk</t>
         </is>
@@ -3853,12 +3854,12 @@
           <t>Gulf and North Africa</t>
         </is>
       </c>
-      <c r="C8" s="41" t="inlineStr">
+      <c r="C8" s="42" t="inlineStr">
         <is>
           <t>the right frame for the roughly 32% that is the Constructions and infrastructure segment</t>
         </is>
       </c>
-      <c r="D8" s="41" t="inlineStr">
+      <c r="D8" s="42" t="inlineStr">
         <is>
           <t>project accounting and backlog quality are not comparable</t>
         </is>
@@ -3882,7 +3883,7 @@
           <t>Trailing enterprise value / EBITDA</t>
         </is>
       </c>
-      <c r="B11" s="34">
+      <c r="B11" s="35">
         <f>'Relative &amp; Normalized'!C13</f>
         <v/>
       </c>
@@ -3893,7 +3894,7 @@
           <t>Trailing price / earnings</t>
         </is>
       </c>
-      <c r="B12" s="34">
+      <c r="B12" s="35">
         <f>'Relative &amp; Normalized'!C14</f>
         <v/>
       </c>
@@ -3904,7 +3905,7 @@
           <t>Trailing price / book</t>
         </is>
       </c>
-      <c r="B13" s="34">
+      <c r="B13" s="35">
         <f>'Relative &amp; Normalized'!C15</f>
         <v/>
       </c>
@@ -3915,7 +3916,7 @@
           <t>Justified enterprise value / EBITDA applied</t>
         </is>
       </c>
-      <c r="B14" s="34">
+      <c r="B14" s="35">
         <f>'Relative &amp; Normalized'!C6</f>
         <v/>
       </c>
@@ -3926,7 +3927,7 @@
           <t>Justified price / earnings applied</t>
         </is>
       </c>
-      <c r="B15" s="34">
+      <c r="B15" s="35">
         <f>'Relative &amp; Normalized'!C27</f>
         <v/>
       </c>
@@ -4014,14 +4015,14 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>19.89441449632232</v>
+        <v>19.63802419176771</v>
       </c>
       <c r="C5" s="8">
         <f>DCF!C62</f>
         <v/>
       </c>
       <c r="D5" s="7" t="n">
-        <v>104.9620537972264</v>
+        <v>101.3067584343183</v>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
@@ -4230,7 +4231,7 @@
       </c>
       <c r="B16" s="13" t="n"/>
       <c r="C16" s="18" t="n">
-        <v>105.2</v>
+        <v>130</v>
       </c>
       <c r="D16" s="13" t="n"/>
       <c r="E16" s="13" t="n"/>
@@ -4427,7 +4428,7 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>19.89441449632232</v>
+        <v>19.63802419176771</v>
       </c>
     </row>
     <row r="7">
@@ -4442,7 +4443,7 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>104.9620537972264</v>
+        <v>101.3067584343183</v>
       </c>
     </row>
     <row r="8">
@@ -4530,7 +4531,7 @@
       </c>
       <c r="C16" s="22" t="inlineStr">
         <is>
-          <t>26.6% → 15.9%</t>
+          <t>26.9% → 15.9%</t>
         </is>
       </c>
     </row>
@@ -4541,7 +4542,7 @@
         </is>
       </c>
       <c r="C17" s="23">
-        <f>(1-Assumptions!$C$59)*(Assumptions!$C$56+Assumptions!$C$33*Assumptions!$C$57)+Assumptions!$C$59*Assumptions!$C$58*(1-Assumptions!$C$7)</f>
+        <f>(1-Assumptions!$C$65)*(Assumptions!$C$62+Assumptions!$C$33*Assumptions!$C$63)+Assumptions!$C$65*Assumptions!$C$64*(1-Assumptions!$C$7)</f>
         <v/>
       </c>
     </row>
@@ -4552,7 +4553,7 @@
         </is>
       </c>
       <c r="C18" s="7" t="n">
-        <v>69.57809227740921</v>
+        <v>70.84778269949645</v>
       </c>
     </row>
     <row r="19">
@@ -4612,13 +4613,13 @@
         </is>
       </c>
       <c r="C23" s="7" t="n">
-        <v>148.4077409306208</v>
+        <v>151.4223547712553</v>
       </c>
       <c r="D23" s="7" t="n">
-        <v>108.8662301594048</v>
+        <v>111.0875245682934</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>187.9492517018369</v>
+        <v>191.7571849742172</v>
       </c>
     </row>
     <row r="24">
@@ -4633,13 +4634,13 @@
         </is>
       </c>
       <c r="C24" s="7" t="n">
-        <v>72.81006662300985</v>
+        <v>74.30796795435184</v>
       </c>
       <c r="D24" s="7" t="n">
-        <v>36.13831647623267</v>
+        <v>36.90047424542561</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>65.71584535779077</v>
+        <v>67.07141566856639</v>
       </c>
     </row>
     <row r="25">
@@ -4654,13 +4655,13 @@
         </is>
       </c>
       <c r="C25" s="7" t="n">
-        <v>54.45131359842825</v>
+        <v>55.21683864604976</v>
       </c>
       <c r="D25" s="7" t="n">
-        <v>46.88400987822836</v>
+        <v>47.64716300797847</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>69.57809227740921</v>
+        <v>70.84778269949645</v>
       </c>
     </row>
     <row r="26">
@@ -4688,7 +4689,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H65"/>
+  <dimension ref="A1:H71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -4775,7 +4776,7 @@
         </is>
       </c>
       <c r="C5" s="7" t="n">
-        <v>105.2</v>
+        <v>130</v>
       </c>
     </row>
     <row r="6">
@@ -5353,17 +5354,17 @@
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
         <is>
-          <t>Days from the 31-Dec-2025 valuation date to the 5-Aug-2026 anchor</t>
+          <t>Days from the 31-Dec-2025 valuation date to the 3-Sep-2026 anchor</t>
         </is>
       </c>
       <c r="C53" s="24" t="n">
-        <v>217</v>
+        <v>246</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>Currency-of-discounting alternative</t>
+          <t>Terminal construction — the sanctioned one, never g x IC</t>
         </is>
       </c>
       <c r="B55" s="13" t="n"/>
@@ -5377,94 +5378,148 @@
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
         <is>
-          <t>US dollar risk-free rate</t>
+          <t>Terminal inflation (house Egyptian macro path)</t>
         </is>
       </c>
       <c r="C56" s="21" t="n">
-        <v>0.043</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="6" t="inlineStr">
         <is>
-          <t>Hard-currency-leg equity risk premium</t>
-        </is>
-      </c>
-      <c r="C57" s="21" t="n">
-        <v>0.075</v>
+          <t>DISCLOSED useful life, derived by identity from note 17 (years)</t>
+        </is>
+      </c>
+      <c r="C57" s="27" t="n">
+        <v>17.2627</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
         <is>
-          <t>US dollar cost of debt</t>
-        </is>
-      </c>
-      <c r="C58" s="21" t="n">
-        <v>0.065</v>
+          <t>Terminal working-capital base (EGP mn, last explicit year)</t>
+        </is>
+      </c>
+      <c r="C58" s="24" t="n">
+        <v>110489.8413121987</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="6" t="inlineStr">
         <is>
-          <t>Debt weight, USD leg</t>
+          <t>Employees' statutory share of profit (mean of FY2024, FY2025, H1-2026)</t>
         </is>
       </c>
       <c r="C59" s="21" t="n">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="6" t="inlineStr">
-        <is>
-          <t>Terminal growth of the USD leg</t>
-        </is>
-      </c>
-      <c r="C60" s="21" t="n">
-        <v>0.035</v>
-      </c>
+        <v>0.1219271916645494</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="10" t="inlineStr">
+        <is>
+          <t>Currency-of-discounting alternative</t>
+        </is>
+      </c>
+      <c r="B61" s="13" t="n"/>
+      <c r="C61" s="13" t="n"/>
+      <c r="D61" s="13" t="n"/>
+      <c r="E61" s="13" t="n"/>
+      <c r="F61" s="13" t="n"/>
+      <c r="G61" s="13" t="n"/>
+      <c r="H61" s="13" t="n"/>
     </row>
     <row r="62">
-      <c r="A62" s="10" t="inlineStr">
-        <is>
-          <t>Lens inputs</t>
-        </is>
-      </c>
-      <c r="B62" s="13" t="n"/>
-      <c r="C62" s="13" t="n"/>
-      <c r="D62" s="13" t="n"/>
-      <c r="E62" s="13" t="n"/>
-      <c r="F62" s="13" t="n"/>
-      <c r="G62" s="13" t="n"/>
-      <c r="H62" s="13" t="n"/>
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t>US dollar risk-free rate</t>
+        </is>
+      </c>
+      <c r="C62" s="21" t="n">
+        <v>0.043</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="6" t="inlineStr">
         <is>
-          <t>Justified EV/EBITDA</t>
-        </is>
-      </c>
-      <c r="C63" s="27" t="n">
-        <v>6.5</v>
+          <t>Hard-currency-leg equity risk premium</t>
+        </is>
+      </c>
+      <c r="C63" s="21" t="n">
+        <v>0.075</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="6" t="inlineStr">
         <is>
-          <t>Justified price/earnings</t>
-        </is>
-      </c>
-      <c r="C64" s="27" t="n">
-        <v>9</v>
+          <t>US dollar cost of debt</t>
+        </is>
+      </c>
+      <c r="C64" s="21" t="n">
+        <v>0.065</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="6" t="inlineStr">
         <is>
+          <t>Debt weight, USD leg</t>
+        </is>
+      </c>
+      <c r="C65" s="21" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t>Terminal growth of the USD leg</t>
+        </is>
+      </c>
+      <c r="C66" s="21" t="n">
+        <v>0.035</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="10" t="inlineStr">
+        <is>
+          <t>Lens inputs</t>
+        </is>
+      </c>
+      <c r="B68" s="13" t="n"/>
+      <c r="C68" s="13" t="n"/>
+      <c r="D68" s="13" t="n"/>
+      <c r="E68" s="13" t="n"/>
+      <c r="F68" s="13" t="n"/>
+      <c r="G68" s="13" t="n"/>
+      <c r="H68" s="13" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t>Justified EV/EBITDA</t>
+        </is>
+      </c>
+      <c r="C69" s="28" t="n">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="6" t="inlineStr">
+        <is>
+          <t>Justified price/earnings</t>
+        </is>
+      </c>
+      <c r="C70" s="28" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="6" t="inlineStr">
+        <is>
           <t>Sustainable return on equity</t>
         </is>
       </c>
-      <c r="C65" s="21" t="n">
+      <c r="C71" s="21" t="n">
         <v>0.235</v>
       </c>
     </row>
@@ -5479,7 +5534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -5553,11 +5608,11 @@
           <t>Enterprise value</t>
         </is>
       </c>
-      <c r="C7" s="28">
+      <c r="C7" s="29">
         <f>C5+C6</f>
         <v/>
       </c>
-      <c r="D7" s="29">
+      <c r="D7" s="30">
         <f>C7/Assumptions!$C$6</f>
         <v/>
       </c>
@@ -5598,7 +5653,7 @@
           <t>Equity before minority interests</t>
         </is>
       </c>
-      <c r="C10" s="30">
+      <c r="C10" s="31">
         <f>C7+C8+C9</f>
         <v/>
       </c>
@@ -5613,8 +5668,8 @@
           <t>Less minority interests at their share of group profit</t>
         </is>
       </c>
-      <c r="C11" s="30">
-        <f>-C10*$C$15</f>
+      <c r="C11" s="31">
+        <f>-C10*$C$17</f>
         <v/>
       </c>
       <c r="D11" s="16">
@@ -5623,40 +5678,66 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="13" t="inlineStr">
-        <is>
-          <t>Equity attributable to shareholders</t>
-        </is>
-      </c>
-      <c r="B12" s="13" t="n"/>
-      <c r="C12" s="31">
-        <f>C10+C11</f>
-        <v/>
-      </c>
-      <c r="D12" s="32">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Less the employees' statutory share of profit</t>
+        </is>
+      </c>
+      <c r="C12" s="29">
+        <f>-(C10+C11)*$C$18</f>
+        <v/>
+      </c>
+      <c r="D12" s="30">
         <f>C12/Assumptions!$C$6</f>
         <v/>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>Terminal value as a share of enterprise value</t>
-        </is>
-      </c>
-      <c r="C14" s="17">
-        <f>DCF!C28</f>
+    <row r="13">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>Equity attributable to ordinary shareholders</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="n"/>
+      <c r="C13" s="32">
+        <f>C10+C11+C12</f>
+        <v/>
+      </c>
+      <c r="D13" s="33">
+        <f>C13/Assumptions!$C$6</f>
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
+          <t>Terminal value as a share of enterprise value</t>
+        </is>
+      </c>
+      <c r="C15" s="17">
+        <f>DCF!C28</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
           <t>Minority share of group profit</t>
         </is>
       </c>
-      <c r="C15" s="9">
+      <c r="C17" s="9">
         <f>(Assumptions!$C$46-Assumptions!$C$47)/Assumptions!$C$46</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Employees' statutory share of profit — an appropriation disclosed only in the earnings-per-share note, below profit attributable to owners</t>
+        </is>
+      </c>
+      <c r="C18" s="17">
+        <f>Assumptions!$C$59</f>
         <v/>
       </c>
     </row>
@@ -5856,7 +5937,7 @@
           <t>Total revenue</t>
         </is>
       </c>
-      <c r="B8" s="33">
+      <c r="B8" s="34">
         <f>SUM(B5:B7)</f>
         <v/>
       </c>
@@ -5865,23 +5946,23 @@
         <v/>
       </c>
       <c r="D8" s="13" t="n"/>
-      <c r="E8" s="33">
+      <c r="E8" s="34">
         <f>SUM(E5:E7)</f>
         <v/>
       </c>
-      <c r="F8" s="33">
+      <c r="F8" s="34">
         <f>SUM(F5:F7)</f>
         <v/>
       </c>
-      <c r="G8" s="33">
+      <c r="G8" s="34">
         <f>SUM(G5:G7)</f>
         <v/>
       </c>
-      <c r="H8" s="33">
+      <c r="H8" s="34">
         <f>SUM(H5:H7)</f>
         <v/>
       </c>
-      <c r="I8" s="33">
+      <c r="I8" s="34">
         <f>SUM(I5:I7)</f>
         <v/>
       </c>
@@ -5990,23 +6071,23 @@
           <t>Group segment profit</t>
         </is>
       </c>
-      <c r="B14" s="33">
+      <c r="B14" s="34">
         <f>SUM(B11:B13)</f>
         <v/>
       </c>
-      <c r="C14" s="33">
+      <c r="C14" s="34">
         <f>SUM(C11:C13)</f>
         <v/>
       </c>
-      <c r="D14" s="33">
+      <c r="D14" s="34">
         <f>SUM(D11:D13)</f>
         <v/>
       </c>
-      <c r="E14" s="33">
+      <c r="E14" s="34">
         <f>SUM(E11:E13)</f>
         <v/>
       </c>
-      <c r="F14" s="33">
+      <c r="F14" s="34">
         <f>SUM(F11:F13)</f>
         <v/>
       </c>
@@ -6076,23 +6157,23 @@
           <t>Cables and its accessories</t>
         </is>
       </c>
-      <c r="B18" s="30">
+      <c r="B18" s="31">
         <f>B11-Assumptions!$B$22*E5</f>
         <v/>
       </c>
-      <c r="C18" s="30">
+      <c r="C18" s="31">
         <f>C11-Assumptions!$C$22*F5</f>
         <v/>
       </c>
-      <c r="D18" s="30">
+      <c r="D18" s="31">
         <f>D11-Assumptions!$D$22*G5</f>
         <v/>
       </c>
-      <c r="E18" s="30">
+      <c r="E18" s="31">
         <f>E11-Assumptions!$E$22*H5</f>
         <v/>
       </c>
-      <c r="F18" s="30">
+      <c r="F18" s="31">
         <f>F11-Assumptions!$F$22*I5</f>
         <v/>
       </c>
@@ -6103,23 +6184,23 @@
           <t>Constructions and infrastructure</t>
         </is>
       </c>
-      <c r="B19" s="30">
+      <c r="B19" s="31">
         <f>B12-Assumptions!$B$22*E6</f>
         <v/>
       </c>
-      <c r="C19" s="30">
+      <c r="C19" s="31">
         <f>C12-Assumptions!$C$22*F6</f>
         <v/>
       </c>
-      <c r="D19" s="30">
+      <c r="D19" s="31">
         <f>D12-Assumptions!$D$22*G6</f>
         <v/>
       </c>
-      <c r="E19" s="30">
+      <c r="E19" s="31">
         <f>E12-Assumptions!$E$22*H6</f>
         <v/>
       </c>
-      <c r="F19" s="30">
+      <c r="F19" s="31">
         <f>F12-Assumptions!$F$22*I6</f>
         <v/>
       </c>
@@ -6130,23 +6211,23 @@
           <t>Electrical products and digital solutions</t>
         </is>
       </c>
-      <c r="B20" s="30">
+      <c r="B20" s="31">
         <f>B13-Assumptions!$B$22*E7</f>
         <v/>
       </c>
-      <c r="C20" s="30">
+      <c r="C20" s="31">
         <f>C13-Assumptions!$C$22*F7</f>
         <v/>
       </c>
-      <c r="D20" s="30">
+      <c r="D20" s="31">
         <f>D13-Assumptions!$D$22*G7</f>
         <v/>
       </c>
-      <c r="E20" s="30">
+      <c r="E20" s="31">
         <f>E13-Assumptions!$E$22*H7</f>
         <v/>
       </c>
-      <c r="F20" s="30">
+      <c r="F20" s="31">
         <f>F13-Assumptions!$F$22*I7</f>
         <v/>
       </c>
@@ -6157,23 +6238,23 @@
           <t>Group EBIT</t>
         </is>
       </c>
-      <c r="B21" s="33">
+      <c r="B21" s="34">
         <f>SUM(B18:B20)</f>
         <v/>
       </c>
-      <c r="C21" s="33">
+      <c r="C21" s="34">
         <f>SUM(C18:C20)</f>
         <v/>
       </c>
-      <c r="D21" s="33">
+      <c r="D21" s="34">
         <f>SUM(D18:D20)</f>
         <v/>
       </c>
-      <c r="E21" s="33">
+      <c r="E21" s="34">
         <f>SUM(E18:E20)</f>
         <v/>
       </c>
-      <c r="F21" s="33">
+      <c r="F21" s="34">
         <f>SUM(F18:F20)</f>
         <v/>
       </c>
@@ -6184,23 +6265,23 @@
           <t>Add back depreciation and amortisation</t>
         </is>
       </c>
-      <c r="B22" s="30">
+      <c r="B22" s="31">
         <f>Assumptions!$C$27*E8</f>
         <v/>
       </c>
-      <c r="C22" s="30">
+      <c r="C22" s="31">
         <f>Assumptions!$C$27*F8</f>
         <v/>
       </c>
-      <c r="D22" s="30">
+      <c r="D22" s="31">
         <f>Assumptions!$C$27*G8</f>
         <v/>
       </c>
-      <c r="E22" s="30">
+      <c r="E22" s="31">
         <f>Assumptions!$C$27*H8</f>
         <v/>
       </c>
-      <c r="F22" s="30">
+      <c r="F22" s="31">
         <f>Assumptions!$C$27*I8</f>
         <v/>
       </c>
@@ -6211,23 +6292,23 @@
           <t>Group EBITDA</t>
         </is>
       </c>
-      <c r="B23" s="33">
+      <c r="B23" s="34">
         <f>B21+B22</f>
         <v/>
       </c>
-      <c r="C23" s="33">
+      <c r="C23" s="34">
         <f>C21+C22</f>
         <v/>
       </c>
-      <c r="D23" s="33">
+      <c r="D23" s="34">
         <f>D21+D22</f>
         <v/>
       </c>
-      <c r="E23" s="33">
+      <c r="E23" s="34">
         <f>E21+E22</f>
         <v/>
       </c>
-      <c r="F23" s="33">
+      <c r="F23" s="34">
         <f>F21+F22</f>
         <v/>
       </c>
@@ -6327,8 +6408,8 @@
           <t>Justified enterprise value / EBITDA</t>
         </is>
       </c>
-      <c r="C6" s="34">
-        <f>Assumptions!$C$63</f>
+      <c r="C6" s="35">
+        <f>Assumptions!$C$69</f>
         <v/>
       </c>
     </row>
@@ -6338,7 +6419,7 @@
           <t>Implied enterprise value AS AT end-FY2027 (EGP mn)</t>
         </is>
       </c>
-      <c r="C7" s="30">
+      <c r="C7" s="31">
         <f>C5*C6</f>
         <v/>
       </c>
@@ -6349,7 +6430,7 @@
           <t>Discount factor back to the valuation date (year-2)</t>
         </is>
       </c>
-      <c r="C8" s="35">
+      <c r="C8" s="36">
         <f>DCF!C16</f>
         <v/>
       </c>
@@ -6371,7 +6452,7 @@
           <t>Implied enterprise value at 31-Dec-2025 (EGP mn)</t>
         </is>
       </c>
-      <c r="C10" s="30">
+      <c r="C10" s="31">
         <f>C7*C8+C9</f>
         <v/>
       </c>
@@ -6383,8 +6464,8 @@
         </is>
       </c>
       <c r="B11" s="13" t="n"/>
-      <c r="C11" s="32">
-        <f>((C10-Assumptions!$C$43+Assumptions!$C$44)*(1-'SOTP Bridge'!$C$15)/Assumptions!$C$6)*DCF!$C$61-Assumptions!$C$49</f>
+      <c r="C11" s="33">
+        <f>((C10-Assumptions!$C$43+Assumptions!$C$44)*(1-'SOTP Bridge'!$C$17)*(1-'SOTP Bridge'!$C$18)/Assumptions!$C$6)*DCF!$C$61-Assumptions!$C$49</f>
         <v/>
       </c>
     </row>
@@ -6395,11 +6476,11 @@
         </is>
       </c>
       <c r="C12" s="16">
-        <f>((5.5*C5*C8+C9-Assumptions!$C$43+Assumptions!$C$44)*(1-'SOTP Bridge'!$C$15)/Assumptions!$C$6)*DCF!$C$61-Assumptions!$C$49</f>
+        <f>((5.5*C5*C8+C9-Assumptions!$C$43+Assumptions!$C$44)*(1-'SOTP Bridge'!$C$17)*(1-'SOTP Bridge'!$C$18)/Assumptions!$C$6)*DCF!$C$61-Assumptions!$C$49</f>
         <v/>
       </c>
       <c r="D12" s="16">
-        <f>((8.0*C5*C8+C9-Assumptions!$C$43+Assumptions!$C$44)*(1-'SOTP Bridge'!$C$15)/Assumptions!$C$6)*DCF!$C$61-Assumptions!$C$49</f>
+        <f>((8.0*C5*C8+C9-Assumptions!$C$43+Assumptions!$C$44)*(1-'SOTP Bridge'!$C$17)*(1-'SOTP Bridge'!$C$18)/Assumptions!$C$6)*DCF!$C$61-Assumptions!$C$49</f>
         <v/>
       </c>
     </row>
@@ -6409,7 +6490,7 @@
           <t>Trailing enterprise value / EBITDA</t>
         </is>
       </c>
-      <c r="C13" s="36">
+      <c r="C13" s="37">
         <f>((Assumptions!$C$5*Assumptions!$C$6)+Assumptions!$C$43)/'Income Statement'!D7</f>
         <v/>
       </c>
@@ -6420,7 +6501,7 @@
           <t>Trailing price / earnings</t>
         </is>
       </c>
-      <c r="C14" s="36">
+      <c r="C14" s="37">
         <f>Assumptions!$C$5/'Income Statement'!D18</f>
         <v/>
       </c>
@@ -6431,7 +6512,7 @@
           <t>Trailing price / book</t>
         </is>
       </c>
-      <c r="C15" s="36">
+      <c r="C15" s="37">
         <f>Assumptions!$C$5/C31</f>
         <v/>
       </c>
@@ -6442,7 +6523,7 @@
           <t>Net bank debt / EBITDA</t>
         </is>
       </c>
-      <c r="C16" s="36">
+      <c r="C16" s="37">
         <f>Assumptions!$C$43/'Income Statement'!D7</f>
         <v/>
       </c>
@@ -6487,7 +6568,7 @@
           <t>Normalised EBITDA (EGP mn)</t>
         </is>
       </c>
-      <c r="C21" s="30">
+      <c r="C21" s="31">
         <f>C19*C20</f>
         <v/>
       </c>
@@ -6498,7 +6579,7 @@
           <t>Normalised EBIT (EGP mn)</t>
         </is>
       </c>
-      <c r="C22" s="30">
+      <c r="C22" s="31">
         <f>C21-C19*Assumptions!$C$27</f>
         <v/>
       </c>
@@ -6531,8 +6612,8 @@
           <t>Normalised attributable earnings (EGP mn)</t>
         </is>
       </c>
-      <c r="C25" s="30">
-        <f>(C22+C23+C24)*(1-Assumptions!$C$7)*(1-'SOTP Bridge'!$C$15)</f>
+      <c r="C25" s="31">
+        <f>(C22+C23+C24)*(1-Assumptions!$C$7)*(1-'SOTP Bridge'!$C$17)*(1-'SOTP Bridge'!$C$18)</f>
         <v/>
       </c>
     </row>
@@ -6553,8 +6634,8 @@
           <t>Justified price / earnings</t>
         </is>
       </c>
-      <c r="C27" s="36">
-        <f>Assumptions!$C$64</f>
+      <c r="C27" s="37">
+        <f>Assumptions!$C$70</f>
         <v/>
       </c>
     </row>
@@ -6565,7 +6646,7 @@
         </is>
       </c>
       <c r="B28" s="13" t="n"/>
-      <c r="C28" s="32">
+      <c r="C28" s="33">
         <f>C26*C27*DCF!$C$61-Assumptions!$C$49</f>
         <v/>
       </c>
@@ -6613,7 +6694,7 @@
         </is>
       </c>
       <c r="C32" s="9">
-        <f>Assumptions!$C$65</f>
+        <f>Assumptions!$C$71</f>
         <v/>
       </c>
     </row>
@@ -6645,7 +6726,7 @@
           <t>Justified price / book</t>
         </is>
       </c>
-      <c r="C35" s="36">
+      <c r="C35" s="37">
         <f>(C32-Assumptions!$C$40)/(C34-Assumptions!$C$40)</f>
         <v/>
       </c>
@@ -6657,7 +6738,7 @@
         </is>
       </c>
       <c r="B36" s="13" t="n"/>
-      <c r="C36" s="32">
+      <c r="C36" s="33">
         <f>C31*C35*DCF!$C$61-Assumptions!$C$49</f>
         <v/>
       </c>
@@ -6667,11 +6748,11 @@
         </is>
       </c>
       <c r="E36" s="16">
-        <f>((Assumptions!$C$65-0.03)/((DCF!C39+DCF!C49)/2-0.03))*C31*DCF!$C$61-Assumptions!$C$49</f>
+        <f>((Assumptions!$C$71-0.03)/((DCF!C39+DCF!C49)/2-0.03))*C31*DCF!$C$61-Assumptions!$C$49</f>
         <v/>
       </c>
       <c r="F36" s="16">
-        <f>((Assumptions!$C$65+0.02-Assumptions!$C$40)/(DCF!C49-Assumptions!$C$40))*C31*DCF!$C$61-Assumptions!$C$49</f>
+        <f>((Assumptions!$C$71+0.02-Assumptions!$C$40)/(DCF!C49-Assumptions!$C$40))*C31*DCF!$C$61-Assumptions!$C$49</f>
         <v/>
       </c>
     </row>
@@ -6686,7 +6767,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F63"/>
+  <dimension ref="A1:F68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -6835,23 +6916,23 @@
           <t>Less depreciation and amortisation</t>
         </is>
       </c>
-      <c r="B8" s="30">
+      <c r="B8" s="31">
         <f>-B5*Assumptions!$C$27</f>
         <v/>
       </c>
-      <c r="C8" s="30">
+      <c r="C8" s="31">
         <f>-C5*Assumptions!$C$27</f>
         <v/>
       </c>
-      <c r="D8" s="30">
+      <c r="D8" s="31">
         <f>-D5*Assumptions!$C$27</f>
         <v/>
       </c>
-      <c r="E8" s="30">
+      <c r="E8" s="31">
         <f>-E5*Assumptions!$C$27</f>
         <v/>
       </c>
-      <c r="F8" s="30">
+      <c r="F8" s="31">
         <f>-F5*Assumptions!$C$27</f>
         <v/>
       </c>
@@ -6862,23 +6943,23 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B9" s="31">
+      <c r="B9" s="32">
         <f>B6+B8</f>
         <v/>
       </c>
-      <c r="C9" s="31">
+      <c r="C9" s="32">
         <f>C6+C8</f>
         <v/>
       </c>
-      <c r="D9" s="31">
+      <c r="D9" s="32">
         <f>D6+D8</f>
         <v/>
       </c>
-      <c r="E9" s="31">
+      <c r="E9" s="32">
         <f>E6+E8</f>
         <v/>
       </c>
-      <c r="F9" s="31">
+      <c r="F9" s="32">
         <f>F6+F8</f>
         <v/>
       </c>
@@ -6889,23 +6970,23 @@
           <t>NOPAT — EBIT x (1 - 24%)</t>
         </is>
       </c>
-      <c r="B10" s="30">
+      <c r="B10" s="31">
         <f>B9*(1-Assumptions!$C$7)</f>
         <v/>
       </c>
-      <c r="C10" s="30">
+      <c r="C10" s="31">
         <f>C9*(1-Assumptions!$C$7)</f>
         <v/>
       </c>
-      <c r="D10" s="30">
+      <c r="D10" s="31">
         <f>D9*(1-Assumptions!$C$7)</f>
         <v/>
       </c>
-      <c r="E10" s="30">
+      <c r="E10" s="31">
         <f>E9*(1-Assumptions!$C$7)</f>
         <v/>
       </c>
-      <c r="F10" s="30">
+      <c r="F10" s="31">
         <f>F9*(1-Assumptions!$C$7)</f>
         <v/>
       </c>
@@ -6916,23 +6997,23 @@
           <t>Add back depreciation and amortisation</t>
         </is>
       </c>
-      <c r="B11" s="30">
+      <c r="B11" s="31">
         <f>-B8</f>
         <v/>
       </c>
-      <c r="C11" s="30">
+      <c r="C11" s="31">
         <f>-C8</f>
         <v/>
       </c>
-      <c r="D11" s="30">
+      <c r="D11" s="31">
         <f>-D8</f>
         <v/>
       </c>
-      <c r="E11" s="30">
+      <c r="E11" s="31">
         <f>-E8</f>
         <v/>
       </c>
-      <c r="F11" s="30">
+      <c r="F11" s="31">
         <f>-F8</f>
         <v/>
       </c>
@@ -6943,23 +7024,23 @@
           <t>Less capital expenditure</t>
         </is>
       </c>
-      <c r="B12" s="30">
+      <c r="B12" s="31">
         <f>-B5*Assumptions!$B$26</f>
         <v/>
       </c>
-      <c r="C12" s="30">
+      <c r="C12" s="31">
         <f>-C5*Assumptions!$C$26</f>
         <v/>
       </c>
-      <c r="D12" s="30">
+      <c r="D12" s="31">
         <f>-D5*Assumptions!$D$26</f>
         <v/>
       </c>
-      <c r="E12" s="30">
+      <c r="E12" s="31">
         <f>-E5*Assumptions!$E$26</f>
         <v/>
       </c>
-      <c r="F12" s="30">
+      <c r="F12" s="31">
         <f>-F5*Assumptions!$F$26</f>
         <v/>
       </c>
@@ -6970,23 +7051,23 @@
           <t>Less change in working capital</t>
         </is>
       </c>
-      <c r="B13" s="30">
+      <c r="B13" s="31">
         <f>-(B5*Assumptions!$C$25-'Balance Sheet'!D16)</f>
         <v/>
       </c>
-      <c r="C13" s="30">
+      <c r="C13" s="31">
         <f>-(C5-B5)*Assumptions!$C$25</f>
         <v/>
       </c>
-      <c r="D13" s="30">
+      <c r="D13" s="31">
         <f>-(D5-C5)*Assumptions!$C$25</f>
         <v/>
       </c>
-      <c r="E13" s="30">
+      <c r="E13" s="31">
         <f>-(E5-D5)*Assumptions!$C$25</f>
         <v/>
       </c>
-      <c r="F13" s="30">
+      <c r="F13" s="31">
         <f>-(F5-E5)*Assumptions!$C$25</f>
         <v/>
       </c>
@@ -6997,23 +7078,23 @@
           <t>Free cash flow to the firm</t>
         </is>
       </c>
-      <c r="B14" s="31">
+      <c r="B14" s="32">
         <f>B10+B11+B12+B13</f>
         <v/>
       </c>
-      <c r="C14" s="31">
+      <c r="C14" s="32">
         <f>C10+C11+C12+C13</f>
         <v/>
       </c>
-      <c r="D14" s="31">
+      <c r="D14" s="32">
         <f>D10+D11+D12+D13</f>
         <v/>
       </c>
-      <c r="E14" s="31">
+      <c r="E14" s="32">
         <f>E10+E11+E12+E13</f>
         <v/>
       </c>
-      <c r="F14" s="31">
+      <c r="F14" s="32">
         <f>F10+F11+F12+F13</f>
         <v/>
       </c>
@@ -7024,23 +7105,23 @@
           <t>Forward cost of capital</t>
         </is>
       </c>
-      <c r="B15" s="37">
+      <c r="B15" s="38">
         <f>$C$46-($C$46-$C$53)*B57</f>
         <v/>
       </c>
-      <c r="C15" s="37">
+      <c r="C15" s="38">
         <f>$C$46-($C$46-$C$53)*C57</f>
         <v/>
       </c>
-      <c r="D15" s="37">
+      <c r="D15" s="38">
         <f>$C$46-($C$46-$C$53)*D57</f>
         <v/>
       </c>
-      <c r="E15" s="37">
+      <c r="E15" s="38">
         <f>$C$46-($C$46-$C$53)*E57</f>
         <v/>
       </c>
-      <c r="F15" s="37">
+      <c r="F15" s="38">
         <f>$C$46-($C$46-$C$53)*F57</f>
         <v/>
       </c>
@@ -7051,23 +7132,23 @@
           <t>Discount factor</t>
         </is>
       </c>
-      <c r="B16" s="38">
+      <c r="B16" s="39">
         <f>1/(1+B15)</f>
         <v/>
       </c>
-      <c r="C16" s="38">
+      <c r="C16" s="39">
         <f>B16/(1+C15)</f>
         <v/>
       </c>
-      <c r="D16" s="38">
+      <c r="D16" s="39">
         <f>C16/(1+D15)</f>
         <v/>
       </c>
-      <c r="E16" s="38">
+      <c r="E16" s="39">
         <f>D16/(1+E15)</f>
         <v/>
       </c>
-      <c r="F16" s="38">
+      <c r="F16" s="39">
         <f>E16/(1+F15)</f>
         <v/>
       </c>
@@ -7078,23 +7159,23 @@
           <t>Present value of FCFF</t>
         </is>
       </c>
-      <c r="B17" s="31">
+      <c r="B17" s="32">
         <f>B14*B16</f>
         <v/>
       </c>
-      <c r="C17" s="31">
+      <c r="C17" s="32">
         <f>C14*C16</f>
         <v/>
       </c>
-      <c r="D17" s="31">
+      <c r="D17" s="32">
         <f>D14*D16</f>
         <v/>
       </c>
-      <c r="E17" s="31">
+      <c r="E17" s="32">
         <f>E14*E16</f>
         <v/>
       </c>
-      <c r="F17" s="31">
+      <c r="F17" s="32">
         <f>F14*F16</f>
         <v/>
       </c>
@@ -7109,40 +7190,40 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Terminal-year NOPAT grown one year (EGP mn)</t>
-        </is>
-      </c>
-      <c r="C20" s="30">
-        <f>F10*(1+C23)</f>
+          <t>Terminal-year NOPAT — the LAST EXPLICIT year (FY2030), NOT grown (EGP mn)</t>
+        </is>
+      </c>
+      <c r="C20" s="31">
+        <f>F10</f>
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>Terminal return on invested capital</t>
-        </is>
-      </c>
-      <c r="C21" s="17">
-        <f>F10*(1+C23)/'Summary Financials'!I13</f>
+          <t>Add back FY2030 book depreciation and amortisation (EGP mn)</t>
+        </is>
+      </c>
+      <c r="C21" s="31">
+        <f>-F8</f>
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Required reinvestment rate (g / return on capital)</t>
-        </is>
-      </c>
-      <c r="C22" s="9">
-        <f>C23/C21</f>
+          <t>Terminal free cash flow to the firm — C20 + C21 less the capital charge on rows 65-67</t>
+        </is>
+      </c>
+      <c r="C22" s="31">
+        <f>C20+C21+C65+C66+C67</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>Terminal growth</t>
+          <t>Terminal growth (nominal, derived from zero real growth and terminal inflation)</t>
         </is>
       </c>
       <c r="C23" s="17">
@@ -7164,11 +7245,11 @@
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>Terminal value — terminal-year FCFF C20×(1−C22), capitalised (EGP mn)</t>
-        </is>
-      </c>
-      <c r="C25" s="30">
-        <f>C20*(1-C22)/(C24-C23)</f>
+          <t>Terminal value — C22 grown one year and capitalised at (C24 − C23) (EGP mn)</t>
+        </is>
+      </c>
+      <c r="C25" s="31">
+        <f>C22*(1+C23)/(C24-C23)</f>
         <v/>
       </c>
     </row>
@@ -7178,7 +7259,7 @@
           <t>Present value of the five forecast years (EGP mn)</t>
         </is>
       </c>
-      <c r="C26" s="30">
+      <c r="C26" s="31">
         <f>SUM(B17:F17)</f>
         <v/>
       </c>
@@ -7189,7 +7270,7 @@
           <t>Present value of the terminal value (EGP mn)</t>
         </is>
       </c>
-      <c r="C27" s="30">
+      <c r="C27" s="31">
         <f>C25*F16</f>
         <v/>
       </c>
@@ -7211,7 +7292,7 @@
           <t>Enterprise value (EGP mn)</t>
         </is>
       </c>
-      <c r="C29" s="30">
+      <c r="C29" s="31">
         <f>C26+C27</f>
         <v/>
       </c>
@@ -7219,11 +7300,11 @@
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>Equity attributable to shareholders (EGP mn)</t>
+          <t>Equity attributable to ordinary shareholders (EGP mn)</t>
         </is>
       </c>
       <c r="C30" s="19">
-        <f>'SOTP Bridge'!C12</f>
+        <f>'SOTP Bridge'!C13</f>
         <v/>
       </c>
     </row>
@@ -7234,7 +7315,7 @@
         </is>
       </c>
       <c r="B31" s="13" t="n"/>
-      <c r="C31" s="32">
+      <c r="C31" s="33">
         <f>C30/Assumptions!$C$6</f>
         <v/>
       </c>
@@ -7275,7 +7356,7 @@
           <t>Risk-free rate net of the sovereign spread</t>
         </is>
       </c>
-      <c r="C36" s="37">
+      <c r="C36" s="38">
         <f>C34-C35</f>
         <v/>
       </c>
@@ -7286,7 +7367,7 @@
           <t>Beta</t>
         </is>
       </c>
-      <c r="C37" s="39">
+      <c r="C37" s="40">
         <f>Assumptions!$C$33</f>
         <v/>
       </c>
@@ -7308,7 +7389,7 @@
           <t>Cost of equity, explicit window</t>
         </is>
       </c>
-      <c r="C39" s="37">
+      <c r="C39" s="38">
         <f>C36+C37*C38</f>
         <v/>
       </c>
@@ -7330,7 +7411,7 @@
           <t>Cost of debt after tax</t>
         </is>
       </c>
-      <c r="C41" s="37">
+      <c r="C41" s="38">
         <f>C40*(1-Assumptions!$C$7)</f>
         <v/>
       </c>
@@ -7363,7 +7444,7 @@
           <t>Debt weight (net debt / (net debt + market capitalisation))</t>
         </is>
       </c>
-      <c r="C44" s="37">
+      <c r="C44" s="38">
         <f>C43/(C43+C42)</f>
         <v/>
       </c>
@@ -7374,7 +7455,7 @@
           <t>Equity weight</t>
         </is>
       </c>
-      <c r="C45" s="37">
+      <c r="C45" s="38">
         <f>1-C44</f>
         <v/>
       </c>
@@ -7386,7 +7467,7 @@
         </is>
       </c>
       <c r="B46" s="13" t="n"/>
-      <c r="C46" s="40">
+      <c r="C46" s="41">
         <f>C45*C39+C44*C41</f>
         <v/>
       </c>
@@ -7420,7 +7501,7 @@
           <t>Terminal cost of equity</t>
         </is>
       </c>
-      <c r="C49" s="37">
+      <c r="C49" s="38">
         <f>C47+C37*C48</f>
         <v/>
       </c>
@@ -7442,7 +7523,7 @@
           <t>Terminal cost of debt after tax</t>
         </is>
       </c>
-      <c r="C51" s="37">
+      <c r="C51" s="38">
         <f>C50*(1-Assumptions!$C$7)</f>
         <v/>
       </c>
@@ -7465,7 +7546,7 @@
         </is>
       </c>
       <c r="B53" s="13" t="n"/>
-      <c r="C53" s="40">
+      <c r="C53" s="41">
         <f>(1-C52)*C49+C52*C51</f>
         <v/>
       </c>
@@ -7536,23 +7617,23 @@
           <t>Glide fraction — cumulative progress of the easing</t>
         </is>
       </c>
-      <c r="B57" s="37">
+      <c r="B57" s="38">
         <f>($B$56-B56)/($B$56-$F$56)</f>
         <v/>
       </c>
-      <c r="C57" s="37">
+      <c r="C57" s="38">
         <f>($B$56-C56)/($B$56-$F$56)</f>
         <v/>
       </c>
-      <c r="D57" s="37">
+      <c r="D57" s="38">
         <f>($B$56-D56)/($B$56-$F$56)</f>
         <v/>
       </c>
-      <c r="E57" s="37">
+      <c r="E57" s="38">
         <f>($B$56-E56)/($B$56-$F$56)</f>
         <v/>
       </c>
-      <c r="F57" s="37">
+      <c r="F57" s="38">
         <f>($B$56-F56)/($B$56-$F$56)</f>
         <v/>
       </c>
@@ -7577,7 +7658,7 @@
           <t>Anchor accretion factor — (1 + cost of equity)^(days to anchor / 365)</t>
         </is>
       </c>
-      <c r="C61" s="38">
+      <c r="C61" s="39">
         <f>(1+C39)^(Assumptions!$C$53/365)</f>
         <v/>
       </c>
@@ -7585,11 +7666,11 @@
     <row r="62">
       <c r="A62" s="13" t="inlineStr">
         <is>
-          <t>Fair value per share at the 5-Aug-2026 anchor (EGP)</t>
+          <t>Fair value per share at the 3-Sep-2026 anchor (EGP)</t>
         </is>
       </c>
       <c r="B62" s="13" t="n"/>
-      <c r="C62" s="32">
+      <c r="C62" s="33">
         <f>C31*C61-Assumptions!$C$49</f>
         <v/>
       </c>
@@ -7600,6 +7681,57 @@
         <is>
           <t>The bridge on row 31 is dated 31-Dec-2025 (the audited balance-sheet date it subtracts net debt at). Row 62 rolls it to the anchor at the cost of equity, net of the EGP 1.85 FY2025 dividend paid in the window. Every lens on every sheet is rolled the same way.</t>
         </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="15" t="inlineStr">
+        <is>
+          <t>THE TERMINAL'S CAPITAL CHARGE — MAINTENANCE AT CURRENT COST, NEVER g x IC</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="6" t="inlineStr">
+        <is>
+          <t>Less maintenance capital at current replacement cost — FY2030 book depreciation escalated over half the DISCLOSED useful life</t>
+        </is>
+      </c>
+      <c r="C65" s="19">
+        <f>F8*(1+Assumptions!$C$56)^(Assumptions!$C$57/2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t>Less capital for real growth — zero, because the stated real growth is zero</t>
+        </is>
+      </c>
+      <c r="C66" s="31">
+        <f>0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="6" t="inlineStr">
+        <is>
+          <t>Less inflation on the terminal working-capital base</t>
+        </is>
+      </c>
+      <c r="C67" s="19">
+        <f>-Assumptions!$C$58*Assumptions!$C$56</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>Terminal return on invested capital (disclosure — it drives nothing here; the retired construction that used it charged g x IC every year for ever, which reads as replacing the whole asset base every 1/g years and is a fact about the inflation rate rather than about the asset)</t>
+        </is>
+      </c>
+      <c r="C68" s="9">
+        <f>F10*(1+C23)/'Summary Financials'!I13</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -7702,32 +7834,32 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B5" s="31" t="n">
+      <c r="B5" s="32" t="n">
         <v>152186.247545</v>
       </c>
-      <c r="C5" s="31" t="n">
+      <c r="C5" s="32" t="n">
         <v>231981.835577</v>
       </c>
-      <c r="D5" s="31" t="n">
+      <c r="D5" s="32" t="n">
         <v>281049.081719</v>
       </c>
-      <c r="E5" s="31">
+      <c r="E5" s="32">
         <f>DCF!B5</f>
         <v/>
       </c>
-      <c r="F5" s="31">
+      <c r="F5" s="32">
         <f>DCF!C5</f>
         <v/>
       </c>
-      <c r="G5" s="31">
+      <c r="G5" s="32">
         <f>DCF!D5</f>
         <v/>
       </c>
-      <c r="H5" s="31">
+      <c r="H5" s="32">
         <f>DCF!E5</f>
         <v/>
       </c>
-      <c r="I5" s="31">
+      <c r="I5" s="32">
         <f>DCF!F5</f>
         <v/>
       </c>
@@ -7774,32 +7906,32 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B7" s="31" t="n">
+      <c r="B7" s="32" t="n">
         <v>20035.105205</v>
       </c>
-      <c r="C7" s="31" t="n">
+      <c r="C7" s="32" t="n">
         <v>31601.46495</v>
       </c>
-      <c r="D7" s="31" t="n">
+      <c r="D7" s="32" t="n">
         <v>28363.203246</v>
       </c>
-      <c r="E7" s="31">
+      <c r="E7" s="32">
         <f>DCF!B6</f>
         <v/>
       </c>
-      <c r="F7" s="31">
+      <c r="F7" s="32">
         <f>DCF!C6</f>
         <v/>
       </c>
-      <c r="G7" s="31">
+      <c r="G7" s="32">
         <f>DCF!D6</f>
         <v/>
       </c>
-      <c r="H7" s="31">
+      <c r="H7" s="32">
         <f>DCF!E6</f>
         <v/>
       </c>
-      <c r="I7" s="31">
+      <c r="I7" s="32">
         <f>DCF!F6</f>
         <v/>
       </c>
@@ -7885,35 +8017,35 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B10" s="31">
+      <c r="B10" s="32">
         <f>B7+B9</f>
         <v/>
       </c>
-      <c r="C10" s="31">
+      <c r="C10" s="32">
         <f>C7+C9</f>
         <v/>
       </c>
-      <c r="D10" s="31">
+      <c r="D10" s="32">
         <f>D7+D9</f>
         <v/>
       </c>
-      <c r="E10" s="31">
+      <c r="E10" s="32">
         <f>E7+E9</f>
         <v/>
       </c>
-      <c r="F10" s="31">
+      <c r="F10" s="32">
         <f>F7+F9</f>
         <v/>
       </c>
-      <c r="G10" s="31">
+      <c r="G10" s="32">
         <f>G7+G9</f>
         <v/>
       </c>
-      <c r="H10" s="31">
+      <c r="H10" s="32">
         <f>H7+H9</f>
         <v/>
       </c>
-      <c r="I10" s="31">
+      <c r="I10" s="32">
         <f>I7+I9</f>
         <v/>
       </c>
@@ -7933,23 +8065,23 @@
       <c r="D11" s="24" t="n">
         <v>-2145.438755</v>
       </c>
-      <c r="E11" s="30">
+      <c r="E11" s="31">
         <f>-(Assumptions!$B$35*'Balance Sheet'!$D$11-Assumptions!$C$52*MAX('Balance Sheet'!$D$11-'Balance Sheet'!D17,0))</f>
         <v/>
       </c>
-      <c r="F11" s="30">
+      <c r="F11" s="31">
         <f>-(Assumptions!$C$35*'Balance Sheet'!$D$11-Assumptions!$C$52*MAX('Balance Sheet'!$D$11-'Balance Sheet'!E17,0))</f>
         <v/>
       </c>
-      <c r="G11" s="30">
+      <c r="G11" s="31">
         <f>-(Assumptions!$D$35*'Balance Sheet'!$D$11-Assumptions!$C$52*MAX('Balance Sheet'!$D$11-'Balance Sheet'!F17,0))</f>
         <v/>
       </c>
-      <c r="H11" s="30">
+      <c r="H11" s="31">
         <f>-(Assumptions!$E$35*'Balance Sheet'!$D$11-Assumptions!$C$52*MAX('Balance Sheet'!$D$11-'Balance Sheet'!G17,0))</f>
         <v/>
       </c>
-      <c r="I11" s="30">
+      <c r="I11" s="31">
         <f>-(Assumptions!$F$35*'Balance Sheet'!$D$11-Assumptions!$C$52*MAX('Balance Sheet'!$D$11-'Balance Sheet'!H17,0))</f>
         <v/>
       </c>
@@ -7969,23 +8101,23 @@
       <c r="D12" s="24" t="n">
         <v>1568.902975</v>
       </c>
-      <c r="E12" s="30">
+      <c r="E12" s="31">
         <f>D12*(1+Assumptions!$C$51)</f>
         <v/>
       </c>
-      <c r="F12" s="30">
+      <c r="F12" s="31">
         <f>E12*(1+Assumptions!$C$51)</f>
         <v/>
       </c>
-      <c r="G12" s="30">
+      <c r="G12" s="31">
         <f>F12*(1+Assumptions!$C$51)</f>
         <v/>
       </c>
-      <c r="H12" s="30">
+      <c r="H12" s="31">
         <f>G12*(1+Assumptions!$C$51)</f>
         <v/>
       </c>
-      <c r="I12" s="30">
+      <c r="I12" s="31">
         <f>H12*(1+Assumptions!$C$51)</f>
         <v/>
       </c>
@@ -7996,35 +8128,35 @@
           <t>Profit before tax</t>
         </is>
       </c>
-      <c r="B13" s="30">
+      <c r="B13" s="31">
         <f>B10+B11+B12</f>
         <v/>
       </c>
-      <c r="C13" s="30">
+      <c r="C13" s="31">
         <f>C10+C11+C12</f>
         <v/>
       </c>
-      <c r="D13" s="30">
+      <c r="D13" s="31">
         <f>D10+D11+D12</f>
         <v/>
       </c>
-      <c r="E13" s="30">
+      <c r="E13" s="31">
         <f>E10+E11+E12</f>
         <v/>
       </c>
-      <c r="F13" s="30">
+      <c r="F13" s="31">
         <f>F10+F11+F12</f>
         <v/>
       </c>
-      <c r="G13" s="30">
+      <c r="G13" s="31">
         <f>G10+G11+G12</f>
         <v/>
       </c>
-      <c r="H13" s="30">
+      <c r="H13" s="31">
         <f>H10+H11+H12</f>
         <v/>
       </c>
-      <c r="I13" s="30">
+      <c r="I13" s="31">
         <f>I10+I11+I12</f>
         <v/>
       </c>
@@ -8044,23 +8176,23 @@
       <c r="D14" s="24" t="n">
         <v>-5591.139782</v>
       </c>
-      <c r="E14" s="30">
+      <c r="E14" s="31">
         <f>-E13*Assumptions!$C$7</f>
         <v/>
       </c>
-      <c r="F14" s="30">
+      <c r="F14" s="31">
         <f>-F13*Assumptions!$C$7</f>
         <v/>
       </c>
-      <c r="G14" s="30">
+      <c r="G14" s="31">
         <f>-G13*Assumptions!$C$7</f>
         <v/>
       </c>
-      <c r="H14" s="30">
+      <c r="H14" s="31">
         <f>-H13*Assumptions!$C$7</f>
         <v/>
       </c>
-      <c r="I14" s="30">
+      <c r="I14" s="31">
         <f>-I13*Assumptions!$C$7</f>
         <v/>
       </c>
@@ -8080,23 +8212,23 @@
       <c r="D15" s="24" t="n">
         <v>19186.550057</v>
       </c>
-      <c r="E15" s="30">
+      <c r="E15" s="31">
         <f>E13+E14</f>
         <v/>
       </c>
-      <c r="F15" s="30">
+      <c r="F15" s="31">
         <f>F13+F14</f>
         <v/>
       </c>
-      <c r="G15" s="30">
+      <c r="G15" s="31">
         <f>G13+G14</f>
         <v/>
       </c>
-      <c r="H15" s="30">
+      <c r="H15" s="31">
         <f>H13+H14</f>
         <v/>
       </c>
-      <c r="I15" s="30">
+      <c r="I15" s="31">
         <f>I13+I14</f>
         <v/>
       </c>
@@ -8116,24 +8248,24 @@
       <c r="D16" s="24" t="n">
         <v>-1856.305067000001</v>
       </c>
-      <c r="E16" s="30">
-        <f>-E15*'SOTP Bridge'!$C$15</f>
-        <v/>
-      </c>
-      <c r="F16" s="30">
-        <f>-F15*'SOTP Bridge'!$C$15</f>
-        <v/>
-      </c>
-      <c r="G16" s="30">
-        <f>-G15*'SOTP Bridge'!$C$15</f>
-        <v/>
-      </c>
-      <c r="H16" s="30">
-        <f>-H15*'SOTP Bridge'!$C$15</f>
-        <v/>
-      </c>
-      <c r="I16" s="30">
-        <f>-I15*'SOTP Bridge'!$C$15</f>
+      <c r="E16" s="31">
+        <f>-E15*'SOTP Bridge'!$C$17</f>
+        <v/>
+      </c>
+      <c r="F16" s="31">
+        <f>-F15*'SOTP Bridge'!$C$17</f>
+        <v/>
+      </c>
+      <c r="G16" s="31">
+        <f>-G15*'SOTP Bridge'!$C$17</f>
+        <v/>
+      </c>
+      <c r="H16" s="31">
+        <f>-H15*'SOTP Bridge'!$C$17</f>
+        <v/>
+      </c>
+      <c r="I16" s="31">
+        <f>-I15*'SOTP Bridge'!$C$17</f>
         <v/>
       </c>
     </row>
@@ -8143,32 +8275,32 @@
           <t>Profit attributable to shareholders</t>
         </is>
       </c>
-      <c r="B17" s="31" t="n">
+      <c r="B17" s="32" t="n">
         <v>10115.701777</v>
       </c>
-      <c r="C17" s="31" t="n">
+      <c r="C17" s="32" t="n">
         <v>17461.358714</v>
       </c>
-      <c r="D17" s="31" t="n">
+      <c r="D17" s="32" t="n">
         <v>17330.24499</v>
       </c>
-      <c r="E17" s="31">
+      <c r="E17" s="32">
         <f>E15+E16</f>
         <v/>
       </c>
-      <c r="F17" s="31">
+      <c r="F17" s="32">
         <f>F15+F16</f>
         <v/>
       </c>
-      <c r="G17" s="31">
+      <c r="G17" s="32">
         <f>G15+G16</f>
         <v/>
       </c>
-      <c r="H17" s="31">
+      <c r="H17" s="32">
         <f>H15+H16</f>
         <v/>
       </c>
-      <c r="I17" s="31">
+      <c r="I17" s="32">
         <f>I15+I16</f>
         <v/>
       </c>

--- a/engine/swdy_study/SWDY_Valuation_Model_05082026_public.xlsx
+++ b/engine/swdy_study/SWDY_Valuation_Model_05082026_public.xlsx
@@ -808,7 +808,7 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>26.9% -&gt; 15.9% on the same easing calendar as the interest forecast; the terminal value is</t>
+          <t>28.8% -&gt; 17.2% on the same easing calendar as the interest forecast; the terminal value is</t>
         </is>
       </c>
     </row>
@@ -2556,111 +2556,111 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>15.2%</t>
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>64.92380553045649</v>
+        <v>54.89390300698878</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>67.81454330477681</v>
+        <v>56.76608049282878</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>71.2657550153391</v>
+        <v>58.9328825766538</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>75.48936116950645</v>
+        <v>61.49018601091854</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>80.81952864869957</v>
+        <v>64.58052940682644</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>14.9%</t>
+          <t>16.2%</t>
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>58.18280778459938</v>
+        <v>49.59394363429544</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>60.28097444263505</v>
+        <v>50.95326657112403</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>62.7254596302354</v>
+        <v>52.49104063008191</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>65.6325529341344</v>
+        <v>54.25965459765457</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>69.17717086762013</v>
+        <v>56.33422840926579</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>17.2%</t>
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>52.49799810153853</v>
+        <v>45.05103667309857</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>54.02258879276857</v>
+        <v>46.03042217002906</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>55.75852138598012</v>
+        <v>47.11281563256473</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>57.76961833972243</v>
+        <v>48.32576211063959</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>60.14827652865958</v>
+        <v>49.7075887045515</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>16.9%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>47.64148809789273</v>
+        <v>41.11553668357441</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>48.74316174823518</v>
+        <v>41.8093978775642</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>49.96902514555856</v>
+        <v>42.55648627630665</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>51.3531520126963</v>
+        <v>43.36987034045674</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>52.94333582385958</v>
+        <v>44.26727799429032</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>19.2%</t>
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>43.44644775731468</v>
+        <v>37.67472174247933</v>
       </c>
       <c r="C10" s="7" t="n">
-        <v>44.23152271678764</v>
+        <v>38.15151148948571</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>45.08351233414617</v>
+        <v>38.648345329237</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>46.01923749436355</v>
+        <v>39.16977223986016</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>47.06167257131559</v>
+        <v>39.72183036633324</v>
       </c>
     </row>
     <row r="12">
@@ -2674,138 +2674,138 @@
       <c r="A13" s="5" t="inlineStr"/>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>23.9%</t>
+          <t>25.8%</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>25.4%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>28.8%</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>28.4%</t>
+          <t>30.3%</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>29.9%</t>
+          <t>31.8%</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>terminal 13.9%</t>
+          <t>terminal 15.2%</t>
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>85.84545509208399</v>
+        <v>68.64247049591957</v>
       </c>
       <c r="C14" s="7" t="n">
-        <v>83.28726331486288</v>
+        <v>66.57546829677946</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>80.81952864869957</v>
+        <v>64.58052940682644</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>78.43825692508688</v>
+        <v>62.65451643723234</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>76.13966662860086</v>
+        <v>60.79445670792633</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>terminal 14.9%</t>
+          <t>terminal 16.2%</t>
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>73.5404678355972</v>
+        <v>59.93237666911776</v>
       </c>
       <c r="C15" s="7" t="n">
-        <v>71.31963462621358</v>
+        <v>58.10144964510826</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>69.17717086762013</v>
+        <v>56.33422840926579</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>67.10962173729665</v>
+        <v>54.62794387184755</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>65.11371611583073</v>
+        <v>52.9799721331991</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>terminal 15.9%</t>
+          <t>terminal 17.2%</t>
         </is>
       </c>
       <c r="B16" s="7" t="n">
-        <v>63.99790976465807</v>
+        <v>52.93321441251824</v>
       </c>
       <c r="C16" s="7" t="n">
-        <v>62.03859171613212</v>
+        <v>51.2919036374145</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>60.14827652865958</v>
+        <v>49.7075887045515</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>58.32392716970243</v>
+        <v>48.17779610598239</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>56.56266789121253</v>
+        <v>46.70018186414503</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>terminal 16.9%</t>
+          <t>terminal 18.2%</t>
         </is>
       </c>
       <c r="B17" s="7" t="n">
-        <v>56.3832632823887</v>
+        <v>47.18722756407969</v>
       </c>
       <c r="C17" s="7" t="n">
-        <v>54.63253200536953</v>
+        <v>45.70150653374164</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>52.94333582385958</v>
+        <v>44.26727799429032</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>51.31297067571722</v>
+        <v>42.88231076920474</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>49.73887592188827</v>
+        <v>41.54449037834811</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>terminal 17.9%</t>
+          <t>terminal 19.2%</t>
         </is>
       </c>
       <c r="B18" s="7" t="n">
-        <v>50.16731028865568</v>
+        <v>42.38652255248041</v>
       </c>
       <c r="C18" s="7" t="n">
-        <v>48.58676906627794</v>
+        <v>41.03072689368742</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>47.06167257131559</v>
+        <v>39.72183036633324</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>45.58958818858307</v>
+        <v>38.45780396819539</v>
       </c>
       <c r="F18" s="7" t="n">
-        <v>44.16821216991782</v>
+        <v>37.23672469018629</v>
       </c>
     </row>
     <row r="20">
@@ -2836,23 +2836,23 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Beta  (0.60 / 0.80 / 1.01 / 1.15 / 1.30)</t>
+          <t>Beta  (0.60 / 0.80 / 1.23 / 1.15 / 1.30)</t>
         </is>
       </c>
       <c r="B22" s="7" t="n">
-        <v>93.45277355246162</v>
+        <v>94.46647146810956</v>
       </c>
       <c r="C22" s="7" t="n">
-        <v>74.44674244752112</v>
+        <v>75.25828072607085</v>
       </c>
       <c r="D22" s="7" t="n">
-        <v>60.14827652865958</v>
+        <v>49.70341773987482</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>52.63301422037497</v>
+        <v>53.21252849781632</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>45.99373037705359</v>
+        <v>46.50262521769896</v>
       </c>
       <c r="H22" s="16">
         <f>MAX(B22:F22)-MIN(B22:F22)</f>
@@ -2866,19 +2866,19 @@
         </is>
       </c>
       <c r="B23" s="7" t="n">
-        <v>50.79365382947766</v>
+        <v>42.07500523515485</v>
       </c>
       <c r="C23" s="7" t="n">
-        <v>52.69688996099238</v>
+        <v>43.51076338157681</v>
       </c>
       <c r="D23" s="7" t="n">
-        <v>56.50336222402186</v>
+        <v>46.38227967442072</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>61.26145255280872</v>
+        <v>49.97167504047564</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>66.01954288159557</v>
+        <v>53.56107040653055</v>
       </c>
       <c r="H23" s="16">
         <f>MAX(B23:F23)-MIN(B23:F23)</f>
@@ -2892,19 +2892,19 @@
         </is>
       </c>
       <c r="B24" s="7" t="n">
-        <v>29.48174706762489</v>
+        <v>23.17689166022818</v>
       </c>
       <c r="C24" s="7" t="n">
-        <v>41.08931851430866</v>
+        <v>33.3438275209025</v>
       </c>
       <c r="D24" s="7" t="n">
-        <v>52.69688996099238</v>
+        <v>43.51076338157681</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>64.30446140767616</v>
+        <v>53.67769924225113</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>75.91203285435989</v>
+        <v>63.84463510292543</v>
       </c>
       <c r="H24" s="16">
         <f>MAX(B24:F24)-MIN(B24:F24)</f>
@@ -2918,19 +2918,19 @@
         </is>
       </c>
       <c r="B25" s="7" t="n">
-        <v>49.8420357637203</v>
+        <v>41.3571261619439</v>
       </c>
       <c r="C25" s="7" t="n">
-        <v>51.26946286235632</v>
+        <v>42.43394477176034</v>
       </c>
       <c r="D25" s="7" t="n">
-        <v>52.69688996099238</v>
+        <v>43.51076338157681</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>54.12431705962842</v>
+        <v>44.58758199139326</v>
       </c>
       <c r="F25" s="7" t="n">
-        <v>55.55174415826449</v>
+        <v>45.66440060120974</v>
       </c>
       <c r="H25" s="16">
         <f>MAX(B25:F25)-MIN(B25:F25)</f>
@@ -2944,19 +2944,19 @@
         </is>
       </c>
       <c r="B26" s="7" t="n">
-        <v>59.90563209825564</v>
+        <v>50.27171997464177</v>
       </c>
       <c r="C26" s="7" t="n">
-        <v>56.17697237208499</v>
+        <v>46.77467346098749</v>
       </c>
       <c r="D26" s="7" t="n">
-        <v>52.69688996099238</v>
+        <v>43.51076338157681</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>48.71965291974369</v>
+        <v>39.7805804336789</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>44.99099319357304</v>
+        <v>36.28353392002459</v>
       </c>
       <c r="H26" s="16">
         <f>MAX(B26:F26)-MIN(B26:F26)</f>
@@ -2970,19 +2970,19 @@
         </is>
       </c>
       <c r="B27" s="7" t="n">
-        <v>49.62272921986233</v>
+        <v>40.98127111072365</v>
       </c>
       <c r="C27" s="7" t="n">
-        <v>56.53511112692783</v>
+        <v>46.71205527626227</v>
       </c>
       <c r="D27" s="7" t="n">
-        <v>60.14827652865958</v>
+        <v>49.7075887045515</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>67.16954483010554</v>
+        <v>55.52864630016783</v>
       </c>
       <c r="F27" s="7" t="n">
-        <v>70.35987494105883</v>
+        <v>58.17362360733951</v>
       </c>
       <c r="H27" s="16">
         <f>MAX(B27:F27)-MIN(B27:F27)</f>
@@ -2996,19 +2996,19 @@
         </is>
       </c>
       <c r="B28" s="7" t="n">
-        <v>52.49799810153853</v>
+        <v>45.05103667309857</v>
       </c>
       <c r="C28" s="7" t="n">
-        <v>54.02258879276857</v>
+        <v>46.03042217002906</v>
       </c>
       <c r="D28" s="7" t="n">
-        <v>55.75852138598012</v>
+        <v>47.11281563256473</v>
       </c>
       <c r="E28" s="7" t="n">
-        <v>57.76961833972243</v>
+        <v>48.32576211063959</v>
       </c>
       <c r="F28" s="7" t="n">
-        <v>60.14827652865958</v>
+        <v>49.7075887045515</v>
       </c>
       <c r="H28" s="16">
         <f>MAX(B28:F28)-MIN(B28:F28)</f>
@@ -4015,14 +4015,14 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>19.63802419176771</v>
+        <v>16.18162005664932</v>
       </c>
       <c r="C5" s="8">
         <f>DCF!C62</f>
         <v/>
       </c>
       <c r="D5" s="7" t="n">
-        <v>101.3067584343183</v>
+        <v>83.79876343050132</v>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
@@ -4428,7 +4428,7 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>19.63802419176771</v>
+        <v>16.18162005664932</v>
       </c>
     </row>
     <row r="7">
@@ -4443,7 +4443,7 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>101.3067584343183</v>
+        <v>83.79876343050132</v>
       </c>
     </row>
     <row r="8">
@@ -4531,7 +4531,7 @@
       </c>
       <c r="C16" s="22" t="inlineStr">
         <is>
-          <t>26.9% → 15.9%</t>
+          <t>28.8% → 17.2%</t>
         </is>
       </c>
     </row>
@@ -4553,7 +4553,7 @@
         </is>
       </c>
       <c r="C18" s="7" t="n">
-        <v>70.84778269949645</v>
+        <v>57.86095793273499</v>
       </c>
     </row>
     <row r="19">
@@ -4613,13 +4613,13 @@
         </is>
       </c>
       <c r="C23" s="7" t="n">
-        <v>151.4223547712553</v>
+        <v>153.052652198775</v>
       </c>
       <c r="D23" s="7" t="n">
-        <v>111.0875245682934</v>
+        <v>112.2887963569921</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>191.7571849742172</v>
+        <v>193.8165080405579</v>
       </c>
     </row>
     <row r="24">
@@ -4634,13 +4634,13 @@
         </is>
       </c>
       <c r="C24" s="7" t="n">
-        <v>74.30796795435184</v>
+        <v>65.48394099946414</v>
       </c>
       <c r="D24" s="7" t="n">
-        <v>36.90047424542561</v>
+        <v>34.12367903228015</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>67.07141566856639</v>
+        <v>59.75270243066323</v>
       </c>
     </row>
     <row r="25">
@@ -4655,13 +4655,13 @@
         </is>
       </c>
       <c r="C25" s="7" t="n">
-        <v>55.21683864604976</v>
+        <v>45.28950840983638</v>
       </c>
       <c r="D25" s="7" t="n">
-        <v>47.64716300797847</v>
+        <v>42.22747080432825</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>70.84778269949645</v>
+        <v>57.86095793273499</v>
       </c>
     </row>
     <row r="26">
@@ -5152,7 +5152,7 @@
         </is>
       </c>
       <c r="C33" s="26" t="n">
-        <v>1.009</v>
+        <v>1.224906574047969</v>
       </c>
     </row>
     <row r="34">
